--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -18,7 +18,8 @@
     <sheet name="BalanceSheet" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Funding" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Valuation" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Check" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Research" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Check" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +35,7 @@
     <numFmt numFmtId="167" formatCode="#,##0;[Red](#,##0)"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -144,6 +145,46 @@
     <font>
       <i val="1"/>
       <color rgb="006B7480"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E9C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E7A3C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B3272D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B3272D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -259,7 +300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -328,6 +369,34 @@
     <xf numFmtId="164" fontId="7" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="17" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="17" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="16" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -696,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -870,137 +939,144 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Drivers        athletes and fans, including monthly cohort churn</t>
+          <t xml:space="preserve">  Research       how each assumption was baselined, with sources</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Revenue        GMV and net revenue, stream by stream</t>
+          <t xml:space="preserve">  Drivers        athletes and fans, including monthly cohort churn</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Costs          COGS and operating costs, line by line</t>
+          <t xml:space="preserve">  Revenue        GMV and net revenue, stream by stream</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  P&amp;L            income statement</t>
+          <t xml:space="preserve">  Costs          COGS and operating costs, line by line</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  WorkingCap     receivables, payables, athlete float, capex, D&amp;A</t>
+          <t xml:space="preserve">  P&amp;L            income statement</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CashFlow       indirect method, tying to closing cash</t>
+          <t xml:space="preserve">  WorkingCap     receivables, payables, athlete float, capex, D&amp;A</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  BalanceSheet   with an explicit balance check row</t>
+          <t xml:space="preserve">  CashFlow       indirect method, tying to closing cash</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Valuation      DCF, NPV, IRR, exit multiples, sensitivity</t>
+          <t xml:space="preserve">  BalanceSheet   with an explicit balance check row</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Funding        rounds, dilution, ownership</t>
+          <t xml:space="preserve">  Valuation      DCF, NPV, IRR, exit multiples, sensitivity</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Funding        rounds, dilution, ownership</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Check          the Python model's figures, to verify the formulas agree</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-    </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>WHY TEN YEARS</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>At Y7 the business is still compounding above 50%, so a terminal value placed</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>there does most of the valuation work and does it badly. Ten years lets growth</t>
+          <t>At Y7 the business is still compounding above 50%, so a terminal value placed</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>there does most of the valuation work and does it badly. Ten years lets growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>decelerate inside the explicit forecast, where it can be argued with.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-    </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>MODEL SHAPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>This is a target-driven model: athlete counts are the plan, and marketing spend</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>is derived from them at segment CAC. It is not a driver-driven model in which</t>
+          <t>This is a target-driven model: athlete counts are the plan, and marketing spend</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>spend produces athletes. That is the normal shape for a plan, but it means the</t>
+          <t>is derived from them at segment CAC. It is not a driver-driven model in which</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
+        <is>
+          <t>spend produces athletes. That is the normal shape for a plan, but it means the</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>athlete trajectory is an assumption to defend, not an output to trust.</t>
         </is>
@@ -2089,6 +2165,1232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Research &amp; Benchmarking - where every assumption came from</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="55" t="inlineStr">
+        <is>
+          <t>SOURCED = published figure | BENCHMARKED = set against named comparables | DERIVED = computed from other assumptions | ESTIMATE = judgement, no benchmark yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="56" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B4" s="56" t="inlineStr">
+        <is>
+          <t>Model value</t>
+        </is>
+      </c>
+      <c r="C4" s="56" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D4" s="56" t="inlineStr">
+        <is>
+          <t>Benchmark / comparable</t>
+        </is>
+      </c>
+      <c r="E4" s="56" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F4" s="56" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="G4" s="56" t="inlineStr">
+        <is>
+          <t>What would replace the estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>— PRICING &amp; TAKE RATE —</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="57" t="inlineStr">
+        <is>
+          <t>Take rate on fan revenue</t>
+        </is>
+      </c>
+      <c r="B6" s="31">
+        <f>Assumptions!$C$37</f>
+        <v/>
+      </c>
+      <c r="C6" s="58" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
+        </is>
+      </c>
+      <c r="D6" s="59" t="inlineStr">
+        <is>
+          <t>Passes charges 10% but adds $0.30/txn and a $29/month creator fee; OnlyFans, Fansly and Fanfix are all 20%; Patreon 8-12%. A flat 15% with no monthly fee pays an athlete more than Passes for anyone under EUR 1,380/month of fan revenue.</t>
+        </is>
+      </c>
+      <c r="E6" s="59" t="inlineStr">
+        <is>
+          <t>Sacra company profile (Passes); Passes rebrand release, Apr 2026; MEXC platform comparison 2026</t>
+        </is>
+      </c>
+      <c r="F6" s="60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G6" s="59" t="inlineStr">
+        <is>
+          <t>Nothing. This is a pricing decision and the comparables are public.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="57" t="inlineStr">
+        <is>
+          <t>Take rate on sponsorship</t>
+        </is>
+      </c>
+      <c r="B7" s="31">
+        <f>Assumptions!$C$38</f>
+        <v/>
+      </c>
+      <c r="C7" s="58" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
+        </is>
+      </c>
+      <c r="D7" s="59" t="inlineStr">
+        <is>
+          <t>Sports agents take 10-20% of an endorsement and 4-10% of a playing contract. On OnlyFans, management agencies take a further 20-50% on top of the platform's 20%.</t>
+        </is>
+      </c>
+      <c r="E7" s="59" t="inlineStr">
+        <is>
+          <t>Oreate and Sapling agent-commission surveys; Aruna Talent agency rate guide 2026</t>
+        </is>
+      </c>
+      <c r="F7" s="60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G7" s="59" t="inlineStr">
+        <is>
+          <t>Observed deal data once the marketplace is running.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="57" t="inlineStr">
+        <is>
+          <t>Suggested tiers 4.99 / 9.99 / 24.99</t>
+        </is>
+      </c>
+      <c r="B8" s="61" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
+      </c>
+      <c r="C8" s="58" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
+        </is>
+      </c>
+      <c r="D8" s="59" t="inlineStr">
+        <is>
+          <t>Patreon's typical patronage is quoted at $8-12/month, so the EUR 9.99 anchor sits inside the observed band. EUR 4.99 retains only 54% of our take after payment fees, against 71% at EUR 9.99 — which is why the floor matters more than the take rate.</t>
+        </is>
+      </c>
+      <c r="E8" s="59" t="inlineStr">
+        <is>
+          <t>Patreon 2024 Transparency Report; independent audits of ~1,200 creators</t>
+        </is>
+      </c>
+      <c r="F8" s="62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G8" s="59" t="inlineStr">
+        <is>
+          <t>Our own tier mix after P1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="57" t="inlineStr">
+        <is>
+          <t>Season pass / annual billing</t>
+        </is>
+      </c>
+      <c r="B9" s="61" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
+      </c>
+      <c r="C9" s="63" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D9" s="59" t="inlineStr">
+        <is>
+          <t>Patreon reports that annual patrons churn at ONE THIRD the rate of monthly patrons. This is the single strongest piece of evidence in the plan for pushing annual billing.</t>
+        </is>
+      </c>
+      <c r="E9" s="59" t="inlineStr">
+        <is>
+          <t>Patreon 2024 Transparency Report</t>
+        </is>
+      </c>
+      <c r="F9" s="60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G9" s="59" t="inlineStr">
+        <is>
+          <t>Already strong. Confirm on our own cohorts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>— FAN ECONOMICS —</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="57" t="inlineStr">
+        <is>
+          <t>Fan ARPU per month</t>
+        </is>
+      </c>
+      <c r="B11" s="31">
+        <f>Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="C11" s="58" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
+        </is>
+      </c>
+      <c r="D11" s="59" t="inlineStr">
+        <is>
+          <t>Patreon's average monthly support rose from $5.40 to $6.10 during 2024, with typical patronage quoted at $8-12. Our EUR 8.00-9.50 sits in the upper-middle of that range.</t>
+        </is>
+      </c>
+      <c r="E11" s="59" t="inlineStr">
+        <is>
+          <t>Patreon 2024 Transparency Report</t>
+        </is>
+      </c>
+      <c r="F11" s="62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G11" s="59" t="inlineStr">
+        <is>
+          <t>Actual ARPU by tier and sport after P1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="57" t="inlineStr">
+        <is>
+          <t>Fan churn per month</t>
+        </is>
+      </c>
+      <c r="B12" s="31">
+        <f>Assumptions!$C$12</f>
+        <v/>
+      </c>
+      <c r="C12" s="64" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="D12" s="59" t="inlineStr">
+        <is>
+          <t>OPTIMISTIC AGAINST BENCHMARK. Patreon runs 10-15% monthly. We assume 6-9% (niche) and 9-13% (popular), arguing that training content is habitual and that competitive seasons create natural renewal moments. That argument is currently untested.</t>
+        </is>
+      </c>
+      <c r="E12" s="59" t="inlineStr">
+        <is>
+          <t>Patreon 2024 Transparency Report (10-15%/month)</t>
+        </is>
+      </c>
+      <c r="F12" s="65" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G12" s="59" t="inlineStr">
+        <is>
+          <t>THE most important number to measure in P1. Three months of real cohorts settles it. Until then the conservative case should be treated as the plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="57" t="inlineStr">
+        <is>
+          <t>Paying fans per monetising athlete</t>
+        </is>
+      </c>
+      <c r="B13" s="31">
+        <f>Assumptions!$C$10</f>
+        <v/>
+      </c>
+      <c r="C13" s="66" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D13" s="59" t="inlineStr">
+        <is>
+          <t>20 rising to 48 over ten years. Cross-check: Patreon creators average $350/month and our modelled niche athlete at maturity earns about EUR 313/month — closely aligned, which is reassuring for an assumption built bottom-up rather than from a comparable.</t>
+        </is>
+      </c>
+      <c r="E13" s="59" t="inlineStr">
+        <is>
+          <t>Patreon 2024 Transparency Report (creator average $350/month)</t>
+        </is>
+      </c>
+      <c r="F13" s="62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G13" s="59" t="inlineStr">
+        <is>
+          <t>Observed fans per athlete, banded by follower count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="57" t="inlineStr">
+        <is>
+          <t>Share of athletes who monetise</t>
+        </is>
+      </c>
+      <c r="B14" s="31">
+        <f>Assumptions!$C$9</f>
+        <v/>
+      </c>
+      <c r="C14" s="64" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="D14" s="59" t="inlineStr">
+        <is>
+          <t>28% rising to 50% for niche sports. No direct comparable exists — neither Patreon nor OnlyFans publishes activation rates for creators who sign up but never charge.</t>
+        </is>
+      </c>
+      <c r="E14" s="59" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="F14" s="65" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G14" s="59" t="inlineStr">
+        <is>
+          <t>Our own activation funnel, available from P1 onward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="57" t="inlineStr">
+        <is>
+          <t>Fan acquisition capacity</t>
+        </is>
+      </c>
+      <c r="B15" s="61" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
+      </c>
+      <c r="C15" s="64" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="D15" s="59" t="inlineStr">
+        <is>
+          <t>An athlete can recruit 30-69 new paying fans a year depending on segment. This ceiling is what makes churn bite in the model: without it, higher churn perversely RAISED revenue, because the year-end target was reachable at any churn rate.</t>
+        </is>
+      </c>
+      <c r="E15" s="59" t="inlineStr">
+        <is>
+          <t>None — introduced to fix a modelling flaw found by stress testing</t>
+        </is>
+      </c>
+      <c r="F15" s="65" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G15" s="59" t="inlineStr">
+        <is>
+          <t>Observed gross adds per athlete per year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>— PAYMENT RAILS —</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="57" t="inlineStr">
+        <is>
+          <t>PSP percentage fee</t>
+        </is>
+      </c>
+      <c r="B17" s="31">
+        <f>Assumptions!$C$40</f>
+        <v/>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D17" s="59" t="inlineStr">
+        <is>
+          <t>Stripe for a Spanish entity: 1.5% + EUR 0.25 on EEA domestic cards, 2.5% on UK cards, 3.25% on non-EEA. 1.9% is the blend for a mostly-European fan base. CORRECTION: an earlier version of this model used the US headline of 2.9% and overstated the largest cost line in the business by about a third.</t>
+        </is>
+      </c>
+      <c r="E17" s="59" t="inlineStr">
+        <is>
+          <t>Stripe published EU/EEA pricing, 2026</t>
+        </is>
+      </c>
+      <c r="F17" s="60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G17" s="59" t="inlineStr">
+        <is>
+          <t>Interchange-plus terms become negotiable above roughly EUR 5M processed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="57" t="inlineStr">
+        <is>
+          <t>PSP fixed fee per transaction</t>
+        </is>
+      </c>
+      <c r="B18" s="31">
+        <f>Assumptions!$C$41</f>
+        <v/>
+      </c>
+      <c r="C18" s="63" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D18" s="59" t="inlineStr">
+        <is>
+          <t>EUR 0.25 per transaction. On a EUR 4.99 tier that single fee is a third of our take, which is why the tier floor and annual billing move more margin than the take rate does.</t>
+        </is>
+      </c>
+      <c r="E18" s="59" t="inlineStr">
+        <is>
+          <t>Stripe published pricing, 2026</t>
+        </is>
+      </c>
+      <c r="F18" s="60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G18" s="59" t="inlineStr">
+        <is>
+          <t>Volume renegotiation; annual billing turns twelve fees into one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="57" t="inlineStr">
+        <is>
+          <t>Payout fees</t>
+        </is>
+      </c>
+      <c r="B19" s="31">
+        <f>Assumptions!$C$42</f>
+        <v/>
+      </c>
+      <c r="C19" s="63" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="inlineStr">
+        <is>
+          <t>Stripe Connect Express: roughly 0.25% + EUR 0.25 per payout, plus a monthly active-account fee that is not modelled as a separate line.</t>
+        </is>
+      </c>
+      <c r="E19" s="59" t="inlineStr">
+        <is>
+          <t>Stripe Connect pricing, 2026</t>
+        </is>
+      </c>
+      <c r="F19" s="62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G19" s="59" t="inlineStr">
+        <is>
+          <t>Actual payout frequency once athletes are onboarded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>— MARKET SIZING —</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="57" t="inlineStr">
+        <is>
+          <t>Sport participation by country</t>
+        </is>
+      </c>
+      <c r="B21" s="61" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
+      </c>
+      <c r="C21" s="63" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D21" s="59" t="inlineStr">
+        <is>
+          <t>Eurobarometer 525, share who NEVER exercise: Finland 8%, Sweden 12%, Denmark 20%, Poland 65%, Greece 68%, Portugal 73%, EU-27 average 45%. Six of the 34 countries in the index are measured; the other 28 are estimates placed inside that distribution.</t>
+        </is>
+      </c>
+      <c r="E21" s="59" t="inlineStr">
+        <is>
+          <t>Special Eurobarometer 525, Sport and Physical Activity, September 2022</t>
+        </is>
+      </c>
+      <c r="F21" s="60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G21" s="59" t="inlineStr">
+        <is>
+          <t>Federation licence counts — published annually and free (CSD in Spain).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="57" t="inlineStr">
+        <is>
+          <t>Padel market size</t>
+        </is>
+      </c>
+      <c r="B22" s="61" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
+      </c>
+      <c r="C22" s="63" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D22" s="59" t="inlineStr">
+        <is>
+          <t>Spain has ~6.0M active players (12.7% of the population), 109,040 federation licences and 17,300+ courts; globally 35M+ players and 77,000+ courts. This is the clearest case for weighting a sport regionally rather than globally — padel scores 77.7 in Spain and 45.1 worldwide.</t>
+        </is>
+      </c>
+      <c r="E22" s="59" t="inlineStr">
+        <is>
+          <t>FIP World Padel Report 2025</t>
+        </is>
+      </c>
+      <c r="F22" s="60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G22" s="59" t="inlineStr">
+        <is>
+          <t>Annual FIP refresh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="57" t="inlineStr">
+        <is>
+          <t>Sports fandom by country</t>
+        </is>
+      </c>
+      <c r="B23" s="61" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
+      </c>
+      <c r="C23" s="64" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="D23" s="59" t="inlineStr">
+        <is>
+          <t>The weakest layer of the sport index, and it drives both the `demand` and `appetite` signals. Commercial audience panels (Nielsen Sports, YouGov) cost more than the entire Y1-Y2 analytics budget.</t>
+        </is>
+      </c>
+      <c r="E23" s="59" t="inlineStr">
+        <is>
+          <t>None — reasoned estimates only</t>
+        </is>
+      </c>
+      <c r="F23" s="65" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G23" s="59" t="inlineStr">
+        <is>
+          <t>Our own engagement data per sport per country once connectors are live. This is what makes the index self-improving rather than something anyone could copy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="57" t="inlineStr">
+        <is>
+          <t>Athlete count trajectory</t>
+        </is>
+      </c>
+      <c r="B24" s="31">
+        <f>Assumptions!$C$5</f>
+        <v/>
+      </c>
+      <c r="C24" s="64" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="D24" s="59" t="inlineStr">
+        <is>
+          <t>400 rising to 85,000 over ten years. This is the PLAN, not a benchmark: marketing spend is derived from it at segment CAC, not the other way round. Everything in the model scales off this line.</t>
+        </is>
+      </c>
+      <c r="E24" s="59" t="inlineStr">
+        <is>
+          <t>None — it is a target</t>
+        </is>
+      </c>
+      <c r="F24" s="65" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G24" s="59" t="inlineStr">
+        <is>
+          <t>The pre-seed gate tests it directly: 400 athletes and EUR 10k MRR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>— COSTS —</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="57" t="inlineStr">
+        <is>
+          <t>Athlete CAC</t>
+        </is>
+      </c>
+      <c r="B26" s="31">
+        <f>Assumptions!$C$17</f>
+        <v/>
+      </c>
+      <c r="C26" s="64" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="D26" s="59" t="inlineStr">
+        <is>
+          <t>EUR 16-36 for niche, EUR 40-88 for popular. The gap reflects displacing an existing agent relationship versus reaching someone with no representation at all. No published comparable exists for athlete acquisition in this segment.</t>
+        </is>
+      </c>
+      <c r="E26" s="59" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="F26" s="65" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G26" s="59" t="inlineStr">
+        <is>
+          <t>Measured CAC by channel from the first federation partnership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="57" t="inlineStr">
+        <is>
+          <t>Loaded salary, Spain</t>
+        </is>
+      </c>
+      <c r="B27" s="31">
+        <f>Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="C27" s="58" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
+        </is>
+      </c>
+      <c r="D27" s="59" t="inlineStr">
+        <is>
+          <t>EUR 38k-76k loaded. Spanish employer social security adds roughly 31% on top of gross, so a senior engineer at ~EUR 55k gross costs ~EUR 72k — around half the London equivalent, which is a real argument for being in Spain rather than an accident of geography.</t>
+        </is>
+      </c>
+      <c r="E27" s="59" t="inlineStr">
+        <is>
+          <t>Spanish Seguridad Social employer contribution rates</t>
+        </is>
+      </c>
+      <c r="F27" s="62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G27" s="59" t="inlineStr">
+        <is>
+          <t>Actual offers accepted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="57" t="inlineStr">
+        <is>
+          <t>AWS infrastructure</t>
+        </is>
+      </c>
+      <c r="B28" s="31">
+        <f>Assumptions!$C$48</f>
+        <v/>
+      </c>
+      <c r="C28" s="58" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
+        </is>
+      </c>
+      <c r="D28" s="59" t="inlineStr">
+        <is>
+          <t>Built up per stage from list prices: Fargate, RDS then Aurora, ElastiCache, S3, MediaConvert, CloudWatch. Reserved capacity and Savings Plans (25-40%) are deliberately excluded and treated as upside.</t>
+        </is>
+      </c>
+      <c r="E28" s="59" t="inlineStr">
+        <is>
+          <t>AWS published list pricing, 2026</t>
+        </is>
+      </c>
+      <c r="F28" s="62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G28" s="59" t="inlineStr">
+        <is>
+          <t>Actual bills; commit to Savings Plans once usage is stable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="57" t="inlineStr">
+        <is>
+          <t>Media egress</t>
+        </is>
+      </c>
+      <c r="B29" s="31">
+        <f>Assumptions!$C$50</f>
+        <v/>
+      </c>
+      <c r="C29" s="63" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D29" s="59" t="inlineStr">
+        <is>
+          <t>EUR 0.008/GB behind a zero-egress object store versus EUR 0.075/GB at CloudFront list price. At Y10 volumes that single architectural choice is worth over EUR 1M a year — the largest cost decision in the plan that is settled by engineering rather than negotiation.</t>
+        </is>
+      </c>
+      <c r="E29" s="59" t="inlineStr">
+        <is>
+          <t>Cloudflare R2 and Backblaze B2 pricing; AWS CloudFront list price</t>
+        </is>
+      </c>
+      <c r="F29" s="60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G29" s="59" t="inlineStr">
+        <is>
+          <t>Nothing. Both are published.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="57" t="inlineStr">
+        <is>
+          <t>Moderation cost</t>
+        </is>
+      </c>
+      <c r="B30" s="31">
+        <f>Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="C30" s="64" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="D30" s="59" t="inlineStr">
+        <is>
+          <t>EUR 22 per 1,000 items reviewed, on a hybrid of automated classification and human review. Vendor pricing varies widely with SLA and content type.</t>
+        </is>
+      </c>
+      <c r="E30" s="59" t="inlineStr">
+        <is>
+          <t>None cited</t>
+        </is>
+      </c>
+      <c r="F30" s="65" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G30" s="59" t="inlineStr">
+        <is>
+          <t>Vendor quotes once P2 scope is fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>— TAX, CAPITAL &amp; VALUATION —</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="57" t="inlineStr">
+        <is>
+          <t>Corporate tax rates</t>
+        </is>
+      </c>
+      <c r="B32" s="31">
+        <f>Assumptions!$C$67</f>
+        <v/>
+      </c>
+      <c r="C32" s="63" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D32" s="59" t="inlineStr">
+        <is>
+          <t>15% for the first four profitable years under the Spanish Startup Law, then the 25% standard rate. Modelled with loss carryforward against the Y1-Y4 losses.</t>
+        </is>
+      </c>
+      <c r="E32" s="59" t="inlineStr">
+        <is>
+          <t>Ley de Startups (Spain); Impuesto sobre Sociedades</t>
+        </is>
+      </c>
+      <c r="F32" s="60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G32" s="59" t="inlineStr">
+        <is>
+          <t>Confirm eligibility with a Spanish tax adviser before filing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="57" t="inlineStr">
+        <is>
+          <t>Risk-free rate</t>
+        </is>
+      </c>
+      <c r="B33" s="31">
+        <f>Assumptions!$C$75</f>
+        <v/>
+      </c>
+      <c r="C33" s="63" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D33" s="59" t="inlineStr">
+        <is>
+          <t>Spanish 10-year sovereign yield, ~3.2% in mid-2026. Used as the floor for the founder opportunity-cost calculation rather than as the discount rate.</t>
+        </is>
+      </c>
+      <c r="E33" s="59" t="inlineStr">
+        <is>
+          <t>Spanish 10Y government bond yield</t>
+        </is>
+      </c>
+      <c r="F33" s="60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G33" s="59" t="inlineStr">
+        <is>
+          <t>Refresh at the date of any raise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="57" t="inlineStr">
+        <is>
+          <t>WACC / discount rate</t>
+        </is>
+      </c>
+      <c r="B34" s="31">
+        <f>Assumptions!$C$72</f>
+        <v/>
+      </c>
+      <c r="C34" s="58" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
+        </is>
+      </c>
+      <c r="D34" s="59" t="inlineStr">
+        <is>
+          <t>25%. The conventional range for pre-revenue to early-revenue venture is 20-35% and we sit mid-range. The sensitivity grid runs 18-30% precisely because this is arguable rather than knowable.</t>
+        </is>
+      </c>
+      <c r="E34" s="59" t="inlineStr">
+        <is>
+          <t>Standard venture valuation practice</t>
+        </is>
+      </c>
+      <c r="F34" s="62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G34" s="59" t="inlineStr">
+        <is>
+          <t>An actual term sheet prices this for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="57" t="inlineStr">
+        <is>
+          <t>Exit revenue multiple</t>
+        </is>
+      </c>
+      <c r="B35" s="31">
+        <f>Assumptions!$C$74</f>
+        <v/>
+      </c>
+      <c r="C35" s="58" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
+        </is>
+      </c>
+      <c r="D35" s="59" t="inlineStr">
+        <is>
+          <t>6.5x blended. Marketplace comparables trade around 4x revenue and high-growth SaaS around 9x; our Y10 mix is roughly 55% marketplace take and 12% SaaS.</t>
+        </is>
+      </c>
+      <c r="E35" s="59" t="inlineStr">
+        <is>
+          <t>Public marketplace and SaaS trading multiples</t>
+        </is>
+      </c>
+      <c r="F35" s="62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G35" s="59" t="inlineStr">
+        <is>
+          <t>Comparable private transactions nearer an exit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="57" t="inlineStr">
+        <is>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="B36" s="31">
+        <f>Assumptions!$C$73</f>
+        <v/>
+      </c>
+      <c r="C36" s="58" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
+        </is>
+      </c>
+      <c r="D36" s="59" t="inlineStr">
+        <is>
+          <t>3%, approximating long-run nominal GDP. Ten explicit forecast years were chosen partly so this assumption carries less of the valuation than it would at Y7.</t>
+        </is>
+      </c>
+      <c r="E36" s="59" t="inlineStr">
+        <is>
+          <t>Standard DCF convention</t>
+        </is>
+      </c>
+      <c r="F36" s="62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G36" s="59" t="inlineStr">
+        <is>
+          <t>Nothing — it is a convention, and the grid shows its effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>— COMPLIANCE —</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="57" t="inlineStr">
+        <is>
+          <t>Payout age floor</t>
+        </is>
+      </c>
+      <c r="B38" s="61" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
+      </c>
+      <c r="C38" s="63" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D38" s="59" t="inlineStr">
+        <is>
+          <t>Stripe Express and Custom Connect require 18. Standard Connect allows 13+, but a legal guardian must own the account and hold the bank account the money lands in.</t>
+        </is>
+      </c>
+      <c r="E38" s="59" t="inlineStr">
+        <is>
+          <t>Stripe Connect documentation</t>
+        </is>
+      </c>
+      <c r="F38" s="60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G38" s="59" t="inlineStr">
+        <is>
+          <t>Nothing — it is a hard platform rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="57" t="inlineStr">
+        <is>
+          <t>Digital consent age, Spain</t>
+        </is>
+      </c>
+      <c r="B39" s="61" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
+      </c>
+      <c r="C39" s="63" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D39" s="59" t="inlineStr">
+        <is>
+          <t>14 today under LOPDGDD Art. 7. A draft Organic Law on the Protection of Minors in Digital Environments would raise it to 16 and make age verification mandatory — which is why 16 is the forward-compatible floor for an account.</t>
+        </is>
+      </c>
+      <c r="E39" s="59" t="inlineStr">
+        <is>
+          <t>LOPDGDD Art. 7; draft Organic Law, Council of Ministers, March 2025</t>
+        </is>
+      </c>
+      <c r="F39" s="60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G39" s="59" t="inlineStr">
+        <is>
+          <t>Track the bill through Parliament.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="67" t="inlineStr">
+        <is>
+          <t>THE THREE ASSUMPTIONS MOST LIKELY TO BE WRONG</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="68" t="inlineStr">
+        <is>
+          <t>1. Fan churn. We assume 6-13%/month; Patreon reports 10-15%. If Patreon is right, Y10 revenue falls from about EUR 58M to EUR 51M and the capital requirement roughly doubles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="68" t="inlineStr">
+        <is>
+          <t>2. Athlete count. The trajectory is a target, not a forecast, and everything scales off it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="68" t="inlineStr">
+        <is>
+          <t>3. Share of athletes who monetise. No published comparable exists at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="69" t="inlineStr"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="69" t="inlineStr">
+        <is>
+          <t>All three are answered by the same thing: three months of real cohort data from P1.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A46:G46"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2335,43 +3637,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C7" s="56">
+      <c r="C7" s="70">
         <f>ROUND(C6-C5,0)</f>
         <v/>
       </c>
-      <c r="D7" s="56">
+      <c r="D7" s="70">
         <f>ROUND(D6-D5,0)</f>
         <v/>
       </c>
-      <c r="E7" s="56">
+      <c r="E7" s="70">
         <f>ROUND(E6-E5,0)</f>
         <v/>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="70">
         <f>ROUND(F6-F5,0)</f>
         <v/>
       </c>
-      <c r="G7" s="56">
+      <c r="G7" s="70">
         <f>ROUND(G6-G5,0)</f>
         <v/>
       </c>
-      <c r="H7" s="56">
+      <c r="H7" s="70">
         <f>ROUND(H6-H5,0)</f>
         <v/>
       </c>
-      <c r="I7" s="56">
+      <c r="I7" s="70">
         <f>ROUND(I6-I5,0)</f>
         <v/>
       </c>
-      <c r="J7" s="56">
+      <c r="J7" s="70">
         <f>ROUND(J6-J5,0)</f>
         <v/>
       </c>
-      <c r="K7" s="56">
+      <c r="K7" s="70">
         <f>ROUND(K6-K5,0)</f>
         <v/>
       </c>
-      <c r="L7" s="56">
+      <c r="L7" s="70">
         <f>ROUND(L6-L5,0)</f>
         <v/>
       </c>
@@ -2406,34 +3708,34 @@
         </is>
       </c>
       <c r="C10" s="19" t="n">
-        <v>14680.34718204357</v>
+        <v>12726.13419188293</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>90534.34495559406</v>
+        <v>76849.51308833165</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>378568.4277152619</v>
+        <v>315757.2344924861</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>1194512.451577747</v>
+        <v>978957.1345808998</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>2941000.036327691</v>
+        <v>2375525.66482911</v>
       </c>
       <c r="H10" s="19" t="n">
-        <v>5587730.984864509</v>
+        <v>4463569.880942384</v>
       </c>
       <c r="I10" s="19" t="n">
-        <v>9039382.759314347</v>
+        <v>7182386.925388074</v>
       </c>
       <c r="J10" s="19" t="n">
-        <v>12737838.07332591</v>
+        <v>10085521.16664168</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>15991727.04334662</v>
+        <v>12661613.18569801</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>19382375.17672797</v>
+        <v>15281260.46768371</v>
       </c>
     </row>
     <row r="11">
@@ -2499,43 +3801,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C12" s="56">
+      <c r="C12" s="70">
         <f>ROUND(C11-C10,0)</f>
         <v/>
       </c>
-      <c r="D12" s="56">
+      <c r="D12" s="70">
         <f>ROUND(D11-D10,0)</f>
         <v/>
       </c>
-      <c r="E12" s="56">
+      <c r="E12" s="70">
         <f>ROUND(E11-E10,0)</f>
         <v/>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="70">
         <f>ROUND(F11-F10,0)</f>
         <v/>
       </c>
-      <c r="G12" s="56">
+      <c r="G12" s="70">
         <f>ROUND(G11-G10,0)</f>
         <v/>
       </c>
-      <c r="H12" s="56">
+      <c r="H12" s="70">
         <f>ROUND(H11-H10,0)</f>
         <v/>
       </c>
-      <c r="I12" s="56">
+      <c r="I12" s="70">
         <f>ROUND(I11-I10,0)</f>
         <v/>
       </c>
-      <c r="J12" s="56">
+      <c r="J12" s="70">
         <f>ROUND(J11-J10,0)</f>
         <v/>
       </c>
-      <c r="K12" s="56">
+      <c r="K12" s="70">
         <f>ROUND(K11-K10,0)</f>
         <v/>
       </c>
-      <c r="L12" s="56">
+      <c r="L12" s="70">
         <f>ROUND(L11-L10,0)</f>
         <v/>
       </c>
@@ -2570,34 +3872,34 @@
         </is>
       </c>
       <c r="C15" s="19" t="n">
-        <v>14485.94767036601</v>
+        <v>16440.16066052664</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>140932.4530533421</v>
+        <v>154617.2849206046</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>660687.4706263749</v>
+        <v>723498.6638491508</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>2175293.003374956</v>
+        <v>2390848.320371803</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>5454820.536151013</v>
+        <v>6020294.907649594</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>10616180.57396737</v>
+        <v>11740341.6778895</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>17484322.74957971</v>
+        <v>19341318.58350598</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>24951721.52693758</v>
+        <v>27604038.43362181</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>31580075.62138253</v>
+        <v>34910189.47903115</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>38579041.45893598</v>
+        <v>42680156.16798024</v>
       </c>
     </row>
     <row r="16">
@@ -2663,43 +3965,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C17" s="56">
+      <c r="C17" s="70">
         <f>ROUND(C16-C15,0)</f>
         <v/>
       </c>
-      <c r="D17" s="56">
+      <c r="D17" s="70">
         <f>ROUND(D16-D15,0)</f>
         <v/>
       </c>
-      <c r="E17" s="56">
+      <c r="E17" s="70">
         <f>ROUND(E16-E15,0)</f>
         <v/>
       </c>
-      <c r="F17" s="56">
+      <c r="F17" s="70">
         <f>ROUND(F16-F15,0)</f>
         <v/>
       </c>
-      <c r="G17" s="56">
+      <c r="G17" s="70">
         <f>ROUND(G16-G15,0)</f>
         <v/>
       </c>
-      <c r="H17" s="56">
+      <c r="H17" s="70">
         <f>ROUND(H16-H15,0)</f>
         <v/>
       </c>
-      <c r="I17" s="56">
+      <c r="I17" s="70">
         <f>ROUND(I16-I15,0)</f>
         <v/>
       </c>
-      <c r="J17" s="56">
+      <c r="J17" s="70">
         <f>ROUND(J16-J15,0)</f>
         <v/>
       </c>
-      <c r="K17" s="56">
+      <c r="K17" s="70">
         <f>ROUND(K16-K15,0)</f>
         <v/>
       </c>
-      <c r="L17" s="56">
+      <c r="L17" s="70">
         <f>ROUND(L16-L15,0)</f>
         <v/>
       </c>
@@ -2827,43 +4129,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C22" s="56">
+      <c r="C22" s="70">
         <f>ROUND(C21-C20,0)</f>
         <v/>
       </c>
-      <c r="D22" s="56">
+      <c r="D22" s="70">
         <f>ROUND(D21-D20,0)</f>
         <v/>
       </c>
-      <c r="E22" s="56">
+      <c r="E22" s="70">
         <f>ROUND(E21-E20,0)</f>
         <v/>
       </c>
-      <c r="F22" s="56">
+      <c r="F22" s="70">
         <f>ROUND(F21-F20,0)</f>
         <v/>
       </c>
-      <c r="G22" s="56">
+      <c r="G22" s="70">
         <f>ROUND(G21-G20,0)</f>
         <v/>
       </c>
-      <c r="H22" s="56">
+      <c r="H22" s="70">
         <f>ROUND(H21-H20,0)</f>
         <v/>
       </c>
-      <c r="I22" s="56">
+      <c r="I22" s="70">
         <f>ROUND(I21-I20,0)</f>
         <v/>
       </c>
-      <c r="J22" s="56">
+      <c r="J22" s="70">
         <f>ROUND(J21-J20,0)</f>
         <v/>
       </c>
-      <c r="K22" s="56">
+      <c r="K22" s="70">
         <f>ROUND(K21-K20,0)</f>
         <v/>
       </c>
-      <c r="L22" s="56">
+      <c r="L22" s="70">
         <f>ROUND(L21-L20,0)</f>
         <v/>
       </c>
@@ -2898,34 +4200,34 @@
         </is>
       </c>
       <c r="C25" s="19" t="n">
-        <v>-92227.35591782676</v>
+        <v>-90273.14292766612</v>
       </c>
       <c r="D25" s="19" t="n">
-        <v>-198648.0907873728</v>
+        <v>-184963.2589201104</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>-327380.8412409561</v>
+        <v>-264569.6480181803</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>-115503.43302126</v>
+        <v>100051.8839755869</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>1184138.890352717</v>
+        <v>1749613.261851298</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>4047422.649260825</v>
+        <v>5171583.753182949</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>8177346.308868185</v>
+        <v>10034342.14279446</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>13497212.7589165</v>
+        <v>16149529.66560073</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>18466968.9082042</v>
+        <v>21797082.76585281</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>24157820.92808286</v>
+        <v>28258935.63712712</v>
       </c>
     </row>
     <row r="26">
@@ -2991,43 +4293,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C27" s="56">
+      <c r="C27" s="70">
         <f>ROUND(C26-C25,0)</f>
         <v/>
       </c>
-      <c r="D27" s="56">
+      <c r="D27" s="70">
         <f>ROUND(D26-D25,0)</f>
         <v/>
       </c>
-      <c r="E27" s="56">
+      <c r="E27" s="70">
         <f>ROUND(E26-E25,0)</f>
         <v/>
       </c>
-      <c r="F27" s="56">
+      <c r="F27" s="70">
         <f>ROUND(F26-F25,0)</f>
         <v/>
       </c>
-      <c r="G27" s="56">
+      <c r="G27" s="70">
         <f>ROUND(G26-G25,0)</f>
         <v/>
       </c>
-      <c r="H27" s="56">
+      <c r="H27" s="70">
         <f>ROUND(H26-H25,0)</f>
         <v/>
       </c>
-      <c r="I27" s="56">
+      <c r="I27" s="70">
         <f>ROUND(I26-I25,0)</f>
         <v/>
       </c>
-      <c r="J27" s="56">
+      <c r="J27" s="70">
         <f>ROUND(J26-J25,0)</f>
         <v/>
       </c>
-      <c r="K27" s="56">
+      <c r="K27" s="70">
         <f>ROUND(K26-K25,0)</f>
         <v/>
       </c>
-      <c r="L27" s="56">
+      <c r="L27" s="70">
         <f>ROUND(L26-L25,0)</f>
         <v/>
       </c>
@@ -3155,43 +4457,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C32" s="57">
+      <c r="C32" s="71">
         <f>ROUND(C31-C30,0)</f>
         <v/>
       </c>
-      <c r="D32" s="57">
+      <c r="D32" s="71">
         <f>ROUND(D31-D30,0)</f>
         <v/>
       </c>
-      <c r="E32" s="57">
+      <c r="E32" s="71">
         <f>ROUND(E31-E30,0)</f>
         <v/>
       </c>
-      <c r="F32" s="57">
+      <c r="F32" s="71">
         <f>ROUND(F31-F30,0)</f>
         <v/>
       </c>
-      <c r="G32" s="57">
+      <c r="G32" s="71">
         <f>ROUND(G31-G30,0)</f>
         <v/>
       </c>
-      <c r="H32" s="57">
+      <c r="H32" s="71">
         <f>ROUND(H31-H30,0)</f>
         <v/>
       </c>
-      <c r="I32" s="57">
+      <c r="I32" s="71">
         <f>ROUND(I31-I30,0)</f>
         <v/>
       </c>
-      <c r="J32" s="57">
+      <c r="J32" s="71">
         <f>ROUND(J31-J30,0)</f>
         <v/>
       </c>
-      <c r="K32" s="57">
+      <c r="K32" s="71">
         <f>ROUND(K31-K30,0)</f>
         <v/>
       </c>
-      <c r="L32" s="57">
+      <c r="L32" s="71">
         <f>ROUND(L31-L30,0)</f>
         <v/>
       </c>
@@ -3319,43 +4621,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C37" s="57">
+      <c r="C37" s="71">
         <f>ROUND(C36-C35,0)</f>
         <v/>
       </c>
-      <c r="D37" s="57">
+      <c r="D37" s="71">
         <f>ROUND(D36-D35,0)</f>
         <v/>
       </c>
-      <c r="E37" s="57">
+      <c r="E37" s="71">
         <f>ROUND(E36-E35,0)</f>
         <v/>
       </c>
-      <c r="F37" s="57">
+      <c r="F37" s="71">
         <f>ROUND(F36-F35,0)</f>
         <v/>
       </c>
-      <c r="G37" s="57">
+      <c r="G37" s="71">
         <f>ROUND(G36-G35,0)</f>
         <v/>
       </c>
-      <c r="H37" s="57">
+      <c r="H37" s="71">
         <f>ROUND(H36-H35,0)</f>
         <v/>
       </c>
-      <c r="I37" s="57">
+      <c r="I37" s="71">
         <f>ROUND(I36-I35,0)</f>
         <v/>
       </c>
-      <c r="J37" s="57">
+      <c r="J37" s="71">
         <f>ROUND(J36-J35,0)</f>
         <v/>
       </c>
-      <c r="K37" s="57">
+      <c r="K37" s="71">
         <f>ROUND(K36-K35,0)</f>
         <v/>
       </c>
-      <c r="L37" s="57">
+      <c r="L37" s="71">
         <f>ROUND(L36-L35,0)</f>
         <v/>
       </c>
@@ -3483,43 +4785,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C42" s="56">
+      <c r="C42" s="70">
         <f>ROUND(C41-C40,0)</f>
         <v/>
       </c>
-      <c r="D42" s="56">
+      <c r="D42" s="70">
         <f>ROUND(D41-D40,0)</f>
         <v/>
       </c>
-      <c r="E42" s="56">
+      <c r="E42" s="70">
         <f>ROUND(E41-E40,0)</f>
         <v/>
       </c>
-      <c r="F42" s="56">
+      <c r="F42" s="70">
         <f>ROUND(F41-F40,0)</f>
         <v/>
       </c>
-      <c r="G42" s="56">
+      <c r="G42" s="70">
         <f>ROUND(G41-G40,0)</f>
         <v/>
       </c>
-      <c r="H42" s="56">
+      <c r="H42" s="70">
         <f>ROUND(H41-H40,0)</f>
         <v/>
       </c>
-      <c r="I42" s="56">
+      <c r="I42" s="70">
         <f>ROUND(I41-I40,0)</f>
         <v/>
       </c>
-      <c r="J42" s="56">
+      <c r="J42" s="70">
         <f>ROUND(J41-J40,0)</f>
         <v/>
       </c>
-      <c r="K42" s="56">
+      <c r="K42" s="70">
         <f>ROUND(K41-K40,0)</f>
         <v/>
       </c>
-      <c r="L42" s="56">
+      <c r="L42" s="70">
         <f>ROUND(L41-L40,0)</f>
         <v/>
       </c>
@@ -3647,43 +4949,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C47" s="57">
+      <c r="C47" s="71">
         <f>ROUND(C46-C45,0)</f>
         <v/>
       </c>
-      <c r="D47" s="57">
+      <c r="D47" s="71">
         <f>ROUND(D46-D45,0)</f>
         <v/>
       </c>
-      <c r="E47" s="57">
+      <c r="E47" s="71">
         <f>ROUND(E46-E45,0)</f>
         <v/>
       </c>
-      <c r="F47" s="57">
+      <c r="F47" s="71">
         <f>ROUND(F46-F45,0)</f>
         <v/>
       </c>
-      <c r="G47" s="57">
+      <c r="G47" s="71">
         <f>ROUND(G46-G45,0)</f>
         <v/>
       </c>
-      <c r="H47" s="57">
+      <c r="H47" s="71">
         <f>ROUND(H46-H45,0)</f>
         <v/>
       </c>
-      <c r="I47" s="57">
+      <c r="I47" s="71">
         <f>ROUND(I46-I45,0)</f>
         <v/>
       </c>
-      <c r="J47" s="57">
+      <c r="J47" s="71">
         <f>ROUND(J46-J45,0)</f>
         <v/>
       </c>
-      <c r="K47" s="57">
+      <c r="K47" s="71">
         <f>ROUND(K46-K45,0)</f>
         <v/>
       </c>
-      <c r="L47" s="57">
+      <c r="L47" s="71">
         <f>ROUND(L46-L45,0)</f>
         <v/>
       </c>
@@ -3706,43 +5008,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C50" s="58">
+      <c r="C50" s="72">
         <f>BalanceSheet!C20</f>
         <v/>
       </c>
-      <c r="D50" s="58">
+      <c r="D50" s="72">
         <f>BalanceSheet!D20</f>
         <v/>
       </c>
-      <c r="E50" s="58">
+      <c r="E50" s="72">
         <f>BalanceSheet!E20</f>
         <v/>
       </c>
-      <c r="F50" s="58">
+      <c r="F50" s="72">
         <f>BalanceSheet!F20</f>
         <v/>
       </c>
-      <c r="G50" s="58">
+      <c r="G50" s="72">
         <f>BalanceSheet!G20</f>
         <v/>
       </c>
-      <c r="H50" s="58">
+      <c r="H50" s="72">
         <f>BalanceSheet!H20</f>
         <v/>
       </c>
-      <c r="I50" s="58">
+      <c r="I50" s="72">
         <f>BalanceSheet!I20</f>
         <v/>
       </c>
-      <c r="J50" s="58">
+      <c r="J50" s="72">
         <f>BalanceSheet!J20</f>
         <v/>
       </c>
-      <c r="K50" s="58">
+      <c r="K50" s="72">
         <f>BalanceSheet!K20</f>
         <v/>
       </c>
-      <c r="L50" s="58">
+      <c r="L50" s="72">
         <f>BalanceSheet!L20</f>
         <v/>
       </c>
@@ -5156,7 +6458,7 @@
         </is>
       </c>
       <c r="C40" s="24" t="n">
-        <v>0.029</v>
+        <v>0.019</v>
       </c>
       <c r="D40" s="25">
         <f>C40</f>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -2256,7 +2256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2853,112 +2853,139 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="58" t="inlineStr">
+        <is>
+          <t>Division I athletes in network</t>
+        </is>
+      </c>
+      <c r="B23" s="59" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C23" s="60" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D23" s="60" t="inlineStr">
+        <is>
+          <t>TEKTA</t>
+        </is>
+      </c>
+      <c r="E23" s="60" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="F23" s="60" t="inlineStr">
+        <is>
+          <t>Publicis Groupe press release, 19 Aug 2026</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" s="62" t="inlineStr">
+      <c r="A24" s="58" t="inlineStr">
+        <is>
+          <t>Power Four universities</t>
+        </is>
+      </c>
+      <c r="B24" s="59" t="n">
+        <v>68</v>
+      </c>
+      <c r="C24" s="60" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D24" s="60" t="inlineStr">
+        <is>
+          <t>TEKTA</t>
+        </is>
+      </c>
+      <c r="E24" s="60" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="F24" s="60" t="inlineStr">
+        <is>
+          <t>Publicis Groupe press release</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="58" t="inlineStr">
+        <is>
+          <t>Claimed speed-to-market gain</t>
+        </is>
+      </c>
+      <c r="B25" s="61" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C25" s="60" t="inlineStr">
+        <is>
+          <t>share faster</t>
+        </is>
+      </c>
+      <c r="D25" s="60" t="inlineStr">
+        <is>
+          <t>TEKTA</t>
+        </is>
+      </c>
+      <c r="E25" s="60" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="F25" s="60" t="inlineStr">
+        <is>
+          <t>Publicis — stated 50-70% vs a traditional agency process</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="62" t="inlineStr">
         <is>
           <t>TAKE RATES - what each platform costs a creator</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Headline take</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Per txn (USD)</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Monthly fee (USD)</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr"/>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr"/>
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>OnlyFans</t>
-        </is>
-      </c>
-      <c r="B26" s="63" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C26" s="64" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="65" t="inlineStr">
-        <is>
-          <t>Company disclosure — 80% creator share</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Fansly</t>
-        </is>
-      </c>
-      <c r="B27" s="63" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C27" s="64" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="65" t="inlineStr">
-        <is>
-          <t>MEXC platform comparison 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Fanfix</t>
-        </is>
-      </c>
-      <c r="B28" s="63" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C28" s="64" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="65" t="inlineStr">
-        <is>
-          <t>Outseeker comparison 2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Patreon</t>
+          <t>OnlyFans</t>
         </is>
       </c>
       <c r="B29" s="63" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C29" s="64" t="n">
         <v>0</v>
@@ -2968,39 +2995,39 @@
       </c>
       <c r="F29" s="65" t="inlineStr">
         <is>
-          <t>8-12% by plan tier; 10% midpoint</t>
+          <t>Company disclosure — 80% creator share</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Passes</t>
+          <t>Fansly</t>
         </is>
       </c>
       <c r="B30" s="63" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C30" s="64" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D30" s="64" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F30" s="65" t="inlineStr">
         <is>
-          <t>Sacra; Passes rebrand release Apr 2026</t>
+          <t>MEXC platform comparison 2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Stride (proposed)</t>
+          <t>Fanfix</t>
         </is>
       </c>
       <c r="B31" s="63" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="C31" s="64" t="n">
         <v>0</v>
@@ -3010,222 +3037,299 @@
       </c>
       <c r="F31" s="65" t="inlineStr">
         <is>
+          <t>Outseeker comparison 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Patreon</t>
+        </is>
+      </c>
+      <c r="B32" s="63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C32" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="65" t="inlineStr">
+        <is>
+          <t>8-12% by plan tier; 10% midpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Passes</t>
+        </is>
+      </c>
+      <c r="B33" s="63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C33" s="64" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D33" s="64" t="n">
+        <v>29</v>
+      </c>
+      <c r="F33" s="65" t="inlineStr">
+        <is>
+          <t>Sacra; Passes rebrand release Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Stride (proposed)</t>
+        </is>
+      </c>
+      <c r="B34" s="63" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C34" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="65" t="inlineStr">
+        <is>
           <t>Our decision — see MarketModel</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="62" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="62" t="inlineStr">
         <is>
           <t>INTERMEDIARIES the athlete already pays</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>Sports agent — endorsement</t>
         </is>
       </c>
-      <c r="B34" s="63" t="n">
+      <c r="B37" s="63" t="n">
         <v>0.1</v>
       </c>
-      <c r="C34" s="63" t="n">
+      <c r="C37" s="63" t="n">
         <v>0.2</v>
       </c>
-      <c r="F34" s="65" t="inlineStr">
+      <c r="F37" s="65" t="inlineStr">
         <is>
           <t>Oreate / Sapling agent-commission surveys</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Sports agent — playing contract</t>
         </is>
       </c>
-      <c r="B35" s="63" t="n">
+      <c r="B38" s="63" t="n">
         <v>0.04</v>
       </c>
-      <c r="C35" s="63" t="n">
+      <c r="C38" s="63" t="n">
         <v>0.1</v>
       </c>
-      <c r="F35" s="65" t="inlineStr">
+      <c r="F38" s="65" t="inlineStr">
         <is>
           <t>Same</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>OnlyFans management agency</t>
         </is>
       </c>
-      <c r="B36" s="63" t="n">
+      <c r="B39" s="63" t="n">
         <v>0.2</v>
       </c>
-      <c r="C36" s="63" t="n">
+      <c r="C39" s="63" t="n">
         <v>0.5</v>
       </c>
-      <c r="F36" s="65" t="inlineStr">
+      <c r="F39" s="65" t="inlineStr">
         <is>
           <t>Aruna Talent rate guide 2026 — on top of the 20%</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>SOURCES</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="66" t="inlineStr">
-        <is>
-          <t>OnlyFans FY2024</t>
-        </is>
-      </c>
-      <c r="B40" s="67" t="inlineStr">
-        <is>
-          <t>https://variety.com/2025/digital/news/onlyfans-fiscal-2024-revenue-earnings-1236495750/</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="66" t="inlineStr">
-        <is>
-          <t>Patreon creators</t>
-        </is>
-      </c>
-      <c r="B41" s="67" t="inlineStr">
-        <is>
-          <t>https://backlinko.com/patreon-users</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="66" t="inlineStr">
-        <is>
-          <t>Passes economics</t>
-        </is>
-      </c>
-      <c r="B42" s="67" t="inlineStr">
-        <is>
-          <t>https://sacra.com/c/passes/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="66" t="inlineStr">
         <is>
-          <t>Platform comparison</t>
+          <t>OnlyFans FY2024</t>
         </is>
       </c>
       <c r="B43" s="67" t="inlineStr">
         <is>
-          <t>https://www.mexc.com/news/1014749</t>
+          <t>https://variety.com/2025/digital/news/onlyfans-fiscal-2024-revenue-earnings-1236495750/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="66" t="inlineStr">
         <is>
-          <t>Agency commissions</t>
+          <t>Patreon creators</t>
         </is>
       </c>
       <c r="B44" s="67" t="inlineStr">
         <is>
-          <t>https://arunatalent.com/blog/onlyfans-agency-commission-rates/</t>
+          <t>https://backlinko.com/patreon-users</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="66" t="inlineStr">
         <is>
-          <t>Agent commissions</t>
+          <t>Passes economics</t>
         </is>
       </c>
       <c r="B45" s="67" t="inlineStr">
         <is>
-          <t>https://www.oreateai.com/blog/understanding-sports-agents-commission-what-percentage-do-they-take/95c2df506ae450b9b71340b89cfcfece</t>
+          <t>https://sacra.com/c/passes/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="66" t="inlineStr">
         <is>
-          <t>Eurobarometer 525</t>
+          <t>Platform comparison</t>
         </is>
       </c>
       <c r="B46" s="67" t="inlineStr">
         <is>
-          <t>https://europa.eu/eurobarometer/surveys/detail/2668</t>
+          <t>https://www.mexc.com/news/1014749</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="66" t="inlineStr">
         <is>
-          <t>FIP World Padel Report 2025</t>
+          <t>Agency commissions</t>
         </is>
       </c>
       <c r="B47" s="67" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/2025/12/online-the-fip-world-padel-report-2025-a-comprehensive-analysis-of-a-sport-in-constant-growth/</t>
+          <t>https://arunatalent.com/blog/onlyfans-agency-commission-rates/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="66" t="inlineStr">
         <is>
-          <t>Stripe EU pricing</t>
+          <t>Agent commissions</t>
         </is>
       </c>
       <c r="B48" s="67" t="inlineStr">
         <is>
-          <t>https://stripe.com/es/pricing</t>
+          <t>https://www.oreateai.com/blog/understanding-sports-agents-commission-what-percentage-do-they-take/95c2df506ae450b9b71340b89cfcfece</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="66" t="inlineStr">
         <is>
+          <t>Eurobarometer 525</t>
+        </is>
+      </c>
+      <c r="B49" s="67" t="inlineStr">
+        <is>
+          <t>https://europa.eu/eurobarometer/surveys/detail/2668</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="66" t="inlineStr">
+        <is>
+          <t>FIP World Padel Report 2025</t>
+        </is>
+      </c>
+      <c r="B50" s="67" t="inlineStr">
+        <is>
+          <t>https://www.padelfip.com/2025/12/online-the-fip-world-padel-report-2025-a-comprehensive-analysis-of-a-sport-in-constant-growth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="66" t="inlineStr">
+        <is>
+          <t>Stripe EU pricing</t>
+        </is>
+      </c>
+      <c r="B51" s="67" t="inlineStr">
+        <is>
+          <t>https://stripe.com/es/pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="66" t="inlineStr">
+        <is>
+          <t>TEKTA launch</t>
+        </is>
+      </c>
+      <c r="B52" s="67" t="inlineStr">
+        <is>
+          <t>https://www.publicisgroupe.com/en/news/press-releases/publicis-sports-and-travis-kelce-s-tekta-join-forces-to-reimagine-the-future-of-nil-marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="66" t="inlineStr">
+        <is>
           <t>Stripe Connect age</t>
         </is>
       </c>
-      <c r="B49" s="67" t="inlineStr">
+      <c r="B53" s="67" t="inlineStr">
         <is>
           <t>https://support.stripe.com/questions/age-requirement-to-create-a-stripe-account</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B53:F53"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B51:F51"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B52:F52"/>
     <mergeCell ref="B49:F49"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3866,7 +3970,7 @@
         </is>
       </c>
       <c r="B47" s="28">
-        <f>B46*(1-Comparables!B26)-B46/Assumptions!$C$44*Comparables!C26*B45-Comparables!D26*B45</f>
+        <f>B46*(1-Comparables!B29)-B46/Assumptions!$C$44*Comparables!C29*B45-Comparables!D29*B45</f>
         <v/>
       </c>
       <c r="D47" s="68" t="inlineStr">
@@ -3882,7 +3986,7 @@
         </is>
       </c>
       <c r="B48" s="28">
-        <f>B46*(1-Comparables!B29)-B46/Assumptions!$C$44*Comparables!C29*B45-Comparables!D29*B45</f>
+        <f>B46*(1-Comparables!B32)-B46/Assumptions!$C$44*Comparables!C32*B45-Comparables!D32*B45</f>
         <v/>
       </c>
       <c r="D48" s="68" t="inlineStr">
@@ -3898,7 +4002,7 @@
         </is>
       </c>
       <c r="B49" s="28">
-        <f>B46*(1-Comparables!B30)-B46/Assumptions!$C$44*Comparables!C30*B45-Comparables!D30*B45</f>
+        <f>B46*(1-Comparables!B33)-B46/Assumptions!$C$44*Comparables!C33*B45-Comparables!D33*B45</f>
         <v/>
       </c>
       <c r="D49" s="68" t="inlineStr">
@@ -3914,7 +4018,7 @@
         </is>
       </c>
       <c r="B50" s="28">
-        <f>B46*(1-Comparables!B31)-B46/Assumptions!$C$44*Comparables!C31*B45-Comparables!D31*B45</f>
+        <f>B46*(1-Comparables!B34)-B46/Assumptions!$C$44*Comparables!C34*B45-Comparables!D34*B45</f>
         <v/>
       </c>
       <c r="D50" s="68" t="inlineStr">
@@ -3930,7 +4034,7 @@
         </is>
       </c>
       <c r="B51" s="29">
-        <f>Comparables!D30*B45/((Comparables!B31-Comparables!B30)-Comparables!C30*B45/Assumptions!$C$44)</f>
+        <f>Comparables!D33*B45/((Comparables!B34-Comparables!B33)-Comparables!C33*B45/Assumptions!$C$44)</f>
         <v/>
       </c>
       <c r="D51" s="68" t="inlineStr">

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -1794,43 +1794,43 @@
         </is>
       </c>
       <c r="C5" s="32">
-        <f>1/(1+Assumptions!$C$72)^1</f>
+        <f>1/(1+Assumptions!$C$81)^1</f>
         <v/>
       </c>
       <c r="D5" s="32">
-        <f>1/(1+Assumptions!$C$72)^2</f>
+        <f>1/(1+Assumptions!$C$81)^2</f>
         <v/>
       </c>
       <c r="E5" s="32">
-        <f>1/(1+Assumptions!$C$72)^3</f>
+        <f>1/(1+Assumptions!$C$81)^3</f>
         <v/>
       </c>
       <c r="F5" s="32">
-        <f>1/(1+Assumptions!$C$72)^4</f>
+        <f>1/(1+Assumptions!$C$81)^4</f>
         <v/>
       </c>
       <c r="G5" s="32">
-        <f>1/(1+Assumptions!$C$72)^5</f>
+        <f>1/(1+Assumptions!$C$81)^5</f>
         <v/>
       </c>
       <c r="H5" s="32">
-        <f>1/(1+Assumptions!$C$72)^6</f>
+        <f>1/(1+Assumptions!$C$81)^6</f>
         <v/>
       </c>
       <c r="I5" s="32">
-        <f>1/(1+Assumptions!$C$72)^7</f>
+        <f>1/(1+Assumptions!$C$81)^7</f>
         <v/>
       </c>
       <c r="J5" s="32">
-        <f>1/(1+Assumptions!$C$72)^8</f>
+        <f>1/(1+Assumptions!$C$81)^8</f>
         <v/>
       </c>
       <c r="K5" s="32">
-        <f>1/(1+Assumptions!$C$72)^9</f>
+        <f>1/(1+Assumptions!$C$81)^9</f>
         <v/>
       </c>
       <c r="L5" s="32">
-        <f>1/(1+Assumptions!$C$72)^10</f>
+        <f>1/(1+Assumptions!$C$81)^10</f>
         <v/>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="C10" s="52">
-        <f>C4*0+L4*(1+Assumptions!$C$73)/(Assumptions!$C$72-Assumptions!$C$73)</f>
+        <f>C4*0+L4*(1+Assumptions!$C$82)/(Assumptions!$C$81-Assumptions!$C$82)</f>
         <v/>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="C15" s="52">
-        <f>NPV(Assumptions!$C$72,C4:L4)</f>
+        <f>NPV(Assumptions!$C$81,C4:L4)</f>
         <v/>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C21" s="52">
-        <f>C21*Assumptions!$C$74</f>
+        <f>C21*Assumptions!$C$83</f>
         <v/>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -4963,26 +4963,26 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="76" t="inlineStr">
         <is>
-          <t>Loaded salary, Spain</t>
+          <t>Admission rate, direct applicants</t>
         </is>
       </c>
       <c r="B27" s="32">
-        <f>Assumptions!$C$57</f>
-        <v/>
-      </c>
-      <c r="C27" s="77" t="inlineStr">
-        <is>
-          <t>BENCHMARKED</t>
+        <f>Assumptions!$C$72</f>
+        <v/>
+      </c>
+      <c r="C27" s="85" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D27" s="78" t="inlineStr">
         <is>
-          <t>EUR 38k-76k loaded. Spanish employer social security adds roughly 31% on top of gross, so a senior engineer at ~EUR 55k gross costs ~EUR 72k — around half the London equivalent, which is a real argument for being in Spain rather than an accident of geography.</t>
+          <t>20% of direct applicants are admitted, 25% go to a human, 40% are refused and 15% never finish the form. Not a judgement: it is the ops-load output of scripts/admission_stress.py run over the admission policy itself, so retuning a threshold moves this figure. The sweep asserts the model and the policy stay in step and fails if they drift.</t>
         </is>
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>Spanish Seguridad Social employer contribution rates</t>
+          <t>scripts/admission_stress.py, section 7 — over a modelled applicant mix</t>
         </is>
       </c>
       <c r="F27" s="81" t="inlineStr">
@@ -4992,90 +4992,90 @@
       </c>
       <c r="G27" s="78" t="inlineStr">
         <is>
-          <t>Actual offers accepted.</t>
+          <t>Real intake data. The mix the sweep assumes is the soft part, not the arithmetic.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="76" t="inlineStr">
         <is>
-          <t>AWS infrastructure</t>
+          <t>Admission rate, club-nominated</t>
         </is>
       </c>
       <c r="B28" s="32">
-        <f>Assumptions!$C$48</f>
-        <v/>
-      </c>
-      <c r="C28" s="77" t="inlineStr">
-        <is>
-          <t>BENCHMARKED</t>
+        <f>Assumptions!$C$74</f>
+        <v/>
+      </c>
+      <c r="C28" s="83" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
         </is>
       </c>
       <c r="D28" s="78" t="inlineStr">
         <is>
-          <t>Built up per stage from list prices: Fargate, RDS then Aurora, ElastiCache, S3, MediaConvert, CloudWatch. Reserved capacity and Savings Plans (25-40%) are deliberately excluded and treated as upside.</t>
+          <t>45% admitted against 20% direct. A verified club's nomination confers a credibility floor of 0.75 x its own legitimacy score, which carries a completed application over the admit line that would otherwise have gone to review. It cannot carry an empty one — no club can supply someone else's date of birth — so the uplift is real but bounded.</t>
         </is>
       </c>
       <c r="E28" s="78" t="inlineStr">
         <is>
-          <t>AWS published list pricing, 2026</t>
-        </is>
-      </c>
-      <c r="F28" s="81" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>None — the mechanism is built and tested, the conversion is not yet measured</t>
+        </is>
+      </c>
+      <c r="F28" s="84" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G28" s="78" t="inlineStr">
         <is>
-          <t>Actual bills; commit to Savings Plans once usage is stable.</t>
+          <t>The first federation partnership: nominated applicants are tagged, so this is measurable from day one of it.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="76" t="inlineStr">
         <is>
-          <t>Media egress</t>
+          <t>Athlete verification cost</t>
         </is>
       </c>
       <c r="B29" s="32">
-        <f>Assumptions!$C$50</f>
-        <v/>
-      </c>
-      <c r="C29" s="82" t="inlineStr">
-        <is>
-          <t>SOURCED</t>
+        <f>Assumptions!$C$77</f>
+        <v/>
+      </c>
+      <c r="C29" s="85" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D29" s="78" t="inlineStr">
         <is>
-          <t>EUR 0.008/GB behind a zero-egress object store versus EUR 0.075/GB at CloudFront list price. At Y10 volumes that single architectural choice is worth over EUR 1M a year — the largest cost decision in the plan that is settled by engineering rather than negotiation.</t>
+          <t>Four minutes per manual review, priced at the same loaded salary the People line uses, over 1,700 productive hours. Peaks at EUR 47k and 0.64 reviewer-FTE in Y10, which is the finding rather than the cost: verification is not a money problem at this scale. The reason to automate it is latency — an athlete sitting in the queue is not listed, not matchable and not earning.</t>
         </is>
       </c>
       <c r="E29" s="78" t="inlineStr">
         <is>
-          <t>Cloudflare R2 and Backblaze B2 pricing; AWS CloudFront list price</t>
-        </is>
-      </c>
-      <c r="F29" s="79" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Derived from the sweep's review volume and the model's own salary line</t>
+        </is>
+      </c>
+      <c r="F29" s="81" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G29" s="78" t="inlineStr">
         <is>
-          <t>Nothing. Both are published.</t>
+          <t>Timing real reviews. Four minutes is an estimate of a mechanical task.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="76" t="inlineStr">
         <is>
-          <t>Moderation cost</t>
+          <t>Athlete CAC vs the funnel</t>
         </is>
       </c>
       <c r="B30" s="32">
-        <f>Assumptions!$C$52</f>
+        <f>Assumptions!$C$17</f>
         <v/>
       </c>
       <c r="C30" s="83" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="D30" s="78" t="inlineStr">
         <is>
-          <t>EUR 22 per 1,000 items reviewed, on a hybrid of automated classification and human review. Vendor pricing varies widely with SLA and content type.</t>
+          <t>Deliberately NOT multiplied by the admission funnel. Segment CAC is defined as the cost of landing one athlete ON the platform, so scaling it by 1/admission-rate would charge the same money twice. The Costs sheet carries a memo line showing what that CAC works out to per application (EUR 3.40 in Y1 rising to EUR 22) — the figure to hold against what a channel actually charges per name reached.</t>
         </is>
       </c>
       <c r="E30" s="78" t="inlineStr">
         <is>
-          <t>None cited</t>
+          <t>None — this is a definitional choice, made explicit so it is not silently reversed</t>
         </is>
       </c>
       <c r="F30" s="84" t="inlineStr">
@@ -5100,67 +5100,90 @@
       </c>
       <c r="G30" s="78" t="inlineStr">
         <is>
-          <t>Vendor quotes once P2 scope is fixed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>— TAX, CAPITAL &amp; VALUATION —</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="12" t="n"/>
+          <t>Channel-level spend against applications, which the funnel now records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="76" t="inlineStr">
+        <is>
+          <t>Loaded salary, Spain</t>
+        </is>
+      </c>
+      <c r="B31" s="32">
+        <f>Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="C31" s="77" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
+        </is>
+      </c>
+      <c r="D31" s="78" t="inlineStr">
+        <is>
+          <t>EUR 38k-76k loaded. Spanish employer social security adds roughly 31% on top of gross, so a senior engineer at ~EUR 55k gross costs ~EUR 72k — around half the London equivalent, which is a real argument for being in Spain rather than an accident of geography.</t>
+        </is>
+      </c>
+      <c r="E31" s="78" t="inlineStr">
+        <is>
+          <t>Spanish Seguridad Social employer contribution rates</t>
+        </is>
+      </c>
+      <c r="F31" s="81" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G31" s="78" t="inlineStr">
+        <is>
+          <t>Actual offers accepted.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="76" t="inlineStr">
         <is>
-          <t>Corporate tax rates</t>
+          <t>AWS infrastructure</t>
         </is>
       </c>
       <c r="B32" s="32">
-        <f>Assumptions!$C$67</f>
-        <v/>
-      </c>
-      <c r="C32" s="82" t="inlineStr">
-        <is>
-          <t>SOURCED</t>
+        <f>Assumptions!$C$48</f>
+        <v/>
+      </c>
+      <c r="C32" s="77" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
         </is>
       </c>
       <c r="D32" s="78" t="inlineStr">
         <is>
-          <t>15% for the first four profitable years under the Spanish Startup Law, then the 25% standard rate. Modelled with loss carryforward against the Y1-Y4 losses.</t>
+          <t>Built up per stage from list prices: Fargate, RDS then Aurora, ElastiCache, S3, MediaConvert, CloudWatch. Reserved capacity and Savings Plans (25-40%) are deliberately excluded and treated as upside.</t>
         </is>
       </c>
       <c r="E32" s="78" t="inlineStr">
         <is>
-          <t>Ley de Startups (Spain); Impuesto sobre Sociedades</t>
-        </is>
-      </c>
-      <c r="F32" s="79" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>AWS published list pricing, 2026</t>
+        </is>
+      </c>
+      <c r="F32" s="81" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G32" s="78" t="inlineStr">
         <is>
-          <t>Confirm eligibility with a Spanish tax adviser before filing.</t>
+          <t>Actual bills; commit to Savings Plans once usage is stable.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="76" t="inlineStr">
         <is>
-          <t>Risk-free rate</t>
+          <t>Media egress</t>
         </is>
       </c>
       <c r="B33" s="32">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="C33" s="82" t="inlineStr">
@@ -5170,12 +5193,12 @@
       </c>
       <c r="D33" s="78" t="inlineStr">
         <is>
-          <t>Spanish 10-year sovereign yield, ~3.2% in mid-2026. Used as the floor for the founder opportunity-cost calculation rather than as the discount rate.</t>
+          <t>EUR 0.008/GB behind a zero-egress object store versus EUR 0.075/GB at CloudFront list price. At Y10 volumes that single architectural choice is worth over EUR 1M a year — the largest cost decision in the plan that is settled by engineering rather than negotiation.</t>
         </is>
       </c>
       <c r="E33" s="78" t="inlineStr">
         <is>
-          <t>Spanish 10Y government bond yield</t>
+          <t>Cloudflare R2 and Backblaze B2 pricing; AWS CloudFront list price</t>
         </is>
       </c>
       <c r="F33" s="79" t="inlineStr">
@@ -5185,238 +5208,359 @@
       </c>
       <c r="G33" s="78" t="inlineStr">
         <is>
-          <t>Refresh at the date of any raise.</t>
+          <t>Nothing. Both are published.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="76" t="inlineStr">
         <is>
-          <t>WACC / discount rate</t>
+          <t>Moderation cost</t>
         </is>
       </c>
       <c r="B34" s="32">
-        <f>Assumptions!$C$72</f>
-        <v/>
-      </c>
-      <c r="C34" s="77" t="inlineStr">
-        <is>
-          <t>BENCHMARKED</t>
+        <f>Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="C34" s="83" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
         </is>
       </c>
       <c r="D34" s="78" t="inlineStr">
         <is>
-          <t>25%. The conventional range for pre-revenue to early-revenue venture is 20-35% and we sit mid-range. The sensitivity grid runs 18-30% precisely because this is arguable rather than knowable.</t>
+          <t>EUR 22 per 1,000 items reviewed, on a hybrid of automated classification and human review. Vendor pricing varies widely with SLA and content type.</t>
         </is>
       </c>
       <c r="E34" s="78" t="inlineStr">
         <is>
-          <t>Standard venture valuation practice</t>
-        </is>
-      </c>
-      <c r="F34" s="81" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>None cited</t>
+        </is>
+      </c>
+      <c r="F34" s="84" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G34" s="78" t="inlineStr">
         <is>
-          <t>An actual term sheet prices this for you.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="76" t="inlineStr">
-        <is>
-          <t>Exit revenue multiple</t>
-        </is>
-      </c>
-      <c r="B35" s="32">
-        <f>Assumptions!$C$74</f>
-        <v/>
-      </c>
-      <c r="C35" s="77" t="inlineStr">
-        <is>
-          <t>BENCHMARKED</t>
-        </is>
-      </c>
-      <c r="D35" s="78" t="inlineStr">
-        <is>
-          <t>6.5x blended. Marketplace comparables trade around 4x revenue and high-growth SaaS around 9x; our Y10 mix is roughly 55% marketplace take and 12% SaaS.</t>
-        </is>
-      </c>
-      <c r="E35" s="78" t="inlineStr">
-        <is>
-          <t>Public marketplace and SaaS trading multiples</t>
-        </is>
-      </c>
-      <c r="F35" s="81" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G35" s="78" t="inlineStr">
-        <is>
-          <t>Comparable private transactions nearer an exit.</t>
-        </is>
-      </c>
+          <t>Vendor quotes once P2 scope is fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>— TAX, CAPITAL &amp; VALUATION —</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="76" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>Corporate tax rates</t>
         </is>
       </c>
       <c r="B36" s="32">
-        <f>Assumptions!$C$73</f>
-        <v/>
-      </c>
-      <c r="C36" s="77" t="inlineStr">
-        <is>
-          <t>BENCHMARKED</t>
+        <f>Assumptions!$C$67</f>
+        <v/>
+      </c>
+      <c r="C36" s="82" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="D36" s="78" t="inlineStr">
         <is>
-          <t>3%, approximating long-run nominal GDP. Ten explicit forecast years were chosen partly so this assumption carries less of the valuation than it would at Y7.</t>
+          <t>15% for the first four profitable years under the Spanish Startup Law, then the 25% standard rate. Modelled with loss carryforward against the Y1-Y4 losses.</t>
         </is>
       </c>
       <c r="E36" s="78" t="inlineStr">
         <is>
-          <t>Standard DCF convention</t>
-        </is>
-      </c>
-      <c r="F36" s="81" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Ley de Startups (Spain); Impuesto sobre Sociedades</t>
+        </is>
+      </c>
+      <c r="F36" s="79" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G36" s="78" t="inlineStr">
         <is>
-          <t>Nothing — it is a convention, and the grid shows its effect.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>— COMPLIANCE —</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="12" t="n"/>
+          <t>Confirm eligibility with a Spanish tax adviser before filing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="76" t="inlineStr">
+        <is>
+          <t>Risk-free rate</t>
+        </is>
+      </c>
+      <c r="B37" s="32">
+        <f>Assumptions!$C$84</f>
+        <v/>
+      </c>
+      <c r="C37" s="82" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D37" s="78" t="inlineStr">
+        <is>
+          <t>Spanish 10-year sovereign yield, ~3.2% in mid-2026. Used as the floor for the founder opportunity-cost calculation rather than as the discount rate.</t>
+        </is>
+      </c>
+      <c r="E37" s="78" t="inlineStr">
+        <is>
+          <t>Spanish 10Y government bond yield</t>
+        </is>
+      </c>
+      <c r="F37" s="79" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G37" s="78" t="inlineStr">
+        <is>
+          <t>Refresh at the date of any raise.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="76" t="inlineStr">
         <is>
-          <t>Payout age floor</t>
-        </is>
-      </c>
-      <c r="B38" s="80" t="inlineStr">
-        <is>
-          <t>see model</t>
-        </is>
-      </c>
-      <c r="C38" s="82" t="inlineStr">
-        <is>
-          <t>SOURCED</t>
+          <t>WACC / discount rate</t>
+        </is>
+      </c>
+      <c r="B38" s="32">
+        <f>Assumptions!$C$81</f>
+        <v/>
+      </c>
+      <c r="C38" s="77" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
         </is>
       </c>
       <c r="D38" s="78" t="inlineStr">
         <is>
-          <t>Stripe Express and Custom Connect require 18. Standard Connect allows 13+, but a legal guardian must own the account and hold the bank account the money lands in.</t>
+          <t>25%. The conventional range for pre-revenue to early-revenue venture is 20-35% and we sit mid-range. The sensitivity grid runs 18-30% precisely because this is arguable rather than knowable.</t>
         </is>
       </c>
       <c r="E38" s="78" t="inlineStr">
         <is>
-          <t>Stripe Connect documentation</t>
-        </is>
-      </c>
-      <c r="F38" s="79" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Standard venture valuation practice</t>
+        </is>
+      </c>
+      <c r="F38" s="81" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G38" s="78" t="inlineStr">
         <is>
-          <t>Nothing — it is a hard platform rule.</t>
+          <t>An actual term sheet prices this for you.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="76" t="inlineStr">
         <is>
+          <t>Exit revenue multiple</t>
+        </is>
+      </c>
+      <c r="B39" s="32">
+        <f>Assumptions!$C$83</f>
+        <v/>
+      </c>
+      <c r="C39" s="77" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
+        </is>
+      </c>
+      <c r="D39" s="78" t="inlineStr">
+        <is>
+          <t>6.5x blended. Marketplace comparables trade around 4x revenue and high-growth SaaS around 9x; our Y10 mix is roughly 55% marketplace take and 12% SaaS.</t>
+        </is>
+      </c>
+      <c r="E39" s="78" t="inlineStr">
+        <is>
+          <t>Public marketplace and SaaS trading multiples</t>
+        </is>
+      </c>
+      <c r="F39" s="81" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G39" s="78" t="inlineStr">
+        <is>
+          <t>Comparable private transactions nearer an exit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="76" t="inlineStr">
+        <is>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="B40" s="32">
+        <f>Assumptions!$C$82</f>
+        <v/>
+      </c>
+      <c r="C40" s="77" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
+        </is>
+      </c>
+      <c r="D40" s="78" t="inlineStr">
+        <is>
+          <t>3%, approximating long-run nominal GDP. Ten explicit forecast years were chosen partly so this assumption carries less of the valuation than it would at Y7.</t>
+        </is>
+      </c>
+      <c r="E40" s="78" t="inlineStr">
+        <is>
+          <t>Standard DCF convention</t>
+        </is>
+      </c>
+      <c r="F40" s="81" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G40" s="78" t="inlineStr">
+        <is>
+          <t>Nothing — it is a convention, and the grid shows its effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>— COMPLIANCE —</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="n"/>
+      <c r="C41" s="12" t="n"/>
+      <c r="D41" s="12" t="n"/>
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="12" t="n"/>
+      <c r="G41" s="12" t="n"/>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="76" t="inlineStr">
+        <is>
+          <t>Payout age floor</t>
+        </is>
+      </c>
+      <c r="B42" s="80" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
+      </c>
+      <c r="C42" s="82" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D42" s="78" t="inlineStr">
+        <is>
+          <t>Stripe Express and Custom Connect require 18. Standard Connect allows 13+, but a legal guardian must own the account and hold the bank account the money lands in.</t>
+        </is>
+      </c>
+      <c r="E42" s="78" t="inlineStr">
+        <is>
+          <t>Stripe Connect documentation</t>
+        </is>
+      </c>
+      <c r="F42" s="79" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G42" s="78" t="inlineStr">
+        <is>
+          <t>Nothing — it is a hard platform rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="76" t="inlineStr">
+        <is>
           <t>Digital consent age, Spain</t>
         </is>
       </c>
-      <c r="B39" s="80" t="inlineStr">
+      <c r="B43" s="80" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C39" s="82" t="inlineStr">
+      <c r="C43" s="82" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D39" s="78" t="inlineStr">
+      <c r="D43" s="78" t="inlineStr">
         <is>
           <t>14 today under LOPDGDD Art. 7. A draft Organic Law on the Protection of Minors in Digital Environments would raise it to 16 and make age verification mandatory — which is why 16 is the forward-compatible floor for an account.</t>
         </is>
       </c>
-      <c r="E39" s="78" t="inlineStr">
+      <c r="E43" s="78" t="inlineStr">
         <is>
           <t>LOPDGDD Art. 7; draft Organic Law, Council of Ministers, March 2025</t>
         </is>
       </c>
-      <c r="F39" s="79" t="inlineStr">
+      <c r="F43" s="79" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G39" s="78" t="inlineStr">
+      <c r="G43" s="78" t="inlineStr">
         <is>
           <t>Track the bill through Parliament.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="86" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="86" t="inlineStr">
         <is>
           <t>THE THREE ASSUMPTIONS MOST LIKELY TO BE WRONG</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="87" t="inlineStr">
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="87" t="inlineStr">
         <is>
           <t>1. Fan churn. We assume 6-13%/month; Patreon reports 10-15%. If Patreon is right, Y10 revenue falls from about EUR 58M to EUR 51M and the capital requirement roughly doubles.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="87" t="inlineStr">
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="87" t="inlineStr">
         <is>
           <t>2. Athlete count. The trajectory is a target, not a forecast, and everything scales off it.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="87" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="87" t="inlineStr">
         <is>
           <t>3. Share of athletes who monetise. No published comparable exists at all.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="88" t="inlineStr"/>
-    </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="88" t="inlineStr">
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="88" t="inlineStr"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="88" t="inlineStr">
         <is>
           <t>All three are answered by the same thing: three months of real cohort data from P1.</t>
         </is>
@@ -5424,10 +5568,10 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A47:G47"/>
     <mergeCell ref="A46:G46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5440,7 +5584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5757,34 +5901,34 @@
         </is>
       </c>
       <c r="C10" s="20" t="n">
-        <v>12726.13419188293</v>
+        <v>13471.23223109862</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>76849.51308833165</v>
+        <v>80172.86367656694</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>315757.2344924861</v>
+        <v>324954.3266336625</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>978957.1345808998</v>
+        <v>997729.1293521416</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>2375525.66482911</v>
+        <v>2405944.872754806</v>
       </c>
       <c r="H10" s="20" t="n">
-        <v>4463569.880942384</v>
+        <v>4500263.01540566</v>
       </c>
       <c r="I10" s="20" t="n">
-        <v>7182386.925388074</v>
+        <v>7225273.097037062</v>
       </c>
       <c r="J10" s="20" t="n">
-        <v>10085521.16664168</v>
+        <v>10131408.91889975</v>
       </c>
       <c r="K10" s="20" t="n">
-        <v>12661613.18569801</v>
+        <v>12708269.29438148</v>
       </c>
       <c r="L10" s="20" t="n">
-        <v>15281260.46768371</v>
+        <v>15327976.37081417</v>
       </c>
     </row>
     <row r="11">
@@ -5799,43 +5943,43 @@
         </is>
       </c>
       <c r="C11" s="29">
-        <f>Costs!C13</f>
+        <f>Costs!C14</f>
         <v/>
       </c>
       <c r="D11" s="29">
-        <f>Costs!D13</f>
+        <f>Costs!D14</f>
         <v/>
       </c>
       <c r="E11" s="29">
-        <f>Costs!E13</f>
+        <f>Costs!E14</f>
         <v/>
       </c>
       <c r="F11" s="29">
-        <f>Costs!F13</f>
+        <f>Costs!F14</f>
         <v/>
       </c>
       <c r="G11" s="29">
-        <f>Costs!G13</f>
+        <f>Costs!G14</f>
         <v/>
       </c>
       <c r="H11" s="29">
-        <f>Costs!H13</f>
+        <f>Costs!H14</f>
         <v/>
       </c>
       <c r="I11" s="29">
-        <f>Costs!I13</f>
+        <f>Costs!I14</f>
         <v/>
       </c>
       <c r="J11" s="29">
-        <f>Costs!J13</f>
+        <f>Costs!J14</f>
         <v/>
       </c>
       <c r="K11" s="29">
-        <f>Costs!K13</f>
+        <f>Costs!K14</f>
         <v/>
       </c>
       <c r="L11" s="29">
-        <f>Costs!L13</f>
+        <f>Costs!L14</f>
         <v/>
       </c>
     </row>
@@ -5921,34 +6065,34 @@
         </is>
       </c>
       <c r="C15" s="20" t="n">
-        <v>16440.16066052664</v>
+        <v>15695.06262131096</v>
       </c>
       <c r="D15" s="20" t="n">
-        <v>154617.2849206046</v>
+        <v>151293.9343323692</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>723498.6638491508</v>
+        <v>714301.5717079744</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>2390848.320371803</v>
+        <v>2372076.325600561</v>
       </c>
       <c r="G15" s="20" t="n">
-        <v>6020294.907649594</v>
+        <v>5989875.699723898</v>
       </c>
       <c r="H15" s="20" t="n">
-        <v>11740341.6778895</v>
+        <v>11703648.54342622</v>
       </c>
       <c r="I15" s="20" t="n">
-        <v>19341318.58350598</v>
+        <v>19298432.41185699</v>
       </c>
       <c r="J15" s="20" t="n">
-        <v>27604038.43362181</v>
+        <v>27558150.68136375</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>34910189.47903115</v>
+        <v>34863533.37034767</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>42680156.16798024</v>
+        <v>42633440.26484978</v>
       </c>
     </row>
     <row r="16">
@@ -6127,43 +6271,43 @@
         </is>
       </c>
       <c r="C21" s="29">
-        <f>Costs!C23</f>
+        <f>Costs!C25</f>
         <v/>
       </c>
       <c r="D21" s="29">
-        <f>Costs!D23</f>
+        <f>Costs!D25</f>
         <v/>
       </c>
       <c r="E21" s="29">
-        <f>Costs!E23</f>
+        <f>Costs!E25</f>
         <v/>
       </c>
       <c r="F21" s="29">
-        <f>Costs!F23</f>
+        <f>Costs!F25</f>
         <v/>
       </c>
       <c r="G21" s="29">
-        <f>Costs!G23</f>
+        <f>Costs!G25</f>
         <v/>
       </c>
       <c r="H21" s="29">
-        <f>Costs!H23</f>
+        <f>Costs!H25</f>
         <v/>
       </c>
       <c r="I21" s="29">
-        <f>Costs!I23</f>
+        <f>Costs!I25</f>
         <v/>
       </c>
       <c r="J21" s="29">
-        <f>Costs!J23</f>
+        <f>Costs!J25</f>
         <v/>
       </c>
       <c r="K21" s="29">
-        <f>Costs!K23</f>
+        <f>Costs!K25</f>
         <v/>
       </c>
       <c r="L21" s="29">
-        <f>Costs!L23</f>
+        <f>Costs!L25</f>
         <v/>
       </c>
     </row>
@@ -6249,34 +6393,34 @@
         </is>
       </c>
       <c r="C25" s="20" t="n">
-        <v>-90273.14292766612</v>
+        <v>-91018.2409668818</v>
       </c>
       <c r="D25" s="20" t="n">
-        <v>-184963.2589201104</v>
+        <v>-188286.6095083457</v>
       </c>
       <c r="E25" s="20" t="n">
-        <v>-264569.6480181803</v>
+        <v>-273766.7401593566</v>
       </c>
       <c r="F25" s="20" t="n">
-        <v>100051.8839755869</v>
+        <v>81279.88920434518</v>
       </c>
       <c r="G25" s="20" t="n">
-        <v>1749613.261851298</v>
+        <v>1719194.053925601</v>
       </c>
       <c r="H25" s="20" t="n">
-        <v>5171583.753182949</v>
+        <v>5134890.618719673</v>
       </c>
       <c r="I25" s="20" t="n">
-        <v>10034342.14279446</v>
+        <v>9991455.97114547</v>
       </c>
       <c r="J25" s="20" t="n">
-        <v>16149529.66560073</v>
+        <v>16103641.91334267</v>
       </c>
       <c r="K25" s="20" t="n">
-        <v>21797082.76585281</v>
+        <v>21750426.65716934</v>
       </c>
       <c r="L25" s="20" t="n">
-        <v>28258935.63712712</v>
+        <v>28212219.73399667</v>
       </c>
     </row>
     <row r="26">
@@ -7040,60 +7184,388 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>APPLICATIONS REQUIRED</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="n"/>
+      <c r="C49" s="12" t="n"/>
+      <c r="D49" s="12" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="12" t="n"/>
+      <c r="G49" s="12" t="n"/>
+      <c r="H49" s="12" t="n"/>
+      <c r="I49" s="12" t="n"/>
+      <c r="J49" s="12" t="n"/>
+      <c r="K49" s="12" t="n"/>
+      <c r="L49" s="12" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Python model</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>model.py</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D50" s="15" t="n">
+        <v>6706.666666666666</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>16562.56</v>
+      </c>
+      <c r="F50" s="15" t="n">
+        <v>32462.96296296296</v>
+      </c>
+      <c r="G50" s="15" t="n">
+        <v>51957.8947368421</v>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>61593.22033898304</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>70819.67213114753</v>
+      </c>
+      <c r="J50" s="15" t="n">
+        <v>74141.93548387096</v>
+      </c>
+      <c r="K50" s="15" t="n">
+        <v>73817.46031746031</v>
+      </c>
+      <c r="L50" s="15" t="n">
+        <v>72199.05511811023</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  This workbook</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>recalculated</t>
+        </is>
+      </c>
+      <c r="C51" s="33">
+        <f>Drivers!C51</f>
+        <v/>
+      </c>
+      <c r="D51" s="33">
+        <f>Drivers!D51</f>
+        <v/>
+      </c>
+      <c r="E51" s="33">
+        <f>Drivers!E51</f>
+        <v/>
+      </c>
+      <c r="F51" s="33">
+        <f>Drivers!F51</f>
+        <v/>
+      </c>
+      <c r="G51" s="33">
+        <f>Drivers!G51</f>
+        <v/>
+      </c>
+      <c r="H51" s="33">
+        <f>Drivers!H51</f>
+        <v/>
+      </c>
+      <c r="I51" s="33">
+        <f>Drivers!I51</f>
+        <v/>
+      </c>
+      <c r="J51" s="33">
+        <f>Drivers!J51</f>
+        <v/>
+      </c>
+      <c r="K51" s="33">
+        <f>Drivers!K51</f>
+        <v/>
+      </c>
+      <c r="L51" s="33">
+        <f>Drivers!L51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  VARIANCE</t>
+        </is>
+      </c>
+      <c r="B52" s="40" t="inlineStr">
+        <is>
+          <t>must be 0</t>
+        </is>
+      </c>
+      <c r="C52" s="90">
+        <f>ROUND(C51-C50,0)</f>
+        <v/>
+      </c>
+      <c r="D52" s="90">
+        <f>ROUND(D51-D50,0)</f>
+        <v/>
+      </c>
+      <c r="E52" s="90">
+        <f>ROUND(E51-E50,0)</f>
+        <v/>
+      </c>
+      <c r="F52" s="90">
+        <f>ROUND(F51-F50,0)</f>
+        <v/>
+      </c>
+      <c r="G52" s="90">
+        <f>ROUND(G51-G50,0)</f>
+        <v/>
+      </c>
+      <c r="H52" s="90">
+        <f>ROUND(H51-H50,0)</f>
+        <v/>
+      </c>
+      <c r="I52" s="90">
+        <f>ROUND(I51-I50,0)</f>
+        <v/>
+      </c>
+      <c r="J52" s="90">
+        <f>ROUND(J51-J50,0)</f>
+        <v/>
+      </c>
+      <c r="K52" s="90">
+        <f>ROUND(K51-K50,0)</f>
+        <v/>
+      </c>
+      <c r="L52" s="90">
+        <f>ROUND(L51-L50,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>ATHLETE VERIFICATION</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="n"/>
+      <c r="C54" s="12" t="n"/>
+      <c r="D54" s="12" t="n"/>
+      <c r="E54" s="12" t="n"/>
+      <c r="F54" s="12" t="n"/>
+      <c r="G54" s="12" t="n"/>
+      <c r="H54" s="12" t="n"/>
+      <c r="I54" s="12" t="n"/>
+      <c r="J54" s="12" t="n"/>
+      <c r="K54" s="12" t="n"/>
+      <c r="L54" s="12" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Python model</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>model.py</t>
+        </is>
+      </c>
+      <c r="C55" s="20" t="n">
+        <v>745.0980392156863</v>
+      </c>
+      <c r="D55" s="20" t="n">
+        <v>3323.350588235294</v>
+      </c>
+      <c r="E55" s="20" t="n">
+        <v>9197.09214117647</v>
+      </c>
+      <c r="F55" s="20" t="n">
+        <v>18771.99477124183</v>
+      </c>
+      <c r="G55" s="20" t="n">
+        <v>30419.20792569659</v>
+      </c>
+      <c r="H55" s="20" t="n">
+        <v>36693.13446327682</v>
+      </c>
+      <c r="I55" s="20" t="n">
+        <v>42886.17164898746</v>
+      </c>
+      <c r="J55" s="20" t="n">
+        <v>45887.7522580645</v>
+      </c>
+      <c r="K55" s="20" t="n">
+        <v>46656.10868347338</v>
+      </c>
+      <c r="L55" s="20" t="n">
+        <v>46715.90313046164</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  This workbook</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>recalculated</t>
+        </is>
+      </c>
+      <c r="C56" s="29">
+        <f>Costs!C13</f>
+        <v/>
+      </c>
+      <c r="D56" s="29">
+        <f>Costs!D13</f>
+        <v/>
+      </c>
+      <c r="E56" s="29">
+        <f>Costs!E13</f>
+        <v/>
+      </c>
+      <c r="F56" s="29">
+        <f>Costs!F13</f>
+        <v/>
+      </c>
+      <c r="G56" s="29">
+        <f>Costs!G13</f>
+        <v/>
+      </c>
+      <c r="H56" s="29">
+        <f>Costs!H13</f>
+        <v/>
+      </c>
+      <c r="I56" s="29">
+        <f>Costs!I13</f>
+        <v/>
+      </c>
+      <c r="J56" s="29">
+        <f>Costs!J13</f>
+        <v/>
+      </c>
+      <c r="K56" s="29">
+        <f>Costs!K13</f>
+        <v/>
+      </c>
+      <c r="L56" s="29">
+        <f>Costs!L13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  VARIANCE</t>
+        </is>
+      </c>
+      <c r="B57" s="40" t="inlineStr">
+        <is>
+          <t>must be 0</t>
+        </is>
+      </c>
+      <c r="C57" s="89">
+        <f>ROUND(C56-C55,0)</f>
+        <v/>
+      </c>
+      <c r="D57" s="89">
+        <f>ROUND(D56-D55,0)</f>
+        <v/>
+      </c>
+      <c r="E57" s="89">
+        <f>ROUND(E56-E55,0)</f>
+        <v/>
+      </c>
+      <c r="F57" s="89">
+        <f>ROUND(F56-F55,0)</f>
+        <v/>
+      </c>
+      <c r="G57" s="89">
+        <f>ROUND(G56-G55,0)</f>
+        <v/>
+      </c>
+      <c r="H57" s="89">
+        <f>ROUND(H56-H55,0)</f>
+        <v/>
+      </c>
+      <c r="I57" s="89">
+        <f>ROUND(I56-I55,0)</f>
+        <v/>
+      </c>
+      <c r="J57" s="89">
+        <f>ROUND(J56-J55,0)</f>
+        <v/>
+      </c>
+      <c r="K57" s="89">
+        <f>ROUND(K56-K55,0)</f>
+        <v/>
+      </c>
+      <c r="L57" s="89">
+        <f>ROUND(L56-L55,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Balance sheet check (from BalanceSheet, must be zero):</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="39" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">  Assets less liabilities and equity</t>
         </is>
       </c>
-      <c r="B50" s="40" t="inlineStr">
+      <c r="B60" s="40" t="inlineStr">
         <is>
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C50" s="91">
+      <c r="C60" s="91">
         <f>BalanceSheet!C20</f>
         <v/>
       </c>
-      <c r="D50" s="91">
+      <c r="D60" s="91">
         <f>BalanceSheet!D20</f>
         <v/>
       </c>
-      <c r="E50" s="91">
+      <c r="E60" s="91">
         <f>BalanceSheet!E20</f>
         <v/>
       </c>
-      <c r="F50" s="91">
+      <c r="F60" s="91">
         <f>BalanceSheet!F20</f>
         <v/>
       </c>
-      <c r="G50" s="91">
+      <c r="G60" s="91">
         <f>BalanceSheet!G20</f>
         <v/>
       </c>
-      <c r="H50" s="91">
+      <c r="H60" s="91">
         <f>BalanceSheet!H20</f>
         <v/>
       </c>
-      <c r="I50" s="91">
+      <c r="I60" s="91">
         <f>BalanceSheet!I20</f>
         <v/>
       </c>
-      <c r="J50" s="91">
+      <c r="J60" s="91">
         <f>BalanceSheet!J20</f>
         <v/>
       </c>
-      <c r="K50" s="91">
+      <c r="K60" s="91">
         <f>BalanceSheet!K20</f>
         <v/>
       </c>
-      <c r="L50" s="91">
+      <c r="L60" s="91">
         <f>BalanceSheet!L20</f>
         <v/>
       </c>
@@ -7116,7 +7588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -9815,7 +10287,7 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>VALUATION</t>
+          <t>ADMISSION — the gate between an applicant and an athlete</t>
         </is>
       </c>
       <c r="B71" s="12" t="n"/>
@@ -9833,16 +10305,16 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>WACC / discount rate</t>
+          <t>Admission rate — direct applicants</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>% admitted</t>
         </is>
       </c>
       <c r="C72" s="16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D72" s="21">
         <f>C72</f>
@@ -9880,25 +10352,25 @@
         <f>C72</f>
         <v/>
       </c>
-      <c r="N72" s="22" t="inlineStr">
-        <is>
-          <t>Early-stage venture hurdle</t>
+      <c r="N72" s="17" t="inlineStr">
+        <is>
+          <t>ops-load output of scripts/admission_stress.py</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>Review rate — direct applicants</t>
         </is>
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>% needing a human</t>
         </is>
       </c>
       <c r="C73" s="16" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="D73" s="21">
         <f>C73</f>
@@ -9936,76 +10408,81 @@
         <f>C73</f>
         <v/>
       </c>
+      <c r="N73" s="17" t="inlineStr">
+        <is>
+          <t>ops-load output of scripts/admission_stress.py</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>Exit revenue multiple</t>
+          <t>Admission rate — club-nominated</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C74" s="19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D74" s="30">
+          <t>% admitted</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D74" s="21">
         <f>C74</f>
         <v/>
       </c>
-      <c r="E74" s="30">
+      <c r="E74" s="21">
         <f>C74</f>
         <v/>
       </c>
-      <c r="F74" s="30">
+      <c r="F74" s="21">
         <f>C74</f>
         <v/>
       </c>
-      <c r="G74" s="30">
+      <c r="G74" s="21">
         <f>C74</f>
         <v/>
       </c>
-      <c r="H74" s="30">
+      <c r="H74" s="21">
         <f>C74</f>
         <v/>
       </c>
-      <c r="I74" s="30">
+      <c r="I74" s="21">
         <f>C74</f>
         <v/>
       </c>
-      <c r="J74" s="30">
+      <c r="J74" s="21">
         <f>C74</f>
         <v/>
       </c>
-      <c r="K74" s="30">
+      <c r="K74" s="21">
         <f>C74</f>
         <v/>
       </c>
-      <c r="L74" s="30">
+      <c r="L74" s="21">
         <f>C74</f>
         <v/>
       </c>
       <c r="N74" s="22" t="inlineStr">
         <is>
-          <t>Blended marketplace + SaaS comparables</t>
+          <t>ESTIMATE — a verified club's floor carries more of them past the bar</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>Risk-free rate (Spanish 10Y)</t>
+          <t>Review rate — club-nominated</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C75" s="36" t="n">
-        <v>0.032</v>
+          <t>% needing a human</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="n">
+        <v>0.18</v>
       </c>
       <c r="D75" s="21">
         <f>C75</f>
@@ -10045,58 +10522,454 @@
       </c>
       <c r="N75" s="22" t="inlineStr">
         <is>
-          <t>Spanish 10Y government bond, mid-2026</t>
+          <t>ESTIMATE</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
+          <t>Applicants arriving via a club</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>% of applicants</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F76" s="16" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G76" s="16" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H76" s="16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I76" s="16" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J76" s="16" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K76" s="16" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L76" s="16" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N76" s="22" t="inlineStr">
+        <is>
+          <t>Grows as federation and club partnerships land</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>Minutes per manual review</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="C77" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" s="30">
+        <f>C77</f>
+        <v/>
+      </c>
+      <c r="E77" s="30">
+        <f>C77</f>
+        <v/>
+      </c>
+      <c r="F77" s="30">
+        <f>C77</f>
+        <v/>
+      </c>
+      <c r="G77" s="30">
+        <f>C77</f>
+        <v/>
+      </c>
+      <c r="H77" s="30">
+        <f>C77</f>
+        <v/>
+      </c>
+      <c r="I77" s="30">
+        <f>C77</f>
+        <v/>
+      </c>
+      <c r="J77" s="30">
+        <f>C77</f>
+        <v/>
+      </c>
+      <c r="K77" s="30">
+        <f>C77</f>
+        <v/>
+      </c>
+      <c r="L77" s="30">
+        <f>C77</f>
+        <v/>
+      </c>
+      <c r="N77" s="22" t="inlineStr">
+        <is>
+          <t>Open the link, decide whether it names the applicant</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>Productive hours per reviewer-year</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="n">
+        <v>1700</v>
+      </c>
+      <c r="D78" s="33">
+        <f>C78</f>
+        <v/>
+      </c>
+      <c r="E78" s="33">
+        <f>C78</f>
+        <v/>
+      </c>
+      <c r="F78" s="33">
+        <f>C78</f>
+        <v/>
+      </c>
+      <c r="G78" s="33">
+        <f>C78</f>
+        <v/>
+      </c>
+      <c r="H78" s="33">
+        <f>C78</f>
+        <v/>
+      </c>
+      <c r="I78" s="33">
+        <f>C78</f>
+        <v/>
+      </c>
+      <c r="J78" s="33">
+        <f>C78</f>
+        <v/>
+      </c>
+      <c r="K78" s="33">
+        <f>C78</f>
+        <v/>
+      </c>
+      <c r="L78" s="33">
+        <f>C78</f>
+        <v/>
+      </c>
+      <c r="N78" s="22" t="inlineStr">
+        <is>
+          <t>Prices review time off the same loaded salary line</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>VALUATION</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="n"/>
+      <c r="C80" s="12" t="n"/>
+      <c r="D80" s="12" t="n"/>
+      <c r="E80" s="12" t="n"/>
+      <c r="F80" s="12" t="n"/>
+      <c r="G80" s="12" t="n"/>
+      <c r="H80" s="12" t="n"/>
+      <c r="I80" s="12" t="n"/>
+      <c r="J80" s="12" t="n"/>
+      <c r="K80" s="12" t="n"/>
+      <c r="L80" s="12" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>WACC / discount rate</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D81" s="21">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="E81" s="21">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="F81" s="21">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="G81" s="21">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="H81" s="21">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="I81" s="21">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="J81" s="21">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="K81" s="21">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="L81" s="21">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="N81" s="22" t="inlineStr">
+        <is>
+          <t>Early-stage venture hurdle</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D82" s="21">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="E82" s="21">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="F82" s="21">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="G82" s="21">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="H82" s="21">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="I82" s="21">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="J82" s="21">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="K82" s="21">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="L82" s="21">
+        <f>C82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>Exit revenue multiple</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C83" s="19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D83" s="30">
+        <f>C83</f>
+        <v/>
+      </c>
+      <c r="E83" s="30">
+        <f>C83</f>
+        <v/>
+      </c>
+      <c r="F83" s="30">
+        <f>C83</f>
+        <v/>
+      </c>
+      <c r="G83" s="30">
+        <f>C83</f>
+        <v/>
+      </c>
+      <c r="H83" s="30">
+        <f>C83</f>
+        <v/>
+      </c>
+      <c r="I83" s="30">
+        <f>C83</f>
+        <v/>
+      </c>
+      <c r="J83" s="30">
+        <f>C83</f>
+        <v/>
+      </c>
+      <c r="K83" s="30">
+        <f>C83</f>
+        <v/>
+      </c>
+      <c r="L83" s="30">
+        <f>C83</f>
+        <v/>
+      </c>
+      <c r="N83" s="22" t="inlineStr">
+        <is>
+          <t>Blended marketplace + SaaS comparables</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>Risk-free rate (Spanish 10Y)</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C84" s="36" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="D84" s="21">
+        <f>C84</f>
+        <v/>
+      </c>
+      <c r="E84" s="21">
+        <f>C84</f>
+        <v/>
+      </c>
+      <c r="F84" s="21">
+        <f>C84</f>
+        <v/>
+      </c>
+      <c r="G84" s="21">
+        <f>C84</f>
+        <v/>
+      </c>
+      <c r="H84" s="21">
+        <f>C84</f>
+        <v/>
+      </c>
+      <c r="I84" s="21">
+        <f>C84</f>
+        <v/>
+      </c>
+      <c r="J84" s="21">
+        <f>C84</f>
+        <v/>
+      </c>
+      <c r="K84" s="21">
+        <f>C84</f>
+        <v/>
+      </c>
+      <c r="L84" s="21">
+        <f>C84</f>
+        <v/>
+      </c>
+      <c r="N84" s="22" t="inlineStr">
+        <is>
+          <t>Spanish 10Y government bond, mid-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
           <t>Founder alternative return</t>
         </is>
       </c>
-      <c r="B76" s="14" t="inlineStr">
+      <c r="B85" s="14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C76" s="16" t="n">
+      <c r="C85" s="16" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="D76" s="21">
-        <f>C76</f>
-        <v/>
-      </c>
-      <c r="E76" s="21">
-        <f>C76</f>
-        <v/>
-      </c>
-      <c r="F76" s="21">
-        <f>C76</f>
-        <v/>
-      </c>
-      <c r="G76" s="21">
-        <f>C76</f>
-        <v/>
-      </c>
-      <c r="H76" s="21">
-        <f>C76</f>
-        <v/>
-      </c>
-      <c r="I76" s="21">
-        <f>C76</f>
-        <v/>
-      </c>
-      <c r="J76" s="21">
-        <f>C76</f>
-        <v/>
-      </c>
-      <c r="K76" s="21">
-        <f>C76</f>
-        <v/>
-      </c>
-      <c r="L76" s="21">
-        <f>C76</f>
+      <c r="D85" s="21">
+        <f>C85</f>
+        <v/>
+      </c>
+      <c r="E85" s="21">
+        <f>C85</f>
+        <v/>
+      </c>
+      <c r="F85" s="21">
+        <f>C85</f>
+        <v/>
+      </c>
+      <c r="G85" s="21">
+        <f>C85</f>
+        <v/>
+      </c>
+      <c r="H85" s="21">
+        <f>C85</f>
+        <v/>
+      </c>
+      <c r="I85" s="21">
+        <f>C85</f>
+        <v/>
+      </c>
+      <c r="J85" s="21">
+        <f>C85</f>
+        <v/>
+      </c>
+      <c r="K85" s="21">
+        <f>C85</f>
+        <v/>
+      </c>
+      <c r="L85" s="21">
+        <f>C85</f>
         <v/>
       </c>
     </row>
@@ -10118,7 +10991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -12009,6 +12882,284 @@
       </c>
       <c r="L46" s="33">
         <f>MAX(0,Assumptions!L31-IF(10=1,0,Assumptions!K31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>ADMISSION FUNNEL</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="n"/>
+      <c r="C48" s="12" t="n"/>
+      <c r="D48" s="12" t="n"/>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="12" t="n"/>
+      <c r="G48" s="12" t="n"/>
+      <c r="H48" s="12" t="n"/>
+      <c r="I48" s="12" t="n"/>
+      <c r="J48" s="12" t="n"/>
+      <c r="K48" s="12" t="n"/>
+      <c r="L48" s="12" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>Blended admission rate</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>weighted by channel</t>
+        </is>
+      </c>
+      <c r="C49" s="21">
+        <f>Assumptions!C76*Assumptions!C74+(1-Assumptions!C76)*Assumptions!C72</f>
+        <v/>
+      </c>
+      <c r="D49" s="21">
+        <f>Assumptions!D76*Assumptions!D74+(1-Assumptions!D76)*Assumptions!D72</f>
+        <v/>
+      </c>
+      <c r="E49" s="21">
+        <f>Assumptions!E76*Assumptions!E74+(1-Assumptions!E76)*Assumptions!E72</f>
+        <v/>
+      </c>
+      <c r="F49" s="21">
+        <f>Assumptions!F76*Assumptions!F74+(1-Assumptions!F76)*Assumptions!F72</f>
+        <v/>
+      </c>
+      <c r="G49" s="21">
+        <f>Assumptions!G76*Assumptions!G74+(1-Assumptions!G76)*Assumptions!G72</f>
+        <v/>
+      </c>
+      <c r="H49" s="21">
+        <f>Assumptions!H76*Assumptions!H74+(1-Assumptions!H76)*Assumptions!H72</f>
+        <v/>
+      </c>
+      <c r="I49" s="21">
+        <f>Assumptions!I76*Assumptions!I74+(1-Assumptions!I76)*Assumptions!I72</f>
+        <v/>
+      </c>
+      <c r="J49" s="21">
+        <f>Assumptions!J76*Assumptions!J74+(1-Assumptions!J76)*Assumptions!J72</f>
+        <v/>
+      </c>
+      <c r="K49" s="21">
+        <f>Assumptions!K76*Assumptions!K74+(1-Assumptions!K76)*Assumptions!K72</f>
+        <v/>
+      </c>
+      <c r="L49" s="21">
+        <f>Assumptions!L76*Assumptions!L74+(1-Assumptions!L76)*Assumptions!L72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>Blended review rate</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>weighted by channel</t>
+        </is>
+      </c>
+      <c r="C50" s="21">
+        <f>Assumptions!C76*Assumptions!C75+(1-Assumptions!C76)*Assumptions!C73</f>
+        <v/>
+      </c>
+      <c r="D50" s="21">
+        <f>Assumptions!D76*Assumptions!D75+(1-Assumptions!D76)*Assumptions!D73</f>
+        <v/>
+      </c>
+      <c r="E50" s="21">
+        <f>Assumptions!E76*Assumptions!E75+(1-Assumptions!E76)*Assumptions!E73</f>
+        <v/>
+      </c>
+      <c r="F50" s="21">
+        <f>Assumptions!F76*Assumptions!F75+(1-Assumptions!F76)*Assumptions!F73</f>
+        <v/>
+      </c>
+      <c r="G50" s="21">
+        <f>Assumptions!G76*Assumptions!G75+(1-Assumptions!G76)*Assumptions!G73</f>
+        <v/>
+      </c>
+      <c r="H50" s="21">
+        <f>Assumptions!H76*Assumptions!H75+(1-Assumptions!H76)*Assumptions!H73</f>
+        <v/>
+      </c>
+      <c r="I50" s="21">
+        <f>Assumptions!I76*Assumptions!I75+(1-Assumptions!I76)*Assumptions!I73</f>
+        <v/>
+      </c>
+      <c r="J50" s="21">
+        <f>Assumptions!J76*Assumptions!J75+(1-Assumptions!J76)*Assumptions!J73</f>
+        <v/>
+      </c>
+      <c r="K50" s="21">
+        <f>Assumptions!K76*Assumptions!K75+(1-Assumptions!K76)*Assumptions!K73</f>
+        <v/>
+      </c>
+      <c r="L50" s="21">
+        <f>Assumptions!L76*Assumptions!L75+(1-Assumptions!L76)*Assumptions!L73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>Applications required</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>gross adds / admission rate</t>
+        </is>
+      </c>
+      <c r="C51" s="38">
+        <f>C38/C49</f>
+        <v/>
+      </c>
+      <c r="D51" s="38">
+        <f>D38/D49</f>
+        <v/>
+      </c>
+      <c r="E51" s="38">
+        <f>E38/E49</f>
+        <v/>
+      </c>
+      <c r="F51" s="38">
+        <f>F38/F49</f>
+        <v/>
+      </c>
+      <c r="G51" s="38">
+        <f>G38/G49</f>
+        <v/>
+      </c>
+      <c r="H51" s="38">
+        <f>H38/H49</f>
+        <v/>
+      </c>
+      <c r="I51" s="38">
+        <f>I38/I49</f>
+        <v/>
+      </c>
+      <c r="J51" s="38">
+        <f>J38/J49</f>
+        <v/>
+      </c>
+      <c r="K51" s="38">
+        <f>K38/K49</f>
+        <v/>
+      </c>
+      <c r="L51" s="38">
+        <f>L38/L49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>Manual reviews</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>applications x review rate</t>
+        </is>
+      </c>
+      <c r="C52" s="38">
+        <f>C51*C50</f>
+        <v/>
+      </c>
+      <c r="D52" s="38">
+        <f>D51*D50</f>
+        <v/>
+      </c>
+      <c r="E52" s="38">
+        <f>E51*E50</f>
+        <v/>
+      </c>
+      <c r="F52" s="38">
+        <f>F51*F50</f>
+        <v/>
+      </c>
+      <c r="G52" s="38">
+        <f>G51*G50</f>
+        <v/>
+      </c>
+      <c r="H52" s="38">
+        <f>H51*H50</f>
+        <v/>
+      </c>
+      <c r="I52" s="38">
+        <f>I51*I50</f>
+        <v/>
+      </c>
+      <c r="J52" s="38">
+        <f>J51*J50</f>
+        <v/>
+      </c>
+      <c r="K52" s="38">
+        <f>K51*K50</f>
+        <v/>
+      </c>
+      <c r="L52" s="38">
+        <f>L51*L50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>Reviewer FTE implied</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>the real constraint, not the euros</t>
+        </is>
+      </c>
+      <c r="C53" s="24">
+        <f>C52*Assumptions!C77/60/Assumptions!C78</f>
+        <v/>
+      </c>
+      <c r="D53" s="24">
+        <f>D52*Assumptions!D77/60/Assumptions!D78</f>
+        <v/>
+      </c>
+      <c r="E53" s="24">
+        <f>E52*Assumptions!E77/60/Assumptions!E78</f>
+        <v/>
+      </c>
+      <c r="F53" s="24">
+        <f>F52*Assumptions!F77/60/Assumptions!F78</f>
+        <v/>
+      </c>
+      <c r="G53" s="24">
+        <f>G52*Assumptions!G77/60/Assumptions!G78</f>
+        <v/>
+      </c>
+      <c r="H53" s="24">
+        <f>H52*Assumptions!H77/60/Assumptions!H78</f>
+        <v/>
+      </c>
+      <c r="I53" s="24">
+        <f>I52*Assumptions!I77/60/Assumptions!I78</f>
+        <v/>
+      </c>
+      <c r="J53" s="24">
+        <f>J52*Assumptions!J77/60/Assumptions!J78</f>
+        <v/>
+      </c>
+      <c r="K53" s="24">
+        <f>K52*Assumptions!K77/60/Assumptions!K78</f>
+        <v/>
+      </c>
+      <c r="L53" s="24">
+        <f>L52*Assumptions!L77/60/Assumptions!L78</f>
         <v/>
       </c>
     </row>
@@ -12964,7 +14115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -13517,464 +14668,568 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Athlete verification</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>reviews x minutes x hourly</t>
+        </is>
+      </c>
+      <c r="C13" s="29">
+        <f>Drivers!C52*Assumptions!C77/60*(Assumptions!C57/Assumptions!C78)</f>
+        <v/>
+      </c>
+      <c r="D13" s="29">
+        <f>Drivers!D52*Assumptions!D77/60*(Assumptions!D57/Assumptions!D78)</f>
+        <v/>
+      </c>
+      <c r="E13" s="29">
+        <f>Drivers!E52*Assumptions!E77/60*(Assumptions!E57/Assumptions!E78)</f>
+        <v/>
+      </c>
+      <c r="F13" s="29">
+        <f>Drivers!F52*Assumptions!F77/60*(Assumptions!F57/Assumptions!F78)</f>
+        <v/>
+      </c>
+      <c r="G13" s="29">
+        <f>Drivers!G52*Assumptions!G77/60*(Assumptions!G57/Assumptions!G78)</f>
+        <v/>
+      </c>
+      <c r="H13" s="29">
+        <f>Drivers!H52*Assumptions!H77/60*(Assumptions!H57/Assumptions!H78)</f>
+        <v/>
+      </c>
+      <c r="I13" s="29">
+        <f>Drivers!I52*Assumptions!I77/60*(Assumptions!I57/Assumptions!I78)</f>
+        <v/>
+      </c>
+      <c r="J13" s="29">
+        <f>Drivers!J52*Assumptions!J77/60*(Assumptions!J57/Assumptions!J78)</f>
+        <v/>
+      </c>
+      <c r="K13" s="29">
+        <f>Drivers!K52*Assumptions!K77/60*(Assumptions!K57/Assumptions!K78)</f>
+        <v/>
+      </c>
+      <c r="L13" s="29">
+        <f>Drivers!L52*Assumptions!L77/60*(Assumptions!L57/Assumptions!L78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="45" t="inlineStr">
         <is>
           <t>TOTAL COST OF SALES</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr"/>
-      <c r="C13" s="46">
-        <f>C7+C8+C10+C12</f>
-        <v/>
-      </c>
-      <c r="D13" s="46">
-        <f>D7+D8+D10+D12</f>
-        <v/>
-      </c>
-      <c r="E13" s="46">
-        <f>E7+E8+E10+E12</f>
-        <v/>
-      </c>
-      <c r="F13" s="46">
-        <f>F7+F8+F10+F12</f>
-        <v/>
-      </c>
-      <c r="G13" s="46">
-        <f>G7+G8+G10+G12</f>
-        <v/>
-      </c>
-      <c r="H13" s="46">
-        <f>H7+H8+H10+H12</f>
-        <v/>
-      </c>
-      <c r="I13" s="46">
-        <f>I7+I8+I10+I12</f>
-        <v/>
-      </c>
-      <c r="J13" s="46">
-        <f>J7+J8+J10+J12</f>
-        <v/>
-      </c>
-      <c r="K13" s="46">
-        <f>K7+K8+K10+K12</f>
-        <v/>
-      </c>
-      <c r="L13" s="46">
-        <f>L7+L8+L10+L12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr"/>
+      <c r="C14" s="46">
+        <f>C7+C8+C10+C12+C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="46">
+        <f>D7+D8+D10+D12+D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="46">
+        <f>E7+E8+E10+E12+E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="46">
+        <f>F7+F8+F10+F12+F13</f>
+        <v/>
+      </c>
+      <c r="G14" s="46">
+        <f>G7+G8+G10+G12+G13</f>
+        <v/>
+      </c>
+      <c r="H14" s="46">
+        <f>H7+H8+H10+H12+H13</f>
+        <v/>
+      </c>
+      <c r="I14" s="46">
+        <f>I7+I8+I10+I12+I13</f>
+        <v/>
+      </c>
+      <c r="J14" s="46">
+        <f>J7+J8+J10+J12+J13</f>
+        <v/>
+      </c>
+      <c r="K14" s="46">
+        <f>K7+K8+K10+K12+K13</f>
+        <v/>
+      </c>
+      <c r="L14" s="46">
+        <f>L7+L8+L10+L12+L13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>OPERATING COSTS</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="12" t="n"/>
-      <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>People</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>FTE x loaded salary</t>
-        </is>
-      </c>
-      <c r="C16" s="29">
-        <f>Assumptions!C56*Assumptions!C57</f>
-        <v/>
-      </c>
-      <c r="D16" s="29">
-        <f>Assumptions!D56*Assumptions!D57</f>
-        <v/>
-      </c>
-      <c r="E16" s="29">
-        <f>Assumptions!E56*Assumptions!E57</f>
-        <v/>
-      </c>
-      <c r="F16" s="29">
-        <f>Assumptions!F56*Assumptions!F57</f>
-        <v/>
-      </c>
-      <c r="G16" s="29">
-        <f>Assumptions!G56*Assumptions!G57</f>
-        <v/>
-      </c>
-      <c r="H16" s="29">
-        <f>Assumptions!H56*Assumptions!H57</f>
-        <v/>
-      </c>
-      <c r="I16" s="29">
-        <f>Assumptions!I56*Assumptions!I57</f>
-        <v/>
-      </c>
-      <c r="J16" s="29">
-        <f>Assumptions!J56*Assumptions!J57</f>
-        <v/>
-      </c>
-      <c r="K16" s="29">
-        <f>Assumptions!K56*Assumptions!K57</f>
-        <v/>
-      </c>
-      <c r="L16" s="29">
-        <f>Assumptions!L56*Assumptions!L57</f>
-        <v/>
-      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Athlete acquisition — niche</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>gross adds x CAC</t>
+          <t>FTE x loaded salary</t>
         </is>
       </c>
       <c r="C17" s="29">
-        <f>Drivers!C11*Assumptions!C17</f>
+        <f>Assumptions!C56*Assumptions!C57</f>
         <v/>
       </c>
       <c r="D17" s="29">
-        <f>Drivers!D11*Assumptions!D17</f>
+        <f>Assumptions!D56*Assumptions!D57</f>
         <v/>
       </c>
       <c r="E17" s="29">
-        <f>Drivers!E11*Assumptions!E17</f>
+        <f>Assumptions!E56*Assumptions!E57</f>
         <v/>
       </c>
       <c r="F17" s="29">
-        <f>Drivers!F11*Assumptions!F17</f>
+        <f>Assumptions!F56*Assumptions!F57</f>
         <v/>
       </c>
       <c r="G17" s="29">
-        <f>Drivers!G11*Assumptions!G17</f>
+        <f>Assumptions!G56*Assumptions!G57</f>
         <v/>
       </c>
       <c r="H17" s="29">
-        <f>Drivers!H11*Assumptions!H17</f>
+        <f>Assumptions!H56*Assumptions!H57</f>
         <v/>
       </c>
       <c r="I17" s="29">
-        <f>Drivers!I11*Assumptions!I17</f>
+        <f>Assumptions!I56*Assumptions!I57</f>
         <v/>
       </c>
       <c r="J17" s="29">
-        <f>Drivers!J11*Assumptions!J17</f>
+        <f>Assumptions!J56*Assumptions!J57</f>
         <v/>
       </c>
       <c r="K17" s="29">
-        <f>Drivers!K11*Assumptions!K17</f>
+        <f>Assumptions!K56*Assumptions!K57</f>
         <v/>
       </c>
       <c r="L17" s="29">
-        <f>Drivers!L11*Assumptions!L17</f>
+        <f>Assumptions!L56*Assumptions!L57</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Athlete acquisition — popular</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr"/>
+          <t>Athlete acquisition — niche</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>gross adds x CAC</t>
+        </is>
+      </c>
       <c r="C18" s="29">
-        <f>Drivers!C24*Assumptions!C28</f>
+        <f>Drivers!C11*Assumptions!C17</f>
         <v/>
       </c>
       <c r="D18" s="29">
-        <f>Drivers!D24*Assumptions!D28</f>
+        <f>Drivers!D11*Assumptions!D17</f>
         <v/>
       </c>
       <c r="E18" s="29">
-        <f>Drivers!E24*Assumptions!E28</f>
+        <f>Drivers!E11*Assumptions!E17</f>
         <v/>
       </c>
       <c r="F18" s="29">
-        <f>Drivers!F24*Assumptions!F28</f>
+        <f>Drivers!F11*Assumptions!F17</f>
         <v/>
       </c>
       <c r="G18" s="29">
-        <f>Drivers!G24*Assumptions!G28</f>
+        <f>Drivers!G11*Assumptions!G17</f>
         <v/>
       </c>
       <c r="H18" s="29">
-        <f>Drivers!H24*Assumptions!H28</f>
+        <f>Drivers!H11*Assumptions!H17</f>
         <v/>
       </c>
       <c r="I18" s="29">
-        <f>Drivers!I24*Assumptions!I28</f>
+        <f>Drivers!I11*Assumptions!I17</f>
         <v/>
       </c>
       <c r="J18" s="29">
-        <f>Drivers!J24*Assumptions!J28</f>
+        <f>Drivers!J11*Assumptions!J17</f>
         <v/>
       </c>
       <c r="K18" s="29">
-        <f>Drivers!K24*Assumptions!K28</f>
+        <f>Drivers!K11*Assumptions!K17</f>
         <v/>
       </c>
       <c r="L18" s="29">
-        <f>Drivers!L24*Assumptions!L28</f>
+        <f>Drivers!L11*Assumptions!L17</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Sponsor acquisition</t>
+          <t>Athlete acquisition — popular</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr"/>
       <c r="C19" s="29">
+        <f>Drivers!C24*Assumptions!C28</f>
+        <v/>
+      </c>
+      <c r="D19" s="29">
+        <f>Drivers!D24*Assumptions!D28</f>
+        <v/>
+      </c>
+      <c r="E19" s="29">
+        <f>Drivers!E24*Assumptions!E28</f>
+        <v/>
+      </c>
+      <c r="F19" s="29">
+        <f>Drivers!F24*Assumptions!F28</f>
+        <v/>
+      </c>
+      <c r="G19" s="29">
+        <f>Drivers!G24*Assumptions!G28</f>
+        <v/>
+      </c>
+      <c r="H19" s="29">
+        <f>Drivers!H24*Assumptions!H28</f>
+        <v/>
+      </c>
+      <c r="I19" s="29">
+        <f>Drivers!I24*Assumptions!I28</f>
+        <v/>
+      </c>
+      <c r="J19" s="29">
+        <f>Drivers!J24*Assumptions!J28</f>
+        <v/>
+      </c>
+      <c r="K19" s="29">
+        <f>Drivers!K24*Assumptions!K28</f>
+        <v/>
+      </c>
+      <c r="L19" s="29">
+        <f>Drivers!L24*Assumptions!L28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Sponsor acquisition</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr"/>
+      <c r="C20" s="29">
         <f>Drivers!C46*Assumptions!C34</f>
         <v/>
       </c>
-      <c r="D19" s="29">
+      <c r="D20" s="29">
         <f>Drivers!D46*Assumptions!D34</f>
         <v/>
       </c>
-      <c r="E19" s="29">
+      <c r="E20" s="29">
         <f>Drivers!E46*Assumptions!E34</f>
         <v/>
       </c>
-      <c r="F19" s="29">
+      <c r="F20" s="29">
         <f>Drivers!F46*Assumptions!F34</f>
         <v/>
       </c>
-      <c r="G19" s="29">
+      <c r="G20" s="29">
         <f>Drivers!G46*Assumptions!G34</f>
         <v/>
       </c>
-      <c r="H19" s="29">
+      <c r="H20" s="29">
         <f>Drivers!H46*Assumptions!H34</f>
         <v/>
       </c>
-      <c r="I19" s="29">
+      <c r="I20" s="29">
         <f>Drivers!I46*Assumptions!I34</f>
         <v/>
       </c>
-      <c r="J19" s="29">
+      <c r="J20" s="29">
         <f>Drivers!J46*Assumptions!J34</f>
         <v/>
       </c>
-      <c r="K19" s="29">
+      <c r="K20" s="29">
         <f>Drivers!K46*Assumptions!K34</f>
         <v/>
       </c>
-      <c r="L19" s="29">
+      <c r="L20" s="29">
         <f>Drivers!L46*Assumptions!L34</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="39" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>Total marketing / CAC</t>
         </is>
       </c>
-      <c r="B20" s="40" t="inlineStr"/>
-      <c r="C20" s="44">
-        <f>SUM(C17:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="44">
-        <f>SUM(D17:D19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="44">
-        <f>SUM(E17:E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="44">
-        <f>SUM(F17:F19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="44">
-        <f>SUM(G17:G19)</f>
-        <v/>
-      </c>
-      <c r="H20" s="44">
-        <f>SUM(H17:H19)</f>
-        <v/>
-      </c>
-      <c r="I20" s="44">
-        <f>SUM(I17:I19)</f>
-        <v/>
-      </c>
-      <c r="J20" s="44">
-        <f>SUM(J17:J19)</f>
-        <v/>
-      </c>
-      <c r="K20" s="44">
-        <f>SUM(K17:K19)</f>
-        <v/>
-      </c>
-      <c r="L20" s="44">
-        <f>SUM(L17:L19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>Legal &amp; compliance</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr"/>
-      <c r="C21" s="29">
-        <f>Assumptions!C58</f>
-        <v/>
-      </c>
-      <c r="D21" s="29">
-        <f>Assumptions!D58</f>
-        <v/>
-      </c>
-      <c r="E21" s="29">
-        <f>Assumptions!E58</f>
-        <v/>
-      </c>
-      <c r="F21" s="29">
-        <f>Assumptions!F58</f>
-        <v/>
-      </c>
-      <c r="G21" s="29">
-        <f>Assumptions!G58</f>
-        <v/>
-      </c>
-      <c r="H21" s="29">
-        <f>Assumptions!H58</f>
-        <v/>
-      </c>
-      <c r="I21" s="29">
-        <f>Assumptions!I58</f>
-        <v/>
-      </c>
-      <c r="J21" s="29">
-        <f>Assumptions!J58</f>
-        <v/>
-      </c>
-      <c r="K21" s="29">
-        <f>Assumptions!K58</f>
-        <v/>
-      </c>
-      <c r="L21" s="29">
-        <f>Assumptions!L58</f>
+      <c r="B21" s="40" t="inlineStr"/>
+      <c r="C21" s="44">
+        <f>SUM(C18:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="44">
+        <f>SUM(D18:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="44">
+        <f>SUM(E18:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="44">
+        <f>SUM(F18:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="44">
+        <f>SUM(G18:G20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="44">
+        <f>SUM(H18:H20)</f>
+        <v/>
+      </c>
+      <c r="I21" s="44">
+        <f>SUM(I18:I20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="44">
+        <f>SUM(J18:J20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="44">
+        <f>SUM(K18:K20)</f>
+        <v/>
+      </c>
+      <c r="L21" s="44">
+        <f>SUM(L18:L20)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
+          <t xml:space="preserve">  memo: athlete marketing per application</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>CAC is per ADMITTED athlete</t>
+        </is>
+      </c>
+      <c r="C22" s="28">
+        <f>(C18+C19)/Drivers!C51</f>
+        <v/>
+      </c>
+      <c r="D22" s="28">
+        <f>(D18+D19)/Drivers!D51</f>
+        <v/>
+      </c>
+      <c r="E22" s="28">
+        <f>(E18+E19)/Drivers!E51</f>
+        <v/>
+      </c>
+      <c r="F22" s="28">
+        <f>(F18+F19)/Drivers!F51</f>
+        <v/>
+      </c>
+      <c r="G22" s="28">
+        <f>(G18+G19)/Drivers!G51</f>
+        <v/>
+      </c>
+      <c r="H22" s="28">
+        <f>(H18+H19)/Drivers!H51</f>
+        <v/>
+      </c>
+      <c r="I22" s="28">
+        <f>(I18+I19)/Drivers!I51</f>
+        <v/>
+      </c>
+      <c r="J22" s="28">
+        <f>(J18+J19)/Drivers!J51</f>
+        <v/>
+      </c>
+      <c r="K22" s="28">
+        <f>(K18+K19)/Drivers!K51</f>
+        <v/>
+      </c>
+      <c r="L22" s="28">
+        <f>(L18+L19)/Drivers!L51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Legal &amp; compliance</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr"/>
+      <c r="C23" s="29">
+        <f>Assumptions!C58</f>
+        <v/>
+      </c>
+      <c r="D23" s="29">
+        <f>Assumptions!D58</f>
+        <v/>
+      </c>
+      <c r="E23" s="29">
+        <f>Assumptions!E58</f>
+        <v/>
+      </c>
+      <c r="F23" s="29">
+        <f>Assumptions!F58</f>
+        <v/>
+      </c>
+      <c r="G23" s="29">
+        <f>Assumptions!G58</f>
+        <v/>
+      </c>
+      <c r="H23" s="29">
+        <f>Assumptions!H58</f>
+        <v/>
+      </c>
+      <c r="I23" s="29">
+        <f>Assumptions!I58</f>
+        <v/>
+      </c>
+      <c r="J23" s="29">
+        <f>Assumptions!J58</f>
+        <v/>
+      </c>
+      <c r="K23" s="29">
+        <f>Assumptions!K58</f>
+        <v/>
+      </c>
+      <c r="L23" s="29">
+        <f>Assumptions!L58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
           <t>Other opex</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>% of revenue</t>
         </is>
       </c>
-      <c r="C22" s="29">
+      <c r="C24" s="29">
         <f>Revenue!C21*Assumptions!C59</f>
         <v/>
       </c>
-      <c r="D22" s="29">
+      <c r="D24" s="29">
         <f>Revenue!D21*Assumptions!D59</f>
         <v/>
       </c>
-      <c r="E22" s="29">
+      <c r="E24" s="29">
         <f>Revenue!E21*Assumptions!E59</f>
         <v/>
       </c>
-      <c r="F22" s="29">
+      <c r="F24" s="29">
         <f>Revenue!F21*Assumptions!F59</f>
         <v/>
       </c>
-      <c r="G22" s="29">
+      <c r="G24" s="29">
         <f>Revenue!G21*Assumptions!G59</f>
         <v/>
       </c>
-      <c r="H22" s="29">
+      <c r="H24" s="29">
         <f>Revenue!H21*Assumptions!H59</f>
         <v/>
       </c>
-      <c r="I22" s="29">
+      <c r="I24" s="29">
         <f>Revenue!I21*Assumptions!I59</f>
         <v/>
       </c>
-      <c r="J22" s="29">
+      <c r="J24" s="29">
         <f>Revenue!J21*Assumptions!J59</f>
         <v/>
       </c>
-      <c r="K22" s="29">
+      <c r="K24" s="29">
         <f>Revenue!K21*Assumptions!K59</f>
         <v/>
       </c>
-      <c r="L22" s="29">
+      <c r="L24" s="29">
         <f>Revenue!L21*Assumptions!L59</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="45" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="45" t="inlineStr">
         <is>
           <t>TOTAL OPERATING COSTS</t>
         </is>
       </c>
-      <c r="B23" s="40" t="inlineStr"/>
-      <c r="C23" s="46">
-        <f>C16+C20+C21+C22</f>
-        <v/>
-      </c>
-      <c r="D23" s="46">
-        <f>D16+D20+D21+D22</f>
-        <v/>
-      </c>
-      <c r="E23" s="46">
-        <f>E16+E20+E21+E22</f>
-        <v/>
-      </c>
-      <c r="F23" s="46">
-        <f>F16+F20+F21+F22</f>
-        <v/>
-      </c>
-      <c r="G23" s="46">
-        <f>G16+G20+G21+G22</f>
-        <v/>
-      </c>
-      <c r="H23" s="46">
-        <f>H16+H20+H21+H22</f>
-        <v/>
-      </c>
-      <c r="I23" s="46">
-        <f>I16+I20+I21+I22</f>
-        <v/>
-      </c>
-      <c r="J23" s="46">
-        <f>J16+J20+J21+J22</f>
-        <v/>
-      </c>
-      <c r="K23" s="46">
-        <f>K16+K20+K21+K22</f>
-        <v/>
-      </c>
-      <c r="L23" s="46">
-        <f>L16+L20+L21+L22</f>
+      <c r="B25" s="40" t="inlineStr"/>
+      <c r="C25" s="46">
+        <f>C17+C21+C23+C24</f>
+        <v/>
+      </c>
+      <c r="D25" s="46">
+        <f>D17+D21+D23+D24</f>
+        <v/>
+      </c>
+      <c r="E25" s="46">
+        <f>E17+E21+E23+E24</f>
+        <v/>
+      </c>
+      <c r="F25" s="46">
+        <f>F17+F21+F23+F24</f>
+        <v/>
+      </c>
+      <c r="G25" s="46">
+        <f>G17+G21+G23+G24</f>
+        <v/>
+      </c>
+      <c r="H25" s="46">
+        <f>H17+H21+H23+H24</f>
+        <v/>
+      </c>
+      <c r="I25" s="46">
+        <f>I17+I21+I23+I24</f>
+        <v/>
+      </c>
+      <c r="J25" s="46">
+        <f>J17+J21+J23+J24</f>
+        <v/>
+      </c>
+      <c r="K25" s="46">
+        <f>K17+K21+K23+K24</f>
+        <v/>
+      </c>
+      <c r="L25" s="46">
+        <f>L17+L21+L23+L24</f>
         <v/>
       </c>
     </row>
@@ -14248,43 +15503,43 @@
         </is>
       </c>
       <c r="C7" s="29">
-        <f>Costs!C23*Assumptions!C64/365</f>
+        <f>Costs!C25*Assumptions!C64/365</f>
         <v/>
       </c>
       <c r="D7" s="29">
-        <f>Costs!D23*Assumptions!D64/365</f>
+        <f>Costs!D25*Assumptions!D64/365</f>
         <v/>
       </c>
       <c r="E7" s="29">
-        <f>Costs!E23*Assumptions!E64/365</f>
+        <f>Costs!E25*Assumptions!E64/365</f>
         <v/>
       </c>
       <c r="F7" s="29">
-        <f>Costs!F23*Assumptions!F64/365</f>
+        <f>Costs!F25*Assumptions!F64/365</f>
         <v/>
       </c>
       <c r="G7" s="29">
-        <f>Costs!G23*Assumptions!G64/365</f>
+        <f>Costs!G25*Assumptions!G64/365</f>
         <v/>
       </c>
       <c r="H7" s="29">
-        <f>Costs!H23*Assumptions!H64/365</f>
+        <f>Costs!H25*Assumptions!H64/365</f>
         <v/>
       </c>
       <c r="I7" s="29">
-        <f>Costs!I23*Assumptions!I64/365</f>
+        <f>Costs!I25*Assumptions!I64/365</f>
         <v/>
       </c>
       <c r="J7" s="29">
-        <f>Costs!J23*Assumptions!J64/365</f>
+        <f>Costs!J25*Assumptions!J64/365</f>
         <v/>
       </c>
       <c r="K7" s="29">
-        <f>Costs!K23*Assumptions!K64/365</f>
+        <f>Costs!K25*Assumptions!K64/365</f>
         <v/>
       </c>
       <c r="L7" s="29">
-        <f>Costs!L23*Assumptions!L64/365</f>
+        <f>Costs!L25*Assumptions!L64/365</f>
         <v/>
       </c>
     </row>
@@ -14422,43 +15677,43 @@
         </is>
       </c>
       <c r="C12" s="29">
-        <f>Costs!C16*Assumptions!C65</f>
+        <f>Costs!C17*Assumptions!C65</f>
         <v/>
       </c>
       <c r="D12" s="29">
-        <f>Costs!D16*Assumptions!D65</f>
+        <f>Costs!D17*Assumptions!D65</f>
         <v/>
       </c>
       <c r="E12" s="29">
-        <f>Costs!E16*Assumptions!E65</f>
+        <f>Costs!E17*Assumptions!E65</f>
         <v/>
       </c>
       <c r="F12" s="29">
-        <f>Costs!F16*Assumptions!F65</f>
+        <f>Costs!F17*Assumptions!F65</f>
         <v/>
       </c>
       <c r="G12" s="29">
-        <f>Costs!G16*Assumptions!G65</f>
+        <f>Costs!G17*Assumptions!G65</f>
         <v/>
       </c>
       <c r="H12" s="29">
-        <f>Costs!H16*Assumptions!H65</f>
+        <f>Costs!H17*Assumptions!H65</f>
         <v/>
       </c>
       <c r="I12" s="29">
-        <f>Costs!I16*Assumptions!I65</f>
+        <f>Costs!I17*Assumptions!I65</f>
         <v/>
       </c>
       <c r="J12" s="29">
-        <f>Costs!J16*Assumptions!J65</f>
+        <f>Costs!J17*Assumptions!J65</f>
         <v/>
       </c>
       <c r="K12" s="29">
-        <f>Costs!K16*Assumptions!K65</f>
+        <f>Costs!K17*Assumptions!K65</f>
         <v/>
       </c>
       <c r="L12" s="29">
-        <f>Costs!L16*Assumptions!L65</f>
+        <f>Costs!L17*Assumptions!L65</f>
         <v/>
       </c>
     </row>
@@ -14758,43 +16013,43 @@
       </c>
       <c r="B5" s="14" t="inlineStr"/>
       <c r="C5" s="29">
-        <f>-Costs!C13</f>
+        <f>-Costs!C14</f>
         <v/>
       </c>
       <c r="D5" s="29">
-        <f>-Costs!D13</f>
+        <f>-Costs!D14</f>
         <v/>
       </c>
       <c r="E5" s="29">
-        <f>-Costs!E13</f>
+        <f>-Costs!E14</f>
         <v/>
       </c>
       <c r="F5" s="29">
-        <f>-Costs!F13</f>
+        <f>-Costs!F14</f>
         <v/>
       </c>
       <c r="G5" s="29">
-        <f>-Costs!G13</f>
+        <f>-Costs!G14</f>
         <v/>
       </c>
       <c r="H5" s="29">
-        <f>-Costs!H13</f>
+        <f>-Costs!H14</f>
         <v/>
       </c>
       <c r="I5" s="29">
-        <f>-Costs!I13</f>
+        <f>-Costs!I14</f>
         <v/>
       </c>
       <c r="J5" s="29">
-        <f>-Costs!J13</f>
+        <f>-Costs!J14</f>
         <v/>
       </c>
       <c r="K5" s="29">
-        <f>-Costs!K13</f>
+        <f>-Costs!K14</f>
         <v/>
       </c>
       <c r="L5" s="29">
-        <f>-Costs!L13</f>
+        <f>-Costs!L14</f>
         <v/>
       </c>
     </row>
@@ -14902,43 +16157,43 @@
       </c>
       <c r="B9" s="14" t="inlineStr"/>
       <c r="C9" s="29">
-        <f>-Costs!C23</f>
+        <f>-Costs!C25</f>
         <v/>
       </c>
       <c r="D9" s="29">
-        <f>-Costs!D23</f>
+        <f>-Costs!D25</f>
         <v/>
       </c>
       <c r="E9" s="29">
-        <f>-Costs!E23</f>
+        <f>-Costs!E25</f>
         <v/>
       </c>
       <c r="F9" s="29">
-        <f>-Costs!F23</f>
+        <f>-Costs!F25</f>
         <v/>
       </c>
       <c r="G9" s="29">
-        <f>-Costs!G23</f>
+        <f>-Costs!G25</f>
         <v/>
       </c>
       <c r="H9" s="29">
-        <f>-Costs!H23</f>
+        <f>-Costs!H25</f>
         <v/>
       </c>
       <c r="I9" s="29">
-        <f>-Costs!I23</f>
+        <f>-Costs!I25</f>
         <v/>
       </c>
       <c r="J9" s="29">
-        <f>-Costs!J23</f>
+        <f>-Costs!J25</f>
         <v/>
       </c>
       <c r="K9" s="29">
-        <f>-Costs!K23</f>
+        <f>-Costs!K25</f>
         <v/>
       </c>
       <c r="L9" s="29">
-        <f>-Costs!L23</f>
+        <f>-Costs!L25</f>
         <v/>
       </c>
     </row>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -12286,47 +12286,47 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>solved: (end - survivors)/annuity</t>
-        </is>
-      </c>
-      <c r="C16" s="38">
-        <f>MAX(0,(C13-C15)/((1-C14^12)/(1-C14)))</f>
-        <v/>
-      </c>
-      <c r="D16" s="38">
-        <f>MAX(0,(D13-D15)/((1-D14^12)/(1-D14)))</f>
-        <v/>
-      </c>
-      <c r="E16" s="38">
-        <f>MAX(0,(E13-E15)/((1-E14^12)/(1-E14)))</f>
-        <v/>
-      </c>
-      <c r="F16" s="38">
-        <f>MAX(0,(F13-F15)/((1-F14^12)/(1-F14)))</f>
-        <v/>
-      </c>
-      <c r="G16" s="38">
-        <f>MAX(0,(G13-G15)/((1-G14^12)/(1-G14)))</f>
-        <v/>
-      </c>
-      <c r="H16" s="38">
-        <f>MAX(0,(H13-H15)/((1-H14^12)/(1-H14)))</f>
-        <v/>
-      </c>
-      <c r="I16" s="38">
-        <f>MAX(0,(I13-I15)/((1-I14^12)/(1-I14)))</f>
-        <v/>
-      </c>
-      <c r="J16" s="38">
-        <f>MAX(0,(J13-J15)/((1-J14^12)/(1-J14)))</f>
-        <v/>
-      </c>
-      <c r="K16" s="38">
-        <f>MAX(0,(K13-K15)/((1-K14^12)/(1-K14)))</f>
-        <v/>
-      </c>
-      <c r="L16" s="38">
-        <f>MAX(0,(L13-L15)/((1-L14^12)/(1-L14)))</f>
+          <t>solved, then capped by capacity</t>
+        </is>
+      </c>
+      <c r="C16" s="17">
+        <f>MIN(MAX(0,(C13-C15)/((1-C14^12)/(1-C14))),C12*Assumptions!C15/12)</f>
+        <v/>
+      </c>
+      <c r="D16" s="17">
+        <f>MIN(MAX(0,(D13-D15)/((1-D14^12)/(1-D14))),D12*Assumptions!D15/12)</f>
+        <v/>
+      </c>
+      <c r="E16" s="17">
+        <f>MIN(MAX(0,(E13-E15)/((1-E14^12)/(1-E14))),E12*Assumptions!E15/12)</f>
+        <v/>
+      </c>
+      <c r="F16" s="17">
+        <f>MIN(MAX(0,(F13-F15)/((1-F14^12)/(1-F14))),F12*Assumptions!F15/12)</f>
+        <v/>
+      </c>
+      <c r="G16" s="17">
+        <f>MIN(MAX(0,(G13-G15)/((1-G14^12)/(1-G14))),G12*Assumptions!G15/12)</f>
+        <v/>
+      </c>
+      <c r="H16" s="17">
+        <f>MIN(MAX(0,(H13-H15)/((1-H14^12)/(1-H14))),H12*Assumptions!H15/12)</f>
+        <v/>
+      </c>
+      <c r="I16" s="17">
+        <f>MIN(MAX(0,(I13-I15)/((1-I14^12)/(1-I14))),I12*Assumptions!I15/12)</f>
+        <v/>
+      </c>
+      <c r="J16" s="17">
+        <f>MIN(MAX(0,(J13-J15)/((1-J14^12)/(1-J14))),J12*Assumptions!J15/12)</f>
+        <v/>
+      </c>
+      <c r="K16" s="17">
+        <f>MIN(MAX(0,(K13-K15)/((1-K14^12)/(1-K14))),K12*Assumptions!K15/12)</f>
+        <v/>
+      </c>
+      <c r="L16" s="17">
+        <f>MIN(MAX(0,(L13-L15)/((1-L14^12)/(1-L14))),L12*Assumptions!L15/12)</f>
         <v/>
       </c>
     </row>
@@ -12338,47 +12338,47 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>x12 months, capped by capacity</t>
-        </is>
-      </c>
-      <c r="C17" s="17">
-        <f>MIN(C16*12,C12*Assumptions!C15)</f>
-        <v/>
-      </c>
-      <c r="D17" s="17">
-        <f>MIN(D16*12,D12*Assumptions!D15)</f>
-        <v/>
-      </c>
-      <c r="E17" s="17">
-        <f>MIN(E16*12,E12*Assumptions!E15)</f>
-        <v/>
-      </c>
-      <c r="F17" s="17">
-        <f>MIN(F16*12,F12*Assumptions!F15)</f>
-        <v/>
-      </c>
-      <c r="G17" s="17">
-        <f>MIN(G16*12,G12*Assumptions!G15)</f>
-        <v/>
-      </c>
-      <c r="H17" s="17">
-        <f>MIN(H16*12,H12*Assumptions!H15)</f>
-        <v/>
-      </c>
-      <c r="I17" s="17">
-        <f>MIN(I16*12,I12*Assumptions!I15)</f>
-        <v/>
-      </c>
-      <c r="J17" s="17">
-        <f>MIN(J16*12,J12*Assumptions!J15)</f>
-        <v/>
-      </c>
-      <c r="K17" s="17">
-        <f>MIN(K16*12,K12*Assumptions!K15)</f>
-        <v/>
-      </c>
-      <c r="L17" s="17">
-        <f>MIN(L16*12,L12*Assumptions!L15)</f>
+          <t>x12 months</t>
+        </is>
+      </c>
+      <c r="C17" s="38">
+        <f>C16*12</f>
+        <v/>
+      </c>
+      <c r="D17" s="38">
+        <f>D16*12</f>
+        <v/>
+      </c>
+      <c r="E17" s="38">
+        <f>E16*12</f>
+        <v/>
+      </c>
+      <c r="F17" s="38">
+        <f>F16*12</f>
+        <v/>
+      </c>
+      <c r="G17" s="38">
+        <f>G16*12</f>
+        <v/>
+      </c>
+      <c r="H17" s="38">
+        <f>H16*12</f>
+        <v/>
+      </c>
+      <c r="I17" s="38">
+        <f>I16*12</f>
+        <v/>
+      </c>
+      <c r="J17" s="38">
+        <f>J16*12</f>
+        <v/>
+      </c>
+      <c r="K17" s="38">
+        <f>K16*12</f>
+        <v/>
+      </c>
+      <c r="L17" s="38">
+        <f>L16*12</f>
         <v/>
       </c>
     </row>
@@ -12859,47 +12859,47 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>solved: (end - survivors)/annuity</t>
-        </is>
-      </c>
-      <c r="C29" s="38">
-        <f>MAX(0,(C26-C28)/((1-C27^12)/(1-C27)))</f>
-        <v/>
-      </c>
-      <c r="D29" s="38">
-        <f>MAX(0,(D26-D28)/((1-D27^12)/(1-D27)))</f>
-        <v/>
-      </c>
-      <c r="E29" s="38">
-        <f>MAX(0,(E26-E28)/((1-E27^12)/(1-E27)))</f>
-        <v/>
-      </c>
-      <c r="F29" s="38">
-        <f>MAX(0,(F26-F28)/((1-F27^12)/(1-F27)))</f>
-        <v/>
-      </c>
-      <c r="G29" s="38">
-        <f>MAX(0,(G26-G28)/((1-G27^12)/(1-G27)))</f>
-        <v/>
-      </c>
-      <c r="H29" s="38">
-        <f>MAX(0,(H26-H28)/((1-H27^12)/(1-H27)))</f>
-        <v/>
-      </c>
-      <c r="I29" s="38">
-        <f>MAX(0,(I26-I28)/((1-I27^12)/(1-I27)))</f>
-        <v/>
-      </c>
-      <c r="J29" s="38">
-        <f>MAX(0,(J26-J28)/((1-J27^12)/(1-J27)))</f>
-        <v/>
-      </c>
-      <c r="K29" s="38">
-        <f>MAX(0,(K26-K28)/((1-K27^12)/(1-K27)))</f>
-        <v/>
-      </c>
-      <c r="L29" s="38">
-        <f>MAX(0,(L26-L28)/((1-L27^12)/(1-L27)))</f>
+          <t>solved, then capped by capacity</t>
+        </is>
+      </c>
+      <c r="C29" s="17">
+        <f>MIN(MAX(0,(C26-C28)/((1-C27^12)/(1-C27))),C25*Assumptions!C27/12)</f>
+        <v/>
+      </c>
+      <c r="D29" s="17">
+        <f>MIN(MAX(0,(D26-D28)/((1-D27^12)/(1-D27))),D25*Assumptions!D27/12)</f>
+        <v/>
+      </c>
+      <c r="E29" s="17">
+        <f>MIN(MAX(0,(E26-E28)/((1-E27^12)/(1-E27))),E25*Assumptions!E27/12)</f>
+        <v/>
+      </c>
+      <c r="F29" s="17">
+        <f>MIN(MAX(0,(F26-F28)/((1-F27^12)/(1-F27))),F25*Assumptions!F27/12)</f>
+        <v/>
+      </c>
+      <c r="G29" s="17">
+        <f>MIN(MAX(0,(G26-G28)/((1-G27^12)/(1-G27))),G25*Assumptions!G27/12)</f>
+        <v/>
+      </c>
+      <c r="H29" s="17">
+        <f>MIN(MAX(0,(H26-H28)/((1-H27^12)/(1-H27))),H25*Assumptions!H27/12)</f>
+        <v/>
+      </c>
+      <c r="I29" s="17">
+        <f>MIN(MAX(0,(I26-I28)/((1-I27^12)/(1-I27))),I25*Assumptions!I27/12)</f>
+        <v/>
+      </c>
+      <c r="J29" s="17">
+        <f>MIN(MAX(0,(J26-J28)/((1-J27^12)/(1-J27))),J25*Assumptions!J27/12)</f>
+        <v/>
+      </c>
+      <c r="K29" s="17">
+        <f>MIN(MAX(0,(K26-K28)/((1-K27^12)/(1-K27))),K25*Assumptions!K27/12)</f>
+        <v/>
+      </c>
+      <c r="L29" s="17">
+        <f>MIN(MAX(0,(L26-L28)/((1-L27^12)/(1-L27))),L25*Assumptions!L27/12)</f>
         <v/>
       </c>
     </row>
@@ -12911,47 +12911,47 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>x12 months, capped by capacity</t>
-        </is>
-      </c>
-      <c r="C30" s="17">
-        <f>MIN(C29*12,C25*Assumptions!C27)</f>
-        <v/>
-      </c>
-      <c r="D30" s="17">
-        <f>MIN(D29*12,D25*Assumptions!D27)</f>
-        <v/>
-      </c>
-      <c r="E30" s="17">
-        <f>MIN(E29*12,E25*Assumptions!E27)</f>
-        <v/>
-      </c>
-      <c r="F30" s="17">
-        <f>MIN(F29*12,F25*Assumptions!F27)</f>
-        <v/>
-      </c>
-      <c r="G30" s="17">
-        <f>MIN(G29*12,G25*Assumptions!G27)</f>
-        <v/>
-      </c>
-      <c r="H30" s="17">
-        <f>MIN(H29*12,H25*Assumptions!H27)</f>
-        <v/>
-      </c>
-      <c r="I30" s="17">
-        <f>MIN(I29*12,I25*Assumptions!I27)</f>
-        <v/>
-      </c>
-      <c r="J30" s="17">
-        <f>MIN(J29*12,J25*Assumptions!J27)</f>
-        <v/>
-      </c>
-      <c r="K30" s="17">
-        <f>MIN(K29*12,K25*Assumptions!K27)</f>
-        <v/>
-      </c>
-      <c r="L30" s="17">
-        <f>MIN(L29*12,L25*Assumptions!L27)</f>
+          <t>x12 months</t>
+        </is>
+      </c>
+      <c r="C30" s="38">
+        <f>C29*12</f>
+        <v/>
+      </c>
+      <c r="D30" s="38">
+        <f>D29*12</f>
+        <v/>
+      </c>
+      <c r="E30" s="38">
+        <f>E29*12</f>
+        <v/>
+      </c>
+      <c r="F30" s="38">
+        <f>F29*12</f>
+        <v/>
+      </c>
+      <c r="G30" s="38">
+        <f>G29*12</f>
+        <v/>
+      </c>
+      <c r="H30" s="38">
+        <f>H29*12</f>
+        <v/>
+      </c>
+      <c r="I30" s="38">
+        <f>I29*12</f>
+        <v/>
+      </c>
+      <c r="J30" s="38">
+        <f>J29*12</f>
+        <v/>
+      </c>
+      <c r="K30" s="38">
+        <f>K29*12</f>
+        <v/>
+      </c>
+      <c r="L30" s="38">
+        <f>L29*12</f>
         <v/>
       </c>
     </row>
@@ -17989,43 +17989,43 @@
       </c>
       <c r="B13" s="14" t="inlineStr"/>
       <c r="C13" s="48">
-        <f>IF(1=1,0,C14)</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="D13" s="48">
-        <f>IF(2=1,0,C14)</f>
+        <f>C14</f>
         <v/>
       </c>
       <c r="E13" s="48">
-        <f>IF(3=1,0,D14)</f>
+        <f>D14</f>
         <v/>
       </c>
       <c r="F13" s="48">
-        <f>IF(4=1,0,E14)</f>
+        <f>E14</f>
         <v/>
       </c>
       <c r="G13" s="48">
-        <f>IF(5=1,0,F14)</f>
+        <f>F14</f>
         <v/>
       </c>
       <c r="H13" s="48">
-        <f>IF(6=1,0,G14)</f>
+        <f>G14</f>
         <v/>
       </c>
       <c r="I13" s="48">
-        <f>IF(7=1,0,H14)</f>
+        <f>H14</f>
         <v/>
       </c>
       <c r="J13" s="48">
-        <f>IF(8=1,0,I14)</f>
+        <f>I14</f>
         <v/>
       </c>
       <c r="K13" s="48">
-        <f>IF(9=1,0,J14)</f>
+        <f>J14</f>
         <v/>
       </c>
       <c r="L13" s="48">
-        <f>IF(10=1,0,K14)</f>
+        <f>K14</f>
         <v/>
       </c>
     </row>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -811,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A56"/>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1131,43 +1131,78 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Follow any assumption backwards and it ends at a cited number.</t>
+          <t xml:space="preserve">  From Assumptions rightwards every link is a formula you can follow with</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Trace Precedents. The first arrow is not: MarketModel shows the derivation</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>MODEL SHAPE</t>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  from the published figures step by step, and Assumptions holds the number</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>This is a target-driven model: athlete counts are the plan, and marketing spend</t>
+          <t xml:space="preserve">  it arrives at, entered rather than linked. So the derivation is auditable</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>is derived from them at segment CAC. It is not a driver-driven model in which</t>
+          <t xml:space="preserve">  but it is not enforced -- change a comparable and MarketModel moves while</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Assumptions does not. Read them side by side before trusting either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>MODEL SHAPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>This is a target-driven model: athlete counts are the plan, and marketing spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>is derived from them at segment CAC. It is not a driver-driven model in which</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>spend produces athletes. That is the normal shape for a plan, but it means the</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>athlete trajectory is an assumption to defend, not an output to trust.</t>
         </is>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -811,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A61"/>
+  <dimension ref="A1:A63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1131,78 +1131,92 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">  From Assumptions rightwards every link is a formula you can follow with</t>
+          <t xml:space="preserve">  From Assumptions rightwards, every link is a formula you can follow with</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Trace Precedents. The first arrow is not: MarketModel shows the derivation</t>
+          <t xml:space="preserve">  Trace Precedents. The first arrow is checked rather than linked: MarketModel</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  from the published figures step by step, and Assumptions holds the number</t>
+          <t xml:space="preserve">  derives each figure from the published ones, and Assumptions carries the</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  it arrives at, entered rather than linked. So the derivation is auditable</t>
+          <t xml:space="preserve">  result rounded for reading -- 37 fans per athlete, not 37.026. Linking the</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  but it is not enforced -- change a comparable and MarketModel moves while</t>
+          <t xml:space="preserve">  cells would put the workbook a hair off the Python everywhere, which the</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Assumptions does not. Read them side by side before trusting either.</t>
+          <t xml:space="preserve">  Check sheet exists to forbid, so scripts/doc_consistency.py asserts the</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  derivation still produces those literals instead. Change a comparable and</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  that check fails; it cannot drift quietly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>MODEL SHAPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>This is a target-driven model: athlete counts are the plan, and marketing spend</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>is derived from them at segment CAC. It is not a driver-driven model in which</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>spend produces athletes. That is the normal shape for a plan, but it means the</t>
+          <t>This is a target-driven model: athlete counts are the plan, and marketing spend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
+        <is>
+          <t>is derived from them at segment CAC. It is not a driver-driven model in which</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>spend produces athletes. That is the normal shape for a plan, but it means the</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>athlete trajectory is an assumption to defend, not an output to trust.</t>
         </is>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -811,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A63"/>
+  <dimension ref="A1:A65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1173,50 +1173,64 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">  derivation still produces those literals instead. Change a comparable and</t>
+          <t xml:space="preserve">  derivation still rounds to those literals instead. Refresh a comparable far</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">  that check fails; it cannot drift quietly.</t>
+          <t xml:space="preserve">  enough to change one of them at the precision it is written and that check</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  fails. A refresh too small to change any displayed figure passes, which is</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  the same statement, not a loophole in it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>MODEL SHAPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>This is a target-driven model: athlete counts are the plan, and marketing spend</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>is derived from them at segment CAC. It is not a driver-driven model in which</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>spend produces athletes. That is the normal shape for a plan, but it means the</t>
+          <t>This is a target-driven model: athlete counts are the plan, and marketing spend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
+        <is>
+          <t>is derived from them at segment CAC. It is not a driver-driven model in which</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>spend produces athletes. That is the normal shape for a plan, but it means the</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>athlete trajectory is an assumption to defend, not an output to trust.</t>
         </is>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -2371,7 +2371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F30" s="65" t="inlineStr">
         <is>
-          <t>MEXC platform comparison 2026</t>
+          <t>Not published in terms; widely reported</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="F31" s="65" t="inlineStr">
         <is>
-          <t>Outseeker comparison 2026</t>
+          <t>Not published in terms; widely reported</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F37" s="65" t="inlineStr">
         <is>
-          <t>Oreate / Sapling agent-commission surveys</t>
+          <t>Unregulated; widely reported, no primary source</t>
         </is>
       </c>
     </row>
@@ -3251,14 +3251,14 @@
         </is>
       </c>
       <c r="B38" s="63" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="C38" s="63" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="F38" s="65" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>NBPA reg. 4.B (Sept 2025); FIFA FFAR art. 15</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3326,12 @@
     <row r="46">
       <c r="A46" s="66" t="inlineStr">
         <is>
-          <t>Platform comparison</t>
+          <t>Fanfix creator terms (states no take rate)</t>
         </is>
       </c>
       <c r="B46" s="67" t="inlineStr">
         <is>
-          <t>https://www.mexc.com/news/1014749</t>
+          <t>https://auth.fanfix.io/creator-terms-of-use</t>
         </is>
       </c>
     </row>
@@ -3350,82 +3350,108 @@
     <row r="48">
       <c r="A48" s="66" t="inlineStr">
         <is>
-          <t>Agent commissions</t>
+          <t>NBPA agent fee cap (amended Sept 2025)</t>
         </is>
       </c>
       <c r="B48" s="67" t="inlineStr">
         <is>
-          <t>https://www.oreateai.com/blog/understanding-sports-agents-commission-what-percentage-do-they-take/95c2df506ae450b9b71340b89cfcfece</t>
+          <t>https://imgix.cosmicjs.com/cd844850-97c7-11f0-91fa-d9e1671c2776-NBPA-REGULATIONS-GOVERNING-PLAYER-AGENTS-09-2025.pdf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="66" t="inlineStr">
         <is>
-          <t>Eurobarometer 525</t>
+          <t>FIFA Football Agent Regulations art. 15</t>
         </is>
       </c>
       <c r="B49" s="67" t="inlineStr">
         <is>
-          <t>https://europa.eu/eurobarometer/surveys/detail/2668</t>
+          <t>https://digitalhub.fifa.com/m/1e7b741fa0fae779/original/FIFA-Football-Agent-Regulations.pdf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="66" t="inlineStr">
         <is>
-          <t>FIP World Padel Report 2025</t>
+          <t>CJEU upholds the FIFA fee cap (16 Jul 2026)</t>
         </is>
       </c>
       <c r="B50" s="67" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/2025/12/online-the-fip-world-padel-report-2025-a-comprehensive-analysis-of-a-sport-in-constant-growth/</t>
+          <t>https://inside.fifa.com/news/welcomes-court-of-justice-european-union-decision-football-agent-regulations</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="66" t="inlineStr">
         <is>
-          <t>Stripe EU pricing</t>
+          <t>Eurobarometer 525</t>
         </is>
       </c>
       <c r="B51" s="67" t="inlineStr">
         <is>
-          <t>https://stripe.com/es/pricing</t>
+          <t>https://europa.eu/eurobarometer/surveys/detail/2668</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="66" t="inlineStr">
         <is>
-          <t>TEKTA launch</t>
+          <t>FIP World Padel Report 2025</t>
         </is>
       </c>
       <c r="B52" s="67" t="inlineStr">
         <is>
-          <t>https://www.publicisgroupe.com/en/news/press-releases/publicis-sports-and-travis-kelce-s-tekta-join-forces-to-reimagine-the-future-of-nil-marketing</t>
+          <t>https://www.padelfip.com/2025/12/online-the-fip-world-padel-report-2025-a-comprehensive-analysis-of-a-sport-in-constant-growth/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="66" t="inlineStr">
         <is>
+          <t>Stripe EU pricing</t>
+        </is>
+      </c>
+      <c r="B53" s="67" t="inlineStr">
+        <is>
+          <t>https://stripe.com/es/pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="66" t="inlineStr">
+        <is>
+          <t>TEKTA launch</t>
+        </is>
+      </c>
+      <c r="B54" s="67" t="inlineStr">
+        <is>
+          <t>https://www.publicisgroupe.com/en/news/press-releases/publicis-sports-and-travis-kelce-s-tekta-join-forces-to-reimagine-the-future-of-nil-marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="66" t="inlineStr">
+        <is>
           <t>Stripe Connect age</t>
         </is>
       </c>
-      <c r="B53" s="67" t="inlineStr">
+      <c r="B55" s="67" t="inlineStr">
         <is>
           <t>https://support.stripe.com/questions/age-requirement-to-create-a-stripe-account</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B55:F55"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B54:F54"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B46:F46"/>
@@ -3445,6 +3471,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -2371,7 +2371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="F5" s="60" t="inlineStr">
         <is>
-          <t>Variety, OnlyFans FY2024 financials</t>
+          <t>Fenix International Ltd filed accounts (Companies House 10354575)</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="F6" s="60" t="inlineStr">
         <is>
-          <t>Variety, OnlyFans FY2024 financials</t>
+          <t>Fenix International Ltd filed accounts (Companies House 10354575)</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="F7" s="60" t="inlineStr">
         <is>
-          <t>Variety — 80% creator share</t>
+          <t>Fenix International Ltd filed accounts — 80.3% of gross</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="F29" s="65" t="inlineStr">
         <is>
-          <t>Company disclosure — 80% creator share</t>
+          <t>Derived: 1.41bn / 7.22bn = 19.5% (filed accounts)</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="F32" s="65" t="inlineStr">
         <is>
-          <t>8-12% by plan tier; 10% midpoint</t>
+          <t>Published: 10% all-in, processing included</t>
         </is>
       </c>
     </row>
@@ -3290,164 +3290,189 @@
     <row r="43">
       <c r="A43" s="66" t="inlineStr">
         <is>
-          <t>OnlyFans FY2024</t>
+          <t>OnlyFans FY2024 filed accounts (Fenix International Ltd)</t>
         </is>
       </c>
       <c r="B43" s="67" t="inlineStr">
         <is>
-          <t>https://variety.com/2025/digital/news/onlyfans-fiscal-2024-revenue-earnings-1236495750/</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/10354575/filing-history</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="66" t="inlineStr">
         <is>
-          <t>Patreon creators</t>
+          <t>OnlyFans FY2024 as reported</t>
         </is>
       </c>
       <c r="B44" s="67" t="inlineStr">
         <is>
-          <t>https://backlinko.com/patreon-users</t>
+          <t>https://variety.com/2025/digital/news/onlyfans-fiscal-2024-revenue-earnings-1236495750/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="66" t="inlineStr">
         <is>
-          <t>Passes economics</t>
+          <t>Patreon published take rate</t>
         </is>
       </c>
       <c r="B45" s="67" t="inlineStr">
         <is>
-          <t>https://sacra.com/c/passes/</t>
+          <t>https://www.patreon.com/pricing</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="66" t="inlineStr">
         <is>
-          <t>Fanfix creator terms (states no take rate)</t>
+          <t>Patreon creators</t>
         </is>
       </c>
       <c r="B46" s="67" t="inlineStr">
         <is>
-          <t>https://auth.fanfix.io/creator-terms-of-use</t>
+          <t>https://backlinko.com/patreon-users</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="66" t="inlineStr">
         <is>
-          <t>Agency commissions</t>
+          <t>Passes economics</t>
         </is>
       </c>
       <c r="B47" s="67" t="inlineStr">
         <is>
-          <t>https://arunatalent.com/blog/onlyfans-agency-commission-rates/</t>
+          <t>https://sacra.com/c/passes/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="66" t="inlineStr">
         <is>
-          <t>NBPA agent fee cap (amended Sept 2025)</t>
+          <t>Fanfix creator terms (states no take rate)</t>
         </is>
       </c>
       <c r="B48" s="67" t="inlineStr">
         <is>
-          <t>https://imgix.cosmicjs.com/cd844850-97c7-11f0-91fa-d9e1671c2776-NBPA-REGULATIONS-GOVERNING-PLAYER-AGENTS-09-2025.pdf</t>
+          <t>https://auth.fanfix.io/creator-terms-of-use</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="66" t="inlineStr">
         <is>
-          <t>FIFA Football Agent Regulations art. 15</t>
+          <t>Agency commissions</t>
         </is>
       </c>
       <c r="B49" s="67" t="inlineStr">
         <is>
-          <t>https://digitalhub.fifa.com/m/1e7b741fa0fae779/original/FIFA-Football-Agent-Regulations.pdf</t>
+          <t>https://arunatalent.com/blog/onlyfans-agency-commission-rates/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="66" t="inlineStr">
         <is>
-          <t>CJEU upholds the FIFA fee cap (16 Jul 2026)</t>
+          <t>NBPA agent fee cap (amended Sept 2025)</t>
         </is>
       </c>
       <c r="B50" s="67" t="inlineStr">
         <is>
-          <t>https://inside.fifa.com/news/welcomes-court-of-justice-european-union-decision-football-agent-regulations</t>
+          <t>https://imgix.cosmicjs.com/cd844850-97c7-11f0-91fa-d9e1671c2776-NBPA-REGULATIONS-GOVERNING-PLAYER-AGENTS-09-2025.pdf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="66" t="inlineStr">
         <is>
-          <t>Eurobarometer 525</t>
+          <t>FIFA Football Agent Regulations art. 15</t>
         </is>
       </c>
       <c r="B51" s="67" t="inlineStr">
         <is>
-          <t>https://europa.eu/eurobarometer/surveys/detail/2668</t>
+          <t>https://digitalhub.fifa.com/m/1e7b741fa0fae779/original/FIFA-Football-Agent-Regulations.pdf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="66" t="inlineStr">
         <is>
-          <t>FIP World Padel Report 2025</t>
+          <t>CJEU upholds the FIFA fee cap (16 Jul 2026)</t>
         </is>
       </c>
       <c r="B52" s="67" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/2025/12/online-the-fip-world-padel-report-2025-a-comprehensive-analysis-of-a-sport-in-constant-growth/</t>
+          <t>https://inside.fifa.com/news/welcomes-court-of-justice-european-union-decision-football-agent-regulations</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="66" t="inlineStr">
         <is>
-          <t>Stripe EU pricing</t>
+          <t>Eurobarometer 525</t>
         </is>
       </c>
       <c r="B53" s="67" t="inlineStr">
         <is>
-          <t>https://stripe.com/es/pricing</t>
+          <t>https://europa.eu/eurobarometer/surveys/detail/2668</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="66" t="inlineStr">
         <is>
-          <t>TEKTA launch</t>
+          <t>FIP World Padel Report 2025</t>
         </is>
       </c>
       <c r="B54" s="67" t="inlineStr">
         <is>
-          <t>https://www.publicisgroupe.com/en/news/press-releases/publicis-sports-and-travis-kelce-s-tekta-join-forces-to-reimagine-the-future-of-nil-marketing</t>
+          <t>https://www.padelfip.com/2025/12/online-the-fip-world-padel-report-2025-a-comprehensive-analysis-of-a-sport-in-constant-growth/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="66" t="inlineStr">
         <is>
+          <t>Stripe EU pricing</t>
+        </is>
+      </c>
+      <c r="B55" s="67" t="inlineStr">
+        <is>
+          <t>https://stripe.com/es/pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="66" t="inlineStr">
+        <is>
+          <t>TEKTA launch</t>
+        </is>
+      </c>
+      <c r="B56" s="67" t="inlineStr">
+        <is>
+          <t>https://www.publicisgroupe.com/en/news/press-releases/publicis-sports-and-travis-kelce-s-tekta-join-forces-to-reimagine-the-future-of-nil-marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="66" t="inlineStr">
+        <is>
           <t>Stripe Connect age</t>
         </is>
       </c>
-      <c r="B55" s="67" t="inlineStr">
+      <c r="B57" s="67" t="inlineStr">
         <is>
           <t>https://support.stripe.com/questions/age-requirement-to-create-a-stripe-account</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B56:F56"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B48:F48"/>
@@ -3457,6 +3482,7 @@
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B57:F57"/>
     <mergeCell ref="B49:F49"/>
   </mergeCells>
   <hyperlinks>
@@ -3473,6 +3499,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -5908,34 +5908,34 @@
         </is>
       </c>
       <c r="C5" s="22" t="n">
-        <v>29166.29485240957</v>
+        <v>24777.03541521453</v>
       </c>
       <c r="D5" s="22" t="n">
-        <v>231466.7980089362</v>
+        <v>202033.1983544927</v>
       </c>
       <c r="E5" s="22" t="n">
-        <v>1039255.898341637</v>
+        <v>919083.1556542454</v>
       </c>
       <c r="F5" s="22" t="n">
-        <v>3369805.454952703</v>
+        <v>3013000.380952647</v>
       </c>
       <c r="G5" s="22" t="n">
-        <v>8395820.572478704</v>
+        <v>7568449.977255126</v>
       </c>
       <c r="H5" s="22" t="n">
-        <v>16203911.55883188</v>
+        <v>14699877.40399329</v>
       </c>
       <c r="I5" s="22" t="n">
-        <v>26523705.50889406</v>
+        <v>24131919.79247443</v>
       </c>
       <c r="J5" s="22" t="n">
-        <v>37689559.60026349</v>
+        <v>34347336.42996982</v>
       </c>
       <c r="K5" s="22" t="n">
-        <v>47571802.66472916</v>
+        <v>43325569.29647037</v>
       </c>
       <c r="L5" s="22" t="n">
-        <v>57961416.63566395</v>
+        <v>52934813.4840198</v>
       </c>
     </row>
     <row r="6">
@@ -6072,34 +6072,34 @@
         </is>
       </c>
       <c r="C10" s="22" t="n">
-        <v>13471.23223109862</v>
+        <v>12020.4441601185</v>
       </c>
       <c r="D10" s="22" t="n">
-        <v>80172.86367656694</v>
+        <v>70444.13474730599</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>324954.3266336625</v>
+        <v>285233.4616352503</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>997729.1293521416</v>
+        <v>879793.8483710603</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>2405944.872754806</v>
+        <v>2132472.910797332</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>4500263.01540566</v>
+        <v>4003132.499105871</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>7225273.097037062</v>
+        <v>6434712.813377975</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>10131408.91889975</v>
+        <v>9026699.212080941</v>
       </c>
       <c r="K10" s="22" t="n">
-        <v>12708269.29438148</v>
+        <v>11304755.83034156</v>
       </c>
       <c r="L10" s="22" t="n">
-        <v>15327976.37081417</v>
+        <v>13666526.18900019</v>
       </c>
     </row>
     <row r="11">
@@ -6236,34 +6236,34 @@
         </is>
       </c>
       <c r="C15" s="22" t="n">
-        <v>15695.06262131096</v>
+        <v>12756.59125509603</v>
       </c>
       <c r="D15" s="22" t="n">
-        <v>151293.9343323692</v>
+        <v>131589.0636071867</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>714301.5717079744</v>
+        <v>633849.6940189952</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>2372076.325600561</v>
+        <v>2133206.532581586</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>5989875.699723898</v>
+        <v>5435977.066457794</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>11703648.54342622</v>
+        <v>10696744.90488742</v>
       </c>
       <c r="I15" s="22" t="n">
-        <v>19298432.41185699</v>
+        <v>17697206.97909645</v>
       </c>
       <c r="J15" s="22" t="n">
-        <v>27558150.68136375</v>
+        <v>25320637.21788888</v>
       </c>
       <c r="K15" s="22" t="n">
-        <v>34863533.37034767</v>
+        <v>32020813.46612882</v>
       </c>
       <c r="L15" s="22" t="n">
-        <v>42633440.26484978</v>
+        <v>39268287.2950196</v>
       </c>
     </row>
     <row r="16">
@@ -6400,34 +6400,34 @@
         </is>
       </c>
       <c r="C20" s="22" t="n">
-        <v>106713.3035881928</v>
+        <v>106362.1628332172</v>
       </c>
       <c r="D20" s="22" t="n">
-        <v>339580.5438407149</v>
+        <v>337225.8558683594</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>988068.311867331</v>
+        <v>978454.4924523397</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>2290796.436396216</v>
+        <v>2262252.030476212</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>4270681.645798297</v>
+        <v>4204491.99818041</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>6568757.92470655</v>
+        <v>6448435.192319464</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>9306976.440711524</v>
+        <v>9115633.583397955</v>
       </c>
       <c r="J20" s="22" t="n">
-        <v>11454508.76802108</v>
+        <v>11187130.91439759</v>
       </c>
       <c r="K20" s="22" t="n">
-        <v>13113106.71317833</v>
+        <v>12773408.04371763</v>
       </c>
       <c r="L20" s="22" t="n">
-        <v>14421220.53085312</v>
+        <v>14019092.27872158</v>
       </c>
     </row>
     <row r="21">
@@ -6564,34 +6564,34 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>-91018.2409668818</v>
+        <v>-93605.57157812113</v>
       </c>
       <c r="D25" s="22" t="n">
-        <v>-188286.6095083457</v>
+        <v>-205636.7922611727</v>
       </c>
       <c r="E25" s="22" t="n">
-        <v>-273766.7401593566</v>
+        <v>-344604.7984333446</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>81279.88920434518</v>
+        <v>-129045.4978946252</v>
       </c>
       <c r="G25" s="22" t="n">
-        <v>1719194.053925601</v>
+        <v>1231485.068277384</v>
       </c>
       <c r="H25" s="22" t="n">
-        <v>5134890.618719673</v>
+        <v>4248309.712567959</v>
       </c>
       <c r="I25" s="22" t="n">
-        <v>9991455.97114547</v>
+        <v>8581573.395698495</v>
       </c>
       <c r="J25" s="22" t="n">
-        <v>16103641.91334267</v>
+        <v>14133506.3034913</v>
       </c>
       <c r="K25" s="22" t="n">
-        <v>21750426.65716934</v>
+        <v>19247405.42241119</v>
       </c>
       <c r="L25" s="22" t="n">
-        <v>28212219.73399667</v>
+        <v>25249195.01629802</v>
       </c>
     </row>
     <row r="26">
@@ -7056,34 +7056,34 @@
         </is>
       </c>
       <c r="C40" s="22" t="n">
-        <v>195421.2990160638</v>
+        <v>166159.5694347635</v>
       </c>
       <c r="D40" s="22" t="n">
-        <v>1368483.186726241</v>
+        <v>1172259.189029952</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>6281119.322277579</v>
+        <v>5479967.704361636</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>21555531.69968468</v>
+        <v>19176831.20635098</v>
       </c>
       <c r="G40" s="22" t="n">
-        <v>56547437.14985803</v>
+        <v>51031633.18170085</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>112416110.3922125</v>
+        <v>102389216.0266219</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>185699583.3926271</v>
+        <v>169754345.2831629</v>
       </c>
       <c r="J40" s="22" t="n">
-        <v>265231690.6684232</v>
+        <v>242950202.8664655</v>
       </c>
       <c r="K40" s="22" t="n">
-        <v>333011385.764861</v>
+        <v>304703163.3098025</v>
       </c>
       <c r="L40" s="22" t="n">
-        <v>410111470.9044263</v>
+        <v>376600783.2267987</v>
       </c>
     </row>
     <row r="41">
@@ -7724,22 +7724,22 @@
         <v>0</v>
       </c>
       <c r="G60" s="22" t="n">
-        <v>107985.3528743043</v>
+        <v>0</v>
       </c>
       <c r="H60" s="22" t="n">
-        <v>696313.5928079509</v>
+        <v>552990.3181017119</v>
       </c>
       <c r="I60" s="22" t="n">
-        <v>1385738.395671821</v>
+        <v>1174256.009354774</v>
       </c>
       <c r="J60" s="22" t="n">
-        <v>2259366.2870014</v>
+        <v>1963845.945523695</v>
       </c>
       <c r="K60" s="22" t="n">
-        <v>5105306.664292335</v>
+        <v>2687730.813361678</v>
       </c>
       <c r="L60" s="22" t="n">
-        <v>6656254.933499167</v>
+        <v>5915498.754074506</v>
       </c>
     </row>
     <row r="61">
@@ -7876,34 +7876,34 @@
         </is>
       </c>
       <c r="C65" s="22" t="n">
-        <v>-96718.2409668818</v>
+        <v>-99305.57157812113</v>
       </c>
       <c r="D65" s="22" t="n">
-        <v>-209586.6095083457</v>
+        <v>-226936.7922611727</v>
       </c>
       <c r="E65" s="22" t="n">
-        <v>-337066.7401593566</v>
+        <v>-407904.7984333446</v>
       </c>
       <c r="F65" s="22" t="n">
-        <v>-65920.11079565482</v>
+        <v>-276245.4978946252</v>
       </c>
       <c r="G65" s="22" t="n">
-        <v>1321208.701051297</v>
+        <v>941485.0682773842</v>
       </c>
       <c r="H65" s="22" t="n">
-        <v>3945777.025911722</v>
+        <v>3202519.394466247</v>
       </c>
       <c r="I65" s="22" t="n">
-        <v>7852517.575473649</v>
+        <v>6654117.386343721</v>
       </c>
       <c r="J65" s="22" t="n">
-        <v>12803075.62634127</v>
+        <v>11128460.3579676</v>
       </c>
       <c r="K65" s="22" t="n">
-        <v>15315919.992877</v>
+        <v>15230474.60904951</v>
       </c>
       <c r="L65" s="22" t="n">
-        <v>19968764.8004975</v>
+        <v>17746496.26222352</v>
       </c>
     </row>
     <row r="66">
@@ -8040,34 +8040,34 @@
         </is>
       </c>
       <c r="C70" s="22" t="n">
-        <v>-91794.11057541128</v>
+        <v>-95612.83890272945</v>
       </c>
       <c r="D70" s="22" t="n">
-        <v>-174889.1779378571</v>
+        <v>-199265.4988776602</v>
       </c>
       <c r="E70" s="22" t="n">
-        <v>-179709.1262577989</v>
+        <v>-276003.8646593865</v>
       </c>
       <c r="F70" s="22" t="n">
-        <v>428037.923168655</v>
+        <v>151325.8217507345</v>
       </c>
       <c r="G70" s="22" t="n">
-        <v>2451393.290187358</v>
+        <v>1939653.467349641</v>
       </c>
       <c r="H70" s="22" t="n">
-        <v>5707074.250576285</v>
+        <v>4773980.047885393</v>
       </c>
       <c r="I70" s="22" t="n">
-        <v>10150756.53571027</v>
+        <v>8703299.470125826</v>
       </c>
       <c r="J70" s="22" t="n">
-        <v>15248579.73307066</v>
+        <v>13307321.18996631</v>
       </c>
       <c r="K70" s="22" t="n">
-        <v>17392334.6690449</v>
+        <v>17053271.0817335</v>
       </c>
       <c r="L70" s="22" t="n">
-        <v>22281419.04604195</v>
+        <v>19840219.36853875</v>
       </c>
     </row>
     <row r="71">

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -1857,43 +1857,43 @@
         </is>
       </c>
       <c r="C5" s="33">
-        <f>1/(1+Assumptions!$C$84)^1</f>
+        <f>1/(1+Assumptions!$C$85)^1</f>
         <v/>
       </c>
       <c r="D5" s="33">
-        <f>1/(1+Assumptions!$C$84)^2</f>
+        <f>1/(1+Assumptions!$C$85)^2</f>
         <v/>
       </c>
       <c r="E5" s="33">
-        <f>1/(1+Assumptions!$C$84)^3</f>
+        <f>1/(1+Assumptions!$C$85)^3</f>
         <v/>
       </c>
       <c r="F5" s="33">
-        <f>1/(1+Assumptions!$C$84)^4</f>
+        <f>1/(1+Assumptions!$C$85)^4</f>
         <v/>
       </c>
       <c r="G5" s="33">
-        <f>1/(1+Assumptions!$C$84)^5</f>
+        <f>1/(1+Assumptions!$C$85)^5</f>
         <v/>
       </c>
       <c r="H5" s="33">
-        <f>1/(1+Assumptions!$C$84)^6</f>
+        <f>1/(1+Assumptions!$C$85)^6</f>
         <v/>
       </c>
       <c r="I5" s="33">
-        <f>1/(1+Assumptions!$C$84)^7</f>
+        <f>1/(1+Assumptions!$C$85)^7</f>
         <v/>
       </c>
       <c r="J5" s="33">
-        <f>1/(1+Assumptions!$C$84)^8</f>
+        <f>1/(1+Assumptions!$C$85)^8</f>
         <v/>
       </c>
       <c r="K5" s="33">
-        <f>1/(1+Assumptions!$C$84)^9</f>
+        <f>1/(1+Assumptions!$C$85)^9</f>
         <v/>
       </c>
       <c r="L5" s="33">
-        <f>1/(1+Assumptions!$C$84)^10</f>
+        <f>1/(1+Assumptions!$C$85)^10</f>
         <v/>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="C11" s="52">
-        <f>L4*(1+Assumptions!$C$85)/(Assumptions!$C$84-Assumptions!$C$85)</f>
+        <f>L4*(1+Assumptions!$C$86)/(Assumptions!$C$85-Assumptions!$C$86)</f>
         <v/>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="C16" s="52">
-        <f>NPV(Assumptions!$C$84,C4:L4)</f>
+        <f>NPV(Assumptions!$C$85,C4:L4)</f>
         <v/>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="C21" s="52">
-        <f>Revenue!L21</f>
+        <f>Revenue!L22</f>
         <v/>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="C22" s="52">
-        <f>C21*Assumptions!$C$86</f>
+        <f>C21*Assumptions!$C$87</f>
         <v/>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="B47" s="29">
-        <f>B46*(1-Comparables!B29)-B46/Assumptions!$C$47*Comparables!C29*B45-Comparables!D29*B45</f>
+        <f>B46*(1-Comparables!B29)-B46/Assumptions!$C$48*Comparables!C29*B45-Comparables!D29*B45</f>
         <v/>
       </c>
       <c r="D47" s="68" t="inlineStr">
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="B48" s="29">
-        <f>B46*(1-Comparables!B32)-B46/Assumptions!$C$47*Comparables!C32*B45-Comparables!D32*B45</f>
+        <f>B46*(1-Comparables!B32)-B46/Assumptions!$C$48*Comparables!C32*B45-Comparables!D32*B45</f>
         <v/>
       </c>
       <c r="D48" s="68" t="inlineStr">
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="B49" s="29">
-        <f>B46*(1-Comparables!B33)-B46/Assumptions!$C$47*Comparables!C33*B45-Comparables!D33*B45</f>
+        <f>B46*(1-Comparables!B33)-B46/Assumptions!$C$48*Comparables!C33*B45-Comparables!D33*B45</f>
         <v/>
       </c>
       <c r="D49" s="68" t="inlineStr">
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="B50" s="29">
-        <f>B46*(1-Comparables!B34)-B46/Assumptions!$C$47*Comparables!C34*B45-Comparables!D34*B45</f>
+        <f>B46*(1-Comparables!B34)-B46/Assumptions!$C$48*Comparables!C34*B45-Comparables!D34*B45</f>
         <v/>
       </c>
       <c r="D50" s="68" t="inlineStr">
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="B51" s="30">
-        <f>Comparables!D33*B45/((Comparables!B34-Comparables!B33)-Comparables!C33*B45/Assumptions!$C$47)</f>
+        <f>Comparables!D33*B45/((Comparables!B34-Comparables!B33)-Comparables!C33*B45/Assumptions!$C$48)</f>
         <v/>
       </c>
       <c r="D51" s="68" t="inlineStr">
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="B17" s="33">
-        <f>Assumptions!$C$43</f>
+        <f>Assumptions!$C$44</f>
         <v/>
       </c>
       <c r="C17" s="82" t="inlineStr">
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="B18" s="33">
-        <f>Assumptions!$C$44</f>
+        <f>Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="C18" s="82" t="inlineStr">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="B19" s="33">
-        <f>Assumptions!$C$45</f>
+        <f>Assumptions!$C$46</f>
         <v/>
       </c>
       <c r="C19" s="82" t="inlineStr">
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="B27" s="33">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="C27" s="85" t="inlineStr">
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="B28" s="33">
-        <f>Assumptions!$C$77</f>
+        <f>Assumptions!$C$78</f>
         <v/>
       </c>
       <c r="C28" s="83" t="inlineStr">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="B29" s="33">
-        <f>Assumptions!$C$80</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="C29" s="85" t="inlineStr">
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$61</f>
         <v/>
       </c>
       <c r="C31" s="77" t="inlineStr">
@@ -5318,7 +5318,7 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>Assumptions!$C$51</f>
+        <f>Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="C32" s="77" t="inlineStr">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="B33" s="33">
-        <f>Assumptions!$C$53</f>
+        <f>Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="C33" s="82" t="inlineStr">
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="B34" s="33">
-        <f>Assumptions!$C$55</f>
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="C34" s="83" t="inlineStr">
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="B36" s="33">
-        <f>Assumptions!$C$70</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="C36" s="82" t="inlineStr">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>Assumptions!$C$87</f>
+        <f>Assumptions!$C$88</f>
         <v/>
       </c>
       <c r="C37" s="82" t="inlineStr">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>Assumptions!$C$84</f>
+        <f>Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="C38" s="77" t="inlineStr">
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>Assumptions!$C$86</f>
+        <f>Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="C39" s="77" t="inlineStr">
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>Assumptions!$C$85</f>
+        <f>Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="C40" s="77" t="inlineStr">
@@ -5950,43 +5950,43 @@
         </is>
       </c>
       <c r="C6" s="30">
-        <f>Revenue!C21</f>
+        <f>Revenue!C22</f>
         <v/>
       </c>
       <c r="D6" s="30">
-        <f>Revenue!D21</f>
+        <f>Revenue!D22</f>
         <v/>
       </c>
       <c r="E6" s="30">
-        <f>Revenue!E21</f>
+        <f>Revenue!E22</f>
         <v/>
       </c>
       <c r="F6" s="30">
-        <f>Revenue!F21</f>
+        <f>Revenue!F22</f>
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>Revenue!G21</f>
+        <f>Revenue!G22</f>
         <v/>
       </c>
       <c r="H6" s="30">
-        <f>Revenue!H21</f>
+        <f>Revenue!H22</f>
         <v/>
       </c>
       <c r="I6" s="30">
-        <f>Revenue!I21</f>
+        <f>Revenue!I22</f>
         <v/>
       </c>
       <c r="J6" s="30">
-        <f>Revenue!J21</f>
+        <f>Revenue!J22</f>
         <v/>
       </c>
       <c r="K6" s="30">
-        <f>Revenue!K21</f>
+        <f>Revenue!K22</f>
         <v/>
       </c>
       <c r="L6" s="30">
-        <f>Revenue!L21</f>
+        <f>Revenue!L22</f>
         <v/>
       </c>
     </row>
@@ -6072,34 +6072,34 @@
         </is>
       </c>
       <c r="C10" s="22" t="n">
-        <v>12020.4441601185</v>
+        <v>13471.23223109862</v>
       </c>
       <c r="D10" s="22" t="n">
-        <v>70444.13474730599</v>
+        <v>80172.86367656694</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>285233.4616352503</v>
+        <v>324954.3266336625</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>879793.8483710603</v>
+        <v>997729.1293521416</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>2132472.910797332</v>
+        <v>2405944.872754806</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>4003132.499105871</v>
+        <v>4500263.01540566</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>6434712.813377975</v>
+        <v>7225273.097037062</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>9026699.212080941</v>
+        <v>10131408.91889975</v>
       </c>
       <c r="K10" s="22" t="n">
-        <v>11304755.83034156</v>
+        <v>12708269.29438148</v>
       </c>
       <c r="L10" s="22" t="n">
-        <v>13666526.18900019</v>
+        <v>15327976.37081417</v>
       </c>
     </row>
     <row r="11">
@@ -6236,34 +6236,34 @@
         </is>
       </c>
       <c r="C15" s="22" t="n">
-        <v>12756.59125509603</v>
+        <v>11305.80318411591</v>
       </c>
       <c r="D15" s="22" t="n">
-        <v>131589.0636071867</v>
+        <v>121860.3346779258</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>633849.6940189952</v>
+        <v>594128.8290205828</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>2133206.532581586</v>
+        <v>2015271.251600505</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>5435977.066457794</v>
+        <v>5162505.10450032</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>10696744.90488742</v>
+        <v>10199614.38858763</v>
       </c>
       <c r="I15" s="22" t="n">
-        <v>17697206.97909645</v>
+        <v>16906646.69543736</v>
       </c>
       <c r="J15" s="22" t="n">
-        <v>25320637.21788888</v>
+        <v>24215927.51107008</v>
       </c>
       <c r="K15" s="22" t="n">
-        <v>32020813.46612882</v>
+        <v>30617300.00208889</v>
       </c>
       <c r="L15" s="22" t="n">
-        <v>39268287.2950196</v>
+        <v>37606837.11320563</v>
       </c>
     </row>
     <row r="16">
@@ -6564,34 +6564,34 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>-93605.57157812113</v>
+        <v>-95056.35964910126</v>
       </c>
       <c r="D25" s="22" t="n">
-        <v>-205636.7922611727</v>
+        <v>-215365.5211904336</v>
       </c>
       <c r="E25" s="22" t="n">
-        <v>-344604.7984333446</v>
+        <v>-384325.6634317569</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>-129045.4978946252</v>
+        <v>-246980.7788757063</v>
       </c>
       <c r="G25" s="22" t="n">
-        <v>1231485.068277384</v>
+        <v>958013.1063199099</v>
       </c>
       <c r="H25" s="22" t="n">
-        <v>4248309.712567959</v>
+        <v>3751179.196268169</v>
       </c>
       <c r="I25" s="22" t="n">
-        <v>8581573.395698495</v>
+        <v>7791013.11203941</v>
       </c>
       <c r="J25" s="22" t="n">
-        <v>14133506.3034913</v>
+        <v>13028796.59667249</v>
       </c>
       <c r="K25" s="22" t="n">
-        <v>19247405.42241119</v>
+        <v>17843891.95837126</v>
       </c>
       <c r="L25" s="22" t="n">
-        <v>25249195.01629802</v>
+        <v>23587744.83448404</v>
       </c>
     </row>
     <row r="26">
@@ -7098,43 +7098,43 @@
         </is>
       </c>
       <c r="C41" s="30">
-        <f>Revenue!C15</f>
+        <f>Revenue!C16</f>
         <v/>
       </c>
       <c r="D41" s="30">
-        <f>Revenue!D15</f>
+        <f>Revenue!D16</f>
         <v/>
       </c>
       <c r="E41" s="30">
-        <f>Revenue!E15</f>
+        <f>Revenue!E16</f>
         <v/>
       </c>
       <c r="F41" s="30">
-        <f>Revenue!F15</f>
+        <f>Revenue!F16</f>
         <v/>
       </c>
       <c r="G41" s="30">
-        <f>Revenue!G15</f>
+        <f>Revenue!G16</f>
         <v/>
       </c>
       <c r="H41" s="30">
-        <f>Revenue!H15</f>
+        <f>Revenue!H16</f>
         <v/>
       </c>
       <c r="I41" s="30">
-        <f>Revenue!I15</f>
+        <f>Revenue!I16</f>
         <v/>
       </c>
       <c r="J41" s="30">
-        <f>Revenue!J15</f>
+        <f>Revenue!J16</f>
         <v/>
       </c>
       <c r="K41" s="30">
-        <f>Revenue!K15</f>
+        <f>Revenue!K16</f>
         <v/>
       </c>
       <c r="L41" s="30">
-        <f>Revenue!L15</f>
+        <f>Revenue!L16</f>
         <v/>
       </c>
     </row>
@@ -7727,19 +7727,19 @@
         <v>0</v>
       </c>
       <c r="H60" s="22" t="n">
-        <v>552990.3181017119</v>
+        <v>412074.5969161622</v>
       </c>
       <c r="I60" s="22" t="n">
-        <v>1174256.009354774</v>
+        <v>1055671.966805911</v>
       </c>
       <c r="J60" s="22" t="n">
-        <v>1963845.945523695</v>
+        <v>1798139.489500874</v>
       </c>
       <c r="K60" s="22" t="n">
-        <v>2687730.813361678</v>
+        <v>2477203.793755689</v>
       </c>
       <c r="L60" s="22" t="n">
-        <v>5915498.754074506</v>
+        <v>5500136.208621011</v>
       </c>
     </row>
     <row r="61">
@@ -7876,34 +7876,34 @@
         </is>
       </c>
       <c r="C65" s="22" t="n">
-        <v>-99305.57157812113</v>
+        <v>-100756.3596491013</v>
       </c>
       <c r="D65" s="22" t="n">
-        <v>-226936.7922611727</v>
+        <v>-236665.5211904336</v>
       </c>
       <c r="E65" s="22" t="n">
-        <v>-407904.7984333446</v>
+        <v>-447625.6634317569</v>
       </c>
       <c r="F65" s="22" t="n">
-        <v>-276245.4978946252</v>
+        <v>-394180.7788757063</v>
       </c>
       <c r="G65" s="22" t="n">
-        <v>941485.0682773842</v>
+        <v>668013.1063199099</v>
       </c>
       <c r="H65" s="22" t="n">
-        <v>3202519.394466247</v>
+        <v>2846304.599352007</v>
       </c>
       <c r="I65" s="22" t="n">
-        <v>6654117.386343721</v>
+        <v>5982141.145233498</v>
       </c>
       <c r="J65" s="22" t="n">
-        <v>11128460.3579676</v>
+        <v>10189457.10717162</v>
       </c>
       <c r="K65" s="22" t="n">
-        <v>15230474.60904951</v>
+        <v>14037488.16461557</v>
       </c>
       <c r="L65" s="22" t="n">
-        <v>17746496.26222352</v>
+        <v>16500408.62586303</v>
       </c>
     </row>
     <row r="66">
@@ -8040,34 +8040,34 @@
         </is>
       </c>
       <c r="C70" s="22" t="n">
-        <v>-95612.83890272945</v>
+        <v>-95861.09014160134</v>
       </c>
       <c r="D70" s="22" t="n">
-        <v>-199265.4988776602</v>
+        <v>-202132.7647337024</v>
       </c>
       <c r="E70" s="22" t="n">
-        <v>-276003.8646593865</v>
+        <v>-290864.6904706898</v>
       </c>
       <c r="F70" s="22" t="n">
-        <v>151325.8217507345</v>
+        <v>98221.31647175329</v>
       </c>
       <c r="G70" s="22" t="n">
-        <v>1939653.467349641</v>
+        <v>1795103.566001351</v>
       </c>
       <c r="H70" s="22" t="n">
-        <v>4773980.047885393</v>
+        <v>4603152.529378005</v>
       </c>
       <c r="I70" s="22" t="n">
-        <v>8703299.470125826</v>
+        <v>8274542.834928216</v>
       </c>
       <c r="J70" s="22" t="n">
-        <v>13307321.18996631</v>
+        <v>12628711.76214951</v>
       </c>
       <c r="K70" s="22" t="n">
-        <v>17053271.0817335</v>
+        <v>16107958.66413932</v>
       </c>
       <c r="L70" s="22" t="n">
-        <v>19840219.36853875</v>
+        <v>18807931.6728318</v>
       </c>
     </row>
     <row r="71">
@@ -8251,7 +8251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:N89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -9762,269 +9762,269 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PPV &amp; tips as multiple of subs</t>
+          <t>VAT on fan subscriptions</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D42" s="25">
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D42" s="23">
         <f>C42</f>
         <v/>
       </c>
-      <c r="E42" s="25">
+      <c r="E42" s="23">
         <f>C42</f>
         <v/>
       </c>
-      <c r="F42" s="25">
+      <c r="F42" s="23">
         <f>C42</f>
         <v/>
       </c>
-      <c r="G42" s="25">
+      <c r="G42" s="23">
         <f>C42</f>
         <v/>
       </c>
-      <c r="H42" s="25">
+      <c r="H42" s="23">
         <f>C42</f>
         <v/>
       </c>
-      <c r="I42" s="25">
+      <c r="I42" s="23">
         <f>C42</f>
         <v/>
       </c>
-      <c r="J42" s="25">
+      <c r="J42" s="23">
         <f>C42</f>
         <v/>
       </c>
-      <c r="K42" s="25">
+      <c r="K42" s="23">
         <f>C42</f>
         <v/>
       </c>
-      <c r="L42" s="25">
+      <c r="L42" s="23">
         <f>C42</f>
         <v/>
+      </c>
+      <c r="N42" s="18" t="inlineStr">
+        <is>
+          <t>Spain's rate. Fan prices are displayed VAT-inclusive, so the take applies to price/(1+VAT) while the processor charges on the price</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>PSP percentage fee</t>
+          <t>PPV &amp; tips as multiple of subs</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C43" s="26" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="D43" s="27">
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D43" s="25">
         <f>C43</f>
         <v/>
       </c>
-      <c r="E43" s="27">
+      <c r="E43" s="25">
         <f>C43</f>
         <v/>
       </c>
-      <c r="F43" s="27">
+      <c r="F43" s="25">
         <f>C43</f>
         <v/>
       </c>
-      <c r="G43" s="27">
+      <c r="G43" s="25">
         <f>C43</f>
         <v/>
       </c>
-      <c r="H43" s="27">
+      <c r="H43" s="25">
         <f>C43</f>
         <v/>
       </c>
-      <c r="I43" s="27">
+      <c r="I43" s="25">
         <f>C43</f>
         <v/>
       </c>
-      <c r="J43" s="27">
+      <c r="J43" s="25">
         <f>C43</f>
         <v/>
       </c>
-      <c r="K43" s="27">
+      <c r="K43" s="25">
         <f>C43</f>
         <v/>
       </c>
-      <c r="L43" s="27">
+      <c r="L43" s="25">
         <f>C43</f>
         <v/>
-      </c>
-      <c r="N43" s="18" t="inlineStr">
-        <is>
-          <t>Stripe published pricing</t>
-        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PSP fixed fee per transaction</t>
+          <t>PSP percentage fee</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C44" s="28" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D44" s="29">
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="D44" s="27">
         <f>C44</f>
         <v/>
       </c>
-      <c r="E44" s="29">
+      <c r="E44" s="27">
         <f>C44</f>
         <v/>
       </c>
-      <c r="F44" s="29">
+      <c r="F44" s="27">
         <f>C44</f>
         <v/>
       </c>
-      <c r="G44" s="29">
+      <c r="G44" s="27">
         <f>C44</f>
         <v/>
       </c>
-      <c r="H44" s="29">
+      <c r="H44" s="27">
         <f>C44</f>
         <v/>
       </c>
-      <c r="I44" s="29">
+      <c r="I44" s="27">
         <f>C44</f>
         <v/>
       </c>
-      <c r="J44" s="29">
+      <c r="J44" s="27">
         <f>C44</f>
         <v/>
       </c>
-      <c r="K44" s="29">
+      <c r="K44" s="27">
         <f>C44</f>
         <v/>
       </c>
-      <c r="L44" s="29">
+      <c r="L44" s="27">
         <f>C44</f>
         <v/>
       </c>
       <c r="N44" s="18" t="inlineStr">
         <is>
-          <t>Stripe. The single most damaging cost at small ticket sizes</t>
+          <t>Stripe published pricing</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>Payout percentage fee</t>
+          <t>PSP fixed fee per transaction</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C45" s="26" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="D45" s="27">
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D45" s="29">
         <f>C45</f>
         <v/>
       </c>
-      <c r="E45" s="27">
+      <c r="E45" s="29">
         <f>C45</f>
         <v/>
       </c>
-      <c r="F45" s="27">
+      <c r="F45" s="29">
         <f>C45</f>
         <v/>
       </c>
-      <c r="G45" s="27">
+      <c r="G45" s="29">
         <f>C45</f>
         <v/>
       </c>
-      <c r="H45" s="27">
+      <c r="H45" s="29">
         <f>C45</f>
         <v/>
       </c>
-      <c r="I45" s="27">
+      <c r="I45" s="29">
         <f>C45</f>
         <v/>
       </c>
-      <c r="J45" s="27">
+      <c r="J45" s="29">
         <f>C45</f>
         <v/>
       </c>
-      <c r="K45" s="27">
+      <c r="K45" s="29">
         <f>C45</f>
         <v/>
       </c>
-      <c r="L45" s="27">
+      <c r="L45" s="29">
         <f>C45</f>
         <v/>
       </c>
       <c r="N45" s="18" t="inlineStr">
         <is>
-          <t>Stripe Connect</t>
+          <t>Stripe. The single most damaging cost at small ticket sizes</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>Payout fixed fee</t>
+          <t>Payout percentage fee</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C46" s="28" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D46" s="29">
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="D46" s="27">
         <f>C46</f>
         <v/>
       </c>
-      <c r="E46" s="29">
+      <c r="E46" s="27">
         <f>C46</f>
         <v/>
       </c>
-      <c r="F46" s="29">
+      <c r="F46" s="27">
         <f>C46</f>
         <v/>
       </c>
-      <c r="G46" s="29">
+      <c r="G46" s="27">
         <f>C46</f>
         <v/>
       </c>
-      <c r="H46" s="29">
+      <c r="H46" s="27">
         <f>C46</f>
         <v/>
       </c>
-      <c r="I46" s="29">
+      <c r="I46" s="27">
         <f>C46</f>
         <v/>
       </c>
-      <c r="J46" s="29">
+      <c r="J46" s="27">
         <f>C46</f>
         <v/>
       </c>
-      <c r="K46" s="29">
+      <c r="K46" s="27">
         <f>C46</f>
         <v/>
       </c>
-      <c r="L46" s="29">
+      <c r="L46" s="27">
         <f>C46</f>
         <v/>
       </c>
@@ -10037,7 +10037,7 @@
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>Average fan transaction</t>
+          <t>Payout fixed fee</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
@@ -10045,8 +10045,8 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C47" s="20" t="n">
-        <v>9.199999999999999</v>
+      <c r="C47" s="28" t="n">
+        <v>0.25</v>
       </c>
       <c r="D47" s="29">
         <f>C47</f>
@@ -10084,229 +10084,229 @@
         <f>C47</f>
         <v/>
       </c>
+      <c r="N47" s="18" t="inlineStr">
+        <is>
+          <t>Stripe Connect</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
+          <t>Average fan transaction</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D48" s="29">
+        <f>C48</f>
+        <v/>
+      </c>
+      <c r="E48" s="29">
+        <f>C48</f>
+        <v/>
+      </c>
+      <c r="F48" s="29">
+        <f>C48</f>
+        <v/>
+      </c>
+      <c r="G48" s="29">
+        <f>C48</f>
+        <v/>
+      </c>
+      <c r="H48" s="29">
+        <f>C48</f>
+        <v/>
+      </c>
+      <c r="I48" s="29">
+        <f>C48</f>
+        <v/>
+      </c>
+      <c r="J48" s="29">
+        <f>C48</f>
+        <v/>
+      </c>
+      <c r="K48" s="29">
+        <f>C48</f>
+        <v/>
+      </c>
+      <c r="L48" s="29">
+        <f>C48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
           <t>Average deal transaction</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="C48" s="22" t="n">
+      <c r="C49" s="22" t="n">
         <v>1800</v>
       </c>
-      <c r="D48" s="30">
-        <f>C48</f>
-        <v/>
-      </c>
-      <c r="E48" s="30">
-        <f>C48</f>
-        <v/>
-      </c>
-      <c r="F48" s="30">
-        <f>C48</f>
-        <v/>
-      </c>
-      <c r="G48" s="30">
-        <f>C48</f>
-        <v/>
-      </c>
-      <c r="H48" s="30">
-        <f>C48</f>
-        <v/>
-      </c>
-      <c r="I48" s="30">
-        <f>C48</f>
-        <v/>
-      </c>
-      <c r="J48" s="30">
-        <f>C48</f>
-        <v/>
-      </c>
-      <c r="K48" s="30">
-        <f>C48</f>
-        <v/>
-      </c>
-      <c r="L48" s="30">
-        <f>C48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+      <c r="D49" s="30">
+        <f>C49</f>
+        <v/>
+      </c>
+      <c r="E49" s="30">
+        <f>C49</f>
+        <v/>
+      </c>
+      <c r="F49" s="30">
+        <f>C49</f>
+        <v/>
+      </c>
+      <c r="G49" s="30">
+        <f>C49</f>
+        <v/>
+      </c>
+      <c r="H49" s="30">
+        <f>C49</f>
+        <v/>
+      </c>
+      <c r="I49" s="30">
+        <f>C49</f>
+        <v/>
+      </c>
+      <c r="J49" s="30">
+        <f>C49</f>
+        <v/>
+      </c>
+      <c r="K49" s="30">
+        <f>C49</f>
+        <v/>
+      </c>
+      <c r="L49" s="30">
+        <f>C49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>INFRASTRUCTURE &amp; CONTENT COSTS</t>
         </is>
       </c>
-      <c r="B50" s="12" t="n"/>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="12" t="n"/>
-      <c r="E50" s="12" t="n"/>
-      <c r="F50" s="12" t="n"/>
-      <c r="G50" s="12" t="n"/>
-      <c r="H50" s="12" t="n"/>
-      <c r="I50" s="12" t="n"/>
-      <c r="J50" s="12" t="n"/>
-      <c r="K50" s="12" t="n"/>
-      <c r="L50" s="12" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="13" t="inlineStr">
-        <is>
-          <t>AWS base cost per month</t>
-        </is>
-      </c>
-      <c r="B51" s="14" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C51" s="22" t="n">
-        <v>180</v>
-      </c>
-      <c r="D51" s="22" t="n">
-        <v>650</v>
-      </c>
-      <c r="E51" s="22" t="n">
-        <v>2100</v>
-      </c>
-      <c r="F51" s="22" t="n">
-        <v>5400</v>
-      </c>
-      <c r="G51" s="22" t="n">
-        <v>11000</v>
-      </c>
-      <c r="H51" s="22" t="n">
-        <v>17000</v>
-      </c>
-      <c r="I51" s="22" t="n">
-        <v>24000</v>
-      </c>
-      <c r="J51" s="22" t="n">
-        <v>30000</v>
-      </c>
-      <c r="K51" s="22" t="n">
-        <v>35000</v>
-      </c>
-      <c r="L51" s="22" t="n">
-        <v>39000</v>
-      </c>
+      <c r="B51" s="12" t="n"/>
+      <c r="C51" s="12" t="n"/>
+      <c r="D51" s="12" t="n"/>
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="12" t="n"/>
+      <c r="G51" s="12" t="n"/>
+      <c r="H51" s="12" t="n"/>
+      <c r="I51" s="12" t="n"/>
+      <c r="J51" s="12" t="n"/>
+      <c r="K51" s="12" t="n"/>
+      <c r="L51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>Media GB per paying fan per month</t>
+          <t>AWS base cost per month</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="C52" s="21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D52" s="31">
-        <f>C52</f>
-        <v/>
-      </c>
-      <c r="E52" s="31">
-        <f>C52</f>
-        <v/>
-      </c>
-      <c r="F52" s="31">
-        <f>C52</f>
-        <v/>
-      </c>
-      <c r="G52" s="31">
-        <f>C52</f>
-        <v/>
-      </c>
-      <c r="H52" s="31">
-        <f>C52</f>
-        <v/>
-      </c>
-      <c r="I52" s="31">
-        <f>C52</f>
-        <v/>
-      </c>
-      <c r="J52" s="31">
-        <f>C52</f>
-        <v/>
-      </c>
-      <c r="K52" s="31">
-        <f>C52</f>
-        <v/>
-      </c>
-      <c r="L52" s="31">
-        <f>C52</f>
-        <v/>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="n">
+        <v>180</v>
+      </c>
+      <c r="D52" s="22" t="n">
+        <v>650</v>
+      </c>
+      <c r="E52" s="22" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F52" s="22" t="n">
+        <v>5400</v>
+      </c>
+      <c r="G52" s="22" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H52" s="22" t="n">
+        <v>17000</v>
+      </c>
+      <c r="I52" s="22" t="n">
+        <v>24000</v>
+      </c>
+      <c r="J52" s="22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K52" s="22" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L52" s="22" t="n">
+        <v>39000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>Egress cost per GB (zero-egress CDN)</t>
+          <t>Media GB per paying fan per month</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C53" s="32" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="D53" s="33">
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D53" s="31">
         <f>C53</f>
         <v/>
       </c>
-      <c r="E53" s="33">
+      <c r="E53" s="31">
         <f>C53</f>
         <v/>
       </c>
-      <c r="F53" s="33">
+      <c r="F53" s="31">
         <f>C53</f>
         <v/>
       </c>
-      <c r="G53" s="33">
+      <c r="G53" s="31">
         <f>C53</f>
         <v/>
       </c>
-      <c r="H53" s="33">
+      <c r="H53" s="31">
         <f>C53</f>
         <v/>
       </c>
-      <c r="I53" s="33">
+      <c r="I53" s="31">
         <f>C53</f>
         <v/>
       </c>
-      <c r="J53" s="33">
+      <c r="J53" s="31">
         <f>C53</f>
         <v/>
       </c>
-      <c r="K53" s="33">
+      <c r="K53" s="31">
         <f>C53</f>
         <v/>
       </c>
-      <c r="L53" s="33">
+      <c r="L53" s="31">
         <f>C53</f>
         <v/>
-      </c>
-      <c r="N53" s="18" t="inlineStr">
-        <is>
-          <t>Cloudflare R2 / Backblaze B2 list</t>
-        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>Egress cost per GB (CloudFront list)</t>
+          <t>Egress cost per GB (zero-egress CDN)</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
@@ -10315,7 +10315,7 @@
         </is>
       </c>
       <c r="C54" s="32" t="n">
-        <v>0.075</v>
+        <v>0.008</v>
       </c>
       <c r="D54" s="33">
         <f>C54</f>
@@ -10355,14 +10355,14 @@
       </c>
       <c r="N54" s="18" t="inlineStr">
         <is>
-          <t>AWS CloudFront list price — the EUR 1.1M/yr trap</t>
+          <t>Cloudflare R2 / Backblaze B2 list</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>Moderation cost per 1,000 items</t>
+          <t>Egress cost per GB (CloudFront list)</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
@@ -10370,203 +10370,217 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C55" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="D55" s="29">
+      <c r="C55" s="32" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D55" s="33">
         <f>C55</f>
         <v/>
       </c>
-      <c r="E55" s="29">
+      <c r="E55" s="33">
         <f>C55</f>
         <v/>
       </c>
-      <c r="F55" s="29">
+      <c r="F55" s="33">
         <f>C55</f>
         <v/>
       </c>
-      <c r="G55" s="29">
+      <c r="G55" s="33">
         <f>C55</f>
         <v/>
       </c>
-      <c r="H55" s="29">
+      <c r="H55" s="33">
         <f>C55</f>
         <v/>
       </c>
-      <c r="I55" s="29">
+      <c r="I55" s="33">
         <f>C55</f>
         <v/>
       </c>
-      <c r="J55" s="29">
+      <c r="J55" s="33">
         <f>C55</f>
         <v/>
       </c>
-      <c r="K55" s="29">
+      <c r="K55" s="33">
         <f>C55</f>
         <v/>
       </c>
-      <c r="L55" s="29">
+      <c r="L55" s="33">
         <f>C55</f>
         <v/>
+      </c>
+      <c r="N55" s="18" t="inlineStr">
+        <is>
+          <t>AWS CloudFront list price — the EUR 1.1M/yr trap</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
+          <t>Moderation cost per 1,000 items</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="D56" s="29">
+        <f>C56</f>
+        <v/>
+      </c>
+      <c r="E56" s="29">
+        <f>C56</f>
+        <v/>
+      </c>
+      <c r="F56" s="29">
+        <f>C56</f>
+        <v/>
+      </c>
+      <c r="G56" s="29">
+        <f>C56</f>
+        <v/>
+      </c>
+      <c r="H56" s="29">
+        <f>C56</f>
+        <v/>
+      </c>
+      <c r="I56" s="29">
+        <f>C56</f>
+        <v/>
+      </c>
+      <c r="J56" s="29">
+        <f>C56</f>
+        <v/>
+      </c>
+      <c r="K56" s="29">
+        <f>C56</f>
+        <v/>
+      </c>
+      <c r="L56" s="29">
+        <f>C56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
           <t>Items per athlete per month</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="C56" s="21" t="n">
+      <c r="C57" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="D56" s="31">
-        <f>C56</f>
-        <v/>
-      </c>
-      <c r="E56" s="31">
-        <f>C56</f>
-        <v/>
-      </c>
-      <c r="F56" s="31">
-        <f>C56</f>
-        <v/>
-      </c>
-      <c r="G56" s="31">
-        <f>C56</f>
-        <v/>
-      </c>
-      <c r="H56" s="31">
-        <f>C56</f>
-        <v/>
-      </c>
-      <c r="I56" s="31">
-        <f>C56</f>
-        <v/>
-      </c>
-      <c r="J56" s="31">
-        <f>C56</f>
-        <v/>
-      </c>
-      <c r="K56" s="31">
-        <f>C56</f>
-        <v/>
-      </c>
-      <c r="L56" s="31">
-        <f>C56</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="D57" s="31">
+        <f>C57</f>
+        <v/>
+      </c>
+      <c r="E57" s="31">
+        <f>C57</f>
+        <v/>
+      </c>
+      <c r="F57" s="31">
+        <f>C57</f>
+        <v/>
+      </c>
+      <c r="G57" s="31">
+        <f>C57</f>
+        <v/>
+      </c>
+      <c r="H57" s="31">
+        <f>C57</f>
+        <v/>
+      </c>
+      <c r="I57" s="31">
+        <f>C57</f>
+        <v/>
+      </c>
+      <c r="J57" s="31">
+        <f>C57</f>
+        <v/>
+      </c>
+      <c r="K57" s="31">
+        <f>C57</f>
+        <v/>
+      </c>
+      <c r="L57" s="31">
+        <f>C57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>PEOPLE &amp; OVERHEAD</t>
         </is>
       </c>
-      <c r="B58" s="12" t="n"/>
-      <c r="C58" s="12" t="n"/>
-      <c r="D58" s="12" t="n"/>
-      <c r="E58" s="12" t="n"/>
-      <c r="F58" s="12" t="n"/>
-      <c r="G58" s="12" t="n"/>
-      <c r="H58" s="12" t="n"/>
-      <c r="I58" s="12" t="n"/>
-      <c r="J58" s="12" t="n"/>
-      <c r="K58" s="12" t="n"/>
-      <c r="L58" s="12" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="13" t="inlineStr">
-        <is>
-          <t>Headcount</t>
-        </is>
-      </c>
-      <c r="B59" s="14" t="inlineStr">
-        <is>
-          <t>FTE</t>
-        </is>
-      </c>
-      <c r="C59" s="21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D59" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E59" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="F59" s="21" t="n">
-        <v>14</v>
-      </c>
-      <c r="G59" s="21" t="n">
-        <v>24</v>
-      </c>
-      <c r="H59" s="21" t="n">
-        <v>36</v>
-      </c>
-      <c r="I59" s="21" t="n">
-        <v>50</v>
-      </c>
-      <c r="J59" s="21" t="n">
-        <v>62</v>
-      </c>
-      <c r="K59" s="21" t="n">
-        <v>72</v>
-      </c>
-      <c r="L59" s="21" t="n">
-        <v>80</v>
-      </c>
+      <c r="B59" s="12" t="n"/>
+      <c r="C59" s="12" t="n"/>
+      <c r="D59" s="12" t="n"/>
+      <c r="E59" s="12" t="n"/>
+      <c r="F59" s="12" t="n"/>
+      <c r="G59" s="12" t="n"/>
+      <c r="H59" s="12" t="n"/>
+      <c r="I59" s="12" t="n"/>
+      <c r="J59" s="12" t="n"/>
+      <c r="K59" s="12" t="n"/>
+      <c r="L59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>Loaded salary (incl. ~31% employer SS)</t>
+          <t>Headcount</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C60" s="22" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D60" s="22" t="n">
-        <v>52000</v>
-      </c>
-      <c r="E60" s="22" t="n">
-        <v>60000</v>
-      </c>
-      <c r="F60" s="22" t="n">
-        <v>64000</v>
-      </c>
-      <c r="G60" s="22" t="n">
-        <v>66000</v>
-      </c>
-      <c r="H60" s="22" t="n">
-        <v>68000</v>
-      </c>
-      <c r="I60" s="22" t="n">
-        <v>70000</v>
-      </c>
-      <c r="J60" s="22" t="n">
-        <v>72000</v>
-      </c>
-      <c r="K60" s="22" t="n">
-        <v>74000</v>
-      </c>
-      <c r="L60" s="22" t="n">
-        <v>76000</v>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D60" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F60" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="G60" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="H60" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="I60" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="J60" s="21" t="n">
+        <v>62</v>
+      </c>
+      <c r="K60" s="21" t="n">
+        <v>72</v>
+      </c>
+      <c r="L60" s="21" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>Legal &amp; compliance</t>
+          <t>Loaded salary (incl. ~31% employer SS)</t>
         </is>
       </c>
       <c r="B61" s="14" t="inlineStr">
@@ -10575,165 +10589,151 @@
         </is>
       </c>
       <c r="C61" s="22" t="n">
-        <v>18000</v>
+        <v>38000</v>
       </c>
       <c r="D61" s="22" t="n">
-        <v>45000</v>
+        <v>52000</v>
       </c>
       <c r="E61" s="22" t="n">
-        <v>90000</v>
+        <v>60000</v>
       </c>
       <c r="F61" s="22" t="n">
-        <v>150000</v>
+        <v>64000</v>
       </c>
       <c r="G61" s="22" t="n">
-        <v>200000</v>
+        <v>66000</v>
       </c>
       <c r="H61" s="22" t="n">
-        <v>235000</v>
+        <v>68000</v>
       </c>
       <c r="I61" s="22" t="n">
-        <v>270000</v>
+        <v>70000</v>
       </c>
       <c r="J61" s="22" t="n">
-        <v>300000</v>
+        <v>72000</v>
       </c>
       <c r="K61" s="22" t="n">
-        <v>325000</v>
+        <v>74000</v>
       </c>
       <c r="L61" s="22" t="n">
-        <v>345000</v>
+        <v>76000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
+          <t>Legal &amp; compliance</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C62" s="22" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D62" s="22" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E62" s="22" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F62" s="22" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G62" s="22" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H62" s="22" t="n">
+        <v>235000</v>
+      </c>
+      <c r="I62" s="22" t="n">
+        <v>270000</v>
+      </c>
+      <c r="J62" s="22" t="n">
+        <v>300000</v>
+      </c>
+      <c r="K62" s="22" t="n">
+        <v>325000</v>
+      </c>
+      <c r="L62" s="22" t="n">
+        <v>345000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
           <t>Other opex as % of revenue</t>
         </is>
       </c>
-      <c r="B62" s="14" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C62" s="16" t="n">
+      <c r="C63" s="16" t="n">
         <v>0.08</v>
       </c>
-      <c r="D62" s="23">
-        <f>C62</f>
-        <v/>
-      </c>
-      <c r="E62" s="23">
-        <f>C62</f>
-        <v/>
-      </c>
-      <c r="F62" s="23">
-        <f>C62</f>
-        <v/>
-      </c>
-      <c r="G62" s="23">
-        <f>C62</f>
-        <v/>
-      </c>
-      <c r="H62" s="23">
-        <f>C62</f>
-        <v/>
-      </c>
-      <c r="I62" s="23">
-        <f>C62</f>
-        <v/>
-      </c>
-      <c r="J62" s="23">
-        <f>C62</f>
-        <v/>
-      </c>
-      <c r="K62" s="23">
-        <f>C62</f>
-        <v/>
-      </c>
-      <c r="L62" s="23">
-        <f>C62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="11" t="inlineStr">
+      <c r="D63" s="23">
+        <f>C63</f>
+        <v/>
+      </c>
+      <c r="E63" s="23">
+        <f>C63</f>
+        <v/>
+      </c>
+      <c r="F63" s="23">
+        <f>C63</f>
+        <v/>
+      </c>
+      <c r="G63" s="23">
+        <f>C63</f>
+        <v/>
+      </c>
+      <c r="H63" s="23">
+        <f>C63</f>
+        <v/>
+      </c>
+      <c r="I63" s="23">
+        <f>C63</f>
+        <v/>
+      </c>
+      <c r="J63" s="23">
+        <f>C63</f>
+        <v/>
+      </c>
+      <c r="K63" s="23">
+        <f>C63</f>
+        <v/>
+      </c>
+      <c r="L63" s="23">
+        <f>C63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>WORKING CAPITAL, CAPEX &amp; TAX</t>
         </is>
       </c>
-      <c r="B64" s="12" t="n"/>
-      <c r="C64" s="12" t="n"/>
-      <c r="D64" s="12" t="n"/>
-      <c r="E64" s="12" t="n"/>
-      <c r="F64" s="12" t="n"/>
-      <c r="G64" s="12" t="n"/>
-      <c r="H64" s="12" t="n"/>
-      <c r="I64" s="12" t="n"/>
-      <c r="J64" s="12" t="n"/>
-      <c r="K64" s="12" t="n"/>
-      <c r="L64" s="12" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="13" t="inlineStr">
-        <is>
-          <t>Athlete payout float</t>
-        </is>
-      </c>
-      <c r="B65" s="14" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="C65" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="D65" s="17">
-        <f>C65</f>
-        <v/>
-      </c>
-      <c r="E65" s="17">
-        <f>C65</f>
-        <v/>
-      </c>
-      <c r="F65" s="17">
-        <f>C65</f>
-        <v/>
-      </c>
-      <c r="G65" s="17">
-        <f>C65</f>
-        <v/>
-      </c>
-      <c r="H65" s="17">
-        <f>C65</f>
-        <v/>
-      </c>
-      <c r="I65" s="17">
-        <f>C65</f>
-        <v/>
-      </c>
-      <c r="J65" s="17">
-        <f>C65</f>
-        <v/>
-      </c>
-      <c r="K65" s="17">
-        <f>C65</f>
-        <v/>
-      </c>
-      <c r="L65" s="17">
-        <f>C65</f>
-        <v/>
-      </c>
-      <c r="N65" s="18" t="inlineStr">
-        <is>
-          <t>We hold fan money before paying athletes — a cash benefit</t>
-        </is>
-      </c>
+      <c r="B65" s="12" t="n"/>
+      <c r="C65" s="12" t="n"/>
+      <c r="D65" s="12" t="n"/>
+      <c r="E65" s="12" t="n"/>
+      <c r="F65" s="12" t="n"/>
+      <c r="G65" s="12" t="n"/>
+      <c r="H65" s="12" t="n"/>
+      <c r="I65" s="12" t="n"/>
+      <c r="J65" s="12" t="n"/>
+      <c r="K65" s="12" t="n"/>
+      <c r="L65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>Sponsor receivable days</t>
+          <t>Athlete payout float</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
@@ -10742,7 +10742,7 @@
         </is>
       </c>
       <c r="C66" s="15" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D66" s="17">
         <f>C66</f>
@@ -10780,11 +10780,16 @@
         <f>C66</f>
         <v/>
       </c>
+      <c r="N66" s="18" t="inlineStr">
+        <is>
+          <t>We hold fan money before paying athletes — a cash benefit</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>Trade payable days</t>
+          <t>Sponsor receivable days</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
@@ -10793,7 +10798,7 @@
         </is>
       </c>
       <c r="C67" s="15" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D67" s="17">
         <f>C67</f>
@@ -10835,50 +10840,50 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>Capitalised development</t>
+          <t>Trade payable days</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>% of people cost</t>
-        </is>
-      </c>
-      <c r="C68" s="16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D68" s="23">
+          <t>days</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="D68" s="17">
         <f>C68</f>
         <v/>
       </c>
-      <c r="E68" s="23">
+      <c r="E68" s="17">
         <f>C68</f>
         <v/>
       </c>
-      <c r="F68" s="23">
+      <c r="F68" s="17">
         <f>C68</f>
         <v/>
       </c>
-      <c r="G68" s="23">
+      <c r="G68" s="17">
         <f>C68</f>
         <v/>
       </c>
-      <c r="H68" s="23">
+      <c r="H68" s="17">
         <f>C68</f>
         <v/>
       </c>
-      <c r="I68" s="23">
+      <c r="I68" s="17">
         <f>C68</f>
         <v/>
       </c>
-      <c r="J68" s="23">
+      <c r="J68" s="17">
         <f>C68</f>
         <v/>
       </c>
-      <c r="K68" s="23">
+      <c r="K68" s="17">
         <f>C68</f>
         <v/>
       </c>
-      <c r="L68" s="23">
+      <c r="L68" s="17">
         <f>C68</f>
         <v/>
       </c>
@@ -10886,50 +10891,50 @@
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>Amortisation period</t>
+          <t>Capitalised development</t>
         </is>
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="C69" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="D69" s="35">
+          <t>% of people cost</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D69" s="23">
         <f>C69</f>
         <v/>
       </c>
-      <c r="E69" s="35">
+      <c r="E69" s="23">
         <f>C69</f>
         <v/>
       </c>
-      <c r="F69" s="35">
+      <c r="F69" s="23">
         <f>C69</f>
         <v/>
       </c>
-      <c r="G69" s="35">
+      <c r="G69" s="23">
         <f>C69</f>
         <v/>
       </c>
-      <c r="H69" s="35">
+      <c r="H69" s="23">
         <f>C69</f>
         <v/>
       </c>
-      <c r="I69" s="35">
+      <c r="I69" s="23">
         <f>C69</f>
         <v/>
       </c>
-      <c r="J69" s="35">
+      <c r="J69" s="23">
         <f>C69</f>
         <v/>
       </c>
-      <c r="K69" s="35">
+      <c r="K69" s="23">
         <f>C69</f>
         <v/>
       </c>
-      <c r="L69" s="35">
+      <c r="L69" s="23">
         <f>C69</f>
         <v/>
       </c>
@@ -10937,63 +10942,58 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>Corporate tax — startup rate</t>
+          <t>Amortisation period</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C70" s="36" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D70" s="23">
+          <t>years</t>
+        </is>
+      </c>
+      <c r="C70" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" s="35">
         <f>C70</f>
         <v/>
       </c>
-      <c r="E70" s="23">
+      <c r="E70" s="35">
         <f>C70</f>
         <v/>
       </c>
-      <c r="F70" s="23">
+      <c r="F70" s="35">
         <f>C70</f>
         <v/>
       </c>
-      <c r="G70" s="23">
+      <c r="G70" s="35">
         <f>C70</f>
         <v/>
       </c>
-      <c r="H70" s="23">
+      <c r="H70" s="35">
         <f>C70</f>
         <v/>
       </c>
-      <c r="I70" s="23">
+      <c r="I70" s="35">
         <f>C70</f>
         <v/>
       </c>
-      <c r="J70" s="23">
+      <c r="J70" s="35">
         <f>C70</f>
         <v/>
       </c>
-      <c r="K70" s="23">
+      <c r="K70" s="35">
         <f>C70</f>
         <v/>
       </c>
-      <c r="L70" s="23">
+      <c r="L70" s="35">
         <f>C70</f>
         <v/>
-      </c>
-      <c r="N70" s="18" t="inlineStr">
-        <is>
-          <t>Spanish Startup Law, first 4 profitable years</t>
-        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>Corporate tax — standard rate</t>
+          <t>Corporate tax — startup rate</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="C71" s="36" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="D71" s="23">
         <f>C71</f>
@@ -11042,148 +11042,148 @@
       </c>
       <c r="N71" s="18" t="inlineStr">
         <is>
-          <t>Spanish corporate income tax</t>
+          <t>Spanish Startup Law, first 4 profitable years</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
+          <t>Corporate tax — standard rate</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C72" s="36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D72" s="23">
+        <f>C72</f>
+        <v/>
+      </c>
+      <c r="E72" s="23">
+        <f>C72</f>
+        <v/>
+      </c>
+      <c r="F72" s="23">
+        <f>C72</f>
+        <v/>
+      </c>
+      <c r="G72" s="23">
+        <f>C72</f>
+        <v/>
+      </c>
+      <c r="H72" s="23">
+        <f>C72</f>
+        <v/>
+      </c>
+      <c r="I72" s="23">
+        <f>C72</f>
+        <v/>
+      </c>
+      <c r="J72" s="23">
+        <f>C72</f>
+        <v/>
+      </c>
+      <c r="K72" s="23">
+        <f>C72</f>
+        <v/>
+      </c>
+      <c r="L72" s="23">
+        <f>C72</f>
+        <v/>
+      </c>
+      <c r="N72" s="18" t="inlineStr">
+        <is>
+          <t>Spanish corporate income tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
           <t>Years at startup rate (from first profit)</t>
         </is>
       </c>
-      <c r="B72" s="14" t="inlineStr">
+      <c r="B73" s="14" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="C72" s="37" t="n">
+      <c r="C73" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="D72" s="35">
-        <f>C72</f>
-        <v/>
-      </c>
-      <c r="E72" s="35">
-        <f>C72</f>
-        <v/>
-      </c>
-      <c r="F72" s="35">
-        <f>C72</f>
-        <v/>
-      </c>
-      <c r="G72" s="35">
-        <f>C72</f>
-        <v/>
-      </c>
-      <c r="H72" s="35">
-        <f>C72</f>
-        <v/>
-      </c>
-      <c r="I72" s="35">
-        <f>C72</f>
-        <v/>
-      </c>
-      <c r="J72" s="35">
-        <f>C72</f>
-        <v/>
-      </c>
-      <c r="K72" s="35">
-        <f>C72</f>
-        <v/>
-      </c>
-      <c r="L72" s="35">
-        <f>C72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="11" t="inlineStr">
+      <c r="D73" s="35">
+        <f>C73</f>
+        <v/>
+      </c>
+      <c r="E73" s="35">
+        <f>C73</f>
+        <v/>
+      </c>
+      <c r="F73" s="35">
+        <f>C73</f>
+        <v/>
+      </c>
+      <c r="G73" s="35">
+        <f>C73</f>
+        <v/>
+      </c>
+      <c r="H73" s="35">
+        <f>C73</f>
+        <v/>
+      </c>
+      <c r="I73" s="35">
+        <f>C73</f>
+        <v/>
+      </c>
+      <c r="J73" s="35">
+        <f>C73</f>
+        <v/>
+      </c>
+      <c r="K73" s="35">
+        <f>C73</f>
+        <v/>
+      </c>
+      <c r="L73" s="35">
+        <f>C73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>ADMISSION — the gate between an applicant and an athlete</t>
         </is>
       </c>
-      <c r="B74" s="12" t="n"/>
-      <c r="C74" s="12" t="n"/>
-      <c r="D74" s="12" t="n"/>
-      <c r="E74" s="12" t="n"/>
-      <c r="F74" s="12" t="n"/>
-      <c r="G74" s="12" t="n"/>
-      <c r="H74" s="12" t="n"/>
-      <c r="I74" s="12" t="n"/>
-      <c r="J74" s="12" t="n"/>
-      <c r="K74" s="12" t="n"/>
-      <c r="L74" s="12" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="13" t="inlineStr">
-        <is>
-          <t>Admission rate — direct applicants</t>
-        </is>
-      </c>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>% admitted</t>
-        </is>
-      </c>
-      <c r="C75" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D75" s="23">
-        <f>C75</f>
-        <v/>
-      </c>
-      <c r="E75" s="23">
-        <f>C75</f>
-        <v/>
-      </c>
-      <c r="F75" s="23">
-        <f>C75</f>
-        <v/>
-      </c>
-      <c r="G75" s="23">
-        <f>C75</f>
-        <v/>
-      </c>
-      <c r="H75" s="23">
-        <f>C75</f>
-        <v/>
-      </c>
-      <c r="I75" s="23">
-        <f>C75</f>
-        <v/>
-      </c>
-      <c r="J75" s="23">
-        <f>C75</f>
-        <v/>
-      </c>
-      <c r="K75" s="23">
-        <f>C75</f>
-        <v/>
-      </c>
-      <c r="L75" s="23">
-        <f>C75</f>
-        <v/>
-      </c>
-      <c r="N75" s="19" t="inlineStr">
-        <is>
-          <t>ops-load output of scripts/admission_stress.py</t>
-        </is>
-      </c>
+      <c r="B75" s="12" t="n"/>
+      <c r="C75" s="12" t="n"/>
+      <c r="D75" s="12" t="n"/>
+      <c r="E75" s="12" t="n"/>
+      <c r="F75" s="12" t="n"/>
+      <c r="G75" s="12" t="n"/>
+      <c r="H75" s="12" t="n"/>
+      <c r="I75" s="12" t="n"/>
+      <c r="J75" s="12" t="n"/>
+      <c r="K75" s="12" t="n"/>
+      <c r="L75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>Review rate — direct applicants</t>
+          <t>Admission rate — direct applicants</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>% needing a human</t>
+          <t>% admitted</t>
         </is>
       </c>
       <c r="C76" s="16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D76" s="23">
         <f>C76</f>
@@ -11230,16 +11230,16 @@
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>Admission rate — club-nominated</t>
+          <t>Review rate — direct applicants</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>% admitted</t>
+          <t>% needing a human</t>
         </is>
       </c>
       <c r="C77" s="16" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="D77" s="23">
         <f>C77</f>
@@ -11277,25 +11277,25 @@
         <f>C77</f>
         <v/>
       </c>
-      <c r="N77" s="18" t="inlineStr">
-        <is>
-          <t>ESTIMATE — a verified club's floor carries more of them past the bar</t>
+      <c r="N77" s="19" t="inlineStr">
+        <is>
+          <t>ops-load output of scripts/admission_stress.py</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>Review rate — club-nominated</t>
+          <t>Admission rate — club-nominated</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>% needing a human</t>
+          <t>% admitted</t>
         </is>
       </c>
       <c r="C78" s="16" t="n">
-        <v>0.18</v>
+        <v>0.45</v>
       </c>
       <c r="D78" s="23">
         <f>C78</f>
@@ -11335,247 +11335,247 @@
       </c>
       <c r="N78" s="18" t="inlineStr">
         <is>
-          <t>ESTIMATE</t>
+          <t>ESTIMATE — a verified club's floor carries more of them past the bar</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>Applicants arriving via a club</t>
+          <t>Review rate — club-nominated</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>% of applicants</t>
+          <t>% needing a human</t>
         </is>
       </c>
       <c r="C79" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E79" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F79" s="16" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="G79" s="16" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H79" s="16" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I79" s="16" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="J79" s="16" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="K79" s="16" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="L79" s="16" t="n">
-        <v>0.47</v>
+        <v>0.18</v>
+      </c>
+      <c r="D79" s="23">
+        <f>C79</f>
+        <v/>
+      </c>
+      <c r="E79" s="23">
+        <f>C79</f>
+        <v/>
+      </c>
+      <c r="F79" s="23">
+        <f>C79</f>
+        <v/>
+      </c>
+      <c r="G79" s="23">
+        <f>C79</f>
+        <v/>
+      </c>
+      <c r="H79" s="23">
+        <f>C79</f>
+        <v/>
+      </c>
+      <c r="I79" s="23">
+        <f>C79</f>
+        <v/>
+      </c>
+      <c r="J79" s="23">
+        <f>C79</f>
+        <v/>
+      </c>
+      <c r="K79" s="23">
+        <f>C79</f>
+        <v/>
+      </c>
+      <c r="L79" s="23">
+        <f>C79</f>
+        <v/>
       </c>
       <c r="N79" s="18" t="inlineStr">
         <is>
-          <t>Grows as federation and club partnerships land</t>
+          <t>ESTIMATE</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>Minutes per manual review</t>
+          <t>Applicants arriving via a club</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="C80" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="D80" s="31">
-        <f>C80</f>
-        <v/>
-      </c>
-      <c r="E80" s="31">
-        <f>C80</f>
-        <v/>
-      </c>
-      <c r="F80" s="31">
-        <f>C80</f>
-        <v/>
-      </c>
-      <c r="G80" s="31">
-        <f>C80</f>
-        <v/>
-      </c>
-      <c r="H80" s="31">
-        <f>C80</f>
-        <v/>
-      </c>
-      <c r="I80" s="31">
-        <f>C80</f>
-        <v/>
-      </c>
-      <c r="J80" s="31">
-        <f>C80</f>
-        <v/>
-      </c>
-      <c r="K80" s="31">
-        <f>C80</f>
-        <v/>
-      </c>
-      <c r="L80" s="31">
-        <f>C80</f>
-        <v/>
+          <t>% of applicants</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F80" s="16" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G80" s="16" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H80" s="16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I80" s="16" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J80" s="16" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K80" s="16" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L80" s="16" t="n">
+        <v>0.47</v>
       </c>
       <c r="N80" s="18" t="inlineStr">
         <is>
-          <t>Open the link, decide whether it names the applicant</t>
+          <t>Grows as federation and club partnerships land</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
+          <t>Minutes per manual review</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="C81" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D81" s="31">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="E81" s="31">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="F81" s="31">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="G81" s="31">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="H81" s="31">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="I81" s="31">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="J81" s="31">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="K81" s="31">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="L81" s="31">
+        <f>C81</f>
+        <v/>
+      </c>
+      <c r="N81" s="18" t="inlineStr">
+        <is>
+          <t>Open the link, decide whether it names the applicant</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
           <t>Productive hours per reviewer-year</t>
         </is>
       </c>
-      <c r="B81" s="14" t="inlineStr">
+      <c r="B82" s="14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="C81" s="15" t="n">
+      <c r="C82" s="15" t="n">
         <v>1700</v>
       </c>
-      <c r="D81" s="17">
-        <f>C81</f>
-        <v/>
-      </c>
-      <c r="E81" s="17">
-        <f>C81</f>
-        <v/>
-      </c>
-      <c r="F81" s="17">
-        <f>C81</f>
-        <v/>
-      </c>
-      <c r="G81" s="17">
-        <f>C81</f>
-        <v/>
-      </c>
-      <c r="H81" s="17">
-        <f>C81</f>
-        <v/>
-      </c>
-      <c r="I81" s="17">
-        <f>C81</f>
-        <v/>
-      </c>
-      <c r="J81" s="17">
-        <f>C81</f>
-        <v/>
-      </c>
-      <c r="K81" s="17">
-        <f>C81</f>
-        <v/>
-      </c>
-      <c r="L81" s="17">
-        <f>C81</f>
-        <v/>
-      </c>
-      <c r="N81" s="18" t="inlineStr">
+      <c r="D82" s="17">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="E82" s="17">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="F82" s="17">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="G82" s="17">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="N82" s="18" t="inlineStr">
         <is>
           <t>Prices review time off the same loaded salary line</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="11" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>VALUATION</t>
         </is>
       </c>
-      <c r="B83" s="12" t="n"/>
-      <c r="C83" s="12" t="n"/>
-      <c r="D83" s="12" t="n"/>
-      <c r="E83" s="12" t="n"/>
-      <c r="F83" s="12" t="n"/>
-      <c r="G83" s="12" t="n"/>
-      <c r="H83" s="12" t="n"/>
-      <c r="I83" s="12" t="n"/>
-      <c r="J83" s="12" t="n"/>
-      <c r="K83" s="12" t="n"/>
-      <c r="L83" s="12" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="13" t="inlineStr">
-        <is>
-          <t>WACC / discount rate</t>
-        </is>
-      </c>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C84" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D84" s="23">
-        <f>C84</f>
-        <v/>
-      </c>
-      <c r="E84" s="23">
-        <f>C84</f>
-        <v/>
-      </c>
-      <c r="F84" s="23">
-        <f>C84</f>
-        <v/>
-      </c>
-      <c r="G84" s="23">
-        <f>C84</f>
-        <v/>
-      </c>
-      <c r="H84" s="23">
-        <f>C84</f>
-        <v/>
-      </c>
-      <c r="I84" s="23">
-        <f>C84</f>
-        <v/>
-      </c>
-      <c r="J84" s="23">
-        <f>C84</f>
-        <v/>
-      </c>
-      <c r="K84" s="23">
-        <f>C84</f>
-        <v/>
-      </c>
-      <c r="L84" s="23">
-        <f>C84</f>
-        <v/>
-      </c>
-      <c r="N84" s="18" t="inlineStr">
-        <is>
-          <t>Early-stage venture hurdle</t>
-        </is>
-      </c>
+      <c r="B84" s="12" t="n"/>
+      <c r="C84" s="12" t="n"/>
+      <c r="D84" s="12" t="n"/>
+      <c r="E84" s="12" t="n"/>
+      <c r="F84" s="12" t="n"/>
+      <c r="G84" s="12" t="n"/>
+      <c r="H84" s="12" t="n"/>
+      <c r="I84" s="12" t="n"/>
+      <c r="J84" s="12" t="n"/>
+      <c r="K84" s="12" t="n"/>
+      <c r="L84" s="12" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>WACC / discount rate</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="C85" s="16" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="D85" s="23">
         <f>C85</f>
@@ -11622,123 +11622,123 @@
         <f>C85</f>
         <v/>
       </c>
+      <c r="N85" s="18" t="inlineStr">
+        <is>
+          <t>Early-stage venture hurdle</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>Exit revenue multiple</t>
+          <t>Terminal growth</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C86" s="21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D86" s="31">
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D86" s="23">
         <f>C86</f>
         <v/>
       </c>
-      <c r="E86" s="31">
+      <c r="E86" s="23">
         <f>C86</f>
         <v/>
       </c>
-      <c r="F86" s="31">
+      <c r="F86" s="23">
         <f>C86</f>
         <v/>
       </c>
-      <c r="G86" s="31">
+      <c r="G86" s="23">
         <f>C86</f>
         <v/>
       </c>
-      <c r="H86" s="31">
+      <c r="H86" s="23">
         <f>C86</f>
         <v/>
       </c>
-      <c r="I86" s="31">
+      <c r="I86" s="23">
         <f>C86</f>
         <v/>
       </c>
-      <c r="J86" s="31">
+      <c r="J86" s="23">
         <f>C86</f>
         <v/>
       </c>
-      <c r="K86" s="31">
+      <c r="K86" s="23">
         <f>C86</f>
         <v/>
       </c>
-      <c r="L86" s="31">
+      <c r="L86" s="23">
         <f>C86</f>
         <v/>
-      </c>
-      <c r="N86" s="18" t="inlineStr">
-        <is>
-          <t>Blended marketplace + SaaS comparables</t>
-        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>Risk-free rate (Spanish 10Y)</t>
+          <t>Exit revenue multiple</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C87" s="36" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="D87" s="23">
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C87" s="21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D87" s="31">
         <f>C87</f>
         <v/>
       </c>
-      <c r="E87" s="23">
+      <c r="E87" s="31">
         <f>C87</f>
         <v/>
       </c>
-      <c r="F87" s="23">
+      <c r="F87" s="31">
         <f>C87</f>
         <v/>
       </c>
-      <c r="G87" s="23">
+      <c r="G87" s="31">
         <f>C87</f>
         <v/>
       </c>
-      <c r="H87" s="23">
+      <c r="H87" s="31">
         <f>C87</f>
         <v/>
       </c>
-      <c r="I87" s="23">
+      <c r="I87" s="31">
         <f>C87</f>
         <v/>
       </c>
-      <c r="J87" s="23">
+      <c r="J87" s="31">
         <f>C87</f>
         <v/>
       </c>
-      <c r="K87" s="23">
+      <c r="K87" s="31">
         <f>C87</f>
         <v/>
       </c>
-      <c r="L87" s="23">
+      <c r="L87" s="31">
         <f>C87</f>
         <v/>
       </c>
       <c r="N87" s="18" t="inlineStr">
         <is>
-          <t>Spanish 10Y government bond, mid-2026</t>
+          <t>Blended marketplace + SaaS comparables</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>Founder alternative return</t>
+          <t>Risk-free rate (Spanish 10Y)</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
@@ -11746,8 +11746,8 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C88" s="16" t="n">
-        <v>0.07000000000000001</v>
+      <c r="C88" s="36" t="n">
+        <v>0.032</v>
       </c>
       <c r="D88" s="23">
         <f>C88</f>
@@ -11783,6 +11783,62 @@
       </c>
       <c r="L88" s="23">
         <f>C88</f>
+        <v/>
+      </c>
+      <c r="N88" s="18" t="inlineStr">
+        <is>
+          <t>Spanish 10Y government bond, mid-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>Founder alternative return</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C89" s="16" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D89" s="23">
+        <f>C89</f>
+        <v/>
+      </c>
+      <c r="E89" s="23">
+        <f>C89</f>
+        <v/>
+      </c>
+      <c r="F89" s="23">
+        <f>C89</f>
+        <v/>
+      </c>
+      <c r="G89" s="23">
+        <f>C89</f>
+        <v/>
+      </c>
+      <c r="H89" s="23">
+        <f>C89</f>
+        <v/>
+      </c>
+      <c r="I89" s="23">
+        <f>C89</f>
+        <v/>
+      </c>
+      <c r="J89" s="23">
+        <f>C89</f>
+        <v/>
+      </c>
+      <c r="K89" s="23">
+        <f>C89</f>
+        <v/>
+      </c>
+      <c r="L89" s="23">
+        <f>C89</f>
         <v/>
       </c>
     </row>
@@ -13780,43 +13836,43 @@
         </is>
       </c>
       <c r="C50" s="23">
-        <f>Assumptions!C79*Assumptions!C77+(1-Assumptions!C79)*Assumptions!C75</f>
+        <f>Assumptions!C80*Assumptions!C78+(1-Assumptions!C80)*Assumptions!C76</f>
         <v/>
       </c>
       <c r="D50" s="23">
-        <f>Assumptions!D79*Assumptions!D77+(1-Assumptions!D79)*Assumptions!D75</f>
+        <f>Assumptions!D80*Assumptions!D78+(1-Assumptions!D80)*Assumptions!D76</f>
         <v/>
       </c>
       <c r="E50" s="23">
-        <f>Assumptions!E79*Assumptions!E77+(1-Assumptions!E79)*Assumptions!E75</f>
+        <f>Assumptions!E80*Assumptions!E78+(1-Assumptions!E80)*Assumptions!E76</f>
         <v/>
       </c>
       <c r="F50" s="23">
-        <f>Assumptions!F79*Assumptions!F77+(1-Assumptions!F79)*Assumptions!F75</f>
+        <f>Assumptions!F80*Assumptions!F78+(1-Assumptions!F80)*Assumptions!F76</f>
         <v/>
       </c>
       <c r="G50" s="23">
-        <f>Assumptions!G79*Assumptions!G77+(1-Assumptions!G79)*Assumptions!G75</f>
+        <f>Assumptions!G80*Assumptions!G78+(1-Assumptions!G80)*Assumptions!G76</f>
         <v/>
       </c>
       <c r="H50" s="23">
-        <f>Assumptions!H79*Assumptions!H77+(1-Assumptions!H79)*Assumptions!H75</f>
+        <f>Assumptions!H80*Assumptions!H78+(1-Assumptions!H80)*Assumptions!H76</f>
         <v/>
       </c>
       <c r="I50" s="23">
-        <f>Assumptions!I79*Assumptions!I77+(1-Assumptions!I79)*Assumptions!I75</f>
+        <f>Assumptions!I80*Assumptions!I78+(1-Assumptions!I80)*Assumptions!I76</f>
         <v/>
       </c>
       <c r="J50" s="23">
-        <f>Assumptions!J79*Assumptions!J77+(1-Assumptions!J79)*Assumptions!J75</f>
+        <f>Assumptions!J80*Assumptions!J78+(1-Assumptions!J80)*Assumptions!J76</f>
         <v/>
       </c>
       <c r="K50" s="23">
-        <f>Assumptions!K79*Assumptions!K77+(1-Assumptions!K79)*Assumptions!K75</f>
+        <f>Assumptions!K80*Assumptions!K78+(1-Assumptions!K80)*Assumptions!K76</f>
         <v/>
       </c>
       <c r="L50" s="23">
-        <f>Assumptions!L79*Assumptions!L77+(1-Assumptions!L79)*Assumptions!L75</f>
+        <f>Assumptions!L80*Assumptions!L78+(1-Assumptions!L80)*Assumptions!L76</f>
         <v/>
       </c>
     </row>
@@ -13832,43 +13888,43 @@
         </is>
       </c>
       <c r="C51" s="23">
-        <f>Assumptions!C79*Assumptions!C78+(1-Assumptions!C79)*Assumptions!C76</f>
+        <f>Assumptions!C80*Assumptions!C79+(1-Assumptions!C80)*Assumptions!C77</f>
         <v/>
       </c>
       <c r="D51" s="23">
-        <f>Assumptions!D79*Assumptions!D78+(1-Assumptions!D79)*Assumptions!D76</f>
+        <f>Assumptions!D80*Assumptions!D79+(1-Assumptions!D80)*Assumptions!D77</f>
         <v/>
       </c>
       <c r="E51" s="23">
-        <f>Assumptions!E79*Assumptions!E78+(1-Assumptions!E79)*Assumptions!E76</f>
+        <f>Assumptions!E80*Assumptions!E79+(1-Assumptions!E80)*Assumptions!E77</f>
         <v/>
       </c>
       <c r="F51" s="23">
-        <f>Assumptions!F79*Assumptions!F78+(1-Assumptions!F79)*Assumptions!F76</f>
+        <f>Assumptions!F80*Assumptions!F79+(1-Assumptions!F80)*Assumptions!F77</f>
         <v/>
       </c>
       <c r="G51" s="23">
-        <f>Assumptions!G79*Assumptions!G78+(1-Assumptions!G79)*Assumptions!G76</f>
+        <f>Assumptions!G80*Assumptions!G79+(1-Assumptions!G80)*Assumptions!G77</f>
         <v/>
       </c>
       <c r="H51" s="23">
-        <f>Assumptions!H79*Assumptions!H78+(1-Assumptions!H79)*Assumptions!H76</f>
+        <f>Assumptions!H80*Assumptions!H79+(1-Assumptions!H80)*Assumptions!H77</f>
         <v/>
       </c>
       <c r="I51" s="23">
-        <f>Assumptions!I79*Assumptions!I78+(1-Assumptions!I79)*Assumptions!I76</f>
+        <f>Assumptions!I80*Assumptions!I79+(1-Assumptions!I80)*Assumptions!I77</f>
         <v/>
       </c>
       <c r="J51" s="23">
-        <f>Assumptions!J79*Assumptions!J78+(1-Assumptions!J79)*Assumptions!J76</f>
+        <f>Assumptions!J80*Assumptions!J79+(1-Assumptions!J80)*Assumptions!J77</f>
         <v/>
       </c>
       <c r="K51" s="23">
-        <f>Assumptions!K79*Assumptions!K78+(1-Assumptions!K79)*Assumptions!K76</f>
+        <f>Assumptions!K80*Assumptions!K79+(1-Assumptions!K80)*Assumptions!K77</f>
         <v/>
       </c>
       <c r="L51" s="23">
-        <f>Assumptions!L79*Assumptions!L78+(1-Assumptions!L79)*Assumptions!L76</f>
+        <f>Assumptions!L80*Assumptions!L79+(1-Assumptions!L80)*Assumptions!L77</f>
         <v/>
       </c>
     </row>
@@ -13988,43 +14044,43 @@
         </is>
       </c>
       <c r="C54" s="25">
-        <f>C53*Assumptions!C80/60/Assumptions!C81</f>
+        <f>C53*Assumptions!C81/60/Assumptions!C82</f>
         <v/>
       </c>
       <c r="D54" s="25">
-        <f>D53*Assumptions!D80/60/Assumptions!D81</f>
+        <f>D53*Assumptions!D81/60/Assumptions!D82</f>
         <v/>
       </c>
       <c r="E54" s="25">
-        <f>E53*Assumptions!E80/60/Assumptions!E81</f>
+        <f>E53*Assumptions!E81/60/Assumptions!E82</f>
         <v/>
       </c>
       <c r="F54" s="25">
-        <f>F53*Assumptions!F80/60/Assumptions!F81</f>
+        <f>F53*Assumptions!F81/60/Assumptions!F82</f>
         <v/>
       </c>
       <c r="G54" s="25">
-        <f>G53*Assumptions!G80/60/Assumptions!G81</f>
+        <f>G53*Assumptions!G81/60/Assumptions!G82</f>
         <v/>
       </c>
       <c r="H54" s="25">
-        <f>H53*Assumptions!H80/60/Assumptions!H81</f>
+        <f>H53*Assumptions!H81/60/Assumptions!H82</f>
         <v/>
       </c>
       <c r="I54" s="25">
-        <f>I53*Assumptions!I80/60/Assumptions!I81</f>
+        <f>I53*Assumptions!I81/60/Assumptions!I82</f>
         <v/>
       </c>
       <c r="J54" s="25">
-        <f>J53*Assumptions!J80/60/Assumptions!J81</f>
+        <f>J53*Assumptions!J81/60/Assumptions!J82</f>
         <v/>
       </c>
       <c r="K54" s="25">
-        <f>K53*Assumptions!K80/60/Assumptions!K81</f>
+        <f>K53*Assumptions!K81/60/Assumptions!K82</f>
         <v/>
       </c>
       <c r="L54" s="25">
-        <f>L53*Assumptions!L80/60/Assumptions!L81</f>
+        <f>L53*Assumptions!L81/60/Assumptions!L82</f>
         <v/>
       </c>
     </row>
@@ -14046,7 +14102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -14167,7 +14223,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>FAN GMV — what fans pay athletes</t>
+          <t>FAN GMV — what fans pay athletes, net of VAT</t>
         </is>
       </c>
       <c r="B4" s="12" t="n"/>
@@ -14190,47 +14246,47 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>avg fans x ARPU x 12</t>
+          <t>avg fans x ARPU x 12, ex-VAT</t>
         </is>
       </c>
       <c r="C5" s="30">
-        <f>Drivers!C19*Assumptions!C12*12</f>
+        <f>Drivers!C19*Assumptions!C12*12/(1+Assumptions!C42)</f>
         <v/>
       </c>
       <c r="D5" s="30">
-        <f>Drivers!D19*Assumptions!D12*12</f>
+        <f>Drivers!D19*Assumptions!D12*12/(1+Assumptions!D42)</f>
         <v/>
       </c>
       <c r="E5" s="30">
-        <f>Drivers!E19*Assumptions!E12*12</f>
+        <f>Drivers!E19*Assumptions!E12*12/(1+Assumptions!E42)</f>
         <v/>
       </c>
       <c r="F5" s="30">
-        <f>Drivers!F19*Assumptions!F12*12</f>
+        <f>Drivers!F19*Assumptions!F12*12/(1+Assumptions!F42)</f>
         <v/>
       </c>
       <c r="G5" s="30">
-        <f>Drivers!G19*Assumptions!G12*12</f>
+        <f>Drivers!G19*Assumptions!G12*12/(1+Assumptions!G42)</f>
         <v/>
       </c>
       <c r="H5" s="30">
-        <f>Drivers!H19*Assumptions!H12*12</f>
+        <f>Drivers!H19*Assumptions!H12*12/(1+Assumptions!H42)</f>
         <v/>
       </c>
       <c r="I5" s="30">
-        <f>Drivers!I19*Assumptions!I12*12</f>
+        <f>Drivers!I19*Assumptions!I12*12/(1+Assumptions!I42)</f>
         <v/>
       </c>
       <c r="J5" s="30">
-        <f>Drivers!J19*Assumptions!J12*12</f>
+        <f>Drivers!J19*Assumptions!J12*12/(1+Assumptions!J42)</f>
         <v/>
       </c>
       <c r="K5" s="30">
-        <f>Drivers!K19*Assumptions!K12*12</f>
+        <f>Drivers!K19*Assumptions!K12*12/(1+Assumptions!K42)</f>
         <v/>
       </c>
       <c r="L5" s="30">
-        <f>Drivers!L19*Assumptions!L12*12</f>
+        <f>Drivers!L19*Assumptions!L12*12/(1+Assumptions!L42)</f>
         <v/>
       </c>
     </row>
@@ -14240,45 +14296,49 @@
           <t>Popular subscription GMV</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr"/>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>ex-VAT</t>
+        </is>
+      </c>
       <c r="C6" s="30">
-        <f>Drivers!C32*Assumptions!C24*12</f>
+        <f>Drivers!C32*Assumptions!C24*12/(1+Assumptions!C42)</f>
         <v/>
       </c>
       <c r="D6" s="30">
-        <f>Drivers!D32*Assumptions!D24*12</f>
+        <f>Drivers!D32*Assumptions!D24*12/(1+Assumptions!D42)</f>
         <v/>
       </c>
       <c r="E6" s="30">
-        <f>Drivers!E32*Assumptions!E24*12</f>
+        <f>Drivers!E32*Assumptions!E24*12/(1+Assumptions!E42)</f>
         <v/>
       </c>
       <c r="F6" s="30">
-        <f>Drivers!F32*Assumptions!F24*12</f>
+        <f>Drivers!F32*Assumptions!F24*12/(1+Assumptions!F42)</f>
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>Drivers!G32*Assumptions!G24*12</f>
+        <f>Drivers!G32*Assumptions!G24*12/(1+Assumptions!G42)</f>
         <v/>
       </c>
       <c r="H6" s="30">
-        <f>Drivers!H32*Assumptions!H24*12</f>
+        <f>Drivers!H32*Assumptions!H24*12/(1+Assumptions!H42)</f>
         <v/>
       </c>
       <c r="I6" s="30">
-        <f>Drivers!I32*Assumptions!I24*12</f>
+        <f>Drivers!I32*Assumptions!I24*12/(1+Assumptions!I42)</f>
         <v/>
       </c>
       <c r="J6" s="30">
-        <f>Drivers!J32*Assumptions!J24*12</f>
+        <f>Drivers!J32*Assumptions!J24*12/(1+Assumptions!J42)</f>
         <v/>
       </c>
       <c r="K6" s="30">
-        <f>Drivers!K32*Assumptions!K24*12</f>
+        <f>Drivers!K32*Assumptions!K24*12/(1+Assumptions!K42)</f>
         <v/>
       </c>
       <c r="L6" s="30">
-        <f>Drivers!L32*Assumptions!L24*12</f>
+        <f>Drivers!L32*Assumptions!L24*12/(1+Assumptions!L42)</f>
         <v/>
       </c>
     </row>
@@ -14342,43 +14402,43 @@
         </is>
       </c>
       <c r="C8" s="30">
-        <f>C7*Assumptions!C42</f>
+        <f>C7*Assumptions!C43</f>
         <v/>
       </c>
       <c r="D8" s="30">
-        <f>D7*Assumptions!D42</f>
+        <f>D7*Assumptions!D43</f>
         <v/>
       </c>
       <c r="E8" s="30">
-        <f>E7*Assumptions!E42</f>
+        <f>E7*Assumptions!E43</f>
         <v/>
       </c>
       <c r="F8" s="30">
-        <f>F7*Assumptions!F42</f>
+        <f>F7*Assumptions!F43</f>
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>G7*Assumptions!G42</f>
+        <f>G7*Assumptions!G43</f>
         <v/>
       </c>
       <c r="H8" s="30">
-        <f>H7*Assumptions!H42</f>
+        <f>H7*Assumptions!H43</f>
         <v/>
       </c>
       <c r="I8" s="30">
-        <f>I7*Assumptions!I42</f>
+        <f>I7*Assumptions!I43</f>
         <v/>
       </c>
       <c r="J8" s="30">
-        <f>J7*Assumptions!J42</f>
+        <f>J7*Assumptions!J43</f>
         <v/>
       </c>
       <c r="K8" s="30">
-        <f>K7*Assumptions!K42</f>
+        <f>K7*Assumptions!K43</f>
         <v/>
       </c>
       <c r="L8" s="30">
-        <f>L7*Assumptions!L42</f>
+        <f>L7*Assumptions!L43</f>
         <v/>
       </c>
     </row>
@@ -14388,7 +14448,11 @@
           <t>Total fan GMV</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr"/>
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>ex-VAT, the take base</t>
+        </is>
+      </c>
       <c r="C9" s="44">
         <f>C7+C8</f>
         <v/>
@@ -14430,535 +14494,587 @@
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Fan GMV including VAT</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>what cards are charged</t>
+        </is>
+      </c>
+      <c r="C10" s="30">
+        <f>C9*(1+Assumptions!C42)</f>
+        <v/>
+      </c>
+      <c r="D10" s="30">
+        <f>D9*(1+Assumptions!D42)</f>
+        <v/>
+      </c>
+      <c r="E10" s="30">
+        <f>E9*(1+Assumptions!E42)</f>
+        <v/>
+      </c>
+      <c r="F10" s="30">
+        <f>F9*(1+Assumptions!F42)</f>
+        <v/>
+      </c>
+      <c r="G10" s="30">
+        <f>G9*(1+Assumptions!G42)</f>
+        <v/>
+      </c>
+      <c r="H10" s="30">
+        <f>H9*(1+Assumptions!H42)</f>
+        <v/>
+      </c>
+      <c r="I10" s="30">
+        <f>I9*(1+Assumptions!I42)</f>
+        <v/>
+      </c>
+      <c r="J10" s="30">
+        <f>J9*(1+Assumptions!J42)</f>
+        <v/>
+      </c>
+      <c r="K10" s="30">
+        <f>K9*(1+Assumptions!K42)</f>
+        <v/>
+      </c>
+      <c r="L10" s="30">
+        <f>L9*(1+Assumptions!L42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>SPONSORSHIP GMV — what sponsors pay athletes and clubs</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Niche sponsorship GMV</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr"/>
-      <c r="C12" s="30">
-        <f>Drivers!C42*Assumptions!C18</f>
-        <v/>
-      </c>
-      <c r="D12" s="30">
-        <f>Drivers!D42*Assumptions!D18</f>
-        <v/>
-      </c>
-      <c r="E12" s="30">
-        <f>Drivers!E42*Assumptions!E18</f>
-        <v/>
-      </c>
-      <c r="F12" s="30">
-        <f>Drivers!F42*Assumptions!F18</f>
-        <v/>
-      </c>
-      <c r="G12" s="30">
-        <f>Drivers!G42*Assumptions!G18</f>
-        <v/>
-      </c>
-      <c r="H12" s="30">
-        <f>Drivers!H42*Assumptions!H18</f>
-        <v/>
-      </c>
-      <c r="I12" s="30">
-        <f>Drivers!I42*Assumptions!I18</f>
-        <v/>
-      </c>
-      <c r="J12" s="30">
-        <f>Drivers!J42*Assumptions!J18</f>
-        <v/>
-      </c>
-      <c r="K12" s="30">
-        <f>Drivers!K42*Assumptions!K18</f>
-        <v/>
-      </c>
-      <c r="L12" s="30">
-        <f>Drivers!L42*Assumptions!L18</f>
-        <v/>
-      </c>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Popular sponsorship GMV</t>
+          <t>Niche sponsorship GMV</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr"/>
       <c r="C13" s="30">
+        <f>Drivers!C42*Assumptions!C18</f>
+        <v/>
+      </c>
+      <c r="D13" s="30">
+        <f>Drivers!D42*Assumptions!D18</f>
+        <v/>
+      </c>
+      <c r="E13" s="30">
+        <f>Drivers!E42*Assumptions!E18</f>
+        <v/>
+      </c>
+      <c r="F13" s="30">
+        <f>Drivers!F42*Assumptions!F18</f>
+        <v/>
+      </c>
+      <c r="G13" s="30">
+        <f>Drivers!G42*Assumptions!G18</f>
+        <v/>
+      </c>
+      <c r="H13" s="30">
+        <f>Drivers!H42*Assumptions!H18</f>
+        <v/>
+      </c>
+      <c r="I13" s="30">
+        <f>Drivers!I42*Assumptions!I18</f>
+        <v/>
+      </c>
+      <c r="J13" s="30">
+        <f>Drivers!J42*Assumptions!J18</f>
+        <v/>
+      </c>
+      <c r="K13" s="30">
+        <f>Drivers!K42*Assumptions!K18</f>
+        <v/>
+      </c>
+      <c r="L13" s="30">
+        <f>Drivers!L42*Assumptions!L18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Popular sponsorship GMV</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr"/>
+      <c r="C14" s="30">
         <f>Drivers!C43*Assumptions!C30</f>
         <v/>
       </c>
-      <c r="D13" s="30">
+      <c r="D14" s="30">
         <f>Drivers!D43*Assumptions!D30</f>
         <v/>
       </c>
-      <c r="E13" s="30">
+      <c r="E14" s="30">
         <f>Drivers!E43*Assumptions!E30</f>
         <v/>
       </c>
-      <c r="F13" s="30">
+      <c r="F14" s="30">
         <f>Drivers!F43*Assumptions!F30</f>
         <v/>
       </c>
-      <c r="G13" s="30">
+      <c r="G14" s="30">
         <f>Drivers!G43*Assumptions!G30</f>
         <v/>
       </c>
-      <c r="H13" s="30">
+      <c r="H14" s="30">
         <f>Drivers!H43*Assumptions!H30</f>
         <v/>
       </c>
-      <c r="I13" s="30">
+      <c r="I14" s="30">
         <f>Drivers!I43*Assumptions!I30</f>
         <v/>
       </c>
-      <c r="J13" s="30">
+      <c r="J14" s="30">
         <f>Drivers!J43*Assumptions!J30</f>
         <v/>
       </c>
-      <c r="K13" s="30">
+      <c r="K14" s="30">
         <f>Drivers!K43*Assumptions!K30</f>
         <v/>
       </c>
-      <c r="L13" s="30">
+      <c r="L14" s="30">
         <f>Drivers!L43*Assumptions!L30</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>Total sponsorship GMV</t>
         </is>
       </c>
-      <c r="B14" s="40" t="inlineStr"/>
-      <c r="C14" s="44">
-        <f>C12+C13</f>
-        <v/>
-      </c>
-      <c r="D14" s="44">
-        <f>D12+D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="44">
-        <f>E12+E13</f>
-        <v/>
-      </c>
-      <c r="F14" s="44">
-        <f>F12+F13</f>
-        <v/>
-      </c>
-      <c r="G14" s="44">
-        <f>G12+G13</f>
-        <v/>
-      </c>
-      <c r="H14" s="44">
-        <f>H12+H13</f>
-        <v/>
-      </c>
-      <c r="I14" s="44">
-        <f>I12+I13</f>
-        <v/>
-      </c>
-      <c r="J14" s="44">
-        <f>J12+J13</f>
-        <v/>
-      </c>
-      <c r="K14" s="44">
-        <f>K12+K13</f>
-        <v/>
-      </c>
-      <c r="L14" s="44">
-        <f>L12+L13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="45" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr"/>
+      <c r="C15" s="44">
+        <f>C13+C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="44">
+        <f>D13+D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="44">
+        <f>E13+E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="44">
+        <f>F13+F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="44">
+        <f>G13+G14</f>
+        <v/>
+      </c>
+      <c r="H15" s="44">
+        <f>H13+H14</f>
+        <v/>
+      </c>
+      <c r="I15" s="44">
+        <f>I13+I14</f>
+        <v/>
+      </c>
+      <c r="J15" s="44">
+        <f>J13+J14</f>
+        <v/>
+      </c>
+      <c r="K15" s="44">
+        <f>K13+K14</f>
+        <v/>
+      </c>
+      <c r="L15" s="44">
+        <f>L13+L14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="inlineStr">
         <is>
           <t>TOTAL GMV</t>
         </is>
       </c>
-      <c r="B15" s="40" t="inlineStr"/>
-      <c r="C15" s="46">
-        <f>C9+C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="46">
-        <f>D9+D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="46">
-        <f>E9+E14</f>
-        <v/>
-      </c>
-      <c r="F15" s="46">
-        <f>F9+F14</f>
-        <v/>
-      </c>
-      <c r="G15" s="46">
-        <f>G9+G14</f>
-        <v/>
-      </c>
-      <c r="H15" s="46">
-        <f>H9+H14</f>
-        <v/>
-      </c>
-      <c r="I15" s="46">
-        <f>I9+I14</f>
-        <v/>
-      </c>
-      <c r="J15" s="46">
-        <f>J9+J14</f>
-        <v/>
-      </c>
-      <c r="K15" s="46">
-        <f>K9+K14</f>
-        <v/>
-      </c>
-      <c r="L15" s="46">
-        <f>L9+L14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr"/>
+      <c r="C16" s="46">
+        <f>C9+C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="46">
+        <f>D9+D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="46">
+        <f>E9+E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="46">
+        <f>F9+F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="46">
+        <f>G9+G15</f>
+        <v/>
+      </c>
+      <c r="H16" s="46">
+        <f>H9+H15</f>
+        <v/>
+      </c>
+      <c r="I16" s="46">
+        <f>I9+I15</f>
+        <v/>
+      </c>
+      <c r="J16" s="46">
+        <f>J9+J15</f>
+        <v/>
+      </c>
+      <c r="K16" s="46">
+        <f>K9+K15</f>
+        <v/>
+      </c>
+      <c r="L16" s="46">
+        <f>L9+L15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>NET REVENUE — our share</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="12" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Fan take</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>fan GMV x take rate</t>
-        </is>
-      </c>
-      <c r="C18" s="30">
-        <f>C9*Assumptions!C40</f>
-        <v/>
-      </c>
-      <c r="D18" s="30">
-        <f>D9*Assumptions!D40</f>
-        <v/>
-      </c>
-      <c r="E18" s="30">
-        <f>E9*Assumptions!E40</f>
-        <v/>
-      </c>
-      <c r="F18" s="30">
-        <f>F9*Assumptions!F40</f>
-        <v/>
-      </c>
-      <c r="G18" s="30">
-        <f>G9*Assumptions!G40</f>
-        <v/>
-      </c>
-      <c r="H18" s="30">
-        <f>H9*Assumptions!H40</f>
-        <v/>
-      </c>
-      <c r="I18" s="30">
-        <f>I9*Assumptions!I40</f>
-        <v/>
-      </c>
-      <c r="J18" s="30">
-        <f>J9*Assumptions!J40</f>
-        <v/>
-      </c>
-      <c r="K18" s="30">
-        <f>K9*Assumptions!K40</f>
-        <v/>
-      </c>
-      <c r="L18" s="30">
-        <f>L9*Assumptions!L40</f>
-        <v/>
-      </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Sponsorship take</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr"/>
+          <t>Fan take</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>fan GMV x take rate</t>
+        </is>
+      </c>
       <c r="C19" s="30">
-        <f>C14*Assumptions!C41</f>
+        <f>C9*Assumptions!C40</f>
         <v/>
       </c>
       <c r="D19" s="30">
-        <f>D14*Assumptions!D41</f>
+        <f>D9*Assumptions!D40</f>
         <v/>
       </c>
       <c r="E19" s="30">
-        <f>E14*Assumptions!E41</f>
+        <f>E9*Assumptions!E40</f>
         <v/>
       </c>
       <c r="F19" s="30">
-        <f>F14*Assumptions!F41</f>
+        <f>F9*Assumptions!F40</f>
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>G14*Assumptions!G41</f>
+        <f>G9*Assumptions!G40</f>
         <v/>
       </c>
       <c r="H19" s="30">
-        <f>H14*Assumptions!H41</f>
+        <f>H9*Assumptions!H40</f>
         <v/>
       </c>
       <c r="I19" s="30">
-        <f>I14*Assumptions!I41</f>
+        <f>I9*Assumptions!I40</f>
         <v/>
       </c>
       <c r="J19" s="30">
-        <f>J14*Assumptions!J41</f>
+        <f>J9*Assumptions!J40</f>
         <v/>
       </c>
       <c r="K19" s="30">
-        <f>K14*Assumptions!K41</f>
+        <f>K9*Assumptions!K40</f>
         <v/>
       </c>
       <c r="L19" s="30">
-        <f>L14*Assumptions!L41</f>
+        <f>L9*Assumptions!L40</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
+          <t>Sponsorship take</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr"/>
+      <c r="C20" s="30">
+        <f>C15*Assumptions!C41</f>
+        <v/>
+      </c>
+      <c r="D20" s="30">
+        <f>D15*Assumptions!D41</f>
+        <v/>
+      </c>
+      <c r="E20" s="30">
+        <f>E15*Assumptions!E41</f>
+        <v/>
+      </c>
+      <c r="F20" s="30">
+        <f>F15*Assumptions!F41</f>
+        <v/>
+      </c>
+      <c r="G20" s="30">
+        <f>G15*Assumptions!G41</f>
+        <v/>
+      </c>
+      <c r="H20" s="30">
+        <f>H15*Assumptions!H41</f>
+        <v/>
+      </c>
+      <c r="I20" s="30">
+        <f>I15*Assumptions!I41</f>
+        <v/>
+      </c>
+      <c r="J20" s="30">
+        <f>J15*Assumptions!J41</f>
+        <v/>
+      </c>
+      <c r="K20" s="30">
+        <f>K15*Assumptions!K41</f>
+        <v/>
+      </c>
+      <c r="L20" s="30">
+        <f>L15*Assumptions!L41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
           <t>Sponsor SaaS</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>paying sponsors x ARPU x 12</t>
         </is>
       </c>
-      <c r="C20" s="30">
+      <c r="C21" s="30">
         <f>Drivers!C46*Assumptions!C36*12</f>
         <v/>
       </c>
-      <c r="D20" s="30">
+      <c r="D21" s="30">
         <f>Drivers!D46*Assumptions!D36*12</f>
         <v/>
       </c>
-      <c r="E20" s="30">
+      <c r="E21" s="30">
         <f>Drivers!E46*Assumptions!E36*12</f>
         <v/>
       </c>
-      <c r="F20" s="30">
+      <c r="F21" s="30">
         <f>Drivers!F46*Assumptions!F36*12</f>
         <v/>
       </c>
-      <c r="G20" s="30">
+      <c r="G21" s="30">
         <f>Drivers!G46*Assumptions!G36*12</f>
         <v/>
       </c>
-      <c r="H20" s="30">
+      <c r="H21" s="30">
         <f>Drivers!H46*Assumptions!H36*12</f>
         <v/>
       </c>
-      <c r="I20" s="30">
+      <c r="I21" s="30">
         <f>Drivers!I46*Assumptions!I36*12</f>
         <v/>
       </c>
-      <c r="J20" s="30">
+      <c r="J21" s="30">
         <f>Drivers!J46*Assumptions!J36*12</f>
         <v/>
       </c>
-      <c r="K20" s="30">
+      <c r="K21" s="30">
         <f>Drivers!K46*Assumptions!K36*12</f>
         <v/>
       </c>
-      <c r="L20" s="30">
+      <c r="L21" s="30">
         <f>Drivers!L46*Assumptions!L36*12</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="45" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="45" t="inlineStr">
         <is>
           <t>NET REVENUE</t>
         </is>
       </c>
-      <c r="B21" s="40" t="inlineStr"/>
-      <c r="C21" s="46">
-        <f>SUM(C18:C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="46">
-        <f>SUM(D18:D20)</f>
-        <v/>
-      </c>
-      <c r="E21" s="46">
-        <f>SUM(E18:E20)</f>
-        <v/>
-      </c>
-      <c r="F21" s="46">
-        <f>SUM(F18:F20)</f>
-        <v/>
-      </c>
-      <c r="G21" s="46">
-        <f>SUM(G18:G20)</f>
-        <v/>
-      </c>
-      <c r="H21" s="46">
-        <f>SUM(H18:H20)</f>
-        <v/>
-      </c>
-      <c r="I21" s="46">
-        <f>SUM(I18:I20)</f>
-        <v/>
-      </c>
-      <c r="J21" s="46">
-        <f>SUM(J18:J20)</f>
-        <v/>
-      </c>
-      <c r="K21" s="46">
-        <f>SUM(K18:K20)</f>
-        <v/>
-      </c>
-      <c r="L21" s="46">
-        <f>SUM(L18:L20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Growth</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>% YoY</t>
-        </is>
-      </c>
-      <c r="C22" s="47">
-        <f>IF(1=1,"",C21/C21-1)</f>
-        <v/>
-      </c>
-      <c r="D22" s="47">
-        <f>IF(2=1,"",D21/C21-1)</f>
-        <v/>
-      </c>
-      <c r="E22" s="47">
-        <f>IF(3=1,"",E21/D21-1)</f>
-        <v/>
-      </c>
-      <c r="F22" s="47">
-        <f>IF(4=1,"",F21/E21-1)</f>
-        <v/>
-      </c>
-      <c r="G22" s="47">
-        <f>IF(5=1,"",G21/F21-1)</f>
-        <v/>
-      </c>
-      <c r="H22" s="47">
-        <f>IF(6=1,"",H21/G21-1)</f>
-        <v/>
-      </c>
-      <c r="I22" s="47">
-        <f>IF(7=1,"",I21/H21-1)</f>
-        <v/>
-      </c>
-      <c r="J22" s="47">
-        <f>IF(8=1,"",J21/I21-1)</f>
-        <v/>
-      </c>
-      <c r="K22" s="47">
-        <f>IF(9=1,"",K21/J21-1)</f>
-        <v/>
-      </c>
-      <c r="L22" s="47">
-        <f>IF(10=1,"",L21/K21-1)</f>
+      <c r="B22" s="40" t="inlineStr"/>
+      <c r="C22" s="46">
+        <f>SUM(C19:C21)</f>
+        <v/>
+      </c>
+      <c r="D22" s="46">
+        <f>SUM(D19:D21)</f>
+        <v/>
+      </c>
+      <c r="E22" s="46">
+        <f>SUM(E19:E21)</f>
+        <v/>
+      </c>
+      <c r="F22" s="46">
+        <f>SUM(F19:F21)</f>
+        <v/>
+      </c>
+      <c r="G22" s="46">
+        <f>SUM(G19:G21)</f>
+        <v/>
+      </c>
+      <c r="H22" s="46">
+        <f>SUM(H19:H21)</f>
+        <v/>
+      </c>
+      <c r="I22" s="46">
+        <f>SUM(I19:I21)</f>
+        <v/>
+      </c>
+      <c r="J22" s="46">
+        <f>SUM(J19:J21)</f>
+        <v/>
+      </c>
+      <c r="K22" s="46">
+        <f>SUM(K19:K21)</f>
+        <v/>
+      </c>
+      <c r="L22" s="46">
+        <f>SUM(L19:L21)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="C23" s="47">
+        <f>IF(1=1,"",C22/C22-1)</f>
+        <v/>
+      </c>
+      <c r="D23" s="47">
+        <f>IF(2=1,"",D22/C22-1)</f>
+        <v/>
+      </c>
+      <c r="E23" s="47">
+        <f>IF(3=1,"",E22/D22-1)</f>
+        <v/>
+      </c>
+      <c r="F23" s="47">
+        <f>IF(4=1,"",F22/E22-1)</f>
+        <v/>
+      </c>
+      <c r="G23" s="47">
+        <f>IF(5=1,"",G22/F22-1)</f>
+        <v/>
+      </c>
+      <c r="H23" s="47">
+        <f>IF(6=1,"",H22/G22-1)</f>
+        <v/>
+      </c>
+      <c r="I23" s="47">
+        <f>IF(7=1,"",I22/H22-1)</f>
+        <v/>
+      </c>
+      <c r="J23" s="47">
+        <f>IF(8=1,"",J22/I22-1)</f>
+        <v/>
+      </c>
+      <c r="K23" s="47">
+        <f>IF(9=1,"",K22/J22-1)</f>
+        <v/>
+      </c>
+      <c r="L23" s="47">
+        <f>IF(10=1,"",L22/K22-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
           <t>Take rate on GMV</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>blended</t>
         </is>
       </c>
-      <c r="C23" s="47">
-        <f>C21/C15</f>
-        <v/>
-      </c>
-      <c r="D23" s="47">
-        <f>D21/D15</f>
-        <v/>
-      </c>
-      <c r="E23" s="47">
-        <f>E21/E15</f>
-        <v/>
-      </c>
-      <c r="F23" s="47">
-        <f>F21/F15</f>
-        <v/>
-      </c>
-      <c r="G23" s="47">
-        <f>G21/G15</f>
-        <v/>
-      </c>
-      <c r="H23" s="47">
-        <f>H21/H15</f>
-        <v/>
-      </c>
-      <c r="I23" s="47">
-        <f>I21/I15</f>
-        <v/>
-      </c>
-      <c r="J23" s="47">
-        <f>J21/J15</f>
-        <v/>
-      </c>
-      <c r="K23" s="47">
-        <f>K21/K15</f>
-        <v/>
-      </c>
-      <c r="L23" s="47">
-        <f>L21/L15</f>
+      <c r="C24" s="47">
+        <f>C22/C16</f>
+        <v/>
+      </c>
+      <c r="D24" s="47">
+        <f>D22/D16</f>
+        <v/>
+      </c>
+      <c r="E24" s="47">
+        <f>E22/E16</f>
+        <v/>
+      </c>
+      <c r="F24" s="47">
+        <f>F22/F16</f>
+        <v/>
+      </c>
+      <c r="G24" s="47">
+        <f>G22/G16</f>
+        <v/>
+      </c>
+      <c r="H24" s="47">
+        <f>H22/H16</f>
+        <v/>
+      </c>
+      <c r="I24" s="47">
+        <f>I22/I16</f>
+        <v/>
+      </c>
+      <c r="J24" s="47">
+        <f>J22/J16</f>
+        <v/>
+      </c>
+      <c r="K24" s="47">
+        <f>K22/K16</f>
+        <v/>
+      </c>
+      <c r="L24" s="47">
+        <f>L22/L16</f>
         <v/>
       </c>
     </row>
@@ -15124,47 +15240,47 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>fan GMV / avg ticket</t>
+          <t>fan GMV incl VAT / avg ticket</t>
         </is>
       </c>
       <c r="C5" s="17">
-        <f>Revenue!C9/Assumptions!C47</f>
+        <f>Revenue!C10/Assumptions!C48</f>
         <v/>
       </c>
       <c r="D5" s="17">
-        <f>Revenue!D9/Assumptions!D47</f>
+        <f>Revenue!D10/Assumptions!D48</f>
         <v/>
       </c>
       <c r="E5" s="17">
-        <f>Revenue!E9/Assumptions!E47</f>
+        <f>Revenue!E10/Assumptions!E48</f>
         <v/>
       </c>
       <c r="F5" s="17">
-        <f>Revenue!F9/Assumptions!F47</f>
+        <f>Revenue!F10/Assumptions!F48</f>
         <v/>
       </c>
       <c r="G5" s="17">
-        <f>Revenue!G9/Assumptions!G47</f>
+        <f>Revenue!G10/Assumptions!G48</f>
         <v/>
       </c>
       <c r="H5" s="17">
-        <f>Revenue!H9/Assumptions!H47</f>
+        <f>Revenue!H10/Assumptions!H48</f>
         <v/>
       </c>
       <c r="I5" s="17">
-        <f>Revenue!I9/Assumptions!I47</f>
+        <f>Revenue!I10/Assumptions!I48</f>
         <v/>
       </c>
       <c r="J5" s="17">
-        <f>Revenue!J9/Assumptions!J47</f>
+        <f>Revenue!J10/Assumptions!J48</f>
         <v/>
       </c>
       <c r="K5" s="17">
-        <f>Revenue!K9/Assumptions!K47</f>
+        <f>Revenue!K10/Assumptions!K48</f>
         <v/>
       </c>
       <c r="L5" s="17">
-        <f>Revenue!L9/Assumptions!L47</f>
+        <f>Revenue!L10/Assumptions!L48</f>
         <v/>
       </c>
     </row>
@@ -15180,43 +15296,43 @@
         </is>
       </c>
       <c r="C6" s="17">
-        <f>Revenue!C14/Assumptions!C48</f>
+        <f>Revenue!C15/Assumptions!C49</f>
         <v/>
       </c>
       <c r="D6" s="17">
-        <f>Revenue!D14/Assumptions!D48</f>
+        <f>Revenue!D15/Assumptions!D49</f>
         <v/>
       </c>
       <c r="E6" s="17">
-        <f>Revenue!E14/Assumptions!E48</f>
+        <f>Revenue!E15/Assumptions!E49</f>
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>Revenue!F14/Assumptions!F48</f>
+        <f>Revenue!F15/Assumptions!F49</f>
         <v/>
       </c>
       <c r="G6" s="17">
-        <f>Revenue!G14/Assumptions!G48</f>
+        <f>Revenue!G15/Assumptions!G49</f>
         <v/>
       </c>
       <c r="H6" s="17">
-        <f>Revenue!H14/Assumptions!H48</f>
+        <f>Revenue!H15/Assumptions!H49</f>
         <v/>
       </c>
       <c r="I6" s="17">
-        <f>Revenue!I14/Assumptions!I48</f>
+        <f>Revenue!I15/Assumptions!I49</f>
         <v/>
       </c>
       <c r="J6" s="17">
-        <f>Revenue!J14/Assumptions!J48</f>
+        <f>Revenue!J15/Assumptions!J49</f>
         <v/>
       </c>
       <c r="K6" s="17">
-        <f>Revenue!K14/Assumptions!K48</f>
+        <f>Revenue!K15/Assumptions!K49</f>
         <v/>
       </c>
       <c r="L6" s="17">
-        <f>Revenue!L14/Assumptions!L48</f>
+        <f>Revenue!L15/Assumptions!L49</f>
         <v/>
       </c>
     </row>
@@ -15228,47 +15344,47 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>% of GMV + fixed</t>
+          <t>% of processed + fixed</t>
         </is>
       </c>
       <c r="C7" s="30">
-        <f>Revenue!C15*Assumptions!C43+(C5+C6)*Assumptions!C44</f>
+        <f>(Revenue!C10+Revenue!C15)*Assumptions!C44+(C5+C6)*Assumptions!C45</f>
         <v/>
       </c>
       <c r="D7" s="30">
-        <f>Revenue!D15*Assumptions!D43+(D5+D6)*Assumptions!D44</f>
+        <f>(Revenue!D10+Revenue!D15)*Assumptions!D44+(D5+D6)*Assumptions!D45</f>
         <v/>
       </c>
       <c r="E7" s="30">
-        <f>Revenue!E15*Assumptions!E43+(E5+E6)*Assumptions!E44</f>
+        <f>(Revenue!E10+Revenue!E15)*Assumptions!E44+(E5+E6)*Assumptions!E45</f>
         <v/>
       </c>
       <c r="F7" s="30">
-        <f>Revenue!F15*Assumptions!F43+(F5+F6)*Assumptions!F44</f>
+        <f>(Revenue!F10+Revenue!F15)*Assumptions!F44+(F5+F6)*Assumptions!F45</f>
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>Revenue!G15*Assumptions!G43+(G5+G6)*Assumptions!G44</f>
+        <f>(Revenue!G10+Revenue!G15)*Assumptions!G44+(G5+G6)*Assumptions!G45</f>
         <v/>
       </c>
       <c r="H7" s="30">
-        <f>Revenue!H15*Assumptions!H43+(H5+H6)*Assumptions!H44</f>
+        <f>(Revenue!H10+Revenue!H15)*Assumptions!H44+(H5+H6)*Assumptions!H45</f>
         <v/>
       </c>
       <c r="I7" s="30">
-        <f>Revenue!I15*Assumptions!I43+(I5+I6)*Assumptions!I44</f>
+        <f>(Revenue!I10+Revenue!I15)*Assumptions!I44+(I5+I6)*Assumptions!I45</f>
         <v/>
       </c>
       <c r="J7" s="30">
-        <f>Revenue!J15*Assumptions!J43+(J5+J6)*Assumptions!J44</f>
+        <f>(Revenue!J10+Revenue!J15)*Assumptions!J44+(J5+J6)*Assumptions!J45</f>
         <v/>
       </c>
       <c r="K7" s="30">
-        <f>Revenue!K15*Assumptions!K43+(K5+K6)*Assumptions!K44</f>
+        <f>(Revenue!K10+Revenue!K15)*Assumptions!K44+(K5+K6)*Assumptions!K45</f>
         <v/>
       </c>
       <c r="L7" s="30">
-        <f>Revenue!L15*Assumptions!L43+(L5+L6)*Assumptions!L44</f>
+        <f>(Revenue!L10+Revenue!L15)*Assumptions!L44+(L5+L6)*Assumptions!L45</f>
         <v/>
       </c>
     </row>
@@ -15284,43 +15400,43 @@
         </is>
       </c>
       <c r="C8" s="30">
-        <f>Revenue!C15*Assumptions!C45+(C5/30+C6)*Assumptions!C46</f>
+        <f>(Revenue!C10+Revenue!C15)*Assumptions!C46+(C5/30+C6)*Assumptions!C47</f>
         <v/>
       </c>
       <c r="D8" s="30">
-        <f>Revenue!D15*Assumptions!D45+(D5/30+D6)*Assumptions!D46</f>
+        <f>(Revenue!D10+Revenue!D15)*Assumptions!D46+(D5/30+D6)*Assumptions!D47</f>
         <v/>
       </c>
       <c r="E8" s="30">
-        <f>Revenue!E15*Assumptions!E45+(E5/30+E6)*Assumptions!E46</f>
+        <f>(Revenue!E10+Revenue!E15)*Assumptions!E46+(E5/30+E6)*Assumptions!E47</f>
         <v/>
       </c>
       <c r="F8" s="30">
-        <f>Revenue!F15*Assumptions!F45+(F5/30+F6)*Assumptions!F46</f>
+        <f>(Revenue!F10+Revenue!F15)*Assumptions!F46+(F5/30+F6)*Assumptions!F47</f>
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>Revenue!G15*Assumptions!G45+(G5/30+G6)*Assumptions!G46</f>
+        <f>(Revenue!G10+Revenue!G15)*Assumptions!G46+(G5/30+G6)*Assumptions!G47</f>
         <v/>
       </c>
       <c r="H8" s="30">
-        <f>Revenue!H15*Assumptions!H45+(H5/30+H6)*Assumptions!H46</f>
+        <f>(Revenue!H10+Revenue!H15)*Assumptions!H46+(H5/30+H6)*Assumptions!H47</f>
         <v/>
       </c>
       <c r="I8" s="30">
-        <f>Revenue!I15*Assumptions!I45+(I5/30+I6)*Assumptions!I46</f>
+        <f>(Revenue!I10+Revenue!I15)*Assumptions!I46+(I5/30+I6)*Assumptions!I47</f>
         <v/>
       </c>
       <c r="J8" s="30">
-        <f>Revenue!J15*Assumptions!J45+(J5/30+J6)*Assumptions!J46</f>
+        <f>(Revenue!J10+Revenue!J15)*Assumptions!J46+(J5/30+J6)*Assumptions!J47</f>
         <v/>
       </c>
       <c r="K8" s="30">
-        <f>Revenue!K15*Assumptions!K45+(K5/30+K6)*Assumptions!K46</f>
+        <f>(Revenue!K10+Revenue!K15)*Assumptions!K46+(K5/30+K6)*Assumptions!K47</f>
         <v/>
       </c>
       <c r="L8" s="30">
-        <f>Revenue!L15*Assumptions!L45+(L5/30+L6)*Assumptions!L46</f>
+        <f>(Revenue!L10+Revenue!L15)*Assumptions!L46+(L5/30+L6)*Assumptions!L47</f>
         <v/>
       </c>
     </row>
@@ -15336,43 +15452,43 @@
         </is>
       </c>
       <c r="C9" s="17">
-        <f>Drivers!C37*Assumptions!C52*12</f>
+        <f>Drivers!C37*Assumptions!C53*12</f>
         <v/>
       </c>
       <c r="D9" s="17">
-        <f>Drivers!D37*Assumptions!D52*12</f>
+        <f>Drivers!D37*Assumptions!D53*12</f>
         <v/>
       </c>
       <c r="E9" s="17">
-        <f>Drivers!E37*Assumptions!E52*12</f>
+        <f>Drivers!E37*Assumptions!E53*12</f>
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>Drivers!F37*Assumptions!F52*12</f>
+        <f>Drivers!F37*Assumptions!F53*12</f>
         <v/>
       </c>
       <c r="G9" s="17">
-        <f>Drivers!G37*Assumptions!G52*12</f>
+        <f>Drivers!G37*Assumptions!G53*12</f>
         <v/>
       </c>
       <c r="H9" s="17">
-        <f>Drivers!H37*Assumptions!H52*12</f>
+        <f>Drivers!H37*Assumptions!H53*12</f>
         <v/>
       </c>
       <c r="I9" s="17">
-        <f>Drivers!I37*Assumptions!I52*12</f>
+        <f>Drivers!I37*Assumptions!I53*12</f>
         <v/>
       </c>
       <c r="J9" s="17">
-        <f>Drivers!J37*Assumptions!J52*12</f>
+        <f>Drivers!J37*Assumptions!J53*12</f>
         <v/>
       </c>
       <c r="K9" s="17">
-        <f>Drivers!K37*Assumptions!K52*12</f>
+        <f>Drivers!K37*Assumptions!K53*12</f>
         <v/>
       </c>
       <c r="L9" s="17">
-        <f>Drivers!L37*Assumptions!L52*12</f>
+        <f>Drivers!L37*Assumptions!L53*12</f>
         <v/>
       </c>
     </row>
@@ -15388,43 +15504,43 @@
         </is>
       </c>
       <c r="C10" s="30">
-        <f>Assumptions!C51*12+C9*Assumptions!C53</f>
+        <f>Assumptions!C52*12+C9*Assumptions!C54</f>
         <v/>
       </c>
       <c r="D10" s="30">
-        <f>Assumptions!D51*12+D9*Assumptions!D53</f>
+        <f>Assumptions!D52*12+D9*Assumptions!D54</f>
         <v/>
       </c>
       <c r="E10" s="30">
-        <f>Assumptions!E51*12+E9*Assumptions!E53</f>
+        <f>Assumptions!E52*12+E9*Assumptions!E54</f>
         <v/>
       </c>
       <c r="F10" s="30">
-        <f>Assumptions!F51*12+F9*Assumptions!F53</f>
+        <f>Assumptions!F52*12+F9*Assumptions!F54</f>
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>Assumptions!G51*12+G9*Assumptions!G53</f>
+        <f>Assumptions!G52*12+G9*Assumptions!G54</f>
         <v/>
       </c>
       <c r="H10" s="30">
-        <f>Assumptions!H51*12+H9*Assumptions!H53</f>
+        <f>Assumptions!H52*12+H9*Assumptions!H54</f>
         <v/>
       </c>
       <c r="I10" s="30">
-        <f>Assumptions!I51*12+I9*Assumptions!I53</f>
+        <f>Assumptions!I52*12+I9*Assumptions!I54</f>
         <v/>
       </c>
       <c r="J10" s="30">
-        <f>Assumptions!J51*12+J9*Assumptions!J53</f>
+        <f>Assumptions!J52*12+J9*Assumptions!J54</f>
         <v/>
       </c>
       <c r="K10" s="30">
-        <f>Assumptions!K51*12+K9*Assumptions!K53</f>
+        <f>Assumptions!K52*12+K9*Assumptions!K54</f>
         <v/>
       </c>
       <c r="L10" s="30">
-        <f>Assumptions!L51*12+L9*Assumptions!L53</f>
+        <f>Assumptions!L52*12+L9*Assumptions!L54</f>
         <v/>
       </c>
     </row>
@@ -15440,43 +15556,43 @@
         </is>
       </c>
       <c r="C11" s="30">
-        <f>Assumptions!C51*12+C9*Assumptions!C54</f>
+        <f>Assumptions!C52*12+C9*Assumptions!C55</f>
         <v/>
       </c>
       <c r="D11" s="30">
-        <f>Assumptions!D51*12+D9*Assumptions!D54</f>
+        <f>Assumptions!D52*12+D9*Assumptions!D55</f>
         <v/>
       </c>
       <c r="E11" s="30">
-        <f>Assumptions!E51*12+E9*Assumptions!E54</f>
+        <f>Assumptions!E52*12+E9*Assumptions!E55</f>
         <v/>
       </c>
       <c r="F11" s="30">
-        <f>Assumptions!F51*12+F9*Assumptions!F54</f>
+        <f>Assumptions!F52*12+F9*Assumptions!F55</f>
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>Assumptions!G51*12+G9*Assumptions!G54</f>
+        <f>Assumptions!G52*12+G9*Assumptions!G55</f>
         <v/>
       </c>
       <c r="H11" s="30">
-        <f>Assumptions!H51*12+H9*Assumptions!H54</f>
+        <f>Assumptions!H52*12+H9*Assumptions!H55</f>
         <v/>
       </c>
       <c r="I11" s="30">
-        <f>Assumptions!I51*12+I9*Assumptions!I54</f>
+        <f>Assumptions!I52*12+I9*Assumptions!I55</f>
         <v/>
       </c>
       <c r="J11" s="30">
-        <f>Assumptions!J51*12+J9*Assumptions!J54</f>
+        <f>Assumptions!J52*12+J9*Assumptions!J55</f>
         <v/>
       </c>
       <c r="K11" s="30">
-        <f>Assumptions!K51*12+K9*Assumptions!K54</f>
+        <f>Assumptions!K52*12+K9*Assumptions!K55</f>
         <v/>
       </c>
       <c r="L11" s="30">
-        <f>Assumptions!L51*12+L9*Assumptions!L54</f>
+        <f>Assumptions!L52*12+L9*Assumptions!L55</f>
         <v/>
       </c>
     </row>
@@ -15492,43 +15608,43 @@
         </is>
       </c>
       <c r="C12" s="30">
-        <f>Drivers!C5*Assumptions!C56*12/1000*Assumptions!C55</f>
+        <f>Drivers!C5*Assumptions!C57*12/1000*Assumptions!C56</f>
         <v/>
       </c>
       <c r="D12" s="30">
-        <f>Drivers!D5*Assumptions!D56*12/1000*Assumptions!D55</f>
+        <f>Drivers!D5*Assumptions!D57*12/1000*Assumptions!D56</f>
         <v/>
       </c>
       <c r="E12" s="30">
-        <f>Drivers!E5*Assumptions!E56*12/1000*Assumptions!E55</f>
+        <f>Drivers!E5*Assumptions!E57*12/1000*Assumptions!E56</f>
         <v/>
       </c>
       <c r="F12" s="30">
-        <f>Drivers!F5*Assumptions!F56*12/1000*Assumptions!F55</f>
+        <f>Drivers!F5*Assumptions!F57*12/1000*Assumptions!F56</f>
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>Drivers!G5*Assumptions!G56*12/1000*Assumptions!G55</f>
+        <f>Drivers!G5*Assumptions!G57*12/1000*Assumptions!G56</f>
         <v/>
       </c>
       <c r="H12" s="30">
-        <f>Drivers!H5*Assumptions!H56*12/1000*Assumptions!H55</f>
+        <f>Drivers!H5*Assumptions!H57*12/1000*Assumptions!H56</f>
         <v/>
       </c>
       <c r="I12" s="30">
-        <f>Drivers!I5*Assumptions!I56*12/1000*Assumptions!I55</f>
+        <f>Drivers!I5*Assumptions!I57*12/1000*Assumptions!I56</f>
         <v/>
       </c>
       <c r="J12" s="30">
-        <f>Drivers!J5*Assumptions!J56*12/1000*Assumptions!J55</f>
+        <f>Drivers!J5*Assumptions!J57*12/1000*Assumptions!J56</f>
         <v/>
       </c>
       <c r="K12" s="30">
-        <f>Drivers!K5*Assumptions!K56*12/1000*Assumptions!K55</f>
+        <f>Drivers!K5*Assumptions!K57*12/1000*Assumptions!K56</f>
         <v/>
       </c>
       <c r="L12" s="30">
-        <f>Drivers!L5*Assumptions!L56*12/1000*Assumptions!L55</f>
+        <f>Drivers!L5*Assumptions!L57*12/1000*Assumptions!L56</f>
         <v/>
       </c>
     </row>
@@ -15544,43 +15660,43 @@
         </is>
       </c>
       <c r="C13" s="30">
-        <f>Drivers!C53*Assumptions!C80/60*(Assumptions!C60/Assumptions!C81)</f>
+        <f>Drivers!C53*Assumptions!C81/60*(Assumptions!C61/Assumptions!C82)</f>
         <v/>
       </c>
       <c r="D13" s="30">
-        <f>Drivers!D53*Assumptions!D80/60*(Assumptions!D60/Assumptions!D81)</f>
+        <f>Drivers!D53*Assumptions!D81/60*(Assumptions!D61/Assumptions!D82)</f>
         <v/>
       </c>
       <c r="E13" s="30">
-        <f>Drivers!E53*Assumptions!E80/60*(Assumptions!E60/Assumptions!E81)</f>
+        <f>Drivers!E53*Assumptions!E81/60*(Assumptions!E61/Assumptions!E82)</f>
         <v/>
       </c>
       <c r="F13" s="30">
-        <f>Drivers!F53*Assumptions!F80/60*(Assumptions!F60/Assumptions!F81)</f>
+        <f>Drivers!F53*Assumptions!F81/60*(Assumptions!F61/Assumptions!F82)</f>
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>Drivers!G53*Assumptions!G80/60*(Assumptions!G60/Assumptions!G81)</f>
+        <f>Drivers!G53*Assumptions!G81/60*(Assumptions!G61/Assumptions!G82)</f>
         <v/>
       </c>
       <c r="H13" s="30">
-        <f>Drivers!H53*Assumptions!H80/60*(Assumptions!H60/Assumptions!H81)</f>
+        <f>Drivers!H53*Assumptions!H81/60*(Assumptions!H61/Assumptions!H82)</f>
         <v/>
       </c>
       <c r="I13" s="30">
-        <f>Drivers!I53*Assumptions!I80/60*(Assumptions!I60/Assumptions!I81)</f>
+        <f>Drivers!I53*Assumptions!I81/60*(Assumptions!I61/Assumptions!I82)</f>
         <v/>
       </c>
       <c r="J13" s="30">
-        <f>Drivers!J53*Assumptions!J80/60*(Assumptions!J60/Assumptions!J81)</f>
+        <f>Drivers!J53*Assumptions!J81/60*(Assumptions!J61/Assumptions!J82)</f>
         <v/>
       </c>
       <c r="K13" s="30">
-        <f>Drivers!K53*Assumptions!K80/60*(Assumptions!K60/Assumptions!K81)</f>
+        <f>Drivers!K53*Assumptions!K81/60*(Assumptions!K61/Assumptions!K82)</f>
         <v/>
       </c>
       <c r="L13" s="30">
-        <f>Drivers!L53*Assumptions!L80/60*(Assumptions!L60/Assumptions!L81)</f>
+        <f>Drivers!L53*Assumptions!L81/60*(Assumptions!L61/Assumptions!L82)</f>
         <v/>
       </c>
     </row>
@@ -15662,43 +15778,43 @@
         </is>
       </c>
       <c r="C17" s="30">
-        <f>Assumptions!C59*Assumptions!C60</f>
+        <f>Assumptions!C60*Assumptions!C61</f>
         <v/>
       </c>
       <c r="D17" s="30">
-        <f>Assumptions!D59*Assumptions!D60</f>
+        <f>Assumptions!D60*Assumptions!D61</f>
         <v/>
       </c>
       <c r="E17" s="30">
-        <f>Assumptions!E59*Assumptions!E60</f>
+        <f>Assumptions!E60*Assumptions!E61</f>
         <v/>
       </c>
       <c r="F17" s="30">
-        <f>Assumptions!F59*Assumptions!F60</f>
+        <f>Assumptions!F60*Assumptions!F61</f>
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>Assumptions!G59*Assumptions!G60</f>
+        <f>Assumptions!G60*Assumptions!G61</f>
         <v/>
       </c>
       <c r="H17" s="30">
-        <f>Assumptions!H59*Assumptions!H60</f>
+        <f>Assumptions!H60*Assumptions!H61</f>
         <v/>
       </c>
       <c r="I17" s="30">
-        <f>Assumptions!I59*Assumptions!I60</f>
+        <f>Assumptions!I60*Assumptions!I61</f>
         <v/>
       </c>
       <c r="J17" s="30">
-        <f>Assumptions!J59*Assumptions!J60</f>
+        <f>Assumptions!J60*Assumptions!J61</f>
         <v/>
       </c>
       <c r="K17" s="30">
-        <f>Assumptions!K59*Assumptions!K60</f>
+        <f>Assumptions!K60*Assumptions!K61</f>
         <v/>
       </c>
       <c r="L17" s="30">
-        <f>Assumptions!L59*Assumptions!L60</f>
+        <f>Assumptions!L60*Assumptions!L61</f>
         <v/>
       </c>
     </row>
@@ -15958,43 +16074,43 @@
       </c>
       <c r="B23" s="14" t="inlineStr"/>
       <c r="C23" s="30">
-        <f>Assumptions!C61</f>
+        <f>Assumptions!C62</f>
         <v/>
       </c>
       <c r="D23" s="30">
-        <f>Assumptions!D61</f>
+        <f>Assumptions!D62</f>
         <v/>
       </c>
       <c r="E23" s="30">
-        <f>Assumptions!E61</f>
+        <f>Assumptions!E62</f>
         <v/>
       </c>
       <c r="F23" s="30">
-        <f>Assumptions!F61</f>
+        <f>Assumptions!F62</f>
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>Assumptions!G61</f>
+        <f>Assumptions!G62</f>
         <v/>
       </c>
       <c r="H23" s="30">
-        <f>Assumptions!H61</f>
+        <f>Assumptions!H62</f>
         <v/>
       </c>
       <c r="I23" s="30">
-        <f>Assumptions!I61</f>
+        <f>Assumptions!I62</f>
         <v/>
       </c>
       <c r="J23" s="30">
-        <f>Assumptions!J61</f>
+        <f>Assumptions!J62</f>
         <v/>
       </c>
       <c r="K23" s="30">
-        <f>Assumptions!K61</f>
+        <f>Assumptions!K62</f>
         <v/>
       </c>
       <c r="L23" s="30">
-        <f>Assumptions!L61</f>
+        <f>Assumptions!L62</f>
         <v/>
       </c>
     </row>
@@ -16010,43 +16126,43 @@
         </is>
       </c>
       <c r="C24" s="30">
-        <f>Revenue!C21*Assumptions!C62</f>
+        <f>Revenue!C22*Assumptions!C63</f>
         <v/>
       </c>
       <c r="D24" s="30">
-        <f>Revenue!D21*Assumptions!D62</f>
+        <f>Revenue!D22*Assumptions!D63</f>
         <v/>
       </c>
       <c r="E24" s="30">
-        <f>Revenue!E21*Assumptions!E62</f>
+        <f>Revenue!E22*Assumptions!E63</f>
         <v/>
       </c>
       <c r="F24" s="30">
-        <f>Revenue!F21*Assumptions!F62</f>
+        <f>Revenue!F22*Assumptions!F63</f>
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>Revenue!G21*Assumptions!G62</f>
+        <f>Revenue!G22*Assumptions!G63</f>
         <v/>
       </c>
       <c r="H24" s="30">
-        <f>Revenue!H21*Assumptions!H62</f>
+        <f>Revenue!H22*Assumptions!H63</f>
         <v/>
       </c>
       <c r="I24" s="30">
-        <f>Revenue!I21*Assumptions!I62</f>
+        <f>Revenue!I22*Assumptions!I63</f>
         <v/>
       </c>
       <c r="J24" s="30">
-        <f>Revenue!J21*Assumptions!J62</f>
+        <f>Revenue!J22*Assumptions!J63</f>
         <v/>
       </c>
       <c r="K24" s="30">
-        <f>Revenue!K21*Assumptions!K62</f>
+        <f>Revenue!K22*Assumptions!K63</f>
         <v/>
       </c>
       <c r="L24" s="30">
-        <f>Revenue!L21*Assumptions!L62</f>
+        <f>Revenue!L22*Assumptions!L63</f>
         <v/>
       </c>
     </row>
@@ -16264,43 +16380,43 @@
         </is>
       </c>
       <c r="C5" s="30">
-        <f>(Revenue!C19+Revenue!C20)*Assumptions!C66/365</f>
+        <f>(Revenue!C20+Revenue!C21)*Assumptions!C67/365</f>
         <v/>
       </c>
       <c r="D5" s="30">
-        <f>(Revenue!D19+Revenue!D20)*Assumptions!D66/365</f>
+        <f>(Revenue!D20+Revenue!D21)*Assumptions!D67/365</f>
         <v/>
       </c>
       <c r="E5" s="30">
-        <f>(Revenue!E19+Revenue!E20)*Assumptions!E66/365</f>
+        <f>(Revenue!E20+Revenue!E21)*Assumptions!E67/365</f>
         <v/>
       </c>
       <c r="F5" s="30">
-        <f>(Revenue!F19+Revenue!F20)*Assumptions!F66/365</f>
+        <f>(Revenue!F20+Revenue!F21)*Assumptions!F67/365</f>
         <v/>
       </c>
       <c r="G5" s="30">
-        <f>(Revenue!G19+Revenue!G20)*Assumptions!G66/365</f>
+        <f>(Revenue!G20+Revenue!G21)*Assumptions!G67/365</f>
         <v/>
       </c>
       <c r="H5" s="30">
-        <f>(Revenue!H19+Revenue!H20)*Assumptions!H66/365</f>
+        <f>(Revenue!H20+Revenue!H21)*Assumptions!H67/365</f>
         <v/>
       </c>
       <c r="I5" s="30">
-        <f>(Revenue!I19+Revenue!I20)*Assumptions!I66/365</f>
+        <f>(Revenue!I20+Revenue!I21)*Assumptions!I67/365</f>
         <v/>
       </c>
       <c r="J5" s="30">
-        <f>(Revenue!J19+Revenue!J20)*Assumptions!J66/365</f>
+        <f>(Revenue!J20+Revenue!J21)*Assumptions!J67/365</f>
         <v/>
       </c>
       <c r="K5" s="30">
-        <f>(Revenue!K19+Revenue!K20)*Assumptions!K66/365</f>
+        <f>(Revenue!K20+Revenue!K21)*Assumptions!K67/365</f>
         <v/>
       </c>
       <c r="L5" s="30">
-        <f>(Revenue!L19+Revenue!L20)*Assumptions!L66/365</f>
+        <f>(Revenue!L20+Revenue!L21)*Assumptions!L67/365</f>
         <v/>
       </c>
     </row>
@@ -16316,43 +16432,43 @@
         </is>
       </c>
       <c r="C6" s="30">
-        <f>Revenue!C15*Assumptions!C65/365</f>
+        <f>Revenue!C16*Assumptions!C66/365</f>
         <v/>
       </c>
       <c r="D6" s="30">
-        <f>Revenue!D15*Assumptions!D65/365</f>
+        <f>Revenue!D16*Assumptions!D66/365</f>
         <v/>
       </c>
       <c r="E6" s="30">
-        <f>Revenue!E15*Assumptions!E65/365</f>
+        <f>Revenue!E16*Assumptions!E66/365</f>
         <v/>
       </c>
       <c r="F6" s="30">
-        <f>Revenue!F15*Assumptions!F65/365</f>
+        <f>Revenue!F16*Assumptions!F66/365</f>
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>Revenue!G15*Assumptions!G65/365</f>
+        <f>Revenue!G16*Assumptions!G66/365</f>
         <v/>
       </c>
       <c r="H6" s="30">
-        <f>Revenue!H15*Assumptions!H65/365</f>
+        <f>Revenue!H16*Assumptions!H66/365</f>
         <v/>
       </c>
       <c r="I6" s="30">
-        <f>Revenue!I15*Assumptions!I65/365</f>
+        <f>Revenue!I16*Assumptions!I66/365</f>
         <v/>
       </c>
       <c r="J6" s="30">
-        <f>Revenue!J15*Assumptions!J65/365</f>
+        <f>Revenue!J16*Assumptions!J66/365</f>
         <v/>
       </c>
       <c r="K6" s="30">
-        <f>Revenue!K15*Assumptions!K65/365</f>
+        <f>Revenue!K16*Assumptions!K66/365</f>
         <v/>
       </c>
       <c r="L6" s="30">
-        <f>Revenue!L15*Assumptions!L65/365</f>
+        <f>Revenue!L16*Assumptions!L66/365</f>
         <v/>
       </c>
     </row>
@@ -16368,43 +16484,43 @@
         </is>
       </c>
       <c r="C7" s="30">
-        <f>Costs!C25*Assumptions!C67/365</f>
+        <f>Costs!C25*Assumptions!C68/365</f>
         <v/>
       </c>
       <c r="D7" s="30">
-        <f>Costs!D25*Assumptions!D67/365</f>
+        <f>Costs!D25*Assumptions!D68/365</f>
         <v/>
       </c>
       <c r="E7" s="30">
-        <f>Costs!E25*Assumptions!E67/365</f>
+        <f>Costs!E25*Assumptions!E68/365</f>
         <v/>
       </c>
       <c r="F7" s="30">
-        <f>Costs!F25*Assumptions!F67/365</f>
+        <f>Costs!F25*Assumptions!F68/365</f>
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>Costs!G25*Assumptions!G67/365</f>
+        <f>Costs!G25*Assumptions!G68/365</f>
         <v/>
       </c>
       <c r="H7" s="30">
-        <f>Costs!H25*Assumptions!H67/365</f>
+        <f>Costs!H25*Assumptions!H68/365</f>
         <v/>
       </c>
       <c r="I7" s="30">
-        <f>Costs!I25*Assumptions!I67/365</f>
+        <f>Costs!I25*Assumptions!I68/365</f>
         <v/>
       </c>
       <c r="J7" s="30">
-        <f>Costs!J25*Assumptions!J67/365</f>
+        <f>Costs!J25*Assumptions!J68/365</f>
         <v/>
       </c>
       <c r="K7" s="30">
-        <f>Costs!K25*Assumptions!K67/365</f>
+        <f>Costs!K25*Assumptions!K68/365</f>
         <v/>
       </c>
       <c r="L7" s="30">
-        <f>Costs!L25*Assumptions!L67/365</f>
+        <f>Costs!L25*Assumptions!L68/365</f>
         <v/>
       </c>
     </row>
@@ -16542,43 +16658,43 @@
         </is>
       </c>
       <c r="C12" s="30">
-        <f>Costs!C17*Assumptions!C68</f>
+        <f>Costs!C17*Assumptions!C69</f>
         <v/>
       </c>
       <c r="D12" s="30">
-        <f>Costs!D17*Assumptions!D68</f>
+        <f>Costs!D17*Assumptions!D69</f>
         <v/>
       </c>
       <c r="E12" s="30">
-        <f>Costs!E17*Assumptions!E68</f>
+        <f>Costs!E17*Assumptions!E69</f>
         <v/>
       </c>
       <c r="F12" s="30">
-        <f>Costs!F17*Assumptions!F68</f>
+        <f>Costs!F17*Assumptions!F69</f>
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>Costs!G17*Assumptions!G68</f>
+        <f>Costs!G17*Assumptions!G69</f>
         <v/>
       </c>
       <c r="H12" s="30">
-        <f>Costs!H17*Assumptions!H68</f>
+        <f>Costs!H17*Assumptions!H69</f>
         <v/>
       </c>
       <c r="I12" s="30">
-        <f>Costs!I17*Assumptions!I68</f>
+        <f>Costs!I17*Assumptions!I69</f>
         <v/>
       </c>
       <c r="J12" s="30">
-        <f>Costs!J17*Assumptions!J68</f>
+        <f>Costs!J17*Assumptions!J69</f>
         <v/>
       </c>
       <c r="K12" s="30">
-        <f>Costs!K17*Assumptions!K68</f>
+        <f>Costs!K17*Assumptions!K69</f>
         <v/>
       </c>
       <c r="L12" s="30">
-        <f>Costs!L17*Assumptions!L68</f>
+        <f>Costs!L17*Assumptions!L69</f>
         <v/>
       </c>
     </row>
@@ -16594,43 +16710,43 @@
         </is>
       </c>
       <c r="C13" s="30">
-        <f>SUM(OFFSET(C12,0,-MIN(Assumptions!C69-1,1-1),1,MIN(Assumptions!C69,1)))/Assumptions!C69</f>
+        <f>SUM(OFFSET(C12,0,-MIN(Assumptions!C70-1,1-1),1,MIN(Assumptions!C70,1)))/Assumptions!C70</f>
         <v/>
       </c>
       <c r="D13" s="30">
-        <f>SUM(OFFSET(D12,0,-MIN(Assumptions!D69-1,2-1),1,MIN(Assumptions!D69,2)))/Assumptions!D69</f>
+        <f>SUM(OFFSET(D12,0,-MIN(Assumptions!D70-1,2-1),1,MIN(Assumptions!D70,2)))/Assumptions!D70</f>
         <v/>
       </c>
       <c r="E13" s="30">
-        <f>SUM(OFFSET(E12,0,-MIN(Assumptions!E69-1,3-1),1,MIN(Assumptions!E69,3)))/Assumptions!E69</f>
+        <f>SUM(OFFSET(E12,0,-MIN(Assumptions!E70-1,3-1),1,MIN(Assumptions!E70,3)))/Assumptions!E70</f>
         <v/>
       </c>
       <c r="F13" s="30">
-        <f>SUM(OFFSET(F12,0,-MIN(Assumptions!F69-1,4-1),1,MIN(Assumptions!F69,4)))/Assumptions!F69</f>
+        <f>SUM(OFFSET(F12,0,-MIN(Assumptions!F70-1,4-1),1,MIN(Assumptions!F70,4)))/Assumptions!F70</f>
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>SUM(OFFSET(G12,0,-MIN(Assumptions!G69-1,5-1),1,MIN(Assumptions!G69,5)))/Assumptions!G69</f>
+        <f>SUM(OFFSET(G12,0,-MIN(Assumptions!G70-1,5-1),1,MIN(Assumptions!G70,5)))/Assumptions!G70</f>
         <v/>
       </c>
       <c r="H13" s="30">
-        <f>SUM(OFFSET(H12,0,-MIN(Assumptions!H69-1,6-1),1,MIN(Assumptions!H69,6)))/Assumptions!H69</f>
+        <f>SUM(OFFSET(H12,0,-MIN(Assumptions!H70-1,6-1),1,MIN(Assumptions!H70,6)))/Assumptions!H70</f>
         <v/>
       </c>
       <c r="I13" s="30">
-        <f>SUM(OFFSET(I12,0,-MIN(Assumptions!I69-1,7-1),1,MIN(Assumptions!I69,7)))/Assumptions!I69</f>
+        <f>SUM(OFFSET(I12,0,-MIN(Assumptions!I70-1,7-1),1,MIN(Assumptions!I70,7)))/Assumptions!I70</f>
         <v/>
       </c>
       <c r="J13" s="30">
-        <f>SUM(OFFSET(J12,0,-MIN(Assumptions!J69-1,8-1),1,MIN(Assumptions!J69,8)))/Assumptions!J69</f>
+        <f>SUM(OFFSET(J12,0,-MIN(Assumptions!J70-1,8-1),1,MIN(Assumptions!J70,8)))/Assumptions!J70</f>
         <v/>
       </c>
       <c r="K13" s="30">
-        <f>SUM(OFFSET(K12,0,-MIN(Assumptions!K69-1,9-1),1,MIN(Assumptions!K69,9)))/Assumptions!K69</f>
+        <f>SUM(OFFSET(K12,0,-MIN(Assumptions!K70-1,9-1),1,MIN(Assumptions!K70,9)))/Assumptions!K70</f>
         <v/>
       </c>
       <c r="L13" s="30">
-        <f>SUM(OFFSET(L12,0,-MIN(Assumptions!L69-1,10-1),1,MIN(Assumptions!L69,10)))/Assumptions!L69</f>
+        <f>SUM(OFFSET(L12,0,-MIN(Assumptions!L70-1,10-1),1,MIN(Assumptions!L70,10)))/Assumptions!L70</f>
         <v/>
       </c>
     </row>
@@ -16830,43 +16946,43 @@
       </c>
       <c r="B4" s="40" t="inlineStr"/>
       <c r="C4" s="49">
-        <f>Revenue!C21</f>
+        <f>Revenue!C22</f>
         <v/>
       </c>
       <c r="D4" s="49">
-        <f>Revenue!D21</f>
+        <f>Revenue!D22</f>
         <v/>
       </c>
       <c r="E4" s="49">
-        <f>Revenue!E21</f>
+        <f>Revenue!E22</f>
         <v/>
       </c>
       <c r="F4" s="49">
-        <f>Revenue!F21</f>
+        <f>Revenue!F22</f>
         <v/>
       </c>
       <c r="G4" s="49">
-        <f>Revenue!G21</f>
+        <f>Revenue!G22</f>
         <v/>
       </c>
       <c r="H4" s="49">
-        <f>Revenue!H21</f>
+        <f>Revenue!H22</f>
         <v/>
       </c>
       <c r="I4" s="49">
-        <f>Revenue!I21</f>
+        <f>Revenue!I22</f>
         <v/>
       </c>
       <c r="J4" s="49">
-        <f>Revenue!J21</f>
+        <f>Revenue!J22</f>
         <v/>
       </c>
       <c r="K4" s="49">
-        <f>Revenue!K21</f>
+        <f>Revenue!K22</f>
         <v/>
       </c>
       <c r="L4" s="49">
-        <f>Revenue!L21</f>
+        <f>Revenue!L22</f>
         <v/>
       </c>
     </row>
@@ -17440,43 +17556,43 @@
         </is>
       </c>
       <c r="C19" s="23">
-        <f>IF(C17&lt;=0,0,IF(COUNTIF($C17:C17,"&gt;0")&lt;=Assumptions!C72,Assumptions!C70,Assumptions!C71))</f>
+        <f>IF(C17&lt;=0,0,IF(COUNTIF($C17:C17,"&gt;0")&lt;=Assumptions!C73,Assumptions!C71,Assumptions!C72))</f>
         <v/>
       </c>
       <c r="D19" s="23">
-        <f>IF(D17&lt;=0,0,IF(COUNTIF($C17:D17,"&gt;0")&lt;=Assumptions!D72,Assumptions!D70,Assumptions!D71))</f>
+        <f>IF(D17&lt;=0,0,IF(COUNTIF($C17:D17,"&gt;0")&lt;=Assumptions!D73,Assumptions!D71,Assumptions!D72))</f>
         <v/>
       </c>
       <c r="E19" s="23">
-        <f>IF(E17&lt;=0,0,IF(COUNTIF($C17:E17,"&gt;0")&lt;=Assumptions!E72,Assumptions!E70,Assumptions!E71))</f>
+        <f>IF(E17&lt;=0,0,IF(COUNTIF($C17:E17,"&gt;0")&lt;=Assumptions!E73,Assumptions!E71,Assumptions!E72))</f>
         <v/>
       </c>
       <c r="F19" s="23">
-        <f>IF(F17&lt;=0,0,IF(COUNTIF($C17:F17,"&gt;0")&lt;=Assumptions!F72,Assumptions!F70,Assumptions!F71))</f>
+        <f>IF(F17&lt;=0,0,IF(COUNTIF($C17:F17,"&gt;0")&lt;=Assumptions!F73,Assumptions!F71,Assumptions!F72))</f>
         <v/>
       </c>
       <c r="G19" s="23">
-        <f>IF(G17&lt;=0,0,IF(COUNTIF($C17:G17,"&gt;0")&lt;=Assumptions!G72,Assumptions!G70,Assumptions!G71))</f>
+        <f>IF(G17&lt;=0,0,IF(COUNTIF($C17:G17,"&gt;0")&lt;=Assumptions!G73,Assumptions!G71,Assumptions!G72))</f>
         <v/>
       </c>
       <c r="H19" s="23">
-        <f>IF(H17&lt;=0,0,IF(COUNTIF($C17:H17,"&gt;0")&lt;=Assumptions!H72,Assumptions!H70,Assumptions!H71))</f>
+        <f>IF(H17&lt;=0,0,IF(COUNTIF($C17:H17,"&gt;0")&lt;=Assumptions!H73,Assumptions!H71,Assumptions!H72))</f>
         <v/>
       </c>
       <c r="I19" s="23">
-        <f>IF(I17&lt;=0,0,IF(COUNTIF($C17:I17,"&gt;0")&lt;=Assumptions!I72,Assumptions!I70,Assumptions!I71))</f>
+        <f>IF(I17&lt;=0,0,IF(COUNTIF($C17:I17,"&gt;0")&lt;=Assumptions!I73,Assumptions!I71,Assumptions!I72))</f>
         <v/>
       </c>
       <c r="J19" s="23">
-        <f>IF(J17&lt;=0,0,IF(COUNTIF($C17:J17,"&gt;0")&lt;=Assumptions!J72,Assumptions!J70,Assumptions!J71))</f>
+        <f>IF(J17&lt;=0,0,IF(COUNTIF($C17:J17,"&gt;0")&lt;=Assumptions!J73,Assumptions!J71,Assumptions!J72))</f>
         <v/>
       </c>
       <c r="K19" s="23">
-        <f>IF(K17&lt;=0,0,IF(COUNTIF($C17:K17,"&gt;0")&lt;=Assumptions!K72,Assumptions!K70,Assumptions!K71))</f>
+        <f>IF(K17&lt;=0,0,IF(COUNTIF($C17:K17,"&gt;0")&lt;=Assumptions!K73,Assumptions!K71,Assumptions!K72))</f>
         <v/>
       </c>
       <c r="L19" s="23">
-        <f>IF(L17&lt;=0,0,IF(COUNTIF($C17:L17,"&gt;0")&lt;=Assumptions!L72,Assumptions!L70,Assumptions!L71))</f>
+        <f>IF(L17&lt;=0,0,IF(COUNTIF($C17:L17,"&gt;0")&lt;=Assumptions!L73,Assumptions!L71,Assumptions!L72))</f>
         <v/>
       </c>
     </row>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -16428,47 +16428,47 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>GMV owed, not yet paid</t>
+          <t>processed GMV owed, not yet paid</t>
         </is>
       </c>
       <c r="C6" s="30">
-        <f>Revenue!C16*Assumptions!C66/365</f>
+        <f>(Revenue!C10+Revenue!C15)*Assumptions!C66/365</f>
         <v/>
       </c>
       <c r="D6" s="30">
-        <f>Revenue!D16*Assumptions!D66/365</f>
+        <f>(Revenue!D10+Revenue!D15)*Assumptions!D66/365</f>
         <v/>
       </c>
       <c r="E6" s="30">
-        <f>Revenue!E16*Assumptions!E66/365</f>
+        <f>(Revenue!E10+Revenue!E15)*Assumptions!E66/365</f>
         <v/>
       </c>
       <c r="F6" s="30">
-        <f>Revenue!F16*Assumptions!F66/365</f>
+        <f>(Revenue!F10+Revenue!F15)*Assumptions!F66/365</f>
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>Revenue!G16*Assumptions!G66/365</f>
+        <f>(Revenue!G10+Revenue!G15)*Assumptions!G66/365</f>
         <v/>
       </c>
       <c r="H6" s="30">
-        <f>Revenue!H16*Assumptions!H66/365</f>
+        <f>(Revenue!H10+Revenue!H15)*Assumptions!H66/365</f>
         <v/>
       </c>
       <c r="I6" s="30">
-        <f>Revenue!I16*Assumptions!I66/365</f>
+        <f>(Revenue!I10+Revenue!I15)*Assumptions!I66/365</f>
         <v/>
       </c>
       <c r="J6" s="30">
-        <f>Revenue!J16*Assumptions!J66/365</f>
+        <f>(Revenue!J10+Revenue!J15)*Assumptions!J66/365</f>
         <v/>
       </c>
       <c r="K6" s="30">
-        <f>Revenue!K16*Assumptions!K66/365</f>
+        <f>(Revenue!K10+Revenue!K15)*Assumptions!K66/365</f>
         <v/>
       </c>
       <c r="L6" s="30">
-        <f>Revenue!L16*Assumptions!L66/365</f>
+        <f>(Revenue!L10+Revenue!L15)*Assumptions!L66/365</f>
         <v/>
       </c>
     </row>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -5911,31 +5911,31 @@
         <v>24777.03541521453</v>
       </c>
       <c r="D5" s="22" t="n">
-        <v>202033.1983544927</v>
+        <v>134332.6980303835</v>
       </c>
       <c r="E5" s="22" t="n">
-        <v>919083.1556542454</v>
+        <v>534652.1305392992</v>
       </c>
       <c r="F5" s="22" t="n">
-        <v>3013000.380952647</v>
+        <v>1503921.075533858</v>
       </c>
       <c r="G5" s="22" t="n">
-        <v>7568449.977255126</v>
+        <v>3426349.530867387</v>
       </c>
       <c r="H5" s="22" t="n">
-        <v>14699877.40399329</v>
+        <v>6526600.150403883</v>
       </c>
       <c r="I5" s="22" t="n">
-        <v>24131919.79247443</v>
+        <v>10701859.50721481</v>
       </c>
       <c r="J5" s="22" t="n">
-        <v>34347336.42996982</v>
+        <v>15394692.9816778</v>
       </c>
       <c r="K5" s="22" t="n">
-        <v>43325569.29647037</v>
+        <v>19918087.18566892</v>
       </c>
       <c r="L5" s="22" t="n">
-        <v>52934813.4840198</v>
+        <v>25383227.91311291</v>
       </c>
     </row>
     <row r="6">
@@ -6075,31 +6075,31 @@
         <v>13471.23223109862</v>
       </c>
       <c r="D10" s="22" t="n">
-        <v>80172.86367656694</v>
+        <v>57539.56283183506</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>324954.3266336625</v>
+        <v>192221.3376375733</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>997729.1293521416</v>
+        <v>505377.2084761651</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>2405944.872754806</v>
+        <v>1102340.973123426</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>4500263.01540566</v>
+        <v>2013276.194355648</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>7225273.097037062</v>
+        <v>3220618.534142933</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>10131408.91889975</v>
+        <v>4554135.809802086</v>
       </c>
       <c r="K10" s="22" t="n">
-        <v>12708269.29438148</v>
+        <v>5873604.154313448</v>
       </c>
       <c r="L10" s="22" t="n">
-        <v>15327976.37081417</v>
+        <v>7384734.519696838</v>
       </c>
     </row>
     <row r="11">
@@ -6239,31 +6239,31 @@
         <v>11305.80318411591</v>
       </c>
       <c r="D15" s="22" t="n">
-        <v>121860.3346779258</v>
+        <v>76793.13519854847</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>594128.8290205828</v>
+        <v>342430.792901726</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>2015271.251600505</v>
+        <v>998543.8670576925</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>5162505.10450032</v>
+        <v>2324008.55774396</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>10199614.38858763</v>
+        <v>4513323.956048235</v>
       </c>
       <c r="I15" s="22" t="n">
-        <v>16906646.69543736</v>
+        <v>7481240.973071881</v>
       </c>
       <c r="J15" s="22" t="n">
-        <v>24215927.51107008</v>
+        <v>10840557.17187572</v>
       </c>
       <c r="K15" s="22" t="n">
-        <v>30617300.00208889</v>
+        <v>14044483.03135547</v>
       </c>
       <c r="L15" s="22" t="n">
-        <v>37606837.11320563</v>
+        <v>17998493.39341607</v>
       </c>
     </row>
     <row r="16">
@@ -6403,31 +6403,31 @@
         <v>106362.1628332172</v>
       </c>
       <c r="D20" s="22" t="n">
-        <v>337225.8558683594</v>
+        <v>246665.8158424307</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>978454.4924523397</v>
+        <v>571790.730443144</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>2262252.030476212</v>
+        <v>1174225.686042709</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>4204491.99818041</v>
+        <v>2049399.962469391</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>6448435.192319464</v>
+        <v>3080254.91203231</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>9115633.583397955</v>
+        <v>4370108.760577185</v>
       </c>
       <c r="J20" s="22" t="n">
-        <v>11187130.91439759</v>
+        <v>5402439.438534224</v>
       </c>
       <c r="K20" s="22" t="n">
-        <v>12773408.04371763</v>
+        <v>6160756.974853514</v>
       </c>
       <c r="L20" s="22" t="n">
-        <v>14019092.27872158</v>
+        <v>7210743.033049033</v>
       </c>
     </row>
     <row r="21">
@@ -6567,31 +6567,31 @@
         <v>-95056.35964910126</v>
       </c>
       <c r="D25" s="22" t="n">
-        <v>-215365.5211904336</v>
+        <v>-169872.6806438822</v>
       </c>
       <c r="E25" s="22" t="n">
-        <v>-384325.6634317569</v>
+        <v>-229359.937541418</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>-246980.7788757063</v>
+        <v>-175681.8189850161</v>
       </c>
       <c r="G25" s="22" t="n">
-        <v>958013.1063199099</v>
+        <v>274608.595274569</v>
       </c>
       <c r="H25" s="22" t="n">
-        <v>3751179.196268169</v>
+        <v>1433069.044015925</v>
       </c>
       <c r="I25" s="22" t="n">
-        <v>7791013.11203941</v>
+        <v>3111132.212494696</v>
       </c>
       <c r="J25" s="22" t="n">
-        <v>13028796.59667249</v>
+        <v>5438117.733341491</v>
       </c>
       <c r="K25" s="22" t="n">
-        <v>17843891.95837126</v>
+        <v>7883726.05650196</v>
       </c>
       <c r="L25" s="22" t="n">
-        <v>23587744.83448404</v>
+        <v>10787750.36036704</v>
       </c>
     </row>
     <row r="26">
@@ -6731,31 +6731,31 @@
         <v>2057.84174041374</v>
       </c>
       <c r="D30" s="15" t="n">
-        <v>12216.77513623969</v>
+        <v>8148.23494677803</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>46332.54873998636</v>
+        <v>25287.70242113075</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>130165.2787389947</v>
+        <v>60196.82975290195</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>285069.434677292</v>
+        <v>120075.7365173497</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>490646.3002045305</v>
+        <v>206657.9512122322</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>759408.0000000001</v>
+        <v>321288</v>
       </c>
       <c r="J30" s="15" t="n">
-        <v>1007675.5</v>
+        <v>434075.5999999999</v>
       </c>
       <c r="K30" s="15" t="n">
-        <v>1237523.200000001</v>
+        <v>553628.8000000002</v>
       </c>
       <c r="L30" s="15" t="n">
-        <v>1415029</v>
+        <v>665896</v>
       </c>
     </row>
     <row r="31">
@@ -6895,31 +6895,31 @@
         <v>1305.616369213765</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>8460.569939583806</v>
+        <v>5897.122422019523</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>33681.45306248255</v>
+        <v>18938.52415509884</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>98963.81839944553</v>
+        <v>47228.17401009858</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>227425.4773897808</v>
+        <v>97836.51656978924</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>414207.6658039982</v>
+        <v>174457.6422218148</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>657721.7669360247</v>
+        <v>277910.9888438896</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>913140.2146882666</v>
+        <v>391108.4765464211</v>
       </c>
       <c r="K35" s="15" t="n">
-        <v>1149376.178943606</v>
+        <v>507748.2506421141</v>
       </c>
       <c r="L35" s="15" t="n">
-        <v>1346876.890546899</v>
+        <v>622730.6704958598</v>
       </c>
     </row>
     <row r="36">
@@ -7059,31 +7059,31 @@
         <v>166159.5694347635</v>
       </c>
       <c r="D40" s="22" t="n">
-        <v>1172259.189029952</v>
+        <v>809909.7202025568</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>5479967.704361636</v>
+        <v>3053787.536928662</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>19176831.20635098</v>
+        <v>9029784.503559049</v>
       </c>
       <c r="G40" s="22" t="n">
-        <v>51031633.18170085</v>
+        <v>21701556.20578258</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>102389216.0266219</v>
+        <v>43115734.33602589</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>169754345.2831629</v>
+        <v>71777410.04809876</v>
       </c>
       <c r="J40" s="22" t="n">
-        <v>242950202.8664655</v>
+        <v>104393238.5445187</v>
       </c>
       <c r="K40" s="22" t="n">
-        <v>304703163.3098025</v>
+        <v>135555526.5711262</v>
       </c>
       <c r="L40" s="22" t="n">
-        <v>376600783.2267987</v>
+        <v>175904826.0874194</v>
       </c>
     </row>
     <row r="41">
@@ -7223,31 +7223,31 @@
         <v>24.54</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>175.824</v>
+        <v>117.216</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>888.8000000000001</v>
+        <v>484.8</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>3355.559999999999</v>
+        <v>1548.72</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>8969.5</v>
+        <v>3767.190000000001</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>17518</v>
+        <v>7376</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>27331.2</v>
+        <v>11563.2</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>37741.6</v>
+        <v>16257.92</v>
       </c>
       <c r="K45" s="15" t="n">
-        <v>44472.16</v>
+        <v>19895.44</v>
       </c>
       <c r="L45" s="15" t="n">
-        <v>54270.8</v>
+        <v>25539.2</v>
       </c>
     </row>
     <row r="46">
@@ -7387,31 +7387,31 @@
         <v>2000</v>
       </c>
       <c r="D50" s="15" t="n">
-        <v>6706.666666666666</v>
+        <v>4040</v>
       </c>
       <c r="E50" s="15" t="n">
-        <v>16562.56</v>
+        <v>8375.039999999999</v>
       </c>
       <c r="F50" s="15" t="n">
-        <v>32462.96296296296</v>
+        <v>13666.66666666667</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>51957.8947368421</v>
+        <v>20336.84210526316</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>61593.22033898304</v>
+        <v>26004.74576271186</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>70819.67213114753</v>
+        <v>30163.9344262295</v>
       </c>
       <c r="J50" s="15" t="n">
-        <v>74141.93548387096</v>
+        <v>32980.64516129032</v>
       </c>
       <c r="K50" s="15" t="n">
-        <v>73817.46031746031</v>
+        <v>35803.17460317459</v>
       </c>
       <c r="L50" s="15" t="n">
-        <v>72199.05511811023</v>
+        <v>38515.90551181103</v>
       </c>
     </row>
     <row r="51">
@@ -7551,31 +7551,31 @@
         <v>745.0980392156863</v>
       </c>
       <c r="D55" s="22" t="n">
-        <v>3323.350588235294</v>
+        <v>2001.938823529412</v>
       </c>
       <c r="E55" s="22" t="n">
-        <v>9197.09214117647</v>
+        <v>4650.610447058823</v>
       </c>
       <c r="F55" s="22" t="n">
-        <v>18771.99477124183</v>
+        <v>7902.870588235294</v>
       </c>
       <c r="G55" s="22" t="n">
-        <v>30419.20792569659</v>
+        <v>11906.38365325077</v>
       </c>
       <c r="H55" s="22" t="n">
-        <v>36693.13446327682</v>
+        <v>15491.89387570621</v>
       </c>
       <c r="I55" s="22" t="n">
-        <v>42886.17164898746</v>
+        <v>18266.33236901318</v>
       </c>
       <c r="J55" s="22" t="n">
-        <v>45887.7522580645</v>
+        <v>20412.30330170778</v>
       </c>
       <c r="K55" s="22" t="n">
-        <v>46656.10868347338</v>
+        <v>22629.29120448179</v>
       </c>
       <c r="L55" s="22" t="n">
-        <v>46715.90313046164</v>
+        <v>24921.45233657558</v>
       </c>
     </row>
     <row r="56">
@@ -7727,19 +7727,19 @@
         <v>0</v>
       </c>
       <c r="H60" s="22" t="n">
-        <v>412074.5969161622</v>
+        <v>86581.02637066146</v>
       </c>
       <c r="I60" s="22" t="n">
-        <v>1055671.966805911</v>
+        <v>418369.8318742043</v>
       </c>
       <c r="J60" s="22" t="n">
-        <v>1798139.489500874</v>
+        <v>747077.6600012236</v>
       </c>
       <c r="K60" s="22" t="n">
-        <v>2477203.793755689</v>
+        <v>1092588.908475294</v>
       </c>
       <c r="L60" s="22" t="n">
-        <v>5500136.208621011</v>
+        <v>2513287.59009176</v>
       </c>
     </row>
     <row r="61">
@@ -7879,31 +7879,31 @@
         <v>-100756.3596491013</v>
       </c>
       <c r="D65" s="22" t="n">
-        <v>-236665.5211904336</v>
+        <v>-185972.6806438822</v>
       </c>
       <c r="E65" s="22" t="n">
-        <v>-447625.6634317569</v>
+        <v>-266459.937541418</v>
       </c>
       <c r="F65" s="22" t="n">
-        <v>-394180.7788757063</v>
+        <v>-245481.8189850161</v>
       </c>
       <c r="G65" s="22" t="n">
-        <v>668013.1063199099</v>
+        <v>149208.595274569</v>
       </c>
       <c r="H65" s="22" t="n">
-        <v>2846304.599352007</v>
+        <v>1140088.017645263</v>
       </c>
       <c r="I65" s="22" t="n">
-        <v>5982141.145233498</v>
+        <v>2370762.380620491</v>
       </c>
       <c r="J65" s="22" t="n">
-        <v>10189457.10717162</v>
+        <v>4233440.073340267</v>
       </c>
       <c r="K65" s="22" t="n">
-        <v>14037488.16461557</v>
+        <v>6191337.148026667</v>
       </c>
       <c r="L65" s="22" t="n">
-        <v>16500408.62586303</v>
+        <v>7539862.770275281</v>
       </c>
     </row>
     <row r="66">
@@ -8043,31 +8043,31 @@
         <v>-95861.09014160134</v>
       </c>
       <c r="D70" s="22" t="n">
-        <v>-202132.7647337024</v>
+        <v>-162705.2532282333</v>
       </c>
       <c r="E70" s="22" t="n">
-        <v>-290864.6904706898</v>
+        <v>-182247.5612904585</v>
       </c>
       <c r="F70" s="22" t="n">
-        <v>98221.31647175329</v>
+        <v>-26821.46881425311</v>
       </c>
       <c r="G70" s="22" t="n">
-        <v>1795103.566001351</v>
+        <v>592124.9727763702</v>
       </c>
       <c r="H70" s="22" t="n">
-        <v>4603152.529378005</v>
+        <v>1861947.574496781</v>
       </c>
       <c r="I70" s="22" t="n">
-        <v>8274542.834928216</v>
+        <v>3324666.637142324</v>
       </c>
       <c r="J70" s="22" t="n">
-        <v>12628711.76214951</v>
+        <v>5295291.75867926</v>
       </c>
       <c r="K70" s="22" t="n">
-        <v>16107958.66413932</v>
+        <v>7226355.933704762</v>
       </c>
       <c r="L70" s="22" t="n">
-        <v>18807931.6728318</v>
+        <v>8864684.894567303</v>
       </c>
     </row>
     <row r="71">
@@ -8402,31 +8402,31 @@
         <v>400</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>5500</v>
+        <v>3000</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>13000</v>
+        <v>6000</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>25000</v>
+        <v>10500</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>38000</v>
+        <v>16000</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>52000</v>
+        <v>22000</v>
       </c>
       <c r="J5" s="15" t="n">
-        <v>65000</v>
+        <v>28000</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>76000</v>
+        <v>34000</v>
       </c>
       <c r="L5" s="15" t="n">
-        <v>85000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="6">
@@ -9476,31 +9476,31 @@
         <v>25</v>
       </c>
       <c r="D34" s="15" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>340</v>
+        <v>230</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>1500</v>
+        <v>900</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>2400</v>
+        <v>1400</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="J34" s="15" t="n">
-        <v>4600</v>
+        <v>2600</v>
       </c>
       <c r="K34" s="15" t="n">
-        <v>5600</v>
+        <v>3100</v>
       </c>
       <c r="L34" s="15" t="n">
-        <v>6400</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="35">
@@ -10550,31 +10550,31 @@
         <v>1.5</v>
       </c>
       <c r="D60" s="21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60" s="21" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="F60" s="21" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G60" s="21" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H60" s="21" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I60" s="21" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="J60" s="21" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="K60" s="21" t="n">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="L60" s="21" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61">

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -1377,22 +1377,22 @@
         </is>
       </c>
       <c r="C4" s="22" t="n">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="D4" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="22" t="n">
         <v>2000000</v>
       </c>
-      <c r="F4" s="22" t="n">
+      <c r="G4" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="22" t="n">
+      <c r="H4" s="22" t="n">
         <v>8000000</v>
-      </c>
-      <c r="H4" s="22" t="n">
-        <v>0</v>
       </c>
       <c r="I4" s="22" t="n">
         <v>0</v>
@@ -1425,16 +1425,16 @@
         <v>0</v>
       </c>
       <c r="E5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="22" t="n">
         <v>10000000</v>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="G5" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="22" t="n">
+      <c r="H5" s="22" t="n">
         <v>40000000</v>
-      </c>
-      <c r="H5" s="22" t="n">
-        <v>0</v>
       </c>
       <c r="I5" s="22" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="D24" s="78" t="inlineStr">
         <is>
-          <t>400 rising to 85,000 over ten years. This is the PLAN, not a benchmark: marketing spend is derived from it at segment CAC, not the other way round. Everything in the model scales off this line.</t>
+          <t>400 rising to 40,000 over ten years. This is the PLAN, not a benchmark: marketing spend is derived from it at segment CAC, not the other way round. Everything in the model scales off this line.</t>
         </is>
       </c>
       <c r="E24" s="78" t="inlineStr">

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -1247,7 +1247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1556,104 +1556,188 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
+          <t>Advisory grant</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>ESOP pool</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t>Founders + team retained</t>
+        </is>
+      </c>
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C10" s="51">
+        <f>(1-C7-C8)*(1-C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="51">
+        <f>(C10*(1-D7)-D8)*(1-D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="51">
+        <f>(D10*(1-E7)-E8)*(1-E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="51">
+        <f>(E10*(1-F7)-F8)*(1-F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="51">
+        <f>(F10*(1-G7)-G8)*(1-G9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="51">
+        <f>(G10*(1-H7)-H8)*(1-H9)</f>
+        <v/>
+      </c>
+      <c r="I10" s="51">
+        <f>(H10*(1-I7)-I8)*(1-I9)</f>
+        <v/>
+      </c>
+      <c r="J10" s="51">
+        <f>(I10*(1-J7)-J8)*(1-J9)</f>
+        <v/>
+      </c>
+      <c r="K10" s="51">
+        <f>(J10*(1-K7)-K8)*(1-K9)</f>
+        <v/>
+      </c>
+      <c r="L10" s="51">
+        <f>(K10*(1-L7)-L8)*(1-L9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
           <t>Cumulative dilution</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C8" s="47">
-        <f>C7</f>
-        <v/>
-      </c>
-      <c r="D8" s="47">
-        <f>1-(1-C8)*(1-D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="47">
-        <f>1-(1-D8)*(1-E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="47">
-        <f>1-(1-E8)*(1-F7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="47">
-        <f>1-(1-F8)*(1-G7)</f>
-        <v/>
-      </c>
-      <c r="H8" s="47">
-        <f>1-(1-G8)*(1-H7)</f>
-        <v/>
-      </c>
-      <c r="I8" s="47">
-        <f>1-(1-H8)*(1-I7)</f>
-        <v/>
-      </c>
-      <c r="J8" s="47">
-        <f>1-(1-I8)*(1-J7)</f>
-        <v/>
-      </c>
-      <c r="K8" s="47">
-        <f>1-(1-J8)*(1-K7)</f>
-        <v/>
-      </c>
-      <c r="L8" s="47">
-        <f>1-(1-K8)*(1-L7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="39" t="inlineStr">
-        <is>
-          <t>Founders + team retained</t>
-        </is>
-      </c>
-      <c r="B9" s="40" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C9" s="51">
-        <f>1-C8</f>
-        <v/>
-      </c>
-      <c r="D9" s="51">
-        <f>1-D8</f>
-        <v/>
-      </c>
-      <c r="E9" s="51">
-        <f>1-E8</f>
-        <v/>
-      </c>
-      <c r="F9" s="51">
-        <f>1-F8</f>
-        <v/>
-      </c>
-      <c r="G9" s="51">
-        <f>1-G8</f>
-        <v/>
-      </c>
-      <c r="H9" s="51">
-        <f>1-H8</f>
-        <v/>
-      </c>
-      <c r="I9" s="51">
-        <f>1-I8</f>
-        <v/>
-      </c>
-      <c r="J9" s="51">
-        <f>1-J8</f>
-        <v/>
-      </c>
-      <c r="K9" s="51">
-        <f>1-K8</f>
-        <v/>
-      </c>
-      <c r="L9" s="51">
-        <f>1-L8</f>
+      <c r="C11" s="47">
+        <f>1-C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="47">
+        <f>1-D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="47">
+        <f>1-E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="47">
+        <f>1-F10</f>
+        <v/>
+      </c>
+      <c r="G11" s="47">
+        <f>1-G10</f>
+        <v/>
+      </c>
+      <c r="H11" s="47">
+        <f>1-H10</f>
+        <v/>
+      </c>
+      <c r="I11" s="47">
+        <f>1-I10</f>
+        <v/>
+      </c>
+      <c r="J11" s="47">
+        <f>1-J10</f>
+        <v/>
+      </c>
+      <c r="K11" s="47">
+        <f>1-K10</f>
+        <v/>
+      </c>
+      <c r="L11" s="47">
+        <f>1-L10</f>
         <v/>
       </c>
     </row>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -1247,7 +1247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1377,22 +1377,22 @@
         </is>
       </c>
       <c r="C4" s="22" t="n">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="D4" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="22" t="n">
         <v>2000000</v>
       </c>
-      <c r="F4" s="22" t="n">
+      <c r="G4" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="22" t="n">
+      <c r="H4" s="22" t="n">
         <v>8000000</v>
-      </c>
-      <c r="H4" s="22" t="n">
-        <v>0</v>
       </c>
       <c r="I4" s="22" t="n">
         <v>0</v>
@@ -1425,16 +1425,16 @@
         <v>0</v>
       </c>
       <c r="E5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="22" t="n">
         <v>10000000</v>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="G5" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="22" t="n">
+      <c r="H5" s="22" t="n">
         <v>40000000</v>
-      </c>
-      <c r="H5" s="22" t="n">
-        <v>0</v>
       </c>
       <c r="I5" s="22" t="n">
         <v>0</v>
@@ -1556,104 +1556,188 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
+          <t>Advisory grant</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>ESOP pool</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t>Founders + team retained</t>
+        </is>
+      </c>
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C10" s="51">
+        <f>(1-C7-C8)*(1-C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="51">
+        <f>(C10*(1-D7)-D8)*(1-D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="51">
+        <f>(D10*(1-E7)-E8)*(1-E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="51">
+        <f>(E10*(1-F7)-F8)*(1-F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="51">
+        <f>(F10*(1-G7)-G8)*(1-G9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="51">
+        <f>(G10*(1-H7)-H8)*(1-H9)</f>
+        <v/>
+      </c>
+      <c r="I10" s="51">
+        <f>(H10*(1-I7)-I8)*(1-I9)</f>
+        <v/>
+      </c>
+      <c r="J10" s="51">
+        <f>(I10*(1-J7)-J8)*(1-J9)</f>
+        <v/>
+      </c>
+      <c r="K10" s="51">
+        <f>(J10*(1-K7)-K8)*(1-K9)</f>
+        <v/>
+      </c>
+      <c r="L10" s="51">
+        <f>(K10*(1-L7)-L8)*(1-L9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
           <t>Cumulative dilution</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C8" s="47">
-        <f>C7</f>
-        <v/>
-      </c>
-      <c r="D8" s="47">
-        <f>1-(1-C8)*(1-D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="47">
-        <f>1-(1-D8)*(1-E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="47">
-        <f>1-(1-E8)*(1-F7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="47">
-        <f>1-(1-F8)*(1-G7)</f>
-        <v/>
-      </c>
-      <c r="H8" s="47">
-        <f>1-(1-G8)*(1-H7)</f>
-        <v/>
-      </c>
-      <c r="I8" s="47">
-        <f>1-(1-H8)*(1-I7)</f>
-        <v/>
-      </c>
-      <c r="J8" s="47">
-        <f>1-(1-I8)*(1-J7)</f>
-        <v/>
-      </c>
-      <c r="K8" s="47">
-        <f>1-(1-J8)*(1-K7)</f>
-        <v/>
-      </c>
-      <c r="L8" s="47">
-        <f>1-(1-K8)*(1-L7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="39" t="inlineStr">
-        <is>
-          <t>Founders + team retained</t>
-        </is>
-      </c>
-      <c r="B9" s="40" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C9" s="51">
-        <f>1-C8</f>
-        <v/>
-      </c>
-      <c r="D9" s="51">
-        <f>1-D8</f>
-        <v/>
-      </c>
-      <c r="E9" s="51">
-        <f>1-E8</f>
-        <v/>
-      </c>
-      <c r="F9" s="51">
-        <f>1-F8</f>
-        <v/>
-      </c>
-      <c r="G9" s="51">
-        <f>1-G8</f>
-        <v/>
-      </c>
-      <c r="H9" s="51">
-        <f>1-H8</f>
-        <v/>
-      </c>
-      <c r="I9" s="51">
-        <f>1-I8</f>
-        <v/>
-      </c>
-      <c r="J9" s="51">
-        <f>1-J8</f>
-        <v/>
-      </c>
-      <c r="K9" s="51">
-        <f>1-K8</f>
-        <v/>
-      </c>
-      <c r="L9" s="51">
-        <f>1-L8</f>
+      <c r="C11" s="47">
+        <f>1-C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="47">
+        <f>1-D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="47">
+        <f>1-E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="47">
+        <f>1-F10</f>
+        <v/>
+      </c>
+      <c r="G11" s="47">
+        <f>1-G10</f>
+        <v/>
+      </c>
+      <c r="H11" s="47">
+        <f>1-H10</f>
+        <v/>
+      </c>
+      <c r="I11" s="47">
+        <f>1-I10</f>
+        <v/>
+      </c>
+      <c r="J11" s="47">
+        <f>1-J10</f>
+        <v/>
+      </c>
+      <c r="K11" s="47">
+        <f>1-K10</f>
+        <v/>
+      </c>
+      <c r="L11" s="47">
+        <f>1-L10</f>
         <v/>
       </c>
     </row>
@@ -5063,7 +5147,7 @@
       </c>
       <c r="D24" s="78" t="inlineStr">
         <is>
-          <t>400 rising to 85,000 over ten years. This is the PLAN, not a benchmark: marketing spend is derived from it at segment CAC, not the other way round. Everything in the model scales off this line.</t>
+          <t>400 rising to 40,000 over ten years. This is the PLAN, not a benchmark: marketing spend is derived from it at segment CAC, not the other way round. Everything in the model scales off this line.</t>
         </is>
       </c>
       <c r="E24" s="78" t="inlineStr">

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -17,11 +17,14 @@
     <sheet name="CashFlow" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="BalanceSheet" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Funding" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Valuation" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Comparables" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="MarketModel" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Research" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Check" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="HiringPlan" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="CAC_CLV" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="KPIs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Valuation" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Comparables" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="MarketModel" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Research" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Check" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +42,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.000"/>
     <numFmt numFmtId="170" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -151,6 +154,12 @@
       <b val="1"/>
       <color rgb="00B3272D"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="8"/>
     </font>
     <font>
       <i val="1"/>
@@ -321,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -385,30 +394,37 @@
     <xf numFmtId="167" fontId="18" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="19" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="17" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="17" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="17" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="12" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="16" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="16" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="17" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="15" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="169" fontId="15" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="15" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="15" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -418,28 +434,28 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="17" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1778,7 +1794,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Valuation — DCF, NPV, IRR and exit multiples</t>
+          <t>Hiring plan — headcount by role, reconciled to the model</t>
         </is>
       </c>
     </row>
@@ -1877,563 +1893,1162 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Free cash flow</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C4" s="30">
-        <f>CashFlow!C9</f>
-        <v/>
-      </c>
-      <c r="D4" s="30">
-        <f>CashFlow!D9</f>
-        <v/>
-      </c>
-      <c r="E4" s="30">
-        <f>CashFlow!E9</f>
-        <v/>
-      </c>
-      <c r="F4" s="30">
-        <f>CashFlow!F9</f>
-        <v/>
-      </c>
-      <c r="G4" s="30">
-        <f>CashFlow!G9</f>
-        <v/>
-      </c>
-      <c r="H4" s="30">
-        <f>CashFlow!H9</f>
-        <v/>
-      </c>
-      <c r="I4" s="30">
-        <f>CashFlow!I9</f>
-        <v/>
-      </c>
-      <c r="J4" s="30">
-        <f>CashFlow!J9</f>
-        <v/>
-      </c>
-      <c r="K4" s="30">
-        <f>CashFlow!K9</f>
-        <v/>
-      </c>
-      <c r="L4" s="30">
-        <f>CashFlow!L9</f>
-        <v/>
-      </c>
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>FTE BY ROLE</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="12" t="n"/>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="12" t="n"/>
+      <c r="L4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Discount factor</t>
+          <t>Founder / CEO</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>1/(1+WACC)^t</t>
-        </is>
-      </c>
-      <c r="C5" s="33">
-        <f>1/(1+Assumptions!$C$85)^1</f>
-        <v/>
-      </c>
-      <c r="D5" s="33">
-        <f>1/(1+Assumptions!$C$85)^2</f>
-        <v/>
-      </c>
-      <c r="E5" s="33">
-        <f>1/(1+Assumptions!$C$85)^3</f>
-        <v/>
-      </c>
-      <c r="F5" s="33">
-        <f>1/(1+Assumptions!$C$85)^4</f>
-        <v/>
-      </c>
-      <c r="G5" s="33">
-        <f>1/(1+Assumptions!$C$85)^5</f>
-        <v/>
-      </c>
-      <c r="H5" s="33">
-        <f>1/(1+Assumptions!$C$85)^6</f>
-        <v/>
-      </c>
-      <c r="I5" s="33">
-        <f>1/(1+Assumptions!$C$85)^7</f>
-        <v/>
-      </c>
-      <c r="J5" s="33">
-        <f>1/(1+Assumptions!$C$85)^8</f>
-        <v/>
-      </c>
-      <c r="K5" s="33">
-        <f>1/(1+Assumptions!$C$85)^9</f>
-        <v/>
-      </c>
-      <c r="L5" s="33">
-        <f>1/(1+Assumptions!$C$85)^10</f>
-        <v/>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
-        <is>
-          <t>Discounted FCF</t>
-        </is>
-      </c>
-      <c r="B6" s="40" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C6" s="43">
-        <f>C4*C5</f>
-        <v/>
-      </c>
-      <c r="D6" s="43">
-        <f>D4*D5</f>
-        <v/>
-      </c>
-      <c r="E6" s="43">
-        <f>E4*E5</f>
-        <v/>
-      </c>
-      <c r="F6" s="43">
-        <f>F4*F5</f>
-        <v/>
-      </c>
-      <c r="G6" s="43">
-        <f>G4*G5</f>
-        <v/>
-      </c>
-      <c r="H6" s="43">
-        <f>H4*H5</f>
-        <v/>
-      </c>
-      <c r="I6" s="43">
-        <f>I4*I5</f>
-        <v/>
-      </c>
-      <c r="J6" s="43">
-        <f>J4*J5</f>
-        <v/>
-      </c>
-      <c r="K6" s="43">
-        <f>K4*K5</f>
-        <v/>
-      </c>
-      <c r="L6" s="43">
-        <f>L4*L5</f>
-        <v/>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H6" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" s="21" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>BD / partnerships</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" s="21" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>FCF incl. terminal value</t>
+          <t>Athlete success</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>for the IRR below</t>
-        </is>
-      </c>
-      <c r="C8" s="47">
-        <f>C4+IF(1=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="47">
-        <f>D4+IF(2=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="E8" s="47">
-        <f>E4+IF(3=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="47">
-        <f>F4+IF(4=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="47">
-        <f>G4+IF(5=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="H8" s="47">
-        <f>H4+IF(6=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="I8" s="47">
-        <f>I4+IF(7=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="J8" s="47">
-        <f>J4+IF(8=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="K8" s="47">
-        <f>K4+IF(9=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="L8" s="47">
-        <f>L4+IF(10=10,$C$11,0)</f>
-        <v/>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I8" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" s="21" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>DCF</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Trust &amp; safety / review</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G9" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" s="21" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PV of explicit forecast</t>
-        </is>
-      </c>
-      <c r="C10" s="51">
-        <f>SUM(C6:L6)</f>
-        <v/>
+          <t>Finance / operations</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Terminal value at Y10</t>
-        </is>
-      </c>
-      <c r="C11" s="51">
-        <f>L4*(1+Assumptions!$C$86)/(Assumptions!$C$85-Assumptions!$C$86)</f>
-        <v/>
+          <t>Data protection officer</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>TOTAL FTE</t>
+        </is>
+      </c>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>FTE</t>
         </is>
       </c>
       <c r="C12" s="51">
-        <f>C11*L5</f>
+        <f>SUM(C5:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="51">
+        <f>SUM(D5:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="51">
+        <f>SUM(E5:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="51">
+        <f>SUM(F5:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="51">
+        <f>SUM(G5:G11)</f>
+        <v/>
+      </c>
+      <c r="H12" s="51">
+        <f>SUM(H5:H11)</f>
+        <v/>
+      </c>
+      <c r="I12" s="51">
+        <f>SUM(I5:I11)</f>
+        <v/>
+      </c>
+      <c r="J12" s="51">
+        <f>SUM(J5:J11)</f>
+        <v/>
+      </c>
+      <c r="K12" s="51">
+        <f>SUM(K5:K11)</f>
+        <v/>
+      </c>
+      <c r="L12" s="51">
+        <f>SUM(L5:L11)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>ENTERPRISE VALUE (DCF)</t>
-        </is>
-      </c>
-      <c r="C13" s="51">
-        <f>C10+C12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>RETURN METRICS</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="12" t="n"/>
-      <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Model headcount</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+      <c r="C13" s="31">
+        <f>Assumptions!C60</f>
+        <v/>
+      </c>
+      <c r="D13" s="31">
+        <f>Assumptions!D60</f>
+        <v/>
+      </c>
+      <c r="E13" s="31">
+        <f>Assumptions!E60</f>
+        <v/>
+      </c>
+      <c r="F13" s="31">
+        <f>Assumptions!F60</f>
+        <v/>
+      </c>
+      <c r="G13" s="31">
+        <f>Assumptions!G60</f>
+        <v/>
+      </c>
+      <c r="H13" s="31">
+        <f>Assumptions!H60</f>
+        <v/>
+      </c>
+      <c r="I13" s="31">
+        <f>Assumptions!I60</f>
+        <v/>
+      </c>
+      <c r="J13" s="31">
+        <f>Assumptions!J60</f>
+        <v/>
+      </c>
+      <c r="K13" s="31">
+        <f>Assumptions!K60</f>
+        <v/>
+      </c>
+      <c r="L13" s="31">
+        <f>Assumptions!L60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="39" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>must be zero</t>
+        </is>
+      </c>
+      <c r="C14" s="52">
+        <f>ROUND(C12-C13,3)</f>
+        <v/>
+      </c>
+      <c r="D14" s="52">
+        <f>ROUND(D12-D13,3)</f>
+        <v/>
+      </c>
+      <c r="E14" s="52">
+        <f>ROUND(E12-E13,3)</f>
+        <v/>
+      </c>
+      <c r="F14" s="52">
+        <f>ROUND(F12-F13,3)</f>
+        <v/>
+      </c>
+      <c r="G14" s="52">
+        <f>ROUND(G12-G13,3)</f>
+        <v/>
+      </c>
+      <c r="H14" s="52">
+        <f>ROUND(H12-H13,3)</f>
+        <v/>
+      </c>
+      <c r="I14" s="52">
+        <f>ROUND(I12-I13,3)</f>
+        <v/>
+      </c>
+      <c r="J14" s="52">
+        <f>ROUND(J12-J13,3)</f>
+        <v/>
+      </c>
+      <c r="K14" s="52">
+        <f>ROUND(K12-K13,3)</f>
+        <v/>
+      </c>
+      <c r="L14" s="52">
+        <f>ROUND(L12-L13,3)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>NPV of FCF at WACC</t>
-        </is>
-      </c>
-      <c r="C16" s="51">
-        <f>NPV(Assumptions!$C$85,C4:L4)</f>
-        <v/>
-      </c>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>COST — ROLE BUILD-UP AGAINST THE MODEL</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>IRR of the plan</t>
-        </is>
-      </c>
-      <c r="C17" s="52">
-        <f>IRR(C4:L4)</f>
-        <v/>
+          <t>Employer social security</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>on gross</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L17" s="36" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>IRR incl. terminal value</t>
-        </is>
-      </c>
-      <c r="C18" s="52">
-        <f>IRR(C8:L8,0.3)</f>
+          <t>Founder / CEO — loaded</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C18" s="47">
+        <f>C5*45000*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="47">
+        <f>D5*45000*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="47">
+        <f>E5*45000*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="47">
+        <f>F5*45000*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="47">
+        <f>G5*45000*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="47">
+        <f>H5*45000*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="47">
+        <f>I5*45000*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="47">
+        <f>J5*45000*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K18" s="47">
+        <f>K5*45000*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L18" s="47">
+        <f>L5*45000*(1+L17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Engineering — loaded</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C19" s="47">
+        <f>C6*55000*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D19" s="47">
+        <f>D6*55000*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E19" s="47">
+        <f>E6*55000*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F19" s="47">
+        <f>F6*55000*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G19" s="47">
+        <f>G6*55000*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H19" s="47">
+        <f>H6*55000*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I19" s="47">
+        <f>I6*55000*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J19" s="47">
+        <f>J6*55000*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K19" s="47">
+        <f>K6*55000*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L19" s="47">
+        <f>L6*55000*(1+L17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>EXIT MULTIPLE</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
-      <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
-      <c r="L20" s="12" t="n"/>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>BD / partnerships — loaded</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C20" s="47">
+        <f>C7*38000*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D20" s="47">
+        <f>D7*38000*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E20" s="47">
+        <f>E7*38000*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F20" s="47">
+        <f>F7*38000*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G20" s="47">
+        <f>G7*38000*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H20" s="47">
+        <f>H7*38000*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I20" s="47">
+        <f>I7*38000*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J20" s="47">
+        <f>J7*38000*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K20" s="47">
+        <f>K7*38000*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L20" s="47">
+        <f>L7*38000*(1+L17)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>Y10 net revenue</t>
-        </is>
-      </c>
-      <c r="C21" s="51">
-        <f>Revenue!L22</f>
+          <t>Athlete success — loaded</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C21" s="47">
+        <f>C8*30000*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D21" s="47">
+        <f>D8*30000*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E21" s="47">
+        <f>E8*30000*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F21" s="47">
+        <f>F8*30000*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G21" s="47">
+        <f>G8*30000*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H21" s="47">
+        <f>H8*30000*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I21" s="47">
+        <f>I8*30000*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J21" s="47">
+        <f>J8*30000*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K21" s="47">
+        <f>K8*30000*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L21" s="47">
+        <f>L8*30000*(1+L17)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>Exit value at Y10</t>
-        </is>
-      </c>
-      <c r="C22" s="51">
-        <f>C21*Assumptions!$C$87</f>
+          <t>Trust &amp; safety / review — loaded</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C22" s="47">
+        <f>C9*34000*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D22" s="47">
+        <f>D9*34000*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E22" s="47">
+        <f>E9*34000*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F22" s="47">
+        <f>F9*34000*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G22" s="47">
+        <f>G9*34000*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H22" s="47">
+        <f>H9*34000*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I22" s="47">
+        <f>I9*34000*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J22" s="47">
+        <f>J9*34000*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K22" s="47">
+        <f>K9*34000*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L22" s="47">
+        <f>L9*34000*(1+L17)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>Discounted to today</t>
-        </is>
-      </c>
-      <c r="C23" s="51">
-        <f>C22*L5</f>
+          <t>Finance / operations — loaded</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C23" s="47">
+        <f>C10*42000*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D23" s="47">
+        <f>D10*42000*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E23" s="47">
+        <f>E10*42000*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F23" s="47">
+        <f>F10*42000*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G23" s="47">
+        <f>G10*42000*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H23" s="47">
+        <f>H10*42000*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I23" s="47">
+        <f>I10*42000*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J23" s="47">
+        <f>J10*42000*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K23" s="47">
+        <f>K10*42000*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L23" s="47">
+        <f>L10*42000*(1+L17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Data protection officer — loaded</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C24" s="47">
+        <f>C11*60000*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D24" s="47">
+        <f>D11*60000*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E24" s="47">
+        <f>E11*60000*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F24" s="47">
+        <f>F11*60000*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G24" s="47">
+        <f>G11*60000*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H24" s="47">
+        <f>H11*60000*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I24" s="47">
+        <f>I11*60000*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J24" s="47">
+        <f>J11*60000*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K24" s="47">
+        <f>K11*60000*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L24" s="47">
+        <f>L11*60000*(1+L17)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>SENSITIVITY — enterprise value by WACC and terminal growth</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="12" t="n"/>
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>TOTAL, role build-up</t>
+        </is>
+      </c>
+      <c r="B25" s="40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C25" s="45">
+        <f>SUM(C18:C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="45">
+        <f>SUM(D18:D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="45">
+        <f>SUM(E18:E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="45">
+        <f>SUM(F18:F24)</f>
+        <v/>
+      </c>
+      <c r="G25" s="45">
+        <f>SUM(G18:G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="45">
+        <f>SUM(H18:H24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="45">
+        <f>SUM(I18:I24)</f>
+        <v/>
+      </c>
+      <c r="J25" s="45">
+        <f>SUM(J18:J24)</f>
+        <v/>
+      </c>
+      <c r="K25" s="45">
+        <f>SUM(K18:K24)</f>
+        <v/>
+      </c>
+      <c r="L25" s="45">
+        <f>SUM(L18:L24)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Terminal growth \ WACC</t>
-        </is>
-      </c>
-      <c r="C26" s="53" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D26" s="53" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E26" s="53" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F26" s="53" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G26" s="53" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H26" s="53" t="n">
-        <v>0.3</v>
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>People cost in the model</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="C26" s="30">
+        <f>Costs!C17</f>
+        <v/>
+      </c>
+      <c r="D26" s="30">
+        <f>Costs!D17</f>
+        <v/>
+      </c>
+      <c r="E26" s="30">
+        <f>Costs!E17</f>
+        <v/>
+      </c>
+      <c r="F26" s="30">
+        <f>Costs!F17</f>
+        <v/>
+      </c>
+      <c r="G26" s="30">
+        <f>Costs!G17</f>
+        <v/>
+      </c>
+      <c r="H26" s="30">
+        <f>Costs!H17</f>
+        <v/>
+      </c>
+      <c r="I26" s="30">
+        <f>Costs!I17</f>
+        <v/>
+      </c>
+      <c r="J26" s="30">
+        <f>Costs!J17</f>
+        <v/>
+      </c>
+      <c r="K26" s="30">
+        <f>Costs!K17</f>
+        <v/>
+      </c>
+      <c r="L26" s="30">
+        <f>Costs!L17</f>
+        <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="52" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C27" s="54">
-        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.01)/(0.18-0.01)/(1+0.18)^10</f>
-        <v/>
-      </c>
-      <c r="D27" s="54">
-        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.01)/(0.2-0.01)/(1+0.2)^10</f>
-        <v/>
-      </c>
-      <c r="E27" s="54">
-        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.01)/(0.22-0.01)/(1+0.22)^10</f>
-        <v/>
-      </c>
-      <c r="F27" s="54">
-        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.01)/(0.25-0.01)/(1+0.25)^10</f>
-        <v/>
-      </c>
-      <c r="G27" s="54">
-        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.01)/(0.28-0.01)/(1+0.28)^10</f>
-        <v/>
-      </c>
-      <c r="H27" s="54">
-        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.01)/(0.3-0.01)/(1+0.3)^10</f>
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Difference — role mix</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>build-up less model</t>
+        </is>
+      </c>
+      <c r="C27" s="47">
+        <f>C25-C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="47">
+        <f>D25-D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="47">
+        <f>E25-E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="47">
+        <f>F25-F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="47">
+        <f>G25-G26</f>
+        <v/>
+      </c>
+      <c r="H27" s="47">
+        <f>H25-H26</f>
+        <v/>
+      </c>
+      <c r="I27" s="47">
+        <f>I25-I26</f>
+        <v/>
+      </c>
+      <c r="J27" s="47">
+        <f>J25-J26</f>
+        <v/>
+      </c>
+      <c r="K27" s="47">
+        <f>K25-K26</f>
+        <v/>
+      </c>
+      <c r="L27" s="47">
+        <f>L25-L26</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="52" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C28" s="54">
-        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.02)/(0.18-0.02)/(1+0.18)^10</f>
-        <v/>
-      </c>
-      <c r="D28" s="54">
-        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.02)/(0.2-0.02)/(1+0.2)^10</f>
-        <v/>
-      </c>
-      <c r="E28" s="54">
-        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.02)/(0.22-0.02)/(1+0.22)^10</f>
-        <v/>
-      </c>
-      <c r="F28" s="54">
-        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.02)/(0.25-0.02)/(1+0.25)^10</f>
-        <v/>
-      </c>
-      <c r="G28" s="54">
-        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.02)/(0.28-0.02)/(1+0.28)^10</f>
-        <v/>
-      </c>
-      <c r="H28" s="54">
-        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.02)/(0.3-0.02)/(1+0.3)^10</f>
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  memo: build-up per FTE</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C28" s="53">
+        <f>IF(C12=0,0,C25/C12)</f>
+        <v/>
+      </c>
+      <c r="D28" s="53">
+        <f>IF(D12=0,0,D25/D12)</f>
+        <v/>
+      </c>
+      <c r="E28" s="53">
+        <f>IF(E12=0,0,E25/E12)</f>
+        <v/>
+      </c>
+      <c r="F28" s="53">
+        <f>IF(F12=0,0,F25/F12)</f>
+        <v/>
+      </c>
+      <c r="G28" s="53">
+        <f>IF(G12=0,0,G25/G12)</f>
+        <v/>
+      </c>
+      <c r="H28" s="53">
+        <f>IF(H12=0,0,H25/H12)</f>
+        <v/>
+      </c>
+      <c r="I28" s="53">
+        <f>IF(I12=0,0,I25/I12)</f>
+        <v/>
+      </c>
+      <c r="J28" s="53">
+        <f>IF(J12=0,0,J25/J12)</f>
+        <v/>
+      </c>
+      <c r="K28" s="53">
+        <f>IF(K12=0,0,K25/K12)</f>
+        <v/>
+      </c>
+      <c r="L28" s="53">
+        <f>IF(L12=0,0,L25/L12)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="52" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C29" s="54">
-        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.03)/(0.18-0.03)/(1+0.18)^10</f>
-        <v/>
-      </c>
-      <c r="D29" s="54">
-        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.03)/(0.2-0.03)/(1+0.2)^10</f>
-        <v/>
-      </c>
-      <c r="E29" s="54">
-        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.03)/(0.22-0.03)/(1+0.22)^10</f>
-        <v/>
-      </c>
-      <c r="F29" s="54">
-        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.03)/(0.25-0.03)/(1+0.25)^10</f>
-        <v/>
-      </c>
-      <c r="G29" s="54">
-        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.03)/(0.28-0.03)/(1+0.28)^10</f>
-        <v/>
-      </c>
-      <c r="H29" s="54">
-        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.03)/(0.3-0.03)/(1+0.3)^10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="52" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C30" s="54">
-        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.04)/(0.18-0.04)/(1+0.18)^10</f>
-        <v/>
-      </c>
-      <c r="D30" s="54">
-        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.04)/(0.2-0.04)/(1+0.2)^10</f>
-        <v/>
-      </c>
-      <c r="E30" s="54">
-        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.04)/(0.22-0.04)/(1+0.22)^10</f>
-        <v/>
-      </c>
-      <c r="F30" s="54">
-        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.04)/(0.25-0.04)/(1+0.25)^10</f>
-        <v/>
-      </c>
-      <c r="G30" s="54">
-        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.04)/(0.28-0.04)/(1+0.28)^10</f>
-        <v/>
-      </c>
-      <c r="H30" s="54">
-        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.04)/(0.3-0.04)/(1+0.3)^10</f>
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  memo: model blended per FTE</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C29" s="30">
+        <f>Assumptions!C61</f>
+        <v/>
+      </c>
+      <c r="D29" s="30">
+        <f>Assumptions!D61</f>
+        <v/>
+      </c>
+      <c r="E29" s="30">
+        <f>Assumptions!E61</f>
+        <v/>
+      </c>
+      <c r="F29" s="30">
+        <f>Assumptions!F61</f>
+        <v/>
+      </c>
+      <c r="G29" s="30">
+        <f>Assumptions!G61</f>
+        <v/>
+      </c>
+      <c r="H29" s="30">
+        <f>Assumptions!H61</f>
+        <v/>
+      </c>
+      <c r="I29" s="30">
+        <f>Assumptions!I61</f>
+        <v/>
+      </c>
+      <c r="J29" s="30">
+        <f>Assumptions!J61</f>
+        <v/>
+      </c>
+      <c r="K29" s="30">
+        <f>Assumptions!K61</f>
+        <v/>
+      </c>
+      <c r="L29" s="30">
+        <f>Assumptions!L61</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="52" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C31" s="54">
-        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.05)/(0.18-0.05)/(1+0.18)^10</f>
-        <v/>
-      </c>
-      <c r="D31" s="54">
-        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.05)/(0.2-0.05)/(1+0.2)^10</f>
-        <v/>
-      </c>
-      <c r="E31" s="54">
-        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.05)/(0.22-0.05)/(1+0.22)^10</f>
-        <v/>
-      </c>
-      <c r="F31" s="54">
-        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.05)/(0.25-0.05)/(1+0.25)^10</f>
-        <v/>
-      </c>
-      <c r="G31" s="54">
-        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.05)/(0.28-0.05)/(1+0.28)^10</f>
-        <v/>
-      </c>
-      <c r="H31" s="54">
-        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.05)/(0.3-0.05)/(1+0.3)^10</f>
-        <v/>
+      <c r="A31" s="54" t="inlineStr">
+        <is>
+          <t>The FTE block reconciles exactly and is the plan. The cost build-up prices those roles at their own salaries; the model prices the same headcount at a blended loaded average that rises from 38k to 76k over the plan, covering seniority and inflation, while the build-up holds today's salaries flat. The model is therefore the more expensive and more conservative of the two, and it is the one that reaches the P&amp;L. The two memo rows below make the gap legible.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2454,6 +3069,2913 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Customer acquisition cost and lifetime value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Input — change me</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Sourced fact</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Formula (this sheet)</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Formula (other sheet)</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Y7</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Y8</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Y9</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Y10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>ATHLETE — BLENDED ACROSS SEGMENTS</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="12" t="n"/>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="12" t="n"/>
+      <c r="L4" s="12" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Niche share of athletes</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C5" s="23">
+        <f>Assumptions!C6</f>
+        <v/>
+      </c>
+      <c r="D5" s="23">
+        <f>Assumptions!D6</f>
+        <v/>
+      </c>
+      <c r="E5" s="23">
+        <f>Assumptions!E6</f>
+        <v/>
+      </c>
+      <c r="F5" s="23">
+        <f>Assumptions!F6</f>
+        <v/>
+      </c>
+      <c r="G5" s="23">
+        <f>Assumptions!G6</f>
+        <v/>
+      </c>
+      <c r="H5" s="23">
+        <f>Assumptions!H6</f>
+        <v/>
+      </c>
+      <c r="I5" s="23">
+        <f>Assumptions!I6</f>
+        <v/>
+      </c>
+      <c r="J5" s="23">
+        <f>Assumptions!J6</f>
+        <v/>
+      </c>
+      <c r="K5" s="23">
+        <f>Assumptions!K6</f>
+        <v/>
+      </c>
+      <c r="L5" s="23">
+        <f>Assumptions!L6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Blended CAC per athlete</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C6" s="30">
+        <f>C5*Assumptions!C19+(1-C5)*Assumptions!C31</f>
+        <v/>
+      </c>
+      <c r="D6" s="30">
+        <f>D5*Assumptions!D19+(1-D5)*Assumptions!D31</f>
+        <v/>
+      </c>
+      <c r="E6" s="30">
+        <f>E5*Assumptions!E19+(1-E5)*Assumptions!E31</f>
+        <v/>
+      </c>
+      <c r="F6" s="30">
+        <f>F5*Assumptions!F19+(1-F5)*Assumptions!F31</f>
+        <v/>
+      </c>
+      <c r="G6" s="30">
+        <f>G5*Assumptions!G19+(1-G5)*Assumptions!G31</f>
+        <v/>
+      </c>
+      <c r="H6" s="30">
+        <f>H5*Assumptions!H19+(1-H5)*Assumptions!H31</f>
+        <v/>
+      </c>
+      <c r="I6" s="30">
+        <f>I5*Assumptions!I19+(1-I5)*Assumptions!I31</f>
+        <v/>
+      </c>
+      <c r="J6" s="30">
+        <f>J5*Assumptions!J19+(1-J5)*Assumptions!J31</f>
+        <v/>
+      </c>
+      <c r="K6" s="30">
+        <f>K5*Assumptions!K19+(1-K5)*Assumptions!K31</f>
+        <v/>
+      </c>
+      <c r="L6" s="30">
+        <f>L5*Assumptions!L19+(1-L5)*Assumptions!L31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Blended athlete churn</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>per year</t>
+        </is>
+      </c>
+      <c r="C7" s="23">
+        <f>C5*Assumptions!C14+(1-C5)*Assumptions!C26</f>
+        <v/>
+      </c>
+      <c r="D7" s="23">
+        <f>D5*Assumptions!D14+(1-D5)*Assumptions!D26</f>
+        <v/>
+      </c>
+      <c r="E7" s="23">
+        <f>E5*Assumptions!E14+(1-E5)*Assumptions!E26</f>
+        <v/>
+      </c>
+      <c r="F7" s="23">
+        <f>F5*Assumptions!F14+(1-F5)*Assumptions!F26</f>
+        <v/>
+      </c>
+      <c r="G7" s="23">
+        <f>G5*Assumptions!G14+(1-G5)*Assumptions!G26</f>
+        <v/>
+      </c>
+      <c r="H7" s="23">
+        <f>H5*Assumptions!H14+(1-H5)*Assumptions!H26</f>
+        <v/>
+      </c>
+      <c r="I7" s="23">
+        <f>I5*Assumptions!I14+(1-I5)*Assumptions!I26</f>
+        <v/>
+      </c>
+      <c r="J7" s="23">
+        <f>J5*Assumptions!J14+(1-J5)*Assumptions!J26</f>
+        <v/>
+      </c>
+      <c r="K7" s="23">
+        <f>K5*Assumptions!K14+(1-K5)*Assumptions!K26</f>
+        <v/>
+      </c>
+      <c r="L7" s="23">
+        <f>L5*Assumptions!L14+(1-L5)*Assumptions!L26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Expected athlete life</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="C8" s="55">
+        <f>IF(C7=0,0,1/C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="55">
+        <f>IF(D7=0,0,1/D7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="55">
+        <f>IF(E7=0,0,1/E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="55">
+        <f>IF(F7=0,0,1/F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="55">
+        <f>IF(G7=0,0,1/G7)</f>
+        <v/>
+      </c>
+      <c r="H8" s="55">
+        <f>IF(H7=0,0,1/H7)</f>
+        <v/>
+      </c>
+      <c r="I8" s="55">
+        <f>IF(I7=0,0,1/I7)</f>
+        <v/>
+      </c>
+      <c r="J8" s="55">
+        <f>IF(J7=0,0,1/J7)</f>
+        <v/>
+      </c>
+      <c r="K8" s="55">
+        <f>IF(K7=0,0,1/K7)</f>
+        <v/>
+      </c>
+      <c r="L8" s="55">
+        <f>IF(L7=0,0,1/L7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Net revenue per athlete</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>EUR/yr</t>
+        </is>
+      </c>
+      <c r="C9" s="30">
+        <f>IF(Drivers!C5=0,0,Revenue!C22/Drivers!C5)</f>
+        <v/>
+      </c>
+      <c r="D9" s="30">
+        <f>IF(Drivers!D5=0,0,Revenue!D22/Drivers!D5)</f>
+        <v/>
+      </c>
+      <c r="E9" s="30">
+        <f>IF(Drivers!E5=0,0,Revenue!E22/Drivers!E5)</f>
+        <v/>
+      </c>
+      <c r="F9" s="30">
+        <f>IF(Drivers!F5=0,0,Revenue!F22/Drivers!F5)</f>
+        <v/>
+      </c>
+      <c r="G9" s="30">
+        <f>IF(Drivers!G5=0,0,Revenue!G22/Drivers!G5)</f>
+        <v/>
+      </c>
+      <c r="H9" s="30">
+        <f>IF(Drivers!H5=0,0,Revenue!H22/Drivers!H5)</f>
+        <v/>
+      </c>
+      <c r="I9" s="30">
+        <f>IF(Drivers!I5=0,0,Revenue!I22/Drivers!I5)</f>
+        <v/>
+      </c>
+      <c r="J9" s="30">
+        <f>IF(Drivers!J5=0,0,Revenue!J22/Drivers!J5)</f>
+        <v/>
+      </c>
+      <c r="K9" s="30">
+        <f>IF(Drivers!K5=0,0,Revenue!K22/Drivers!K5)</f>
+        <v/>
+      </c>
+      <c r="L9" s="30">
+        <f>IF(Drivers!L5=0,0,Revenue!L22/Drivers!L5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Contribution per athlete per year</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>after COGS</t>
+        </is>
+      </c>
+      <c r="C10" s="30">
+        <f>IF(Revenue!C22=0,0,C9*'P&amp;L'!C6/Revenue!C22)</f>
+        <v/>
+      </c>
+      <c r="D10" s="30">
+        <f>IF(Revenue!D22=0,0,D9*'P&amp;L'!D6/Revenue!D22)</f>
+        <v/>
+      </c>
+      <c r="E10" s="30">
+        <f>IF(Revenue!E22=0,0,E9*'P&amp;L'!E6/Revenue!E22)</f>
+        <v/>
+      </c>
+      <c r="F10" s="30">
+        <f>IF(Revenue!F22=0,0,F9*'P&amp;L'!F6/Revenue!F22)</f>
+        <v/>
+      </c>
+      <c r="G10" s="30">
+        <f>IF(Revenue!G22=0,0,G9*'P&amp;L'!G6/Revenue!G22)</f>
+        <v/>
+      </c>
+      <c r="H10" s="30">
+        <f>IF(Revenue!H22=0,0,H9*'P&amp;L'!H6/Revenue!H22)</f>
+        <v/>
+      </c>
+      <c r="I10" s="30">
+        <f>IF(Revenue!I22=0,0,I9*'P&amp;L'!I6/Revenue!I22)</f>
+        <v/>
+      </c>
+      <c r="J10" s="30">
+        <f>IF(Revenue!J22=0,0,J9*'P&amp;L'!J6/Revenue!J22)</f>
+        <v/>
+      </c>
+      <c r="K10" s="30">
+        <f>IF(Revenue!K22=0,0,K9*'P&amp;L'!K6/Revenue!K22)</f>
+        <v/>
+      </c>
+      <c r="L10" s="30">
+        <f>IF(Revenue!L22=0,0,L9*'P&amp;L'!L6/Revenue!L22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>ATHLETE LTV</t>
+        </is>
+      </c>
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C11" s="45">
+        <f>C10*C8</f>
+        <v/>
+      </c>
+      <c r="D11" s="45">
+        <f>D10*D8</f>
+        <v/>
+      </c>
+      <c r="E11" s="45">
+        <f>E10*E8</f>
+        <v/>
+      </c>
+      <c r="F11" s="45">
+        <f>F10*F8</f>
+        <v/>
+      </c>
+      <c r="G11" s="45">
+        <f>G10*G8</f>
+        <v/>
+      </c>
+      <c r="H11" s="45">
+        <f>H10*H8</f>
+        <v/>
+      </c>
+      <c r="I11" s="45">
+        <f>I10*I8</f>
+        <v/>
+      </c>
+      <c r="J11" s="45">
+        <f>J10*J8</f>
+        <v/>
+      </c>
+      <c r="K11" s="45">
+        <f>K10*K8</f>
+        <v/>
+      </c>
+      <c r="L11" s="45">
+        <f>L10*L8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>LTV / CAC</t>
+        </is>
+      </c>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C12" s="52">
+        <f>IF(C6=0,0,C11/C6)</f>
+        <v/>
+      </c>
+      <c r="D12" s="52">
+        <f>IF(D6=0,0,D11/D6)</f>
+        <v/>
+      </c>
+      <c r="E12" s="52">
+        <f>IF(E6=0,0,E11/E6)</f>
+        <v/>
+      </c>
+      <c r="F12" s="52">
+        <f>IF(F6=0,0,F11/F6)</f>
+        <v/>
+      </c>
+      <c r="G12" s="52">
+        <f>IF(G6=0,0,G11/G6)</f>
+        <v/>
+      </c>
+      <c r="H12" s="52">
+        <f>IF(H6=0,0,H11/H6)</f>
+        <v/>
+      </c>
+      <c r="I12" s="52">
+        <f>IF(I6=0,0,I11/I6)</f>
+        <v/>
+      </c>
+      <c r="J12" s="52">
+        <f>IF(J6=0,0,J11/J6)</f>
+        <v/>
+      </c>
+      <c r="K12" s="52">
+        <f>IF(K6=0,0,K11/K6)</f>
+        <v/>
+      </c>
+      <c r="L12" s="52">
+        <f>IF(L6=0,0,L11/L6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>CAC payback</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="C13" s="56">
+        <f>IF(C10&lt;=0,0,12*C6/C10)</f>
+        <v/>
+      </c>
+      <c r="D13" s="56">
+        <f>IF(D10&lt;=0,0,12*D6/D10)</f>
+        <v/>
+      </c>
+      <c r="E13" s="56">
+        <f>IF(E10&lt;=0,0,12*E6/E10)</f>
+        <v/>
+      </c>
+      <c r="F13" s="56">
+        <f>IF(F10&lt;=0,0,12*F6/F10)</f>
+        <v/>
+      </c>
+      <c r="G13" s="56">
+        <f>IF(G10&lt;=0,0,12*G6/G10)</f>
+        <v/>
+      </c>
+      <c r="H13" s="56">
+        <f>IF(H10&lt;=0,0,12*H6/H10)</f>
+        <v/>
+      </c>
+      <c r="I13" s="56">
+        <f>IF(I10&lt;=0,0,12*I6/I10)</f>
+        <v/>
+      </c>
+      <c r="J13" s="56">
+        <f>IF(J10&lt;=0,0,12*J6/J10)</f>
+        <v/>
+      </c>
+      <c r="K13" s="56">
+        <f>IF(K10&lt;=0,0,12*K6/K10)</f>
+        <v/>
+      </c>
+      <c r="L13" s="56">
+        <f>IF(L10&lt;=0,0,12*L6/L10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="54" t="inlineStr">
+        <is>
+          <t>The athlete LTV/CAC ratio is unusually high, and that is the thesis rather than an error: acquisition is cheap precisely because there is no incumbent agent to outbid in these sports. It should be read alongside the fan LTV below, which is small — the economics work on volume of athletes, not on the value of any one of them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>FAN — NICHE, THE SEGMENT THE PLAN STARTS IN</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="12" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Fan ARPU, VAT inclusive</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>EUR/mo</t>
+        </is>
+      </c>
+      <c r="C19" s="29">
+        <f>Assumptions!C12</f>
+        <v/>
+      </c>
+      <c r="D19" s="29">
+        <f>Assumptions!D12</f>
+        <v/>
+      </c>
+      <c r="E19" s="29">
+        <f>Assumptions!E12</f>
+        <v/>
+      </c>
+      <c r="F19" s="29">
+        <f>Assumptions!F12</f>
+        <v/>
+      </c>
+      <c r="G19" s="29">
+        <f>Assumptions!G12</f>
+        <v/>
+      </c>
+      <c r="H19" s="29">
+        <f>Assumptions!H12</f>
+        <v/>
+      </c>
+      <c r="I19" s="29">
+        <f>Assumptions!I12</f>
+        <v/>
+      </c>
+      <c r="J19" s="29">
+        <f>Assumptions!J12</f>
+        <v/>
+      </c>
+      <c r="K19" s="29">
+        <f>Assumptions!K12</f>
+        <v/>
+      </c>
+      <c r="L19" s="29">
+        <f>Assumptions!L12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Net of VAT</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>EUR/mo</t>
+        </is>
+      </c>
+      <c r="C20" s="29">
+        <f>C19/(1+Assumptions!C42)</f>
+        <v/>
+      </c>
+      <c r="D20" s="29">
+        <f>D19/(1+Assumptions!D42)</f>
+        <v/>
+      </c>
+      <c r="E20" s="29">
+        <f>E19/(1+Assumptions!E42)</f>
+        <v/>
+      </c>
+      <c r="F20" s="29">
+        <f>F19/(1+Assumptions!F42)</f>
+        <v/>
+      </c>
+      <c r="G20" s="29">
+        <f>G19/(1+Assumptions!G42)</f>
+        <v/>
+      </c>
+      <c r="H20" s="29">
+        <f>H19/(1+Assumptions!H42)</f>
+        <v/>
+      </c>
+      <c r="I20" s="29">
+        <f>I19/(1+Assumptions!I42)</f>
+        <v/>
+      </c>
+      <c r="J20" s="29">
+        <f>J19/(1+Assumptions!J42)</f>
+        <v/>
+      </c>
+      <c r="K20" s="29">
+        <f>K19/(1+Assumptions!K42)</f>
+        <v/>
+      </c>
+      <c r="L20" s="29">
+        <f>L19/(1+Assumptions!L42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Our take</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>EUR/mo</t>
+        </is>
+      </c>
+      <c r="C21" s="29">
+        <f>C20*Assumptions!C40</f>
+        <v/>
+      </c>
+      <c r="D21" s="29">
+        <f>D20*Assumptions!D40</f>
+        <v/>
+      </c>
+      <c r="E21" s="29">
+        <f>E20*Assumptions!E40</f>
+        <v/>
+      </c>
+      <c r="F21" s="29">
+        <f>F20*Assumptions!F40</f>
+        <v/>
+      </c>
+      <c r="G21" s="29">
+        <f>G20*Assumptions!G40</f>
+        <v/>
+      </c>
+      <c r="H21" s="29">
+        <f>H20*Assumptions!H40</f>
+        <v/>
+      </c>
+      <c r="I21" s="29">
+        <f>I20*Assumptions!I40</f>
+        <v/>
+      </c>
+      <c r="J21" s="29">
+        <f>J20*Assumptions!J40</f>
+        <v/>
+      </c>
+      <c r="K21" s="29">
+        <f>K20*Assumptions!K40</f>
+        <v/>
+      </c>
+      <c r="L21" s="29">
+        <f>L20*Assumptions!L40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Payment cost on the charge</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>EUR/mo</t>
+        </is>
+      </c>
+      <c r="C22" s="29">
+        <f>C19*Assumptions!C44+Assumptions!C45</f>
+        <v/>
+      </c>
+      <c r="D22" s="29">
+        <f>D19*Assumptions!D44+Assumptions!D45</f>
+        <v/>
+      </c>
+      <c r="E22" s="29">
+        <f>E19*Assumptions!E44+Assumptions!E45</f>
+        <v/>
+      </c>
+      <c r="F22" s="29">
+        <f>F19*Assumptions!F44+Assumptions!F45</f>
+        <v/>
+      </c>
+      <c r="G22" s="29">
+        <f>G19*Assumptions!G44+Assumptions!G45</f>
+        <v/>
+      </c>
+      <c r="H22" s="29">
+        <f>H19*Assumptions!H44+Assumptions!H45</f>
+        <v/>
+      </c>
+      <c r="I22" s="29">
+        <f>I19*Assumptions!I44+Assumptions!I45</f>
+        <v/>
+      </c>
+      <c r="J22" s="29">
+        <f>J19*Assumptions!J44+Assumptions!J45</f>
+        <v/>
+      </c>
+      <c r="K22" s="29">
+        <f>K19*Assumptions!K44+Assumptions!K45</f>
+        <v/>
+      </c>
+      <c r="L22" s="29">
+        <f>L19*Assumptions!L44+Assumptions!L45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Contribution per fan month</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C23" s="57">
+        <f>C21-C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="57">
+        <f>D21-D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="57">
+        <f>E21-E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="57">
+        <f>F21-F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="57">
+        <f>G21-G22</f>
+        <v/>
+      </c>
+      <c r="H23" s="57">
+        <f>H21-H22</f>
+        <v/>
+      </c>
+      <c r="I23" s="57">
+        <f>I21-I22</f>
+        <v/>
+      </c>
+      <c r="J23" s="57">
+        <f>J21-J22</f>
+        <v/>
+      </c>
+      <c r="K23" s="57">
+        <f>K21-K22</f>
+        <v/>
+      </c>
+      <c r="L23" s="57">
+        <f>L21-L22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Fan churn</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>per month</t>
+        </is>
+      </c>
+      <c r="C24" s="23">
+        <f>Assumptions!C13</f>
+        <v/>
+      </c>
+      <c r="D24" s="23">
+        <f>Assumptions!D13</f>
+        <v/>
+      </c>
+      <c r="E24" s="23">
+        <f>Assumptions!E13</f>
+        <v/>
+      </c>
+      <c r="F24" s="23">
+        <f>Assumptions!F13</f>
+        <v/>
+      </c>
+      <c r="G24" s="23">
+        <f>Assumptions!G13</f>
+        <v/>
+      </c>
+      <c r="H24" s="23">
+        <f>Assumptions!H13</f>
+        <v/>
+      </c>
+      <c r="I24" s="23">
+        <f>Assumptions!I13</f>
+        <v/>
+      </c>
+      <c r="J24" s="23">
+        <f>Assumptions!J13</f>
+        <v/>
+      </c>
+      <c r="K24" s="23">
+        <f>Assumptions!K13</f>
+        <v/>
+      </c>
+      <c r="L24" s="23">
+        <f>Assumptions!L13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Expected fan life</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="C25" s="56">
+        <f>IF(C24=0,0,1/C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="56">
+        <f>IF(D24=0,0,1/D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="56">
+        <f>IF(E24=0,0,1/E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="56">
+        <f>IF(F24=0,0,1/F24)</f>
+        <v/>
+      </c>
+      <c r="G25" s="56">
+        <f>IF(G24=0,0,1/G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="56">
+        <f>IF(H24=0,0,1/H24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="56">
+        <f>IF(I24=0,0,1/I24)</f>
+        <v/>
+      </c>
+      <c r="J25" s="56">
+        <f>IF(J24=0,0,1/J24)</f>
+        <v/>
+      </c>
+      <c r="K25" s="56">
+        <f>IF(K24=0,0,1/K24)</f>
+        <v/>
+      </c>
+      <c r="L25" s="56">
+        <f>IF(L24=0,0,1/L24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>FAN LTV</t>
+        </is>
+      </c>
+      <c r="B26" s="40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C26" s="58">
+        <f>C23*C25</f>
+        <v/>
+      </c>
+      <c r="D26" s="58">
+        <f>D23*D25</f>
+        <v/>
+      </c>
+      <c r="E26" s="58">
+        <f>E23*E25</f>
+        <v/>
+      </c>
+      <c r="F26" s="58">
+        <f>F23*F25</f>
+        <v/>
+      </c>
+      <c r="G26" s="58">
+        <f>G23*G25</f>
+        <v/>
+      </c>
+      <c r="H26" s="58">
+        <f>H23*H25</f>
+        <v/>
+      </c>
+      <c r="I26" s="58">
+        <f>I23*I25</f>
+        <v/>
+      </c>
+      <c r="J26" s="58">
+        <f>J23*J25</f>
+        <v/>
+      </c>
+      <c r="K26" s="58">
+        <f>K23*K25</f>
+        <v/>
+      </c>
+      <c r="L26" s="58">
+        <f>L23*L25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Fan CAC</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="54" t="inlineStr">
+        <is>
+          <t>Fan CAC is zero by construction: athletes bring their own audiences and the model spends nothing acquiring fans. That understates the risk rather than flattering the return, and the plan discloses it as such.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>SPONSOR</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>Sponsor CAC</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C32" s="30">
+        <f>Assumptions!C37</f>
+        <v/>
+      </c>
+      <c r="D32" s="30">
+        <f>Assumptions!D37</f>
+        <v/>
+      </c>
+      <c r="E32" s="30">
+        <f>Assumptions!E37</f>
+        <v/>
+      </c>
+      <c r="F32" s="30">
+        <f>Assumptions!F37</f>
+        <v/>
+      </c>
+      <c r="G32" s="30">
+        <f>Assumptions!G37</f>
+        <v/>
+      </c>
+      <c r="H32" s="30">
+        <f>Assumptions!H37</f>
+        <v/>
+      </c>
+      <c r="I32" s="30">
+        <f>Assumptions!I37</f>
+        <v/>
+      </c>
+      <c r="J32" s="30">
+        <f>Assumptions!J37</f>
+        <v/>
+      </c>
+      <c r="K32" s="30">
+        <f>Assumptions!K37</f>
+        <v/>
+      </c>
+      <c r="L32" s="30">
+        <f>Assumptions!L37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>SaaS per paying sponsor</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>EUR/yr</t>
+        </is>
+      </c>
+      <c r="C33" s="30">
+        <f>Assumptions!C36*12</f>
+        <v/>
+      </c>
+      <c r="D33" s="30">
+        <f>Assumptions!D36*12</f>
+        <v/>
+      </c>
+      <c r="E33" s="30">
+        <f>Assumptions!E36*12</f>
+        <v/>
+      </c>
+      <c r="F33" s="30">
+        <f>Assumptions!F36*12</f>
+        <v/>
+      </c>
+      <c r="G33" s="30">
+        <f>Assumptions!G36*12</f>
+        <v/>
+      </c>
+      <c r="H33" s="30">
+        <f>Assumptions!H36*12</f>
+        <v/>
+      </c>
+      <c r="I33" s="30">
+        <f>Assumptions!I36*12</f>
+        <v/>
+      </c>
+      <c r="J33" s="30">
+        <f>Assumptions!J36*12</f>
+        <v/>
+      </c>
+      <c r="K33" s="30">
+        <f>Assumptions!K36*12</f>
+        <v/>
+      </c>
+      <c r="L33" s="30">
+        <f>Assumptions!L36*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Sponsorship take per paying sponsor</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>EUR/yr</t>
+        </is>
+      </c>
+      <c r="C34" s="30">
+        <f>IF(Drivers!C48=0,0,Revenue!C20/Drivers!C48)</f>
+        <v/>
+      </c>
+      <c r="D34" s="30">
+        <f>IF(Drivers!D48=0,0,Revenue!D20/Drivers!D48)</f>
+        <v/>
+      </c>
+      <c r="E34" s="30">
+        <f>IF(Drivers!E48=0,0,Revenue!E20/Drivers!E48)</f>
+        <v/>
+      </c>
+      <c r="F34" s="30">
+        <f>IF(Drivers!F48=0,0,Revenue!F20/Drivers!F48)</f>
+        <v/>
+      </c>
+      <c r="G34" s="30">
+        <f>IF(Drivers!G48=0,0,Revenue!G20/Drivers!G48)</f>
+        <v/>
+      </c>
+      <c r="H34" s="30">
+        <f>IF(Drivers!H48=0,0,Revenue!H20/Drivers!H48)</f>
+        <v/>
+      </c>
+      <c r="I34" s="30">
+        <f>IF(Drivers!I48=0,0,Revenue!I20/Drivers!I48)</f>
+        <v/>
+      </c>
+      <c r="J34" s="30">
+        <f>IF(Drivers!J48=0,0,Revenue!J20/Drivers!J48)</f>
+        <v/>
+      </c>
+      <c r="K34" s="30">
+        <f>IF(Drivers!K48=0,0,Revenue!K20/Drivers!K48)</f>
+        <v/>
+      </c>
+      <c r="L34" s="30">
+        <f>IF(Drivers!L48=0,0,Revenue!L20/Drivers!L48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>Contribution per sponsor per year</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C35" s="47">
+        <f>C33+C34</f>
+        <v/>
+      </c>
+      <c r="D35" s="47">
+        <f>D33+D34</f>
+        <v/>
+      </c>
+      <c r="E35" s="47">
+        <f>E33+E34</f>
+        <v/>
+      </c>
+      <c r="F35" s="47">
+        <f>F33+F34</f>
+        <v/>
+      </c>
+      <c r="G35" s="47">
+        <f>G33+G34</f>
+        <v/>
+      </c>
+      <c r="H35" s="47">
+        <f>H33+H34</f>
+        <v/>
+      </c>
+      <c r="I35" s="47">
+        <f>I33+I34</f>
+        <v/>
+      </c>
+      <c r="J35" s="47">
+        <f>J33+J34</f>
+        <v/>
+      </c>
+      <c r="K35" s="47">
+        <f>K33+K34</f>
+        <v/>
+      </c>
+      <c r="L35" s="47">
+        <f>L33+L34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="44" t="inlineStr">
+        <is>
+          <t>CAC payback</t>
+        </is>
+      </c>
+      <c r="B36" s="40" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="C36" s="51">
+        <f>IF(C35&lt;=0,0,12*C32/C35)</f>
+        <v/>
+      </c>
+      <c r="D36" s="51">
+        <f>IF(D35&lt;=0,0,12*D32/D35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="51">
+        <f>IF(E35&lt;=0,0,12*E32/E35)</f>
+        <v/>
+      </c>
+      <c r="F36" s="51">
+        <f>IF(F35&lt;=0,0,12*F32/F35)</f>
+        <v/>
+      </c>
+      <c r="G36" s="51">
+        <f>IF(G35&lt;=0,0,12*G32/G35)</f>
+        <v/>
+      </c>
+      <c r="H36" s="51">
+        <f>IF(H35&lt;=0,0,12*H32/H35)</f>
+        <v/>
+      </c>
+      <c r="I36" s="51">
+        <f>IF(I35&lt;=0,0,12*I32/I35)</f>
+        <v/>
+      </c>
+      <c r="J36" s="51">
+        <f>IF(J35&lt;=0,0,12*J32/J35)</f>
+        <v/>
+      </c>
+      <c r="K36" s="51">
+        <f>IF(K35&lt;=0,0,12*K32/K35)</f>
+        <v/>
+      </c>
+      <c r="L36" s="51">
+        <f>IF(L35&lt;=0,0,12*L32/L35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="54" t="inlineStr">
+        <is>
+          <t>No sponsor LTV is shown. It needs a sponsor retention assumption the model does not make, and inventing one here would create a figure nothing else in the plan validates. Payback needs no such assumption, so payback is what is reported.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="I2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KPIs — the dozen numbers that describe the business</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Input — change me</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Sourced fact</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Formula (this sheet)</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Formula (other sheet)</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Y7</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Y8</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Y9</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Y10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>SCALE</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="12" t="n"/>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="12" t="n"/>
+      <c r="L4" s="12" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Active athletes</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C5" s="17">
+        <f>Drivers!C5</f>
+        <v/>
+      </c>
+      <c r="D5" s="17">
+        <f>Drivers!D5</f>
+        <v/>
+      </c>
+      <c r="E5" s="17">
+        <f>Drivers!E5</f>
+        <v/>
+      </c>
+      <c r="F5" s="17">
+        <f>Drivers!F5</f>
+        <v/>
+      </c>
+      <c r="G5" s="17">
+        <f>Drivers!G5</f>
+        <v/>
+      </c>
+      <c r="H5" s="17">
+        <f>Drivers!H5</f>
+        <v/>
+      </c>
+      <c r="I5" s="17">
+        <f>Drivers!I5</f>
+        <v/>
+      </c>
+      <c r="J5" s="17">
+        <f>Drivers!J5</f>
+        <v/>
+      </c>
+      <c r="K5" s="17">
+        <f>Drivers!K5</f>
+        <v/>
+      </c>
+      <c r="L5" s="17">
+        <f>Drivers!L5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Paying fans, year end</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C6" s="17">
+        <f>Drivers!C38</f>
+        <v/>
+      </c>
+      <c r="D6" s="17">
+        <f>Drivers!D38</f>
+        <v/>
+      </c>
+      <c r="E6" s="17">
+        <f>Drivers!E38</f>
+        <v/>
+      </c>
+      <c r="F6" s="17">
+        <f>Drivers!F38</f>
+        <v/>
+      </c>
+      <c r="G6" s="17">
+        <f>Drivers!G38</f>
+        <v/>
+      </c>
+      <c r="H6" s="17">
+        <f>Drivers!H38</f>
+        <v/>
+      </c>
+      <c r="I6" s="17">
+        <f>Drivers!I38</f>
+        <v/>
+      </c>
+      <c r="J6" s="17">
+        <f>Drivers!J38</f>
+        <v/>
+      </c>
+      <c r="K6" s="17">
+        <f>Drivers!K38</f>
+        <v/>
+      </c>
+      <c r="L6" s="17">
+        <f>Drivers!L38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Paying sponsors</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C7" s="17">
+        <f>Drivers!C48</f>
+        <v/>
+      </c>
+      <c r="D7" s="17">
+        <f>Drivers!D48</f>
+        <v/>
+      </c>
+      <c r="E7" s="17">
+        <f>Drivers!E48</f>
+        <v/>
+      </c>
+      <c r="F7" s="17">
+        <f>Drivers!F48</f>
+        <v/>
+      </c>
+      <c r="G7" s="17">
+        <f>Drivers!G48</f>
+        <v/>
+      </c>
+      <c r="H7" s="17">
+        <f>Drivers!H48</f>
+        <v/>
+      </c>
+      <c r="I7" s="17">
+        <f>Drivers!I48</f>
+        <v/>
+      </c>
+      <c r="J7" s="17">
+        <f>Drivers!J48</f>
+        <v/>
+      </c>
+      <c r="K7" s="17">
+        <f>Drivers!K48</f>
+        <v/>
+      </c>
+      <c r="L7" s="17">
+        <f>Drivers!L48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Recurring MRR</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>fan subs + SaaS / 12</t>
+        </is>
+      </c>
+      <c r="C8" s="30">
+        <f>(Revenue!C19+Revenue!C21)/12</f>
+        <v/>
+      </c>
+      <c r="D8" s="30">
+        <f>(Revenue!D19+Revenue!D21)/12</f>
+        <v/>
+      </c>
+      <c r="E8" s="30">
+        <f>(Revenue!E19+Revenue!E21)/12</f>
+        <v/>
+      </c>
+      <c r="F8" s="30">
+        <f>(Revenue!F19+Revenue!F21)/12</f>
+        <v/>
+      </c>
+      <c r="G8" s="30">
+        <f>(Revenue!G19+Revenue!G21)/12</f>
+        <v/>
+      </c>
+      <c r="H8" s="30">
+        <f>(Revenue!H19+Revenue!H21)/12</f>
+        <v/>
+      </c>
+      <c r="I8" s="30">
+        <f>(Revenue!I19+Revenue!I21)/12</f>
+        <v/>
+      </c>
+      <c r="J8" s="30">
+        <f>(Revenue!J19+Revenue!J21)/12</f>
+        <v/>
+      </c>
+      <c r="K8" s="30">
+        <f>(Revenue!K19+Revenue!K21)/12</f>
+        <v/>
+      </c>
+      <c r="L8" s="30">
+        <f>(Revenue!L19+Revenue!L21)/12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>QUALITY OF REVENUE</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="12" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Net revenue</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C11" s="30">
+        <f>Revenue!C22</f>
+        <v/>
+      </c>
+      <c r="D11" s="30">
+        <f>Revenue!D22</f>
+        <v/>
+      </c>
+      <c r="E11" s="30">
+        <f>Revenue!E22</f>
+        <v/>
+      </c>
+      <c r="F11" s="30">
+        <f>Revenue!F22</f>
+        <v/>
+      </c>
+      <c r="G11" s="30">
+        <f>Revenue!G22</f>
+        <v/>
+      </c>
+      <c r="H11" s="30">
+        <f>Revenue!H22</f>
+        <v/>
+      </c>
+      <c r="I11" s="30">
+        <f>Revenue!I22</f>
+        <v/>
+      </c>
+      <c r="J11" s="30">
+        <f>Revenue!J22</f>
+        <v/>
+      </c>
+      <c r="K11" s="30">
+        <f>Revenue!K22</f>
+        <v/>
+      </c>
+      <c r="L11" s="30">
+        <f>Revenue!L22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C12" s="23">
+        <f>'P&amp;L'!C7</f>
+        <v/>
+      </c>
+      <c r="D12" s="23">
+        <f>'P&amp;L'!D7</f>
+        <v/>
+      </c>
+      <c r="E12" s="23">
+        <f>'P&amp;L'!E7</f>
+        <v/>
+      </c>
+      <c r="F12" s="23">
+        <f>'P&amp;L'!F7</f>
+        <v/>
+      </c>
+      <c r="G12" s="23">
+        <f>'P&amp;L'!G7</f>
+        <v/>
+      </c>
+      <c r="H12" s="23">
+        <f>'P&amp;L'!H7</f>
+        <v/>
+      </c>
+      <c r="I12" s="23">
+        <f>'P&amp;L'!I7</f>
+        <v/>
+      </c>
+      <c r="J12" s="23">
+        <f>'P&amp;L'!J7</f>
+        <v/>
+      </c>
+      <c r="K12" s="23">
+        <f>'P&amp;L'!K7</f>
+        <v/>
+      </c>
+      <c r="L12" s="23">
+        <f>'P&amp;L'!L7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>EBITDA margin</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C13" s="23">
+        <f>'P&amp;L'!C11</f>
+        <v/>
+      </c>
+      <c r="D13" s="23">
+        <f>'P&amp;L'!D11</f>
+        <v/>
+      </c>
+      <c r="E13" s="23">
+        <f>'P&amp;L'!E11</f>
+        <v/>
+      </c>
+      <c r="F13" s="23">
+        <f>'P&amp;L'!F11</f>
+        <v/>
+      </c>
+      <c r="G13" s="23">
+        <f>'P&amp;L'!G11</f>
+        <v/>
+      </c>
+      <c r="H13" s="23">
+        <f>'P&amp;L'!H11</f>
+        <v/>
+      </c>
+      <c r="I13" s="23">
+        <f>'P&amp;L'!I11</f>
+        <v/>
+      </c>
+      <c r="J13" s="23">
+        <f>'P&amp;L'!J11</f>
+        <v/>
+      </c>
+      <c r="K13" s="23">
+        <f>'P&amp;L'!K11</f>
+        <v/>
+      </c>
+      <c r="L13" s="23">
+        <f>'P&amp;L'!L11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Revenue per FTE</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C14" s="30">
+        <f>IF(Assumptions!C60=0,0,Revenue!C22/Assumptions!C60)</f>
+        <v/>
+      </c>
+      <c r="D14" s="30">
+        <f>IF(Assumptions!D60=0,0,Revenue!D22/Assumptions!D60)</f>
+        <v/>
+      </c>
+      <c r="E14" s="30">
+        <f>IF(Assumptions!E60=0,0,Revenue!E22/Assumptions!E60)</f>
+        <v/>
+      </c>
+      <c r="F14" s="30">
+        <f>IF(Assumptions!F60=0,0,Revenue!F22/Assumptions!F60)</f>
+        <v/>
+      </c>
+      <c r="G14" s="30">
+        <f>IF(Assumptions!G60=0,0,Revenue!G22/Assumptions!G60)</f>
+        <v/>
+      </c>
+      <c r="H14" s="30">
+        <f>IF(Assumptions!H60=0,0,Revenue!H22/Assumptions!H60)</f>
+        <v/>
+      </c>
+      <c r="I14" s="30">
+        <f>IF(Assumptions!I60=0,0,Revenue!I22/Assumptions!I60)</f>
+        <v/>
+      </c>
+      <c r="J14" s="30">
+        <f>IF(Assumptions!J60=0,0,Revenue!J22/Assumptions!J60)</f>
+        <v/>
+      </c>
+      <c r="K14" s="30">
+        <f>IF(Assumptions!K60=0,0,Revenue!K22/Assumptions!K60)</f>
+        <v/>
+      </c>
+      <c r="L14" s="30">
+        <f>IF(Assumptions!L60=0,0,Revenue!L22/Assumptions!L60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>RETENTION AND EFFICIENCY</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Fan churn, niche</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>per month</t>
+        </is>
+      </c>
+      <c r="C17" s="23">
+        <f>Assumptions!C13</f>
+        <v/>
+      </c>
+      <c r="D17" s="23">
+        <f>Assumptions!D13</f>
+        <v/>
+      </c>
+      <c r="E17" s="23">
+        <f>Assumptions!E13</f>
+        <v/>
+      </c>
+      <c r="F17" s="23">
+        <f>Assumptions!F13</f>
+        <v/>
+      </c>
+      <c r="G17" s="23">
+        <f>Assumptions!G13</f>
+        <v/>
+      </c>
+      <c r="H17" s="23">
+        <f>Assumptions!H13</f>
+        <v/>
+      </c>
+      <c r="I17" s="23">
+        <f>Assumptions!I13</f>
+        <v/>
+      </c>
+      <c r="J17" s="23">
+        <f>Assumptions!J13</f>
+        <v/>
+      </c>
+      <c r="K17" s="23">
+        <f>Assumptions!K13</f>
+        <v/>
+      </c>
+      <c r="L17" s="23">
+        <f>Assumptions!L13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Athlete churn, niche</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>per year</t>
+        </is>
+      </c>
+      <c r="C18" s="23">
+        <f>Assumptions!C14</f>
+        <v/>
+      </c>
+      <c r="D18" s="23">
+        <f>Assumptions!D14</f>
+        <v/>
+      </c>
+      <c r="E18" s="23">
+        <f>Assumptions!E14</f>
+        <v/>
+      </c>
+      <c r="F18" s="23">
+        <f>Assumptions!F14</f>
+        <v/>
+      </c>
+      <c r="G18" s="23">
+        <f>Assumptions!G14</f>
+        <v/>
+      </c>
+      <c r="H18" s="23">
+        <f>Assumptions!H14</f>
+        <v/>
+      </c>
+      <c r="I18" s="23">
+        <f>Assumptions!I14</f>
+        <v/>
+      </c>
+      <c r="J18" s="23">
+        <f>Assumptions!J14</f>
+        <v/>
+      </c>
+      <c r="K18" s="23">
+        <f>Assumptions!K14</f>
+        <v/>
+      </c>
+      <c r="L18" s="23">
+        <f>Assumptions!L14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Athlete LTV / CAC</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C19" s="31">
+        <f>CAC_CLV!C12</f>
+        <v/>
+      </c>
+      <c r="D19" s="31">
+        <f>CAC_CLV!D12</f>
+        <v/>
+      </c>
+      <c r="E19" s="31">
+        <f>CAC_CLV!E12</f>
+        <v/>
+      </c>
+      <c r="F19" s="31">
+        <f>CAC_CLV!F12</f>
+        <v/>
+      </c>
+      <c r="G19" s="31">
+        <f>CAC_CLV!G12</f>
+        <v/>
+      </c>
+      <c r="H19" s="31">
+        <f>CAC_CLV!H12</f>
+        <v/>
+      </c>
+      <c r="I19" s="31">
+        <f>CAC_CLV!I12</f>
+        <v/>
+      </c>
+      <c r="J19" s="31">
+        <f>CAC_CLV!J12</f>
+        <v/>
+      </c>
+      <c r="K19" s="31">
+        <f>CAC_CLV!K12</f>
+        <v/>
+      </c>
+      <c r="L19" s="31">
+        <f>CAC_CLV!L12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Take rate on GMV</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C20" s="23">
+        <f>Revenue!C24</f>
+        <v/>
+      </c>
+      <c r="D20" s="23">
+        <f>Revenue!D24</f>
+        <v/>
+      </c>
+      <c r="E20" s="23">
+        <f>Revenue!E24</f>
+        <v/>
+      </c>
+      <c r="F20" s="23">
+        <f>Revenue!F24</f>
+        <v/>
+      </c>
+      <c r="G20" s="23">
+        <f>Revenue!G24</f>
+        <v/>
+      </c>
+      <c r="H20" s="23">
+        <f>Revenue!H24</f>
+        <v/>
+      </c>
+      <c r="I20" s="23">
+        <f>Revenue!I24</f>
+        <v/>
+      </c>
+      <c r="J20" s="23">
+        <f>Revenue!J24</f>
+        <v/>
+      </c>
+      <c r="K20" s="23">
+        <f>Revenue!K24</f>
+        <v/>
+      </c>
+      <c r="L20" s="23">
+        <f>Revenue!L24</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="I2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Valuation — DCF, NPV, IRR and exit multiples</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Input — change me</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Sourced fact</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Formula (this sheet)</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Formula (other sheet)</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Y7</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Y8</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Y9</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Y10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C4" s="30">
+        <f>CashFlow!C9</f>
+        <v/>
+      </c>
+      <c r="D4" s="30">
+        <f>CashFlow!D9</f>
+        <v/>
+      </c>
+      <c r="E4" s="30">
+        <f>CashFlow!E9</f>
+        <v/>
+      </c>
+      <c r="F4" s="30">
+        <f>CashFlow!F9</f>
+        <v/>
+      </c>
+      <c r="G4" s="30">
+        <f>CashFlow!G9</f>
+        <v/>
+      </c>
+      <c r="H4" s="30">
+        <f>CashFlow!H9</f>
+        <v/>
+      </c>
+      <c r="I4" s="30">
+        <f>CashFlow!I9</f>
+        <v/>
+      </c>
+      <c r="J4" s="30">
+        <f>CashFlow!J9</f>
+        <v/>
+      </c>
+      <c r="K4" s="30">
+        <f>CashFlow!K9</f>
+        <v/>
+      </c>
+      <c r="L4" s="30">
+        <f>CashFlow!L9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>1/(1+WACC)^t</t>
+        </is>
+      </c>
+      <c r="C5" s="33">
+        <f>1/(1+Assumptions!$C$85)^1</f>
+        <v/>
+      </c>
+      <c r="D5" s="33">
+        <f>1/(1+Assumptions!$C$85)^2</f>
+        <v/>
+      </c>
+      <c r="E5" s="33">
+        <f>1/(1+Assumptions!$C$85)^3</f>
+        <v/>
+      </c>
+      <c r="F5" s="33">
+        <f>1/(1+Assumptions!$C$85)^4</f>
+        <v/>
+      </c>
+      <c r="G5" s="33">
+        <f>1/(1+Assumptions!$C$85)^5</f>
+        <v/>
+      </c>
+      <c r="H5" s="33">
+        <f>1/(1+Assumptions!$C$85)^6</f>
+        <v/>
+      </c>
+      <c r="I5" s="33">
+        <f>1/(1+Assumptions!$C$85)^7</f>
+        <v/>
+      </c>
+      <c r="J5" s="33">
+        <f>1/(1+Assumptions!$C$85)^8</f>
+        <v/>
+      </c>
+      <c r="K5" s="33">
+        <f>1/(1+Assumptions!$C$85)^9</f>
+        <v/>
+      </c>
+      <c r="L5" s="33">
+        <f>1/(1+Assumptions!$C$85)^10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="39" t="inlineStr">
+        <is>
+          <t>Discounted FCF</t>
+        </is>
+      </c>
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C6" s="43">
+        <f>C4*C5</f>
+        <v/>
+      </c>
+      <c r="D6" s="43">
+        <f>D4*D5</f>
+        <v/>
+      </c>
+      <c r="E6" s="43">
+        <f>E4*E5</f>
+        <v/>
+      </c>
+      <c r="F6" s="43">
+        <f>F4*F5</f>
+        <v/>
+      </c>
+      <c r="G6" s="43">
+        <f>G4*G5</f>
+        <v/>
+      </c>
+      <c r="H6" s="43">
+        <f>H4*H5</f>
+        <v/>
+      </c>
+      <c r="I6" s="43">
+        <f>I4*I5</f>
+        <v/>
+      </c>
+      <c r="J6" s="43">
+        <f>J4*J5</f>
+        <v/>
+      </c>
+      <c r="K6" s="43">
+        <f>K4*K5</f>
+        <v/>
+      </c>
+      <c r="L6" s="43">
+        <f>L4*L5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>FCF incl. terminal value</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>for the IRR below</t>
+        </is>
+      </c>
+      <c r="C8" s="47">
+        <f>C4+IF(1=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="47">
+        <f>D4+IF(2=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="E8" s="47">
+        <f>E4+IF(3=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="47">
+        <f>F4+IF(4=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="47">
+        <f>G4+IF(5=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="47">
+        <f>H4+IF(6=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="I8" s="47">
+        <f>I4+IF(7=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="J8" s="47">
+        <f>J4+IF(8=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="47">
+        <f>K4+IF(9=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="L8" s="47">
+        <f>L4+IF(10=10,$C$11,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>PV of explicit forecast</t>
+        </is>
+      </c>
+      <c r="C10" s="59">
+        <f>SUM(C6:L6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Terminal value at Y10</t>
+        </is>
+      </c>
+      <c r="C11" s="59">
+        <f>L4*(1+Assumptions!$C$86)/(Assumptions!$C$85-Assumptions!$C$86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="C12" s="59">
+        <f>C11*L5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ENTERPRISE VALUE (DCF)</t>
+        </is>
+      </c>
+      <c r="C13" s="59">
+        <f>C10+C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>RETURN METRICS</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="12" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>NPV of FCF at WACC</t>
+        </is>
+      </c>
+      <c r="C16" s="59">
+        <f>NPV(Assumptions!$C$85,C4:L4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>IRR of the plan</t>
+        </is>
+      </c>
+      <c r="C17" s="60">
+        <f>IRR(C4:L4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>IRR incl. terminal value</t>
+        </is>
+      </c>
+      <c r="C18" s="60">
+        <f>IRR(C8:L8,0.3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>EXIT MULTIPLE</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Y10 net revenue</t>
+        </is>
+      </c>
+      <c r="C21" s="59">
+        <f>Revenue!L22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Exit value at Y10</t>
+        </is>
+      </c>
+      <c r="C22" s="59">
+        <f>C21*Assumptions!$C$87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Discounted to today</t>
+        </is>
+      </c>
+      <c r="C23" s="59">
+        <f>C22*L5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>SENSITIVITY — enterprise value by WACC and terminal growth</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Terminal growth \ WACC</t>
+        </is>
+      </c>
+      <c r="C26" s="61" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D26" s="61" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E26" s="61" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F26" s="61" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G26" s="61" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H26" s="61" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C27" s="62">
+        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.01)/(0.18-0.01)/(1+0.18)^10</f>
+        <v/>
+      </c>
+      <c r="D27" s="62">
+        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.01)/(0.2-0.01)/(1+0.2)^10</f>
+        <v/>
+      </c>
+      <c r="E27" s="62">
+        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.01)/(0.22-0.01)/(1+0.22)^10</f>
+        <v/>
+      </c>
+      <c r="F27" s="62">
+        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.01)/(0.25-0.01)/(1+0.25)^10</f>
+        <v/>
+      </c>
+      <c r="G27" s="62">
+        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.01)/(0.28-0.01)/(1+0.28)^10</f>
+        <v/>
+      </c>
+      <c r="H27" s="62">
+        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.01)/(0.3-0.01)/(1+0.3)^10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="60" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C28" s="62">
+        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.02)/(0.18-0.02)/(1+0.18)^10</f>
+        <v/>
+      </c>
+      <c r="D28" s="62">
+        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.02)/(0.2-0.02)/(1+0.2)^10</f>
+        <v/>
+      </c>
+      <c r="E28" s="62">
+        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.02)/(0.22-0.02)/(1+0.22)^10</f>
+        <v/>
+      </c>
+      <c r="F28" s="62">
+        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.02)/(0.25-0.02)/(1+0.25)^10</f>
+        <v/>
+      </c>
+      <c r="G28" s="62">
+        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.02)/(0.28-0.02)/(1+0.28)^10</f>
+        <v/>
+      </c>
+      <c r="H28" s="62">
+        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.02)/(0.3-0.02)/(1+0.3)^10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="60" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C29" s="62">
+        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.03)/(0.18-0.03)/(1+0.18)^10</f>
+        <v/>
+      </c>
+      <c r="D29" s="62">
+        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.03)/(0.2-0.03)/(1+0.2)^10</f>
+        <v/>
+      </c>
+      <c r="E29" s="62">
+        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.03)/(0.22-0.03)/(1+0.22)^10</f>
+        <v/>
+      </c>
+      <c r="F29" s="62">
+        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.03)/(0.25-0.03)/(1+0.25)^10</f>
+        <v/>
+      </c>
+      <c r="G29" s="62">
+        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.03)/(0.28-0.03)/(1+0.28)^10</f>
+        <v/>
+      </c>
+      <c r="H29" s="62">
+        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.03)/(0.3-0.03)/(1+0.3)^10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="60" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C30" s="62">
+        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.04)/(0.18-0.04)/(1+0.18)^10</f>
+        <v/>
+      </c>
+      <c r="D30" s="62">
+        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.04)/(0.2-0.04)/(1+0.2)^10</f>
+        <v/>
+      </c>
+      <c r="E30" s="62">
+        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.04)/(0.22-0.04)/(1+0.22)^10</f>
+        <v/>
+      </c>
+      <c r="F30" s="62">
+        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.04)/(0.25-0.04)/(1+0.25)^10</f>
+        <v/>
+      </c>
+      <c r="G30" s="62">
+        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.04)/(0.28-0.04)/(1+0.28)^10</f>
+        <v/>
+      </c>
+      <c r="H30" s="62">
+        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.04)/(0.3-0.04)/(1+0.3)^10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="60" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C31" s="62">
+        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.05)/(0.18-0.05)/(1+0.18)^10</f>
+        <v/>
+      </c>
+      <c r="D31" s="62">
+        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.05)/(0.2-0.05)/(1+0.2)^10</f>
+        <v/>
+      </c>
+      <c r="E31" s="62">
+        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.05)/(0.22-0.05)/(1+0.22)^10</f>
+        <v/>
+      </c>
+      <c r="F31" s="62">
+        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.05)/(0.25-0.05)/(1+0.25)^10</f>
+        <v/>
+      </c>
+      <c r="G31" s="62">
+        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.05)/(0.28-0.05)/(1+0.28)^10</f>
+        <v/>
+      </c>
+      <c r="H31" s="62">
+        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.05)/(0.3-0.05)/(1+0.3)^10</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="I2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2473,676 +5995,676 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="55" t="inlineStr">
+      <c r="A2" s="63" t="inlineStr">
         <is>
           <t>Nothing on this sheet is our estimate. Every figure is published and cited, so it can be refreshed independently of anything we concluded from it. MarketModel derives our assumptions from these numbers; Assumptions then uses what MarketModel produces.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="56" t="inlineStr">
+      <c r="A4" s="64" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="56" t="inlineStr">
+      <c r="B4" s="64" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C4" s="56" t="inlineStr">
+      <c r="C4" s="64" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D4" s="56" t="inlineStr">
+      <c r="D4" s="64" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E4" s="56" t="inlineStr">
+      <c r="E4" s="64" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F4" s="56" t="inlineStr">
+      <c r="F4" s="64" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="57" t="inlineStr">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>Gross payments (GMV)</t>
         </is>
       </c>
-      <c r="B5" s="58" t="n">
+      <c r="B5" s="66" t="n">
         <v>7220000000</v>
       </c>
-      <c r="C5" s="59" t="inlineStr">
+      <c r="C5" s="67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D5" s="59" t="inlineStr">
+      <c r="D5" s="67" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E5" s="59" t="inlineStr">
+      <c r="E5" s="67" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F5" s="59" t="inlineStr">
+      <c r="F5" s="67" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts (Companies House 10354575)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="57" t="inlineStr">
+      <c r="A6" s="65" t="inlineStr">
         <is>
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="B6" s="58" t="n">
+      <c r="B6" s="66" t="n">
         <v>1410000000</v>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="67" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
+      <c r="E6" s="67" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F6" s="59" t="inlineStr">
+      <c r="F6" s="67" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts (Companies House 10354575)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="57" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>Paid to creators</t>
         </is>
       </c>
-      <c r="B7" s="58" t="n">
+      <c r="B7" s="66" t="n">
         <v>5800000000</v>
       </c>
-      <c r="C7" s="59" t="inlineStr">
+      <c r="C7" s="67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D7" s="59" t="inlineStr">
+      <c r="D7" s="67" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E7" s="59" t="inlineStr">
+      <c r="E7" s="67" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F7" s="59" t="inlineStr">
+      <c r="F7" s="67" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts — 80.3% of gross</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="57" t="inlineStr">
+      <c r="A8" s="65" t="inlineStr">
         <is>
           <t>Creator accounts</t>
         </is>
       </c>
-      <c r="B8" s="58" t="n">
+      <c r="B8" s="66" t="n">
         <v>4634000</v>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="67" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="67" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr">
+      <c r="E8" s="67" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F8" s="59" t="inlineStr">
+      <c r="F8" s="67" t="inlineStr">
         <is>
           <t>Variety — +13% YoY</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="57" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>Fan accounts</t>
         </is>
       </c>
-      <c r="B9" s="58" t="n">
+      <c r="B9" s="66" t="n">
         <v>377500000</v>
       </c>
-      <c r="C9" s="59" t="inlineStr">
+      <c r="C9" s="67" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D9" s="59" t="inlineStr">
+      <c r="D9" s="67" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E9" s="59" t="inlineStr">
+      <c r="E9" s="67" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F9" s="59" t="inlineStr">
+      <c r="F9" s="67" t="inlineStr">
         <is>
           <t>Variety — +24% YoY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="57" t="inlineStr">
+      <c r="A10" s="65" t="inlineStr">
         <is>
           <t>Reported average creator earnings</t>
         </is>
       </c>
-      <c r="B10" s="58" t="n">
+      <c r="B10" s="66" t="n">
         <v>131</v>
       </c>
-      <c r="C10" s="59" t="inlineStr">
+      <c r="C10" s="67" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D10" s="59" t="inlineStr">
+      <c r="D10" s="67" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E10" s="59" t="inlineStr">
+      <c r="E10" s="67" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F10" s="59" t="inlineStr">
+      <c r="F10" s="67" t="inlineStr">
         <is>
           <t>Sci-Tech Today / ElectroIQ — after platform fees</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="57" t="inlineStr">
+      <c r="A11" s="65" t="inlineStr">
         <is>
           <t>Revenue concentration</t>
         </is>
       </c>
-      <c r="B11" s="60" t="n">
+      <c r="B11" s="68" t="n">
         <v>0.76</v>
       </c>
-      <c r="C11" s="59" t="inlineStr">
+      <c r="C11" s="67" t="inlineStr">
         <is>
           <t>share to top 0.1%</t>
         </is>
       </c>
-      <c r="D11" s="59" t="inlineStr">
+      <c r="D11" s="67" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E11" s="59" t="inlineStr">
+      <c r="E11" s="67" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F11" s="59" t="inlineStr">
+      <c r="F11" s="67" t="inlineStr">
         <is>
           <t>ElectroIQ — power-law distribution</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="57" t="inlineStr">
+      <c r="A12" s="65" t="inlineStr">
         <is>
           <t>Creators with &gt;=1 paying member</t>
         </is>
       </c>
-      <c r="B12" s="58" t="n">
+      <c r="B12" s="66" t="n">
         <v>286287</v>
       </c>
-      <c r="C12" s="59" t="inlineStr">
+      <c r="C12" s="67" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D12" s="59" t="inlineStr">
+      <c r="D12" s="67" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E12" s="59" t="inlineStr">
+      <c r="E12" s="67" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
       </c>
-      <c r="F12" s="59" t="inlineStr">
+      <c r="F12" s="67" t="inlineStr">
         <is>
           <t>Graphtreon</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="57" t="inlineStr">
+      <c r="A13" s="65" t="inlineStr">
         <is>
           <t>Active creators</t>
         </is>
       </c>
-      <c r="B13" s="58" t="n">
+      <c r="B13" s="66" t="n">
         <v>300000</v>
       </c>
-      <c r="C13" s="59" t="inlineStr">
+      <c r="C13" s="67" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D13" s="59" t="inlineStr">
+      <c r="D13" s="67" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E13" s="59" t="inlineStr">
+      <c r="E13" s="67" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F13" s="59" t="inlineStr">
+      <c r="F13" s="67" t="inlineStr">
         <is>
           <t>Jack Conte, Patreon</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="57" t="inlineStr">
+      <c r="A14" s="65" t="inlineStr">
         <is>
           <t>Active paying members</t>
         </is>
       </c>
-      <c r="B14" s="58" t="n">
+      <c r="B14" s="66" t="n">
         <v>10000000</v>
       </c>
-      <c r="C14" s="59" t="inlineStr">
+      <c r="C14" s="67" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D14" s="59" t="inlineStr">
+      <c r="D14" s="67" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E14" s="59" t="inlineStr">
+      <c r="E14" s="67" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F14" s="59" t="inlineStr">
+      <c r="F14" s="67" t="inlineStr">
         <is>
           <t>Patreon / Backlinko</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="57" t="inlineStr">
+      <c r="A15" s="65" t="inlineStr">
         <is>
           <t>Paid to creators annually</t>
         </is>
       </c>
-      <c r="B15" s="58" t="n">
+      <c r="B15" s="66" t="n">
         <v>2000000000</v>
       </c>
-      <c r="C15" s="59" t="inlineStr">
+      <c r="C15" s="67" t="inlineStr">
         <is>
           <t>USD/year</t>
         </is>
       </c>
-      <c r="D15" s="59" t="inlineStr">
+      <c r="D15" s="67" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E15" s="59" t="inlineStr">
+      <c r="E15" s="67" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F15" s="59" t="inlineStr">
+      <c r="F15" s="67" t="inlineStr">
         <is>
           <t>Patreon / Backlinko</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="57" t="inlineStr">
+      <c r="A16" s="65" t="inlineStr">
         <is>
           <t>Average monthly support per member</t>
         </is>
       </c>
-      <c r="B16" s="60" t="n">
+      <c r="B16" s="68" t="n">
         <v>6.1</v>
       </c>
-      <c r="C16" s="59" t="inlineStr">
+      <c r="C16" s="67" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D16" s="59" t="inlineStr">
+      <c r="D16" s="67" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E16" s="59" t="inlineStr">
+      <c r="E16" s="67" t="inlineStr">
         <is>
           <t>Aug 2024</t>
         </is>
       </c>
-      <c r="F16" s="59" t="inlineStr">
+      <c r="F16" s="67" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report; audit of ~1,200 creators</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="57" t="inlineStr">
+      <c r="A17" s="65" t="inlineStr">
         <is>
           <t>Typical patronage band (low)</t>
         </is>
       </c>
-      <c r="B17" s="60" t="n">
+      <c r="B17" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="C17" s="59" t="inlineStr">
+      <c r="C17" s="67" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D17" s="59" t="inlineStr">
+      <c r="D17" s="67" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E17" s="59" t="inlineStr">
+      <c r="E17" s="67" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F17" s="59" t="inlineStr">
+      <c r="F17" s="67" t="inlineStr">
         <is>
           <t>Creator-economy benchmarks</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="57" t="inlineStr">
+      <c r="A18" s="65" t="inlineStr">
         <is>
           <t>Typical patronage band (high)</t>
         </is>
       </c>
-      <c r="B18" s="60" t="n">
+      <c r="B18" s="68" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="59" t="inlineStr">
+      <c r="C18" s="67" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D18" s="59" t="inlineStr">
+      <c r="D18" s="67" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E18" s="59" t="inlineStr">
+      <c r="E18" s="67" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F18" s="59" t="inlineStr">
+      <c r="F18" s="67" t="inlineStr">
         <is>
           <t>Creator-economy benchmarks</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="57" t="inlineStr">
+      <c r="A19" s="65" t="inlineStr">
         <is>
           <t>Monthly churn (low)</t>
         </is>
       </c>
-      <c r="B19" s="60" t="n">
+      <c r="B19" s="68" t="n">
         <v>0.1</v>
       </c>
-      <c r="C19" s="59" t="inlineStr">
+      <c r="C19" s="67" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D19" s="59" t="inlineStr">
+      <c r="D19" s="67" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E19" s="59" t="inlineStr">
+      <c r="E19" s="67" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F19" s="59" t="inlineStr">
+      <c r="F19" s="67" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="57" t="inlineStr">
+      <c r="A20" s="65" t="inlineStr">
         <is>
           <t>Monthly churn (high)</t>
         </is>
       </c>
-      <c r="B20" s="60" t="n">
+      <c r="B20" s="68" t="n">
         <v>0.15</v>
       </c>
-      <c r="C20" s="59" t="inlineStr">
+      <c r="C20" s="67" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D20" s="59" t="inlineStr">
+      <c r="D20" s="67" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E20" s="59" t="inlineStr">
+      <c r="E20" s="67" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F20" s="59" t="inlineStr">
+      <c r="F20" s="67" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="57" t="inlineStr">
+      <c r="A21" s="65" t="inlineStr">
         <is>
           <t>Annual-plan churn multiplier</t>
         </is>
       </c>
-      <c r="B21" s="60" t="n">
+      <c r="B21" s="68" t="n">
         <v>0.333</v>
       </c>
-      <c r="C21" s="59" t="inlineStr">
+      <c r="C21" s="67" t="inlineStr">
         <is>
           <t>x monthly churn</t>
         </is>
       </c>
-      <c r="D21" s="59" t="inlineStr">
+      <c r="D21" s="67" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E21" s="59" t="inlineStr">
+      <c r="E21" s="67" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F21" s="59" t="inlineStr">
+      <c r="F21" s="67" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report — annual patrons churn at 1/3 the rate</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="57" t="inlineStr">
+      <c r="A22" s="65" t="inlineStr">
         <is>
           <t>Creators with &gt;2,000 patrons</t>
         </is>
       </c>
-      <c r="B22" s="60" t="n">
+      <c r="B22" s="68" t="n">
         <v>0.003</v>
       </c>
-      <c r="C22" s="59" t="inlineStr">
+      <c r="C22" s="67" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D22" s="59" t="inlineStr">
+      <c r="D22" s="67" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E22" s="59" t="inlineStr">
+      <c r="E22" s="67" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F22" s="59" t="inlineStr">
+      <c r="F22" s="67" t="inlineStr">
         <is>
           <t>Graphtreon — power-law distribution</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="57" t="inlineStr">
+      <c r="A23" s="65" t="inlineStr">
         <is>
           <t>Division I athletes in network</t>
         </is>
       </c>
-      <c r="B23" s="58" t="n">
+      <c r="B23" s="66" t="n">
         <v>45000</v>
       </c>
-      <c r="C23" s="59" t="inlineStr">
+      <c r="C23" s="67" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D23" s="59" t="inlineStr">
+      <c r="D23" s="67" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E23" s="59" t="inlineStr">
+      <c r="E23" s="67" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F23" s="59" t="inlineStr">
+      <c r="F23" s="67" t="inlineStr">
         <is>
           <t>Publicis Groupe press release, 19 Aug 2026</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="57" t="inlineStr">
+      <c r="A24" s="65" t="inlineStr">
         <is>
           <t>Power Four universities</t>
         </is>
       </c>
-      <c r="B24" s="58" t="n">
+      <c r="B24" s="66" t="n">
         <v>68</v>
       </c>
-      <c r="C24" s="59" t="inlineStr">
+      <c r="C24" s="67" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D24" s="59" t="inlineStr">
+      <c r="D24" s="67" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E24" s="59" t="inlineStr">
+      <c r="E24" s="67" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F24" s="59" t="inlineStr">
+      <c r="F24" s="67" t="inlineStr">
         <is>
           <t>Publicis Groupe press release</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="57" t="inlineStr">
+      <c r="A25" s="65" t="inlineStr">
         <is>
           <t>Claimed speed-to-market gain</t>
         </is>
       </c>
-      <c r="B25" s="60" t="n">
+      <c r="B25" s="68" t="n">
         <v>0.6</v>
       </c>
-      <c r="C25" s="59" t="inlineStr">
+      <c r="C25" s="67" t="inlineStr">
         <is>
           <t>share faster</t>
         </is>
       </c>
-      <c r="D25" s="59" t="inlineStr">
+      <c r="D25" s="67" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E25" s="59" t="inlineStr">
+      <c r="E25" s="67" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F25" s="59" t="inlineStr">
+      <c r="F25" s="67" t="inlineStr">
         <is>
           <t>Publicis — stated 50-70% vs a traditional agency process</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="61" t="inlineStr">
+      <c r="A27" s="69" t="inlineStr">
         <is>
           <t>TAKE RATES - what each platform costs a creator</t>
         </is>
@@ -3182,16 +6704,16 @@
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="B29" s="62" t="n">
+      <c r="B29" s="70" t="n">
         <v>0.2</v>
       </c>
-      <c r="C29" s="63" t="n">
+      <c r="C29" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="63" t="n">
+      <c r="D29" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="64" t="inlineStr">
+      <c r="F29" s="72" t="inlineStr">
         <is>
           <t>Derived: 1.41bn / 7.22bn = 19.5% (filed accounts)</t>
         </is>
@@ -3203,16 +6725,16 @@
           <t>Fansly</t>
         </is>
       </c>
-      <c r="B30" s="62" t="n">
+      <c r="B30" s="70" t="n">
         <v>0.2</v>
       </c>
-      <c r="C30" s="63" t="n">
+      <c r="C30" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="63" t="n">
+      <c r="D30" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="64" t="inlineStr">
+      <c r="F30" s="72" t="inlineStr">
         <is>
           <t>Not published in terms; widely reported</t>
         </is>
@@ -3224,16 +6746,16 @@
           <t>Fanfix</t>
         </is>
       </c>
-      <c r="B31" s="62" t="n">
+      <c r="B31" s="70" t="n">
         <v>0.2</v>
       </c>
-      <c r="C31" s="63" t="n">
+      <c r="C31" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="63" t="n">
+      <c r="D31" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="64" t="inlineStr">
+      <c r="F31" s="72" t="inlineStr">
         <is>
           <t>Not published in terms; widely reported</t>
         </is>
@@ -3245,16 +6767,16 @@
           <t>Patreon</t>
         </is>
       </c>
-      <c r="B32" s="62" t="n">
+      <c r="B32" s="70" t="n">
         <v>0.1</v>
       </c>
-      <c r="C32" s="63" t="n">
+      <c r="C32" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="63" t="n">
+      <c r="D32" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="64" t="inlineStr">
+      <c r="F32" s="72" t="inlineStr">
         <is>
           <t>Published: 10% all-in, processing included</t>
         </is>
@@ -3266,16 +6788,16 @@
           <t>Passes</t>
         </is>
       </c>
-      <c r="B33" s="62" t="n">
+      <c r="B33" s="70" t="n">
         <v>0.1</v>
       </c>
-      <c r="C33" s="63" t="n">
+      <c r="C33" s="71" t="n">
         <v>0.3</v>
       </c>
-      <c r="D33" s="63" t="n">
+      <c r="D33" s="71" t="n">
         <v>29</v>
       </c>
-      <c r="F33" s="64" t="inlineStr">
+      <c r="F33" s="72" t="inlineStr">
         <is>
           <t>Sacra; Passes rebrand release Apr 2026</t>
         </is>
@@ -3287,23 +6809,23 @@
           <t>Stride (proposed)</t>
         </is>
       </c>
-      <c r="B34" s="62" t="n">
+      <c r="B34" s="70" t="n">
         <v>0.15</v>
       </c>
-      <c r="C34" s="63" t="n">
+      <c r="C34" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="63" t="n">
+      <c r="D34" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="64" t="inlineStr">
+      <c r="F34" s="72" t="inlineStr">
         <is>
           <t>Our decision — see MarketModel</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="61" t="inlineStr">
+      <c r="A36" s="69" t="inlineStr">
         <is>
           <t>INTERMEDIARIES the athlete already pays</t>
         </is>
@@ -3315,13 +6837,13 @@
           <t>Sports agent — endorsement</t>
         </is>
       </c>
-      <c r="B37" s="62" t="n">
+      <c r="B37" s="70" t="n">
         <v>0.1</v>
       </c>
-      <c r="C37" s="62" t="n">
+      <c r="C37" s="70" t="n">
         <v>0.2</v>
       </c>
-      <c r="F37" s="64" t="inlineStr">
+      <c r="F37" s="72" t="inlineStr">
         <is>
           <t>Unregulated; widely reported, no primary source</t>
         </is>
@@ -3333,13 +6855,13 @@
           <t>Sports agent — playing contract</t>
         </is>
       </c>
-      <c r="B38" s="62" t="n">
+      <c r="B38" s="70" t="n">
         <v>0.02</v>
       </c>
-      <c r="C38" s="62" t="n">
+      <c r="C38" s="70" t="n">
         <v>0.05</v>
       </c>
-      <c r="F38" s="64" t="inlineStr">
+      <c r="F38" s="72" t="inlineStr">
         <is>
           <t>NBPA reg. 4.B (Sept 2025); FIFA FFAR art. 15</t>
         </is>
@@ -3351,13 +6873,13 @@
           <t>OnlyFans management agency</t>
         </is>
       </c>
-      <c r="B39" s="62" t="n">
+      <c r="B39" s="70" t="n">
         <v>0.2</v>
       </c>
-      <c r="C39" s="62" t="n">
+      <c r="C39" s="70" t="n">
         <v>0.5</v>
       </c>
-      <c r="F39" s="64" t="inlineStr">
+      <c r="F39" s="72" t="inlineStr">
         <is>
           <t>Aruna Talent rate guide 2026 — on top of the 20%</t>
         </is>
@@ -3371,180 +6893,180 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="65" t="inlineStr">
+      <c r="A43" s="73" t="inlineStr">
         <is>
           <t>OnlyFans FY2024 filed accounts (Fenix International Ltd)</t>
         </is>
       </c>
-      <c r="B43" s="66" t="inlineStr">
+      <c r="B43" s="74" t="inlineStr">
         <is>
           <t>https://find-and-update.company-information.service.gov.uk/company/10354575/filing-history</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="65" t="inlineStr">
+      <c r="A44" s="73" t="inlineStr">
         <is>
           <t>OnlyFans FY2024 as reported</t>
         </is>
       </c>
-      <c r="B44" s="66" t="inlineStr">
+      <c r="B44" s="74" t="inlineStr">
         <is>
           <t>https://variety.com/2025/digital/news/onlyfans-fiscal-2024-revenue-earnings-1236495750/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="65" t="inlineStr">
+      <c r="A45" s="73" t="inlineStr">
         <is>
           <t>Patreon published take rate</t>
         </is>
       </c>
-      <c r="B45" s="66" t="inlineStr">
+      <c r="B45" s="74" t="inlineStr">
         <is>
           <t>https://www.patreon.com/pricing</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="65" t="inlineStr">
+      <c r="A46" s="73" t="inlineStr">
         <is>
           <t>Patreon creators</t>
         </is>
       </c>
-      <c r="B46" s="66" t="inlineStr">
+      <c r="B46" s="74" t="inlineStr">
         <is>
           <t>https://backlinko.com/patreon-users</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="65" t="inlineStr">
+      <c r="A47" s="73" t="inlineStr">
         <is>
           <t>Passes economics</t>
         </is>
       </c>
-      <c r="B47" s="66" t="inlineStr">
+      <c r="B47" s="74" t="inlineStr">
         <is>
           <t>https://sacra.com/c/passes/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="65" t="inlineStr">
+      <c r="A48" s="73" t="inlineStr">
         <is>
           <t>Fanfix creator terms (states no take rate)</t>
         </is>
       </c>
-      <c r="B48" s="66" t="inlineStr">
+      <c r="B48" s="74" t="inlineStr">
         <is>
           <t>https://auth.fanfix.io/creator-terms-of-use</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="65" t="inlineStr">
+      <c r="A49" s="73" t="inlineStr">
         <is>
           <t>Agency commissions</t>
         </is>
       </c>
-      <c r="B49" s="66" t="inlineStr">
+      <c r="B49" s="74" t="inlineStr">
         <is>
           <t>https://arunatalent.com/blog/onlyfans-agency-commission-rates/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="65" t="inlineStr">
+      <c r="A50" s="73" t="inlineStr">
         <is>
           <t>NBPA agent fee cap (amended Sept 2025)</t>
         </is>
       </c>
-      <c r="B50" s="66" t="inlineStr">
+      <c r="B50" s="74" t="inlineStr">
         <is>
           <t>https://imgix.cosmicjs.com/cd844850-97c7-11f0-91fa-d9e1671c2776-NBPA-REGULATIONS-GOVERNING-PLAYER-AGENTS-09-2025.pdf</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="65" t="inlineStr">
+      <c r="A51" s="73" t="inlineStr">
         <is>
           <t>FIFA Football Agent Regulations art. 15</t>
         </is>
       </c>
-      <c r="B51" s="66" t="inlineStr">
+      <c r="B51" s="74" t="inlineStr">
         <is>
           <t>https://digitalhub.fifa.com/m/1e7b741fa0fae779/original/FIFA-Football-Agent-Regulations.pdf</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="65" t="inlineStr">
+      <c r="A52" s="73" t="inlineStr">
         <is>
           <t>CJEU upholds the FIFA fee cap (16 Jul 2026)</t>
         </is>
       </c>
-      <c r="B52" s="66" t="inlineStr">
+      <c r="B52" s="74" t="inlineStr">
         <is>
           <t>https://inside.fifa.com/news/welcomes-court-of-justice-european-union-decision-football-agent-regulations</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="65" t="inlineStr">
+      <c r="A53" s="73" t="inlineStr">
         <is>
           <t>Eurobarometer 525</t>
         </is>
       </c>
-      <c r="B53" s="66" t="inlineStr">
+      <c r="B53" s="74" t="inlineStr">
         <is>
           <t>https://europa.eu/eurobarometer/surveys/detail/2668</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="65" t="inlineStr">
+      <c r="A54" s="73" t="inlineStr">
         <is>
           <t>FIP World Padel Report 2025</t>
         </is>
       </c>
-      <c r="B54" s="66" t="inlineStr">
+      <c r="B54" s="74" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/2025/12/online-the-fip-world-padel-report-2025-a-comprehensive-analysis-of-a-sport-in-constant-growth/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="65" t="inlineStr">
+      <c r="A55" s="73" t="inlineStr">
         <is>
           <t>Stripe EU pricing</t>
         </is>
       </c>
-      <c r="B55" s="66" t="inlineStr">
+      <c r="B55" s="74" t="inlineStr">
         <is>
           <t>https://stripe.com/es/pricing</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="65" t="inlineStr">
+      <c r="A56" s="73" t="inlineStr">
         <is>
           <t>TEKTA launch</t>
         </is>
       </c>
-      <c r="B56" s="66" t="inlineStr">
+      <c r="B56" s="74" t="inlineStr">
         <is>
           <t>https://www.publicisgroupe.com/en/news/press-releases/publicis-sports-and-travis-kelce-s-tekta-join-forces-to-reimagine-the-future-of-nil-marketing</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="65" t="inlineStr">
+      <c r="A57" s="73" t="inlineStr">
         <is>
           <t>Stripe Connect age</t>
         </is>
       </c>
-      <c r="B57" s="66" t="inlineStr">
+      <c r="B57" s="74" t="inlineStr">
         <is>
           <t>https://support.stripe.com/questions/age-requirement-to-create-a-stripe-account</t>
         </is>
@@ -3589,7 +7111,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3612,7 +7134,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="55" t="inlineStr">
+      <c r="A2" s="63" t="inlineStr">
         <is>
           <t>Each block starts from a published figure on Comparables and ends in a number the Assumptions sheet uses. Adjustment factors are blue because they are our judgement; everything else is a formula you can trace.</t>
         </is>
@@ -3670,7 +7192,7 @@
         <f>Comparables!B14</f>
         <v/>
       </c>
-      <c r="D6" s="67" t="inlineStr">
+      <c r="D6" s="75" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -3686,7 +7208,7 @@
         <f>Comparables!B12</f>
         <v/>
       </c>
-      <c r="D7" s="67" t="inlineStr">
+      <c r="D7" s="75" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -3698,11 +7220,11 @@
           <t>Members per paying creator</t>
         </is>
       </c>
-      <c r="B8" s="68">
+      <c r="B8" s="56">
         <f>B6/B7</f>
         <v/>
       </c>
-      <c r="D8" s="67" t="inlineStr">
+      <c r="D8" s="75" t="inlineStr">
         <is>
           <t>The single most useful benchmark we found: it is measured, not modelled.</t>
         </is>
@@ -3718,7 +7240,7 @@
         <f>Comparables!B9/Comparables!B8</f>
         <v/>
       </c>
-      <c r="D9" s="67" t="inlineStr">
+      <c r="D9" s="75" t="inlineStr">
         <is>
           <t>Fan ACCOUNTS, not paying fans - most follow free. Shown as an upper bound only.</t>
         </is>
@@ -3733,7 +7255,7 @@
       <c r="B10" s="24" t="n">
         <v>1.06</v>
       </c>
-      <c r="D10" s="67" t="inlineStr">
+      <c r="D10" s="75" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: +6% on the Patreon benchmark. Sport audiences are smaller but convert better, because the fan usually does the sport themselves.</t>
         </is>
@@ -3748,7 +7270,7 @@
       <c r="B11" s="24" t="n">
         <v>1.37</v>
       </c>
-      <c r="D11" s="67" t="inlineStr">
+      <c r="D11" s="75" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: +37%. Much larger followings, much weaker conversion - more paying fans in absolute terms even though a smaller share converts.</t>
         </is>
@@ -3760,11 +7282,11 @@
           <t>→ Niche fans per athlete, mature</t>
         </is>
       </c>
-      <c r="B12" s="69">
+      <c r="B12" s="76">
         <f>B8*B10</f>
         <v/>
       </c>
-      <c r="D12" s="67" t="inlineStr"/>
+      <c r="D12" s="75" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -3772,11 +7294,11 @@
           <t>→ Popular fans per athlete, mature</t>
         </is>
       </c>
-      <c r="B13" s="69">
+      <c r="B13" s="76">
         <f>B8*B11</f>
         <v/>
       </c>
-      <c r="D13" s="67" t="inlineStr"/>
+      <c r="D13" s="75" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -3797,7 +7319,7 @@
       <c r="B15" s="20" t="n">
         <v>4.99</v>
       </c>
-      <c r="D15" s="67" t="inlineStr"/>
+      <c r="D15" s="75" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
@@ -3808,7 +7330,7 @@
       <c r="B16" s="20" t="n">
         <v>9.99</v>
       </c>
-      <c r="D16" s="67" t="inlineStr"/>
+      <c r="D16" s="75" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
@@ -3819,7 +7341,7 @@
       <c r="B17" s="20" t="n">
         <v>24.99</v>
       </c>
-      <c r="D17" s="67" t="inlineStr"/>
+      <c r="D17" s="75" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
@@ -3830,7 +7352,7 @@
       <c r="B18" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="D18" s="67" t="inlineStr">
+      <c r="D18" s="75" t="inlineStr">
         <is>
           <t>Assumed distribution; replace with the real tier mix after P1.</t>
         </is>
@@ -3845,7 +7367,7 @@
       <c r="B19" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="D19" s="67" t="inlineStr"/>
+      <c r="D19" s="75" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="13" t="inlineStr">
@@ -3856,7 +7378,7 @@
       <c r="B20" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="D20" s="67" t="inlineStr"/>
+      <c r="D20" s="75" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
@@ -3868,7 +7390,7 @@
         <f>B18+B19+B20</f>
         <v/>
       </c>
-      <c r="D21" s="67" t="inlineStr"/>
+      <c r="D21" s="75" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -3876,11 +7398,11 @@
           <t>→ Weighted ARPU per month</t>
         </is>
       </c>
-      <c r="B22" s="70">
+      <c r="B22" s="77">
         <f>B15*B18+B16*B19+B17*B20</f>
         <v/>
       </c>
-      <c r="D22" s="67" t="inlineStr">
+      <c r="D22" s="75" t="inlineStr">
         <is>
           <t>Cross-check: Patreon reports $6.10 average support and a $8-12 typical band. Landing inside that band from an independent tier build is a good sign.</t>
         </is>
@@ -3896,7 +7418,7 @@
         <f>Comparables!B16</f>
         <v/>
       </c>
-      <c r="D23" s="67" t="inlineStr">
+      <c r="D23" s="75" t="inlineStr">
         <is>
           <t>Published average - below our figure because Patreon's long tail includes many $1-3 tiers. Our EUR 9.49 sits inside their $8-12 typical band.</t>
         </is>
@@ -3911,7 +7433,7 @@
       <c r="B24" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="67" t="inlineStr">
+      <c r="D24" s="75" t="inlineStr">
         <is>
           <t>Niche fans buy knowledge and sit at the tier mix above.</t>
         </is>
@@ -3926,7 +7448,7 @@
       <c r="B25" s="24" t="n">
         <v>0.87</v>
       </c>
-      <c r="D25" s="67" t="inlineStr">
+      <c r="D25" s="75" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: -13%. Popular-sport fans skew to the cheapest tier.</t>
         </is>
@@ -3938,11 +7460,11 @@
           <t>→ Niche ARPU, mature</t>
         </is>
       </c>
-      <c r="B26" s="70">
+      <c r="B26" s="77">
         <f>B22*B24</f>
         <v/>
       </c>
-      <c r="D26" s="67" t="inlineStr"/>
+      <c r="D26" s="75" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -3950,11 +7472,11 @@
           <t>→ Popular ARPU, mature</t>
         </is>
       </c>
-      <c r="B27" s="70">
+      <c r="B27" s="77">
         <f>B22*B25</f>
         <v/>
       </c>
-      <c r="D27" s="67" t="inlineStr"/>
+      <c r="D27" s="75" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -3976,7 +7498,7 @@
         <f>Comparables!B19</f>
         <v/>
       </c>
-      <c r="D29" s="67" t="inlineStr"/>
+      <c r="D29" s="75" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="13" t="inlineStr">
@@ -3988,7 +7510,7 @@
         <f>Comparables!B20</f>
         <v/>
       </c>
-      <c r="D30" s="67" t="inlineStr"/>
+      <c r="D30" s="75" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="13" t="inlineStr">
@@ -4000,7 +7522,7 @@
         <f>(B29+B30)/2</f>
         <v/>
       </c>
-      <c r="D31" s="67" t="inlineStr"/>
+      <c r="D31" s="75" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="13" t="inlineStr">
@@ -4012,7 +7534,7 @@
         <f>Comparables!B21</f>
         <v/>
       </c>
-      <c r="D32" s="67" t="inlineStr">
+      <c r="D32" s="75" t="inlineStr">
         <is>
           <t>Patreon: annual patrons churn at one third the monthly rate.</t>
         </is>
@@ -4027,7 +7549,7 @@
       <c r="B33" s="16" t="n">
         <v>0.3</v>
       </c>
-      <c r="D33" s="67" t="inlineStr">
+      <c r="D33" s="75" t="inlineStr">
         <is>
           <t>Our target for the season pass. This is the one lever that improves churn without changing the product.</t>
         </is>
@@ -4043,7 +7565,7 @@
         <f>B31*(1-B33)+B31*B32*B33</f>
         <v/>
       </c>
-      <c r="D34" s="67" t="inlineStr">
+      <c r="D34" s="75" t="inlineStr">
         <is>
           <t>What a Patreon-like platform would see with our annual mix.</t>
         </is>
@@ -4058,7 +7580,7 @@
       <c r="B35" s="24" t="n">
         <v>0.55</v>
       </c>
-      <c r="D35" s="67" t="inlineStr">
+      <c r="D35" s="75" t="inlineStr">
         <is>
           <t>OUR CLAIM, UNTESTED, AND THE MOST OPTIMISTIC JUDGEMENT IN THE MODEL: this says niche fans churn 45% SLOWER than the Patreon benchmark, because training content is habitual and competitive seasons create renewal moments. Nothing yet proves it. If it is wrong and we are merely at benchmark, Y10 revenue falls by roughly EUR 7M.</t>
         </is>
@@ -4073,7 +7595,7 @@
       <c r="B36" s="24" t="n">
         <v>0.85</v>
       </c>
-      <c r="D36" s="67" t="inlineStr">
+      <c r="D36" s="75" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: 15% better than benchmark. Impulse follows after a result, with many free substitutes - but still a sport fan rather than a general creator audience.</t>
         </is>
@@ -4085,11 +7607,11 @@
           <t>→ Niche churn, mature</t>
         </is>
       </c>
-      <c r="B37" s="71">
+      <c r="B37" s="78">
         <f>B34*B35</f>
         <v/>
       </c>
-      <c r="D37" s="67" t="inlineStr"/>
+      <c r="D37" s="75" t="inlineStr"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -4097,11 +7619,11 @@
           <t>→ Popular churn, mature</t>
         </is>
       </c>
-      <c r="B38" s="71">
+      <c r="B38" s="78">
         <f>B34*B36</f>
         <v/>
       </c>
-      <c r="D38" s="67" t="inlineStr"/>
+      <c r="D38" s="75" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -4123,7 +7645,7 @@
         <f>Comparables!B7/Comparables!B8/12</f>
         <v/>
       </c>
-      <c r="D40" s="67" t="inlineStr">
+      <c r="D40" s="75" t="inlineStr">
         <is>
           <t>Includes dormant accounts, so this is a floor.</t>
         </is>
@@ -4139,7 +7661,7 @@
         <f>Comparables!B15/Comparables!B12/12</f>
         <v/>
       </c>
-      <c r="D41" s="67" t="inlineStr">
+      <c r="D41" s="75" t="inlineStr">
         <is>
           <t>Denominator is creators WITH members, so this is a ceiling.</t>
         </is>
@@ -4151,11 +7673,11 @@
           <t>Stride: modelled niche athlete, mature</t>
         </is>
       </c>
-      <c r="B42" s="70">
+      <c r="B42" s="77">
         <f>B12*B22*(1-Assumptions!$C$40)</f>
         <v/>
       </c>
-      <c r="D42" s="67" t="inlineStr">
+      <c r="D42" s="75" t="inlineStr">
         <is>
           <t>Ours sits between the two, which is where a plausible figure should sit.</t>
         </is>
@@ -4171,7 +7693,7 @@
         <f>Comparables!B11</f>
         <v/>
       </c>
-      <c r="D43" s="67" t="inlineStr">
+      <c r="D43" s="75" t="inlineStr">
         <is>
           <t>THE CAVEAT ON EVERY AVERAGE ABOVE: earnings follow a power law. Totals are unaffected, but the median athlete earns far less than the mean. Do not pitch the mean to an athlete.</t>
         </is>
@@ -4196,7 +7718,7 @@
       <c r="B45" s="24" t="n">
         <v>0.92</v>
       </c>
-      <c r="D45" s="67" t="inlineStr">
+      <c r="D45" s="75" t="inlineStr">
         <is>
           <t>Comparables are published in USD; this model is in EUR. Applied to the per-transaction and monthly creator fees below.</t>
         </is>
@@ -4211,7 +7733,7 @@
       <c r="B46" s="20" t="n">
         <v>300</v>
       </c>
-      <c r="D46" s="67" t="inlineStr">
+      <c r="D46" s="75" t="inlineStr">
         <is>
           <t>Change this to see who is cheapest at any revenue level.</t>
         </is>
@@ -4227,7 +7749,7 @@
         <f>B46*(1-Comparables!B29)-B46/Assumptions!$C$48*Comparables!C29*B45-Comparables!D29*B45</f>
         <v/>
       </c>
-      <c r="D47" s="67" t="inlineStr">
+      <c r="D47" s="75" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -4243,7 +7765,7 @@
         <f>B46*(1-Comparables!B32)-B46/Assumptions!$C$48*Comparables!C32*B45-Comparables!D32*B45</f>
         <v/>
       </c>
-      <c r="D48" s="67" t="inlineStr">
+      <c r="D48" s="75" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -4259,7 +7781,7 @@
         <f>B46*(1-Comparables!B33)-B46/Assumptions!$C$48*Comparables!C33*B45-Comparables!D33*B45</f>
         <v/>
       </c>
-      <c r="D49" s="67" t="inlineStr">
+      <c r="D49" s="75" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -4275,7 +7797,7 @@
         <f>B46*(1-Comparables!B34)-B46/Assumptions!$C$48*Comparables!C34*B45-Comparables!D34*B45</f>
         <v/>
       </c>
-      <c r="D50" s="67" t="inlineStr">
+      <c r="D50" s="75" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -4291,7 +7813,7 @@
         <f>Comparables!D33*B45/((Comparables!B34-Comparables!B33)-Comparables!C33*B45/Assumptions!$C$48)</f>
         <v/>
       </c>
-      <c r="D51" s="67" t="inlineStr">
+      <c r="D51" s="75" t="inlineStr">
         <is>
           <t>Below this, our flat 15% pays the athlete more than Passes' 10% plus fees. Our modelled athlete earns far less than this, so the long tail is on our side of the line.</t>
         </is>
@@ -4313,10 +7835,10 @@
           <t>Population, 34 countries in scope</t>
         </is>
       </c>
-      <c r="B53" s="72" t="n">
+      <c r="B53" s="79" t="n">
         <v>2726.2</v>
       </c>
-      <c r="D53" s="67" t="inlineStr">
+      <c r="D53" s="75" t="inlineStr">
         <is>
           <t>Millions. Eurostat / national statistics offices.</t>
         </is>
@@ -4328,10 +7850,10 @@
           <t>Population, Spain</t>
         </is>
       </c>
-      <c r="B54" s="72" t="n">
+      <c r="B54" s="79" t="n">
         <v>48.6</v>
       </c>
-      <c r="D54" s="67" t="inlineStr">
+      <c r="D54" s="75" t="inlineStr">
         <is>
           <t>Millions.</t>
         </is>
@@ -4346,7 +7868,7 @@
       <c r="B55" s="16" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D55" s="67" t="inlineStr">
+      <c r="D55" s="75" t="inlineStr">
         <is>
           <t>Eurobarometer 525 - Spain sits near the EU average of 55% who exercise at all.</t>
         </is>
@@ -4361,7 +7883,7 @@
       <c r="B56" s="16" t="n">
         <v>0.02</v>
       </c>
-      <c r="D56" s="67" t="inlineStr">
+      <c r="D56" s="75" t="inlineStr">
         <is>
           <t>OUR ESTIMATE: competes, posts publicly, has a following worth sponsoring.</t>
         </is>
@@ -4376,7 +7898,7 @@
       <c r="B57" s="16" t="n">
         <v>0.25</v>
       </c>
-      <c r="D57" s="67" t="inlineStr">
+      <c r="D57" s="75" t="inlineStr">
         <is>
           <t>OUR ESTIMATE: would monetise if the tooling existed.</t>
         </is>
@@ -4388,11 +7910,11 @@
           <t>→ Addressable athletes, Spain</t>
         </is>
       </c>
-      <c r="B58" s="73">
+      <c r="B58" s="80">
         <f>B54*1000000*B55*B56*B57</f>
         <v/>
       </c>
-      <c r="D58" s="67" t="inlineStr"/>
+      <c r="D58" s="75" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -4400,11 +7922,11 @@
           <t>→ Addressable athletes, all 34 countries</t>
         </is>
       </c>
-      <c r="B59" s="73">
+      <c r="B59" s="80">
         <f>B53*1000000*0.5*B56*B57</f>
         <v/>
       </c>
-      <c r="D59" s="67" t="inlineStr">
+      <c r="D59" s="75" t="inlineStr">
         <is>
           <t>Using a 50% blended participation rate across the 34 countries.</t>
         </is>
@@ -4420,7 +7942,7 @@
         <f>Assumptions!$L$5</f>
         <v/>
       </c>
-      <c r="D60" s="67" t="inlineStr"/>
+      <c r="D60" s="75" t="inlineStr"/>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -4428,11 +7950,11 @@
           <t>→ Y10 penetration of Spain SAM</t>
         </is>
       </c>
-      <c r="B61" s="71">
+      <c r="B61" s="78">
         <f>Assumptions!$L$5/B58</f>
         <v/>
       </c>
-      <c r="D61" s="67" t="inlineStr"/>
+      <c r="D61" s="75" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -4440,11 +7962,11 @@
           <t>→ Y10 penetration of full TAM</t>
         </is>
       </c>
-      <c r="B62" s="71">
+      <c r="B62" s="78">
         <f>Assumptions!$L$5/B59</f>
         <v/>
       </c>
-      <c r="D62" s="67" t="inlineStr">
+      <c r="D62" s="75" t="inlineStr">
         <is>
           <t>If this reads as implausibly high, the athlete trajectory is too aggressive - that is exactly what this block exists to reveal.</t>
         </is>
@@ -4462,7 +7984,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4488,44 +8010,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="55" t="inlineStr">
+      <c r="A2" s="63" t="inlineStr">
         <is>
           <t>SOURCED = published figure | BENCHMARKED = set against named comparables | DERIVED = computed from other assumptions | ESTIMATE = judgement, no benchmark yet</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="74" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B4" s="74" t="inlineStr">
+      <c r="B4" s="81" t="inlineStr">
         <is>
           <t>Model value</t>
         </is>
       </c>
-      <c r="C4" s="74" t="inlineStr">
+      <c r="C4" s="81" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="D4" s="74" t="inlineStr">
+      <c r="D4" s="81" t="inlineStr">
         <is>
           <t>Benchmark / comparable</t>
         </is>
       </c>
-      <c r="E4" s="74" t="inlineStr">
+      <c r="E4" s="81" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F4" s="74" t="inlineStr">
+      <c r="F4" s="81" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="G4" s="74" t="inlineStr">
+      <c r="G4" s="81" t="inlineStr">
         <is>
           <t>What would replace the estimate</t>
         </is>
@@ -4545,7 +8067,7 @@
       <c r="G5" s="12" t="n"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="75" t="inlineStr">
+      <c r="A6" s="82" t="inlineStr">
         <is>
           <t>Take rate on fan revenue</t>
         </is>
@@ -4554,34 +8076,34 @@
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
-      <c r="C6" s="76" t="inlineStr">
+      <c r="C6" s="83" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D6" s="77" t="inlineStr">
+      <c r="D6" s="84" t="inlineStr">
         <is>
           <t>Passes charges 10% but adds $0.30/txn and a $29/month creator fee; OnlyFans, Fansly and Fanfix are all 20%; Patreon 8-12%. A flat 15% with no monthly fee pays an athlete more than Passes for anyone under EUR 1,380/month of fan revenue.</t>
         </is>
       </c>
-      <c r="E6" s="77" t="inlineStr">
+      <c r="E6" s="84" t="inlineStr">
         <is>
           <t>Sacra company profile (Passes); Passes rebrand release, Apr 2026; MEXC platform comparison 2026</t>
         </is>
       </c>
-      <c r="F6" s="78" t="inlineStr">
+      <c r="F6" s="85" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G6" s="77" t="inlineStr">
+      <c r="G6" s="84" t="inlineStr">
         <is>
           <t>Nothing. This is a pricing decision and the comparables are public.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="75" t="inlineStr">
+      <c r="A7" s="82" t="inlineStr">
         <is>
           <t>Take rate on sponsorship</t>
         </is>
@@ -4590,101 +8112,101 @@
         <f>Assumptions!$C$41</f>
         <v/>
       </c>
-      <c r="C7" s="76" t="inlineStr">
+      <c r="C7" s="83" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D7" s="77" t="inlineStr">
+      <c r="D7" s="84" t="inlineStr">
         <is>
           <t>Sports agents take 10-20% of an endorsement and 4-10% of a playing contract. On OnlyFans, management agencies take a further 20-50% on top of the platform's 20%.</t>
         </is>
       </c>
-      <c r="E7" s="77" t="inlineStr">
+      <c r="E7" s="84" t="inlineStr">
         <is>
           <t>Oreate and Sapling agent-commission surveys; Aruna Talent agency rate guide 2026</t>
         </is>
       </c>
-      <c r="F7" s="78" t="inlineStr">
+      <c r="F7" s="85" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G7" s="77" t="inlineStr">
+      <c r="G7" s="84" t="inlineStr">
         <is>
           <t>Observed deal data once the marketplace is running.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="75" t="inlineStr">
+      <c r="A8" s="82" t="inlineStr">
         <is>
           <t>Suggested tiers 4.99 / 9.99 / 24.99</t>
         </is>
       </c>
-      <c r="B8" s="79" t="inlineStr">
+      <c r="B8" s="86" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C8" s="76" t="inlineStr">
+      <c r="C8" s="83" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D8" s="77" t="inlineStr">
+      <c r="D8" s="84" t="inlineStr">
         <is>
           <t>Patreon's typical patronage is quoted at $8-12/month, so the EUR 9.99 anchor sits inside the observed band. EUR 4.99 retains only 54% of our take after payment fees, against 71% at EUR 9.99 — which is why the floor matters more than the take rate.</t>
         </is>
       </c>
-      <c r="E8" s="77" t="inlineStr">
+      <c r="E8" s="84" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report; independent audits of ~1,200 creators</t>
         </is>
       </c>
-      <c r="F8" s="80" t="inlineStr">
+      <c r="F8" s="87" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G8" s="77" t="inlineStr">
+      <c r="G8" s="84" t="inlineStr">
         <is>
           <t>Our own tier mix after P1.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="75" t="inlineStr">
+      <c r="A9" s="82" t="inlineStr">
         <is>
           <t>Season pass / annual billing</t>
         </is>
       </c>
-      <c r="B9" s="79" t="inlineStr">
+      <c r="B9" s="86" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C9" s="81" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D9" s="77" t="inlineStr">
+      <c r="D9" s="84" t="inlineStr">
         <is>
           <t>Patreon reports that annual patrons churn at ONE THIRD the rate of monthly patrons. This is the single strongest piece of evidence in the plan for pushing annual billing.</t>
         </is>
       </c>
-      <c r="E9" s="77" t="inlineStr">
+      <c r="E9" s="84" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
-      <c r="F9" s="78" t="inlineStr">
+      <c r="F9" s="85" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G9" s="77" t="inlineStr">
+      <c r="G9" s="84" t="inlineStr">
         <is>
           <t>Already strong. Confirm on our own cohorts.</t>
         </is>
@@ -4704,7 +8226,7 @@
       <c r="G10" s="12" t="n"/>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="75" t="inlineStr">
+      <c r="A11" s="82" t="inlineStr">
         <is>
           <t>Fan ARPU per month</t>
         </is>
@@ -4713,34 +8235,34 @@
         <f>Assumptions!$C$12</f>
         <v/>
       </c>
-      <c r="C11" s="76" t="inlineStr">
+      <c r="C11" s="83" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D11" s="77" t="inlineStr">
+      <c r="D11" s="84" t="inlineStr">
         <is>
           <t>Patreon's average monthly support rose from $5.40 to $6.10 during 2024, with typical patronage quoted at $8-12. Our EUR 8.00-9.50 sits in the upper-middle of that range.</t>
         </is>
       </c>
-      <c r="E11" s="77" t="inlineStr">
+      <c r="E11" s="84" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
-      <c r="F11" s="80" t="inlineStr">
+      <c r="F11" s="87" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G11" s="77" t="inlineStr">
+      <c r="G11" s="84" t="inlineStr">
         <is>
           <t>Actual ARPU by tier and sport after P1.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="75" t="inlineStr">
+      <c r="A12" s="82" t="inlineStr">
         <is>
           <t>Fan churn per month</t>
         </is>
@@ -4749,34 +8271,34 @@
         <f>Assumptions!$C$13</f>
         <v/>
       </c>
-      <c r="C12" s="82" t="inlineStr">
+      <c r="C12" s="89" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D12" s="77" t="inlineStr">
+      <c r="D12" s="84" t="inlineStr">
         <is>
           <t>OPTIMISTIC AGAINST BENCHMARK. Patreon runs 10-15% monthly. We assume 6-9% (niche) and 9-13% (popular), arguing that training content is habitual and that competitive seasons create natural renewal moments. That argument is currently untested.</t>
         </is>
       </c>
-      <c r="E12" s="77" t="inlineStr">
+      <c r="E12" s="84" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report (10-15%/month)</t>
         </is>
       </c>
-      <c r="F12" s="83" t="inlineStr">
+      <c r="F12" s="90" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G12" s="77" t="inlineStr">
+      <c r="G12" s="84" t="inlineStr">
         <is>
           <t>THE most important number to measure in P1. Three months of real cohorts settles it. Until then the conservative case should be treated as the plan.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="75" t="inlineStr">
+      <c r="A13" s="82" t="inlineStr">
         <is>
           <t>Paying fans per monetising athlete</t>
         </is>
@@ -4785,34 +8307,34 @@
         <f>Assumptions!$C$11</f>
         <v/>
       </c>
-      <c r="C13" s="84" t="inlineStr">
+      <c r="C13" s="91" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D13" s="77" t="inlineStr">
+      <c r="D13" s="84" t="inlineStr">
         <is>
           <t>20 rising to 48 over ten years. Cross-check: Patreon creators average $350/month and our modelled niche athlete at maturity earns about EUR 313/month — closely aligned, which is reassuring for an assumption built bottom-up rather than from a comparable.</t>
         </is>
       </c>
-      <c r="E13" s="77" t="inlineStr">
+      <c r="E13" s="84" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report (creator average $350/month)</t>
         </is>
       </c>
-      <c r="F13" s="80" t="inlineStr">
+      <c r="F13" s="87" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G13" s="77" t="inlineStr">
+      <c r="G13" s="84" t="inlineStr">
         <is>
           <t>Observed fans per athlete, banded by follower count.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="75" t="inlineStr">
+      <c r="A14" s="82" t="inlineStr">
         <is>
           <t>Share of athletes who monetise</t>
         </is>
@@ -4821,64 +8343,64 @@
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="C14" s="82" t="inlineStr">
+      <c r="C14" s="89" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D14" s="77" t="inlineStr">
+      <c r="D14" s="84" t="inlineStr">
         <is>
           <t>28% rising to 50% for niche sports. No direct comparable exists — neither Patreon nor OnlyFans publishes activation rates for creators who sign up but never charge.</t>
         </is>
       </c>
-      <c r="E14" s="77" t="inlineStr">
+      <c r="E14" s="84" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="F14" s="83" t="inlineStr">
+      <c r="F14" s="90" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G14" s="77" t="inlineStr">
+      <c r="G14" s="84" t="inlineStr">
         <is>
           <t>Our own activation funnel, available from P1 onward.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="75" t="inlineStr">
+      <c r="A15" s="82" t="inlineStr">
         <is>
           <t>Fan acquisition capacity</t>
         </is>
       </c>
-      <c r="B15" s="79" t="inlineStr">
+      <c r="B15" s="86" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C15" s="82" t="inlineStr">
+      <c r="C15" s="89" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D15" s="77" t="inlineStr">
+      <c r="D15" s="84" t="inlineStr">
         <is>
           <t>An athlete can recruit 30-69 new paying fans a year depending on segment. This ceiling is what makes churn bite in the model: without it, higher churn perversely RAISED revenue, because the year-end target was reachable at any churn rate.</t>
         </is>
       </c>
-      <c r="E15" s="77" t="inlineStr">
+      <c r="E15" s="84" t="inlineStr">
         <is>
           <t>None — introduced to fix a modelling flaw found by stress testing</t>
         </is>
       </c>
-      <c r="F15" s="83" t="inlineStr">
+      <c r="F15" s="90" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G15" s="77" t="inlineStr">
+      <c r="G15" s="84" t="inlineStr">
         <is>
           <t>Observed gross adds per athlete per year.</t>
         </is>
@@ -4898,7 +8420,7 @@
       <c r="G16" s="12" t="n"/>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="75" t="inlineStr">
+      <c r="A17" s="82" t="inlineStr">
         <is>
           <t>PSP percentage fee</t>
         </is>
@@ -4907,34 +8429,34 @@
         <f>Assumptions!$C$44</f>
         <v/>
       </c>
-      <c r="C17" s="81" t="inlineStr">
+      <c r="C17" s="88" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D17" s="77" t="inlineStr">
+      <c r="D17" s="84" t="inlineStr">
         <is>
           <t>Stripe for a Spanish entity: 1.5% + EUR 0.25 on EEA domestic cards, 2.5% on UK cards, 3.25% on non-EEA. 1.9% is the blend for a mostly-European fan base. CORRECTION: an earlier version of this model used the US headline of 2.9% and overstated the largest cost line in the business by about a third.</t>
         </is>
       </c>
-      <c r="E17" s="77" t="inlineStr">
+      <c r="E17" s="84" t="inlineStr">
         <is>
           <t>Stripe published EU/EEA pricing, 2026</t>
         </is>
       </c>
-      <c r="F17" s="78" t="inlineStr">
+      <c r="F17" s="85" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G17" s="77" t="inlineStr">
+      <c r="G17" s="84" t="inlineStr">
         <is>
           <t>Interchange-plus terms become negotiable above roughly EUR 5M processed.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="75" t="inlineStr">
+      <c r="A18" s="82" t="inlineStr">
         <is>
           <t>PSP fixed fee per transaction</t>
         </is>
@@ -4943,34 +8465,34 @@
         <f>Assumptions!$C$45</f>
         <v/>
       </c>
-      <c r="C18" s="81" t="inlineStr">
+      <c r="C18" s="88" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D18" s="77" t="inlineStr">
+      <c r="D18" s="84" t="inlineStr">
         <is>
           <t>EUR 0.25 per transaction. On a EUR 4.99 tier that single fee is a third of our take, which is why the tier floor and annual billing move more margin than the take rate does.</t>
         </is>
       </c>
-      <c r="E18" s="77" t="inlineStr">
+      <c r="E18" s="84" t="inlineStr">
         <is>
           <t>Stripe published pricing, 2026</t>
         </is>
       </c>
-      <c r="F18" s="78" t="inlineStr">
+      <c r="F18" s="85" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G18" s="77" t="inlineStr">
+      <c r="G18" s="84" t="inlineStr">
         <is>
           <t>Volume renegotiation; annual billing turns twelve fees into one.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="75" t="inlineStr">
+      <c r="A19" s="82" t="inlineStr">
         <is>
           <t>Payout fees</t>
         </is>
@@ -4979,27 +8501,27 @@
         <f>Assumptions!$C$46</f>
         <v/>
       </c>
-      <c r="C19" s="81" t="inlineStr">
+      <c r="C19" s="88" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D19" s="77" t="inlineStr">
+      <c r="D19" s="84" t="inlineStr">
         <is>
           <t>Stripe Connect Express: roughly 0.25% + EUR 0.25 per payout, plus a monthly active-account fee that is not modelled as a separate line.</t>
         </is>
       </c>
-      <c r="E19" s="77" t="inlineStr">
+      <c r="E19" s="84" t="inlineStr">
         <is>
           <t>Stripe Connect pricing, 2026</t>
         </is>
       </c>
-      <c r="F19" s="80" t="inlineStr">
+      <c r="F19" s="87" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G19" s="77" t="inlineStr">
+      <c r="G19" s="84" t="inlineStr">
         <is>
           <t>Actual payout frequency once athletes are onboarded.</t>
         </is>
@@ -5019,118 +8541,118 @@
       <c r="G20" s="12" t="n"/>
     </row>
     <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="75" t="inlineStr">
+      <c r="A21" s="82" t="inlineStr">
         <is>
           <t>Sport participation by country</t>
         </is>
       </c>
-      <c r="B21" s="79" t="inlineStr">
+      <c r="B21" s="86" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C21" s="81" t="inlineStr">
+      <c r="C21" s="88" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D21" s="77" t="inlineStr">
+      <c r="D21" s="84" t="inlineStr">
         <is>
           <t>Eurobarometer 525, share who NEVER exercise: Finland 8%, Sweden 12%, Denmark 20%, Poland 65%, Greece 68%, Portugal 73%, EU-27 average 45%. Six of the 34 countries in the index are measured; the other 28 are estimates placed inside that distribution.</t>
         </is>
       </c>
-      <c r="E21" s="77" t="inlineStr">
+      <c r="E21" s="84" t="inlineStr">
         <is>
           <t>Special Eurobarometer 525, Sport and Physical Activity, September 2022</t>
         </is>
       </c>
-      <c r="F21" s="78" t="inlineStr">
+      <c r="F21" s="85" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G21" s="77" t="inlineStr">
+      <c r="G21" s="84" t="inlineStr">
         <is>
           <t>Federation licence counts — published annually and free (CSD in Spain).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="75" t="inlineStr">
+      <c r="A22" s="82" t="inlineStr">
         <is>
           <t>Padel market size</t>
         </is>
       </c>
-      <c r="B22" s="79" t="inlineStr">
+      <c r="B22" s="86" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C22" s="81" t="inlineStr">
+      <c r="C22" s="88" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D22" s="77" t="inlineStr">
+      <c r="D22" s="84" t="inlineStr">
         <is>
           <t>Spain has ~6.0M active players (12.7% of the population), 109,040 federation licences and 17,300+ courts; globally 35M+ players and 77,000+ courts. This is the clearest case for weighting a sport regionally rather than globally — padel scores 77.7 in Spain and 45.1 worldwide.</t>
         </is>
       </c>
-      <c r="E22" s="77" t="inlineStr">
+      <c r="E22" s="84" t="inlineStr">
         <is>
           <t>FIP World Padel Report 2025</t>
         </is>
       </c>
-      <c r="F22" s="78" t="inlineStr">
+      <c r="F22" s="85" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G22" s="77" t="inlineStr">
+      <c r="G22" s="84" t="inlineStr">
         <is>
           <t>Annual FIP refresh.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="75" t="inlineStr">
+      <c r="A23" s="82" t="inlineStr">
         <is>
           <t>Sports fandom by country</t>
         </is>
       </c>
-      <c r="B23" s="79" t="inlineStr">
+      <c r="B23" s="86" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C23" s="82" t="inlineStr">
+      <c r="C23" s="89" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D23" s="77" t="inlineStr">
+      <c r="D23" s="84" t="inlineStr">
         <is>
           <t>The weakest layer of the sport index, and it drives both the `demand` and `appetite` signals. Commercial audience panels (Nielsen Sports, YouGov) cost more than the entire Y1-Y2 analytics budget.</t>
         </is>
       </c>
-      <c r="E23" s="77" t="inlineStr">
+      <c r="E23" s="84" t="inlineStr">
         <is>
           <t>None — reasoned estimates only</t>
         </is>
       </c>
-      <c r="F23" s="83" t="inlineStr">
+      <c r="F23" s="90" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G23" s="77" t="inlineStr">
+      <c r="G23" s="84" t="inlineStr">
         <is>
           <t>Our own engagement data per sport per country once connectors are live. This is what makes the index self-improving rather than something anyone could copy.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="75" t="inlineStr">
+      <c r="A24" s="82" t="inlineStr">
         <is>
           <t>Athlete count trajectory</t>
         </is>
@@ -5139,27 +8661,27 @@
         <f>Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="C24" s="82" t="inlineStr">
+      <c r="C24" s="89" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D24" s="77" t="inlineStr">
+      <c r="D24" s="84" t="inlineStr">
         <is>
           <t>400 rising to 40,000 over ten years. This is the PLAN, not a benchmark: marketing spend is derived from it at segment CAC, not the other way round. Everything in the model scales off this line.</t>
         </is>
       </c>
-      <c r="E24" s="77" t="inlineStr">
+      <c r="E24" s="84" t="inlineStr">
         <is>
           <t>None — it is a target</t>
         </is>
       </c>
-      <c r="F24" s="83" t="inlineStr">
+      <c r="F24" s="90" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G24" s="77" t="inlineStr">
+      <c r="G24" s="84" t="inlineStr">
         <is>
           <t>The pre-seed gate tests it directly: 400 athletes and EUR 10k MRR.</t>
         </is>
@@ -5179,7 +8701,7 @@
       <c r="G25" s="12" t="n"/>
     </row>
     <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="75" t="inlineStr">
+      <c r="A26" s="82" t="inlineStr">
         <is>
           <t>Athlete CAC</t>
         </is>
@@ -5188,34 +8710,34 @@
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="C26" s="82" t="inlineStr">
+      <c r="C26" s="89" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D26" s="77" t="inlineStr">
+      <c r="D26" s="84" t="inlineStr">
         <is>
           <t>EUR 16-36 for niche, EUR 40-88 for popular. The gap reflects displacing an existing agent relationship versus reaching someone with no representation at all. No published comparable exists for athlete acquisition in this segment.</t>
         </is>
       </c>
-      <c r="E26" s="77" t="inlineStr">
+      <c r="E26" s="84" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="F26" s="83" t="inlineStr">
+      <c r="F26" s="90" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G26" s="77" t="inlineStr">
+      <c r="G26" s="84" t="inlineStr">
         <is>
           <t>Measured CAC by channel from the first federation partnership.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="75" t="inlineStr">
+      <c r="A27" s="82" t="inlineStr">
         <is>
           <t>Admission rate, direct applicants</t>
         </is>
@@ -5224,34 +8746,34 @@
         <f>Assumptions!$C$76</f>
         <v/>
       </c>
-      <c r="C27" s="84" t="inlineStr">
+      <c r="C27" s="91" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D27" s="77" t="inlineStr">
+      <c r="D27" s="84" t="inlineStr">
         <is>
           <t>20% of direct applicants are admitted, 25% go to a human, 40% are refused and 15% never finish the form. Not a judgement: it is the ops-load output of scripts/admission_stress.py run over the admission policy itself, so retuning a threshold moves this figure. The sweep asserts the model and the policy stay in step and fails if they drift.</t>
         </is>
       </c>
-      <c r="E27" s="77" t="inlineStr">
+      <c r="E27" s="84" t="inlineStr">
         <is>
           <t>scripts/admission_stress.py, section 7 — over a modelled applicant mix</t>
         </is>
       </c>
-      <c r="F27" s="80" t="inlineStr">
+      <c r="F27" s="87" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G27" s="77" t="inlineStr">
+      <c r="G27" s="84" t="inlineStr">
         <is>
           <t>Real intake data. The mix the sweep assumes is the soft part, not the arithmetic.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="75" t="inlineStr">
+      <c r="A28" s="82" t="inlineStr">
         <is>
           <t>Admission rate, club-nominated</t>
         </is>
@@ -5260,34 +8782,34 @@
         <f>Assumptions!$C$78</f>
         <v/>
       </c>
-      <c r="C28" s="82" t="inlineStr">
+      <c r="C28" s="89" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D28" s="77" t="inlineStr">
+      <c r="D28" s="84" t="inlineStr">
         <is>
           <t>45% admitted against 20% direct. A verified club's nomination confers a credibility floor of 0.75 x its own legitimacy score, which carries a completed application over the admit line that would otherwise have gone to review. It cannot carry an empty one — no club can supply someone else's date of birth — so the uplift is real but bounded.</t>
         </is>
       </c>
-      <c r="E28" s="77" t="inlineStr">
+      <c r="E28" s="84" t="inlineStr">
         <is>
           <t>None — the mechanism is built and tested, the conversion is not yet measured</t>
         </is>
       </c>
-      <c r="F28" s="83" t="inlineStr">
+      <c r="F28" s="90" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G28" s="77" t="inlineStr">
+      <c r="G28" s="84" t="inlineStr">
         <is>
           <t>The first federation partnership: nominated applicants are tagged, so this is measurable from day one of it.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="75" t="inlineStr">
+      <c r="A29" s="82" t="inlineStr">
         <is>
           <t>Athlete verification cost</t>
         </is>
@@ -5296,34 +8818,34 @@
         <f>Assumptions!$C$81</f>
         <v/>
       </c>
-      <c r="C29" s="84" t="inlineStr">
+      <c r="C29" s="91" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D29" s="77" t="inlineStr">
+      <c r="D29" s="84" t="inlineStr">
         <is>
           <t>Four minutes per manual review, priced at the same loaded salary the People line uses, over 1,700 productive hours. Peaks at EUR 47k and 0.64 reviewer-FTE in Y10, which is the finding rather than the cost: verification is not a money problem at this scale. The reason to automate it is latency — an athlete sitting in the queue is not listed, not matchable and not earning.</t>
         </is>
       </c>
-      <c r="E29" s="77" t="inlineStr">
+      <c r="E29" s="84" t="inlineStr">
         <is>
           <t>Derived from the sweep's review volume and the model's own salary line</t>
         </is>
       </c>
-      <c r="F29" s="80" t="inlineStr">
+      <c r="F29" s="87" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G29" s="77" t="inlineStr">
+      <c r="G29" s="84" t="inlineStr">
         <is>
           <t>Timing real reviews. Four minutes is an estimate of a mechanical task.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="75" t="inlineStr">
+      <c r="A30" s="82" t="inlineStr">
         <is>
           <t>Athlete CAC vs the funnel</t>
         </is>
@@ -5332,34 +8854,34 @@
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="C30" s="82" t="inlineStr">
+      <c r="C30" s="89" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D30" s="77" t="inlineStr">
+      <c r="D30" s="84" t="inlineStr">
         <is>
           <t>Deliberately NOT multiplied by the admission funnel. Segment CAC is defined as the cost of landing one athlete ON the platform, so scaling it by 1/admission-rate would charge the same money twice. The Costs sheet carries a memo line showing what that CAC works out to per application (EUR 3.40 in Y1 rising to EUR 22) — the figure to hold against what a channel actually charges per name reached.</t>
         </is>
       </c>
-      <c r="E30" s="77" t="inlineStr">
+      <c r="E30" s="84" t="inlineStr">
         <is>
           <t>None — this is a definitional choice, made explicit so it is not silently reversed</t>
         </is>
       </c>
-      <c r="F30" s="83" t="inlineStr">
+      <c r="F30" s="90" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G30" s="77" t="inlineStr">
+      <c r="G30" s="84" t="inlineStr">
         <is>
           <t>Channel-level spend against applications, which the funnel now records.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="75" t="inlineStr">
+      <c r="A31" s="82" t="inlineStr">
         <is>
           <t>Loaded salary, Spain</t>
         </is>
@@ -5368,34 +8890,34 @@
         <f>Assumptions!$C$61</f>
         <v/>
       </c>
-      <c r="C31" s="76" t="inlineStr">
+      <c r="C31" s="83" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D31" s="77" t="inlineStr">
+      <c r="D31" s="84" t="inlineStr">
         <is>
           <t>EUR 38k-76k loaded. Spanish employer social security adds roughly 31% on top of gross, so a senior engineer at ~EUR 55k gross costs ~EUR 72k — around half the London equivalent, which is a real argument for being in Spain rather than an accident of geography.</t>
         </is>
       </c>
-      <c r="E31" s="77" t="inlineStr">
+      <c r="E31" s="84" t="inlineStr">
         <is>
           <t>Spanish Seguridad Social employer contribution rates</t>
         </is>
       </c>
-      <c r="F31" s="80" t="inlineStr">
+      <c r="F31" s="87" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G31" s="77" t="inlineStr">
+      <c r="G31" s="84" t="inlineStr">
         <is>
           <t>Actual offers accepted.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="75" t="inlineStr">
+      <c r="A32" s="82" t="inlineStr">
         <is>
           <t>AWS infrastructure</t>
         </is>
@@ -5404,34 +8926,34 @@
         <f>Assumptions!$C$52</f>
         <v/>
       </c>
-      <c r="C32" s="76" t="inlineStr">
+      <c r="C32" s="83" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D32" s="77" t="inlineStr">
+      <c r="D32" s="84" t="inlineStr">
         <is>
           <t>Built up per stage from list prices: Fargate, RDS then Aurora, ElastiCache, S3, MediaConvert, CloudWatch. Reserved capacity and Savings Plans (25-40%) are deliberately excluded and treated as upside.</t>
         </is>
       </c>
-      <c r="E32" s="77" t="inlineStr">
+      <c r="E32" s="84" t="inlineStr">
         <is>
           <t>AWS published list pricing, 2026</t>
         </is>
       </c>
-      <c r="F32" s="80" t="inlineStr">
+      <c r="F32" s="87" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G32" s="77" t="inlineStr">
+      <c r="G32" s="84" t="inlineStr">
         <is>
           <t>Actual bills; commit to Savings Plans once usage is stable.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="75" t="inlineStr">
+      <c r="A33" s="82" t="inlineStr">
         <is>
           <t>Media egress</t>
         </is>
@@ -5440,34 +8962,34 @@
         <f>Assumptions!$C$54</f>
         <v/>
       </c>
-      <c r="C33" s="81" t="inlineStr">
+      <c r="C33" s="88" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D33" s="77" t="inlineStr">
+      <c r="D33" s="84" t="inlineStr">
         <is>
           <t>EUR 0.008/GB behind a zero-egress object store versus EUR 0.075/GB at CloudFront list price. At Y10 volumes that single architectural choice is worth over EUR 1M a year — the largest cost decision in the plan that is settled by engineering rather than negotiation.</t>
         </is>
       </c>
-      <c r="E33" s="77" t="inlineStr">
+      <c r="E33" s="84" t="inlineStr">
         <is>
           <t>Cloudflare R2 and Backblaze B2 pricing; AWS CloudFront list price</t>
         </is>
       </c>
-      <c r="F33" s="78" t="inlineStr">
+      <c r="F33" s="85" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G33" s="77" t="inlineStr">
+      <c r="G33" s="84" t="inlineStr">
         <is>
           <t>Nothing. Both are published.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="75" t="inlineStr">
+      <c r="A34" s="82" t="inlineStr">
         <is>
           <t>Moderation cost</t>
         </is>
@@ -5476,27 +8998,27 @@
         <f>Assumptions!$C$56</f>
         <v/>
       </c>
-      <c r="C34" s="82" t="inlineStr">
+      <c r="C34" s="89" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D34" s="77" t="inlineStr">
+      <c r="D34" s="84" t="inlineStr">
         <is>
           <t>EUR 22 per 1,000 items reviewed, on a hybrid of automated classification and human review. Vendor pricing varies widely with SLA and content type.</t>
         </is>
       </c>
-      <c r="E34" s="77" t="inlineStr">
+      <c r="E34" s="84" t="inlineStr">
         <is>
           <t>None cited</t>
         </is>
       </c>
-      <c r="F34" s="83" t="inlineStr">
+      <c r="F34" s="90" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G34" s="77" t="inlineStr">
+      <c r="G34" s="84" t="inlineStr">
         <is>
           <t>Vendor quotes once P2 scope is fixed.</t>
         </is>
@@ -5516,7 +9038,7 @@
       <c r="G35" s="12" t="n"/>
     </row>
     <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="75" t="inlineStr">
+      <c r="A36" s="82" t="inlineStr">
         <is>
           <t>Corporate tax rates</t>
         </is>
@@ -5525,34 +9047,34 @@
         <f>Assumptions!$C$71</f>
         <v/>
       </c>
-      <c r="C36" s="81" t="inlineStr">
+      <c r="C36" s="88" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D36" s="77" t="inlineStr">
+      <c r="D36" s="84" t="inlineStr">
         <is>
           <t>15% for the first four profitable years under the Spanish Startup Law, then the 25% standard rate. Modelled with loss carryforward against the Y1-Y4 losses.</t>
         </is>
       </c>
-      <c r="E36" s="77" t="inlineStr">
+      <c r="E36" s="84" t="inlineStr">
         <is>
           <t>Ley de Startups (Spain); Impuesto sobre Sociedades</t>
         </is>
       </c>
-      <c r="F36" s="78" t="inlineStr">
+      <c r="F36" s="85" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G36" s="77" t="inlineStr">
+      <c r="G36" s="84" t="inlineStr">
         <is>
           <t>Confirm eligibility with a Spanish tax adviser before filing.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="75" t="inlineStr">
+      <c r="A37" s="82" t="inlineStr">
         <is>
           <t>Risk-free rate</t>
         </is>
@@ -5561,34 +9083,34 @@
         <f>Assumptions!$C$88</f>
         <v/>
       </c>
-      <c r="C37" s="81" t="inlineStr">
+      <c r="C37" s="88" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D37" s="77" t="inlineStr">
+      <c r="D37" s="84" t="inlineStr">
         <is>
           <t>Spanish 10-year sovereign yield, ~3.2% in mid-2026. Used as the floor for the founder opportunity-cost calculation rather than as the discount rate.</t>
         </is>
       </c>
-      <c r="E37" s="77" t="inlineStr">
+      <c r="E37" s="84" t="inlineStr">
         <is>
           <t>Spanish 10Y government bond yield</t>
         </is>
       </c>
-      <c r="F37" s="78" t="inlineStr">
+      <c r="F37" s="85" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G37" s="77" t="inlineStr">
+      <c r="G37" s="84" t="inlineStr">
         <is>
           <t>Refresh at the date of any raise.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
-      <c r="A38" s="75" t="inlineStr">
+      <c r="A38" s="82" t="inlineStr">
         <is>
           <t>WACC / discount rate</t>
         </is>
@@ -5597,34 +9119,34 @@
         <f>Assumptions!$C$85</f>
         <v/>
       </c>
-      <c r="C38" s="76" t="inlineStr">
+      <c r="C38" s="83" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D38" s="77" t="inlineStr">
+      <c r="D38" s="84" t="inlineStr">
         <is>
           <t>25%. The conventional range for pre-revenue to early-revenue venture is 20-35% and we sit mid-range. The sensitivity grid runs 18-30% precisely because this is arguable rather than knowable.</t>
         </is>
       </c>
-      <c r="E38" s="77" t="inlineStr">
+      <c r="E38" s="84" t="inlineStr">
         <is>
           <t>Standard venture valuation practice</t>
         </is>
       </c>
-      <c r="F38" s="80" t="inlineStr">
+      <c r="F38" s="87" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G38" s="77" t="inlineStr">
+      <c r="G38" s="84" t="inlineStr">
         <is>
           <t>An actual term sheet prices this for you.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="75" t="inlineStr">
+      <c r="A39" s="82" t="inlineStr">
         <is>
           <t>Exit revenue multiple</t>
         </is>
@@ -5633,34 +9155,34 @@
         <f>Assumptions!$C$87</f>
         <v/>
       </c>
-      <c r="C39" s="76" t="inlineStr">
+      <c r="C39" s="83" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D39" s="77" t="inlineStr">
+      <c r="D39" s="84" t="inlineStr">
         <is>
           <t>6.5x blended. Marketplace comparables trade around 4x revenue and high-growth SaaS around 9x; our Y10 mix is roughly 55% marketplace take and 12% SaaS.</t>
         </is>
       </c>
-      <c r="E39" s="77" t="inlineStr">
+      <c r="E39" s="84" t="inlineStr">
         <is>
           <t>Public marketplace and SaaS trading multiples</t>
         </is>
       </c>
-      <c r="F39" s="80" t="inlineStr">
+      <c r="F39" s="87" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G39" s="77" t="inlineStr">
+      <c r="G39" s="84" t="inlineStr">
         <is>
           <t>Comparable private transactions nearer an exit.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="75" t="inlineStr">
+      <c r="A40" s="82" t="inlineStr">
         <is>
           <t>Terminal growth</t>
         </is>
@@ -5669,27 +9191,27 @@
         <f>Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="C40" s="76" t="inlineStr">
+      <c r="C40" s="83" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D40" s="77" t="inlineStr">
+      <c r="D40" s="84" t="inlineStr">
         <is>
           <t>3%, approximating long-run nominal GDP. Ten explicit forecast years were chosen partly so this assumption carries less of the valuation than it would at Y7.</t>
         </is>
       </c>
-      <c r="E40" s="77" t="inlineStr">
+      <c r="E40" s="84" t="inlineStr">
         <is>
           <t>Standard DCF convention</t>
         </is>
       </c>
-      <c r="F40" s="80" t="inlineStr">
+      <c r="F40" s="87" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G40" s="77" t="inlineStr">
+      <c r="G40" s="84" t="inlineStr">
         <is>
           <t>Nothing — it is a convention, and the grid shows its effect.</t>
         </is>
@@ -5709,112 +9231,112 @@
       <c r="G41" s="12" t="n"/>
     </row>
     <row r="42" ht="58" customHeight="1">
-      <c r="A42" s="75" t="inlineStr">
+      <c r="A42" s="82" t="inlineStr">
         <is>
           <t>Payout age floor</t>
         </is>
       </c>
-      <c r="B42" s="79" t="inlineStr">
+      <c r="B42" s="86" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C42" s="81" t="inlineStr">
+      <c r="C42" s="88" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D42" s="77" t="inlineStr">
+      <c r="D42" s="84" t="inlineStr">
         <is>
           <t>Stripe Express and Custom Connect require 18. Standard Connect allows 13+, but a legal guardian must own the account and hold the bank account the money lands in.</t>
         </is>
       </c>
-      <c r="E42" s="77" t="inlineStr">
+      <c r="E42" s="84" t="inlineStr">
         <is>
           <t>Stripe Connect documentation</t>
         </is>
       </c>
-      <c r="F42" s="78" t="inlineStr">
+      <c r="F42" s="85" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G42" s="77" t="inlineStr">
+      <c r="G42" s="84" t="inlineStr">
         <is>
           <t>Nothing — it is a hard platform rule.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
-      <c r="A43" s="75" t="inlineStr">
+      <c r="A43" s="82" t="inlineStr">
         <is>
           <t>Digital consent age, Spain</t>
         </is>
       </c>
-      <c r="B43" s="79" t="inlineStr">
+      <c r="B43" s="86" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C43" s="81" t="inlineStr">
+      <c r="C43" s="88" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D43" s="77" t="inlineStr">
+      <c r="D43" s="84" t="inlineStr">
         <is>
           <t>14 today under LOPDGDD Art. 7. A draft Organic Law on the Protection of Minors in Digital Environments would raise it to 16 and make age verification mandatory — which is why 16 is the forward-compatible floor for an account.</t>
         </is>
       </c>
-      <c r="E43" s="77" t="inlineStr">
+      <c r="E43" s="84" t="inlineStr">
         <is>
           <t>LOPDGDD Art. 7; draft Organic Law, Council of Ministers, March 2025</t>
         </is>
       </c>
-      <c r="F43" s="78" t="inlineStr">
+      <c r="F43" s="85" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G43" s="77" t="inlineStr">
+      <c r="G43" s="84" t="inlineStr">
         <is>
           <t>Track the bill through Parliament.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="85" t="inlineStr">
+      <c r="A45" s="92" t="inlineStr">
         <is>
           <t>THE THREE ASSUMPTIONS MOST LIKELY TO BE WRONG</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="86" t="inlineStr">
+      <c r="A46" s="93" t="inlineStr">
         <is>
           <t>1. Fan churn. We assume 6-13%/month; Patreon reports 10-15%. If Patreon is right, Y10 revenue falls from about EUR 58M to EUR 51M and the capital requirement roughly doubles.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="86" t="inlineStr">
+      <c r="A47" s="93" t="inlineStr">
         <is>
           <t>2. Athlete count. The trajectory is a target, not a forecast, and everything scales off it.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="86" t="inlineStr">
+      <c r="A48" s="93" t="inlineStr">
         <is>
           <t>3. Share of athletes who monetise. No published comparable exists at all.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="87" t="inlineStr"/>
+      <c r="A49" s="94" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="87" t="inlineStr">
+      <c r="A50" s="94" t="inlineStr">
         <is>
           <t>All three are answered by the same thing: three months of real cohort data from P1.</t>
         </is>
@@ -5832,7 +9354,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5863,7 +9385,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="55" t="inlineStr">
+      <c r="A2" s="63" t="inlineStr">
         <is>
           <t>Each pair is the Python model's figure and the workbook's own calculation. VARIANCE must be zero — if a formula is wrong, it shows up here on open.</t>
         </is>
@@ -6084,43 +9606,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C7" s="88">
+      <c r="C7" s="95">
         <f>ROUND(C6-C5,0)</f>
         <v/>
       </c>
-      <c r="D7" s="88">
+      <c r="D7" s="95">
         <f>ROUND(D6-D5,0)</f>
         <v/>
       </c>
-      <c r="E7" s="88">
+      <c r="E7" s="95">
         <f>ROUND(E6-E5,0)</f>
         <v/>
       </c>
-      <c r="F7" s="88">
+      <c r="F7" s="95">
         <f>ROUND(F6-F5,0)</f>
         <v/>
       </c>
-      <c r="G7" s="88">
+      <c r="G7" s="95">
         <f>ROUND(G6-G5,0)</f>
         <v/>
       </c>
-      <c r="H7" s="88">
+      <c r="H7" s="95">
         <f>ROUND(H6-H5,0)</f>
         <v/>
       </c>
-      <c r="I7" s="88">
+      <c r="I7" s="95">
         <f>ROUND(I6-I5,0)</f>
         <v/>
       </c>
-      <c r="J7" s="88">
+      <c r="J7" s="95">
         <f>ROUND(J6-J5,0)</f>
         <v/>
       </c>
-      <c r="K7" s="88">
+      <c r="K7" s="95">
         <f>ROUND(K6-K5,0)</f>
         <v/>
       </c>
-      <c r="L7" s="88">
+      <c r="L7" s="95">
         <f>ROUND(L6-L5,0)</f>
         <v/>
       </c>
@@ -6248,43 +9770,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C12" s="88">
+      <c r="C12" s="95">
         <f>ROUND(C11-C10,0)</f>
         <v/>
       </c>
-      <c r="D12" s="88">
+      <c r="D12" s="95">
         <f>ROUND(D11-D10,0)</f>
         <v/>
       </c>
-      <c r="E12" s="88">
+      <c r="E12" s="95">
         <f>ROUND(E11-E10,0)</f>
         <v/>
       </c>
-      <c r="F12" s="88">
+      <c r="F12" s="95">
         <f>ROUND(F11-F10,0)</f>
         <v/>
       </c>
-      <c r="G12" s="88">
+      <c r="G12" s="95">
         <f>ROUND(G11-G10,0)</f>
         <v/>
       </c>
-      <c r="H12" s="88">
+      <c r="H12" s="95">
         <f>ROUND(H11-H10,0)</f>
         <v/>
       </c>
-      <c r="I12" s="88">
+      <c r="I12" s="95">
         <f>ROUND(I11-I10,0)</f>
         <v/>
       </c>
-      <c r="J12" s="88">
+      <c r="J12" s="95">
         <f>ROUND(J11-J10,0)</f>
         <v/>
       </c>
-      <c r="K12" s="88">
+      <c r="K12" s="95">
         <f>ROUND(K11-K10,0)</f>
         <v/>
       </c>
-      <c r="L12" s="88">
+      <c r="L12" s="95">
         <f>ROUND(L11-L10,0)</f>
         <v/>
       </c>
@@ -6412,43 +9934,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C17" s="88">
+      <c r="C17" s="95">
         <f>ROUND(C16-C15,0)</f>
         <v/>
       </c>
-      <c r="D17" s="88">
+      <c r="D17" s="95">
         <f>ROUND(D16-D15,0)</f>
         <v/>
       </c>
-      <c r="E17" s="88">
+      <c r="E17" s="95">
         <f>ROUND(E16-E15,0)</f>
         <v/>
       </c>
-      <c r="F17" s="88">
+      <c r="F17" s="95">
         <f>ROUND(F16-F15,0)</f>
         <v/>
       </c>
-      <c r="G17" s="88">
+      <c r="G17" s="95">
         <f>ROUND(G16-G15,0)</f>
         <v/>
       </c>
-      <c r="H17" s="88">
+      <c r="H17" s="95">
         <f>ROUND(H16-H15,0)</f>
         <v/>
       </c>
-      <c r="I17" s="88">
+      <c r="I17" s="95">
         <f>ROUND(I16-I15,0)</f>
         <v/>
       </c>
-      <c r="J17" s="88">
+      <c r="J17" s="95">
         <f>ROUND(J16-J15,0)</f>
         <v/>
       </c>
-      <c r="K17" s="88">
+      <c r="K17" s="95">
         <f>ROUND(K16-K15,0)</f>
         <v/>
       </c>
-      <c r="L17" s="88">
+      <c r="L17" s="95">
         <f>ROUND(L16-L15,0)</f>
         <v/>
       </c>
@@ -6576,43 +10098,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C22" s="88">
+      <c r="C22" s="95">
         <f>ROUND(C21-C20,0)</f>
         <v/>
       </c>
-      <c r="D22" s="88">
+      <c r="D22" s="95">
         <f>ROUND(D21-D20,0)</f>
         <v/>
       </c>
-      <c r="E22" s="88">
+      <c r="E22" s="95">
         <f>ROUND(E21-E20,0)</f>
         <v/>
       </c>
-      <c r="F22" s="88">
+      <c r="F22" s="95">
         <f>ROUND(F21-F20,0)</f>
         <v/>
       </c>
-      <c r="G22" s="88">
+      <c r="G22" s="95">
         <f>ROUND(G21-G20,0)</f>
         <v/>
       </c>
-      <c r="H22" s="88">
+      <c r="H22" s="95">
         <f>ROUND(H21-H20,0)</f>
         <v/>
       </c>
-      <c r="I22" s="88">
+      <c r="I22" s="95">
         <f>ROUND(I21-I20,0)</f>
         <v/>
       </c>
-      <c r="J22" s="88">
+      <c r="J22" s="95">
         <f>ROUND(J21-J20,0)</f>
         <v/>
       </c>
-      <c r="K22" s="88">
+      <c r="K22" s="95">
         <f>ROUND(K21-K20,0)</f>
         <v/>
       </c>
-      <c r="L22" s="88">
+      <c r="L22" s="95">
         <f>ROUND(L21-L20,0)</f>
         <v/>
       </c>
@@ -6740,43 +10262,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C27" s="88">
+      <c r="C27" s="95">
         <f>ROUND(C26-C25,0)</f>
         <v/>
       </c>
-      <c r="D27" s="88">
+      <c r="D27" s="95">
         <f>ROUND(D26-D25,0)</f>
         <v/>
       </c>
-      <c r="E27" s="88">
+      <c r="E27" s="95">
         <f>ROUND(E26-E25,0)</f>
         <v/>
       </c>
-      <c r="F27" s="88">
+      <c r="F27" s="95">
         <f>ROUND(F26-F25,0)</f>
         <v/>
       </c>
-      <c r="G27" s="88">
+      <c r="G27" s="95">
         <f>ROUND(G26-G25,0)</f>
         <v/>
       </c>
-      <c r="H27" s="88">
+      <c r="H27" s="95">
         <f>ROUND(H26-H25,0)</f>
         <v/>
       </c>
-      <c r="I27" s="88">
+      <c r="I27" s="95">
         <f>ROUND(I26-I25,0)</f>
         <v/>
       </c>
-      <c r="J27" s="88">
+      <c r="J27" s="95">
         <f>ROUND(J26-J25,0)</f>
         <v/>
       </c>
-      <c r="K27" s="88">
+      <c r="K27" s="95">
         <f>ROUND(K26-K25,0)</f>
         <v/>
       </c>
-      <c r="L27" s="88">
+      <c r="L27" s="95">
         <f>ROUND(L26-L25,0)</f>
         <v/>
       </c>
@@ -6904,43 +10426,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C32" s="89">
+      <c r="C32" s="96">
         <f>ROUND(C31-C30,0)</f>
         <v/>
       </c>
-      <c r="D32" s="89">
+      <c r="D32" s="96">
         <f>ROUND(D31-D30,0)</f>
         <v/>
       </c>
-      <c r="E32" s="89">
+      <c r="E32" s="96">
         <f>ROUND(E31-E30,0)</f>
         <v/>
       </c>
-      <c r="F32" s="89">
+      <c r="F32" s="96">
         <f>ROUND(F31-F30,0)</f>
         <v/>
       </c>
-      <c r="G32" s="89">
+      <c r="G32" s="96">
         <f>ROUND(G31-G30,0)</f>
         <v/>
       </c>
-      <c r="H32" s="89">
+      <c r="H32" s="96">
         <f>ROUND(H31-H30,0)</f>
         <v/>
       </c>
-      <c r="I32" s="89">
+      <c r="I32" s="96">
         <f>ROUND(I31-I30,0)</f>
         <v/>
       </c>
-      <c r="J32" s="89">
+      <c r="J32" s="96">
         <f>ROUND(J31-J30,0)</f>
         <v/>
       </c>
-      <c r="K32" s="89">
+      <c r="K32" s="96">
         <f>ROUND(K31-K30,0)</f>
         <v/>
       </c>
-      <c r="L32" s="89">
+      <c r="L32" s="96">
         <f>ROUND(L31-L30,0)</f>
         <v/>
       </c>
@@ -7068,43 +10590,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C37" s="89">
+      <c r="C37" s="96">
         <f>ROUND(C36-C35,0)</f>
         <v/>
       </c>
-      <c r="D37" s="89">
+      <c r="D37" s="96">
         <f>ROUND(D36-D35,0)</f>
         <v/>
       </c>
-      <c r="E37" s="89">
+      <c r="E37" s="96">
         <f>ROUND(E36-E35,0)</f>
         <v/>
       </c>
-      <c r="F37" s="89">
+      <c r="F37" s="96">
         <f>ROUND(F36-F35,0)</f>
         <v/>
       </c>
-      <c r="G37" s="89">
+      <c r="G37" s="96">
         <f>ROUND(G36-G35,0)</f>
         <v/>
       </c>
-      <c r="H37" s="89">
+      <c r="H37" s="96">
         <f>ROUND(H36-H35,0)</f>
         <v/>
       </c>
-      <c r="I37" s="89">
+      <c r="I37" s="96">
         <f>ROUND(I36-I35,0)</f>
         <v/>
       </c>
-      <c r="J37" s="89">
+      <c r="J37" s="96">
         <f>ROUND(J36-J35,0)</f>
         <v/>
       </c>
-      <c r="K37" s="89">
+      <c r="K37" s="96">
         <f>ROUND(K36-K35,0)</f>
         <v/>
       </c>
-      <c r="L37" s="89">
+      <c r="L37" s="96">
         <f>ROUND(L36-L35,0)</f>
         <v/>
       </c>
@@ -7232,43 +10754,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C42" s="88">
+      <c r="C42" s="95">
         <f>ROUND(C41-C40,0)</f>
         <v/>
       </c>
-      <c r="D42" s="88">
+      <c r="D42" s="95">
         <f>ROUND(D41-D40,0)</f>
         <v/>
       </c>
-      <c r="E42" s="88">
+      <c r="E42" s="95">
         <f>ROUND(E41-E40,0)</f>
         <v/>
       </c>
-      <c r="F42" s="88">
+      <c r="F42" s="95">
         <f>ROUND(F41-F40,0)</f>
         <v/>
       </c>
-      <c r="G42" s="88">
+      <c r="G42" s="95">
         <f>ROUND(G41-G40,0)</f>
         <v/>
       </c>
-      <c r="H42" s="88">
+      <c r="H42" s="95">
         <f>ROUND(H41-H40,0)</f>
         <v/>
       </c>
-      <c r="I42" s="88">
+      <c r="I42" s="95">
         <f>ROUND(I41-I40,0)</f>
         <v/>
       </c>
-      <c r="J42" s="88">
+      <c r="J42" s="95">
         <f>ROUND(J41-J40,0)</f>
         <v/>
       </c>
-      <c r="K42" s="88">
+      <c r="K42" s="95">
         <f>ROUND(K41-K40,0)</f>
         <v/>
       </c>
-      <c r="L42" s="88">
+      <c r="L42" s="95">
         <f>ROUND(L41-L40,0)</f>
         <v/>
       </c>
@@ -7396,43 +10918,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C47" s="89">
+      <c r="C47" s="96">
         <f>ROUND(C46-C45,0)</f>
         <v/>
       </c>
-      <c r="D47" s="89">
+      <c r="D47" s="96">
         <f>ROUND(D46-D45,0)</f>
         <v/>
       </c>
-      <c r="E47" s="89">
+      <c r="E47" s="96">
         <f>ROUND(E46-E45,0)</f>
         <v/>
       </c>
-      <c r="F47" s="89">
+      <c r="F47" s="96">
         <f>ROUND(F46-F45,0)</f>
         <v/>
       </c>
-      <c r="G47" s="89">
+      <c r="G47" s="96">
         <f>ROUND(G46-G45,0)</f>
         <v/>
       </c>
-      <c r="H47" s="89">
+      <c r="H47" s="96">
         <f>ROUND(H46-H45,0)</f>
         <v/>
       </c>
-      <c r="I47" s="89">
+      <c r="I47" s="96">
         <f>ROUND(I46-I45,0)</f>
         <v/>
       </c>
-      <c r="J47" s="89">
+      <c r="J47" s="96">
         <f>ROUND(J46-J45,0)</f>
         <v/>
       </c>
-      <c r="K47" s="89">
+      <c r="K47" s="96">
         <f>ROUND(K46-K45,0)</f>
         <v/>
       </c>
-      <c r="L47" s="89">
+      <c r="L47" s="96">
         <f>ROUND(L46-L45,0)</f>
         <v/>
       </c>
@@ -7560,43 +11082,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C52" s="89">
+      <c r="C52" s="96">
         <f>ROUND(C51-C50,0)</f>
         <v/>
       </c>
-      <c r="D52" s="89">
+      <c r="D52" s="96">
         <f>ROUND(D51-D50,0)</f>
         <v/>
       </c>
-      <c r="E52" s="89">
+      <c r="E52" s="96">
         <f>ROUND(E51-E50,0)</f>
         <v/>
       </c>
-      <c r="F52" s="89">
+      <c r="F52" s="96">
         <f>ROUND(F51-F50,0)</f>
         <v/>
       </c>
-      <c r="G52" s="89">
+      <c r="G52" s="96">
         <f>ROUND(G51-G50,0)</f>
         <v/>
       </c>
-      <c r="H52" s="89">
+      <c r="H52" s="96">
         <f>ROUND(H51-H50,0)</f>
         <v/>
       </c>
-      <c r="I52" s="89">
+      <c r="I52" s="96">
         <f>ROUND(I51-I50,0)</f>
         <v/>
       </c>
-      <c r="J52" s="89">
+      <c r="J52" s="96">
         <f>ROUND(J51-J50,0)</f>
         <v/>
       </c>
-      <c r="K52" s="89">
+      <c r="K52" s="96">
         <f>ROUND(K51-K50,0)</f>
         <v/>
       </c>
-      <c r="L52" s="89">
+      <c r="L52" s="96">
         <f>ROUND(L51-L50,0)</f>
         <v/>
       </c>
@@ -7724,43 +11246,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C57" s="88">
+      <c r="C57" s="95">
         <f>ROUND(C56-C55,0)</f>
         <v/>
       </c>
-      <c r="D57" s="88">
+      <c r="D57" s="95">
         <f>ROUND(D56-D55,0)</f>
         <v/>
       </c>
-      <c r="E57" s="88">
+      <c r="E57" s="95">
         <f>ROUND(E56-E55,0)</f>
         <v/>
       </c>
-      <c r="F57" s="88">
+      <c r="F57" s="95">
         <f>ROUND(F56-F55,0)</f>
         <v/>
       </c>
-      <c r="G57" s="88">
+      <c r="G57" s="95">
         <f>ROUND(G56-G55,0)</f>
         <v/>
       </c>
-      <c r="H57" s="88">
+      <c r="H57" s="95">
         <f>ROUND(H56-H55,0)</f>
         <v/>
       </c>
-      <c r="I57" s="88">
+      <c r="I57" s="95">
         <f>ROUND(I56-I55,0)</f>
         <v/>
       </c>
-      <c r="J57" s="88">
+      <c r="J57" s="95">
         <f>ROUND(J56-J55,0)</f>
         <v/>
       </c>
-      <c r="K57" s="88">
+      <c r="K57" s="95">
         <f>ROUND(K56-K55,0)</f>
         <v/>
       </c>
-      <c r="L57" s="88">
+      <c r="L57" s="95">
         <f>ROUND(L56-L55,0)</f>
         <v/>
       </c>
@@ -7888,43 +11410,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C62" s="88">
+      <c r="C62" s="95">
         <f>ROUND(C61-C60,0)</f>
         <v/>
       </c>
-      <c r="D62" s="88">
+      <c r="D62" s="95">
         <f>ROUND(D61-D60,0)</f>
         <v/>
       </c>
-      <c r="E62" s="88">
+      <c r="E62" s="95">
         <f>ROUND(E61-E60,0)</f>
         <v/>
       </c>
-      <c r="F62" s="88">
+      <c r="F62" s="95">
         <f>ROUND(F61-F60,0)</f>
         <v/>
       </c>
-      <c r="G62" s="88">
+      <c r="G62" s="95">
         <f>ROUND(G61-G60,0)</f>
         <v/>
       </c>
-      <c r="H62" s="88">
+      <c r="H62" s="95">
         <f>ROUND(H61-H60,0)</f>
         <v/>
       </c>
-      <c r="I62" s="88">
+      <c r="I62" s="95">
         <f>ROUND(I61-I60,0)</f>
         <v/>
       </c>
-      <c r="J62" s="88">
+      <c r="J62" s="95">
         <f>ROUND(J61-J60,0)</f>
         <v/>
       </c>
-      <c r="K62" s="88">
+      <c r="K62" s="95">
         <f>ROUND(K61-K60,0)</f>
         <v/>
       </c>
-      <c r="L62" s="88">
+      <c r="L62" s="95">
         <f>ROUND(L61-L60,0)</f>
         <v/>
       </c>
@@ -8052,43 +11574,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C67" s="88">
+      <c r="C67" s="95">
         <f>ROUND(C66-C65,0)</f>
         <v/>
       </c>
-      <c r="D67" s="88">
+      <c r="D67" s="95">
         <f>ROUND(D66-D65,0)</f>
         <v/>
       </c>
-      <c r="E67" s="88">
+      <c r="E67" s="95">
         <f>ROUND(E66-E65,0)</f>
         <v/>
       </c>
-      <c r="F67" s="88">
+      <c r="F67" s="95">
         <f>ROUND(F66-F65,0)</f>
         <v/>
       </c>
-      <c r="G67" s="88">
+      <c r="G67" s="95">
         <f>ROUND(G66-G65,0)</f>
         <v/>
       </c>
-      <c r="H67" s="88">
+      <c r="H67" s="95">
         <f>ROUND(H66-H65,0)</f>
         <v/>
       </c>
-      <c r="I67" s="88">
+      <c r="I67" s="95">
         <f>ROUND(I66-I65,0)</f>
         <v/>
       </c>
-      <c r="J67" s="88">
+      <c r="J67" s="95">
         <f>ROUND(J66-J65,0)</f>
         <v/>
       </c>
-      <c r="K67" s="88">
+      <c r="K67" s="95">
         <f>ROUND(K66-K65,0)</f>
         <v/>
       </c>
-      <c r="L67" s="88">
+      <c r="L67" s="95">
         <f>ROUND(L66-L65,0)</f>
         <v/>
       </c>
@@ -8216,43 +11738,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C72" s="88">
+      <c r="C72" s="95">
         <f>ROUND(C71-C70,0)</f>
         <v/>
       </c>
-      <c r="D72" s="88">
+      <c r="D72" s="95">
         <f>ROUND(D71-D70,0)</f>
         <v/>
       </c>
-      <c r="E72" s="88">
+      <c r="E72" s="95">
         <f>ROUND(E71-E70,0)</f>
         <v/>
       </c>
-      <c r="F72" s="88">
+      <c r="F72" s="95">
         <f>ROUND(F71-F70,0)</f>
         <v/>
       </c>
-      <c r="G72" s="88">
+      <c r="G72" s="95">
         <f>ROUND(G71-G70,0)</f>
         <v/>
       </c>
-      <c r="H72" s="88">
+      <c r="H72" s="95">
         <f>ROUND(H71-H70,0)</f>
         <v/>
       </c>
-      <c r="I72" s="88">
+      <c r="I72" s="95">
         <f>ROUND(I71-I70,0)</f>
         <v/>
       </c>
-      <c r="J72" s="88">
+      <c r="J72" s="95">
         <f>ROUND(J71-J70,0)</f>
         <v/>
       </c>
-      <c r="K72" s="88">
+      <c r="K72" s="95">
         <f>ROUND(K71-K70,0)</f>
         <v/>
       </c>
-      <c r="L72" s="88">
+      <c r="L72" s="95">
         <f>ROUND(L71-L70,0)</f>
         <v/>
       </c>
@@ -8275,43 +11797,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C75" s="90">
+      <c r="C75" s="97">
         <f>BalanceSheet!C20</f>
         <v/>
       </c>
-      <c r="D75" s="90">
+      <c r="D75" s="97">
         <f>BalanceSheet!D20</f>
         <v/>
       </c>
-      <c r="E75" s="90">
+      <c r="E75" s="97">
         <f>BalanceSheet!E20</f>
         <v/>
       </c>
-      <c r="F75" s="90">
+      <c r="F75" s="97">
         <f>BalanceSheet!F20</f>
         <v/>
       </c>
-      <c r="G75" s="90">
+      <c r="G75" s="97">
         <f>BalanceSheet!G20</f>
         <v/>
       </c>
-      <c r="H75" s="90">
+      <c r="H75" s="97">
         <f>BalanceSheet!H20</f>
         <v/>
       </c>
-      <c r="I75" s="90">
+      <c r="I75" s="97">
         <f>BalanceSheet!I20</f>
         <v/>
       </c>
-      <c r="J75" s="90">
+      <c r="J75" s="97">
         <f>BalanceSheet!J20</f>
         <v/>
       </c>
-      <c r="K75" s="90">
+      <c r="K75" s="97">
         <f>BalanceSheet!K20</f>
         <v/>
       </c>
-      <c r="L75" s="90">
+      <c r="L75" s="97">
         <f>BalanceSheet!L20</f>
         <v/>
       </c>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -826,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A65"/>
+  <dimension ref="A1:A68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1084,168 +1084,189 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Check          the Python model's figures, to verify the formulas agree</t>
+          <t xml:space="preserve">  HiringPlan     headcount by role, reconciled to the model</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CAC_CLV        acquisition cost against lifetime value</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>WHY TEN YEARS</t>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  KPIs           scale, quality of revenue, efficiency</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Check          the Python model's figures, to verify the formulas agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>WHY TEN YEARS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>At Y7 the business is still compounding above 50%, so a terminal value placed</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>there does most of the valuation work and does it badly. Ten years lets growth</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>decelerate inside the explicit forecast, where it can be argued with.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>EVIDENCE CHAIN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Comparables (published facts) -&gt; MarketModel (derives ours) -&gt; Assumptions</t>
+          <t>decelerate inside the explicit forecast, where it can be argued with.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -&gt; Drivers -&gt; Revenue and Costs -&gt; statements -&gt; Valuation.</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  From Assumptions rightwards, every link is a formula you can follow with</t>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>EVIDENCE CHAIN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Trace Precedents. The first arrow is checked rather than linked: MarketModel</t>
+          <t xml:space="preserve">  Comparables (published facts) -&gt; MarketModel (derives ours) -&gt; Assumptions</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  derives each figure from the published ones, and Assumptions carries the</t>
+          <t xml:space="preserve">  -&gt; Drivers -&gt; Revenue and Costs -&gt; statements -&gt; Valuation.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  result rounded for reading -- 37 fans per athlete, not 37.026. Linking the</t>
+          <t xml:space="preserve">  From Assumptions rightwards, every link is a formula you can follow with</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  cells would put the workbook a hair off the Python everywhere, which the</t>
+          <t xml:space="preserve">  Trace Precedents. The first arrow is checked rather than linked: MarketModel</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Check sheet exists to forbid, so scripts/doc_consistency.py asserts the</t>
+          <t xml:space="preserve">  derives each figure from the published ones, and Assumptions carries the</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">  derivation still rounds to those literals instead. Refresh a comparable far</t>
+          <t xml:space="preserve">  result rounded for reading -- 37 fans per athlete, not 37.026. Linking the</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">  enough to change one of them at the precision it is written and that check</t>
+          <t xml:space="preserve">  cells would put the workbook a hair off the Python everywhere, which the</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  fails. A refresh too small to change any displayed figure passes, which is</t>
+          <t xml:space="preserve">  Check sheet exists to forbid, so scripts/doc_consistency.py asserts the</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">  the same statement, not a loophole in it.</t>
+          <t xml:space="preserve">  derivation still rounds to those literals instead. Refresh a comparable far</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  enough to change one of them at the precision it is written and that check</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>MODEL SHAPE</t>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  fails. A refresh too small to change any displayed figure passes, which is</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>This is a target-driven model: athlete counts are the plan, and marketing spend</t>
+          <t xml:space="preserve">  the same statement, not a loophole in it.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>is derived from them at segment CAC. It is not a driver-driven model in which</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>spend produces athletes. That is the normal shape for a plan, but it means the</t>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>MODEL SHAPE</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
+        <is>
+          <t>This is a target-driven model: athlete counts are the plan, and marketing spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>is derived from them at segment CAC. It is not a driver-driven model in which</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>spend produces athletes. That is the normal shape for a plan, but it means the</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>athlete trajectory is an assumption to defend, not an output to trust.</t>
         </is>
@@ -3047,7 +3068,7 @@
     <row r="31">
       <c r="A31" s="54" t="inlineStr">
         <is>
-          <t>The FTE block reconciles exactly and is the plan. The cost build-up prices those roles at their own salaries; the model prices the same headcount at a blended loaded average that rises from 38k to 76k over the plan, covering seniority and inflation, while the build-up holds today's salaries flat. The model is therefore the more expensive and more conservative of the two, and it is the one that reaches the P&amp;L. The two memo rows below make the gap legible.</t>
+          <t>The FTE block reconciles exactly and is the plan. The cost build-up prices those roles at their own salaries; the model prices the same headcount at a blended loaded average that rises from 38k to 76k over the plan, while the build-up holds today's salaries flat. The two cross over at Y4: the build-up is the higher figure in Y1-Y3, where one founder salary dominates a team of two or three, and the model is higher from Y4 as its blended rate climbs. The model is the one that reaches the P&amp;L either way. The memo rows below make the two rates comparable.</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3909,7 +3930,7 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>Contribution per fan month</t>
+          <t>Payout cost, share per fan month</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
@@ -3917,378 +3938,378 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C23" s="57">
-        <f>C21-C22</f>
-        <v/>
-      </c>
-      <c r="D23" s="57">
-        <f>D21-D22</f>
-        <v/>
-      </c>
-      <c r="E23" s="57">
-        <f>E21-E22</f>
-        <v/>
-      </c>
-      <c r="F23" s="57">
-        <f>F21-F22</f>
-        <v/>
-      </c>
-      <c r="G23" s="57">
-        <f>G21-G22</f>
-        <v/>
-      </c>
-      <c r="H23" s="57">
-        <f>H21-H22</f>
-        <v/>
-      </c>
-      <c r="I23" s="57">
-        <f>I21-I22</f>
-        <v/>
-      </c>
-      <c r="J23" s="57">
-        <f>J21-J22</f>
-        <v/>
-      </c>
-      <c r="K23" s="57">
-        <f>K21-K22</f>
-        <v/>
-      </c>
-      <c r="L23" s="57">
-        <f>L21-L22</f>
+      <c r="C23" s="29">
+        <f>C19*Assumptions!C46+Assumptions!C47/30</f>
+        <v/>
+      </c>
+      <c r="D23" s="29">
+        <f>D19*Assumptions!D46+Assumptions!D47/30</f>
+        <v/>
+      </c>
+      <c r="E23" s="29">
+        <f>E19*Assumptions!E46+Assumptions!E47/30</f>
+        <v/>
+      </c>
+      <c r="F23" s="29">
+        <f>F19*Assumptions!F46+Assumptions!F47/30</f>
+        <v/>
+      </c>
+      <c r="G23" s="29">
+        <f>G19*Assumptions!G46+Assumptions!G47/30</f>
+        <v/>
+      </c>
+      <c r="H23" s="29">
+        <f>H19*Assumptions!H46+Assumptions!H47/30</f>
+        <v/>
+      </c>
+      <c r="I23" s="29">
+        <f>I19*Assumptions!I46+Assumptions!I47/30</f>
+        <v/>
+      </c>
+      <c r="J23" s="29">
+        <f>J19*Assumptions!J46+Assumptions!J47/30</f>
+        <v/>
+      </c>
+      <c r="K23" s="29">
+        <f>K19*Assumptions!K46+Assumptions!K47/30</f>
+        <v/>
+      </c>
+      <c r="L23" s="29">
+        <f>L19*Assumptions!L46+Assumptions!L47/30</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>Fan churn</t>
+          <t>Contribution per fan month</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>per month</t>
-        </is>
-      </c>
-      <c r="C24" s="23">
-        <f>Assumptions!C13</f>
-        <v/>
-      </c>
-      <c r="D24" s="23">
-        <f>Assumptions!D13</f>
-        <v/>
-      </c>
-      <c r="E24" s="23">
-        <f>Assumptions!E13</f>
-        <v/>
-      </c>
-      <c r="F24" s="23">
-        <f>Assumptions!F13</f>
-        <v/>
-      </c>
-      <c r="G24" s="23">
-        <f>Assumptions!G13</f>
-        <v/>
-      </c>
-      <c r="H24" s="23">
-        <f>Assumptions!H13</f>
-        <v/>
-      </c>
-      <c r="I24" s="23">
-        <f>Assumptions!I13</f>
-        <v/>
-      </c>
-      <c r="J24" s="23">
-        <f>Assumptions!J13</f>
-        <v/>
-      </c>
-      <c r="K24" s="23">
-        <f>Assumptions!K13</f>
-        <v/>
-      </c>
-      <c r="L24" s="23">
-        <f>Assumptions!L13</f>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C24" s="57">
+        <f>C21-C22-C23</f>
+        <v/>
+      </c>
+      <c r="D24" s="57">
+        <f>D21-D22-D23</f>
+        <v/>
+      </c>
+      <c r="E24" s="57">
+        <f>E21-E22-E23</f>
+        <v/>
+      </c>
+      <c r="F24" s="57">
+        <f>F21-F22-F23</f>
+        <v/>
+      </c>
+      <c r="G24" s="57">
+        <f>G21-G22-G23</f>
+        <v/>
+      </c>
+      <c r="H24" s="57">
+        <f>H21-H22-H23</f>
+        <v/>
+      </c>
+      <c r="I24" s="57">
+        <f>I21-I22-I23</f>
+        <v/>
+      </c>
+      <c r="J24" s="57">
+        <f>J21-J22-J23</f>
+        <v/>
+      </c>
+      <c r="K24" s="57">
+        <f>K21-K22-K23</f>
+        <v/>
+      </c>
+      <c r="L24" s="57">
+        <f>L21-L22-L23</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
+          <t>Fan churn</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>per month</t>
+        </is>
+      </c>
+      <c r="C25" s="23">
+        <f>Assumptions!C13</f>
+        <v/>
+      </c>
+      <c r="D25" s="23">
+        <f>Assumptions!D13</f>
+        <v/>
+      </c>
+      <c r="E25" s="23">
+        <f>Assumptions!E13</f>
+        <v/>
+      </c>
+      <c r="F25" s="23">
+        <f>Assumptions!F13</f>
+        <v/>
+      </c>
+      <c r="G25" s="23">
+        <f>Assumptions!G13</f>
+        <v/>
+      </c>
+      <c r="H25" s="23">
+        <f>Assumptions!H13</f>
+        <v/>
+      </c>
+      <c r="I25" s="23">
+        <f>Assumptions!I13</f>
+        <v/>
+      </c>
+      <c r="J25" s="23">
+        <f>Assumptions!J13</f>
+        <v/>
+      </c>
+      <c r="K25" s="23">
+        <f>Assumptions!K13</f>
+        <v/>
+      </c>
+      <c r="L25" s="23">
+        <f>Assumptions!L13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
           <t>Expected fan life</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>months</t>
         </is>
       </c>
-      <c r="C25" s="56">
-        <f>IF(C24=0,0,1/C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="56">
-        <f>IF(D24=0,0,1/D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="56">
-        <f>IF(E24=0,0,1/E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="56">
-        <f>IF(F24=0,0,1/F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="56">
-        <f>IF(G24=0,0,1/G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="56">
-        <f>IF(H24=0,0,1/H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="56">
-        <f>IF(I24=0,0,1/I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="56">
-        <f>IF(J24=0,0,1/J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="56">
-        <f>IF(K24=0,0,1/K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="56">
-        <f>IF(L24=0,0,1/L24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="44" t="inlineStr">
+      <c r="C26" s="56">
+        <f>IF(C25=0,0,1/C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="56">
+        <f>IF(D25=0,0,1/D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="56">
+        <f>IF(E25=0,0,1/E25)</f>
+        <v/>
+      </c>
+      <c r="F26" s="56">
+        <f>IF(F25=0,0,1/F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="56">
+        <f>IF(G25=0,0,1/G25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="56">
+        <f>IF(H25=0,0,1/H25)</f>
+        <v/>
+      </c>
+      <c r="I26" s="56">
+        <f>IF(I25=0,0,1/I25)</f>
+        <v/>
+      </c>
+      <c r="J26" s="56">
+        <f>IF(J25=0,0,1/J25)</f>
+        <v/>
+      </c>
+      <c r="K26" s="56">
+        <f>IF(K25=0,0,1/K25)</f>
+        <v/>
+      </c>
+      <c r="L26" s="56">
+        <f>IF(L25=0,0,1/L25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="inlineStr">
         <is>
           <t>FAN LTV</t>
         </is>
       </c>
-      <c r="B26" s="40" t="inlineStr">
+      <c r="B27" s="40" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="C26" s="58">
-        <f>C23*C25</f>
-        <v/>
-      </c>
-      <c r="D26" s="58">
-        <f>D23*D25</f>
-        <v/>
-      </c>
-      <c r="E26" s="58">
-        <f>E23*E25</f>
-        <v/>
-      </c>
-      <c r="F26" s="58">
-        <f>F23*F25</f>
-        <v/>
-      </c>
-      <c r="G26" s="58">
-        <f>G23*G25</f>
-        <v/>
-      </c>
-      <c r="H26" s="58">
-        <f>H23*H25</f>
-        <v/>
-      </c>
-      <c r="I26" s="58">
-        <f>I23*I25</f>
-        <v/>
-      </c>
-      <c r="J26" s="58">
-        <f>J23*J25</f>
-        <v/>
-      </c>
-      <c r="K26" s="58">
-        <f>K23*K25</f>
-        <v/>
-      </c>
-      <c r="L26" s="58">
-        <f>L23*L25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="C27" s="58">
+        <f>C24*C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="58">
+        <f>D24*D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="58">
+        <f>E24*E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="58">
+        <f>F24*F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="58">
+        <f>G24*G26</f>
+        <v/>
+      </c>
+      <c r="H27" s="58">
+        <f>H24*H26</f>
+        <v/>
+      </c>
+      <c r="I27" s="58">
+        <f>I24*I26</f>
+        <v/>
+      </c>
+      <c r="J27" s="58">
+        <f>J24*J26</f>
+        <v/>
+      </c>
+      <c r="K27" s="58">
+        <f>K24*K26</f>
+        <v/>
+      </c>
+      <c r="L27" s="58">
+        <f>L24*L26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Fan CAC</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="C27" s="28" t="n">
+      <c r="C28" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="28" t="n">
+      <c r="D28" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="28" t="n">
+      <c r="E28" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="28" t="n">
+      <c r="F28" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="28" t="n">
+      <c r="G28" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="28" t="n">
+      <c r="H28" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="28" t="n">
+      <c r="I28" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="28" t="n">
+      <c r="J28" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K27" s="28" t="n">
+      <c r="K28" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="28" t="n">
+      <c r="L28" s="28" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="54" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="54" t="inlineStr">
         <is>
           <t>Fan CAC is zero by construction: athletes bring their own audiences and the model spends nothing acquiring fans. That understates the risk rather than flattering the return, and the plan discloses it as such.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>SPONSOR</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="12" t="n"/>
-      <c r="H31" s="12" t="n"/>
-      <c r="I31" s="12" t="n"/>
-      <c r="J31" s="12" t="n"/>
-      <c r="K31" s="12" t="n"/>
-      <c r="L31" s="12" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>Sponsor CAC</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C32" s="30">
-        <f>Assumptions!C37</f>
-        <v/>
-      </c>
-      <c r="D32" s="30">
-        <f>Assumptions!D37</f>
-        <v/>
-      </c>
-      <c r="E32" s="30">
-        <f>Assumptions!E37</f>
-        <v/>
-      </c>
-      <c r="F32" s="30">
-        <f>Assumptions!F37</f>
-        <v/>
-      </c>
-      <c r="G32" s="30">
-        <f>Assumptions!G37</f>
-        <v/>
-      </c>
-      <c r="H32" s="30">
-        <f>Assumptions!H37</f>
-        <v/>
-      </c>
-      <c r="I32" s="30">
-        <f>Assumptions!I37</f>
-        <v/>
-      </c>
-      <c r="J32" s="30">
-        <f>Assumptions!J37</f>
-        <v/>
-      </c>
-      <c r="K32" s="30">
-        <f>Assumptions!K37</f>
-        <v/>
-      </c>
-      <c r="L32" s="30">
-        <f>Assumptions!L37</f>
-        <v/>
-      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>SaaS per paying sponsor</t>
+          <t>Sponsor CAC</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>EUR/yr</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="C33" s="30">
-        <f>Assumptions!C36*12</f>
+        <f>Assumptions!C37</f>
         <v/>
       </c>
       <c r="D33" s="30">
-        <f>Assumptions!D36*12</f>
+        <f>Assumptions!D37</f>
         <v/>
       </c>
       <c r="E33" s="30">
-        <f>Assumptions!E36*12</f>
+        <f>Assumptions!E37</f>
         <v/>
       </c>
       <c r="F33" s="30">
-        <f>Assumptions!F36*12</f>
+        <f>Assumptions!F37</f>
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>Assumptions!G36*12</f>
+        <f>Assumptions!G37</f>
         <v/>
       </c>
       <c r="H33" s="30">
-        <f>Assumptions!H36*12</f>
+        <f>Assumptions!H37</f>
         <v/>
       </c>
       <c r="I33" s="30">
-        <f>Assumptions!I36*12</f>
+        <f>Assumptions!I37</f>
         <v/>
       </c>
       <c r="J33" s="30">
-        <f>Assumptions!J36*12</f>
+        <f>Assumptions!J37</f>
         <v/>
       </c>
       <c r="K33" s="30">
-        <f>Assumptions!K36*12</f>
+        <f>Assumptions!K37</f>
         <v/>
       </c>
       <c r="L33" s="30">
-        <f>Assumptions!L36*12</f>
+        <f>Assumptions!L37</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>Sponsorship take per paying sponsor</t>
+          <t>SaaS per paying sponsor</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
@@ -4297,152 +4318,256 @@
         </is>
       </c>
       <c r="C34" s="30">
-        <f>IF(Drivers!C48=0,0,Revenue!C20/Drivers!C48)</f>
+        <f>Assumptions!C36*12</f>
         <v/>
       </c>
       <c r="D34" s="30">
-        <f>IF(Drivers!D48=0,0,Revenue!D20/Drivers!D48)</f>
+        <f>Assumptions!D36*12</f>
         <v/>
       </c>
       <c r="E34" s="30">
-        <f>IF(Drivers!E48=0,0,Revenue!E20/Drivers!E48)</f>
+        <f>Assumptions!E36*12</f>
         <v/>
       </c>
       <c r="F34" s="30">
-        <f>IF(Drivers!F48=0,0,Revenue!F20/Drivers!F48)</f>
+        <f>Assumptions!F36*12</f>
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(Drivers!G48=0,0,Revenue!G20/Drivers!G48)</f>
+        <f>Assumptions!G36*12</f>
         <v/>
       </c>
       <c r="H34" s="30">
-        <f>IF(Drivers!H48=0,0,Revenue!H20/Drivers!H48)</f>
+        <f>Assumptions!H36*12</f>
         <v/>
       </c>
       <c r="I34" s="30">
-        <f>IF(Drivers!I48=0,0,Revenue!I20/Drivers!I48)</f>
+        <f>Assumptions!I36*12</f>
         <v/>
       </c>
       <c r="J34" s="30">
-        <f>IF(Drivers!J48=0,0,Revenue!J20/Drivers!J48)</f>
+        <f>Assumptions!J36*12</f>
         <v/>
       </c>
       <c r="K34" s="30">
-        <f>IF(Drivers!K48=0,0,Revenue!K20/Drivers!K48)</f>
+        <f>Assumptions!K36*12</f>
         <v/>
       </c>
       <c r="L34" s="30">
-        <f>IF(Drivers!L48=0,0,Revenue!L20/Drivers!L48)</f>
+        <f>Assumptions!L36*12</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
+          <t>Sponsorship take per paying sponsor</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>EUR/yr</t>
+        </is>
+      </c>
+      <c r="C35" s="30">
+        <f>IF(Drivers!C48=0,0,Revenue!C20/Drivers!C48)</f>
+        <v/>
+      </c>
+      <c r="D35" s="30">
+        <f>IF(Drivers!D48=0,0,Revenue!D20/Drivers!D48)</f>
+        <v/>
+      </c>
+      <c r="E35" s="30">
+        <f>IF(Drivers!E48=0,0,Revenue!E20/Drivers!E48)</f>
+        <v/>
+      </c>
+      <c r="F35" s="30">
+        <f>IF(Drivers!F48=0,0,Revenue!F20/Drivers!F48)</f>
+        <v/>
+      </c>
+      <c r="G35" s="30">
+        <f>IF(Drivers!G48=0,0,Revenue!G20/Drivers!G48)</f>
+        <v/>
+      </c>
+      <c r="H35" s="30">
+        <f>IF(Drivers!H48=0,0,Revenue!H20/Drivers!H48)</f>
+        <v/>
+      </c>
+      <c r="I35" s="30">
+        <f>IF(Drivers!I48=0,0,Revenue!I20/Drivers!I48)</f>
+        <v/>
+      </c>
+      <c r="J35" s="30">
+        <f>IF(Drivers!J48=0,0,Revenue!J20/Drivers!J48)</f>
+        <v/>
+      </c>
+      <c r="K35" s="30">
+        <f>IF(Drivers!K48=0,0,Revenue!K20/Drivers!K48)</f>
+        <v/>
+      </c>
+      <c r="L35" s="30">
+        <f>IF(Drivers!L48=0,0,Revenue!L20/Drivers!L48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
           <t>Contribution per sponsor per year</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="C35" s="47">
-        <f>C33+C34</f>
-        <v/>
-      </c>
-      <c r="D35" s="47">
-        <f>D33+D34</f>
-        <v/>
-      </c>
-      <c r="E35" s="47">
-        <f>E33+E34</f>
-        <v/>
-      </c>
-      <c r="F35" s="47">
-        <f>F33+F34</f>
-        <v/>
-      </c>
-      <c r="G35" s="47">
-        <f>G33+G34</f>
-        <v/>
-      </c>
-      <c r="H35" s="47">
-        <f>H33+H34</f>
-        <v/>
-      </c>
-      <c r="I35" s="47">
-        <f>I33+I34</f>
-        <v/>
-      </c>
-      <c r="J35" s="47">
-        <f>J33+J34</f>
-        <v/>
-      </c>
-      <c r="K35" s="47">
-        <f>K33+K34</f>
-        <v/>
-      </c>
-      <c r="L35" s="47">
-        <f>L33+L34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="44" t="inlineStr">
+      <c r="C36" s="47">
+        <f>C34+C35</f>
+        <v/>
+      </c>
+      <c r="D36" s="47">
+        <f>D34+D35</f>
+        <v/>
+      </c>
+      <c r="E36" s="47">
+        <f>E34+E35</f>
+        <v/>
+      </c>
+      <c r="F36" s="47">
+        <f>F34+F35</f>
+        <v/>
+      </c>
+      <c r="G36" s="47">
+        <f>G34+G35</f>
+        <v/>
+      </c>
+      <c r="H36" s="47">
+        <f>H34+H35</f>
+        <v/>
+      </c>
+      <c r="I36" s="47">
+        <f>I34+I35</f>
+        <v/>
+      </c>
+      <c r="J36" s="47">
+        <f>J34+J35</f>
+        <v/>
+      </c>
+      <c r="K36" s="47">
+        <f>K34+K35</f>
+        <v/>
+      </c>
+      <c r="L36" s="47">
+        <f>L34+L35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  at gross margin</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C37" s="30">
+        <f>C36*'P&amp;L'!C7</f>
+        <v/>
+      </c>
+      <c r="D37" s="30">
+        <f>D36*'P&amp;L'!D7</f>
+        <v/>
+      </c>
+      <c r="E37" s="30">
+        <f>E36*'P&amp;L'!E7</f>
+        <v/>
+      </c>
+      <c r="F37" s="30">
+        <f>F36*'P&amp;L'!F7</f>
+        <v/>
+      </c>
+      <c r="G37" s="30">
+        <f>G36*'P&amp;L'!G7</f>
+        <v/>
+      </c>
+      <c r="H37" s="30">
+        <f>H36*'P&amp;L'!H7</f>
+        <v/>
+      </c>
+      <c r="I37" s="30">
+        <f>I36*'P&amp;L'!I7</f>
+        <v/>
+      </c>
+      <c r="J37" s="30">
+        <f>J36*'P&amp;L'!J7</f>
+        <v/>
+      </c>
+      <c r="K37" s="30">
+        <f>K36*'P&amp;L'!K7</f>
+        <v/>
+      </c>
+      <c r="L37" s="30">
+        <f>L36*'P&amp;L'!L7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="44" t="inlineStr">
         <is>
           <t>CAC payback</t>
         </is>
       </c>
-      <c r="B36" s="40" t="inlineStr">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>months</t>
         </is>
       </c>
-      <c r="C36" s="51">
-        <f>IF(C35&lt;=0,0,12*C32/C35)</f>
-        <v/>
-      </c>
-      <c r="D36" s="51">
-        <f>IF(D35&lt;=0,0,12*D32/D35)</f>
-        <v/>
-      </c>
-      <c r="E36" s="51">
-        <f>IF(E35&lt;=0,0,12*E32/E35)</f>
-        <v/>
-      </c>
-      <c r="F36" s="51">
-        <f>IF(F35&lt;=0,0,12*F32/F35)</f>
-        <v/>
-      </c>
-      <c r="G36" s="51">
-        <f>IF(G35&lt;=0,0,12*G32/G35)</f>
-        <v/>
-      </c>
-      <c r="H36" s="51">
-        <f>IF(H35&lt;=0,0,12*H32/H35)</f>
-        <v/>
-      </c>
-      <c r="I36" s="51">
-        <f>IF(I35&lt;=0,0,12*I32/I35)</f>
-        <v/>
-      </c>
-      <c r="J36" s="51">
-        <f>IF(J35&lt;=0,0,12*J32/J35)</f>
-        <v/>
-      </c>
-      <c r="K36" s="51">
-        <f>IF(K35&lt;=0,0,12*K32/K35)</f>
-        <v/>
-      </c>
-      <c r="L36" s="51">
-        <f>IF(L35&lt;=0,0,12*L32/L35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="54" t="inlineStr">
+      <c r="C38" s="51">
+        <f>IF(C37&lt;=0,0,12*C33/C37)</f>
+        <v/>
+      </c>
+      <c r="D38" s="51">
+        <f>IF(D37&lt;=0,0,12*D33/D37)</f>
+        <v/>
+      </c>
+      <c r="E38" s="51">
+        <f>IF(E37&lt;=0,0,12*E33/E37)</f>
+        <v/>
+      </c>
+      <c r="F38" s="51">
+        <f>IF(F37&lt;=0,0,12*F33/F37)</f>
+        <v/>
+      </c>
+      <c r="G38" s="51">
+        <f>IF(G37&lt;=0,0,12*G33/G37)</f>
+        <v/>
+      </c>
+      <c r="H38" s="51">
+        <f>IF(H37&lt;=0,0,12*H33/H37)</f>
+        <v/>
+      </c>
+      <c r="I38" s="51">
+        <f>IF(I37&lt;=0,0,12*I33/I37)</f>
+        <v/>
+      </c>
+      <c r="J38" s="51">
+        <f>IF(J37&lt;=0,0,12*J33/J37)</f>
+        <v/>
+      </c>
+      <c r="K38" s="51">
+        <f>IF(K37&lt;=0,0,12*K33/K37)</f>
+        <v/>
+      </c>
+      <c r="L38" s="51">
+        <f>IF(L37&lt;=0,0,12*L33/L37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="54" t="inlineStr">
         <is>
           <t>No sponsor LTV is shown. It needs a sponsor retention assumption the model does not make, and inventing one here would create a figure nothing else in the plan validates. Payback needs no such assumption, so payback is what is reported.</t>
         </is>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -330,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -400,6 +400,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="16" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="16" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="16" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="17" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3704,12 +3705,16 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>FAN — NICHE, THE SEGMENT THE PLAN STARTS IN</t>
+          <t>FAN — NICHE SUBSCRIPTION ONLY</t>
         </is>
       </c>
       <c r="B18" s="12" t="n"/>
       <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
+      <c r="D18" s="57" t="inlineStr">
+        <is>
+          <t>excludes PPV and tips, which the revenue model carries separately</t>
+        </is>
+      </c>
       <c r="E18" s="12" t="n"/>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
@@ -3990,43 +3995,43 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C24" s="57">
+      <c r="C24" s="58">
         <f>C21-C22-C23</f>
         <v/>
       </c>
-      <c r="D24" s="57">
+      <c r="D24" s="58">
         <f>D21-D22-D23</f>
         <v/>
       </c>
-      <c r="E24" s="57">
+      <c r="E24" s="58">
         <f>E21-E22-E23</f>
         <v/>
       </c>
-      <c r="F24" s="57">
+      <c r="F24" s="58">
         <f>F21-F22-F23</f>
         <v/>
       </c>
-      <c r="G24" s="57">
+      <c r="G24" s="58">
         <f>G21-G22-G23</f>
         <v/>
       </c>
-      <c r="H24" s="57">
+      <c r="H24" s="58">
         <f>H21-H22-H23</f>
         <v/>
       </c>
-      <c r="I24" s="57">
+      <c r="I24" s="58">
         <f>I21-I22-I23</f>
         <v/>
       </c>
-      <c r="J24" s="57">
+      <c r="J24" s="58">
         <f>J21-J22-J23</f>
         <v/>
       </c>
-      <c r="K24" s="57">
+      <c r="K24" s="58">
         <f>K21-K22-K23</f>
         <v/>
       </c>
-      <c r="L24" s="57">
+      <c r="L24" s="58">
         <f>L21-L22-L23</f>
         <v/>
       </c>
@@ -4146,43 +4151,43 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C27" s="58">
+      <c r="C27" s="59">
         <f>C24*C26</f>
         <v/>
       </c>
-      <c r="D27" s="58">
+      <c r="D27" s="59">
         <f>D24*D26</f>
         <v/>
       </c>
-      <c r="E27" s="58">
+      <c r="E27" s="59">
         <f>E24*E26</f>
         <v/>
       </c>
-      <c r="F27" s="58">
+      <c r="F27" s="59">
         <f>F24*F26</f>
         <v/>
       </c>
-      <c r="G27" s="58">
+      <c r="G27" s="59">
         <f>G24*G26</f>
         <v/>
       </c>
-      <c r="H27" s="58">
+      <c r="H27" s="59">
         <f>H24*H26</f>
         <v/>
       </c>
-      <c r="I27" s="58">
+      <c r="I27" s="59">
         <f>I24*I26</f>
         <v/>
       </c>
-      <c r="J27" s="58">
+      <c r="J27" s="59">
         <f>J24*J26</f>
         <v/>
       </c>
-      <c r="K27" s="58">
+      <c r="K27" s="59">
         <f>K24*K26</f>
         <v/>
       </c>
-      <c r="L27" s="58">
+      <c r="L27" s="59">
         <f>L24*L26</f>
         <v/>
       </c>
@@ -5755,7 +5760,7 @@
           <t>PV of explicit forecast</t>
         </is>
       </c>
-      <c r="C10" s="59">
+      <c r="C10" s="60">
         <f>SUM(C6:L6)</f>
         <v/>
       </c>
@@ -5766,7 +5771,7 @@
           <t>Terminal value at Y10</t>
         </is>
       </c>
-      <c r="C11" s="59">
+      <c r="C11" s="60">
         <f>L4*(1+Assumptions!$C$86)/(Assumptions!$C$85-Assumptions!$C$86)</f>
         <v/>
       </c>
@@ -5777,7 +5782,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C12" s="59">
+      <c r="C12" s="60">
         <f>C11*L5</f>
         <v/>
       </c>
@@ -5788,7 +5793,7 @@
           <t>ENTERPRISE VALUE (DCF)</t>
         </is>
       </c>
-      <c r="C13" s="59">
+      <c r="C13" s="60">
         <f>C10+C12</f>
         <v/>
       </c>
@@ -5817,7 +5822,7 @@
           <t>NPV of FCF at WACC</t>
         </is>
       </c>
-      <c r="C16" s="59">
+      <c r="C16" s="60">
         <f>NPV(Assumptions!$C$85,C4:L4)</f>
         <v/>
       </c>
@@ -5828,7 +5833,7 @@
           <t>IRR of the plan</t>
         </is>
       </c>
-      <c r="C17" s="60">
+      <c r="C17" s="61">
         <f>IRR(C4:L4)</f>
         <v/>
       </c>
@@ -5839,7 +5844,7 @@
           <t>IRR incl. terminal value</t>
         </is>
       </c>
-      <c r="C18" s="60">
+      <c r="C18" s="61">
         <f>IRR(C8:L8,0.3)</f>
         <v/>
       </c>
@@ -5868,7 +5873,7 @@
           <t>Y10 net revenue</t>
         </is>
       </c>
-      <c r="C21" s="59">
+      <c r="C21" s="60">
         <f>Revenue!L22</f>
         <v/>
       </c>
@@ -5879,7 +5884,7 @@
           <t>Exit value at Y10</t>
         </is>
       </c>
-      <c r="C22" s="59">
+      <c r="C22" s="60">
         <f>C21*Assumptions!$C$87</f>
         <v/>
       </c>
@@ -5890,7 +5895,7 @@
           <t>Discounted to today</t>
         </is>
       </c>
-      <c r="C23" s="59">
+      <c r="C23" s="60">
         <f>C22*L5</f>
         <v/>
       </c>
@@ -5919,166 +5924,166 @@
           <t>Terminal growth \ WACC</t>
         </is>
       </c>
-      <c r="C26" s="61" t="n">
+      <c r="C26" s="62" t="n">
         <v>0.18</v>
       </c>
-      <c r="D26" s="61" t="n">
+      <c r="D26" s="62" t="n">
         <v>0.2</v>
       </c>
-      <c r="E26" s="61" t="n">
+      <c r="E26" s="62" t="n">
         <v>0.22</v>
       </c>
-      <c r="F26" s="61" t="n">
+      <c r="F26" s="62" t="n">
         <v>0.25</v>
       </c>
-      <c r="G26" s="61" t="n">
+      <c r="G26" s="62" t="n">
         <v>0.28</v>
       </c>
-      <c r="H26" s="61" t="n">
+      <c r="H26" s="62" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="60" t="n">
+      <c r="A27" s="61" t="n">
         <v>0.01</v>
       </c>
-      <c r="C27" s="62">
+      <c r="C27" s="63">
         <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.01)/(0.18-0.01)/(1+0.18)^10</f>
         <v/>
       </c>
-      <c r="D27" s="62">
+      <c r="D27" s="63">
         <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.01)/(0.2-0.01)/(1+0.2)^10</f>
         <v/>
       </c>
-      <c r="E27" s="62">
+      <c r="E27" s="63">
         <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.01)/(0.22-0.01)/(1+0.22)^10</f>
         <v/>
       </c>
-      <c r="F27" s="62">
+      <c r="F27" s="63">
         <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.01)/(0.25-0.01)/(1+0.25)^10</f>
         <v/>
       </c>
-      <c r="G27" s="62">
+      <c r="G27" s="63">
         <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.01)/(0.28-0.01)/(1+0.28)^10</f>
         <v/>
       </c>
-      <c r="H27" s="62">
+      <c r="H27" s="63">
         <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.01)/(0.3-0.01)/(1+0.3)^10</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="60" t="n">
+      <c r="A28" s="61" t="n">
         <v>0.02</v>
       </c>
-      <c r="C28" s="62">
+      <c r="C28" s="63">
         <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.02)/(0.18-0.02)/(1+0.18)^10</f>
         <v/>
       </c>
-      <c r="D28" s="62">
+      <c r="D28" s="63">
         <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.02)/(0.2-0.02)/(1+0.2)^10</f>
         <v/>
       </c>
-      <c r="E28" s="62">
+      <c r="E28" s="63">
         <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.02)/(0.22-0.02)/(1+0.22)^10</f>
         <v/>
       </c>
-      <c r="F28" s="62">
+      <c r="F28" s="63">
         <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.02)/(0.25-0.02)/(1+0.25)^10</f>
         <v/>
       </c>
-      <c r="G28" s="62">
+      <c r="G28" s="63">
         <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.02)/(0.28-0.02)/(1+0.28)^10</f>
         <v/>
       </c>
-      <c r="H28" s="62">
+      <c r="H28" s="63">
         <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.02)/(0.3-0.02)/(1+0.3)^10</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="60" t="n">
+      <c r="A29" s="61" t="n">
         <v>0.03</v>
       </c>
-      <c r="C29" s="62">
+      <c r="C29" s="63">
         <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.03)/(0.18-0.03)/(1+0.18)^10</f>
         <v/>
       </c>
-      <c r="D29" s="62">
+      <c r="D29" s="63">
         <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.03)/(0.2-0.03)/(1+0.2)^10</f>
         <v/>
       </c>
-      <c r="E29" s="62">
+      <c r="E29" s="63">
         <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.03)/(0.22-0.03)/(1+0.22)^10</f>
         <v/>
       </c>
-      <c r="F29" s="62">
+      <c r="F29" s="63">
         <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.03)/(0.25-0.03)/(1+0.25)^10</f>
         <v/>
       </c>
-      <c r="G29" s="62">
+      <c r="G29" s="63">
         <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.03)/(0.28-0.03)/(1+0.28)^10</f>
         <v/>
       </c>
-      <c r="H29" s="62">
+      <c r="H29" s="63">
         <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.03)/(0.3-0.03)/(1+0.3)^10</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="60" t="n">
+      <c r="A30" s="61" t="n">
         <v>0.04</v>
       </c>
-      <c r="C30" s="62">
+      <c r="C30" s="63">
         <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.04)/(0.18-0.04)/(1+0.18)^10</f>
         <v/>
       </c>
-      <c r="D30" s="62">
+      <c r="D30" s="63">
         <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.04)/(0.2-0.04)/(1+0.2)^10</f>
         <v/>
       </c>
-      <c r="E30" s="62">
+      <c r="E30" s="63">
         <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.04)/(0.22-0.04)/(1+0.22)^10</f>
         <v/>
       </c>
-      <c r="F30" s="62">
+      <c r="F30" s="63">
         <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.04)/(0.25-0.04)/(1+0.25)^10</f>
         <v/>
       </c>
-      <c r="G30" s="62">
+      <c r="G30" s="63">
         <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.04)/(0.28-0.04)/(1+0.28)^10</f>
         <v/>
       </c>
-      <c r="H30" s="62">
+      <c r="H30" s="63">
         <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.04)/(0.3-0.04)/(1+0.3)^10</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="60" t="n">
+      <c r="A31" s="61" t="n">
         <v>0.05</v>
       </c>
-      <c r="C31" s="62">
+      <c r="C31" s="63">
         <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.05)/(0.18-0.05)/(1+0.18)^10</f>
         <v/>
       </c>
-      <c r="D31" s="62">
+      <c r="D31" s="63">
         <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.05)/(0.2-0.05)/(1+0.2)^10</f>
         <v/>
       </c>
-      <c r="E31" s="62">
+      <c r="E31" s="63">
         <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.05)/(0.22-0.05)/(1+0.22)^10</f>
         <v/>
       </c>
-      <c r="F31" s="62">
+      <c r="F31" s="63">
         <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.05)/(0.25-0.05)/(1+0.25)^10</f>
         <v/>
       </c>
-      <c r="G31" s="62">
+      <c r="G31" s="63">
         <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.05)/(0.28-0.05)/(1+0.28)^10</f>
         <v/>
       </c>
-      <c r="H31" s="62">
+      <c r="H31" s="63">
         <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.05)/(0.3-0.05)/(1+0.3)^10</f>
         <v/>
       </c>
@@ -6120,676 +6125,676 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="64" t="inlineStr">
         <is>
           <t>Nothing on this sheet is our estimate. Every figure is published and cited, so it can be refreshed independently of anything we concluded from it. MarketModel derives our assumptions from these numbers; Assumptions then uses what MarketModel produces.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="64" t="inlineStr">
+      <c r="A4" s="65" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="64" t="inlineStr">
+      <c r="B4" s="65" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C4" s="64" t="inlineStr">
+      <c r="C4" s="65" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D4" s="64" t="inlineStr">
+      <c r="D4" s="65" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E4" s="64" t="inlineStr">
+      <c r="E4" s="65" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F4" s="64" t="inlineStr">
+      <c r="F4" s="65" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="65" t="inlineStr">
+      <c r="A5" s="66" t="inlineStr">
         <is>
           <t>Gross payments (GMV)</t>
         </is>
       </c>
-      <c r="B5" s="66" t="n">
+      <c r="B5" s="67" t="n">
         <v>7220000000</v>
       </c>
-      <c r="C5" s="67" t="inlineStr">
+      <c r="C5" s="68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D5" s="67" t="inlineStr">
+      <c r="D5" s="68" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E5" s="67" t="inlineStr">
+      <c r="E5" s="68" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F5" s="67" t="inlineStr">
+      <c r="F5" s="68" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts (Companies House 10354575)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="65" t="inlineStr">
+      <c r="A6" s="66" t="inlineStr">
         <is>
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="B6" s="66" t="n">
+      <c r="B6" s="67" t="n">
         <v>1410000000</v>
       </c>
-      <c r="C6" s="67" t="inlineStr">
+      <c r="C6" s="68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D6" s="67" t="inlineStr">
+      <c r="D6" s="68" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E6" s="67" t="inlineStr">
+      <c r="E6" s="68" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F6" s="67" t="inlineStr">
+      <c r="F6" s="68" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts (Companies House 10354575)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="inlineStr">
+      <c r="A7" s="66" t="inlineStr">
         <is>
           <t>Paid to creators</t>
         </is>
       </c>
-      <c r="B7" s="66" t="n">
+      <c r="B7" s="67" t="n">
         <v>5800000000</v>
       </c>
-      <c r="C7" s="67" t="inlineStr">
+      <c r="C7" s="68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D7" s="67" t="inlineStr">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E7" s="67" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F7" s="67" t="inlineStr">
+      <c r="F7" s="68" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts — 80.3% of gross</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="65" t="inlineStr">
+      <c r="A8" s="66" t="inlineStr">
         <is>
           <t>Creator accounts</t>
         </is>
       </c>
-      <c r="B8" s="66" t="n">
+      <c r="B8" s="67" t="n">
         <v>4634000</v>
       </c>
-      <c r="C8" s="67" t="inlineStr">
+      <c r="C8" s="68" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D8" s="67" t="inlineStr">
+      <c r="D8" s="68" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E8" s="67" t="inlineStr">
+      <c r="E8" s="68" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F8" s="67" t="inlineStr">
+      <c r="F8" s="68" t="inlineStr">
         <is>
           <t>Variety — +13% YoY</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="65" t="inlineStr">
+      <c r="A9" s="66" t="inlineStr">
         <is>
           <t>Fan accounts</t>
         </is>
       </c>
-      <c r="B9" s="66" t="n">
+      <c r="B9" s="67" t="n">
         <v>377500000</v>
       </c>
-      <c r="C9" s="67" t="inlineStr">
+      <c r="C9" s="68" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D9" s="67" t="inlineStr">
+      <c r="D9" s="68" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E9" s="67" t="inlineStr">
+      <c r="E9" s="68" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F9" s="67" t="inlineStr">
+      <c r="F9" s="68" t="inlineStr">
         <is>
           <t>Variety — +24% YoY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="65" t="inlineStr">
+      <c r="A10" s="66" t="inlineStr">
         <is>
           <t>Reported average creator earnings</t>
         </is>
       </c>
-      <c r="B10" s="66" t="n">
+      <c r="B10" s="67" t="n">
         <v>131</v>
       </c>
-      <c r="C10" s="67" t="inlineStr">
+      <c r="C10" s="68" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D10" s="67" t="inlineStr">
+      <c r="D10" s="68" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E10" s="67" t="inlineStr">
+      <c r="E10" s="68" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F10" s="67" t="inlineStr">
+      <c r="F10" s="68" t="inlineStr">
         <is>
           <t>Sci-Tech Today / ElectroIQ — after platform fees</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="65" t="inlineStr">
+      <c r="A11" s="66" t="inlineStr">
         <is>
           <t>Revenue concentration</t>
         </is>
       </c>
-      <c r="B11" s="68" t="n">
+      <c r="B11" s="69" t="n">
         <v>0.76</v>
       </c>
-      <c r="C11" s="67" t="inlineStr">
+      <c r="C11" s="68" t="inlineStr">
         <is>
           <t>share to top 0.1%</t>
         </is>
       </c>
-      <c r="D11" s="67" t="inlineStr">
+      <c r="D11" s="68" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E11" s="67" t="inlineStr">
+      <c r="E11" s="68" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F11" s="67" t="inlineStr">
+      <c r="F11" s="68" t="inlineStr">
         <is>
           <t>ElectroIQ — power-law distribution</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="65" t="inlineStr">
+      <c r="A12" s="66" t="inlineStr">
         <is>
           <t>Creators with &gt;=1 paying member</t>
         </is>
       </c>
-      <c r="B12" s="66" t="n">
+      <c r="B12" s="67" t="n">
         <v>286287</v>
       </c>
-      <c r="C12" s="67" t="inlineStr">
+      <c r="C12" s="68" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D12" s="67" t="inlineStr">
+      <c r="D12" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E12" s="67" t="inlineStr">
+      <c r="E12" s="68" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
       </c>
-      <c r="F12" s="67" t="inlineStr">
+      <c r="F12" s="68" t="inlineStr">
         <is>
           <t>Graphtreon</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="65" t="inlineStr">
+      <c r="A13" s="66" t="inlineStr">
         <is>
           <t>Active creators</t>
         </is>
       </c>
-      <c r="B13" s="66" t="n">
+      <c r="B13" s="67" t="n">
         <v>300000</v>
       </c>
-      <c r="C13" s="67" t="inlineStr">
+      <c r="C13" s="68" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D13" s="67" t="inlineStr">
+      <c r="D13" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E13" s="67" t="inlineStr">
+      <c r="E13" s="68" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F13" s="67" t="inlineStr">
+      <c r="F13" s="68" t="inlineStr">
         <is>
           <t>Jack Conte, Patreon</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="65" t="inlineStr">
+      <c r="A14" s="66" t="inlineStr">
         <is>
           <t>Active paying members</t>
         </is>
       </c>
-      <c r="B14" s="66" t="n">
+      <c r="B14" s="67" t="n">
         <v>10000000</v>
       </c>
-      <c r="C14" s="67" t="inlineStr">
+      <c r="C14" s="68" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D14" s="67" t="inlineStr">
+      <c r="D14" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E14" s="67" t="inlineStr">
+      <c r="E14" s="68" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F14" s="67" t="inlineStr">
+      <c r="F14" s="68" t="inlineStr">
         <is>
           <t>Patreon / Backlinko</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="65" t="inlineStr">
+      <c r="A15" s="66" t="inlineStr">
         <is>
           <t>Paid to creators annually</t>
         </is>
       </c>
-      <c r="B15" s="66" t="n">
+      <c r="B15" s="67" t="n">
         <v>2000000000</v>
       </c>
-      <c r="C15" s="67" t="inlineStr">
+      <c r="C15" s="68" t="inlineStr">
         <is>
           <t>USD/year</t>
         </is>
       </c>
-      <c r="D15" s="67" t="inlineStr">
+      <c r="D15" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E15" s="67" t="inlineStr">
+      <c r="E15" s="68" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F15" s="67" t="inlineStr">
+      <c r="F15" s="68" t="inlineStr">
         <is>
           <t>Patreon / Backlinko</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="65" t="inlineStr">
+      <c r="A16" s="66" t="inlineStr">
         <is>
           <t>Average monthly support per member</t>
         </is>
       </c>
-      <c r="B16" s="68" t="n">
+      <c r="B16" s="69" t="n">
         <v>6.1</v>
       </c>
-      <c r="C16" s="67" t="inlineStr">
+      <c r="C16" s="68" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D16" s="67" t="inlineStr">
+      <c r="D16" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E16" s="67" t="inlineStr">
+      <c r="E16" s="68" t="inlineStr">
         <is>
           <t>Aug 2024</t>
         </is>
       </c>
-      <c r="F16" s="67" t="inlineStr">
+      <c r="F16" s="68" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report; audit of ~1,200 creators</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="65" t="inlineStr">
+      <c r="A17" s="66" t="inlineStr">
         <is>
           <t>Typical patronage band (low)</t>
         </is>
       </c>
-      <c r="B17" s="68" t="n">
+      <c r="B17" s="69" t="n">
         <v>8</v>
       </c>
-      <c r="C17" s="67" t="inlineStr">
+      <c r="C17" s="68" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D17" s="67" t="inlineStr">
+      <c r="D17" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E17" s="67" t="inlineStr">
+      <c r="E17" s="68" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F17" s="67" t="inlineStr">
+      <c r="F17" s="68" t="inlineStr">
         <is>
           <t>Creator-economy benchmarks</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="65" t="inlineStr">
+      <c r="A18" s="66" t="inlineStr">
         <is>
           <t>Typical patronage band (high)</t>
         </is>
       </c>
-      <c r="B18" s="68" t="n">
+      <c r="B18" s="69" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="67" t="inlineStr">
+      <c r="C18" s="68" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D18" s="67" t="inlineStr">
+      <c r="D18" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E18" s="67" t="inlineStr">
+      <c r="E18" s="68" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F18" s="67" t="inlineStr">
+      <c r="F18" s="68" t="inlineStr">
         <is>
           <t>Creator-economy benchmarks</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="65" t="inlineStr">
+      <c r="A19" s="66" t="inlineStr">
         <is>
           <t>Monthly churn (low)</t>
         </is>
       </c>
-      <c r="B19" s="68" t="n">
+      <c r="B19" s="69" t="n">
         <v>0.1</v>
       </c>
-      <c r="C19" s="67" t="inlineStr">
+      <c r="C19" s="68" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D19" s="67" t="inlineStr">
+      <c r="D19" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E19" s="67" t="inlineStr">
+      <c r="E19" s="68" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F19" s="67" t="inlineStr">
+      <c r="F19" s="68" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="65" t="inlineStr">
+      <c r="A20" s="66" t="inlineStr">
         <is>
           <t>Monthly churn (high)</t>
         </is>
       </c>
-      <c r="B20" s="68" t="n">
+      <c r="B20" s="69" t="n">
         <v>0.15</v>
       </c>
-      <c r="C20" s="67" t="inlineStr">
+      <c r="C20" s="68" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D20" s="67" t="inlineStr">
+      <c r="D20" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E20" s="67" t="inlineStr">
+      <c r="E20" s="68" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F20" s="67" t="inlineStr">
+      <c r="F20" s="68" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="65" t="inlineStr">
+      <c r="A21" s="66" t="inlineStr">
         <is>
           <t>Annual-plan churn multiplier</t>
         </is>
       </c>
-      <c r="B21" s="68" t="n">
+      <c r="B21" s="69" t="n">
         <v>0.333</v>
       </c>
-      <c r="C21" s="67" t="inlineStr">
+      <c r="C21" s="68" t="inlineStr">
         <is>
           <t>x monthly churn</t>
         </is>
       </c>
-      <c r="D21" s="67" t="inlineStr">
+      <c r="D21" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E21" s="67" t="inlineStr">
+      <c r="E21" s="68" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F21" s="67" t="inlineStr">
+      <c r="F21" s="68" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report — annual patrons churn at 1/3 the rate</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="65" t="inlineStr">
+      <c r="A22" s="66" t="inlineStr">
         <is>
           <t>Creators with &gt;2,000 patrons</t>
         </is>
       </c>
-      <c r="B22" s="68" t="n">
+      <c r="B22" s="69" t="n">
         <v>0.003</v>
       </c>
-      <c r="C22" s="67" t="inlineStr">
+      <c r="C22" s="68" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D22" s="67" t="inlineStr">
+      <c r="D22" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E22" s="67" t="inlineStr">
+      <c r="E22" s="68" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F22" s="67" t="inlineStr">
+      <c r="F22" s="68" t="inlineStr">
         <is>
           <t>Graphtreon — power-law distribution</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="65" t="inlineStr">
+      <c r="A23" s="66" t="inlineStr">
         <is>
           <t>Division I athletes in network</t>
         </is>
       </c>
-      <c r="B23" s="66" t="n">
+      <c r="B23" s="67" t="n">
         <v>45000</v>
       </c>
-      <c r="C23" s="67" t="inlineStr">
+      <c r="C23" s="68" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D23" s="67" t="inlineStr">
+      <c r="D23" s="68" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E23" s="67" t="inlineStr">
+      <c r="E23" s="68" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F23" s="67" t="inlineStr">
+      <c r="F23" s="68" t="inlineStr">
         <is>
           <t>Publicis Groupe press release, 19 Aug 2026</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="65" t="inlineStr">
+      <c r="A24" s="66" t="inlineStr">
         <is>
           <t>Power Four universities</t>
         </is>
       </c>
-      <c r="B24" s="66" t="n">
+      <c r="B24" s="67" t="n">
         <v>68</v>
       </c>
-      <c r="C24" s="67" t="inlineStr">
+      <c r="C24" s="68" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D24" s="67" t="inlineStr">
+      <c r="D24" s="68" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E24" s="67" t="inlineStr">
+      <c r="E24" s="68" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F24" s="67" t="inlineStr">
+      <c r="F24" s="68" t="inlineStr">
         <is>
           <t>Publicis Groupe press release</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="65" t="inlineStr">
+      <c r="A25" s="66" t="inlineStr">
         <is>
           <t>Claimed speed-to-market gain</t>
         </is>
       </c>
-      <c r="B25" s="68" t="n">
+      <c r="B25" s="69" t="n">
         <v>0.6</v>
       </c>
-      <c r="C25" s="67" t="inlineStr">
+      <c r="C25" s="68" t="inlineStr">
         <is>
           <t>share faster</t>
         </is>
       </c>
-      <c r="D25" s="67" t="inlineStr">
+      <c r="D25" s="68" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E25" s="67" t="inlineStr">
+      <c r="E25" s="68" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F25" s="67" t="inlineStr">
+      <c r="F25" s="68" t="inlineStr">
         <is>
           <t>Publicis — stated 50-70% vs a traditional agency process</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="69" t="inlineStr">
+      <c r="A27" s="70" t="inlineStr">
         <is>
           <t>TAKE RATES - what each platform costs a creator</t>
         </is>
@@ -6829,16 +6834,16 @@
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="B29" s="70" t="n">
+      <c r="B29" s="71" t="n">
         <v>0.2</v>
       </c>
-      <c r="C29" s="71" t="n">
+      <c r="C29" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="71" t="n">
+      <c r="D29" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="72" t="inlineStr">
+      <c r="F29" s="73" t="inlineStr">
         <is>
           <t>Derived: 1.41bn / 7.22bn = 19.5% (filed accounts)</t>
         </is>
@@ -6850,16 +6855,16 @@
           <t>Fansly</t>
         </is>
       </c>
-      <c r="B30" s="70" t="n">
+      <c r="B30" s="71" t="n">
         <v>0.2</v>
       </c>
-      <c r="C30" s="71" t="n">
+      <c r="C30" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="71" t="n">
+      <c r="D30" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="72" t="inlineStr">
+      <c r="F30" s="73" t="inlineStr">
         <is>
           <t>Not published in terms; widely reported</t>
         </is>
@@ -6871,16 +6876,16 @@
           <t>Fanfix</t>
         </is>
       </c>
-      <c r="B31" s="70" t="n">
+      <c r="B31" s="71" t="n">
         <v>0.2</v>
       </c>
-      <c r="C31" s="71" t="n">
+      <c r="C31" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="71" t="n">
+      <c r="D31" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="72" t="inlineStr">
+      <c r="F31" s="73" t="inlineStr">
         <is>
           <t>Not published in terms; widely reported</t>
         </is>
@@ -6892,16 +6897,16 @@
           <t>Patreon</t>
         </is>
       </c>
-      <c r="B32" s="70" t="n">
+      <c r="B32" s="71" t="n">
         <v>0.1</v>
       </c>
-      <c r="C32" s="71" t="n">
+      <c r="C32" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="71" t="n">
+      <c r="D32" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="72" t="inlineStr">
+      <c r="F32" s="73" t="inlineStr">
         <is>
           <t>Published: 10% all-in, processing included</t>
         </is>
@@ -6913,16 +6918,16 @@
           <t>Passes</t>
         </is>
       </c>
-      <c r="B33" s="70" t="n">
+      <c r="B33" s="71" t="n">
         <v>0.1</v>
       </c>
-      <c r="C33" s="71" t="n">
+      <c r="C33" s="72" t="n">
         <v>0.3</v>
       </c>
-      <c r="D33" s="71" t="n">
+      <c r="D33" s="72" t="n">
         <v>29</v>
       </c>
-      <c r="F33" s="72" t="inlineStr">
+      <c r="F33" s="73" t="inlineStr">
         <is>
           <t>Sacra; Passes rebrand release Apr 2026</t>
         </is>
@@ -6934,23 +6939,23 @@
           <t>Stride (proposed)</t>
         </is>
       </c>
-      <c r="B34" s="70" t="n">
+      <c r="B34" s="71" t="n">
         <v>0.15</v>
       </c>
-      <c r="C34" s="71" t="n">
+      <c r="C34" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="71" t="n">
+      <c r="D34" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="72" t="inlineStr">
+      <c r="F34" s="73" t="inlineStr">
         <is>
           <t>Our decision — see MarketModel</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="69" t="inlineStr">
+      <c r="A36" s="70" t="inlineStr">
         <is>
           <t>INTERMEDIARIES the athlete already pays</t>
         </is>
@@ -6962,13 +6967,13 @@
           <t>Sports agent — endorsement</t>
         </is>
       </c>
-      <c r="B37" s="70" t="n">
+      <c r="B37" s="71" t="n">
         <v>0.1</v>
       </c>
-      <c r="C37" s="70" t="n">
+      <c r="C37" s="71" t="n">
         <v>0.2</v>
       </c>
-      <c r="F37" s="72" t="inlineStr">
+      <c r="F37" s="73" t="inlineStr">
         <is>
           <t>Unregulated; widely reported, no primary source</t>
         </is>
@@ -6980,13 +6985,13 @@
           <t>Sports agent — playing contract</t>
         </is>
       </c>
-      <c r="B38" s="70" t="n">
+      <c r="B38" s="71" t="n">
         <v>0.02</v>
       </c>
-      <c r="C38" s="70" t="n">
+      <c r="C38" s="71" t="n">
         <v>0.05</v>
       </c>
-      <c r="F38" s="72" t="inlineStr">
+      <c r="F38" s="73" t="inlineStr">
         <is>
           <t>NBPA reg. 4.B (Sept 2025); FIFA FFAR art. 15</t>
         </is>
@@ -6998,13 +7003,13 @@
           <t>OnlyFans management agency</t>
         </is>
       </c>
-      <c r="B39" s="70" t="n">
+      <c r="B39" s="71" t="n">
         <v>0.2</v>
       </c>
-      <c r="C39" s="70" t="n">
+      <c r="C39" s="71" t="n">
         <v>0.5</v>
       </c>
-      <c r="F39" s="72" t="inlineStr">
+      <c r="F39" s="73" t="inlineStr">
         <is>
           <t>Aruna Talent rate guide 2026 — on top of the 20%</t>
         </is>
@@ -7018,180 +7023,180 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="73" t="inlineStr">
+      <c r="A43" s="74" t="inlineStr">
         <is>
           <t>OnlyFans FY2024 filed accounts (Fenix International Ltd)</t>
         </is>
       </c>
-      <c r="B43" s="74" t="inlineStr">
+      <c r="B43" s="75" t="inlineStr">
         <is>
           <t>https://find-and-update.company-information.service.gov.uk/company/10354575/filing-history</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="73" t="inlineStr">
+      <c r="A44" s="74" t="inlineStr">
         <is>
           <t>OnlyFans FY2024 as reported</t>
         </is>
       </c>
-      <c r="B44" s="74" t="inlineStr">
+      <c r="B44" s="75" t="inlineStr">
         <is>
           <t>https://variety.com/2025/digital/news/onlyfans-fiscal-2024-revenue-earnings-1236495750/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="73" t="inlineStr">
+      <c r="A45" s="74" t="inlineStr">
         <is>
           <t>Patreon published take rate</t>
         </is>
       </c>
-      <c r="B45" s="74" t="inlineStr">
+      <c r="B45" s="75" t="inlineStr">
         <is>
           <t>https://www.patreon.com/pricing</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="73" t="inlineStr">
+      <c r="A46" s="74" t="inlineStr">
         <is>
           <t>Patreon creators</t>
         </is>
       </c>
-      <c r="B46" s="74" t="inlineStr">
+      <c r="B46" s="75" t="inlineStr">
         <is>
           <t>https://backlinko.com/patreon-users</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="73" t="inlineStr">
+      <c r="A47" s="74" t="inlineStr">
         <is>
           <t>Passes economics</t>
         </is>
       </c>
-      <c r="B47" s="74" t="inlineStr">
+      <c r="B47" s="75" t="inlineStr">
         <is>
           <t>https://sacra.com/c/passes/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="73" t="inlineStr">
+      <c r="A48" s="74" t="inlineStr">
         <is>
           <t>Fanfix creator terms (states no take rate)</t>
         </is>
       </c>
-      <c r="B48" s="74" t="inlineStr">
+      <c r="B48" s="75" t="inlineStr">
         <is>
           <t>https://auth.fanfix.io/creator-terms-of-use</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="73" t="inlineStr">
+      <c r="A49" s="74" t="inlineStr">
         <is>
           <t>Agency commissions</t>
         </is>
       </c>
-      <c r="B49" s="74" t="inlineStr">
+      <c r="B49" s="75" t="inlineStr">
         <is>
           <t>https://arunatalent.com/blog/onlyfans-agency-commission-rates/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="73" t="inlineStr">
+      <c r="A50" s="74" t="inlineStr">
         <is>
           <t>NBPA agent fee cap (amended Sept 2025)</t>
         </is>
       </c>
-      <c r="B50" s="74" t="inlineStr">
+      <c r="B50" s="75" t="inlineStr">
         <is>
           <t>https://imgix.cosmicjs.com/cd844850-97c7-11f0-91fa-d9e1671c2776-NBPA-REGULATIONS-GOVERNING-PLAYER-AGENTS-09-2025.pdf</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="73" t="inlineStr">
+      <c r="A51" s="74" t="inlineStr">
         <is>
           <t>FIFA Football Agent Regulations art. 15</t>
         </is>
       </c>
-      <c r="B51" s="74" t="inlineStr">
+      <c r="B51" s="75" t="inlineStr">
         <is>
           <t>https://digitalhub.fifa.com/m/1e7b741fa0fae779/original/FIFA-Football-Agent-Regulations.pdf</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="73" t="inlineStr">
+      <c r="A52" s="74" t="inlineStr">
         <is>
           <t>CJEU upholds the FIFA fee cap (16 Jul 2026)</t>
         </is>
       </c>
-      <c r="B52" s="74" t="inlineStr">
+      <c r="B52" s="75" t="inlineStr">
         <is>
           <t>https://inside.fifa.com/news/welcomes-court-of-justice-european-union-decision-football-agent-regulations</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="73" t="inlineStr">
+      <c r="A53" s="74" t="inlineStr">
         <is>
           <t>Eurobarometer 525</t>
         </is>
       </c>
-      <c r="B53" s="74" t="inlineStr">
+      <c r="B53" s="75" t="inlineStr">
         <is>
           <t>https://europa.eu/eurobarometer/surveys/detail/2668</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="73" t="inlineStr">
+      <c r="A54" s="74" t="inlineStr">
         <is>
           <t>FIP World Padel Report 2025</t>
         </is>
       </c>
-      <c r="B54" s="74" t="inlineStr">
+      <c r="B54" s="75" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/2025/12/online-the-fip-world-padel-report-2025-a-comprehensive-analysis-of-a-sport-in-constant-growth/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="73" t="inlineStr">
+      <c r="A55" s="74" t="inlineStr">
         <is>
           <t>Stripe EU pricing</t>
         </is>
       </c>
-      <c r="B55" s="74" t="inlineStr">
+      <c r="B55" s="75" t="inlineStr">
         <is>
           <t>https://stripe.com/es/pricing</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="73" t="inlineStr">
+      <c r="A56" s="74" t="inlineStr">
         <is>
           <t>TEKTA launch</t>
         </is>
       </c>
-      <c r="B56" s="74" t="inlineStr">
+      <c r="B56" s="75" t="inlineStr">
         <is>
           <t>https://www.publicisgroupe.com/en/news/press-releases/publicis-sports-and-travis-kelce-s-tekta-join-forces-to-reimagine-the-future-of-nil-marketing</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="73" t="inlineStr">
+      <c r="A57" s="74" t="inlineStr">
         <is>
           <t>Stripe Connect age</t>
         </is>
       </c>
-      <c r="B57" s="74" t="inlineStr">
+      <c r="B57" s="75" t="inlineStr">
         <is>
           <t>https://support.stripe.com/questions/age-requirement-to-create-a-stripe-account</t>
         </is>
@@ -7259,7 +7264,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="64" t="inlineStr">
         <is>
           <t>Each block starts from a published figure on Comparables and ends in a number the Assumptions sheet uses. Adjustment factors are blue because they are our judgement; everything else is a formula you can trace.</t>
         </is>
@@ -7317,7 +7322,7 @@
         <f>Comparables!B14</f>
         <v/>
       </c>
-      <c r="D6" s="75" t="inlineStr">
+      <c r="D6" s="76" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -7333,7 +7338,7 @@
         <f>Comparables!B12</f>
         <v/>
       </c>
-      <c r="D7" s="75" t="inlineStr">
+      <c r="D7" s="76" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -7349,7 +7354,7 @@
         <f>B6/B7</f>
         <v/>
       </c>
-      <c r="D8" s="75" t="inlineStr">
+      <c r="D8" s="76" t="inlineStr">
         <is>
           <t>The single most useful benchmark we found: it is measured, not modelled.</t>
         </is>
@@ -7365,7 +7370,7 @@
         <f>Comparables!B9/Comparables!B8</f>
         <v/>
       </c>
-      <c r="D9" s="75" t="inlineStr">
+      <c r="D9" s="76" t="inlineStr">
         <is>
           <t>Fan ACCOUNTS, not paying fans - most follow free. Shown as an upper bound only.</t>
         </is>
@@ -7380,7 +7385,7 @@
       <c r="B10" s="24" t="n">
         <v>1.06</v>
       </c>
-      <c r="D10" s="75" t="inlineStr">
+      <c r="D10" s="76" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: +6% on the Patreon benchmark. Sport audiences are smaller but convert better, because the fan usually does the sport themselves.</t>
         </is>
@@ -7395,7 +7400,7 @@
       <c r="B11" s="24" t="n">
         <v>1.37</v>
       </c>
-      <c r="D11" s="75" t="inlineStr">
+      <c r="D11" s="76" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: +37%. Much larger followings, much weaker conversion - more paying fans in absolute terms even though a smaller share converts.</t>
         </is>
@@ -7407,11 +7412,11 @@
           <t>→ Niche fans per athlete, mature</t>
         </is>
       </c>
-      <c r="B12" s="76">
+      <c r="B12" s="77">
         <f>B8*B10</f>
         <v/>
       </c>
-      <c r="D12" s="75" t="inlineStr"/>
+      <c r="D12" s="76" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -7419,11 +7424,11 @@
           <t>→ Popular fans per athlete, mature</t>
         </is>
       </c>
-      <c r="B13" s="76">
+      <c r="B13" s="77">
         <f>B8*B11</f>
         <v/>
       </c>
-      <c r="D13" s="75" t="inlineStr"/>
+      <c r="D13" s="76" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -7444,7 +7449,7 @@
       <c r="B15" s="20" t="n">
         <v>4.99</v>
       </c>
-      <c r="D15" s="75" t="inlineStr"/>
+      <c r="D15" s="76" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
@@ -7455,7 +7460,7 @@
       <c r="B16" s="20" t="n">
         <v>9.99</v>
       </c>
-      <c r="D16" s="75" t="inlineStr"/>
+      <c r="D16" s="76" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
@@ -7466,7 +7471,7 @@
       <c r="B17" s="20" t="n">
         <v>24.99</v>
       </c>
-      <c r="D17" s="75" t="inlineStr"/>
+      <c r="D17" s="76" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
@@ -7477,7 +7482,7 @@
       <c r="B18" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="D18" s="75" t="inlineStr">
+      <c r="D18" s="76" t="inlineStr">
         <is>
           <t>Assumed distribution; replace with the real tier mix after P1.</t>
         </is>
@@ -7492,7 +7497,7 @@
       <c r="B19" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="D19" s="75" t="inlineStr"/>
+      <c r="D19" s="76" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="13" t="inlineStr">
@@ -7503,7 +7508,7 @@
       <c r="B20" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="D20" s="75" t="inlineStr"/>
+      <c r="D20" s="76" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
@@ -7515,7 +7520,7 @@
         <f>B18+B19+B20</f>
         <v/>
       </c>
-      <c r="D21" s="75" t="inlineStr"/>
+      <c r="D21" s="76" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -7523,11 +7528,11 @@
           <t>→ Weighted ARPU per month</t>
         </is>
       </c>
-      <c r="B22" s="77">
+      <c r="B22" s="78">
         <f>B15*B18+B16*B19+B17*B20</f>
         <v/>
       </c>
-      <c r="D22" s="75" t="inlineStr">
+      <c r="D22" s="76" t="inlineStr">
         <is>
           <t>Cross-check: Patreon reports $6.10 average support and a $8-12 typical band. Landing inside that band from an independent tier build is a good sign.</t>
         </is>
@@ -7543,7 +7548,7 @@
         <f>Comparables!B16</f>
         <v/>
       </c>
-      <c r="D23" s="75" t="inlineStr">
+      <c r="D23" s="76" t="inlineStr">
         <is>
           <t>Published average - below our figure because Patreon's long tail includes many $1-3 tiers. Our EUR 9.49 sits inside their $8-12 typical band.</t>
         </is>
@@ -7558,7 +7563,7 @@
       <c r="B24" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="75" t="inlineStr">
+      <c r="D24" s="76" t="inlineStr">
         <is>
           <t>Niche fans buy knowledge and sit at the tier mix above.</t>
         </is>
@@ -7573,7 +7578,7 @@
       <c r="B25" s="24" t="n">
         <v>0.87</v>
       </c>
-      <c r="D25" s="75" t="inlineStr">
+      <c r="D25" s="76" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: -13%. Popular-sport fans skew to the cheapest tier.</t>
         </is>
@@ -7585,11 +7590,11 @@
           <t>→ Niche ARPU, mature</t>
         </is>
       </c>
-      <c r="B26" s="77">
+      <c r="B26" s="78">
         <f>B22*B24</f>
         <v/>
       </c>
-      <c r="D26" s="75" t="inlineStr"/>
+      <c r="D26" s="76" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -7597,11 +7602,11 @@
           <t>→ Popular ARPU, mature</t>
         </is>
       </c>
-      <c r="B27" s="77">
+      <c r="B27" s="78">
         <f>B22*B25</f>
         <v/>
       </c>
-      <c r="D27" s="75" t="inlineStr"/>
+      <c r="D27" s="76" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -7623,7 +7628,7 @@
         <f>Comparables!B19</f>
         <v/>
       </c>
-      <c r="D29" s="75" t="inlineStr"/>
+      <c r="D29" s="76" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="13" t="inlineStr">
@@ -7635,7 +7640,7 @@
         <f>Comparables!B20</f>
         <v/>
       </c>
-      <c r="D30" s="75" t="inlineStr"/>
+      <c r="D30" s="76" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="13" t="inlineStr">
@@ -7647,7 +7652,7 @@
         <f>(B29+B30)/2</f>
         <v/>
       </c>
-      <c r="D31" s="75" t="inlineStr"/>
+      <c r="D31" s="76" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="13" t="inlineStr">
@@ -7659,7 +7664,7 @@
         <f>Comparables!B21</f>
         <v/>
       </c>
-      <c r="D32" s="75" t="inlineStr">
+      <c r="D32" s="76" t="inlineStr">
         <is>
           <t>Patreon: annual patrons churn at one third the monthly rate.</t>
         </is>
@@ -7674,7 +7679,7 @@
       <c r="B33" s="16" t="n">
         <v>0.3</v>
       </c>
-      <c r="D33" s="75" t="inlineStr">
+      <c r="D33" s="76" t="inlineStr">
         <is>
           <t>Our target for the season pass. This is the one lever that improves churn without changing the product.</t>
         </is>
@@ -7690,7 +7695,7 @@
         <f>B31*(1-B33)+B31*B32*B33</f>
         <v/>
       </c>
-      <c r="D34" s="75" t="inlineStr">
+      <c r="D34" s="76" t="inlineStr">
         <is>
           <t>What a Patreon-like platform would see with our annual mix.</t>
         </is>
@@ -7705,7 +7710,7 @@
       <c r="B35" s="24" t="n">
         <v>0.55</v>
       </c>
-      <c r="D35" s="75" t="inlineStr">
+      <c r="D35" s="76" t="inlineStr">
         <is>
           <t>OUR CLAIM, UNTESTED, AND THE MOST OPTIMISTIC JUDGEMENT IN THE MODEL: this says niche fans churn 45% SLOWER than the Patreon benchmark, because training content is habitual and competitive seasons create renewal moments. Nothing yet proves it. If it is wrong and we are merely at benchmark, Y10 revenue falls by roughly EUR 7M.</t>
         </is>
@@ -7720,7 +7725,7 @@
       <c r="B36" s="24" t="n">
         <v>0.85</v>
       </c>
-      <c r="D36" s="75" t="inlineStr">
+      <c r="D36" s="76" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: 15% better than benchmark. Impulse follows after a result, with many free substitutes - but still a sport fan rather than a general creator audience.</t>
         </is>
@@ -7732,11 +7737,11 @@
           <t>→ Niche churn, mature</t>
         </is>
       </c>
-      <c r="B37" s="78">
+      <c r="B37" s="79">
         <f>B34*B35</f>
         <v/>
       </c>
-      <c r="D37" s="75" t="inlineStr"/>
+      <c r="D37" s="76" t="inlineStr"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -7744,11 +7749,11 @@
           <t>→ Popular churn, mature</t>
         </is>
       </c>
-      <c r="B38" s="78">
+      <c r="B38" s="79">
         <f>B34*B36</f>
         <v/>
       </c>
-      <c r="D38" s="75" t="inlineStr"/>
+      <c r="D38" s="76" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -7770,7 +7775,7 @@
         <f>Comparables!B7/Comparables!B8/12</f>
         <v/>
       </c>
-      <c r="D40" s="75" t="inlineStr">
+      <c r="D40" s="76" t="inlineStr">
         <is>
           <t>Includes dormant accounts, so this is a floor.</t>
         </is>
@@ -7786,7 +7791,7 @@
         <f>Comparables!B15/Comparables!B12/12</f>
         <v/>
       </c>
-      <c r="D41" s="75" t="inlineStr">
+      <c r="D41" s="76" t="inlineStr">
         <is>
           <t>Denominator is creators WITH members, so this is a ceiling.</t>
         </is>
@@ -7798,11 +7803,11 @@
           <t>Stride: modelled niche athlete, mature</t>
         </is>
       </c>
-      <c r="B42" s="77">
+      <c r="B42" s="78">
         <f>B12*B22*(1-Assumptions!$C$40)</f>
         <v/>
       </c>
-      <c r="D42" s="75" t="inlineStr">
+      <c r="D42" s="76" t="inlineStr">
         <is>
           <t>Ours sits between the two, which is where a plausible figure should sit.</t>
         </is>
@@ -7818,7 +7823,7 @@
         <f>Comparables!B11</f>
         <v/>
       </c>
-      <c r="D43" s="75" t="inlineStr">
+      <c r="D43" s="76" t="inlineStr">
         <is>
           <t>THE CAVEAT ON EVERY AVERAGE ABOVE: earnings follow a power law. Totals are unaffected, but the median athlete earns far less than the mean. Do not pitch the mean to an athlete.</t>
         </is>
@@ -7843,7 +7848,7 @@
       <c r="B45" s="24" t="n">
         <v>0.92</v>
       </c>
-      <c r="D45" s="75" t="inlineStr">
+      <c r="D45" s="76" t="inlineStr">
         <is>
           <t>Comparables are published in USD; this model is in EUR. Applied to the per-transaction and monthly creator fees below.</t>
         </is>
@@ -7858,7 +7863,7 @@
       <c r="B46" s="20" t="n">
         <v>300</v>
       </c>
-      <c r="D46" s="75" t="inlineStr">
+      <c r="D46" s="76" t="inlineStr">
         <is>
           <t>Change this to see who is cheapest at any revenue level.</t>
         </is>
@@ -7874,7 +7879,7 @@
         <f>B46*(1-Comparables!B29)-B46/Assumptions!$C$48*Comparables!C29*B45-Comparables!D29*B45</f>
         <v/>
       </c>
-      <c r="D47" s="75" t="inlineStr">
+      <c r="D47" s="76" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -7890,7 +7895,7 @@
         <f>B46*(1-Comparables!B32)-B46/Assumptions!$C$48*Comparables!C32*B45-Comparables!D32*B45</f>
         <v/>
       </c>
-      <c r="D48" s="75" t="inlineStr">
+      <c r="D48" s="76" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -7906,7 +7911,7 @@
         <f>B46*(1-Comparables!B33)-B46/Assumptions!$C$48*Comparables!C33*B45-Comparables!D33*B45</f>
         <v/>
       </c>
-      <c r="D49" s="75" t="inlineStr">
+      <c r="D49" s="76" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -7922,7 +7927,7 @@
         <f>B46*(1-Comparables!B34)-B46/Assumptions!$C$48*Comparables!C34*B45-Comparables!D34*B45</f>
         <v/>
       </c>
-      <c r="D50" s="75" t="inlineStr">
+      <c r="D50" s="76" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -7938,7 +7943,7 @@
         <f>Comparables!D33*B45/((Comparables!B34-Comparables!B33)-Comparables!C33*B45/Assumptions!$C$48)</f>
         <v/>
       </c>
-      <c r="D51" s="75" t="inlineStr">
+      <c r="D51" s="76" t="inlineStr">
         <is>
           <t>Below this, our flat 15% pays the athlete more than Passes' 10% plus fees. Our modelled athlete earns far less than this, so the long tail is on our side of the line.</t>
         </is>
@@ -7960,10 +7965,10 @@
           <t>Population, 34 countries in scope</t>
         </is>
       </c>
-      <c r="B53" s="79" t="n">
+      <c r="B53" s="80" t="n">
         <v>2726.2</v>
       </c>
-      <c r="D53" s="75" t="inlineStr">
+      <c r="D53" s="76" t="inlineStr">
         <is>
           <t>Millions. Eurostat / national statistics offices.</t>
         </is>
@@ -7975,10 +7980,10 @@
           <t>Population, Spain</t>
         </is>
       </c>
-      <c r="B54" s="79" t="n">
+      <c r="B54" s="80" t="n">
         <v>48.6</v>
       </c>
-      <c r="D54" s="75" t="inlineStr">
+      <c r="D54" s="76" t="inlineStr">
         <is>
           <t>Millions.</t>
         </is>
@@ -7993,7 +7998,7 @@
       <c r="B55" s="16" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D55" s="75" t="inlineStr">
+      <c r="D55" s="76" t="inlineStr">
         <is>
           <t>Eurobarometer 525 - Spain sits near the EU average of 55% who exercise at all.</t>
         </is>
@@ -8008,7 +8013,7 @@
       <c r="B56" s="16" t="n">
         <v>0.02</v>
       </c>
-      <c r="D56" s="75" t="inlineStr">
+      <c r="D56" s="76" t="inlineStr">
         <is>
           <t>OUR ESTIMATE: competes, posts publicly, has a following worth sponsoring.</t>
         </is>
@@ -8023,7 +8028,7 @@
       <c r="B57" s="16" t="n">
         <v>0.25</v>
       </c>
-      <c r="D57" s="75" t="inlineStr">
+      <c r="D57" s="76" t="inlineStr">
         <is>
           <t>OUR ESTIMATE: would monetise if the tooling existed.</t>
         </is>
@@ -8035,11 +8040,11 @@
           <t>→ Addressable athletes, Spain</t>
         </is>
       </c>
-      <c r="B58" s="80">
+      <c r="B58" s="81">
         <f>B54*1000000*B55*B56*B57</f>
         <v/>
       </c>
-      <c r="D58" s="75" t="inlineStr"/>
+      <c r="D58" s="76" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -8047,11 +8052,11 @@
           <t>→ Addressable athletes, all 34 countries</t>
         </is>
       </c>
-      <c r="B59" s="80">
+      <c r="B59" s="81">
         <f>B53*1000000*0.5*B56*B57</f>
         <v/>
       </c>
-      <c r="D59" s="75" t="inlineStr">
+      <c r="D59" s="76" t="inlineStr">
         <is>
           <t>Using a 50% blended participation rate across the 34 countries.</t>
         </is>
@@ -8067,7 +8072,7 @@
         <f>Assumptions!$L$5</f>
         <v/>
       </c>
-      <c r="D60" s="75" t="inlineStr"/>
+      <c r="D60" s="76" t="inlineStr"/>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -8075,11 +8080,11 @@
           <t>→ Y10 penetration of Spain SAM</t>
         </is>
       </c>
-      <c r="B61" s="78">
+      <c r="B61" s="79">
         <f>Assumptions!$L$5/B58</f>
         <v/>
       </c>
-      <c r="D61" s="75" t="inlineStr"/>
+      <c r="D61" s="76" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -8087,11 +8092,11 @@
           <t>→ Y10 penetration of full TAM</t>
         </is>
       </c>
-      <c r="B62" s="78">
+      <c r="B62" s="79">
         <f>Assumptions!$L$5/B59</f>
         <v/>
       </c>
-      <c r="D62" s="75" t="inlineStr">
+      <c r="D62" s="76" t="inlineStr">
         <is>
           <t>If this reads as implausibly high, the athlete trajectory is too aggressive - that is exactly what this block exists to reveal.</t>
         </is>
@@ -8135,44 +8140,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="64" t="inlineStr">
         <is>
           <t>SOURCED = published figure | BENCHMARKED = set against named comparables | DERIVED = computed from other assumptions | ESTIMATE = judgement, no benchmark yet</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="81" t="inlineStr">
+      <c r="A4" s="82" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B4" s="81" t="inlineStr">
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>Model value</t>
         </is>
       </c>
-      <c r="C4" s="81" t="inlineStr">
+      <c r="C4" s="82" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="D4" s="81" t="inlineStr">
+      <c r="D4" s="82" t="inlineStr">
         <is>
           <t>Benchmark / comparable</t>
         </is>
       </c>
-      <c r="E4" s="81" t="inlineStr">
+      <c r="E4" s="82" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F4" s="81" t="inlineStr">
+      <c r="F4" s="82" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="G4" s="81" t="inlineStr">
+      <c r="G4" s="82" t="inlineStr">
         <is>
           <t>What would replace the estimate</t>
         </is>
@@ -8192,7 +8197,7 @@
       <c r="G5" s="12" t="n"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="82" t="inlineStr">
+      <c r="A6" s="83" t="inlineStr">
         <is>
           <t>Take rate on fan revenue</t>
         </is>
@@ -8201,34 +8206,34 @@
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
-      <c r="C6" s="83" t="inlineStr">
+      <c r="C6" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D6" s="84" t="inlineStr">
+      <c r="D6" s="85" t="inlineStr">
         <is>
           <t>Passes charges 10% but adds $0.30/txn and a $29/month creator fee; OnlyFans, Fansly and Fanfix are all 20%; Patreon 8-12%. A flat 15% with no monthly fee pays an athlete more than Passes for anyone under EUR 1,380/month of fan revenue.</t>
         </is>
       </c>
-      <c r="E6" s="84" t="inlineStr">
+      <c r="E6" s="85" t="inlineStr">
         <is>
           <t>Sacra company profile (Passes); Passes rebrand release, Apr 2026; MEXC platform comparison 2026</t>
         </is>
       </c>
-      <c r="F6" s="85" t="inlineStr">
+      <c r="F6" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G6" s="84" t="inlineStr">
+      <c r="G6" s="85" t="inlineStr">
         <is>
           <t>Nothing. This is a pricing decision and the comparables are public.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="82" t="inlineStr">
+      <c r="A7" s="83" t="inlineStr">
         <is>
           <t>Take rate on sponsorship</t>
         </is>
@@ -8237,101 +8242,101 @@
         <f>Assumptions!$C$41</f>
         <v/>
       </c>
-      <c r="C7" s="83" t="inlineStr">
+      <c r="C7" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D7" s="84" t="inlineStr">
+      <c r="D7" s="85" t="inlineStr">
         <is>
           <t>Sports agents take 10-20% of an endorsement and 4-10% of a playing contract. On OnlyFans, management agencies take a further 20-50% on top of the platform's 20%.</t>
         </is>
       </c>
-      <c r="E7" s="84" t="inlineStr">
+      <c r="E7" s="85" t="inlineStr">
         <is>
           <t>Oreate and Sapling agent-commission surveys; Aruna Talent agency rate guide 2026</t>
         </is>
       </c>
-      <c r="F7" s="85" t="inlineStr">
+      <c r="F7" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G7" s="84" t="inlineStr">
+      <c r="G7" s="85" t="inlineStr">
         <is>
           <t>Observed deal data once the marketplace is running.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="82" t="inlineStr">
+      <c r="A8" s="83" t="inlineStr">
         <is>
           <t>Suggested tiers 4.99 / 9.99 / 24.99</t>
         </is>
       </c>
-      <c r="B8" s="86" t="inlineStr">
+      <c r="B8" s="87" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C8" s="83" t="inlineStr">
+      <c r="C8" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D8" s="84" t="inlineStr">
+      <c r="D8" s="85" t="inlineStr">
         <is>
           <t>Patreon's typical patronage is quoted at $8-12/month, so the EUR 9.99 anchor sits inside the observed band. EUR 4.99 retains only 54% of our take after payment fees, against 71% at EUR 9.99 — which is why the floor matters more than the take rate.</t>
         </is>
       </c>
-      <c r="E8" s="84" t="inlineStr">
+      <c r="E8" s="85" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report; independent audits of ~1,200 creators</t>
         </is>
       </c>
-      <c r="F8" s="87" t="inlineStr">
+      <c r="F8" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G8" s="84" t="inlineStr">
+      <c r="G8" s="85" t="inlineStr">
         <is>
           <t>Our own tier mix after P1.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="82" t="inlineStr">
+      <c r="A9" s="83" t="inlineStr">
         <is>
           <t>Season pass / annual billing</t>
         </is>
       </c>
-      <c r="B9" s="86" t="inlineStr">
+      <c r="B9" s="87" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C9" s="88" t="inlineStr">
+      <c r="C9" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D9" s="84" t="inlineStr">
+      <c r="D9" s="85" t="inlineStr">
         <is>
           <t>Patreon reports that annual patrons churn at ONE THIRD the rate of monthly patrons. This is the single strongest piece of evidence in the plan for pushing annual billing.</t>
         </is>
       </c>
-      <c r="E9" s="84" t="inlineStr">
+      <c r="E9" s="85" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
-      <c r="F9" s="85" t="inlineStr">
+      <c r="F9" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G9" s="84" t="inlineStr">
+      <c r="G9" s="85" t="inlineStr">
         <is>
           <t>Already strong. Confirm on our own cohorts.</t>
         </is>
@@ -8351,7 +8356,7 @@
       <c r="G10" s="12" t="n"/>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="82" t="inlineStr">
+      <c r="A11" s="83" t="inlineStr">
         <is>
           <t>Fan ARPU per month</t>
         </is>
@@ -8360,34 +8365,34 @@
         <f>Assumptions!$C$12</f>
         <v/>
       </c>
-      <c r="C11" s="83" t="inlineStr">
+      <c r="C11" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D11" s="84" t="inlineStr">
+      <c r="D11" s="85" t="inlineStr">
         <is>
           <t>Patreon's average monthly support rose from $5.40 to $6.10 during 2024, with typical patronage quoted at $8-12. Our EUR 8.00-9.50 sits in the upper-middle of that range.</t>
         </is>
       </c>
-      <c r="E11" s="84" t="inlineStr">
+      <c r="E11" s="85" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
-      <c r="F11" s="87" t="inlineStr">
+      <c r="F11" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G11" s="84" t="inlineStr">
+      <c r="G11" s="85" t="inlineStr">
         <is>
           <t>Actual ARPU by tier and sport after P1.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="82" t="inlineStr">
+      <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Fan churn per month</t>
         </is>
@@ -8396,34 +8401,34 @@
         <f>Assumptions!$C$13</f>
         <v/>
       </c>
-      <c r="C12" s="89" t="inlineStr">
+      <c r="C12" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D12" s="84" t="inlineStr">
+      <c r="D12" s="85" t="inlineStr">
         <is>
           <t>OPTIMISTIC AGAINST BENCHMARK. Patreon runs 10-15% monthly. We assume 6-9% (niche) and 9-13% (popular), arguing that training content is habitual and that competitive seasons create natural renewal moments. That argument is currently untested.</t>
         </is>
       </c>
-      <c r="E12" s="84" t="inlineStr">
+      <c r="E12" s="85" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report (10-15%/month)</t>
         </is>
       </c>
-      <c r="F12" s="90" t="inlineStr">
+      <c r="F12" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G12" s="84" t="inlineStr">
+      <c r="G12" s="85" t="inlineStr">
         <is>
           <t>THE most important number to measure in P1. Three months of real cohorts settles it. Until then the conservative case should be treated as the plan.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="82" t="inlineStr">
+      <c r="A13" s="83" t="inlineStr">
         <is>
           <t>Paying fans per monetising athlete</t>
         </is>
@@ -8432,34 +8437,34 @@
         <f>Assumptions!$C$11</f>
         <v/>
       </c>
-      <c r="C13" s="91" t="inlineStr">
+      <c r="C13" s="92" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D13" s="84" t="inlineStr">
+      <c r="D13" s="85" t="inlineStr">
         <is>
           <t>20 rising to 48 over ten years. Cross-check: Patreon creators average $350/month and our modelled niche athlete at maturity earns about EUR 313/month — closely aligned, which is reassuring for an assumption built bottom-up rather than from a comparable.</t>
         </is>
       </c>
-      <c r="E13" s="84" t="inlineStr">
+      <c r="E13" s="85" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report (creator average $350/month)</t>
         </is>
       </c>
-      <c r="F13" s="87" t="inlineStr">
+      <c r="F13" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G13" s="84" t="inlineStr">
+      <c r="G13" s="85" t="inlineStr">
         <is>
           <t>Observed fans per athlete, banded by follower count.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="82" t="inlineStr">
+      <c r="A14" s="83" t="inlineStr">
         <is>
           <t>Share of athletes who monetise</t>
         </is>
@@ -8468,64 +8473,64 @@
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="C14" s="89" t="inlineStr">
+      <c r="C14" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D14" s="84" t="inlineStr">
+      <c r="D14" s="85" t="inlineStr">
         <is>
           <t>28% rising to 50% for niche sports. No direct comparable exists — neither Patreon nor OnlyFans publishes activation rates for creators who sign up but never charge.</t>
         </is>
       </c>
-      <c r="E14" s="84" t="inlineStr">
+      <c r="E14" s="85" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="F14" s="90" t="inlineStr">
+      <c r="F14" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G14" s="84" t="inlineStr">
+      <c r="G14" s="85" t="inlineStr">
         <is>
           <t>Our own activation funnel, available from P1 onward.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="82" t="inlineStr">
+      <c r="A15" s="83" t="inlineStr">
         <is>
           <t>Fan acquisition capacity</t>
         </is>
       </c>
-      <c r="B15" s="86" t="inlineStr">
+      <c r="B15" s="87" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C15" s="89" t="inlineStr">
+      <c r="C15" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D15" s="84" t="inlineStr">
+      <c r="D15" s="85" t="inlineStr">
         <is>
           <t>An athlete can recruit 30-69 new paying fans a year depending on segment. This ceiling is what makes churn bite in the model: without it, higher churn perversely RAISED revenue, because the year-end target was reachable at any churn rate.</t>
         </is>
       </c>
-      <c r="E15" s="84" t="inlineStr">
+      <c r="E15" s="85" t="inlineStr">
         <is>
           <t>None — introduced to fix a modelling flaw found by stress testing</t>
         </is>
       </c>
-      <c r="F15" s="90" t="inlineStr">
+      <c r="F15" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G15" s="84" t="inlineStr">
+      <c r="G15" s="85" t="inlineStr">
         <is>
           <t>Observed gross adds per athlete per year.</t>
         </is>
@@ -8545,7 +8550,7 @@
       <c r="G16" s="12" t="n"/>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="82" t="inlineStr">
+      <c r="A17" s="83" t="inlineStr">
         <is>
           <t>PSP percentage fee</t>
         </is>
@@ -8554,34 +8559,34 @@
         <f>Assumptions!$C$44</f>
         <v/>
       </c>
-      <c r="C17" s="88" t="inlineStr">
+      <c r="C17" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D17" s="84" t="inlineStr">
+      <c r="D17" s="85" t="inlineStr">
         <is>
           <t>Stripe for a Spanish entity: 1.5% + EUR 0.25 on EEA domestic cards, 2.5% on UK cards, 3.25% on non-EEA. 1.9% is the blend for a mostly-European fan base. CORRECTION: an earlier version of this model used the US headline of 2.9% and overstated the largest cost line in the business by about a third.</t>
         </is>
       </c>
-      <c r="E17" s="84" t="inlineStr">
+      <c r="E17" s="85" t="inlineStr">
         <is>
           <t>Stripe published EU/EEA pricing, 2026</t>
         </is>
       </c>
-      <c r="F17" s="85" t="inlineStr">
+      <c r="F17" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G17" s="84" t="inlineStr">
+      <c r="G17" s="85" t="inlineStr">
         <is>
           <t>Interchange-plus terms become negotiable above roughly EUR 5M processed.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="82" t="inlineStr">
+      <c r="A18" s="83" t="inlineStr">
         <is>
           <t>PSP fixed fee per transaction</t>
         </is>
@@ -8590,34 +8595,34 @@
         <f>Assumptions!$C$45</f>
         <v/>
       </c>
-      <c r="C18" s="88" t="inlineStr">
+      <c r="C18" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D18" s="84" t="inlineStr">
+      <c r="D18" s="85" t="inlineStr">
         <is>
           <t>EUR 0.25 per transaction. On a EUR 4.99 tier that single fee is a third of our take, which is why the tier floor and annual billing move more margin than the take rate does.</t>
         </is>
       </c>
-      <c r="E18" s="84" t="inlineStr">
+      <c r="E18" s="85" t="inlineStr">
         <is>
           <t>Stripe published pricing, 2026</t>
         </is>
       </c>
-      <c r="F18" s="85" t="inlineStr">
+      <c r="F18" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G18" s="84" t="inlineStr">
+      <c r="G18" s="85" t="inlineStr">
         <is>
           <t>Volume renegotiation; annual billing turns twelve fees into one.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="82" t="inlineStr">
+      <c r="A19" s="83" t="inlineStr">
         <is>
           <t>Payout fees</t>
         </is>
@@ -8626,27 +8631,27 @@
         <f>Assumptions!$C$46</f>
         <v/>
       </c>
-      <c r="C19" s="88" t="inlineStr">
+      <c r="C19" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D19" s="84" t="inlineStr">
+      <c r="D19" s="85" t="inlineStr">
         <is>
           <t>Stripe Connect Express: roughly 0.25% + EUR 0.25 per payout, plus a monthly active-account fee that is not modelled as a separate line.</t>
         </is>
       </c>
-      <c r="E19" s="84" t="inlineStr">
+      <c r="E19" s="85" t="inlineStr">
         <is>
           <t>Stripe Connect pricing, 2026</t>
         </is>
       </c>
-      <c r="F19" s="87" t="inlineStr">
+      <c r="F19" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G19" s="84" t="inlineStr">
+      <c r="G19" s="85" t="inlineStr">
         <is>
           <t>Actual payout frequency once athletes are onboarded.</t>
         </is>
@@ -8666,118 +8671,118 @@
       <c r="G20" s="12" t="n"/>
     </row>
     <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="82" t="inlineStr">
+      <c r="A21" s="83" t="inlineStr">
         <is>
           <t>Sport participation by country</t>
         </is>
       </c>
-      <c r="B21" s="86" t="inlineStr">
+      <c r="B21" s="87" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C21" s="88" t="inlineStr">
+      <c r="C21" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D21" s="84" t="inlineStr">
+      <c r="D21" s="85" t="inlineStr">
         <is>
           <t>Eurobarometer 525, share who NEVER exercise: Finland 8%, Sweden 12%, Denmark 20%, Poland 65%, Greece 68%, Portugal 73%, EU-27 average 45%. Six of the 34 countries in the index are measured; the other 28 are estimates placed inside that distribution.</t>
         </is>
       </c>
-      <c r="E21" s="84" t="inlineStr">
+      <c r="E21" s="85" t="inlineStr">
         <is>
           <t>Special Eurobarometer 525, Sport and Physical Activity, September 2022</t>
         </is>
       </c>
-      <c r="F21" s="85" t="inlineStr">
+      <c r="F21" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G21" s="84" t="inlineStr">
+      <c r="G21" s="85" t="inlineStr">
         <is>
           <t>Federation licence counts — published annually and free (CSD in Spain).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="82" t="inlineStr">
+      <c r="A22" s="83" t="inlineStr">
         <is>
           <t>Padel market size</t>
         </is>
       </c>
-      <c r="B22" s="86" t="inlineStr">
+      <c r="B22" s="87" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C22" s="88" t="inlineStr">
+      <c r="C22" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D22" s="84" t="inlineStr">
+      <c r="D22" s="85" t="inlineStr">
         <is>
           <t>Spain has ~6.0M active players (12.7% of the population), 109,040 federation licences and 17,300+ courts; globally 35M+ players and 77,000+ courts. This is the clearest case for weighting a sport regionally rather than globally — padel scores 77.7 in Spain and 45.1 worldwide.</t>
         </is>
       </c>
-      <c r="E22" s="84" t="inlineStr">
+      <c r="E22" s="85" t="inlineStr">
         <is>
           <t>FIP World Padel Report 2025</t>
         </is>
       </c>
-      <c r="F22" s="85" t="inlineStr">
+      <c r="F22" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G22" s="84" t="inlineStr">
+      <c r="G22" s="85" t="inlineStr">
         <is>
           <t>Annual FIP refresh.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="82" t="inlineStr">
+      <c r="A23" s="83" t="inlineStr">
         <is>
           <t>Sports fandom by country</t>
         </is>
       </c>
-      <c r="B23" s="86" t="inlineStr">
+      <c r="B23" s="87" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C23" s="89" t="inlineStr">
+      <c r="C23" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D23" s="84" t="inlineStr">
+      <c r="D23" s="85" t="inlineStr">
         <is>
           <t>The weakest layer of the sport index, and it drives both the `demand` and `appetite` signals. Commercial audience panels (Nielsen Sports, YouGov) cost more than the entire Y1-Y2 analytics budget.</t>
         </is>
       </c>
-      <c r="E23" s="84" t="inlineStr">
+      <c r="E23" s="85" t="inlineStr">
         <is>
           <t>None — reasoned estimates only</t>
         </is>
       </c>
-      <c r="F23" s="90" t="inlineStr">
+      <c r="F23" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G23" s="84" t="inlineStr">
+      <c r="G23" s="85" t="inlineStr">
         <is>
           <t>Our own engagement data per sport per country once connectors are live. This is what makes the index self-improving rather than something anyone could copy.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="82" t="inlineStr">
+      <c r="A24" s="83" t="inlineStr">
         <is>
           <t>Athlete count trajectory</t>
         </is>
@@ -8786,27 +8791,27 @@
         <f>Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="C24" s="89" t="inlineStr">
+      <c r="C24" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D24" s="84" t="inlineStr">
+      <c r="D24" s="85" t="inlineStr">
         <is>
           <t>400 rising to 40,000 over ten years. This is the PLAN, not a benchmark: marketing spend is derived from it at segment CAC, not the other way round. Everything in the model scales off this line.</t>
         </is>
       </c>
-      <c r="E24" s="84" t="inlineStr">
+      <c r="E24" s="85" t="inlineStr">
         <is>
           <t>None — it is a target</t>
         </is>
       </c>
-      <c r="F24" s="90" t="inlineStr">
+      <c r="F24" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G24" s="84" t="inlineStr">
+      <c r="G24" s="85" t="inlineStr">
         <is>
           <t>The pre-seed gate tests it directly: 400 athletes and EUR 10k MRR.</t>
         </is>
@@ -8826,7 +8831,7 @@
       <c r="G25" s="12" t="n"/>
     </row>
     <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="82" t="inlineStr">
+      <c r="A26" s="83" t="inlineStr">
         <is>
           <t>Athlete CAC</t>
         </is>
@@ -8835,34 +8840,34 @@
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="C26" s="89" t="inlineStr">
+      <c r="C26" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D26" s="84" t="inlineStr">
+      <c r="D26" s="85" t="inlineStr">
         <is>
           <t>EUR 16-36 for niche, EUR 40-88 for popular. The gap reflects displacing an existing agent relationship versus reaching someone with no representation at all. No published comparable exists for athlete acquisition in this segment.</t>
         </is>
       </c>
-      <c r="E26" s="84" t="inlineStr">
+      <c r="E26" s="85" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="F26" s="90" t="inlineStr">
+      <c r="F26" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G26" s="84" t="inlineStr">
+      <c r="G26" s="85" t="inlineStr">
         <is>
           <t>Measured CAC by channel from the first federation partnership.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="82" t="inlineStr">
+      <c r="A27" s="83" t="inlineStr">
         <is>
           <t>Admission rate, direct applicants</t>
         </is>
@@ -8871,34 +8876,34 @@
         <f>Assumptions!$C$76</f>
         <v/>
       </c>
-      <c r="C27" s="91" t="inlineStr">
+      <c r="C27" s="92" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D27" s="84" t="inlineStr">
+      <c r="D27" s="85" t="inlineStr">
         <is>
           <t>20% of direct applicants are admitted, 25% go to a human, 40% are refused and 15% never finish the form. Not a judgement: it is the ops-load output of scripts/admission_stress.py run over the admission policy itself, so retuning a threshold moves this figure. The sweep asserts the model and the policy stay in step and fails if they drift.</t>
         </is>
       </c>
-      <c r="E27" s="84" t="inlineStr">
+      <c r="E27" s="85" t="inlineStr">
         <is>
           <t>scripts/admission_stress.py, section 7 — over a modelled applicant mix</t>
         </is>
       </c>
-      <c r="F27" s="87" t="inlineStr">
+      <c r="F27" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G27" s="84" t="inlineStr">
+      <c r="G27" s="85" t="inlineStr">
         <is>
           <t>Real intake data. The mix the sweep assumes is the soft part, not the arithmetic.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="82" t="inlineStr">
+      <c r="A28" s="83" t="inlineStr">
         <is>
           <t>Admission rate, club-nominated</t>
         </is>
@@ -8907,34 +8912,34 @@
         <f>Assumptions!$C$78</f>
         <v/>
       </c>
-      <c r="C28" s="89" t="inlineStr">
+      <c r="C28" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D28" s="84" t="inlineStr">
+      <c r="D28" s="85" t="inlineStr">
         <is>
           <t>45% admitted against 20% direct. A verified club's nomination confers a credibility floor of 0.75 x its own legitimacy score, which carries a completed application over the admit line that would otherwise have gone to review. It cannot carry an empty one — no club can supply someone else's date of birth — so the uplift is real but bounded.</t>
         </is>
       </c>
-      <c r="E28" s="84" t="inlineStr">
+      <c r="E28" s="85" t="inlineStr">
         <is>
           <t>None — the mechanism is built and tested, the conversion is not yet measured</t>
         </is>
       </c>
-      <c r="F28" s="90" t="inlineStr">
+      <c r="F28" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G28" s="84" t="inlineStr">
+      <c r="G28" s="85" t="inlineStr">
         <is>
           <t>The first federation partnership: nominated applicants are tagged, so this is measurable from day one of it.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="82" t="inlineStr">
+      <c r="A29" s="83" t="inlineStr">
         <is>
           <t>Athlete verification cost</t>
         </is>
@@ -8943,34 +8948,34 @@
         <f>Assumptions!$C$81</f>
         <v/>
       </c>
-      <c r="C29" s="91" t="inlineStr">
+      <c r="C29" s="92" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D29" s="84" t="inlineStr">
+      <c r="D29" s="85" t="inlineStr">
         <is>
           <t>Four minutes per manual review, priced at the same loaded salary the People line uses, over 1,700 productive hours. Peaks at EUR 47k and 0.64 reviewer-FTE in Y10, which is the finding rather than the cost: verification is not a money problem at this scale. The reason to automate it is latency — an athlete sitting in the queue is not listed, not matchable and not earning.</t>
         </is>
       </c>
-      <c r="E29" s="84" t="inlineStr">
+      <c r="E29" s="85" t="inlineStr">
         <is>
           <t>Derived from the sweep's review volume and the model's own salary line</t>
         </is>
       </c>
-      <c r="F29" s="87" t="inlineStr">
+      <c r="F29" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G29" s="84" t="inlineStr">
+      <c r="G29" s="85" t="inlineStr">
         <is>
           <t>Timing real reviews. Four minutes is an estimate of a mechanical task.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="82" t="inlineStr">
+      <c r="A30" s="83" t="inlineStr">
         <is>
           <t>Athlete CAC vs the funnel</t>
         </is>
@@ -8979,34 +8984,34 @@
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="C30" s="89" t="inlineStr">
+      <c r="C30" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D30" s="84" t="inlineStr">
+      <c r="D30" s="85" t="inlineStr">
         <is>
           <t>Deliberately NOT multiplied by the admission funnel. Segment CAC is defined as the cost of landing one athlete ON the platform, so scaling it by 1/admission-rate would charge the same money twice. The Costs sheet carries a memo line showing what that CAC works out to per application (EUR 3.40 in Y1 rising to EUR 22) — the figure to hold against what a channel actually charges per name reached.</t>
         </is>
       </c>
-      <c r="E30" s="84" t="inlineStr">
+      <c r="E30" s="85" t="inlineStr">
         <is>
           <t>None — this is a definitional choice, made explicit so it is not silently reversed</t>
         </is>
       </c>
-      <c r="F30" s="90" t="inlineStr">
+      <c r="F30" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G30" s="84" t="inlineStr">
+      <c r="G30" s="85" t="inlineStr">
         <is>
           <t>Channel-level spend against applications, which the funnel now records.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="82" t="inlineStr">
+      <c r="A31" s="83" t="inlineStr">
         <is>
           <t>Loaded salary, Spain</t>
         </is>
@@ -9015,34 +9020,34 @@
         <f>Assumptions!$C$61</f>
         <v/>
       </c>
-      <c r="C31" s="83" t="inlineStr">
+      <c r="C31" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D31" s="84" t="inlineStr">
+      <c r="D31" s="85" t="inlineStr">
         <is>
           <t>EUR 38k-76k loaded. Spanish employer social security adds roughly 31% on top of gross, so a senior engineer at ~EUR 55k gross costs ~EUR 72k — around half the London equivalent, which is a real argument for being in Spain rather than an accident of geography.</t>
         </is>
       </c>
-      <c r="E31" s="84" t="inlineStr">
+      <c r="E31" s="85" t="inlineStr">
         <is>
           <t>Spanish Seguridad Social employer contribution rates</t>
         </is>
       </c>
-      <c r="F31" s="87" t="inlineStr">
+      <c r="F31" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G31" s="84" t="inlineStr">
+      <c r="G31" s="85" t="inlineStr">
         <is>
           <t>Actual offers accepted.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="82" t="inlineStr">
+      <c r="A32" s="83" t="inlineStr">
         <is>
           <t>AWS infrastructure</t>
         </is>
@@ -9051,34 +9056,34 @@
         <f>Assumptions!$C$52</f>
         <v/>
       </c>
-      <c r="C32" s="83" t="inlineStr">
+      <c r="C32" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D32" s="84" t="inlineStr">
+      <c r="D32" s="85" t="inlineStr">
         <is>
           <t>Built up per stage from list prices: Fargate, RDS then Aurora, ElastiCache, S3, MediaConvert, CloudWatch. Reserved capacity and Savings Plans (25-40%) are deliberately excluded and treated as upside.</t>
         </is>
       </c>
-      <c r="E32" s="84" t="inlineStr">
+      <c r="E32" s="85" t="inlineStr">
         <is>
           <t>AWS published list pricing, 2026</t>
         </is>
       </c>
-      <c r="F32" s="87" t="inlineStr">
+      <c r="F32" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G32" s="84" t="inlineStr">
+      <c r="G32" s="85" t="inlineStr">
         <is>
           <t>Actual bills; commit to Savings Plans once usage is stable.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="82" t="inlineStr">
+      <c r="A33" s="83" t="inlineStr">
         <is>
           <t>Media egress</t>
         </is>
@@ -9087,34 +9092,34 @@
         <f>Assumptions!$C$54</f>
         <v/>
       </c>
-      <c r="C33" s="88" t="inlineStr">
+      <c r="C33" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D33" s="84" t="inlineStr">
+      <c r="D33" s="85" t="inlineStr">
         <is>
           <t>EUR 0.008/GB behind a zero-egress object store versus EUR 0.075/GB at CloudFront list price. At Y10 volumes that single architectural choice is worth over EUR 1M a year — the largest cost decision in the plan that is settled by engineering rather than negotiation.</t>
         </is>
       </c>
-      <c r="E33" s="84" t="inlineStr">
+      <c r="E33" s="85" t="inlineStr">
         <is>
           <t>Cloudflare R2 and Backblaze B2 pricing; AWS CloudFront list price</t>
         </is>
       </c>
-      <c r="F33" s="85" t="inlineStr">
+      <c r="F33" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G33" s="84" t="inlineStr">
+      <c r="G33" s="85" t="inlineStr">
         <is>
           <t>Nothing. Both are published.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="82" t="inlineStr">
+      <c r="A34" s="83" t="inlineStr">
         <is>
           <t>Moderation cost</t>
         </is>
@@ -9123,27 +9128,27 @@
         <f>Assumptions!$C$56</f>
         <v/>
       </c>
-      <c r="C34" s="89" t="inlineStr">
+      <c r="C34" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D34" s="84" t="inlineStr">
+      <c r="D34" s="85" t="inlineStr">
         <is>
           <t>EUR 22 per 1,000 items reviewed, on a hybrid of automated classification and human review. Vendor pricing varies widely with SLA and content type.</t>
         </is>
       </c>
-      <c r="E34" s="84" t="inlineStr">
+      <c r="E34" s="85" t="inlineStr">
         <is>
           <t>None cited</t>
         </is>
       </c>
-      <c r="F34" s="90" t="inlineStr">
+      <c r="F34" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G34" s="84" t="inlineStr">
+      <c r="G34" s="85" t="inlineStr">
         <is>
           <t>Vendor quotes once P2 scope is fixed.</t>
         </is>
@@ -9163,7 +9168,7 @@
       <c r="G35" s="12" t="n"/>
     </row>
     <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="82" t="inlineStr">
+      <c r="A36" s="83" t="inlineStr">
         <is>
           <t>Corporate tax rates</t>
         </is>
@@ -9172,34 +9177,34 @@
         <f>Assumptions!$C$71</f>
         <v/>
       </c>
-      <c r="C36" s="88" t="inlineStr">
+      <c r="C36" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D36" s="84" t="inlineStr">
+      <c r="D36" s="85" t="inlineStr">
         <is>
           <t>15% for the first four profitable years under the Spanish Startup Law, then the 25% standard rate. Modelled with loss carryforward against the Y1-Y4 losses.</t>
         </is>
       </c>
-      <c r="E36" s="84" t="inlineStr">
+      <c r="E36" s="85" t="inlineStr">
         <is>
           <t>Ley de Startups (Spain); Impuesto sobre Sociedades</t>
         </is>
       </c>
-      <c r="F36" s="85" t="inlineStr">
+      <c r="F36" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G36" s="84" t="inlineStr">
+      <c r="G36" s="85" t="inlineStr">
         <is>
           <t>Confirm eligibility with a Spanish tax adviser before filing.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="82" t="inlineStr">
+      <c r="A37" s="83" t="inlineStr">
         <is>
           <t>Risk-free rate</t>
         </is>
@@ -9208,34 +9213,34 @@
         <f>Assumptions!$C$88</f>
         <v/>
       </c>
-      <c r="C37" s="88" t="inlineStr">
+      <c r="C37" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D37" s="84" t="inlineStr">
+      <c r="D37" s="85" t="inlineStr">
         <is>
           <t>Spanish 10-year sovereign yield, ~3.2% in mid-2026. Used as the floor for the founder opportunity-cost calculation rather than as the discount rate.</t>
         </is>
       </c>
-      <c r="E37" s="84" t="inlineStr">
+      <c r="E37" s="85" t="inlineStr">
         <is>
           <t>Spanish 10Y government bond yield</t>
         </is>
       </c>
-      <c r="F37" s="85" t="inlineStr">
+      <c r="F37" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G37" s="84" t="inlineStr">
+      <c r="G37" s="85" t="inlineStr">
         <is>
           <t>Refresh at the date of any raise.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
-      <c r="A38" s="82" t="inlineStr">
+      <c r="A38" s="83" t="inlineStr">
         <is>
           <t>WACC / discount rate</t>
         </is>
@@ -9244,34 +9249,34 @@
         <f>Assumptions!$C$85</f>
         <v/>
       </c>
-      <c r="C38" s="83" t="inlineStr">
+      <c r="C38" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D38" s="84" t="inlineStr">
+      <c r="D38" s="85" t="inlineStr">
         <is>
           <t>25%. The conventional range for pre-revenue to early-revenue venture is 20-35% and we sit mid-range. The sensitivity grid runs 18-30% precisely because this is arguable rather than knowable.</t>
         </is>
       </c>
-      <c r="E38" s="84" t="inlineStr">
+      <c r="E38" s="85" t="inlineStr">
         <is>
           <t>Standard venture valuation practice</t>
         </is>
       </c>
-      <c r="F38" s="87" t="inlineStr">
+      <c r="F38" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G38" s="84" t="inlineStr">
+      <c r="G38" s="85" t="inlineStr">
         <is>
           <t>An actual term sheet prices this for you.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="82" t="inlineStr">
+      <c r="A39" s="83" t="inlineStr">
         <is>
           <t>Exit revenue multiple</t>
         </is>
@@ -9280,34 +9285,34 @@
         <f>Assumptions!$C$87</f>
         <v/>
       </c>
-      <c r="C39" s="83" t="inlineStr">
+      <c r="C39" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D39" s="84" t="inlineStr">
+      <c r="D39" s="85" t="inlineStr">
         <is>
           <t>6.5x blended. Marketplace comparables trade around 4x revenue and high-growth SaaS around 9x; our Y10 mix is roughly 55% marketplace take and 12% SaaS.</t>
         </is>
       </c>
-      <c r="E39" s="84" t="inlineStr">
+      <c r="E39" s="85" t="inlineStr">
         <is>
           <t>Public marketplace and SaaS trading multiples</t>
         </is>
       </c>
-      <c r="F39" s="87" t="inlineStr">
+      <c r="F39" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G39" s="84" t="inlineStr">
+      <c r="G39" s="85" t="inlineStr">
         <is>
           <t>Comparable private transactions nearer an exit.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="82" t="inlineStr">
+      <c r="A40" s="83" t="inlineStr">
         <is>
           <t>Terminal growth</t>
         </is>
@@ -9316,27 +9321,27 @@
         <f>Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="C40" s="83" t="inlineStr">
+      <c r="C40" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D40" s="84" t="inlineStr">
+      <c r="D40" s="85" t="inlineStr">
         <is>
           <t>3%, approximating long-run nominal GDP. Ten explicit forecast years were chosen partly so this assumption carries less of the valuation than it would at Y7.</t>
         </is>
       </c>
-      <c r="E40" s="84" t="inlineStr">
+      <c r="E40" s="85" t="inlineStr">
         <is>
           <t>Standard DCF convention</t>
         </is>
       </c>
-      <c r="F40" s="87" t="inlineStr">
+      <c r="F40" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G40" s="84" t="inlineStr">
+      <c r="G40" s="85" t="inlineStr">
         <is>
           <t>Nothing — it is a convention, and the grid shows its effect.</t>
         </is>
@@ -9356,112 +9361,112 @@
       <c r="G41" s="12" t="n"/>
     </row>
     <row r="42" ht="58" customHeight="1">
-      <c r="A42" s="82" t="inlineStr">
+      <c r="A42" s="83" t="inlineStr">
         <is>
           <t>Payout age floor</t>
         </is>
       </c>
-      <c r="B42" s="86" t="inlineStr">
+      <c r="B42" s="87" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C42" s="88" t="inlineStr">
+      <c r="C42" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D42" s="84" t="inlineStr">
+      <c r="D42" s="85" t="inlineStr">
         <is>
           <t>Stripe Express and Custom Connect require 18. Standard Connect allows 13+, but a legal guardian must own the account and hold the bank account the money lands in.</t>
         </is>
       </c>
-      <c r="E42" s="84" t="inlineStr">
+      <c r="E42" s="85" t="inlineStr">
         <is>
           <t>Stripe Connect documentation</t>
         </is>
       </c>
-      <c r="F42" s="85" t="inlineStr">
+      <c r="F42" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G42" s="84" t="inlineStr">
+      <c r="G42" s="85" t="inlineStr">
         <is>
           <t>Nothing — it is a hard platform rule.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
-      <c r="A43" s="82" t="inlineStr">
+      <c r="A43" s="83" t="inlineStr">
         <is>
           <t>Digital consent age, Spain</t>
         </is>
       </c>
-      <c r="B43" s="86" t="inlineStr">
+      <c r="B43" s="87" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C43" s="88" t="inlineStr">
+      <c r="C43" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D43" s="84" t="inlineStr">
+      <c r="D43" s="85" t="inlineStr">
         <is>
           <t>14 today under LOPDGDD Art. 7. A draft Organic Law on the Protection of Minors in Digital Environments would raise it to 16 and make age verification mandatory — which is why 16 is the forward-compatible floor for an account.</t>
         </is>
       </c>
-      <c r="E43" s="84" t="inlineStr">
+      <c r="E43" s="85" t="inlineStr">
         <is>
           <t>LOPDGDD Art. 7; draft Organic Law, Council of Ministers, March 2025</t>
         </is>
       </c>
-      <c r="F43" s="85" t="inlineStr">
+      <c r="F43" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G43" s="84" t="inlineStr">
+      <c r="G43" s="85" t="inlineStr">
         <is>
           <t>Track the bill through Parliament.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="92" t="inlineStr">
+      <c r="A45" s="93" t="inlineStr">
         <is>
           <t>THE THREE ASSUMPTIONS MOST LIKELY TO BE WRONG</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="93" t="inlineStr">
+      <c r="A46" s="94" t="inlineStr">
         <is>
           <t>1. Fan churn. We assume 6-13%/month; Patreon reports 10-15%. If Patreon is right, Y10 revenue falls from about EUR 58M to EUR 51M and the capital requirement roughly doubles.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="93" t="inlineStr">
+      <c r="A47" s="94" t="inlineStr">
         <is>
           <t>2. Athlete count. The trajectory is a target, not a forecast, and everything scales off it.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="93" t="inlineStr">
+      <c r="A48" s="94" t="inlineStr">
         <is>
           <t>3. Share of athletes who monetise. No published comparable exists at all.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="94" t="inlineStr"/>
+      <c r="A49" s="95" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="94" t="inlineStr">
+      <c r="A50" s="95" t="inlineStr">
         <is>
           <t>All three are answered by the same thing: three months of real cohort data from P1.</t>
         </is>
@@ -9510,7 +9515,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="64" t="inlineStr">
         <is>
           <t>Each pair is the Python model's figure and the workbook's own calculation. VARIANCE must be zero — if a formula is wrong, it shows up here on open.</t>
         </is>
@@ -9731,43 +9736,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C7" s="95">
+      <c r="C7" s="96">
         <f>ROUND(C6-C5,0)</f>
         <v/>
       </c>
-      <c r="D7" s="95">
+      <c r="D7" s="96">
         <f>ROUND(D6-D5,0)</f>
         <v/>
       </c>
-      <c r="E7" s="95">
+      <c r="E7" s="96">
         <f>ROUND(E6-E5,0)</f>
         <v/>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="96">
         <f>ROUND(F6-F5,0)</f>
         <v/>
       </c>
-      <c r="G7" s="95">
+      <c r="G7" s="96">
         <f>ROUND(G6-G5,0)</f>
         <v/>
       </c>
-      <c r="H7" s="95">
+      <c r="H7" s="96">
         <f>ROUND(H6-H5,0)</f>
         <v/>
       </c>
-      <c r="I7" s="95">
+      <c r="I7" s="96">
         <f>ROUND(I6-I5,0)</f>
         <v/>
       </c>
-      <c r="J7" s="95">
+      <c r="J7" s="96">
         <f>ROUND(J6-J5,0)</f>
         <v/>
       </c>
-      <c r="K7" s="95">
+      <c r="K7" s="96">
         <f>ROUND(K6-K5,0)</f>
         <v/>
       </c>
-      <c r="L7" s="95">
+      <c r="L7" s="96">
         <f>ROUND(L6-L5,0)</f>
         <v/>
       </c>
@@ -9895,43 +9900,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C12" s="95">
+      <c r="C12" s="96">
         <f>ROUND(C11-C10,0)</f>
         <v/>
       </c>
-      <c r="D12" s="95">
+      <c r="D12" s="96">
         <f>ROUND(D11-D10,0)</f>
         <v/>
       </c>
-      <c r="E12" s="95">
+      <c r="E12" s="96">
         <f>ROUND(E11-E10,0)</f>
         <v/>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="96">
         <f>ROUND(F11-F10,0)</f>
         <v/>
       </c>
-      <c r="G12" s="95">
+      <c r="G12" s="96">
         <f>ROUND(G11-G10,0)</f>
         <v/>
       </c>
-      <c r="H12" s="95">
+      <c r="H12" s="96">
         <f>ROUND(H11-H10,0)</f>
         <v/>
       </c>
-      <c r="I12" s="95">
+      <c r="I12" s="96">
         <f>ROUND(I11-I10,0)</f>
         <v/>
       </c>
-      <c r="J12" s="95">
+      <c r="J12" s="96">
         <f>ROUND(J11-J10,0)</f>
         <v/>
       </c>
-      <c r="K12" s="95">
+      <c r="K12" s="96">
         <f>ROUND(K11-K10,0)</f>
         <v/>
       </c>
-      <c r="L12" s="95">
+      <c r="L12" s="96">
         <f>ROUND(L11-L10,0)</f>
         <v/>
       </c>
@@ -10059,43 +10064,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C17" s="95">
+      <c r="C17" s="96">
         <f>ROUND(C16-C15,0)</f>
         <v/>
       </c>
-      <c r="D17" s="95">
+      <c r="D17" s="96">
         <f>ROUND(D16-D15,0)</f>
         <v/>
       </c>
-      <c r="E17" s="95">
+      <c r="E17" s="96">
         <f>ROUND(E16-E15,0)</f>
         <v/>
       </c>
-      <c r="F17" s="95">
+      <c r="F17" s="96">
         <f>ROUND(F16-F15,0)</f>
         <v/>
       </c>
-      <c r="G17" s="95">
+      <c r="G17" s="96">
         <f>ROUND(G16-G15,0)</f>
         <v/>
       </c>
-      <c r="H17" s="95">
+      <c r="H17" s="96">
         <f>ROUND(H16-H15,0)</f>
         <v/>
       </c>
-      <c r="I17" s="95">
+      <c r="I17" s="96">
         <f>ROUND(I16-I15,0)</f>
         <v/>
       </c>
-      <c r="J17" s="95">
+      <c r="J17" s="96">
         <f>ROUND(J16-J15,0)</f>
         <v/>
       </c>
-      <c r="K17" s="95">
+      <c r="K17" s="96">
         <f>ROUND(K16-K15,0)</f>
         <v/>
       </c>
-      <c r="L17" s="95">
+      <c r="L17" s="96">
         <f>ROUND(L16-L15,0)</f>
         <v/>
       </c>
@@ -10223,43 +10228,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C22" s="95">
+      <c r="C22" s="96">
         <f>ROUND(C21-C20,0)</f>
         <v/>
       </c>
-      <c r="D22" s="95">
+      <c r="D22" s="96">
         <f>ROUND(D21-D20,0)</f>
         <v/>
       </c>
-      <c r="E22" s="95">
+      <c r="E22" s="96">
         <f>ROUND(E21-E20,0)</f>
         <v/>
       </c>
-      <c r="F22" s="95">
+      <c r="F22" s="96">
         <f>ROUND(F21-F20,0)</f>
         <v/>
       </c>
-      <c r="G22" s="95">
+      <c r="G22" s="96">
         <f>ROUND(G21-G20,0)</f>
         <v/>
       </c>
-      <c r="H22" s="95">
+      <c r="H22" s="96">
         <f>ROUND(H21-H20,0)</f>
         <v/>
       </c>
-      <c r="I22" s="95">
+      <c r="I22" s="96">
         <f>ROUND(I21-I20,0)</f>
         <v/>
       </c>
-      <c r="J22" s="95">
+      <c r="J22" s="96">
         <f>ROUND(J21-J20,0)</f>
         <v/>
       </c>
-      <c r="K22" s="95">
+      <c r="K22" s="96">
         <f>ROUND(K21-K20,0)</f>
         <v/>
       </c>
-      <c r="L22" s="95">
+      <c r="L22" s="96">
         <f>ROUND(L21-L20,0)</f>
         <v/>
       </c>
@@ -10387,43 +10392,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C27" s="95">
+      <c r="C27" s="96">
         <f>ROUND(C26-C25,0)</f>
         <v/>
       </c>
-      <c r="D27" s="95">
+      <c r="D27" s="96">
         <f>ROUND(D26-D25,0)</f>
         <v/>
       </c>
-      <c r="E27" s="95">
+      <c r="E27" s="96">
         <f>ROUND(E26-E25,0)</f>
         <v/>
       </c>
-      <c r="F27" s="95">
+      <c r="F27" s="96">
         <f>ROUND(F26-F25,0)</f>
         <v/>
       </c>
-      <c r="G27" s="95">
+      <c r="G27" s="96">
         <f>ROUND(G26-G25,0)</f>
         <v/>
       </c>
-      <c r="H27" s="95">
+      <c r="H27" s="96">
         <f>ROUND(H26-H25,0)</f>
         <v/>
       </c>
-      <c r="I27" s="95">
+      <c r="I27" s="96">
         <f>ROUND(I26-I25,0)</f>
         <v/>
       </c>
-      <c r="J27" s="95">
+      <c r="J27" s="96">
         <f>ROUND(J26-J25,0)</f>
         <v/>
       </c>
-      <c r="K27" s="95">
+      <c r="K27" s="96">
         <f>ROUND(K26-K25,0)</f>
         <v/>
       </c>
-      <c r="L27" s="95">
+      <c r="L27" s="96">
         <f>ROUND(L26-L25,0)</f>
         <v/>
       </c>
@@ -10551,43 +10556,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C32" s="96">
+      <c r="C32" s="97">
         <f>ROUND(C31-C30,0)</f>
         <v/>
       </c>
-      <c r="D32" s="96">
+      <c r="D32" s="97">
         <f>ROUND(D31-D30,0)</f>
         <v/>
       </c>
-      <c r="E32" s="96">
+      <c r="E32" s="97">
         <f>ROUND(E31-E30,0)</f>
         <v/>
       </c>
-      <c r="F32" s="96">
+      <c r="F32" s="97">
         <f>ROUND(F31-F30,0)</f>
         <v/>
       </c>
-      <c r="G32" s="96">
+      <c r="G32" s="97">
         <f>ROUND(G31-G30,0)</f>
         <v/>
       </c>
-      <c r="H32" s="96">
+      <c r="H32" s="97">
         <f>ROUND(H31-H30,0)</f>
         <v/>
       </c>
-      <c r="I32" s="96">
+      <c r="I32" s="97">
         <f>ROUND(I31-I30,0)</f>
         <v/>
       </c>
-      <c r="J32" s="96">
+      <c r="J32" s="97">
         <f>ROUND(J31-J30,0)</f>
         <v/>
       </c>
-      <c r="K32" s="96">
+      <c r="K32" s="97">
         <f>ROUND(K31-K30,0)</f>
         <v/>
       </c>
-      <c r="L32" s="96">
+      <c r="L32" s="97">
         <f>ROUND(L31-L30,0)</f>
         <v/>
       </c>
@@ -10715,43 +10720,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C37" s="96">
+      <c r="C37" s="97">
         <f>ROUND(C36-C35,0)</f>
         <v/>
       </c>
-      <c r="D37" s="96">
+      <c r="D37" s="97">
         <f>ROUND(D36-D35,0)</f>
         <v/>
       </c>
-      <c r="E37" s="96">
+      <c r="E37" s="97">
         <f>ROUND(E36-E35,0)</f>
         <v/>
       </c>
-      <c r="F37" s="96">
+      <c r="F37" s="97">
         <f>ROUND(F36-F35,0)</f>
         <v/>
       </c>
-      <c r="G37" s="96">
+      <c r="G37" s="97">
         <f>ROUND(G36-G35,0)</f>
         <v/>
       </c>
-      <c r="H37" s="96">
+      <c r="H37" s="97">
         <f>ROUND(H36-H35,0)</f>
         <v/>
       </c>
-      <c r="I37" s="96">
+      <c r="I37" s="97">
         <f>ROUND(I36-I35,0)</f>
         <v/>
       </c>
-      <c r="J37" s="96">
+      <c r="J37" s="97">
         <f>ROUND(J36-J35,0)</f>
         <v/>
       </c>
-      <c r="K37" s="96">
+      <c r="K37" s="97">
         <f>ROUND(K36-K35,0)</f>
         <v/>
       </c>
-      <c r="L37" s="96">
+      <c r="L37" s="97">
         <f>ROUND(L36-L35,0)</f>
         <v/>
       </c>
@@ -10879,43 +10884,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C42" s="95">
+      <c r="C42" s="96">
         <f>ROUND(C41-C40,0)</f>
         <v/>
       </c>
-      <c r="D42" s="95">
+      <c r="D42" s="96">
         <f>ROUND(D41-D40,0)</f>
         <v/>
       </c>
-      <c r="E42" s="95">
+      <c r="E42" s="96">
         <f>ROUND(E41-E40,0)</f>
         <v/>
       </c>
-      <c r="F42" s="95">
+      <c r="F42" s="96">
         <f>ROUND(F41-F40,0)</f>
         <v/>
       </c>
-      <c r="G42" s="95">
+      <c r="G42" s="96">
         <f>ROUND(G41-G40,0)</f>
         <v/>
       </c>
-      <c r="H42" s="95">
+      <c r="H42" s="96">
         <f>ROUND(H41-H40,0)</f>
         <v/>
       </c>
-      <c r="I42" s="95">
+      <c r="I42" s="96">
         <f>ROUND(I41-I40,0)</f>
         <v/>
       </c>
-      <c r="J42" s="95">
+      <c r="J42" s="96">
         <f>ROUND(J41-J40,0)</f>
         <v/>
       </c>
-      <c r="K42" s="95">
+      <c r="K42" s="96">
         <f>ROUND(K41-K40,0)</f>
         <v/>
       </c>
-      <c r="L42" s="95">
+      <c r="L42" s="96">
         <f>ROUND(L41-L40,0)</f>
         <v/>
       </c>
@@ -11043,43 +11048,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C47" s="96">
+      <c r="C47" s="97">
         <f>ROUND(C46-C45,0)</f>
         <v/>
       </c>
-      <c r="D47" s="96">
+      <c r="D47" s="97">
         <f>ROUND(D46-D45,0)</f>
         <v/>
       </c>
-      <c r="E47" s="96">
+      <c r="E47" s="97">
         <f>ROUND(E46-E45,0)</f>
         <v/>
       </c>
-      <c r="F47" s="96">
+      <c r="F47" s="97">
         <f>ROUND(F46-F45,0)</f>
         <v/>
       </c>
-      <c r="G47" s="96">
+      <c r="G47" s="97">
         <f>ROUND(G46-G45,0)</f>
         <v/>
       </c>
-      <c r="H47" s="96">
+      <c r="H47" s="97">
         <f>ROUND(H46-H45,0)</f>
         <v/>
       </c>
-      <c r="I47" s="96">
+      <c r="I47" s="97">
         <f>ROUND(I46-I45,0)</f>
         <v/>
       </c>
-      <c r="J47" s="96">
+      <c r="J47" s="97">
         <f>ROUND(J46-J45,0)</f>
         <v/>
       </c>
-      <c r="K47" s="96">
+      <c r="K47" s="97">
         <f>ROUND(K46-K45,0)</f>
         <v/>
       </c>
-      <c r="L47" s="96">
+      <c r="L47" s="97">
         <f>ROUND(L46-L45,0)</f>
         <v/>
       </c>
@@ -11207,43 +11212,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C52" s="96">
+      <c r="C52" s="97">
         <f>ROUND(C51-C50,0)</f>
         <v/>
       </c>
-      <c r="D52" s="96">
+      <c r="D52" s="97">
         <f>ROUND(D51-D50,0)</f>
         <v/>
       </c>
-      <c r="E52" s="96">
+      <c r="E52" s="97">
         <f>ROUND(E51-E50,0)</f>
         <v/>
       </c>
-      <c r="F52" s="96">
+      <c r="F52" s="97">
         <f>ROUND(F51-F50,0)</f>
         <v/>
       </c>
-      <c r="G52" s="96">
+      <c r="G52" s="97">
         <f>ROUND(G51-G50,0)</f>
         <v/>
       </c>
-      <c r="H52" s="96">
+      <c r="H52" s="97">
         <f>ROUND(H51-H50,0)</f>
         <v/>
       </c>
-      <c r="I52" s="96">
+      <c r="I52" s="97">
         <f>ROUND(I51-I50,0)</f>
         <v/>
       </c>
-      <c r="J52" s="96">
+      <c r="J52" s="97">
         <f>ROUND(J51-J50,0)</f>
         <v/>
       </c>
-      <c r="K52" s="96">
+      <c r="K52" s="97">
         <f>ROUND(K51-K50,0)</f>
         <v/>
       </c>
-      <c r="L52" s="96">
+      <c r="L52" s="97">
         <f>ROUND(L51-L50,0)</f>
         <v/>
       </c>
@@ -11371,43 +11376,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C57" s="95">
+      <c r="C57" s="96">
         <f>ROUND(C56-C55,0)</f>
         <v/>
       </c>
-      <c r="D57" s="95">
+      <c r="D57" s="96">
         <f>ROUND(D56-D55,0)</f>
         <v/>
       </c>
-      <c r="E57" s="95">
+      <c r="E57" s="96">
         <f>ROUND(E56-E55,0)</f>
         <v/>
       </c>
-      <c r="F57" s="95">
+      <c r="F57" s="96">
         <f>ROUND(F56-F55,0)</f>
         <v/>
       </c>
-      <c r="G57" s="95">
+      <c r="G57" s="96">
         <f>ROUND(G56-G55,0)</f>
         <v/>
       </c>
-      <c r="H57" s="95">
+      <c r="H57" s="96">
         <f>ROUND(H56-H55,0)</f>
         <v/>
       </c>
-      <c r="I57" s="95">
+      <c r="I57" s="96">
         <f>ROUND(I56-I55,0)</f>
         <v/>
       </c>
-      <c r="J57" s="95">
+      <c r="J57" s="96">
         <f>ROUND(J56-J55,0)</f>
         <v/>
       </c>
-      <c r="K57" s="95">
+      <c r="K57" s="96">
         <f>ROUND(K56-K55,0)</f>
         <v/>
       </c>
-      <c r="L57" s="95">
+      <c r="L57" s="96">
         <f>ROUND(L56-L55,0)</f>
         <v/>
       </c>
@@ -11535,43 +11540,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C62" s="95">
+      <c r="C62" s="96">
         <f>ROUND(C61-C60,0)</f>
         <v/>
       </c>
-      <c r="D62" s="95">
+      <c r="D62" s="96">
         <f>ROUND(D61-D60,0)</f>
         <v/>
       </c>
-      <c r="E62" s="95">
+      <c r="E62" s="96">
         <f>ROUND(E61-E60,0)</f>
         <v/>
       </c>
-      <c r="F62" s="95">
+      <c r="F62" s="96">
         <f>ROUND(F61-F60,0)</f>
         <v/>
       </c>
-      <c r="G62" s="95">
+      <c r="G62" s="96">
         <f>ROUND(G61-G60,0)</f>
         <v/>
       </c>
-      <c r="H62" s="95">
+      <c r="H62" s="96">
         <f>ROUND(H61-H60,0)</f>
         <v/>
       </c>
-      <c r="I62" s="95">
+      <c r="I62" s="96">
         <f>ROUND(I61-I60,0)</f>
         <v/>
       </c>
-      <c r="J62" s="95">
+      <c r="J62" s="96">
         <f>ROUND(J61-J60,0)</f>
         <v/>
       </c>
-      <c r="K62" s="95">
+      <c r="K62" s="96">
         <f>ROUND(K61-K60,0)</f>
         <v/>
       </c>
-      <c r="L62" s="95">
+      <c r="L62" s="96">
         <f>ROUND(L61-L60,0)</f>
         <v/>
       </c>
@@ -11699,43 +11704,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C67" s="95">
+      <c r="C67" s="96">
         <f>ROUND(C66-C65,0)</f>
         <v/>
       </c>
-      <c r="D67" s="95">
+      <c r="D67" s="96">
         <f>ROUND(D66-D65,0)</f>
         <v/>
       </c>
-      <c r="E67" s="95">
+      <c r="E67" s="96">
         <f>ROUND(E66-E65,0)</f>
         <v/>
       </c>
-      <c r="F67" s="95">
+      <c r="F67" s="96">
         <f>ROUND(F66-F65,0)</f>
         <v/>
       </c>
-      <c r="G67" s="95">
+      <c r="G67" s="96">
         <f>ROUND(G66-G65,0)</f>
         <v/>
       </c>
-      <c r="H67" s="95">
+      <c r="H67" s="96">
         <f>ROUND(H66-H65,0)</f>
         <v/>
       </c>
-      <c r="I67" s="95">
+      <c r="I67" s="96">
         <f>ROUND(I66-I65,0)</f>
         <v/>
       </c>
-      <c r="J67" s="95">
+      <c r="J67" s="96">
         <f>ROUND(J66-J65,0)</f>
         <v/>
       </c>
-      <c r="K67" s="95">
+      <c r="K67" s="96">
         <f>ROUND(K66-K65,0)</f>
         <v/>
       </c>
-      <c r="L67" s="95">
+      <c r="L67" s="96">
         <f>ROUND(L66-L65,0)</f>
         <v/>
       </c>
@@ -11863,43 +11868,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C72" s="95">
+      <c r="C72" s="96">
         <f>ROUND(C71-C70,0)</f>
         <v/>
       </c>
-      <c r="D72" s="95">
+      <c r="D72" s="96">
         <f>ROUND(D71-D70,0)</f>
         <v/>
       </c>
-      <c r="E72" s="95">
+      <c r="E72" s="96">
         <f>ROUND(E71-E70,0)</f>
         <v/>
       </c>
-      <c r="F72" s="95">
+      <c r="F72" s="96">
         <f>ROUND(F71-F70,0)</f>
         <v/>
       </c>
-      <c r="G72" s="95">
+      <c r="G72" s="96">
         <f>ROUND(G71-G70,0)</f>
         <v/>
       </c>
-      <c r="H72" s="95">
+      <c r="H72" s="96">
         <f>ROUND(H71-H70,0)</f>
         <v/>
       </c>
-      <c r="I72" s="95">
+      <c r="I72" s="96">
         <f>ROUND(I71-I70,0)</f>
         <v/>
       </c>
-      <c r="J72" s="95">
+      <c r="J72" s="96">
         <f>ROUND(J71-J70,0)</f>
         <v/>
       </c>
-      <c r="K72" s="95">
+      <c r="K72" s="96">
         <f>ROUND(K71-K70,0)</f>
         <v/>
       </c>
-      <c r="L72" s="95">
+      <c r="L72" s="96">
         <f>ROUND(L71-L70,0)</f>
         <v/>
       </c>
@@ -11922,43 +11927,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C75" s="97">
+      <c r="C75" s="98">
         <f>BalanceSheet!C20</f>
         <v/>
       </c>
-      <c r="D75" s="97">
+      <c r="D75" s="98">
         <f>BalanceSheet!D20</f>
         <v/>
       </c>
-      <c r="E75" s="97">
+      <c r="E75" s="98">
         <f>BalanceSheet!E20</f>
         <v/>
       </c>
-      <c r="F75" s="97">
+      <c r="F75" s="98">
         <f>BalanceSheet!F20</f>
         <v/>
       </c>
-      <c r="G75" s="97">
+      <c r="G75" s="98">
         <f>BalanceSheet!G20</f>
         <v/>
       </c>
-      <c r="H75" s="97">
+      <c r="H75" s="98">
         <f>BalanceSheet!H20</f>
         <v/>
       </c>
-      <c r="I75" s="97">
+      <c r="I75" s="98">
         <f>BalanceSheet!I20</f>
         <v/>
       </c>
-      <c r="J75" s="97">
+      <c r="J75" s="98">
         <f>BalanceSheet!J20</f>
         <v/>
       </c>
-      <c r="K75" s="97">
+      <c r="K75" s="98">
         <f>BalanceSheet!K20</f>
         <v/>
       </c>
-      <c r="L75" s="97">
+      <c r="L75" s="98">
         <f>BalanceSheet!L20</f>
         <v/>
       </c>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -3282,52 +3282,52 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Blended CAC per athlete</t>
+          <t>Blended CAC per athlete acquired</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>spend / gross adds</t>
         </is>
       </c>
       <c r="C6" s="30">
-        <f>C5*Assumptions!C19+(1-C5)*Assumptions!C31</f>
+        <f>IF(Drivers!C40=0,0,(Costs!C18+Costs!C19)/Drivers!C40)</f>
         <v/>
       </c>
       <c r="D6" s="30">
-        <f>D5*Assumptions!D19+(1-D5)*Assumptions!D31</f>
+        <f>IF(Drivers!D40=0,0,(Costs!D18+Costs!D19)/Drivers!D40)</f>
         <v/>
       </c>
       <c r="E6" s="30">
-        <f>E5*Assumptions!E19+(1-E5)*Assumptions!E31</f>
+        <f>IF(Drivers!E40=0,0,(Costs!E18+Costs!E19)/Drivers!E40)</f>
         <v/>
       </c>
       <c r="F6" s="30">
-        <f>F5*Assumptions!F19+(1-F5)*Assumptions!F31</f>
+        <f>IF(Drivers!F40=0,0,(Costs!F18+Costs!F19)/Drivers!F40)</f>
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>G5*Assumptions!G19+(1-G5)*Assumptions!G31</f>
+        <f>IF(Drivers!G40=0,0,(Costs!G18+Costs!G19)/Drivers!G40)</f>
         <v/>
       </c>
       <c r="H6" s="30">
-        <f>H5*Assumptions!H19+(1-H5)*Assumptions!H31</f>
+        <f>IF(Drivers!H40=0,0,(Costs!H18+Costs!H19)/Drivers!H40)</f>
         <v/>
       </c>
       <c r="I6" s="30">
-        <f>I5*Assumptions!I19+(1-I5)*Assumptions!I31</f>
+        <f>IF(Drivers!I40=0,0,(Costs!I18+Costs!I19)/Drivers!I40)</f>
         <v/>
       </c>
       <c r="J6" s="30">
-        <f>J5*Assumptions!J19+(1-J5)*Assumptions!J31</f>
+        <f>IF(Drivers!J40=0,0,(Costs!J18+Costs!J19)/Drivers!J40)</f>
         <v/>
       </c>
       <c r="K6" s="30">
-        <f>K5*Assumptions!K19+(1-K5)*Assumptions!K31</f>
+        <f>IF(Drivers!K40=0,0,(Costs!K18+Costs!K19)/Drivers!K40)</f>
         <v/>
       </c>
       <c r="L6" s="30">
-        <f>L5*Assumptions!L19+(1-L5)*Assumptions!L31</f>
+        <f>IF(Drivers!L40=0,0,(Costs!L18+Costs!L19)/Drivers!L40)</f>
         <v/>
       </c>
     </row>
@@ -4896,47 +4896,47 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>fan subs + SaaS / 12</t>
+          <t>subs x take + SaaS / 12</t>
         </is>
       </c>
       <c r="C8" s="30">
-        <f>(Revenue!C19+Revenue!C21)/12</f>
+        <f>(Revenue!C7*Assumptions!C40+Revenue!C21)/12</f>
         <v/>
       </c>
       <c r="D8" s="30">
-        <f>(Revenue!D19+Revenue!D21)/12</f>
+        <f>(Revenue!D7*Assumptions!D40+Revenue!D21)/12</f>
         <v/>
       </c>
       <c r="E8" s="30">
-        <f>(Revenue!E19+Revenue!E21)/12</f>
+        <f>(Revenue!E7*Assumptions!E40+Revenue!E21)/12</f>
         <v/>
       </c>
       <c r="F8" s="30">
-        <f>(Revenue!F19+Revenue!F21)/12</f>
+        <f>(Revenue!F7*Assumptions!F40+Revenue!F21)/12</f>
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>(Revenue!G19+Revenue!G21)/12</f>
+        <f>(Revenue!G7*Assumptions!G40+Revenue!G21)/12</f>
         <v/>
       </c>
       <c r="H8" s="30">
-        <f>(Revenue!H19+Revenue!H21)/12</f>
+        <f>(Revenue!H7*Assumptions!H40+Revenue!H21)/12</f>
         <v/>
       </c>
       <c r="I8" s="30">
-        <f>(Revenue!I19+Revenue!I21)/12</f>
+        <f>(Revenue!I7*Assumptions!I40+Revenue!I21)/12</f>
         <v/>
       </c>
       <c r="J8" s="30">
-        <f>(Revenue!J19+Revenue!J21)/12</f>
+        <f>(Revenue!J7*Assumptions!J40+Revenue!J21)/12</f>
         <v/>
       </c>
       <c r="K8" s="30">
-        <f>(Revenue!K19+Revenue!K21)/12</f>
+        <f>(Revenue!K7*Assumptions!K40+Revenue!K21)/12</f>
         <v/>
       </c>
       <c r="L8" s="30">
-        <f>(Revenue!L19+Revenue!L21)/12</f>
+        <f>(Revenue!L7*Assumptions!L40+Revenue!L21)/12</f>
         <v/>
       </c>
     </row>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -3339,47 +3339,47 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>per year</t>
+          <t>gross-add weighted</t>
         </is>
       </c>
       <c r="C7" s="23">
-        <f>C5*Assumptions!C14+(1-C5)*Assumptions!C26</f>
+        <f>IF(Drivers!C40=0,0,(Drivers!C11*Assumptions!C14+Drivers!C25*Assumptions!C26)/Drivers!C40)</f>
         <v/>
       </c>
       <c r="D7" s="23">
-        <f>D5*Assumptions!D14+(1-D5)*Assumptions!D26</f>
+        <f>IF(Drivers!D40=0,0,(Drivers!D11*Assumptions!D14+Drivers!D25*Assumptions!D26)/Drivers!D40)</f>
         <v/>
       </c>
       <c r="E7" s="23">
-        <f>E5*Assumptions!E14+(1-E5)*Assumptions!E26</f>
+        <f>IF(Drivers!E40=0,0,(Drivers!E11*Assumptions!E14+Drivers!E25*Assumptions!E26)/Drivers!E40)</f>
         <v/>
       </c>
       <c r="F7" s="23">
-        <f>F5*Assumptions!F14+(1-F5)*Assumptions!F26</f>
+        <f>IF(Drivers!F40=0,0,(Drivers!F11*Assumptions!F14+Drivers!F25*Assumptions!F26)/Drivers!F40)</f>
         <v/>
       </c>
       <c r="G7" s="23">
-        <f>G5*Assumptions!G14+(1-G5)*Assumptions!G26</f>
+        <f>IF(Drivers!G40=0,0,(Drivers!G11*Assumptions!G14+Drivers!G25*Assumptions!G26)/Drivers!G40)</f>
         <v/>
       </c>
       <c r="H7" s="23">
-        <f>H5*Assumptions!H14+(1-H5)*Assumptions!H26</f>
+        <f>IF(Drivers!H40=0,0,(Drivers!H11*Assumptions!H14+Drivers!H25*Assumptions!H26)/Drivers!H40)</f>
         <v/>
       </c>
       <c r="I7" s="23">
-        <f>I5*Assumptions!I14+(1-I5)*Assumptions!I26</f>
+        <f>IF(Drivers!I40=0,0,(Drivers!I11*Assumptions!I14+Drivers!I25*Assumptions!I26)/Drivers!I40)</f>
         <v/>
       </c>
       <c r="J7" s="23">
-        <f>J5*Assumptions!J14+(1-J5)*Assumptions!J26</f>
+        <f>IF(Drivers!J40=0,0,(Drivers!J11*Assumptions!J14+Drivers!J25*Assumptions!J26)/Drivers!J40)</f>
         <v/>
       </c>
       <c r="K7" s="23">
-        <f>K5*Assumptions!K14+(1-K5)*Assumptions!K26</f>
+        <f>IF(Drivers!K40=0,0,(Drivers!K11*Assumptions!K14+Drivers!K25*Assumptions!K26)/Drivers!K40)</f>
         <v/>
       </c>
       <c r="L7" s="23">
-        <f>L5*Assumptions!L14+(1-L5)*Assumptions!L26</f>
+        <f>IF(Drivers!L40=0,0,(Drivers!L11*Assumptions!L14+Drivers!L25*Assumptions!L26)/Drivers!L40)</f>
         <v/>
       </c>
     </row>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -17,11 +17,14 @@
     <sheet name="CashFlow" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="BalanceSheet" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Funding" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Valuation" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Comparables" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="MarketModel" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Research" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Check" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="HiringPlan" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="CAC_CLV" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="KPIs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Valuation" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Comparables" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="MarketModel" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Research" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Check" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +42,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.000"/>
     <numFmt numFmtId="170" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -151,6 +154,12 @@
       <b val="1"/>
       <color rgb="00B3272D"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="8"/>
     </font>
     <font>
       <i val="1"/>
@@ -321,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -385,30 +394,38 @@
     <xf numFmtId="167" fontId="18" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="19" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="17" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="17" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="17" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="12" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="16" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="16" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="17" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="15" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="169" fontId="15" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="15" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="15" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -418,28 +435,28 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="17" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -810,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A65"/>
+  <dimension ref="A1:A68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1068,168 +1085,189 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Check          the Python model's figures, to verify the formulas agree</t>
+          <t xml:space="preserve">  HiringPlan     headcount by role, reconciled to the model</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CAC_CLV        acquisition cost against lifetime value</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>WHY TEN YEARS</t>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  KPIs           scale, quality of revenue, efficiency</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Check          the Python model's figures, to verify the formulas agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>WHY TEN YEARS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>At Y7 the business is still compounding above 50%, so a terminal value placed</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>there does most of the valuation work and does it badly. Ten years lets growth</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>decelerate inside the explicit forecast, where it can be argued with.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>EVIDENCE CHAIN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Comparables (published facts) -&gt; MarketModel (derives ours) -&gt; Assumptions</t>
+          <t>decelerate inside the explicit forecast, where it can be argued with.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -&gt; Drivers -&gt; Revenue and Costs -&gt; statements -&gt; Valuation.</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  From Assumptions rightwards, every link is a formula you can follow with</t>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>EVIDENCE CHAIN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Trace Precedents. The first arrow is checked rather than linked: MarketModel</t>
+          <t xml:space="preserve">  Comparables (published facts) -&gt; MarketModel (derives ours) -&gt; Assumptions</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  derives each figure from the published ones, and Assumptions carries the</t>
+          <t xml:space="preserve">  -&gt; Drivers -&gt; Revenue and Costs -&gt; statements -&gt; Valuation.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  result rounded for reading -- 37 fans per athlete, not 37.026. Linking the</t>
+          <t xml:space="preserve">  From Assumptions rightwards, every link is a formula you can follow with</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  cells would put the workbook a hair off the Python everywhere, which the</t>
+          <t xml:space="preserve">  Trace Precedents. The first arrow is checked rather than linked: MarketModel</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Check sheet exists to forbid, so scripts/doc_consistency.py asserts the</t>
+          <t xml:space="preserve">  derives each figure from the published ones, and Assumptions carries the</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">  derivation still rounds to those literals instead. Refresh a comparable far</t>
+          <t xml:space="preserve">  result rounded for reading -- 37 fans per athlete, not 37.026. Linking the</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">  enough to change one of them at the precision it is written and that check</t>
+          <t xml:space="preserve">  cells would put the workbook a hair off the Python everywhere, which the</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  fails. A refresh too small to change any displayed figure passes, which is</t>
+          <t xml:space="preserve">  Check sheet exists to forbid, so scripts/doc_consistency.py asserts the</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">  the same statement, not a loophole in it.</t>
+          <t xml:space="preserve">  derivation still rounds to those literals instead. Refresh a comparable far</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  enough to change one of them at the precision it is written and that check</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>MODEL SHAPE</t>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  fails. A refresh too small to change any displayed figure passes, which is</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>This is a target-driven model: athlete counts are the plan, and marketing spend</t>
+          <t xml:space="preserve">  the same statement, not a loophole in it.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>is derived from them at segment CAC. It is not a driver-driven model in which</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>spend produces athletes. That is the normal shape for a plan, but it means the</t>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>MODEL SHAPE</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
+        <is>
+          <t>This is a target-driven model: athlete counts are the plan, and marketing spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>is derived from them at segment CAC. It is not a driver-driven model in which</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>spend produces athletes. That is the normal shape for a plan, but it means the</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>athlete trajectory is an assumption to defend, not an output to trust.</t>
         </is>
@@ -1778,7 +1816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Valuation — DCF, NPV, IRR and exit multiples</t>
+          <t>Hiring plan — headcount by role, reconciled to the model</t>
         </is>
       </c>
     </row>
@@ -1877,563 +1915,1162 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Free cash flow</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C4" s="30">
-        <f>CashFlow!C9</f>
-        <v/>
-      </c>
-      <c r="D4" s="30">
-        <f>CashFlow!D9</f>
-        <v/>
-      </c>
-      <c r="E4" s="30">
-        <f>CashFlow!E9</f>
-        <v/>
-      </c>
-      <c r="F4" s="30">
-        <f>CashFlow!F9</f>
-        <v/>
-      </c>
-      <c r="G4" s="30">
-        <f>CashFlow!G9</f>
-        <v/>
-      </c>
-      <c r="H4" s="30">
-        <f>CashFlow!H9</f>
-        <v/>
-      </c>
-      <c r="I4" s="30">
-        <f>CashFlow!I9</f>
-        <v/>
-      </c>
-      <c r="J4" s="30">
-        <f>CashFlow!J9</f>
-        <v/>
-      </c>
-      <c r="K4" s="30">
-        <f>CashFlow!K9</f>
-        <v/>
-      </c>
-      <c r="L4" s="30">
-        <f>CashFlow!L9</f>
-        <v/>
-      </c>
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>FTE BY ROLE</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="12" t="n"/>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="12" t="n"/>
+      <c r="L4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Discount factor</t>
+          <t>Founder / CEO</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>1/(1+WACC)^t</t>
-        </is>
-      </c>
-      <c r="C5" s="33">
-        <f>1/(1+Assumptions!$C$85)^1</f>
-        <v/>
-      </c>
-      <c r="D5" s="33">
-        <f>1/(1+Assumptions!$C$85)^2</f>
-        <v/>
-      </c>
-      <c r="E5" s="33">
-        <f>1/(1+Assumptions!$C$85)^3</f>
-        <v/>
-      </c>
-      <c r="F5" s="33">
-        <f>1/(1+Assumptions!$C$85)^4</f>
-        <v/>
-      </c>
-      <c r="G5" s="33">
-        <f>1/(1+Assumptions!$C$85)^5</f>
-        <v/>
-      </c>
-      <c r="H5" s="33">
-        <f>1/(1+Assumptions!$C$85)^6</f>
-        <v/>
-      </c>
-      <c r="I5" s="33">
-        <f>1/(1+Assumptions!$C$85)^7</f>
-        <v/>
-      </c>
-      <c r="J5" s="33">
-        <f>1/(1+Assumptions!$C$85)^8</f>
-        <v/>
-      </c>
-      <c r="K5" s="33">
-        <f>1/(1+Assumptions!$C$85)^9</f>
-        <v/>
-      </c>
-      <c r="L5" s="33">
-        <f>1/(1+Assumptions!$C$85)^10</f>
-        <v/>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
-        <is>
-          <t>Discounted FCF</t>
-        </is>
-      </c>
-      <c r="B6" s="40" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C6" s="43">
-        <f>C4*C5</f>
-        <v/>
-      </c>
-      <c r="D6" s="43">
-        <f>D4*D5</f>
-        <v/>
-      </c>
-      <c r="E6" s="43">
-        <f>E4*E5</f>
-        <v/>
-      </c>
-      <c r="F6" s="43">
-        <f>F4*F5</f>
-        <v/>
-      </c>
-      <c r="G6" s="43">
-        <f>G4*G5</f>
-        <v/>
-      </c>
-      <c r="H6" s="43">
-        <f>H4*H5</f>
-        <v/>
-      </c>
-      <c r="I6" s="43">
-        <f>I4*I5</f>
-        <v/>
-      </c>
-      <c r="J6" s="43">
-        <f>J4*J5</f>
-        <v/>
-      </c>
-      <c r="K6" s="43">
-        <f>K4*K5</f>
-        <v/>
-      </c>
-      <c r="L6" s="43">
-        <f>L4*L5</f>
-        <v/>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H6" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" s="21" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>BD / partnerships</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" s="21" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>FCF incl. terminal value</t>
+          <t>Athlete success</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>for the IRR below</t>
-        </is>
-      </c>
-      <c r="C8" s="47">
-        <f>C4+IF(1=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="47">
-        <f>D4+IF(2=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="E8" s="47">
-        <f>E4+IF(3=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="47">
-        <f>F4+IF(4=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="47">
-        <f>G4+IF(5=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="H8" s="47">
-        <f>H4+IF(6=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="I8" s="47">
-        <f>I4+IF(7=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="J8" s="47">
-        <f>J4+IF(8=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="K8" s="47">
-        <f>K4+IF(9=10,$C$11,0)</f>
-        <v/>
-      </c>
-      <c r="L8" s="47">
-        <f>L4+IF(10=10,$C$11,0)</f>
-        <v/>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I8" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" s="21" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>DCF</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Trust &amp; safety / review</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G9" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" s="21" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PV of explicit forecast</t>
-        </is>
-      </c>
-      <c r="C10" s="51">
-        <f>SUM(C6:L6)</f>
-        <v/>
+          <t>Finance / operations</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Terminal value at Y10</t>
-        </is>
-      </c>
-      <c r="C11" s="51">
-        <f>L4*(1+Assumptions!$C$86)/(Assumptions!$C$85-Assumptions!$C$86)</f>
-        <v/>
+          <t>Data protection officer</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>TOTAL FTE</t>
+        </is>
+      </c>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>FTE</t>
         </is>
       </c>
       <c r="C12" s="51">
-        <f>C11*L5</f>
+        <f>SUM(C5:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="51">
+        <f>SUM(D5:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="51">
+        <f>SUM(E5:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="51">
+        <f>SUM(F5:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="51">
+        <f>SUM(G5:G11)</f>
+        <v/>
+      </c>
+      <c r="H12" s="51">
+        <f>SUM(H5:H11)</f>
+        <v/>
+      </c>
+      <c r="I12" s="51">
+        <f>SUM(I5:I11)</f>
+        <v/>
+      </c>
+      <c r="J12" s="51">
+        <f>SUM(J5:J11)</f>
+        <v/>
+      </c>
+      <c r="K12" s="51">
+        <f>SUM(K5:K11)</f>
+        <v/>
+      </c>
+      <c r="L12" s="51">
+        <f>SUM(L5:L11)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>ENTERPRISE VALUE (DCF)</t>
-        </is>
-      </c>
-      <c r="C13" s="51">
-        <f>C10+C12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>RETURN METRICS</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="12" t="n"/>
-      <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Model headcount</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+      <c r="C13" s="31">
+        <f>Assumptions!C60</f>
+        <v/>
+      </c>
+      <c r="D13" s="31">
+        <f>Assumptions!D60</f>
+        <v/>
+      </c>
+      <c r="E13" s="31">
+        <f>Assumptions!E60</f>
+        <v/>
+      </c>
+      <c r="F13" s="31">
+        <f>Assumptions!F60</f>
+        <v/>
+      </c>
+      <c r="G13" s="31">
+        <f>Assumptions!G60</f>
+        <v/>
+      </c>
+      <c r="H13" s="31">
+        <f>Assumptions!H60</f>
+        <v/>
+      </c>
+      <c r="I13" s="31">
+        <f>Assumptions!I60</f>
+        <v/>
+      </c>
+      <c r="J13" s="31">
+        <f>Assumptions!J60</f>
+        <v/>
+      </c>
+      <c r="K13" s="31">
+        <f>Assumptions!K60</f>
+        <v/>
+      </c>
+      <c r="L13" s="31">
+        <f>Assumptions!L60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="39" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>must be zero</t>
+        </is>
+      </c>
+      <c r="C14" s="52">
+        <f>ROUND(C12-C13,3)</f>
+        <v/>
+      </c>
+      <c r="D14" s="52">
+        <f>ROUND(D12-D13,3)</f>
+        <v/>
+      </c>
+      <c r="E14" s="52">
+        <f>ROUND(E12-E13,3)</f>
+        <v/>
+      </c>
+      <c r="F14" s="52">
+        <f>ROUND(F12-F13,3)</f>
+        <v/>
+      </c>
+      <c r="G14" s="52">
+        <f>ROUND(G12-G13,3)</f>
+        <v/>
+      </c>
+      <c r="H14" s="52">
+        <f>ROUND(H12-H13,3)</f>
+        <v/>
+      </c>
+      <c r="I14" s="52">
+        <f>ROUND(I12-I13,3)</f>
+        <v/>
+      </c>
+      <c r="J14" s="52">
+        <f>ROUND(J12-J13,3)</f>
+        <v/>
+      </c>
+      <c r="K14" s="52">
+        <f>ROUND(K12-K13,3)</f>
+        <v/>
+      </c>
+      <c r="L14" s="52">
+        <f>ROUND(L12-L13,3)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>NPV of FCF at WACC</t>
-        </is>
-      </c>
-      <c r="C16" s="51">
-        <f>NPV(Assumptions!$C$85,C4:L4)</f>
-        <v/>
-      </c>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>COST — ROLE BUILD-UP AGAINST THE MODEL</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>IRR of the plan</t>
-        </is>
-      </c>
-      <c r="C17" s="52">
-        <f>IRR(C4:L4)</f>
-        <v/>
+          <t>Employer social security</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>on gross</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K17" s="36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L17" s="36" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>IRR incl. terminal value</t>
-        </is>
-      </c>
-      <c r="C18" s="52">
-        <f>IRR(C8:L8,0.3)</f>
+          <t>Founder / CEO — loaded</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C18" s="47">
+        <f>C5*45000*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="47">
+        <f>D5*45000*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="47">
+        <f>E5*45000*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="47">
+        <f>F5*45000*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="47">
+        <f>G5*45000*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="47">
+        <f>H5*45000*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="47">
+        <f>I5*45000*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="47">
+        <f>J5*45000*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K18" s="47">
+        <f>K5*45000*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L18" s="47">
+        <f>L5*45000*(1+L17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Engineering — loaded</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C19" s="47">
+        <f>C6*55000*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D19" s="47">
+        <f>D6*55000*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E19" s="47">
+        <f>E6*55000*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F19" s="47">
+        <f>F6*55000*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G19" s="47">
+        <f>G6*55000*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H19" s="47">
+        <f>H6*55000*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I19" s="47">
+        <f>I6*55000*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J19" s="47">
+        <f>J6*55000*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K19" s="47">
+        <f>K6*55000*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L19" s="47">
+        <f>L6*55000*(1+L17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>EXIT MULTIPLE</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
-      <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
-      <c r="L20" s="12" t="n"/>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>BD / partnerships — loaded</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C20" s="47">
+        <f>C7*38000*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D20" s="47">
+        <f>D7*38000*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E20" s="47">
+        <f>E7*38000*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F20" s="47">
+        <f>F7*38000*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G20" s="47">
+        <f>G7*38000*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H20" s="47">
+        <f>H7*38000*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I20" s="47">
+        <f>I7*38000*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J20" s="47">
+        <f>J7*38000*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K20" s="47">
+        <f>K7*38000*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L20" s="47">
+        <f>L7*38000*(1+L17)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>Y10 net revenue</t>
-        </is>
-      </c>
-      <c r="C21" s="51">
-        <f>Revenue!L22</f>
+          <t>Athlete success — loaded</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C21" s="47">
+        <f>C8*30000*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D21" s="47">
+        <f>D8*30000*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E21" s="47">
+        <f>E8*30000*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F21" s="47">
+        <f>F8*30000*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G21" s="47">
+        <f>G8*30000*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H21" s="47">
+        <f>H8*30000*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I21" s="47">
+        <f>I8*30000*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J21" s="47">
+        <f>J8*30000*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K21" s="47">
+        <f>K8*30000*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L21" s="47">
+        <f>L8*30000*(1+L17)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>Exit value at Y10</t>
-        </is>
-      </c>
-      <c r="C22" s="51">
-        <f>C21*Assumptions!$C$87</f>
+          <t>Trust &amp; safety / review — loaded</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C22" s="47">
+        <f>C9*34000*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D22" s="47">
+        <f>D9*34000*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E22" s="47">
+        <f>E9*34000*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F22" s="47">
+        <f>F9*34000*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G22" s="47">
+        <f>G9*34000*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H22" s="47">
+        <f>H9*34000*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I22" s="47">
+        <f>I9*34000*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J22" s="47">
+        <f>J9*34000*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K22" s="47">
+        <f>K9*34000*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L22" s="47">
+        <f>L9*34000*(1+L17)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>Discounted to today</t>
-        </is>
-      </c>
-      <c r="C23" s="51">
-        <f>C22*L5</f>
+          <t>Finance / operations — loaded</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C23" s="47">
+        <f>C10*42000*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D23" s="47">
+        <f>D10*42000*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E23" s="47">
+        <f>E10*42000*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F23" s="47">
+        <f>F10*42000*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G23" s="47">
+        <f>G10*42000*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H23" s="47">
+        <f>H10*42000*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I23" s="47">
+        <f>I10*42000*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J23" s="47">
+        <f>J10*42000*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K23" s="47">
+        <f>K10*42000*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L23" s="47">
+        <f>L10*42000*(1+L17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Data protection officer — loaded</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C24" s="47">
+        <f>C11*60000*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D24" s="47">
+        <f>D11*60000*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E24" s="47">
+        <f>E11*60000*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F24" s="47">
+        <f>F11*60000*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G24" s="47">
+        <f>G11*60000*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H24" s="47">
+        <f>H11*60000*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I24" s="47">
+        <f>I11*60000*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J24" s="47">
+        <f>J11*60000*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K24" s="47">
+        <f>K11*60000*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L24" s="47">
+        <f>L11*60000*(1+L17)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>SENSITIVITY — enterprise value by WACC and terminal growth</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="12" t="n"/>
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>TOTAL, role build-up</t>
+        </is>
+      </c>
+      <c r="B25" s="40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C25" s="45">
+        <f>SUM(C18:C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="45">
+        <f>SUM(D18:D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="45">
+        <f>SUM(E18:E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="45">
+        <f>SUM(F18:F24)</f>
+        <v/>
+      </c>
+      <c r="G25" s="45">
+        <f>SUM(G18:G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="45">
+        <f>SUM(H18:H24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="45">
+        <f>SUM(I18:I24)</f>
+        <v/>
+      </c>
+      <c r="J25" s="45">
+        <f>SUM(J18:J24)</f>
+        <v/>
+      </c>
+      <c r="K25" s="45">
+        <f>SUM(K18:K24)</f>
+        <v/>
+      </c>
+      <c r="L25" s="45">
+        <f>SUM(L18:L24)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Terminal growth \ WACC</t>
-        </is>
-      </c>
-      <c r="C26" s="53" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D26" s="53" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E26" s="53" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F26" s="53" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G26" s="53" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H26" s="53" t="n">
-        <v>0.3</v>
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>People cost in the model</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="C26" s="30">
+        <f>Costs!C17</f>
+        <v/>
+      </c>
+      <c r="D26" s="30">
+        <f>Costs!D17</f>
+        <v/>
+      </c>
+      <c r="E26" s="30">
+        <f>Costs!E17</f>
+        <v/>
+      </c>
+      <c r="F26" s="30">
+        <f>Costs!F17</f>
+        <v/>
+      </c>
+      <c r="G26" s="30">
+        <f>Costs!G17</f>
+        <v/>
+      </c>
+      <c r="H26" s="30">
+        <f>Costs!H17</f>
+        <v/>
+      </c>
+      <c r="I26" s="30">
+        <f>Costs!I17</f>
+        <v/>
+      </c>
+      <c r="J26" s="30">
+        <f>Costs!J17</f>
+        <v/>
+      </c>
+      <c r="K26" s="30">
+        <f>Costs!K17</f>
+        <v/>
+      </c>
+      <c r="L26" s="30">
+        <f>Costs!L17</f>
+        <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="52" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C27" s="54">
-        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.01)/(0.18-0.01)/(1+0.18)^10</f>
-        <v/>
-      </c>
-      <c r="D27" s="54">
-        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.01)/(0.2-0.01)/(1+0.2)^10</f>
-        <v/>
-      </c>
-      <c r="E27" s="54">
-        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.01)/(0.22-0.01)/(1+0.22)^10</f>
-        <v/>
-      </c>
-      <c r="F27" s="54">
-        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.01)/(0.25-0.01)/(1+0.25)^10</f>
-        <v/>
-      </c>
-      <c r="G27" s="54">
-        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.01)/(0.28-0.01)/(1+0.28)^10</f>
-        <v/>
-      </c>
-      <c r="H27" s="54">
-        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.01)/(0.3-0.01)/(1+0.3)^10</f>
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Difference — role mix</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>build-up less model</t>
+        </is>
+      </c>
+      <c r="C27" s="47">
+        <f>C25-C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="47">
+        <f>D25-D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="47">
+        <f>E25-E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="47">
+        <f>F25-F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="47">
+        <f>G25-G26</f>
+        <v/>
+      </c>
+      <c r="H27" s="47">
+        <f>H25-H26</f>
+        <v/>
+      </c>
+      <c r="I27" s="47">
+        <f>I25-I26</f>
+        <v/>
+      </c>
+      <c r="J27" s="47">
+        <f>J25-J26</f>
+        <v/>
+      </c>
+      <c r="K27" s="47">
+        <f>K25-K26</f>
+        <v/>
+      </c>
+      <c r="L27" s="47">
+        <f>L25-L26</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="52" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C28" s="54">
-        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.02)/(0.18-0.02)/(1+0.18)^10</f>
-        <v/>
-      </c>
-      <c r="D28" s="54">
-        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.02)/(0.2-0.02)/(1+0.2)^10</f>
-        <v/>
-      </c>
-      <c r="E28" s="54">
-        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.02)/(0.22-0.02)/(1+0.22)^10</f>
-        <v/>
-      </c>
-      <c r="F28" s="54">
-        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.02)/(0.25-0.02)/(1+0.25)^10</f>
-        <v/>
-      </c>
-      <c r="G28" s="54">
-        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.02)/(0.28-0.02)/(1+0.28)^10</f>
-        <v/>
-      </c>
-      <c r="H28" s="54">
-        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.02)/(0.3-0.02)/(1+0.3)^10</f>
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  memo: build-up per FTE</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C28" s="53">
+        <f>IF(C12=0,0,C25/C12)</f>
+        <v/>
+      </c>
+      <c r="D28" s="53">
+        <f>IF(D12=0,0,D25/D12)</f>
+        <v/>
+      </c>
+      <c r="E28" s="53">
+        <f>IF(E12=0,0,E25/E12)</f>
+        <v/>
+      </c>
+      <c r="F28" s="53">
+        <f>IF(F12=0,0,F25/F12)</f>
+        <v/>
+      </c>
+      <c r="G28" s="53">
+        <f>IF(G12=0,0,G25/G12)</f>
+        <v/>
+      </c>
+      <c r="H28" s="53">
+        <f>IF(H12=0,0,H25/H12)</f>
+        <v/>
+      </c>
+      <c r="I28" s="53">
+        <f>IF(I12=0,0,I25/I12)</f>
+        <v/>
+      </c>
+      <c r="J28" s="53">
+        <f>IF(J12=0,0,J25/J12)</f>
+        <v/>
+      </c>
+      <c r="K28" s="53">
+        <f>IF(K12=0,0,K25/K12)</f>
+        <v/>
+      </c>
+      <c r="L28" s="53">
+        <f>IF(L12=0,0,L25/L12)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="52" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C29" s="54">
-        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.03)/(0.18-0.03)/(1+0.18)^10</f>
-        <v/>
-      </c>
-      <c r="D29" s="54">
-        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.03)/(0.2-0.03)/(1+0.2)^10</f>
-        <v/>
-      </c>
-      <c r="E29" s="54">
-        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.03)/(0.22-0.03)/(1+0.22)^10</f>
-        <v/>
-      </c>
-      <c r="F29" s="54">
-        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.03)/(0.25-0.03)/(1+0.25)^10</f>
-        <v/>
-      </c>
-      <c r="G29" s="54">
-        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.03)/(0.28-0.03)/(1+0.28)^10</f>
-        <v/>
-      </c>
-      <c r="H29" s="54">
-        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.03)/(0.3-0.03)/(1+0.3)^10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="52" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C30" s="54">
-        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.04)/(0.18-0.04)/(1+0.18)^10</f>
-        <v/>
-      </c>
-      <c r="D30" s="54">
-        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.04)/(0.2-0.04)/(1+0.2)^10</f>
-        <v/>
-      </c>
-      <c r="E30" s="54">
-        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.04)/(0.22-0.04)/(1+0.22)^10</f>
-        <v/>
-      </c>
-      <c r="F30" s="54">
-        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.04)/(0.25-0.04)/(1+0.25)^10</f>
-        <v/>
-      </c>
-      <c r="G30" s="54">
-        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.04)/(0.28-0.04)/(1+0.28)^10</f>
-        <v/>
-      </c>
-      <c r="H30" s="54">
-        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.04)/(0.3-0.04)/(1+0.3)^10</f>
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  memo: model blended per FTE</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C29" s="30">
+        <f>Assumptions!C61</f>
+        <v/>
+      </c>
+      <c r="D29" s="30">
+        <f>Assumptions!D61</f>
+        <v/>
+      </c>
+      <c r="E29" s="30">
+        <f>Assumptions!E61</f>
+        <v/>
+      </c>
+      <c r="F29" s="30">
+        <f>Assumptions!F61</f>
+        <v/>
+      </c>
+      <c r="G29" s="30">
+        <f>Assumptions!G61</f>
+        <v/>
+      </c>
+      <c r="H29" s="30">
+        <f>Assumptions!H61</f>
+        <v/>
+      </c>
+      <c r="I29" s="30">
+        <f>Assumptions!I61</f>
+        <v/>
+      </c>
+      <c r="J29" s="30">
+        <f>Assumptions!J61</f>
+        <v/>
+      </c>
+      <c r="K29" s="30">
+        <f>Assumptions!K61</f>
+        <v/>
+      </c>
+      <c r="L29" s="30">
+        <f>Assumptions!L61</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="52" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C31" s="54">
-        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.05)/(0.18-0.05)/(1+0.18)^10</f>
-        <v/>
-      </c>
-      <c r="D31" s="54">
-        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.05)/(0.2-0.05)/(1+0.2)^10</f>
-        <v/>
-      </c>
-      <c r="E31" s="54">
-        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.05)/(0.22-0.05)/(1+0.22)^10</f>
-        <v/>
-      </c>
-      <c r="F31" s="54">
-        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.05)/(0.25-0.05)/(1+0.25)^10</f>
-        <v/>
-      </c>
-      <c r="G31" s="54">
-        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.05)/(0.28-0.05)/(1+0.28)^10</f>
-        <v/>
-      </c>
-      <c r="H31" s="54">
-        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.05)/(0.3-0.05)/(1+0.3)^10</f>
-        <v/>
+      <c r="A31" s="54" t="inlineStr">
+        <is>
+          <t>The FTE block reconciles exactly and is the plan. The cost build-up prices those roles at their own salaries; the model prices the same headcount at a blended loaded average that rises from 38k to 76k over the plan, while the build-up holds today's salaries flat. The two cross over at Y4: the build-up is the higher figure in Y1-Y3, where one founder salary dominates a team of two or three, and the model is higher from Y4 as its blended rate climbs. The model is the one that reaches the P&amp;L either way. The memo rows below make the two rates comparable.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2454,6 +3091,3021 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Customer acquisition cost and lifetime value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Input — change me</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Sourced fact</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Formula (this sheet)</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Formula (other sheet)</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Y7</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Y8</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Y9</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Y10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>ATHLETE — BLENDED ACROSS SEGMENTS</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="12" t="n"/>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="12" t="n"/>
+      <c r="L4" s="12" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Niche share of athletes</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C5" s="23">
+        <f>Assumptions!C6</f>
+        <v/>
+      </c>
+      <c r="D5" s="23">
+        <f>Assumptions!D6</f>
+        <v/>
+      </c>
+      <c r="E5" s="23">
+        <f>Assumptions!E6</f>
+        <v/>
+      </c>
+      <c r="F5" s="23">
+        <f>Assumptions!F6</f>
+        <v/>
+      </c>
+      <c r="G5" s="23">
+        <f>Assumptions!G6</f>
+        <v/>
+      </c>
+      <c r="H5" s="23">
+        <f>Assumptions!H6</f>
+        <v/>
+      </c>
+      <c r="I5" s="23">
+        <f>Assumptions!I6</f>
+        <v/>
+      </c>
+      <c r="J5" s="23">
+        <f>Assumptions!J6</f>
+        <v/>
+      </c>
+      <c r="K5" s="23">
+        <f>Assumptions!K6</f>
+        <v/>
+      </c>
+      <c r="L5" s="23">
+        <f>Assumptions!L6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Blended CAC per athlete acquired</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>spend / gross adds</t>
+        </is>
+      </c>
+      <c r="C6" s="30">
+        <f>IF(Drivers!C40=0,0,(Costs!C18+Costs!C19)/Drivers!C40)</f>
+        <v/>
+      </c>
+      <c r="D6" s="30">
+        <f>IF(Drivers!D40=0,0,(Costs!D18+Costs!D19)/Drivers!D40)</f>
+        <v/>
+      </c>
+      <c r="E6" s="30">
+        <f>IF(Drivers!E40=0,0,(Costs!E18+Costs!E19)/Drivers!E40)</f>
+        <v/>
+      </c>
+      <c r="F6" s="30">
+        <f>IF(Drivers!F40=0,0,(Costs!F18+Costs!F19)/Drivers!F40)</f>
+        <v/>
+      </c>
+      <c r="G6" s="30">
+        <f>IF(Drivers!G40=0,0,(Costs!G18+Costs!G19)/Drivers!G40)</f>
+        <v/>
+      </c>
+      <c r="H6" s="30">
+        <f>IF(Drivers!H40=0,0,(Costs!H18+Costs!H19)/Drivers!H40)</f>
+        <v/>
+      </c>
+      <c r="I6" s="30">
+        <f>IF(Drivers!I40=0,0,(Costs!I18+Costs!I19)/Drivers!I40)</f>
+        <v/>
+      </c>
+      <c r="J6" s="30">
+        <f>IF(Drivers!J40=0,0,(Costs!J18+Costs!J19)/Drivers!J40)</f>
+        <v/>
+      </c>
+      <c r="K6" s="30">
+        <f>IF(Drivers!K40=0,0,(Costs!K18+Costs!K19)/Drivers!K40)</f>
+        <v/>
+      </c>
+      <c r="L6" s="30">
+        <f>IF(Drivers!L40=0,0,(Costs!L18+Costs!L19)/Drivers!L40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Blended athlete churn</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>gross-add weighted</t>
+        </is>
+      </c>
+      <c r="C7" s="23">
+        <f>IF(Drivers!C40=0,0,(Drivers!C11*Assumptions!C14+Drivers!C25*Assumptions!C26)/Drivers!C40)</f>
+        <v/>
+      </c>
+      <c r="D7" s="23">
+        <f>IF(Drivers!D40=0,0,(Drivers!D11*Assumptions!D14+Drivers!D25*Assumptions!D26)/Drivers!D40)</f>
+        <v/>
+      </c>
+      <c r="E7" s="23">
+        <f>IF(Drivers!E40=0,0,(Drivers!E11*Assumptions!E14+Drivers!E25*Assumptions!E26)/Drivers!E40)</f>
+        <v/>
+      </c>
+      <c r="F7" s="23">
+        <f>IF(Drivers!F40=0,0,(Drivers!F11*Assumptions!F14+Drivers!F25*Assumptions!F26)/Drivers!F40)</f>
+        <v/>
+      </c>
+      <c r="G7" s="23">
+        <f>IF(Drivers!G40=0,0,(Drivers!G11*Assumptions!G14+Drivers!G25*Assumptions!G26)/Drivers!G40)</f>
+        <v/>
+      </c>
+      <c r="H7" s="23">
+        <f>IF(Drivers!H40=0,0,(Drivers!H11*Assumptions!H14+Drivers!H25*Assumptions!H26)/Drivers!H40)</f>
+        <v/>
+      </c>
+      <c r="I7" s="23">
+        <f>IF(Drivers!I40=0,0,(Drivers!I11*Assumptions!I14+Drivers!I25*Assumptions!I26)/Drivers!I40)</f>
+        <v/>
+      </c>
+      <c r="J7" s="23">
+        <f>IF(Drivers!J40=0,0,(Drivers!J11*Assumptions!J14+Drivers!J25*Assumptions!J26)/Drivers!J40)</f>
+        <v/>
+      </c>
+      <c r="K7" s="23">
+        <f>IF(Drivers!K40=0,0,(Drivers!K11*Assumptions!K14+Drivers!K25*Assumptions!K26)/Drivers!K40)</f>
+        <v/>
+      </c>
+      <c r="L7" s="23">
+        <f>IF(Drivers!L40=0,0,(Drivers!L11*Assumptions!L14+Drivers!L25*Assumptions!L26)/Drivers!L40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Expected athlete life</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="C8" s="55">
+        <f>IF(C7=0,0,1/C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="55">
+        <f>IF(D7=0,0,1/D7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="55">
+        <f>IF(E7=0,0,1/E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="55">
+        <f>IF(F7=0,0,1/F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="55">
+        <f>IF(G7=0,0,1/G7)</f>
+        <v/>
+      </c>
+      <c r="H8" s="55">
+        <f>IF(H7=0,0,1/H7)</f>
+        <v/>
+      </c>
+      <c r="I8" s="55">
+        <f>IF(I7=0,0,1/I7)</f>
+        <v/>
+      </c>
+      <c r="J8" s="55">
+        <f>IF(J7=0,0,1/J7)</f>
+        <v/>
+      </c>
+      <c r="K8" s="55">
+        <f>IF(K7=0,0,1/K7)</f>
+        <v/>
+      </c>
+      <c r="L8" s="55">
+        <f>IF(L7=0,0,1/L7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Net revenue per athlete</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>EUR/yr</t>
+        </is>
+      </c>
+      <c r="C9" s="30">
+        <f>IF(Drivers!C5=0,0,Revenue!C22/Drivers!C5)</f>
+        <v/>
+      </c>
+      <c r="D9" s="30">
+        <f>IF(Drivers!D5=0,0,Revenue!D22/Drivers!D5)</f>
+        <v/>
+      </c>
+      <c r="E9" s="30">
+        <f>IF(Drivers!E5=0,0,Revenue!E22/Drivers!E5)</f>
+        <v/>
+      </c>
+      <c r="F9" s="30">
+        <f>IF(Drivers!F5=0,0,Revenue!F22/Drivers!F5)</f>
+        <v/>
+      </c>
+      <c r="G9" s="30">
+        <f>IF(Drivers!G5=0,0,Revenue!G22/Drivers!G5)</f>
+        <v/>
+      </c>
+      <c r="H9" s="30">
+        <f>IF(Drivers!H5=0,0,Revenue!H22/Drivers!H5)</f>
+        <v/>
+      </c>
+      <c r="I9" s="30">
+        <f>IF(Drivers!I5=0,0,Revenue!I22/Drivers!I5)</f>
+        <v/>
+      </c>
+      <c r="J9" s="30">
+        <f>IF(Drivers!J5=0,0,Revenue!J22/Drivers!J5)</f>
+        <v/>
+      </c>
+      <c r="K9" s="30">
+        <f>IF(Drivers!K5=0,0,Revenue!K22/Drivers!K5)</f>
+        <v/>
+      </c>
+      <c r="L9" s="30">
+        <f>IF(Drivers!L5=0,0,Revenue!L22/Drivers!L5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Contribution per athlete per year</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>after COGS</t>
+        </is>
+      </c>
+      <c r="C10" s="30">
+        <f>IF(Revenue!C22=0,0,C9*'P&amp;L'!C6/Revenue!C22)</f>
+        <v/>
+      </c>
+      <c r="D10" s="30">
+        <f>IF(Revenue!D22=0,0,D9*'P&amp;L'!D6/Revenue!D22)</f>
+        <v/>
+      </c>
+      <c r="E10" s="30">
+        <f>IF(Revenue!E22=0,0,E9*'P&amp;L'!E6/Revenue!E22)</f>
+        <v/>
+      </c>
+      <c r="F10" s="30">
+        <f>IF(Revenue!F22=0,0,F9*'P&amp;L'!F6/Revenue!F22)</f>
+        <v/>
+      </c>
+      <c r="G10" s="30">
+        <f>IF(Revenue!G22=0,0,G9*'P&amp;L'!G6/Revenue!G22)</f>
+        <v/>
+      </c>
+      <c r="H10" s="30">
+        <f>IF(Revenue!H22=0,0,H9*'P&amp;L'!H6/Revenue!H22)</f>
+        <v/>
+      </c>
+      <c r="I10" s="30">
+        <f>IF(Revenue!I22=0,0,I9*'P&amp;L'!I6/Revenue!I22)</f>
+        <v/>
+      </c>
+      <c r="J10" s="30">
+        <f>IF(Revenue!J22=0,0,J9*'P&amp;L'!J6/Revenue!J22)</f>
+        <v/>
+      </c>
+      <c r="K10" s="30">
+        <f>IF(Revenue!K22=0,0,K9*'P&amp;L'!K6/Revenue!K22)</f>
+        <v/>
+      </c>
+      <c r="L10" s="30">
+        <f>IF(Revenue!L22=0,0,L9*'P&amp;L'!L6/Revenue!L22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>ATHLETE LTV</t>
+        </is>
+      </c>
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C11" s="45">
+        <f>C10*C8</f>
+        <v/>
+      </c>
+      <c r="D11" s="45">
+        <f>D10*D8</f>
+        <v/>
+      </c>
+      <c r="E11" s="45">
+        <f>E10*E8</f>
+        <v/>
+      </c>
+      <c r="F11" s="45">
+        <f>F10*F8</f>
+        <v/>
+      </c>
+      <c r="G11" s="45">
+        <f>G10*G8</f>
+        <v/>
+      </c>
+      <c r="H11" s="45">
+        <f>H10*H8</f>
+        <v/>
+      </c>
+      <c r="I11" s="45">
+        <f>I10*I8</f>
+        <v/>
+      </c>
+      <c r="J11" s="45">
+        <f>J10*J8</f>
+        <v/>
+      </c>
+      <c r="K11" s="45">
+        <f>K10*K8</f>
+        <v/>
+      </c>
+      <c r="L11" s="45">
+        <f>L10*L8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>LTV / CAC</t>
+        </is>
+      </c>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C12" s="52">
+        <f>IF(C6=0,0,C11/C6)</f>
+        <v/>
+      </c>
+      <c r="D12" s="52">
+        <f>IF(D6=0,0,D11/D6)</f>
+        <v/>
+      </c>
+      <c r="E12" s="52">
+        <f>IF(E6=0,0,E11/E6)</f>
+        <v/>
+      </c>
+      <c r="F12" s="52">
+        <f>IF(F6=0,0,F11/F6)</f>
+        <v/>
+      </c>
+      <c r="G12" s="52">
+        <f>IF(G6=0,0,G11/G6)</f>
+        <v/>
+      </c>
+      <c r="H12" s="52">
+        <f>IF(H6=0,0,H11/H6)</f>
+        <v/>
+      </c>
+      <c r="I12" s="52">
+        <f>IF(I6=0,0,I11/I6)</f>
+        <v/>
+      </c>
+      <c r="J12" s="52">
+        <f>IF(J6=0,0,J11/J6)</f>
+        <v/>
+      </c>
+      <c r="K12" s="52">
+        <f>IF(K6=0,0,K11/K6)</f>
+        <v/>
+      </c>
+      <c r="L12" s="52">
+        <f>IF(L6=0,0,L11/L6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>CAC payback</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="C13" s="56">
+        <f>IF(C10&lt;=0,0,12*C6/C10)</f>
+        <v/>
+      </c>
+      <c r="D13" s="56">
+        <f>IF(D10&lt;=0,0,12*D6/D10)</f>
+        <v/>
+      </c>
+      <c r="E13" s="56">
+        <f>IF(E10&lt;=0,0,12*E6/E10)</f>
+        <v/>
+      </c>
+      <c r="F13" s="56">
+        <f>IF(F10&lt;=0,0,12*F6/F10)</f>
+        <v/>
+      </c>
+      <c r="G13" s="56">
+        <f>IF(G10&lt;=0,0,12*G6/G10)</f>
+        <v/>
+      </c>
+      <c r="H13" s="56">
+        <f>IF(H10&lt;=0,0,12*H6/H10)</f>
+        <v/>
+      </c>
+      <c r="I13" s="56">
+        <f>IF(I10&lt;=0,0,12*I6/I10)</f>
+        <v/>
+      </c>
+      <c r="J13" s="56">
+        <f>IF(J10&lt;=0,0,12*J6/J10)</f>
+        <v/>
+      </c>
+      <c r="K13" s="56">
+        <f>IF(K10&lt;=0,0,12*K6/K10)</f>
+        <v/>
+      </c>
+      <c r="L13" s="56">
+        <f>IF(L10&lt;=0,0,12*L6/L10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="54" t="inlineStr">
+        <is>
+          <t>The athlete LTV/CAC ratio is unusually high, and that is the thesis rather than an error: acquisition is cheap precisely because there is no incumbent agent to outbid in these sports. It should be read alongside the fan LTV below, which is small — the economics work on volume of athletes, not on the value of any one of them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>FAN — NICHE SUBSCRIPTION ONLY</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="57" t="inlineStr">
+        <is>
+          <t>excludes PPV and tips, which the revenue model carries separately</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="12" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Fan ARPU, VAT inclusive</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>EUR/mo</t>
+        </is>
+      </c>
+      <c r="C19" s="29">
+        <f>Assumptions!C12</f>
+        <v/>
+      </c>
+      <c r="D19" s="29">
+        <f>Assumptions!D12</f>
+        <v/>
+      </c>
+      <c r="E19" s="29">
+        <f>Assumptions!E12</f>
+        <v/>
+      </c>
+      <c r="F19" s="29">
+        <f>Assumptions!F12</f>
+        <v/>
+      </c>
+      <c r="G19" s="29">
+        <f>Assumptions!G12</f>
+        <v/>
+      </c>
+      <c r="H19" s="29">
+        <f>Assumptions!H12</f>
+        <v/>
+      </c>
+      <c r="I19" s="29">
+        <f>Assumptions!I12</f>
+        <v/>
+      </c>
+      <c r="J19" s="29">
+        <f>Assumptions!J12</f>
+        <v/>
+      </c>
+      <c r="K19" s="29">
+        <f>Assumptions!K12</f>
+        <v/>
+      </c>
+      <c r="L19" s="29">
+        <f>Assumptions!L12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Net of VAT</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>EUR/mo</t>
+        </is>
+      </c>
+      <c r="C20" s="29">
+        <f>C19/(1+Assumptions!C42)</f>
+        <v/>
+      </c>
+      <c r="D20" s="29">
+        <f>D19/(1+Assumptions!D42)</f>
+        <v/>
+      </c>
+      <c r="E20" s="29">
+        <f>E19/(1+Assumptions!E42)</f>
+        <v/>
+      </c>
+      <c r="F20" s="29">
+        <f>F19/(1+Assumptions!F42)</f>
+        <v/>
+      </c>
+      <c r="G20" s="29">
+        <f>G19/(1+Assumptions!G42)</f>
+        <v/>
+      </c>
+      <c r="H20" s="29">
+        <f>H19/(1+Assumptions!H42)</f>
+        <v/>
+      </c>
+      <c r="I20" s="29">
+        <f>I19/(1+Assumptions!I42)</f>
+        <v/>
+      </c>
+      <c r="J20" s="29">
+        <f>J19/(1+Assumptions!J42)</f>
+        <v/>
+      </c>
+      <c r="K20" s="29">
+        <f>K19/(1+Assumptions!K42)</f>
+        <v/>
+      </c>
+      <c r="L20" s="29">
+        <f>L19/(1+Assumptions!L42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Our take</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>EUR/mo</t>
+        </is>
+      </c>
+      <c r="C21" s="29">
+        <f>C20*Assumptions!C40</f>
+        <v/>
+      </c>
+      <c r="D21" s="29">
+        <f>D20*Assumptions!D40</f>
+        <v/>
+      </c>
+      <c r="E21" s="29">
+        <f>E20*Assumptions!E40</f>
+        <v/>
+      </c>
+      <c r="F21" s="29">
+        <f>F20*Assumptions!F40</f>
+        <v/>
+      </c>
+      <c r="G21" s="29">
+        <f>G20*Assumptions!G40</f>
+        <v/>
+      </c>
+      <c r="H21" s="29">
+        <f>H20*Assumptions!H40</f>
+        <v/>
+      </c>
+      <c r="I21" s="29">
+        <f>I20*Assumptions!I40</f>
+        <v/>
+      </c>
+      <c r="J21" s="29">
+        <f>J20*Assumptions!J40</f>
+        <v/>
+      </c>
+      <c r="K21" s="29">
+        <f>K20*Assumptions!K40</f>
+        <v/>
+      </c>
+      <c r="L21" s="29">
+        <f>L20*Assumptions!L40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Payment cost on the charge</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>EUR/mo</t>
+        </is>
+      </c>
+      <c r="C22" s="29">
+        <f>C19*Assumptions!C44+Assumptions!C45</f>
+        <v/>
+      </c>
+      <c r="D22" s="29">
+        <f>D19*Assumptions!D44+Assumptions!D45</f>
+        <v/>
+      </c>
+      <c r="E22" s="29">
+        <f>E19*Assumptions!E44+Assumptions!E45</f>
+        <v/>
+      </c>
+      <c r="F22" s="29">
+        <f>F19*Assumptions!F44+Assumptions!F45</f>
+        <v/>
+      </c>
+      <c r="G22" s="29">
+        <f>G19*Assumptions!G44+Assumptions!G45</f>
+        <v/>
+      </c>
+      <c r="H22" s="29">
+        <f>H19*Assumptions!H44+Assumptions!H45</f>
+        <v/>
+      </c>
+      <c r="I22" s="29">
+        <f>I19*Assumptions!I44+Assumptions!I45</f>
+        <v/>
+      </c>
+      <c r="J22" s="29">
+        <f>J19*Assumptions!J44+Assumptions!J45</f>
+        <v/>
+      </c>
+      <c r="K22" s="29">
+        <f>K19*Assumptions!K44+Assumptions!K45</f>
+        <v/>
+      </c>
+      <c r="L22" s="29">
+        <f>L19*Assumptions!L44+Assumptions!L45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Payout cost, share per fan month</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C23" s="29">
+        <f>C19*Assumptions!C46+Assumptions!C47/30</f>
+        <v/>
+      </c>
+      <c r="D23" s="29">
+        <f>D19*Assumptions!D46+Assumptions!D47/30</f>
+        <v/>
+      </c>
+      <c r="E23" s="29">
+        <f>E19*Assumptions!E46+Assumptions!E47/30</f>
+        <v/>
+      </c>
+      <c r="F23" s="29">
+        <f>F19*Assumptions!F46+Assumptions!F47/30</f>
+        <v/>
+      </c>
+      <c r="G23" s="29">
+        <f>G19*Assumptions!G46+Assumptions!G47/30</f>
+        <v/>
+      </c>
+      <c r="H23" s="29">
+        <f>H19*Assumptions!H46+Assumptions!H47/30</f>
+        <v/>
+      </c>
+      <c r="I23" s="29">
+        <f>I19*Assumptions!I46+Assumptions!I47/30</f>
+        <v/>
+      </c>
+      <c r="J23" s="29">
+        <f>J19*Assumptions!J46+Assumptions!J47/30</f>
+        <v/>
+      </c>
+      <c r="K23" s="29">
+        <f>K19*Assumptions!K46+Assumptions!K47/30</f>
+        <v/>
+      </c>
+      <c r="L23" s="29">
+        <f>L19*Assumptions!L46+Assumptions!L47/30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Contribution per fan month</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C24" s="58">
+        <f>C21-C22-C23</f>
+        <v/>
+      </c>
+      <c r="D24" s="58">
+        <f>D21-D22-D23</f>
+        <v/>
+      </c>
+      <c r="E24" s="58">
+        <f>E21-E22-E23</f>
+        <v/>
+      </c>
+      <c r="F24" s="58">
+        <f>F21-F22-F23</f>
+        <v/>
+      </c>
+      <c r="G24" s="58">
+        <f>G21-G22-G23</f>
+        <v/>
+      </c>
+      <c r="H24" s="58">
+        <f>H21-H22-H23</f>
+        <v/>
+      </c>
+      <c r="I24" s="58">
+        <f>I21-I22-I23</f>
+        <v/>
+      </c>
+      <c r="J24" s="58">
+        <f>J21-J22-J23</f>
+        <v/>
+      </c>
+      <c r="K24" s="58">
+        <f>K21-K22-K23</f>
+        <v/>
+      </c>
+      <c r="L24" s="58">
+        <f>L21-L22-L23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Fan churn</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>per month</t>
+        </is>
+      </c>
+      <c r="C25" s="23">
+        <f>Assumptions!C13</f>
+        <v/>
+      </c>
+      <c r="D25" s="23">
+        <f>Assumptions!D13</f>
+        <v/>
+      </c>
+      <c r="E25" s="23">
+        <f>Assumptions!E13</f>
+        <v/>
+      </c>
+      <c r="F25" s="23">
+        <f>Assumptions!F13</f>
+        <v/>
+      </c>
+      <c r="G25" s="23">
+        <f>Assumptions!G13</f>
+        <v/>
+      </c>
+      <c r="H25" s="23">
+        <f>Assumptions!H13</f>
+        <v/>
+      </c>
+      <c r="I25" s="23">
+        <f>Assumptions!I13</f>
+        <v/>
+      </c>
+      <c r="J25" s="23">
+        <f>Assumptions!J13</f>
+        <v/>
+      </c>
+      <c r="K25" s="23">
+        <f>Assumptions!K13</f>
+        <v/>
+      </c>
+      <c r="L25" s="23">
+        <f>Assumptions!L13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Expected fan life</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="C26" s="56">
+        <f>IF(C25=0,0,1/C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="56">
+        <f>IF(D25=0,0,1/D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="56">
+        <f>IF(E25=0,0,1/E25)</f>
+        <v/>
+      </c>
+      <c r="F26" s="56">
+        <f>IF(F25=0,0,1/F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="56">
+        <f>IF(G25=0,0,1/G25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="56">
+        <f>IF(H25=0,0,1/H25)</f>
+        <v/>
+      </c>
+      <c r="I26" s="56">
+        <f>IF(I25=0,0,1/I25)</f>
+        <v/>
+      </c>
+      <c r="J26" s="56">
+        <f>IF(J25=0,0,1/J25)</f>
+        <v/>
+      </c>
+      <c r="K26" s="56">
+        <f>IF(K25=0,0,1/K25)</f>
+        <v/>
+      </c>
+      <c r="L26" s="56">
+        <f>IF(L25=0,0,1/L25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>FAN LTV</t>
+        </is>
+      </c>
+      <c r="B27" s="40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C27" s="59">
+        <f>C24*C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="59">
+        <f>D24*D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="59">
+        <f>E24*E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="59">
+        <f>F24*F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="59">
+        <f>G24*G26</f>
+        <v/>
+      </c>
+      <c r="H27" s="59">
+        <f>H24*H26</f>
+        <v/>
+      </c>
+      <c r="I27" s="59">
+        <f>I24*I26</f>
+        <v/>
+      </c>
+      <c r="J27" s="59">
+        <f>J24*J26</f>
+        <v/>
+      </c>
+      <c r="K27" s="59">
+        <f>K24*K26</f>
+        <v/>
+      </c>
+      <c r="L27" s="59">
+        <f>L24*L26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Fan CAC</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="54" t="inlineStr">
+        <is>
+          <t>Fan CAC is zero by construction: athletes bring their own audiences and the model spends nothing acquiring fans. That understates the risk rather than flattering the return, and the plan discloses it as such.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>SPONSOR</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Sponsor CAC</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C33" s="30">
+        <f>Assumptions!C37</f>
+        <v/>
+      </c>
+      <c r="D33" s="30">
+        <f>Assumptions!D37</f>
+        <v/>
+      </c>
+      <c r="E33" s="30">
+        <f>Assumptions!E37</f>
+        <v/>
+      </c>
+      <c r="F33" s="30">
+        <f>Assumptions!F37</f>
+        <v/>
+      </c>
+      <c r="G33" s="30">
+        <f>Assumptions!G37</f>
+        <v/>
+      </c>
+      <c r="H33" s="30">
+        <f>Assumptions!H37</f>
+        <v/>
+      </c>
+      <c r="I33" s="30">
+        <f>Assumptions!I37</f>
+        <v/>
+      </c>
+      <c r="J33" s="30">
+        <f>Assumptions!J37</f>
+        <v/>
+      </c>
+      <c r="K33" s="30">
+        <f>Assumptions!K37</f>
+        <v/>
+      </c>
+      <c r="L33" s="30">
+        <f>Assumptions!L37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>SaaS per paying sponsor</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>EUR/yr</t>
+        </is>
+      </c>
+      <c r="C34" s="30">
+        <f>Assumptions!C36*12</f>
+        <v/>
+      </c>
+      <c r="D34" s="30">
+        <f>Assumptions!D36*12</f>
+        <v/>
+      </c>
+      <c r="E34" s="30">
+        <f>Assumptions!E36*12</f>
+        <v/>
+      </c>
+      <c r="F34" s="30">
+        <f>Assumptions!F36*12</f>
+        <v/>
+      </c>
+      <c r="G34" s="30">
+        <f>Assumptions!G36*12</f>
+        <v/>
+      </c>
+      <c r="H34" s="30">
+        <f>Assumptions!H36*12</f>
+        <v/>
+      </c>
+      <c r="I34" s="30">
+        <f>Assumptions!I36*12</f>
+        <v/>
+      </c>
+      <c r="J34" s="30">
+        <f>Assumptions!J36*12</f>
+        <v/>
+      </c>
+      <c r="K34" s="30">
+        <f>Assumptions!K36*12</f>
+        <v/>
+      </c>
+      <c r="L34" s="30">
+        <f>Assumptions!L36*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>Sponsorship take per paying sponsor</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>EUR/yr</t>
+        </is>
+      </c>
+      <c r="C35" s="30">
+        <f>IF(Drivers!C48=0,0,Revenue!C20/Drivers!C48)</f>
+        <v/>
+      </c>
+      <c r="D35" s="30">
+        <f>IF(Drivers!D48=0,0,Revenue!D20/Drivers!D48)</f>
+        <v/>
+      </c>
+      <c r="E35" s="30">
+        <f>IF(Drivers!E48=0,0,Revenue!E20/Drivers!E48)</f>
+        <v/>
+      </c>
+      <c r="F35" s="30">
+        <f>IF(Drivers!F48=0,0,Revenue!F20/Drivers!F48)</f>
+        <v/>
+      </c>
+      <c r="G35" s="30">
+        <f>IF(Drivers!G48=0,0,Revenue!G20/Drivers!G48)</f>
+        <v/>
+      </c>
+      <c r="H35" s="30">
+        <f>IF(Drivers!H48=0,0,Revenue!H20/Drivers!H48)</f>
+        <v/>
+      </c>
+      <c r="I35" s="30">
+        <f>IF(Drivers!I48=0,0,Revenue!I20/Drivers!I48)</f>
+        <v/>
+      </c>
+      <c r="J35" s="30">
+        <f>IF(Drivers!J48=0,0,Revenue!J20/Drivers!J48)</f>
+        <v/>
+      </c>
+      <c r="K35" s="30">
+        <f>IF(Drivers!K48=0,0,Revenue!K20/Drivers!K48)</f>
+        <v/>
+      </c>
+      <c r="L35" s="30">
+        <f>IF(Drivers!L48=0,0,Revenue!L20/Drivers!L48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>Contribution per sponsor per year</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C36" s="47">
+        <f>C34+C35</f>
+        <v/>
+      </c>
+      <c r="D36" s="47">
+        <f>D34+D35</f>
+        <v/>
+      </c>
+      <c r="E36" s="47">
+        <f>E34+E35</f>
+        <v/>
+      </c>
+      <c r="F36" s="47">
+        <f>F34+F35</f>
+        <v/>
+      </c>
+      <c r="G36" s="47">
+        <f>G34+G35</f>
+        <v/>
+      </c>
+      <c r="H36" s="47">
+        <f>H34+H35</f>
+        <v/>
+      </c>
+      <c r="I36" s="47">
+        <f>I34+I35</f>
+        <v/>
+      </c>
+      <c r="J36" s="47">
+        <f>J34+J35</f>
+        <v/>
+      </c>
+      <c r="K36" s="47">
+        <f>K34+K35</f>
+        <v/>
+      </c>
+      <c r="L36" s="47">
+        <f>L34+L35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  at gross margin</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C37" s="30">
+        <f>C36*'P&amp;L'!C7</f>
+        <v/>
+      </c>
+      <c r="D37" s="30">
+        <f>D36*'P&amp;L'!D7</f>
+        <v/>
+      </c>
+      <c r="E37" s="30">
+        <f>E36*'P&amp;L'!E7</f>
+        <v/>
+      </c>
+      <c r="F37" s="30">
+        <f>F36*'P&amp;L'!F7</f>
+        <v/>
+      </c>
+      <c r="G37" s="30">
+        <f>G36*'P&amp;L'!G7</f>
+        <v/>
+      </c>
+      <c r="H37" s="30">
+        <f>H36*'P&amp;L'!H7</f>
+        <v/>
+      </c>
+      <c r="I37" s="30">
+        <f>I36*'P&amp;L'!I7</f>
+        <v/>
+      </c>
+      <c r="J37" s="30">
+        <f>J36*'P&amp;L'!J7</f>
+        <v/>
+      </c>
+      <c r="K37" s="30">
+        <f>K36*'P&amp;L'!K7</f>
+        <v/>
+      </c>
+      <c r="L37" s="30">
+        <f>L36*'P&amp;L'!L7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="44" t="inlineStr">
+        <is>
+          <t>CAC payback</t>
+        </is>
+      </c>
+      <c r="B38" s="40" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="C38" s="51">
+        <f>IF(C37&lt;=0,0,12*C33/C37)</f>
+        <v/>
+      </c>
+      <c r="D38" s="51">
+        <f>IF(D37&lt;=0,0,12*D33/D37)</f>
+        <v/>
+      </c>
+      <c r="E38" s="51">
+        <f>IF(E37&lt;=0,0,12*E33/E37)</f>
+        <v/>
+      </c>
+      <c r="F38" s="51">
+        <f>IF(F37&lt;=0,0,12*F33/F37)</f>
+        <v/>
+      </c>
+      <c r="G38" s="51">
+        <f>IF(G37&lt;=0,0,12*G33/G37)</f>
+        <v/>
+      </c>
+      <c r="H38" s="51">
+        <f>IF(H37&lt;=0,0,12*H33/H37)</f>
+        <v/>
+      </c>
+      <c r="I38" s="51">
+        <f>IF(I37&lt;=0,0,12*I33/I37)</f>
+        <v/>
+      </c>
+      <c r="J38" s="51">
+        <f>IF(J37&lt;=0,0,12*J33/J37)</f>
+        <v/>
+      </c>
+      <c r="K38" s="51">
+        <f>IF(K37&lt;=0,0,12*K33/K37)</f>
+        <v/>
+      </c>
+      <c r="L38" s="51">
+        <f>IF(L37&lt;=0,0,12*L33/L37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="54" t="inlineStr">
+        <is>
+          <t>No sponsor LTV is shown. It needs a sponsor retention assumption the model does not make, and inventing one here would create a figure nothing else in the plan validates. Payback needs no such assumption, so payback is what is reported.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="I2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KPIs — the dozen numbers that describe the business</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Input — change me</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Sourced fact</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Formula (this sheet)</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Formula (other sheet)</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Y7</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Y8</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Y9</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Y10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>SCALE</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="12" t="n"/>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="12" t="n"/>
+      <c r="L4" s="12" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Active athletes</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C5" s="17">
+        <f>Drivers!C5</f>
+        <v/>
+      </c>
+      <c r="D5" s="17">
+        <f>Drivers!D5</f>
+        <v/>
+      </c>
+      <c r="E5" s="17">
+        <f>Drivers!E5</f>
+        <v/>
+      </c>
+      <c r="F5" s="17">
+        <f>Drivers!F5</f>
+        <v/>
+      </c>
+      <c r="G5" s="17">
+        <f>Drivers!G5</f>
+        <v/>
+      </c>
+      <c r="H5" s="17">
+        <f>Drivers!H5</f>
+        <v/>
+      </c>
+      <c r="I5" s="17">
+        <f>Drivers!I5</f>
+        <v/>
+      </c>
+      <c r="J5" s="17">
+        <f>Drivers!J5</f>
+        <v/>
+      </c>
+      <c r="K5" s="17">
+        <f>Drivers!K5</f>
+        <v/>
+      </c>
+      <c r="L5" s="17">
+        <f>Drivers!L5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Paying fans, year end</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C6" s="17">
+        <f>Drivers!C38</f>
+        <v/>
+      </c>
+      <c r="D6" s="17">
+        <f>Drivers!D38</f>
+        <v/>
+      </c>
+      <c r="E6" s="17">
+        <f>Drivers!E38</f>
+        <v/>
+      </c>
+      <c r="F6" s="17">
+        <f>Drivers!F38</f>
+        <v/>
+      </c>
+      <c r="G6" s="17">
+        <f>Drivers!G38</f>
+        <v/>
+      </c>
+      <c r="H6" s="17">
+        <f>Drivers!H38</f>
+        <v/>
+      </c>
+      <c r="I6" s="17">
+        <f>Drivers!I38</f>
+        <v/>
+      </c>
+      <c r="J6" s="17">
+        <f>Drivers!J38</f>
+        <v/>
+      </c>
+      <c r="K6" s="17">
+        <f>Drivers!K38</f>
+        <v/>
+      </c>
+      <c r="L6" s="17">
+        <f>Drivers!L38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Paying sponsors</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C7" s="17">
+        <f>Drivers!C48</f>
+        <v/>
+      </c>
+      <c r="D7" s="17">
+        <f>Drivers!D48</f>
+        <v/>
+      </c>
+      <c r="E7" s="17">
+        <f>Drivers!E48</f>
+        <v/>
+      </c>
+      <c r="F7" s="17">
+        <f>Drivers!F48</f>
+        <v/>
+      </c>
+      <c r="G7" s="17">
+        <f>Drivers!G48</f>
+        <v/>
+      </c>
+      <c r="H7" s="17">
+        <f>Drivers!H48</f>
+        <v/>
+      </c>
+      <c r="I7" s="17">
+        <f>Drivers!I48</f>
+        <v/>
+      </c>
+      <c r="J7" s="17">
+        <f>Drivers!J48</f>
+        <v/>
+      </c>
+      <c r="K7" s="17">
+        <f>Drivers!K48</f>
+        <v/>
+      </c>
+      <c r="L7" s="17">
+        <f>Drivers!L48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Recurring MRR</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>subs x take + SaaS / 12</t>
+        </is>
+      </c>
+      <c r="C8" s="30">
+        <f>(Revenue!C7*Assumptions!C40+Revenue!C21)/12</f>
+        <v/>
+      </c>
+      <c r="D8" s="30">
+        <f>(Revenue!D7*Assumptions!D40+Revenue!D21)/12</f>
+        <v/>
+      </c>
+      <c r="E8" s="30">
+        <f>(Revenue!E7*Assumptions!E40+Revenue!E21)/12</f>
+        <v/>
+      </c>
+      <c r="F8" s="30">
+        <f>(Revenue!F7*Assumptions!F40+Revenue!F21)/12</f>
+        <v/>
+      </c>
+      <c r="G8" s="30">
+        <f>(Revenue!G7*Assumptions!G40+Revenue!G21)/12</f>
+        <v/>
+      </c>
+      <c r="H8" s="30">
+        <f>(Revenue!H7*Assumptions!H40+Revenue!H21)/12</f>
+        <v/>
+      </c>
+      <c r="I8" s="30">
+        <f>(Revenue!I7*Assumptions!I40+Revenue!I21)/12</f>
+        <v/>
+      </c>
+      <c r="J8" s="30">
+        <f>(Revenue!J7*Assumptions!J40+Revenue!J21)/12</f>
+        <v/>
+      </c>
+      <c r="K8" s="30">
+        <f>(Revenue!K7*Assumptions!K40+Revenue!K21)/12</f>
+        <v/>
+      </c>
+      <c r="L8" s="30">
+        <f>(Revenue!L7*Assumptions!L40+Revenue!L21)/12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>QUALITY OF REVENUE</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="12" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Net revenue</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C11" s="30">
+        <f>Revenue!C22</f>
+        <v/>
+      </c>
+      <c r="D11" s="30">
+        <f>Revenue!D22</f>
+        <v/>
+      </c>
+      <c r="E11" s="30">
+        <f>Revenue!E22</f>
+        <v/>
+      </c>
+      <c r="F11" s="30">
+        <f>Revenue!F22</f>
+        <v/>
+      </c>
+      <c r="G11" s="30">
+        <f>Revenue!G22</f>
+        <v/>
+      </c>
+      <c r="H11" s="30">
+        <f>Revenue!H22</f>
+        <v/>
+      </c>
+      <c r="I11" s="30">
+        <f>Revenue!I22</f>
+        <v/>
+      </c>
+      <c r="J11" s="30">
+        <f>Revenue!J22</f>
+        <v/>
+      </c>
+      <c r="K11" s="30">
+        <f>Revenue!K22</f>
+        <v/>
+      </c>
+      <c r="L11" s="30">
+        <f>Revenue!L22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C12" s="23">
+        <f>'P&amp;L'!C7</f>
+        <v/>
+      </c>
+      <c r="D12" s="23">
+        <f>'P&amp;L'!D7</f>
+        <v/>
+      </c>
+      <c r="E12" s="23">
+        <f>'P&amp;L'!E7</f>
+        <v/>
+      </c>
+      <c r="F12" s="23">
+        <f>'P&amp;L'!F7</f>
+        <v/>
+      </c>
+      <c r="G12" s="23">
+        <f>'P&amp;L'!G7</f>
+        <v/>
+      </c>
+      <c r="H12" s="23">
+        <f>'P&amp;L'!H7</f>
+        <v/>
+      </c>
+      <c r="I12" s="23">
+        <f>'P&amp;L'!I7</f>
+        <v/>
+      </c>
+      <c r="J12" s="23">
+        <f>'P&amp;L'!J7</f>
+        <v/>
+      </c>
+      <c r="K12" s="23">
+        <f>'P&amp;L'!K7</f>
+        <v/>
+      </c>
+      <c r="L12" s="23">
+        <f>'P&amp;L'!L7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>EBITDA margin</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C13" s="23">
+        <f>'P&amp;L'!C11</f>
+        <v/>
+      </c>
+      <c r="D13" s="23">
+        <f>'P&amp;L'!D11</f>
+        <v/>
+      </c>
+      <c r="E13" s="23">
+        <f>'P&amp;L'!E11</f>
+        <v/>
+      </c>
+      <c r="F13" s="23">
+        <f>'P&amp;L'!F11</f>
+        <v/>
+      </c>
+      <c r="G13" s="23">
+        <f>'P&amp;L'!G11</f>
+        <v/>
+      </c>
+      <c r="H13" s="23">
+        <f>'P&amp;L'!H11</f>
+        <v/>
+      </c>
+      <c r="I13" s="23">
+        <f>'P&amp;L'!I11</f>
+        <v/>
+      </c>
+      <c r="J13" s="23">
+        <f>'P&amp;L'!J11</f>
+        <v/>
+      </c>
+      <c r="K13" s="23">
+        <f>'P&amp;L'!K11</f>
+        <v/>
+      </c>
+      <c r="L13" s="23">
+        <f>'P&amp;L'!L11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Revenue per FTE</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C14" s="30">
+        <f>IF(Assumptions!C60=0,0,Revenue!C22/Assumptions!C60)</f>
+        <v/>
+      </c>
+      <c r="D14" s="30">
+        <f>IF(Assumptions!D60=0,0,Revenue!D22/Assumptions!D60)</f>
+        <v/>
+      </c>
+      <c r="E14" s="30">
+        <f>IF(Assumptions!E60=0,0,Revenue!E22/Assumptions!E60)</f>
+        <v/>
+      </c>
+      <c r="F14" s="30">
+        <f>IF(Assumptions!F60=0,0,Revenue!F22/Assumptions!F60)</f>
+        <v/>
+      </c>
+      <c r="G14" s="30">
+        <f>IF(Assumptions!G60=0,0,Revenue!G22/Assumptions!G60)</f>
+        <v/>
+      </c>
+      <c r="H14" s="30">
+        <f>IF(Assumptions!H60=0,0,Revenue!H22/Assumptions!H60)</f>
+        <v/>
+      </c>
+      <c r="I14" s="30">
+        <f>IF(Assumptions!I60=0,0,Revenue!I22/Assumptions!I60)</f>
+        <v/>
+      </c>
+      <c r="J14" s="30">
+        <f>IF(Assumptions!J60=0,0,Revenue!J22/Assumptions!J60)</f>
+        <v/>
+      </c>
+      <c r="K14" s="30">
+        <f>IF(Assumptions!K60=0,0,Revenue!K22/Assumptions!K60)</f>
+        <v/>
+      </c>
+      <c r="L14" s="30">
+        <f>IF(Assumptions!L60=0,0,Revenue!L22/Assumptions!L60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>RETENTION AND EFFICIENCY</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Fan churn, niche</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>per month</t>
+        </is>
+      </c>
+      <c r="C17" s="23">
+        <f>Assumptions!C13</f>
+        <v/>
+      </c>
+      <c r="D17" s="23">
+        <f>Assumptions!D13</f>
+        <v/>
+      </c>
+      <c r="E17" s="23">
+        <f>Assumptions!E13</f>
+        <v/>
+      </c>
+      <c r="F17" s="23">
+        <f>Assumptions!F13</f>
+        <v/>
+      </c>
+      <c r="G17" s="23">
+        <f>Assumptions!G13</f>
+        <v/>
+      </c>
+      <c r="H17" s="23">
+        <f>Assumptions!H13</f>
+        <v/>
+      </c>
+      <c r="I17" s="23">
+        <f>Assumptions!I13</f>
+        <v/>
+      </c>
+      <c r="J17" s="23">
+        <f>Assumptions!J13</f>
+        <v/>
+      </c>
+      <c r="K17" s="23">
+        <f>Assumptions!K13</f>
+        <v/>
+      </c>
+      <c r="L17" s="23">
+        <f>Assumptions!L13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Athlete churn, niche</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>per year</t>
+        </is>
+      </c>
+      <c r="C18" s="23">
+        <f>Assumptions!C14</f>
+        <v/>
+      </c>
+      <c r="D18" s="23">
+        <f>Assumptions!D14</f>
+        <v/>
+      </c>
+      <c r="E18" s="23">
+        <f>Assumptions!E14</f>
+        <v/>
+      </c>
+      <c r="F18" s="23">
+        <f>Assumptions!F14</f>
+        <v/>
+      </c>
+      <c r="G18" s="23">
+        <f>Assumptions!G14</f>
+        <v/>
+      </c>
+      <c r="H18" s="23">
+        <f>Assumptions!H14</f>
+        <v/>
+      </c>
+      <c r="I18" s="23">
+        <f>Assumptions!I14</f>
+        <v/>
+      </c>
+      <c r="J18" s="23">
+        <f>Assumptions!J14</f>
+        <v/>
+      </c>
+      <c r="K18" s="23">
+        <f>Assumptions!K14</f>
+        <v/>
+      </c>
+      <c r="L18" s="23">
+        <f>Assumptions!L14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Athlete LTV / CAC</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C19" s="31">
+        <f>CAC_CLV!C12</f>
+        <v/>
+      </c>
+      <c r="D19" s="31">
+        <f>CAC_CLV!D12</f>
+        <v/>
+      </c>
+      <c r="E19" s="31">
+        <f>CAC_CLV!E12</f>
+        <v/>
+      </c>
+      <c r="F19" s="31">
+        <f>CAC_CLV!F12</f>
+        <v/>
+      </c>
+      <c r="G19" s="31">
+        <f>CAC_CLV!G12</f>
+        <v/>
+      </c>
+      <c r="H19" s="31">
+        <f>CAC_CLV!H12</f>
+        <v/>
+      </c>
+      <c r="I19" s="31">
+        <f>CAC_CLV!I12</f>
+        <v/>
+      </c>
+      <c r="J19" s="31">
+        <f>CAC_CLV!J12</f>
+        <v/>
+      </c>
+      <c r="K19" s="31">
+        <f>CAC_CLV!K12</f>
+        <v/>
+      </c>
+      <c r="L19" s="31">
+        <f>CAC_CLV!L12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Take rate on GMV</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C20" s="23">
+        <f>Revenue!C24</f>
+        <v/>
+      </c>
+      <c r="D20" s="23">
+        <f>Revenue!D24</f>
+        <v/>
+      </c>
+      <c r="E20" s="23">
+        <f>Revenue!E24</f>
+        <v/>
+      </c>
+      <c r="F20" s="23">
+        <f>Revenue!F24</f>
+        <v/>
+      </c>
+      <c r="G20" s="23">
+        <f>Revenue!G24</f>
+        <v/>
+      </c>
+      <c r="H20" s="23">
+        <f>Revenue!H24</f>
+        <v/>
+      </c>
+      <c r="I20" s="23">
+        <f>Revenue!I24</f>
+        <v/>
+      </c>
+      <c r="J20" s="23">
+        <f>Revenue!J24</f>
+        <v/>
+      </c>
+      <c r="K20" s="23">
+        <f>Revenue!K24</f>
+        <v/>
+      </c>
+      <c r="L20" s="23">
+        <f>Revenue!L24</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="I2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Valuation — DCF, NPV, IRR and exit multiples</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Input — change me</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Sourced fact</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Formula (this sheet)</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Formula (other sheet)</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Y7</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Y8</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Y9</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Y10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C4" s="30">
+        <f>CashFlow!C9</f>
+        <v/>
+      </c>
+      <c r="D4" s="30">
+        <f>CashFlow!D9</f>
+        <v/>
+      </c>
+      <c r="E4" s="30">
+        <f>CashFlow!E9</f>
+        <v/>
+      </c>
+      <c r="F4" s="30">
+        <f>CashFlow!F9</f>
+        <v/>
+      </c>
+      <c r="G4" s="30">
+        <f>CashFlow!G9</f>
+        <v/>
+      </c>
+      <c r="H4" s="30">
+        <f>CashFlow!H9</f>
+        <v/>
+      </c>
+      <c r="I4" s="30">
+        <f>CashFlow!I9</f>
+        <v/>
+      </c>
+      <c r="J4" s="30">
+        <f>CashFlow!J9</f>
+        <v/>
+      </c>
+      <c r="K4" s="30">
+        <f>CashFlow!K9</f>
+        <v/>
+      </c>
+      <c r="L4" s="30">
+        <f>CashFlow!L9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>1/(1+WACC)^t</t>
+        </is>
+      </c>
+      <c r="C5" s="33">
+        <f>1/(1+Assumptions!$C$85)^1</f>
+        <v/>
+      </c>
+      <c r="D5" s="33">
+        <f>1/(1+Assumptions!$C$85)^2</f>
+        <v/>
+      </c>
+      <c r="E5" s="33">
+        <f>1/(1+Assumptions!$C$85)^3</f>
+        <v/>
+      </c>
+      <c r="F5" s="33">
+        <f>1/(1+Assumptions!$C$85)^4</f>
+        <v/>
+      </c>
+      <c r="G5" s="33">
+        <f>1/(1+Assumptions!$C$85)^5</f>
+        <v/>
+      </c>
+      <c r="H5" s="33">
+        <f>1/(1+Assumptions!$C$85)^6</f>
+        <v/>
+      </c>
+      <c r="I5" s="33">
+        <f>1/(1+Assumptions!$C$85)^7</f>
+        <v/>
+      </c>
+      <c r="J5" s="33">
+        <f>1/(1+Assumptions!$C$85)^8</f>
+        <v/>
+      </c>
+      <c r="K5" s="33">
+        <f>1/(1+Assumptions!$C$85)^9</f>
+        <v/>
+      </c>
+      <c r="L5" s="33">
+        <f>1/(1+Assumptions!$C$85)^10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="39" t="inlineStr">
+        <is>
+          <t>Discounted FCF</t>
+        </is>
+      </c>
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C6" s="43">
+        <f>C4*C5</f>
+        <v/>
+      </c>
+      <c r="D6" s="43">
+        <f>D4*D5</f>
+        <v/>
+      </c>
+      <c r="E6" s="43">
+        <f>E4*E5</f>
+        <v/>
+      </c>
+      <c r="F6" s="43">
+        <f>F4*F5</f>
+        <v/>
+      </c>
+      <c r="G6" s="43">
+        <f>G4*G5</f>
+        <v/>
+      </c>
+      <c r="H6" s="43">
+        <f>H4*H5</f>
+        <v/>
+      </c>
+      <c r="I6" s="43">
+        <f>I4*I5</f>
+        <v/>
+      </c>
+      <c r="J6" s="43">
+        <f>J4*J5</f>
+        <v/>
+      </c>
+      <c r="K6" s="43">
+        <f>K4*K5</f>
+        <v/>
+      </c>
+      <c r="L6" s="43">
+        <f>L4*L5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>FCF incl. terminal value</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>for the IRR below</t>
+        </is>
+      </c>
+      <c r="C8" s="47">
+        <f>C4+IF(1=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="47">
+        <f>D4+IF(2=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="E8" s="47">
+        <f>E4+IF(3=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="47">
+        <f>F4+IF(4=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="47">
+        <f>G4+IF(5=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="47">
+        <f>H4+IF(6=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="I8" s="47">
+        <f>I4+IF(7=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="J8" s="47">
+        <f>J4+IF(8=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="47">
+        <f>K4+IF(9=10,$C$11,0)</f>
+        <v/>
+      </c>
+      <c r="L8" s="47">
+        <f>L4+IF(10=10,$C$11,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>PV of explicit forecast</t>
+        </is>
+      </c>
+      <c r="C10" s="60">
+        <f>SUM(C6:L6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Terminal value at Y10</t>
+        </is>
+      </c>
+      <c r="C11" s="60">
+        <f>L4*(1+Assumptions!$C$86)/(Assumptions!$C$85-Assumptions!$C$86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="C12" s="60">
+        <f>C11*L5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ENTERPRISE VALUE (DCF)</t>
+        </is>
+      </c>
+      <c r="C13" s="60">
+        <f>C10+C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>RETURN METRICS</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="12" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>NPV of FCF at WACC</t>
+        </is>
+      </c>
+      <c r="C16" s="60">
+        <f>NPV(Assumptions!$C$85,C4:L4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>IRR of the plan</t>
+        </is>
+      </c>
+      <c r="C17" s="61">
+        <f>IRR(C4:L4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>IRR incl. terminal value</t>
+        </is>
+      </c>
+      <c r="C18" s="61">
+        <f>IRR(C8:L8,0.3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>EXIT MULTIPLE</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Y10 net revenue</t>
+        </is>
+      </c>
+      <c r="C21" s="60">
+        <f>Revenue!L22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Exit value at Y10</t>
+        </is>
+      </c>
+      <c r="C22" s="60">
+        <f>C21*Assumptions!$C$87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Discounted to today</t>
+        </is>
+      </c>
+      <c r="C23" s="60">
+        <f>C22*L5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>SENSITIVITY — enterprise value by WACC and terminal growth</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Terminal growth \ WACC</t>
+        </is>
+      </c>
+      <c r="C26" s="62" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D26" s="62" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E26" s="62" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F26" s="62" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G26" s="62" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H26" s="62" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C27" s="63">
+        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.01)/(0.18-0.01)/(1+0.18)^10</f>
+        <v/>
+      </c>
+      <c r="D27" s="63">
+        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.01)/(0.2-0.01)/(1+0.2)^10</f>
+        <v/>
+      </c>
+      <c r="E27" s="63">
+        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.01)/(0.22-0.01)/(1+0.22)^10</f>
+        <v/>
+      </c>
+      <c r="F27" s="63">
+        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.01)/(0.25-0.01)/(1+0.25)^10</f>
+        <v/>
+      </c>
+      <c r="G27" s="63">
+        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.01)/(0.28-0.01)/(1+0.28)^10</f>
+        <v/>
+      </c>
+      <c r="H27" s="63">
+        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.01)/(0.3-0.01)/(1+0.3)^10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="61" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C28" s="63">
+        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.02)/(0.18-0.02)/(1+0.18)^10</f>
+        <v/>
+      </c>
+      <c r="D28" s="63">
+        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.02)/(0.2-0.02)/(1+0.2)^10</f>
+        <v/>
+      </c>
+      <c r="E28" s="63">
+        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.02)/(0.22-0.02)/(1+0.22)^10</f>
+        <v/>
+      </c>
+      <c r="F28" s="63">
+        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.02)/(0.25-0.02)/(1+0.25)^10</f>
+        <v/>
+      </c>
+      <c r="G28" s="63">
+        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.02)/(0.28-0.02)/(1+0.28)^10</f>
+        <v/>
+      </c>
+      <c r="H28" s="63">
+        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.02)/(0.3-0.02)/(1+0.3)^10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="61" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C29" s="63">
+        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.03)/(0.18-0.03)/(1+0.18)^10</f>
+        <v/>
+      </c>
+      <c r="D29" s="63">
+        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.03)/(0.2-0.03)/(1+0.2)^10</f>
+        <v/>
+      </c>
+      <c r="E29" s="63">
+        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.03)/(0.22-0.03)/(1+0.22)^10</f>
+        <v/>
+      </c>
+      <c r="F29" s="63">
+        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.03)/(0.25-0.03)/(1+0.25)^10</f>
+        <v/>
+      </c>
+      <c r="G29" s="63">
+        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.03)/(0.28-0.03)/(1+0.28)^10</f>
+        <v/>
+      </c>
+      <c r="H29" s="63">
+        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.03)/(0.3-0.03)/(1+0.3)^10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C30" s="63">
+        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.04)/(0.18-0.04)/(1+0.18)^10</f>
+        <v/>
+      </c>
+      <c r="D30" s="63">
+        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.04)/(0.2-0.04)/(1+0.2)^10</f>
+        <v/>
+      </c>
+      <c r="E30" s="63">
+        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.04)/(0.22-0.04)/(1+0.22)^10</f>
+        <v/>
+      </c>
+      <c r="F30" s="63">
+        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.04)/(0.25-0.04)/(1+0.25)^10</f>
+        <v/>
+      </c>
+      <c r="G30" s="63">
+        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.04)/(0.28-0.04)/(1+0.28)^10</f>
+        <v/>
+      </c>
+      <c r="H30" s="63">
+        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.04)/(0.3-0.04)/(1+0.3)^10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="61" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C31" s="63">
+        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.05)/(0.18-0.05)/(1+0.18)^10</f>
+        <v/>
+      </c>
+      <c r="D31" s="63">
+        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.05)/(0.2-0.05)/(1+0.2)^10</f>
+        <v/>
+      </c>
+      <c r="E31" s="63">
+        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.05)/(0.22-0.05)/(1+0.22)^10</f>
+        <v/>
+      </c>
+      <c r="F31" s="63">
+        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.05)/(0.25-0.05)/(1+0.25)^10</f>
+        <v/>
+      </c>
+      <c r="G31" s="63">
+        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.05)/(0.28-0.05)/(1+0.28)^10</f>
+        <v/>
+      </c>
+      <c r="H31" s="63">
+        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.05)/(0.3-0.05)/(1+0.3)^10</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="I2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2473,676 +6125,676 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="55" t="inlineStr">
+      <c r="A2" s="64" t="inlineStr">
         <is>
           <t>Nothing on this sheet is our estimate. Every figure is published and cited, so it can be refreshed independently of anything we concluded from it. MarketModel derives our assumptions from these numbers; Assumptions then uses what MarketModel produces.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="56" t="inlineStr">
+      <c r="A4" s="65" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="56" t="inlineStr">
+      <c r="B4" s="65" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C4" s="56" t="inlineStr">
+      <c r="C4" s="65" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D4" s="56" t="inlineStr">
+      <c r="D4" s="65" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E4" s="56" t="inlineStr">
+      <c r="E4" s="65" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F4" s="56" t="inlineStr">
+      <c r="F4" s="65" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="57" t="inlineStr">
+      <c r="A5" s="66" t="inlineStr">
         <is>
           <t>Gross payments (GMV)</t>
         </is>
       </c>
-      <c r="B5" s="58" t="n">
+      <c r="B5" s="67" t="n">
         <v>7220000000</v>
       </c>
-      <c r="C5" s="59" t="inlineStr">
+      <c r="C5" s="68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D5" s="59" t="inlineStr">
+      <c r="D5" s="68" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E5" s="59" t="inlineStr">
+      <c r="E5" s="68" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F5" s="59" t="inlineStr">
+      <c r="F5" s="68" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts (Companies House 10354575)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="57" t="inlineStr">
+      <c r="A6" s="66" t="inlineStr">
         <is>
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="B6" s="58" t="n">
+      <c r="B6" s="67" t="n">
         <v>1410000000</v>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="68" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
+      <c r="E6" s="68" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F6" s="59" t="inlineStr">
+      <c r="F6" s="68" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts (Companies House 10354575)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="57" t="inlineStr">
+      <c r="A7" s="66" t="inlineStr">
         <is>
           <t>Paid to creators</t>
         </is>
       </c>
-      <c r="B7" s="58" t="n">
+      <c r="B7" s="67" t="n">
         <v>5800000000</v>
       </c>
-      <c r="C7" s="59" t="inlineStr">
+      <c r="C7" s="68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D7" s="59" t="inlineStr">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E7" s="59" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F7" s="59" t="inlineStr">
+      <c r="F7" s="68" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts — 80.3% of gross</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="57" t="inlineStr">
+      <c r="A8" s="66" t="inlineStr">
         <is>
           <t>Creator accounts</t>
         </is>
       </c>
-      <c r="B8" s="58" t="n">
+      <c r="B8" s="67" t="n">
         <v>4634000</v>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="68" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="68" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr">
+      <c r="E8" s="68" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F8" s="59" t="inlineStr">
+      <c r="F8" s="68" t="inlineStr">
         <is>
           <t>Variety — +13% YoY</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="57" t="inlineStr">
+      <c r="A9" s="66" t="inlineStr">
         <is>
           <t>Fan accounts</t>
         </is>
       </c>
-      <c r="B9" s="58" t="n">
+      <c r="B9" s="67" t="n">
         <v>377500000</v>
       </c>
-      <c r="C9" s="59" t="inlineStr">
+      <c r="C9" s="68" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D9" s="59" t="inlineStr">
+      <c r="D9" s="68" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E9" s="59" t="inlineStr">
+      <c r="E9" s="68" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F9" s="59" t="inlineStr">
+      <c r="F9" s="68" t="inlineStr">
         <is>
           <t>Variety — +24% YoY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="57" t="inlineStr">
+      <c r="A10" s="66" t="inlineStr">
         <is>
           <t>Reported average creator earnings</t>
         </is>
       </c>
-      <c r="B10" s="58" t="n">
+      <c r="B10" s="67" t="n">
         <v>131</v>
       </c>
-      <c r="C10" s="59" t="inlineStr">
+      <c r="C10" s="68" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D10" s="59" t="inlineStr">
+      <c r="D10" s="68" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E10" s="59" t="inlineStr">
+      <c r="E10" s="68" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F10" s="59" t="inlineStr">
+      <c r="F10" s="68" t="inlineStr">
         <is>
           <t>Sci-Tech Today / ElectroIQ — after platform fees</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="57" t="inlineStr">
+      <c r="A11" s="66" t="inlineStr">
         <is>
           <t>Revenue concentration</t>
         </is>
       </c>
-      <c r="B11" s="60" t="n">
+      <c r="B11" s="69" t="n">
         <v>0.76</v>
       </c>
-      <c r="C11" s="59" t="inlineStr">
+      <c r="C11" s="68" t="inlineStr">
         <is>
           <t>share to top 0.1%</t>
         </is>
       </c>
-      <c r="D11" s="59" t="inlineStr">
+      <c r="D11" s="68" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E11" s="59" t="inlineStr">
+      <c r="E11" s="68" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F11" s="59" t="inlineStr">
+      <c r="F11" s="68" t="inlineStr">
         <is>
           <t>ElectroIQ — power-law distribution</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="57" t="inlineStr">
+      <c r="A12" s="66" t="inlineStr">
         <is>
           <t>Creators with &gt;=1 paying member</t>
         </is>
       </c>
-      <c r="B12" s="58" t="n">
+      <c r="B12" s="67" t="n">
         <v>286287</v>
       </c>
-      <c r="C12" s="59" t="inlineStr">
+      <c r="C12" s="68" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D12" s="59" t="inlineStr">
+      <c r="D12" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E12" s="59" t="inlineStr">
+      <c r="E12" s="68" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
       </c>
-      <c r="F12" s="59" t="inlineStr">
+      <c r="F12" s="68" t="inlineStr">
         <is>
           <t>Graphtreon</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="57" t="inlineStr">
+      <c r="A13" s="66" t="inlineStr">
         <is>
           <t>Active creators</t>
         </is>
       </c>
-      <c r="B13" s="58" t="n">
+      <c r="B13" s="67" t="n">
         <v>300000</v>
       </c>
-      <c r="C13" s="59" t="inlineStr">
+      <c r="C13" s="68" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D13" s="59" t="inlineStr">
+      <c r="D13" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E13" s="59" t="inlineStr">
+      <c r="E13" s="68" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F13" s="59" t="inlineStr">
+      <c r="F13" s="68" t="inlineStr">
         <is>
           <t>Jack Conte, Patreon</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="57" t="inlineStr">
+      <c r="A14" s="66" t="inlineStr">
         <is>
           <t>Active paying members</t>
         </is>
       </c>
-      <c r="B14" s="58" t="n">
+      <c r="B14" s="67" t="n">
         <v>10000000</v>
       </c>
-      <c r="C14" s="59" t="inlineStr">
+      <c r="C14" s="68" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D14" s="59" t="inlineStr">
+      <c r="D14" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E14" s="59" t="inlineStr">
+      <c r="E14" s="68" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F14" s="59" t="inlineStr">
+      <c r="F14" s="68" t="inlineStr">
         <is>
           <t>Patreon / Backlinko</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="57" t="inlineStr">
+      <c r="A15" s="66" t="inlineStr">
         <is>
           <t>Paid to creators annually</t>
         </is>
       </c>
-      <c r="B15" s="58" t="n">
+      <c r="B15" s="67" t="n">
         <v>2000000000</v>
       </c>
-      <c r="C15" s="59" t="inlineStr">
+      <c r="C15" s="68" t="inlineStr">
         <is>
           <t>USD/year</t>
         </is>
       </c>
-      <c r="D15" s="59" t="inlineStr">
+      <c r="D15" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E15" s="59" t="inlineStr">
+      <c r="E15" s="68" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F15" s="59" t="inlineStr">
+      <c r="F15" s="68" t="inlineStr">
         <is>
           <t>Patreon / Backlinko</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="57" t="inlineStr">
+      <c r="A16" s="66" t="inlineStr">
         <is>
           <t>Average monthly support per member</t>
         </is>
       </c>
-      <c r="B16" s="60" t="n">
+      <c r="B16" s="69" t="n">
         <v>6.1</v>
       </c>
-      <c r="C16" s="59" t="inlineStr">
+      <c r="C16" s="68" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D16" s="59" t="inlineStr">
+      <c r="D16" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E16" s="59" t="inlineStr">
+      <c r="E16" s="68" t="inlineStr">
         <is>
           <t>Aug 2024</t>
         </is>
       </c>
-      <c r="F16" s="59" t="inlineStr">
+      <c r="F16" s="68" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report; audit of ~1,200 creators</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="57" t="inlineStr">
+      <c r="A17" s="66" t="inlineStr">
         <is>
           <t>Typical patronage band (low)</t>
         </is>
       </c>
-      <c r="B17" s="60" t="n">
+      <c r="B17" s="69" t="n">
         <v>8</v>
       </c>
-      <c r="C17" s="59" t="inlineStr">
+      <c r="C17" s="68" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D17" s="59" t="inlineStr">
+      <c r="D17" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E17" s="59" t="inlineStr">
+      <c r="E17" s="68" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F17" s="59" t="inlineStr">
+      <c r="F17" s="68" t="inlineStr">
         <is>
           <t>Creator-economy benchmarks</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="57" t="inlineStr">
+      <c r="A18" s="66" t="inlineStr">
         <is>
           <t>Typical patronage band (high)</t>
         </is>
       </c>
-      <c r="B18" s="60" t="n">
+      <c r="B18" s="69" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="59" t="inlineStr">
+      <c r="C18" s="68" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D18" s="59" t="inlineStr">
+      <c r="D18" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E18" s="59" t="inlineStr">
+      <c r="E18" s="68" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F18" s="59" t="inlineStr">
+      <c r="F18" s="68" t="inlineStr">
         <is>
           <t>Creator-economy benchmarks</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="57" t="inlineStr">
+      <c r="A19" s="66" t="inlineStr">
         <is>
           <t>Monthly churn (low)</t>
         </is>
       </c>
-      <c r="B19" s="60" t="n">
+      <c r="B19" s="69" t="n">
         <v>0.1</v>
       </c>
-      <c r="C19" s="59" t="inlineStr">
+      <c r="C19" s="68" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D19" s="59" t="inlineStr">
+      <c r="D19" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E19" s="59" t="inlineStr">
+      <c r="E19" s="68" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F19" s="59" t="inlineStr">
+      <c r="F19" s="68" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="57" t="inlineStr">
+      <c r="A20" s="66" t="inlineStr">
         <is>
           <t>Monthly churn (high)</t>
         </is>
       </c>
-      <c r="B20" s="60" t="n">
+      <c r="B20" s="69" t="n">
         <v>0.15</v>
       </c>
-      <c r="C20" s="59" t="inlineStr">
+      <c r="C20" s="68" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D20" s="59" t="inlineStr">
+      <c r="D20" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E20" s="59" t="inlineStr">
+      <c r="E20" s="68" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F20" s="59" t="inlineStr">
+      <c r="F20" s="68" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="57" t="inlineStr">
+      <c r="A21" s="66" t="inlineStr">
         <is>
           <t>Annual-plan churn multiplier</t>
         </is>
       </c>
-      <c r="B21" s="60" t="n">
+      <c r="B21" s="69" t="n">
         <v>0.333</v>
       </c>
-      <c r="C21" s="59" t="inlineStr">
+      <c r="C21" s="68" t="inlineStr">
         <is>
           <t>x monthly churn</t>
         </is>
       </c>
-      <c r="D21" s="59" t="inlineStr">
+      <c r="D21" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E21" s="59" t="inlineStr">
+      <c r="E21" s="68" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F21" s="59" t="inlineStr">
+      <c r="F21" s="68" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report — annual patrons churn at 1/3 the rate</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="57" t="inlineStr">
+      <c r="A22" s="66" t="inlineStr">
         <is>
           <t>Creators with &gt;2,000 patrons</t>
         </is>
       </c>
-      <c r="B22" s="60" t="n">
+      <c r="B22" s="69" t="n">
         <v>0.003</v>
       </c>
-      <c r="C22" s="59" t="inlineStr">
+      <c r="C22" s="68" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D22" s="59" t="inlineStr">
+      <c r="D22" s="68" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E22" s="59" t="inlineStr">
+      <c r="E22" s="68" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F22" s="59" t="inlineStr">
+      <c r="F22" s="68" t="inlineStr">
         <is>
           <t>Graphtreon — power-law distribution</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="57" t="inlineStr">
+      <c r="A23" s="66" t="inlineStr">
         <is>
           <t>Division I athletes in network</t>
         </is>
       </c>
-      <c r="B23" s="58" t="n">
+      <c r="B23" s="67" t="n">
         <v>45000</v>
       </c>
-      <c r="C23" s="59" t="inlineStr">
+      <c r="C23" s="68" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D23" s="59" t="inlineStr">
+      <c r="D23" s="68" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E23" s="59" t="inlineStr">
+      <c r="E23" s="68" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F23" s="59" t="inlineStr">
+      <c r="F23" s="68" t="inlineStr">
         <is>
           <t>Publicis Groupe press release, 19 Aug 2026</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="57" t="inlineStr">
+      <c r="A24" s="66" t="inlineStr">
         <is>
           <t>Power Four universities</t>
         </is>
       </c>
-      <c r="B24" s="58" t="n">
+      <c r="B24" s="67" t="n">
         <v>68</v>
       </c>
-      <c r="C24" s="59" t="inlineStr">
+      <c r="C24" s="68" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D24" s="59" t="inlineStr">
+      <c r="D24" s="68" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E24" s="59" t="inlineStr">
+      <c r="E24" s="68" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F24" s="59" t="inlineStr">
+      <c r="F24" s="68" t="inlineStr">
         <is>
           <t>Publicis Groupe press release</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="57" t="inlineStr">
+      <c r="A25" s="66" t="inlineStr">
         <is>
           <t>Claimed speed-to-market gain</t>
         </is>
       </c>
-      <c r="B25" s="60" t="n">
+      <c r="B25" s="69" t="n">
         <v>0.6</v>
       </c>
-      <c r="C25" s="59" t="inlineStr">
+      <c r="C25" s="68" t="inlineStr">
         <is>
           <t>share faster</t>
         </is>
       </c>
-      <c r="D25" s="59" t="inlineStr">
+      <c r="D25" s="68" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E25" s="59" t="inlineStr">
+      <c r="E25" s="68" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F25" s="59" t="inlineStr">
+      <c r="F25" s="68" t="inlineStr">
         <is>
           <t>Publicis — stated 50-70% vs a traditional agency process</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="61" t="inlineStr">
+      <c r="A27" s="70" t="inlineStr">
         <is>
           <t>TAKE RATES - what each platform costs a creator</t>
         </is>
@@ -3182,16 +6834,16 @@
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="B29" s="62" t="n">
+      <c r="B29" s="71" t="n">
         <v>0.2</v>
       </c>
-      <c r="C29" s="63" t="n">
+      <c r="C29" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="63" t="n">
+      <c r="D29" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="64" t="inlineStr">
+      <c r="F29" s="73" t="inlineStr">
         <is>
           <t>Derived: 1.41bn / 7.22bn = 19.5% (filed accounts)</t>
         </is>
@@ -3203,16 +6855,16 @@
           <t>Fansly</t>
         </is>
       </c>
-      <c r="B30" s="62" t="n">
+      <c r="B30" s="71" t="n">
         <v>0.2</v>
       </c>
-      <c r="C30" s="63" t="n">
+      <c r="C30" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="63" t="n">
+      <c r="D30" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="64" t="inlineStr">
+      <c r="F30" s="73" t="inlineStr">
         <is>
           <t>Not published in terms; widely reported</t>
         </is>
@@ -3224,16 +6876,16 @@
           <t>Fanfix</t>
         </is>
       </c>
-      <c r="B31" s="62" t="n">
+      <c r="B31" s="71" t="n">
         <v>0.2</v>
       </c>
-      <c r="C31" s="63" t="n">
+      <c r="C31" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="63" t="n">
+      <c r="D31" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="64" t="inlineStr">
+      <c r="F31" s="73" t="inlineStr">
         <is>
           <t>Not published in terms; widely reported</t>
         </is>
@@ -3245,16 +6897,16 @@
           <t>Patreon</t>
         </is>
       </c>
-      <c r="B32" s="62" t="n">
+      <c r="B32" s="71" t="n">
         <v>0.1</v>
       </c>
-      <c r="C32" s="63" t="n">
+      <c r="C32" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="63" t="n">
+      <c r="D32" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="64" t="inlineStr">
+      <c r="F32" s="73" t="inlineStr">
         <is>
           <t>Published: 10% all-in, processing included</t>
         </is>
@@ -3266,16 +6918,16 @@
           <t>Passes</t>
         </is>
       </c>
-      <c r="B33" s="62" t="n">
+      <c r="B33" s="71" t="n">
         <v>0.1</v>
       </c>
-      <c r="C33" s="63" t="n">
+      <c r="C33" s="72" t="n">
         <v>0.3</v>
       </c>
-      <c r="D33" s="63" t="n">
+      <c r="D33" s="72" t="n">
         <v>29</v>
       </c>
-      <c r="F33" s="64" t="inlineStr">
+      <c r="F33" s="73" t="inlineStr">
         <is>
           <t>Sacra; Passes rebrand release Apr 2026</t>
         </is>
@@ -3287,23 +6939,23 @@
           <t>Stride (proposed)</t>
         </is>
       </c>
-      <c r="B34" s="62" t="n">
+      <c r="B34" s="71" t="n">
         <v>0.15</v>
       </c>
-      <c r="C34" s="63" t="n">
+      <c r="C34" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="63" t="n">
+      <c r="D34" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="64" t="inlineStr">
+      <c r="F34" s="73" t="inlineStr">
         <is>
           <t>Our decision — see MarketModel</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="61" t="inlineStr">
+      <c r="A36" s="70" t="inlineStr">
         <is>
           <t>INTERMEDIARIES the athlete already pays</t>
         </is>
@@ -3315,13 +6967,13 @@
           <t>Sports agent — endorsement</t>
         </is>
       </c>
-      <c r="B37" s="62" t="n">
+      <c r="B37" s="71" t="n">
         <v>0.1</v>
       </c>
-      <c r="C37" s="62" t="n">
+      <c r="C37" s="71" t="n">
         <v>0.2</v>
       </c>
-      <c r="F37" s="64" t="inlineStr">
+      <c r="F37" s="73" t="inlineStr">
         <is>
           <t>Unregulated; widely reported, no primary source</t>
         </is>
@@ -3333,13 +6985,13 @@
           <t>Sports agent — playing contract</t>
         </is>
       </c>
-      <c r="B38" s="62" t="n">
+      <c r="B38" s="71" t="n">
         <v>0.02</v>
       </c>
-      <c r="C38" s="62" t="n">
+      <c r="C38" s="71" t="n">
         <v>0.05</v>
       </c>
-      <c r="F38" s="64" t="inlineStr">
+      <c r="F38" s="73" t="inlineStr">
         <is>
           <t>NBPA reg. 4.B (Sept 2025); FIFA FFAR art. 15</t>
         </is>
@@ -3351,13 +7003,13 @@
           <t>OnlyFans management agency</t>
         </is>
       </c>
-      <c r="B39" s="62" t="n">
+      <c r="B39" s="71" t="n">
         <v>0.2</v>
       </c>
-      <c r="C39" s="62" t="n">
+      <c r="C39" s="71" t="n">
         <v>0.5</v>
       </c>
-      <c r="F39" s="64" t="inlineStr">
+      <c r="F39" s="73" t="inlineStr">
         <is>
           <t>Aruna Talent rate guide 2026 — on top of the 20%</t>
         </is>
@@ -3371,180 +7023,180 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="65" t="inlineStr">
+      <c r="A43" s="74" t="inlineStr">
         <is>
           <t>OnlyFans FY2024 filed accounts (Fenix International Ltd)</t>
         </is>
       </c>
-      <c r="B43" s="66" t="inlineStr">
+      <c r="B43" s="75" t="inlineStr">
         <is>
           <t>https://find-and-update.company-information.service.gov.uk/company/10354575/filing-history</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="65" t="inlineStr">
+      <c r="A44" s="74" t="inlineStr">
         <is>
           <t>OnlyFans FY2024 as reported</t>
         </is>
       </c>
-      <c r="B44" s="66" t="inlineStr">
+      <c r="B44" s="75" t="inlineStr">
         <is>
           <t>https://variety.com/2025/digital/news/onlyfans-fiscal-2024-revenue-earnings-1236495750/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="65" t="inlineStr">
+      <c r="A45" s="74" t="inlineStr">
         <is>
           <t>Patreon published take rate</t>
         </is>
       </c>
-      <c r="B45" s="66" t="inlineStr">
+      <c r="B45" s="75" t="inlineStr">
         <is>
           <t>https://www.patreon.com/pricing</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="65" t="inlineStr">
+      <c r="A46" s="74" t="inlineStr">
         <is>
           <t>Patreon creators</t>
         </is>
       </c>
-      <c r="B46" s="66" t="inlineStr">
+      <c r="B46" s="75" t="inlineStr">
         <is>
           <t>https://backlinko.com/patreon-users</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="65" t="inlineStr">
+      <c r="A47" s="74" t="inlineStr">
         <is>
           <t>Passes economics</t>
         </is>
       </c>
-      <c r="B47" s="66" t="inlineStr">
+      <c r="B47" s="75" t="inlineStr">
         <is>
           <t>https://sacra.com/c/passes/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="65" t="inlineStr">
+      <c r="A48" s="74" t="inlineStr">
         <is>
           <t>Fanfix creator terms (states no take rate)</t>
         </is>
       </c>
-      <c r="B48" s="66" t="inlineStr">
+      <c r="B48" s="75" t="inlineStr">
         <is>
           <t>https://auth.fanfix.io/creator-terms-of-use</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="65" t="inlineStr">
+      <c r="A49" s="74" t="inlineStr">
         <is>
           <t>Agency commissions</t>
         </is>
       </c>
-      <c r="B49" s="66" t="inlineStr">
+      <c r="B49" s="75" t="inlineStr">
         <is>
           <t>https://arunatalent.com/blog/onlyfans-agency-commission-rates/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="65" t="inlineStr">
+      <c r="A50" s="74" t="inlineStr">
         <is>
           <t>NBPA agent fee cap (amended Sept 2025)</t>
         </is>
       </c>
-      <c r="B50" s="66" t="inlineStr">
+      <c r="B50" s="75" t="inlineStr">
         <is>
           <t>https://imgix.cosmicjs.com/cd844850-97c7-11f0-91fa-d9e1671c2776-NBPA-REGULATIONS-GOVERNING-PLAYER-AGENTS-09-2025.pdf</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="65" t="inlineStr">
+      <c r="A51" s="74" t="inlineStr">
         <is>
           <t>FIFA Football Agent Regulations art. 15</t>
         </is>
       </c>
-      <c r="B51" s="66" t="inlineStr">
+      <c r="B51" s="75" t="inlineStr">
         <is>
           <t>https://digitalhub.fifa.com/m/1e7b741fa0fae779/original/FIFA-Football-Agent-Regulations.pdf</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="65" t="inlineStr">
+      <c r="A52" s="74" t="inlineStr">
         <is>
           <t>CJEU upholds the FIFA fee cap (16 Jul 2026)</t>
         </is>
       </c>
-      <c r="B52" s="66" t="inlineStr">
+      <c r="B52" s="75" t="inlineStr">
         <is>
           <t>https://inside.fifa.com/news/welcomes-court-of-justice-european-union-decision-football-agent-regulations</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="65" t="inlineStr">
+      <c r="A53" s="74" t="inlineStr">
         <is>
           <t>Eurobarometer 525</t>
         </is>
       </c>
-      <c r="B53" s="66" t="inlineStr">
+      <c r="B53" s="75" t="inlineStr">
         <is>
           <t>https://europa.eu/eurobarometer/surveys/detail/2668</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="65" t="inlineStr">
+      <c r="A54" s="74" t="inlineStr">
         <is>
           <t>FIP World Padel Report 2025</t>
         </is>
       </c>
-      <c r="B54" s="66" t="inlineStr">
+      <c r="B54" s="75" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/2025/12/online-the-fip-world-padel-report-2025-a-comprehensive-analysis-of-a-sport-in-constant-growth/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="65" t="inlineStr">
+      <c r="A55" s="74" t="inlineStr">
         <is>
           <t>Stripe EU pricing</t>
         </is>
       </c>
-      <c r="B55" s="66" t="inlineStr">
+      <c r="B55" s="75" t="inlineStr">
         <is>
           <t>https://stripe.com/es/pricing</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="65" t="inlineStr">
+      <c r="A56" s="74" t="inlineStr">
         <is>
           <t>TEKTA launch</t>
         </is>
       </c>
-      <c r="B56" s="66" t="inlineStr">
+      <c r="B56" s="75" t="inlineStr">
         <is>
           <t>https://www.publicisgroupe.com/en/news/press-releases/publicis-sports-and-travis-kelce-s-tekta-join-forces-to-reimagine-the-future-of-nil-marketing</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="65" t="inlineStr">
+      <c r="A57" s="74" t="inlineStr">
         <is>
           <t>Stripe Connect age</t>
         </is>
       </c>
-      <c r="B57" s="66" t="inlineStr">
+      <c r="B57" s="75" t="inlineStr">
         <is>
           <t>https://support.stripe.com/questions/age-requirement-to-create-a-stripe-account</t>
         </is>
@@ -3589,7 +7241,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3612,7 +7264,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="55" t="inlineStr">
+      <c r="A2" s="64" t="inlineStr">
         <is>
           <t>Each block starts from a published figure on Comparables and ends in a number the Assumptions sheet uses. Adjustment factors are blue because they are our judgement; everything else is a formula you can trace.</t>
         </is>
@@ -3670,7 +7322,7 @@
         <f>Comparables!B14</f>
         <v/>
       </c>
-      <c r="D6" s="67" t="inlineStr">
+      <c r="D6" s="76" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -3686,7 +7338,7 @@
         <f>Comparables!B12</f>
         <v/>
       </c>
-      <c r="D7" s="67" t="inlineStr">
+      <c r="D7" s="76" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -3698,11 +7350,11 @@
           <t>Members per paying creator</t>
         </is>
       </c>
-      <c r="B8" s="68">
+      <c r="B8" s="56">
         <f>B6/B7</f>
         <v/>
       </c>
-      <c r="D8" s="67" t="inlineStr">
+      <c r="D8" s="76" t="inlineStr">
         <is>
           <t>The single most useful benchmark we found: it is measured, not modelled.</t>
         </is>
@@ -3718,7 +7370,7 @@
         <f>Comparables!B9/Comparables!B8</f>
         <v/>
       </c>
-      <c r="D9" s="67" t="inlineStr">
+      <c r="D9" s="76" t="inlineStr">
         <is>
           <t>Fan ACCOUNTS, not paying fans - most follow free. Shown as an upper bound only.</t>
         </is>
@@ -3733,7 +7385,7 @@
       <c r="B10" s="24" t="n">
         <v>1.06</v>
       </c>
-      <c r="D10" s="67" t="inlineStr">
+      <c r="D10" s="76" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: +6% on the Patreon benchmark. Sport audiences are smaller but convert better, because the fan usually does the sport themselves.</t>
         </is>
@@ -3748,7 +7400,7 @@
       <c r="B11" s="24" t="n">
         <v>1.37</v>
       </c>
-      <c r="D11" s="67" t="inlineStr">
+      <c r="D11" s="76" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: +37%. Much larger followings, much weaker conversion - more paying fans in absolute terms even though a smaller share converts.</t>
         </is>
@@ -3760,11 +7412,11 @@
           <t>→ Niche fans per athlete, mature</t>
         </is>
       </c>
-      <c r="B12" s="69">
+      <c r="B12" s="77">
         <f>B8*B10</f>
         <v/>
       </c>
-      <c r="D12" s="67" t="inlineStr"/>
+      <c r="D12" s="76" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -3772,11 +7424,11 @@
           <t>→ Popular fans per athlete, mature</t>
         </is>
       </c>
-      <c r="B13" s="69">
+      <c r="B13" s="77">
         <f>B8*B11</f>
         <v/>
       </c>
-      <c r="D13" s="67" t="inlineStr"/>
+      <c r="D13" s="76" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -3797,7 +7449,7 @@
       <c r="B15" s="20" t="n">
         <v>4.99</v>
       </c>
-      <c r="D15" s="67" t="inlineStr"/>
+      <c r="D15" s="76" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
@@ -3808,7 +7460,7 @@
       <c r="B16" s="20" t="n">
         <v>9.99</v>
       </c>
-      <c r="D16" s="67" t="inlineStr"/>
+      <c r="D16" s="76" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
@@ -3819,7 +7471,7 @@
       <c r="B17" s="20" t="n">
         <v>24.99</v>
       </c>
-      <c r="D17" s="67" t="inlineStr"/>
+      <c r="D17" s="76" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
@@ -3830,7 +7482,7 @@
       <c r="B18" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="D18" s="67" t="inlineStr">
+      <c r="D18" s="76" t="inlineStr">
         <is>
           <t>Assumed distribution; replace with the real tier mix after P1.</t>
         </is>
@@ -3845,7 +7497,7 @@
       <c r="B19" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="D19" s="67" t="inlineStr"/>
+      <c r="D19" s="76" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="13" t="inlineStr">
@@ -3856,7 +7508,7 @@
       <c r="B20" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="D20" s="67" t="inlineStr"/>
+      <c r="D20" s="76" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
@@ -3868,7 +7520,7 @@
         <f>B18+B19+B20</f>
         <v/>
       </c>
-      <c r="D21" s="67" t="inlineStr"/>
+      <c r="D21" s="76" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -3876,11 +7528,11 @@
           <t>→ Weighted ARPU per month</t>
         </is>
       </c>
-      <c r="B22" s="70">
+      <c r="B22" s="78">
         <f>B15*B18+B16*B19+B17*B20</f>
         <v/>
       </c>
-      <c r="D22" s="67" t="inlineStr">
+      <c r="D22" s="76" t="inlineStr">
         <is>
           <t>Cross-check: Patreon reports $6.10 average support and a $8-12 typical band. Landing inside that band from an independent tier build is a good sign.</t>
         </is>
@@ -3896,7 +7548,7 @@
         <f>Comparables!B16</f>
         <v/>
       </c>
-      <c r="D23" s="67" t="inlineStr">
+      <c r="D23" s="76" t="inlineStr">
         <is>
           <t>Published average - below our figure because Patreon's long tail includes many $1-3 tiers. Our EUR 9.49 sits inside their $8-12 typical band.</t>
         </is>
@@ -3911,7 +7563,7 @@
       <c r="B24" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="67" t="inlineStr">
+      <c r="D24" s="76" t="inlineStr">
         <is>
           <t>Niche fans buy knowledge and sit at the tier mix above.</t>
         </is>
@@ -3926,7 +7578,7 @@
       <c r="B25" s="24" t="n">
         <v>0.87</v>
       </c>
-      <c r="D25" s="67" t="inlineStr">
+      <c r="D25" s="76" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: -13%. Popular-sport fans skew to the cheapest tier.</t>
         </is>
@@ -3938,11 +7590,11 @@
           <t>→ Niche ARPU, mature</t>
         </is>
       </c>
-      <c r="B26" s="70">
+      <c r="B26" s="78">
         <f>B22*B24</f>
         <v/>
       </c>
-      <c r="D26" s="67" t="inlineStr"/>
+      <c r="D26" s="76" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -3950,11 +7602,11 @@
           <t>→ Popular ARPU, mature</t>
         </is>
       </c>
-      <c r="B27" s="70">
+      <c r="B27" s="78">
         <f>B22*B25</f>
         <v/>
       </c>
-      <c r="D27" s="67" t="inlineStr"/>
+      <c r="D27" s="76" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -3976,7 +7628,7 @@
         <f>Comparables!B19</f>
         <v/>
       </c>
-      <c r="D29" s="67" t="inlineStr"/>
+      <c r="D29" s="76" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="13" t="inlineStr">
@@ -3988,7 +7640,7 @@
         <f>Comparables!B20</f>
         <v/>
       </c>
-      <c r="D30" s="67" t="inlineStr"/>
+      <c r="D30" s="76" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="13" t="inlineStr">
@@ -4000,7 +7652,7 @@
         <f>(B29+B30)/2</f>
         <v/>
       </c>
-      <c r="D31" s="67" t="inlineStr"/>
+      <c r="D31" s="76" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="13" t="inlineStr">
@@ -4012,7 +7664,7 @@
         <f>Comparables!B21</f>
         <v/>
       </c>
-      <c r="D32" s="67" t="inlineStr">
+      <c r="D32" s="76" t="inlineStr">
         <is>
           <t>Patreon: annual patrons churn at one third the monthly rate.</t>
         </is>
@@ -4027,7 +7679,7 @@
       <c r="B33" s="16" t="n">
         <v>0.3</v>
       </c>
-      <c r="D33" s="67" t="inlineStr">
+      <c r="D33" s="76" t="inlineStr">
         <is>
           <t>Our target for the season pass. This is the one lever that improves churn without changing the product.</t>
         </is>
@@ -4043,7 +7695,7 @@
         <f>B31*(1-B33)+B31*B32*B33</f>
         <v/>
       </c>
-      <c r="D34" s="67" t="inlineStr">
+      <c r="D34" s="76" t="inlineStr">
         <is>
           <t>What a Patreon-like platform would see with our annual mix.</t>
         </is>
@@ -4058,7 +7710,7 @@
       <c r="B35" s="24" t="n">
         <v>0.55</v>
       </c>
-      <c r="D35" s="67" t="inlineStr">
+      <c r="D35" s="76" t="inlineStr">
         <is>
           <t>OUR CLAIM, UNTESTED, AND THE MOST OPTIMISTIC JUDGEMENT IN THE MODEL: this says niche fans churn 45% SLOWER than the Patreon benchmark, because training content is habitual and competitive seasons create renewal moments. Nothing yet proves it. If it is wrong and we are merely at benchmark, Y10 revenue falls by roughly EUR 7M.</t>
         </is>
@@ -4073,7 +7725,7 @@
       <c r="B36" s="24" t="n">
         <v>0.85</v>
       </c>
-      <c r="D36" s="67" t="inlineStr">
+      <c r="D36" s="76" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: 15% better than benchmark. Impulse follows after a result, with many free substitutes - but still a sport fan rather than a general creator audience.</t>
         </is>
@@ -4085,11 +7737,11 @@
           <t>→ Niche churn, mature</t>
         </is>
       </c>
-      <c r="B37" s="71">
+      <c r="B37" s="79">
         <f>B34*B35</f>
         <v/>
       </c>
-      <c r="D37" s="67" t="inlineStr"/>
+      <c r="D37" s="76" t="inlineStr"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -4097,11 +7749,11 @@
           <t>→ Popular churn, mature</t>
         </is>
       </c>
-      <c r="B38" s="71">
+      <c r="B38" s="79">
         <f>B34*B36</f>
         <v/>
       </c>
-      <c r="D38" s="67" t="inlineStr"/>
+      <c r="D38" s="76" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -4123,7 +7775,7 @@
         <f>Comparables!B7/Comparables!B8/12</f>
         <v/>
       </c>
-      <c r="D40" s="67" t="inlineStr">
+      <c r="D40" s="76" t="inlineStr">
         <is>
           <t>Includes dormant accounts, so this is a floor.</t>
         </is>
@@ -4139,7 +7791,7 @@
         <f>Comparables!B15/Comparables!B12/12</f>
         <v/>
       </c>
-      <c r="D41" s="67" t="inlineStr">
+      <c r="D41" s="76" t="inlineStr">
         <is>
           <t>Denominator is creators WITH members, so this is a ceiling.</t>
         </is>
@@ -4151,11 +7803,11 @@
           <t>Stride: modelled niche athlete, mature</t>
         </is>
       </c>
-      <c r="B42" s="70">
+      <c r="B42" s="78">
         <f>B12*B22*(1-Assumptions!$C$40)</f>
         <v/>
       </c>
-      <c r="D42" s="67" t="inlineStr">
+      <c r="D42" s="76" t="inlineStr">
         <is>
           <t>Ours sits between the two, which is where a plausible figure should sit.</t>
         </is>
@@ -4171,7 +7823,7 @@
         <f>Comparables!B11</f>
         <v/>
       </c>
-      <c r="D43" s="67" t="inlineStr">
+      <c r="D43" s="76" t="inlineStr">
         <is>
           <t>THE CAVEAT ON EVERY AVERAGE ABOVE: earnings follow a power law. Totals are unaffected, but the median athlete earns far less than the mean. Do not pitch the mean to an athlete.</t>
         </is>
@@ -4196,7 +7848,7 @@
       <c r="B45" s="24" t="n">
         <v>0.92</v>
       </c>
-      <c r="D45" s="67" t="inlineStr">
+      <c r="D45" s="76" t="inlineStr">
         <is>
           <t>Comparables are published in USD; this model is in EUR. Applied to the per-transaction and monthly creator fees below.</t>
         </is>
@@ -4211,7 +7863,7 @@
       <c r="B46" s="20" t="n">
         <v>300</v>
       </c>
-      <c r="D46" s="67" t="inlineStr">
+      <c r="D46" s="76" t="inlineStr">
         <is>
           <t>Change this to see who is cheapest at any revenue level.</t>
         </is>
@@ -4227,7 +7879,7 @@
         <f>B46*(1-Comparables!B29)-B46/Assumptions!$C$48*Comparables!C29*B45-Comparables!D29*B45</f>
         <v/>
       </c>
-      <c r="D47" s="67" t="inlineStr">
+      <c r="D47" s="76" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -4243,7 +7895,7 @@
         <f>B46*(1-Comparables!B32)-B46/Assumptions!$C$48*Comparables!C32*B45-Comparables!D32*B45</f>
         <v/>
       </c>
-      <c r="D48" s="67" t="inlineStr">
+      <c r="D48" s="76" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -4259,7 +7911,7 @@
         <f>B46*(1-Comparables!B33)-B46/Assumptions!$C$48*Comparables!C33*B45-Comparables!D33*B45</f>
         <v/>
       </c>
-      <c r="D49" s="67" t="inlineStr">
+      <c r="D49" s="76" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -4275,7 +7927,7 @@
         <f>B46*(1-Comparables!B34)-B46/Assumptions!$C$48*Comparables!C34*B45-Comparables!D34*B45</f>
         <v/>
       </c>
-      <c r="D50" s="67" t="inlineStr">
+      <c r="D50" s="76" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -4291,7 +7943,7 @@
         <f>Comparables!D33*B45/((Comparables!B34-Comparables!B33)-Comparables!C33*B45/Assumptions!$C$48)</f>
         <v/>
       </c>
-      <c r="D51" s="67" t="inlineStr">
+      <c r="D51" s="76" t="inlineStr">
         <is>
           <t>Below this, our flat 15% pays the athlete more than Passes' 10% plus fees. Our modelled athlete earns far less than this, so the long tail is on our side of the line.</t>
         </is>
@@ -4313,10 +7965,10 @@
           <t>Population, 34 countries in scope</t>
         </is>
       </c>
-      <c r="B53" s="72" t="n">
+      <c r="B53" s="80" t="n">
         <v>2726.2</v>
       </c>
-      <c r="D53" s="67" t="inlineStr">
+      <c r="D53" s="76" t="inlineStr">
         <is>
           <t>Millions. Eurostat / national statistics offices.</t>
         </is>
@@ -4328,10 +7980,10 @@
           <t>Population, Spain</t>
         </is>
       </c>
-      <c r="B54" s="72" t="n">
+      <c r="B54" s="80" t="n">
         <v>48.6</v>
       </c>
-      <c r="D54" s="67" t="inlineStr">
+      <c r="D54" s="76" t="inlineStr">
         <is>
           <t>Millions.</t>
         </is>
@@ -4346,7 +7998,7 @@
       <c r="B55" s="16" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D55" s="67" t="inlineStr">
+      <c r="D55" s="76" t="inlineStr">
         <is>
           <t>Eurobarometer 525 - Spain sits near the EU average of 55% who exercise at all.</t>
         </is>
@@ -4361,7 +8013,7 @@
       <c r="B56" s="16" t="n">
         <v>0.02</v>
       </c>
-      <c r="D56" s="67" t="inlineStr">
+      <c r="D56" s="76" t="inlineStr">
         <is>
           <t>OUR ESTIMATE: competes, posts publicly, has a following worth sponsoring.</t>
         </is>
@@ -4376,7 +8028,7 @@
       <c r="B57" s="16" t="n">
         <v>0.25</v>
       </c>
-      <c r="D57" s="67" t="inlineStr">
+      <c r="D57" s="76" t="inlineStr">
         <is>
           <t>OUR ESTIMATE: would monetise if the tooling existed.</t>
         </is>
@@ -4388,11 +8040,11 @@
           <t>→ Addressable athletes, Spain</t>
         </is>
       </c>
-      <c r="B58" s="73">
+      <c r="B58" s="81">
         <f>B54*1000000*B55*B56*B57</f>
         <v/>
       </c>
-      <c r="D58" s="67" t="inlineStr"/>
+      <c r="D58" s="76" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -4400,11 +8052,11 @@
           <t>→ Addressable athletes, all 34 countries</t>
         </is>
       </c>
-      <c r="B59" s="73">
+      <c r="B59" s="81">
         <f>B53*1000000*0.5*B56*B57</f>
         <v/>
       </c>
-      <c r="D59" s="67" t="inlineStr">
+      <c r="D59" s="76" t="inlineStr">
         <is>
           <t>Using a 50% blended participation rate across the 34 countries.</t>
         </is>
@@ -4420,7 +8072,7 @@
         <f>Assumptions!$L$5</f>
         <v/>
       </c>
-      <c r="D60" s="67" t="inlineStr"/>
+      <c r="D60" s="76" t="inlineStr"/>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -4428,11 +8080,11 @@
           <t>→ Y10 penetration of Spain SAM</t>
         </is>
       </c>
-      <c r="B61" s="71">
+      <c r="B61" s="79">
         <f>Assumptions!$L$5/B58</f>
         <v/>
       </c>
-      <c r="D61" s="67" t="inlineStr"/>
+      <c r="D61" s="76" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -4440,11 +8092,11 @@
           <t>→ Y10 penetration of full TAM</t>
         </is>
       </c>
-      <c r="B62" s="71">
+      <c r="B62" s="79">
         <f>Assumptions!$L$5/B59</f>
         <v/>
       </c>
-      <c r="D62" s="67" t="inlineStr">
+      <c r="D62" s="76" t="inlineStr">
         <is>
           <t>If this reads as implausibly high, the athlete trajectory is too aggressive - that is exactly what this block exists to reveal.</t>
         </is>
@@ -4462,7 +8114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4488,44 +8140,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="55" t="inlineStr">
+      <c r="A2" s="64" t="inlineStr">
         <is>
           <t>SOURCED = published figure | BENCHMARKED = set against named comparables | DERIVED = computed from other assumptions | ESTIMATE = judgement, no benchmark yet</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="74" t="inlineStr">
+      <c r="A4" s="82" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B4" s="74" t="inlineStr">
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>Model value</t>
         </is>
       </c>
-      <c r="C4" s="74" t="inlineStr">
+      <c r="C4" s="82" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="D4" s="74" t="inlineStr">
+      <c r="D4" s="82" t="inlineStr">
         <is>
           <t>Benchmark / comparable</t>
         </is>
       </c>
-      <c r="E4" s="74" t="inlineStr">
+      <c r="E4" s="82" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F4" s="74" t="inlineStr">
+      <c r="F4" s="82" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="G4" s="74" t="inlineStr">
+      <c r="G4" s="82" t="inlineStr">
         <is>
           <t>What would replace the estimate</t>
         </is>
@@ -4545,7 +8197,7 @@
       <c r="G5" s="12" t="n"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="75" t="inlineStr">
+      <c r="A6" s="83" t="inlineStr">
         <is>
           <t>Take rate on fan revenue</t>
         </is>
@@ -4554,34 +8206,34 @@
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
-      <c r="C6" s="76" t="inlineStr">
+      <c r="C6" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D6" s="77" t="inlineStr">
+      <c r="D6" s="85" t="inlineStr">
         <is>
           <t>Passes charges 10% but adds $0.30/txn and a $29/month creator fee; OnlyFans, Fansly and Fanfix are all 20%; Patreon 8-12%. A flat 15% with no monthly fee pays an athlete more than Passes for anyone under EUR 1,380/month of fan revenue.</t>
         </is>
       </c>
-      <c r="E6" s="77" t="inlineStr">
+      <c r="E6" s="85" t="inlineStr">
         <is>
           <t>Sacra company profile (Passes); Passes rebrand release, Apr 2026; MEXC platform comparison 2026</t>
         </is>
       </c>
-      <c r="F6" s="78" t="inlineStr">
+      <c r="F6" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G6" s="77" t="inlineStr">
+      <c r="G6" s="85" t="inlineStr">
         <is>
           <t>Nothing. This is a pricing decision and the comparables are public.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="75" t="inlineStr">
+      <c r="A7" s="83" t="inlineStr">
         <is>
           <t>Take rate on sponsorship</t>
         </is>
@@ -4590,101 +8242,101 @@
         <f>Assumptions!$C$41</f>
         <v/>
       </c>
-      <c r="C7" s="76" t="inlineStr">
+      <c r="C7" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D7" s="77" t="inlineStr">
+      <c r="D7" s="85" t="inlineStr">
         <is>
           <t>Sports agents take 10-20% of an endorsement and 4-10% of a playing contract. On OnlyFans, management agencies take a further 20-50% on top of the platform's 20%.</t>
         </is>
       </c>
-      <c r="E7" s="77" t="inlineStr">
+      <c r="E7" s="85" t="inlineStr">
         <is>
           <t>Oreate and Sapling agent-commission surveys; Aruna Talent agency rate guide 2026</t>
         </is>
       </c>
-      <c r="F7" s="78" t="inlineStr">
+      <c r="F7" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G7" s="77" t="inlineStr">
+      <c r="G7" s="85" t="inlineStr">
         <is>
           <t>Observed deal data once the marketplace is running.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="75" t="inlineStr">
+      <c r="A8" s="83" t="inlineStr">
         <is>
           <t>Suggested tiers 4.99 / 9.99 / 24.99</t>
         </is>
       </c>
-      <c r="B8" s="79" t="inlineStr">
+      <c r="B8" s="87" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C8" s="76" t="inlineStr">
+      <c r="C8" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D8" s="77" t="inlineStr">
+      <c r="D8" s="85" t="inlineStr">
         <is>
           <t>Patreon's typical patronage is quoted at $8-12/month, so the EUR 9.99 anchor sits inside the observed band. EUR 4.99 retains only 54% of our take after payment fees, against 71% at EUR 9.99 — which is why the floor matters more than the take rate.</t>
         </is>
       </c>
-      <c r="E8" s="77" t="inlineStr">
+      <c r="E8" s="85" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report; independent audits of ~1,200 creators</t>
         </is>
       </c>
-      <c r="F8" s="80" t="inlineStr">
+      <c r="F8" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G8" s="77" t="inlineStr">
+      <c r="G8" s="85" t="inlineStr">
         <is>
           <t>Our own tier mix after P1.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="75" t="inlineStr">
+      <c r="A9" s="83" t="inlineStr">
         <is>
           <t>Season pass / annual billing</t>
         </is>
       </c>
-      <c r="B9" s="79" t="inlineStr">
+      <c r="B9" s="87" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C9" s="81" t="inlineStr">
+      <c r="C9" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D9" s="77" t="inlineStr">
+      <c r="D9" s="85" t="inlineStr">
         <is>
           <t>Patreon reports that annual patrons churn at ONE THIRD the rate of monthly patrons. This is the single strongest piece of evidence in the plan for pushing annual billing.</t>
         </is>
       </c>
-      <c r="E9" s="77" t="inlineStr">
+      <c r="E9" s="85" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
-      <c r="F9" s="78" t="inlineStr">
+      <c r="F9" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G9" s="77" t="inlineStr">
+      <c r="G9" s="85" t="inlineStr">
         <is>
           <t>Already strong. Confirm on our own cohorts.</t>
         </is>
@@ -4704,7 +8356,7 @@
       <c r="G10" s="12" t="n"/>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="75" t="inlineStr">
+      <c r="A11" s="83" t="inlineStr">
         <is>
           <t>Fan ARPU per month</t>
         </is>
@@ -4713,34 +8365,34 @@
         <f>Assumptions!$C$12</f>
         <v/>
       </c>
-      <c r="C11" s="76" t="inlineStr">
+      <c r="C11" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D11" s="77" t="inlineStr">
+      <c r="D11" s="85" t="inlineStr">
         <is>
           <t>Patreon's average monthly support rose from $5.40 to $6.10 during 2024, with typical patronage quoted at $8-12. Our EUR 8.00-9.50 sits in the upper-middle of that range.</t>
         </is>
       </c>
-      <c r="E11" s="77" t="inlineStr">
+      <c r="E11" s="85" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
-      <c r="F11" s="80" t="inlineStr">
+      <c r="F11" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G11" s="77" t="inlineStr">
+      <c r="G11" s="85" t="inlineStr">
         <is>
           <t>Actual ARPU by tier and sport after P1.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="75" t="inlineStr">
+      <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Fan churn per month</t>
         </is>
@@ -4749,34 +8401,34 @@
         <f>Assumptions!$C$13</f>
         <v/>
       </c>
-      <c r="C12" s="82" t="inlineStr">
+      <c r="C12" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D12" s="77" t="inlineStr">
+      <c r="D12" s="85" t="inlineStr">
         <is>
           <t>OPTIMISTIC AGAINST BENCHMARK. Patreon runs 10-15% monthly. We assume 6-9% (niche) and 9-13% (popular), arguing that training content is habitual and that competitive seasons create natural renewal moments. That argument is currently untested.</t>
         </is>
       </c>
-      <c r="E12" s="77" t="inlineStr">
+      <c r="E12" s="85" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report (10-15%/month)</t>
         </is>
       </c>
-      <c r="F12" s="83" t="inlineStr">
+      <c r="F12" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G12" s="77" t="inlineStr">
+      <c r="G12" s="85" t="inlineStr">
         <is>
           <t>THE most important number to measure in P1. Three months of real cohorts settles it. Until then the conservative case should be treated as the plan.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="75" t="inlineStr">
+      <c r="A13" s="83" t="inlineStr">
         <is>
           <t>Paying fans per monetising athlete</t>
         </is>
@@ -4785,34 +8437,34 @@
         <f>Assumptions!$C$11</f>
         <v/>
       </c>
-      <c r="C13" s="84" t="inlineStr">
+      <c r="C13" s="92" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D13" s="77" t="inlineStr">
+      <c r="D13" s="85" t="inlineStr">
         <is>
           <t>20 rising to 48 over ten years. Cross-check: Patreon creators average $350/month and our modelled niche athlete at maturity earns about EUR 313/month — closely aligned, which is reassuring for an assumption built bottom-up rather than from a comparable.</t>
         </is>
       </c>
-      <c r="E13" s="77" t="inlineStr">
+      <c r="E13" s="85" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report (creator average $350/month)</t>
         </is>
       </c>
-      <c r="F13" s="80" t="inlineStr">
+      <c r="F13" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G13" s="77" t="inlineStr">
+      <c r="G13" s="85" t="inlineStr">
         <is>
           <t>Observed fans per athlete, banded by follower count.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="75" t="inlineStr">
+      <c r="A14" s="83" t="inlineStr">
         <is>
           <t>Share of athletes who monetise</t>
         </is>
@@ -4821,64 +8473,64 @@
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="C14" s="82" t="inlineStr">
+      <c r="C14" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D14" s="77" t="inlineStr">
+      <c r="D14" s="85" t="inlineStr">
         <is>
           <t>28% rising to 50% for niche sports. No direct comparable exists — neither Patreon nor OnlyFans publishes activation rates for creators who sign up but never charge.</t>
         </is>
       </c>
-      <c r="E14" s="77" t="inlineStr">
+      <c r="E14" s="85" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="F14" s="83" t="inlineStr">
+      <c r="F14" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G14" s="77" t="inlineStr">
+      <c r="G14" s="85" t="inlineStr">
         <is>
           <t>Our own activation funnel, available from P1 onward.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="75" t="inlineStr">
+      <c r="A15" s="83" t="inlineStr">
         <is>
           <t>Fan acquisition capacity</t>
         </is>
       </c>
-      <c r="B15" s="79" t="inlineStr">
+      <c r="B15" s="87" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C15" s="82" t="inlineStr">
+      <c r="C15" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D15" s="77" t="inlineStr">
+      <c r="D15" s="85" t="inlineStr">
         <is>
           <t>An athlete can recruit 30-69 new paying fans a year depending on segment. This ceiling is what makes churn bite in the model: without it, higher churn perversely RAISED revenue, because the year-end target was reachable at any churn rate.</t>
         </is>
       </c>
-      <c r="E15" s="77" t="inlineStr">
+      <c r="E15" s="85" t="inlineStr">
         <is>
           <t>None — introduced to fix a modelling flaw found by stress testing</t>
         </is>
       </c>
-      <c r="F15" s="83" t="inlineStr">
+      <c r="F15" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G15" s="77" t="inlineStr">
+      <c r="G15" s="85" t="inlineStr">
         <is>
           <t>Observed gross adds per athlete per year.</t>
         </is>
@@ -4898,7 +8550,7 @@
       <c r="G16" s="12" t="n"/>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="75" t="inlineStr">
+      <c r="A17" s="83" t="inlineStr">
         <is>
           <t>PSP percentage fee</t>
         </is>
@@ -4907,34 +8559,34 @@
         <f>Assumptions!$C$44</f>
         <v/>
       </c>
-      <c r="C17" s="81" t="inlineStr">
+      <c r="C17" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D17" s="77" t="inlineStr">
+      <c r="D17" s="85" t="inlineStr">
         <is>
           <t>Stripe for a Spanish entity: 1.5% + EUR 0.25 on EEA domestic cards, 2.5% on UK cards, 3.25% on non-EEA. 1.9% is the blend for a mostly-European fan base. CORRECTION: an earlier version of this model used the US headline of 2.9% and overstated the largest cost line in the business by about a third.</t>
         </is>
       </c>
-      <c r="E17" s="77" t="inlineStr">
+      <c r="E17" s="85" t="inlineStr">
         <is>
           <t>Stripe published EU/EEA pricing, 2026</t>
         </is>
       </c>
-      <c r="F17" s="78" t="inlineStr">
+      <c r="F17" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G17" s="77" t="inlineStr">
+      <c r="G17" s="85" t="inlineStr">
         <is>
           <t>Interchange-plus terms become negotiable above roughly EUR 5M processed.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="75" t="inlineStr">
+      <c r="A18" s="83" t="inlineStr">
         <is>
           <t>PSP fixed fee per transaction</t>
         </is>
@@ -4943,34 +8595,34 @@
         <f>Assumptions!$C$45</f>
         <v/>
       </c>
-      <c r="C18" s="81" t="inlineStr">
+      <c r="C18" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D18" s="77" t="inlineStr">
+      <c r="D18" s="85" t="inlineStr">
         <is>
           <t>EUR 0.25 per transaction. On a EUR 4.99 tier that single fee is a third of our take, which is why the tier floor and annual billing move more margin than the take rate does.</t>
         </is>
       </c>
-      <c r="E18" s="77" t="inlineStr">
+      <c r="E18" s="85" t="inlineStr">
         <is>
           <t>Stripe published pricing, 2026</t>
         </is>
       </c>
-      <c r="F18" s="78" t="inlineStr">
+      <c r="F18" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G18" s="77" t="inlineStr">
+      <c r="G18" s="85" t="inlineStr">
         <is>
           <t>Volume renegotiation; annual billing turns twelve fees into one.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="75" t="inlineStr">
+      <c r="A19" s="83" t="inlineStr">
         <is>
           <t>Payout fees</t>
         </is>
@@ -4979,27 +8631,27 @@
         <f>Assumptions!$C$46</f>
         <v/>
       </c>
-      <c r="C19" s="81" t="inlineStr">
+      <c r="C19" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D19" s="77" t="inlineStr">
+      <c r="D19" s="85" t="inlineStr">
         <is>
           <t>Stripe Connect Express: roughly 0.25% + EUR 0.25 per payout, plus a monthly active-account fee that is not modelled as a separate line.</t>
         </is>
       </c>
-      <c r="E19" s="77" t="inlineStr">
+      <c r="E19" s="85" t="inlineStr">
         <is>
           <t>Stripe Connect pricing, 2026</t>
         </is>
       </c>
-      <c r="F19" s="80" t="inlineStr">
+      <c r="F19" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G19" s="77" t="inlineStr">
+      <c r="G19" s="85" t="inlineStr">
         <is>
           <t>Actual payout frequency once athletes are onboarded.</t>
         </is>
@@ -5019,118 +8671,118 @@
       <c r="G20" s="12" t="n"/>
     </row>
     <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="75" t="inlineStr">
+      <c r="A21" s="83" t="inlineStr">
         <is>
           <t>Sport participation by country</t>
         </is>
       </c>
-      <c r="B21" s="79" t="inlineStr">
+      <c r="B21" s="87" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C21" s="81" t="inlineStr">
+      <c r="C21" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D21" s="77" t="inlineStr">
+      <c r="D21" s="85" t="inlineStr">
         <is>
           <t>Eurobarometer 525, share who NEVER exercise: Finland 8%, Sweden 12%, Denmark 20%, Poland 65%, Greece 68%, Portugal 73%, EU-27 average 45%. Six of the 34 countries in the index are measured; the other 28 are estimates placed inside that distribution.</t>
         </is>
       </c>
-      <c r="E21" s="77" t="inlineStr">
+      <c r="E21" s="85" t="inlineStr">
         <is>
           <t>Special Eurobarometer 525, Sport and Physical Activity, September 2022</t>
         </is>
       </c>
-      <c r="F21" s="78" t="inlineStr">
+      <c r="F21" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G21" s="77" t="inlineStr">
+      <c r="G21" s="85" t="inlineStr">
         <is>
           <t>Federation licence counts — published annually and free (CSD in Spain).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="75" t="inlineStr">
+      <c r="A22" s="83" t="inlineStr">
         <is>
           <t>Padel market size</t>
         </is>
       </c>
-      <c r="B22" s="79" t="inlineStr">
+      <c r="B22" s="87" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C22" s="81" t="inlineStr">
+      <c r="C22" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D22" s="77" t="inlineStr">
+      <c r="D22" s="85" t="inlineStr">
         <is>
           <t>Spain has ~6.0M active players (12.7% of the population), 109,040 federation licences and 17,300+ courts; globally 35M+ players and 77,000+ courts. This is the clearest case for weighting a sport regionally rather than globally — padel scores 77.7 in Spain and 45.1 worldwide.</t>
         </is>
       </c>
-      <c r="E22" s="77" t="inlineStr">
+      <c r="E22" s="85" t="inlineStr">
         <is>
           <t>FIP World Padel Report 2025</t>
         </is>
       </c>
-      <c r="F22" s="78" t="inlineStr">
+      <c r="F22" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G22" s="77" t="inlineStr">
+      <c r="G22" s="85" t="inlineStr">
         <is>
           <t>Annual FIP refresh.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="75" t="inlineStr">
+      <c r="A23" s="83" t="inlineStr">
         <is>
           <t>Sports fandom by country</t>
         </is>
       </c>
-      <c r="B23" s="79" t="inlineStr">
+      <c r="B23" s="87" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C23" s="82" t="inlineStr">
+      <c r="C23" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D23" s="77" t="inlineStr">
+      <c r="D23" s="85" t="inlineStr">
         <is>
           <t>The weakest layer of the sport index, and it drives both the `demand` and `appetite` signals. Commercial audience panels (Nielsen Sports, YouGov) cost more than the entire Y1-Y2 analytics budget.</t>
         </is>
       </c>
-      <c r="E23" s="77" t="inlineStr">
+      <c r="E23" s="85" t="inlineStr">
         <is>
           <t>None — reasoned estimates only</t>
         </is>
       </c>
-      <c r="F23" s="83" t="inlineStr">
+      <c r="F23" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G23" s="77" t="inlineStr">
+      <c r="G23" s="85" t="inlineStr">
         <is>
           <t>Our own engagement data per sport per country once connectors are live. This is what makes the index self-improving rather than something anyone could copy.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="75" t="inlineStr">
+      <c r="A24" s="83" t="inlineStr">
         <is>
           <t>Athlete count trajectory</t>
         </is>
@@ -5139,27 +8791,27 @@
         <f>Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="C24" s="82" t="inlineStr">
+      <c r="C24" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D24" s="77" t="inlineStr">
+      <c r="D24" s="85" t="inlineStr">
         <is>
           <t>400 rising to 40,000 over ten years. This is the PLAN, not a benchmark: marketing spend is derived from it at segment CAC, not the other way round. Everything in the model scales off this line.</t>
         </is>
       </c>
-      <c r="E24" s="77" t="inlineStr">
+      <c r="E24" s="85" t="inlineStr">
         <is>
           <t>None — it is a target</t>
         </is>
       </c>
-      <c r="F24" s="83" t="inlineStr">
+      <c r="F24" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G24" s="77" t="inlineStr">
+      <c r="G24" s="85" t="inlineStr">
         <is>
           <t>The pre-seed gate tests it directly: 400 athletes and EUR 10k MRR.</t>
         </is>
@@ -5179,7 +8831,7 @@
       <c r="G25" s="12" t="n"/>
     </row>
     <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="75" t="inlineStr">
+      <c r="A26" s="83" t="inlineStr">
         <is>
           <t>Athlete CAC</t>
         </is>
@@ -5188,34 +8840,34 @@
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="C26" s="82" t="inlineStr">
+      <c r="C26" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D26" s="77" t="inlineStr">
+      <c r="D26" s="85" t="inlineStr">
         <is>
           <t>EUR 16-36 for niche, EUR 40-88 for popular. The gap reflects displacing an existing agent relationship versus reaching someone with no representation at all. No published comparable exists for athlete acquisition in this segment.</t>
         </is>
       </c>
-      <c r="E26" s="77" t="inlineStr">
+      <c r="E26" s="85" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="F26" s="83" t="inlineStr">
+      <c r="F26" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G26" s="77" t="inlineStr">
+      <c r="G26" s="85" t="inlineStr">
         <is>
           <t>Measured CAC by channel from the first federation partnership.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="75" t="inlineStr">
+      <c r="A27" s="83" t="inlineStr">
         <is>
           <t>Admission rate, direct applicants</t>
         </is>
@@ -5224,34 +8876,34 @@
         <f>Assumptions!$C$76</f>
         <v/>
       </c>
-      <c r="C27" s="84" t="inlineStr">
+      <c r="C27" s="92" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D27" s="77" t="inlineStr">
+      <c r="D27" s="85" t="inlineStr">
         <is>
           <t>20% of direct applicants are admitted, 25% go to a human, 40% are refused and 15% never finish the form. Not a judgement: it is the ops-load output of scripts/admission_stress.py run over the admission policy itself, so retuning a threshold moves this figure. The sweep asserts the model and the policy stay in step and fails if they drift.</t>
         </is>
       </c>
-      <c r="E27" s="77" t="inlineStr">
+      <c r="E27" s="85" t="inlineStr">
         <is>
           <t>scripts/admission_stress.py, section 7 — over a modelled applicant mix</t>
         </is>
       </c>
-      <c r="F27" s="80" t="inlineStr">
+      <c r="F27" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G27" s="77" t="inlineStr">
+      <c r="G27" s="85" t="inlineStr">
         <is>
           <t>Real intake data. The mix the sweep assumes is the soft part, not the arithmetic.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="75" t="inlineStr">
+      <c r="A28" s="83" t="inlineStr">
         <is>
           <t>Admission rate, club-nominated</t>
         </is>
@@ -5260,34 +8912,34 @@
         <f>Assumptions!$C$78</f>
         <v/>
       </c>
-      <c r="C28" s="82" t="inlineStr">
+      <c r="C28" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D28" s="77" t="inlineStr">
+      <c r="D28" s="85" t="inlineStr">
         <is>
           <t>45% admitted against 20% direct. A verified club's nomination confers a credibility floor of 0.75 x its own legitimacy score, which carries a completed application over the admit line that would otherwise have gone to review. It cannot carry an empty one — no club can supply someone else's date of birth — so the uplift is real but bounded.</t>
         </is>
       </c>
-      <c r="E28" s="77" t="inlineStr">
+      <c r="E28" s="85" t="inlineStr">
         <is>
           <t>None — the mechanism is built and tested, the conversion is not yet measured</t>
         </is>
       </c>
-      <c r="F28" s="83" t="inlineStr">
+      <c r="F28" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G28" s="77" t="inlineStr">
+      <c r="G28" s="85" t="inlineStr">
         <is>
           <t>The first federation partnership: nominated applicants are tagged, so this is measurable from day one of it.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="75" t="inlineStr">
+      <c r="A29" s="83" t="inlineStr">
         <is>
           <t>Athlete verification cost</t>
         </is>
@@ -5296,34 +8948,34 @@
         <f>Assumptions!$C$81</f>
         <v/>
       </c>
-      <c r="C29" s="84" t="inlineStr">
+      <c r="C29" s="92" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D29" s="77" t="inlineStr">
+      <c r="D29" s="85" t="inlineStr">
         <is>
           <t>Four minutes per manual review, priced at the same loaded salary the People line uses, over 1,700 productive hours. Peaks at EUR 47k and 0.64 reviewer-FTE in Y10, which is the finding rather than the cost: verification is not a money problem at this scale. The reason to automate it is latency — an athlete sitting in the queue is not listed, not matchable and not earning.</t>
         </is>
       </c>
-      <c r="E29" s="77" t="inlineStr">
+      <c r="E29" s="85" t="inlineStr">
         <is>
           <t>Derived from the sweep's review volume and the model's own salary line</t>
         </is>
       </c>
-      <c r="F29" s="80" t="inlineStr">
+      <c r="F29" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G29" s="77" t="inlineStr">
+      <c r="G29" s="85" t="inlineStr">
         <is>
           <t>Timing real reviews. Four minutes is an estimate of a mechanical task.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="75" t="inlineStr">
+      <c r="A30" s="83" t="inlineStr">
         <is>
           <t>Athlete CAC vs the funnel</t>
         </is>
@@ -5332,34 +8984,34 @@
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="C30" s="82" t="inlineStr">
+      <c r="C30" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D30" s="77" t="inlineStr">
+      <c r="D30" s="85" t="inlineStr">
         <is>
           <t>Deliberately NOT multiplied by the admission funnel. Segment CAC is defined as the cost of landing one athlete ON the platform, so scaling it by 1/admission-rate would charge the same money twice. The Costs sheet carries a memo line showing what that CAC works out to per application (EUR 3.40 in Y1 rising to EUR 22) — the figure to hold against what a channel actually charges per name reached.</t>
         </is>
       </c>
-      <c r="E30" s="77" t="inlineStr">
+      <c r="E30" s="85" t="inlineStr">
         <is>
           <t>None — this is a definitional choice, made explicit so it is not silently reversed</t>
         </is>
       </c>
-      <c r="F30" s="83" t="inlineStr">
+      <c r="F30" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G30" s="77" t="inlineStr">
+      <c r="G30" s="85" t="inlineStr">
         <is>
           <t>Channel-level spend against applications, which the funnel now records.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="75" t="inlineStr">
+      <c r="A31" s="83" t="inlineStr">
         <is>
           <t>Loaded salary, Spain</t>
         </is>
@@ -5368,34 +9020,34 @@
         <f>Assumptions!$C$61</f>
         <v/>
       </c>
-      <c r="C31" s="76" t="inlineStr">
+      <c r="C31" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D31" s="77" t="inlineStr">
+      <c r="D31" s="85" t="inlineStr">
         <is>
           <t>EUR 38k-76k loaded. Spanish employer social security adds roughly 31% on top of gross, so a senior engineer at ~EUR 55k gross costs ~EUR 72k — around half the London equivalent, which is a real argument for being in Spain rather than an accident of geography.</t>
         </is>
       </c>
-      <c r="E31" s="77" t="inlineStr">
+      <c r="E31" s="85" t="inlineStr">
         <is>
           <t>Spanish Seguridad Social employer contribution rates</t>
         </is>
       </c>
-      <c r="F31" s="80" t="inlineStr">
+      <c r="F31" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G31" s="77" t="inlineStr">
+      <c r="G31" s="85" t="inlineStr">
         <is>
           <t>Actual offers accepted.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="75" t="inlineStr">
+      <c r="A32" s="83" t="inlineStr">
         <is>
           <t>AWS infrastructure</t>
         </is>
@@ -5404,34 +9056,34 @@
         <f>Assumptions!$C$52</f>
         <v/>
       </c>
-      <c r="C32" s="76" t="inlineStr">
+      <c r="C32" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D32" s="77" t="inlineStr">
+      <c r="D32" s="85" t="inlineStr">
         <is>
           <t>Built up per stage from list prices: Fargate, RDS then Aurora, ElastiCache, S3, MediaConvert, CloudWatch. Reserved capacity and Savings Plans (25-40%) are deliberately excluded and treated as upside.</t>
         </is>
       </c>
-      <c r="E32" s="77" t="inlineStr">
+      <c r="E32" s="85" t="inlineStr">
         <is>
           <t>AWS published list pricing, 2026</t>
         </is>
       </c>
-      <c r="F32" s="80" t="inlineStr">
+      <c r="F32" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G32" s="77" t="inlineStr">
+      <c r="G32" s="85" t="inlineStr">
         <is>
           <t>Actual bills; commit to Savings Plans once usage is stable.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="75" t="inlineStr">
+      <c r="A33" s="83" t="inlineStr">
         <is>
           <t>Media egress</t>
         </is>
@@ -5440,34 +9092,34 @@
         <f>Assumptions!$C$54</f>
         <v/>
       </c>
-      <c r="C33" s="81" t="inlineStr">
+      <c r="C33" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D33" s="77" t="inlineStr">
+      <c r="D33" s="85" t="inlineStr">
         <is>
           <t>EUR 0.008/GB behind a zero-egress object store versus EUR 0.075/GB at CloudFront list price. At Y10 volumes that single architectural choice is worth over EUR 1M a year — the largest cost decision in the plan that is settled by engineering rather than negotiation.</t>
         </is>
       </c>
-      <c r="E33" s="77" t="inlineStr">
+      <c r="E33" s="85" t="inlineStr">
         <is>
           <t>Cloudflare R2 and Backblaze B2 pricing; AWS CloudFront list price</t>
         </is>
       </c>
-      <c r="F33" s="78" t="inlineStr">
+      <c r="F33" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G33" s="77" t="inlineStr">
+      <c r="G33" s="85" t="inlineStr">
         <is>
           <t>Nothing. Both are published.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="75" t="inlineStr">
+      <c r="A34" s="83" t="inlineStr">
         <is>
           <t>Moderation cost</t>
         </is>
@@ -5476,27 +9128,27 @@
         <f>Assumptions!$C$56</f>
         <v/>
       </c>
-      <c r="C34" s="82" t="inlineStr">
+      <c r="C34" s="90" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D34" s="77" t="inlineStr">
+      <c r="D34" s="85" t="inlineStr">
         <is>
           <t>EUR 22 per 1,000 items reviewed, on a hybrid of automated classification and human review. Vendor pricing varies widely with SLA and content type.</t>
         </is>
       </c>
-      <c r="E34" s="77" t="inlineStr">
+      <c r="E34" s="85" t="inlineStr">
         <is>
           <t>None cited</t>
         </is>
       </c>
-      <c r="F34" s="83" t="inlineStr">
+      <c r="F34" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G34" s="77" t="inlineStr">
+      <c r="G34" s="85" t="inlineStr">
         <is>
           <t>Vendor quotes once P2 scope is fixed.</t>
         </is>
@@ -5516,7 +9168,7 @@
       <c r="G35" s="12" t="n"/>
     </row>
     <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="75" t="inlineStr">
+      <c r="A36" s="83" t="inlineStr">
         <is>
           <t>Corporate tax rates</t>
         </is>
@@ -5525,34 +9177,34 @@
         <f>Assumptions!$C$71</f>
         <v/>
       </c>
-      <c r="C36" s="81" t="inlineStr">
+      <c r="C36" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D36" s="77" t="inlineStr">
+      <c r="D36" s="85" t="inlineStr">
         <is>
           <t>15% for the first four profitable years under the Spanish Startup Law, then the 25% standard rate. Modelled with loss carryforward against the Y1-Y4 losses.</t>
         </is>
       </c>
-      <c r="E36" s="77" t="inlineStr">
+      <c r="E36" s="85" t="inlineStr">
         <is>
           <t>Ley de Startups (Spain); Impuesto sobre Sociedades</t>
         </is>
       </c>
-      <c r="F36" s="78" t="inlineStr">
+      <c r="F36" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G36" s="77" t="inlineStr">
+      <c r="G36" s="85" t="inlineStr">
         <is>
           <t>Confirm eligibility with a Spanish tax adviser before filing.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="75" t="inlineStr">
+      <c r="A37" s="83" t="inlineStr">
         <is>
           <t>Risk-free rate</t>
         </is>
@@ -5561,34 +9213,34 @@
         <f>Assumptions!$C$88</f>
         <v/>
       </c>
-      <c r="C37" s="81" t="inlineStr">
+      <c r="C37" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D37" s="77" t="inlineStr">
+      <c r="D37" s="85" t="inlineStr">
         <is>
           <t>Spanish 10-year sovereign yield, ~3.2% in mid-2026. Used as the floor for the founder opportunity-cost calculation rather than as the discount rate.</t>
         </is>
       </c>
-      <c r="E37" s="77" t="inlineStr">
+      <c r="E37" s="85" t="inlineStr">
         <is>
           <t>Spanish 10Y government bond yield</t>
         </is>
       </c>
-      <c r="F37" s="78" t="inlineStr">
+      <c r="F37" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G37" s="77" t="inlineStr">
+      <c r="G37" s="85" t="inlineStr">
         <is>
           <t>Refresh at the date of any raise.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
-      <c r="A38" s="75" t="inlineStr">
+      <c r="A38" s="83" t="inlineStr">
         <is>
           <t>WACC / discount rate</t>
         </is>
@@ -5597,34 +9249,34 @@
         <f>Assumptions!$C$85</f>
         <v/>
       </c>
-      <c r="C38" s="76" t="inlineStr">
+      <c r="C38" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D38" s="77" t="inlineStr">
+      <c r="D38" s="85" t="inlineStr">
         <is>
           <t>25%. The conventional range for pre-revenue to early-revenue venture is 20-35% and we sit mid-range. The sensitivity grid runs 18-30% precisely because this is arguable rather than knowable.</t>
         </is>
       </c>
-      <c r="E38" s="77" t="inlineStr">
+      <c r="E38" s="85" t="inlineStr">
         <is>
           <t>Standard venture valuation practice</t>
         </is>
       </c>
-      <c r="F38" s="80" t="inlineStr">
+      <c r="F38" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G38" s="77" t="inlineStr">
+      <c r="G38" s="85" t="inlineStr">
         <is>
           <t>An actual term sheet prices this for you.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="75" t="inlineStr">
+      <c r="A39" s="83" t="inlineStr">
         <is>
           <t>Exit revenue multiple</t>
         </is>
@@ -5633,34 +9285,34 @@
         <f>Assumptions!$C$87</f>
         <v/>
       </c>
-      <c r="C39" s="76" t="inlineStr">
+      <c r="C39" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D39" s="77" t="inlineStr">
+      <c r="D39" s="85" t="inlineStr">
         <is>
           <t>6.5x blended. Marketplace comparables trade around 4x revenue and high-growth SaaS around 9x; our Y10 mix is roughly 55% marketplace take and 12% SaaS.</t>
         </is>
       </c>
-      <c r="E39" s="77" t="inlineStr">
+      <c r="E39" s="85" t="inlineStr">
         <is>
           <t>Public marketplace and SaaS trading multiples</t>
         </is>
       </c>
-      <c r="F39" s="80" t="inlineStr">
+      <c r="F39" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G39" s="77" t="inlineStr">
+      <c r="G39" s="85" t="inlineStr">
         <is>
           <t>Comparable private transactions nearer an exit.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="75" t="inlineStr">
+      <c r="A40" s="83" t="inlineStr">
         <is>
           <t>Terminal growth</t>
         </is>
@@ -5669,27 +9321,27 @@
         <f>Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="C40" s="76" t="inlineStr">
+      <c r="C40" s="84" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D40" s="77" t="inlineStr">
+      <c r="D40" s="85" t="inlineStr">
         <is>
           <t>3%, approximating long-run nominal GDP. Ten explicit forecast years were chosen partly so this assumption carries less of the valuation than it would at Y7.</t>
         </is>
       </c>
-      <c r="E40" s="77" t="inlineStr">
+      <c r="E40" s="85" t="inlineStr">
         <is>
           <t>Standard DCF convention</t>
         </is>
       </c>
-      <c r="F40" s="80" t="inlineStr">
+      <c r="F40" s="88" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G40" s="77" t="inlineStr">
+      <c r="G40" s="85" t="inlineStr">
         <is>
           <t>Nothing — it is a convention, and the grid shows its effect.</t>
         </is>
@@ -5709,112 +9361,112 @@
       <c r="G41" s="12" t="n"/>
     </row>
     <row r="42" ht="58" customHeight="1">
-      <c r="A42" s="75" t="inlineStr">
+      <c r="A42" s="83" t="inlineStr">
         <is>
           <t>Payout age floor</t>
         </is>
       </c>
-      <c r="B42" s="79" t="inlineStr">
+      <c r="B42" s="87" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C42" s="81" t="inlineStr">
+      <c r="C42" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D42" s="77" t="inlineStr">
+      <c r="D42" s="85" t="inlineStr">
         <is>
           <t>Stripe Express and Custom Connect require 18. Standard Connect allows 13+, but a legal guardian must own the account and hold the bank account the money lands in.</t>
         </is>
       </c>
-      <c r="E42" s="77" t="inlineStr">
+      <c r="E42" s="85" t="inlineStr">
         <is>
           <t>Stripe Connect documentation</t>
         </is>
       </c>
-      <c r="F42" s="78" t="inlineStr">
+      <c r="F42" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G42" s="77" t="inlineStr">
+      <c r="G42" s="85" t="inlineStr">
         <is>
           <t>Nothing — it is a hard platform rule.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
-      <c r="A43" s="75" t="inlineStr">
+      <c r="A43" s="83" t="inlineStr">
         <is>
           <t>Digital consent age, Spain</t>
         </is>
       </c>
-      <c r="B43" s="79" t="inlineStr">
+      <c r="B43" s="87" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C43" s="81" t="inlineStr">
+      <c r="C43" s="89" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D43" s="77" t="inlineStr">
+      <c r="D43" s="85" t="inlineStr">
         <is>
           <t>14 today under LOPDGDD Art. 7. A draft Organic Law on the Protection of Minors in Digital Environments would raise it to 16 and make age verification mandatory — which is why 16 is the forward-compatible floor for an account.</t>
         </is>
       </c>
-      <c r="E43" s="77" t="inlineStr">
+      <c r="E43" s="85" t="inlineStr">
         <is>
           <t>LOPDGDD Art. 7; draft Organic Law, Council of Ministers, March 2025</t>
         </is>
       </c>
-      <c r="F43" s="78" t="inlineStr">
+      <c r="F43" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G43" s="77" t="inlineStr">
+      <c r="G43" s="85" t="inlineStr">
         <is>
           <t>Track the bill through Parliament.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="85" t="inlineStr">
+      <c r="A45" s="93" t="inlineStr">
         <is>
           <t>THE THREE ASSUMPTIONS MOST LIKELY TO BE WRONG</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="86" t="inlineStr">
+      <c r="A46" s="94" t="inlineStr">
         <is>
           <t>1. Fan churn. We assume 6-13%/month; Patreon reports 10-15%. If Patreon is right, Y10 revenue falls from about EUR 58M to EUR 51M and the capital requirement roughly doubles.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="86" t="inlineStr">
+      <c r="A47" s="94" t="inlineStr">
         <is>
           <t>2. Athlete count. The trajectory is a target, not a forecast, and everything scales off it.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="86" t="inlineStr">
+      <c r="A48" s="94" t="inlineStr">
         <is>
           <t>3. Share of athletes who monetise. No published comparable exists at all.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="87" t="inlineStr"/>
+      <c r="A49" s="95" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="87" t="inlineStr">
+      <c r="A50" s="95" t="inlineStr">
         <is>
           <t>All three are answered by the same thing: three months of real cohort data from P1.</t>
         </is>
@@ -5832,7 +9484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5863,7 +9515,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="55" t="inlineStr">
+      <c r="A2" s="64" t="inlineStr">
         <is>
           <t>Each pair is the Python model's figure and the workbook's own calculation. VARIANCE must be zero — if a formula is wrong, it shows up here on open.</t>
         </is>
@@ -6084,43 +9736,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C7" s="88">
+      <c r="C7" s="96">
         <f>ROUND(C6-C5,0)</f>
         <v/>
       </c>
-      <c r="D7" s="88">
+      <c r="D7" s="96">
         <f>ROUND(D6-D5,0)</f>
         <v/>
       </c>
-      <c r="E7" s="88">
+      <c r="E7" s="96">
         <f>ROUND(E6-E5,0)</f>
         <v/>
       </c>
-      <c r="F7" s="88">
+      <c r="F7" s="96">
         <f>ROUND(F6-F5,0)</f>
         <v/>
       </c>
-      <c r="G7" s="88">
+      <c r="G7" s="96">
         <f>ROUND(G6-G5,0)</f>
         <v/>
       </c>
-      <c r="H7" s="88">
+      <c r="H7" s="96">
         <f>ROUND(H6-H5,0)</f>
         <v/>
       </c>
-      <c r="I7" s="88">
+      <c r="I7" s="96">
         <f>ROUND(I6-I5,0)</f>
         <v/>
       </c>
-      <c r="J7" s="88">
+      <c r="J7" s="96">
         <f>ROUND(J6-J5,0)</f>
         <v/>
       </c>
-      <c r="K7" s="88">
+      <c r="K7" s="96">
         <f>ROUND(K6-K5,0)</f>
         <v/>
       </c>
-      <c r="L7" s="88">
+      <c r="L7" s="96">
         <f>ROUND(L6-L5,0)</f>
         <v/>
       </c>
@@ -6248,43 +9900,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C12" s="88">
+      <c r="C12" s="96">
         <f>ROUND(C11-C10,0)</f>
         <v/>
       </c>
-      <c r="D12" s="88">
+      <c r="D12" s="96">
         <f>ROUND(D11-D10,0)</f>
         <v/>
       </c>
-      <c r="E12" s="88">
+      <c r="E12" s="96">
         <f>ROUND(E11-E10,0)</f>
         <v/>
       </c>
-      <c r="F12" s="88">
+      <c r="F12" s="96">
         <f>ROUND(F11-F10,0)</f>
         <v/>
       </c>
-      <c r="G12" s="88">
+      <c r="G12" s="96">
         <f>ROUND(G11-G10,0)</f>
         <v/>
       </c>
-      <c r="H12" s="88">
+      <c r="H12" s="96">
         <f>ROUND(H11-H10,0)</f>
         <v/>
       </c>
-      <c r="I12" s="88">
+      <c r="I12" s="96">
         <f>ROUND(I11-I10,0)</f>
         <v/>
       </c>
-      <c r="J12" s="88">
+      <c r="J12" s="96">
         <f>ROUND(J11-J10,0)</f>
         <v/>
       </c>
-      <c r="K12" s="88">
+      <c r="K12" s="96">
         <f>ROUND(K11-K10,0)</f>
         <v/>
       </c>
-      <c r="L12" s="88">
+      <c r="L12" s="96">
         <f>ROUND(L11-L10,0)</f>
         <v/>
       </c>
@@ -6412,43 +10064,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C17" s="88">
+      <c r="C17" s="96">
         <f>ROUND(C16-C15,0)</f>
         <v/>
       </c>
-      <c r="D17" s="88">
+      <c r="D17" s="96">
         <f>ROUND(D16-D15,0)</f>
         <v/>
       </c>
-      <c r="E17" s="88">
+      <c r="E17" s="96">
         <f>ROUND(E16-E15,0)</f>
         <v/>
       </c>
-      <c r="F17" s="88">
+      <c r="F17" s="96">
         <f>ROUND(F16-F15,0)</f>
         <v/>
       </c>
-      <c r="G17" s="88">
+      <c r="G17" s="96">
         <f>ROUND(G16-G15,0)</f>
         <v/>
       </c>
-      <c r="H17" s="88">
+      <c r="H17" s="96">
         <f>ROUND(H16-H15,0)</f>
         <v/>
       </c>
-      <c r="I17" s="88">
+      <c r="I17" s="96">
         <f>ROUND(I16-I15,0)</f>
         <v/>
       </c>
-      <c r="J17" s="88">
+      <c r="J17" s="96">
         <f>ROUND(J16-J15,0)</f>
         <v/>
       </c>
-      <c r="K17" s="88">
+      <c r="K17" s="96">
         <f>ROUND(K16-K15,0)</f>
         <v/>
       </c>
-      <c r="L17" s="88">
+      <c r="L17" s="96">
         <f>ROUND(L16-L15,0)</f>
         <v/>
       </c>
@@ -6576,43 +10228,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C22" s="88">
+      <c r="C22" s="96">
         <f>ROUND(C21-C20,0)</f>
         <v/>
       </c>
-      <c r="D22" s="88">
+      <c r="D22" s="96">
         <f>ROUND(D21-D20,0)</f>
         <v/>
       </c>
-      <c r="E22" s="88">
+      <c r="E22" s="96">
         <f>ROUND(E21-E20,0)</f>
         <v/>
       </c>
-      <c r="F22" s="88">
+      <c r="F22" s="96">
         <f>ROUND(F21-F20,0)</f>
         <v/>
       </c>
-      <c r="G22" s="88">
+      <c r="G22" s="96">
         <f>ROUND(G21-G20,0)</f>
         <v/>
       </c>
-      <c r="H22" s="88">
+      <c r="H22" s="96">
         <f>ROUND(H21-H20,0)</f>
         <v/>
       </c>
-      <c r="I22" s="88">
+      <c r="I22" s="96">
         <f>ROUND(I21-I20,0)</f>
         <v/>
       </c>
-      <c r="J22" s="88">
+      <c r="J22" s="96">
         <f>ROUND(J21-J20,0)</f>
         <v/>
       </c>
-      <c r="K22" s="88">
+      <c r="K22" s="96">
         <f>ROUND(K21-K20,0)</f>
         <v/>
       </c>
-      <c r="L22" s="88">
+      <c r="L22" s="96">
         <f>ROUND(L21-L20,0)</f>
         <v/>
       </c>
@@ -6740,43 +10392,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C27" s="88">
+      <c r="C27" s="96">
         <f>ROUND(C26-C25,0)</f>
         <v/>
       </c>
-      <c r="D27" s="88">
+      <c r="D27" s="96">
         <f>ROUND(D26-D25,0)</f>
         <v/>
       </c>
-      <c r="E27" s="88">
+      <c r="E27" s="96">
         <f>ROUND(E26-E25,0)</f>
         <v/>
       </c>
-      <c r="F27" s="88">
+      <c r="F27" s="96">
         <f>ROUND(F26-F25,0)</f>
         <v/>
       </c>
-      <c r="G27" s="88">
+      <c r="G27" s="96">
         <f>ROUND(G26-G25,0)</f>
         <v/>
       </c>
-      <c r="H27" s="88">
+      <c r="H27" s="96">
         <f>ROUND(H26-H25,0)</f>
         <v/>
       </c>
-      <c r="I27" s="88">
+      <c r="I27" s="96">
         <f>ROUND(I26-I25,0)</f>
         <v/>
       </c>
-      <c r="J27" s="88">
+      <c r="J27" s="96">
         <f>ROUND(J26-J25,0)</f>
         <v/>
       </c>
-      <c r="K27" s="88">
+      <c r="K27" s="96">
         <f>ROUND(K26-K25,0)</f>
         <v/>
       </c>
-      <c r="L27" s="88">
+      <c r="L27" s="96">
         <f>ROUND(L26-L25,0)</f>
         <v/>
       </c>
@@ -6904,43 +10556,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C32" s="89">
+      <c r="C32" s="97">
         <f>ROUND(C31-C30,0)</f>
         <v/>
       </c>
-      <c r="D32" s="89">
+      <c r="D32" s="97">
         <f>ROUND(D31-D30,0)</f>
         <v/>
       </c>
-      <c r="E32" s="89">
+      <c r="E32" s="97">
         <f>ROUND(E31-E30,0)</f>
         <v/>
       </c>
-      <c r="F32" s="89">
+      <c r="F32" s="97">
         <f>ROUND(F31-F30,0)</f>
         <v/>
       </c>
-      <c r="G32" s="89">
+      <c r="G32" s="97">
         <f>ROUND(G31-G30,0)</f>
         <v/>
       </c>
-      <c r="H32" s="89">
+      <c r="H32" s="97">
         <f>ROUND(H31-H30,0)</f>
         <v/>
       </c>
-      <c r="I32" s="89">
+      <c r="I32" s="97">
         <f>ROUND(I31-I30,0)</f>
         <v/>
       </c>
-      <c r="J32" s="89">
+      <c r="J32" s="97">
         <f>ROUND(J31-J30,0)</f>
         <v/>
       </c>
-      <c r="K32" s="89">
+      <c r="K32" s="97">
         <f>ROUND(K31-K30,0)</f>
         <v/>
       </c>
-      <c r="L32" s="89">
+      <c r="L32" s="97">
         <f>ROUND(L31-L30,0)</f>
         <v/>
       </c>
@@ -7068,43 +10720,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C37" s="89">
+      <c r="C37" s="97">
         <f>ROUND(C36-C35,0)</f>
         <v/>
       </c>
-      <c r="D37" s="89">
+      <c r="D37" s="97">
         <f>ROUND(D36-D35,0)</f>
         <v/>
       </c>
-      <c r="E37" s="89">
+      <c r="E37" s="97">
         <f>ROUND(E36-E35,0)</f>
         <v/>
       </c>
-      <c r="F37" s="89">
+      <c r="F37" s="97">
         <f>ROUND(F36-F35,0)</f>
         <v/>
       </c>
-      <c r="G37" s="89">
+      <c r="G37" s="97">
         <f>ROUND(G36-G35,0)</f>
         <v/>
       </c>
-      <c r="H37" s="89">
+      <c r="H37" s="97">
         <f>ROUND(H36-H35,0)</f>
         <v/>
       </c>
-      <c r="I37" s="89">
+      <c r="I37" s="97">
         <f>ROUND(I36-I35,0)</f>
         <v/>
       </c>
-      <c r="J37" s="89">
+      <c r="J37" s="97">
         <f>ROUND(J36-J35,0)</f>
         <v/>
       </c>
-      <c r="K37" s="89">
+      <c r="K37" s="97">
         <f>ROUND(K36-K35,0)</f>
         <v/>
       </c>
-      <c r="L37" s="89">
+      <c r="L37" s="97">
         <f>ROUND(L36-L35,0)</f>
         <v/>
       </c>
@@ -7232,43 +10884,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C42" s="88">
+      <c r="C42" s="96">
         <f>ROUND(C41-C40,0)</f>
         <v/>
       </c>
-      <c r="D42" s="88">
+      <c r="D42" s="96">
         <f>ROUND(D41-D40,0)</f>
         <v/>
       </c>
-      <c r="E42" s="88">
+      <c r="E42" s="96">
         <f>ROUND(E41-E40,0)</f>
         <v/>
       </c>
-      <c r="F42" s="88">
+      <c r="F42" s="96">
         <f>ROUND(F41-F40,0)</f>
         <v/>
       </c>
-      <c r="G42" s="88">
+      <c r="G42" s="96">
         <f>ROUND(G41-G40,0)</f>
         <v/>
       </c>
-      <c r="H42" s="88">
+      <c r="H42" s="96">
         <f>ROUND(H41-H40,0)</f>
         <v/>
       </c>
-      <c r="I42" s="88">
+      <c r="I42" s="96">
         <f>ROUND(I41-I40,0)</f>
         <v/>
       </c>
-      <c r="J42" s="88">
+      <c r="J42" s="96">
         <f>ROUND(J41-J40,0)</f>
         <v/>
       </c>
-      <c r="K42" s="88">
+      <c r="K42" s="96">
         <f>ROUND(K41-K40,0)</f>
         <v/>
       </c>
-      <c r="L42" s="88">
+      <c r="L42" s="96">
         <f>ROUND(L41-L40,0)</f>
         <v/>
       </c>
@@ -7396,43 +11048,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C47" s="89">
+      <c r="C47" s="97">
         <f>ROUND(C46-C45,0)</f>
         <v/>
       </c>
-      <c r="D47" s="89">
+      <c r="D47" s="97">
         <f>ROUND(D46-D45,0)</f>
         <v/>
       </c>
-      <c r="E47" s="89">
+      <c r="E47" s="97">
         <f>ROUND(E46-E45,0)</f>
         <v/>
       </c>
-      <c r="F47" s="89">
+      <c r="F47" s="97">
         <f>ROUND(F46-F45,0)</f>
         <v/>
       </c>
-      <c r="G47" s="89">
+      <c r="G47" s="97">
         <f>ROUND(G46-G45,0)</f>
         <v/>
       </c>
-      <c r="H47" s="89">
+      <c r="H47" s="97">
         <f>ROUND(H46-H45,0)</f>
         <v/>
       </c>
-      <c r="I47" s="89">
+      <c r="I47" s="97">
         <f>ROUND(I46-I45,0)</f>
         <v/>
       </c>
-      <c r="J47" s="89">
+      <c r="J47" s="97">
         <f>ROUND(J46-J45,0)</f>
         <v/>
       </c>
-      <c r="K47" s="89">
+      <c r="K47" s="97">
         <f>ROUND(K46-K45,0)</f>
         <v/>
       </c>
-      <c r="L47" s="89">
+      <c r="L47" s="97">
         <f>ROUND(L46-L45,0)</f>
         <v/>
       </c>
@@ -7560,43 +11212,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C52" s="89">
+      <c r="C52" s="97">
         <f>ROUND(C51-C50,0)</f>
         <v/>
       </c>
-      <c r="D52" s="89">
+      <c r="D52" s="97">
         <f>ROUND(D51-D50,0)</f>
         <v/>
       </c>
-      <c r="E52" s="89">
+      <c r="E52" s="97">
         <f>ROUND(E51-E50,0)</f>
         <v/>
       </c>
-      <c r="F52" s="89">
+      <c r="F52" s="97">
         <f>ROUND(F51-F50,0)</f>
         <v/>
       </c>
-      <c r="G52" s="89">
+      <c r="G52" s="97">
         <f>ROUND(G51-G50,0)</f>
         <v/>
       </c>
-      <c r="H52" s="89">
+      <c r="H52" s="97">
         <f>ROUND(H51-H50,0)</f>
         <v/>
       </c>
-      <c r="I52" s="89">
+      <c r="I52" s="97">
         <f>ROUND(I51-I50,0)</f>
         <v/>
       </c>
-      <c r="J52" s="89">
+      <c r="J52" s="97">
         <f>ROUND(J51-J50,0)</f>
         <v/>
       </c>
-      <c r="K52" s="89">
+      <c r="K52" s="97">
         <f>ROUND(K51-K50,0)</f>
         <v/>
       </c>
-      <c r="L52" s="89">
+      <c r="L52" s="97">
         <f>ROUND(L51-L50,0)</f>
         <v/>
       </c>
@@ -7724,43 +11376,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C57" s="88">
+      <c r="C57" s="96">
         <f>ROUND(C56-C55,0)</f>
         <v/>
       </c>
-      <c r="D57" s="88">
+      <c r="D57" s="96">
         <f>ROUND(D56-D55,0)</f>
         <v/>
       </c>
-      <c r="E57" s="88">
+      <c r="E57" s="96">
         <f>ROUND(E56-E55,0)</f>
         <v/>
       </c>
-      <c r="F57" s="88">
+      <c r="F57" s="96">
         <f>ROUND(F56-F55,0)</f>
         <v/>
       </c>
-      <c r="G57" s="88">
+      <c r="G57" s="96">
         <f>ROUND(G56-G55,0)</f>
         <v/>
       </c>
-      <c r="H57" s="88">
+      <c r="H57" s="96">
         <f>ROUND(H56-H55,0)</f>
         <v/>
       </c>
-      <c r="I57" s="88">
+      <c r="I57" s="96">
         <f>ROUND(I56-I55,0)</f>
         <v/>
       </c>
-      <c r="J57" s="88">
+      <c r="J57" s="96">
         <f>ROUND(J56-J55,0)</f>
         <v/>
       </c>
-      <c r="K57" s="88">
+      <c r="K57" s="96">
         <f>ROUND(K56-K55,0)</f>
         <v/>
       </c>
-      <c r="L57" s="88">
+      <c r="L57" s="96">
         <f>ROUND(L56-L55,0)</f>
         <v/>
       </c>
@@ -7888,43 +11540,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C62" s="88">
+      <c r="C62" s="96">
         <f>ROUND(C61-C60,0)</f>
         <v/>
       </c>
-      <c r="D62" s="88">
+      <c r="D62" s="96">
         <f>ROUND(D61-D60,0)</f>
         <v/>
       </c>
-      <c r="E62" s="88">
+      <c r="E62" s="96">
         <f>ROUND(E61-E60,0)</f>
         <v/>
       </c>
-      <c r="F62" s="88">
+      <c r="F62" s="96">
         <f>ROUND(F61-F60,0)</f>
         <v/>
       </c>
-      <c r="G62" s="88">
+      <c r="G62" s="96">
         <f>ROUND(G61-G60,0)</f>
         <v/>
       </c>
-      <c r="H62" s="88">
+      <c r="H62" s="96">
         <f>ROUND(H61-H60,0)</f>
         <v/>
       </c>
-      <c r="I62" s="88">
+      <c r="I62" s="96">
         <f>ROUND(I61-I60,0)</f>
         <v/>
       </c>
-      <c r="J62" s="88">
+      <c r="J62" s="96">
         <f>ROUND(J61-J60,0)</f>
         <v/>
       </c>
-      <c r="K62" s="88">
+      <c r="K62" s="96">
         <f>ROUND(K61-K60,0)</f>
         <v/>
       </c>
-      <c r="L62" s="88">
+      <c r="L62" s="96">
         <f>ROUND(L61-L60,0)</f>
         <v/>
       </c>
@@ -8052,43 +11704,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C67" s="88">
+      <c r="C67" s="96">
         <f>ROUND(C66-C65,0)</f>
         <v/>
       </c>
-      <c r="D67" s="88">
+      <c r="D67" s="96">
         <f>ROUND(D66-D65,0)</f>
         <v/>
       </c>
-      <c r="E67" s="88">
+      <c r="E67" s="96">
         <f>ROUND(E66-E65,0)</f>
         <v/>
       </c>
-      <c r="F67" s="88">
+      <c r="F67" s="96">
         <f>ROUND(F66-F65,0)</f>
         <v/>
       </c>
-      <c r="G67" s="88">
+      <c r="G67" s="96">
         <f>ROUND(G66-G65,0)</f>
         <v/>
       </c>
-      <c r="H67" s="88">
+      <c r="H67" s="96">
         <f>ROUND(H66-H65,0)</f>
         <v/>
       </c>
-      <c r="I67" s="88">
+      <c r="I67" s="96">
         <f>ROUND(I66-I65,0)</f>
         <v/>
       </c>
-      <c r="J67" s="88">
+      <c r="J67" s="96">
         <f>ROUND(J66-J65,0)</f>
         <v/>
       </c>
-      <c r="K67" s="88">
+      <c r="K67" s="96">
         <f>ROUND(K66-K65,0)</f>
         <v/>
       </c>
-      <c r="L67" s="88">
+      <c r="L67" s="96">
         <f>ROUND(L66-L65,0)</f>
         <v/>
       </c>
@@ -8216,43 +11868,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C72" s="88">
+      <c r="C72" s="96">
         <f>ROUND(C71-C70,0)</f>
         <v/>
       </c>
-      <c r="D72" s="88">
+      <c r="D72" s="96">
         <f>ROUND(D71-D70,0)</f>
         <v/>
       </c>
-      <c r="E72" s="88">
+      <c r="E72" s="96">
         <f>ROUND(E71-E70,0)</f>
         <v/>
       </c>
-      <c r="F72" s="88">
+      <c r="F72" s="96">
         <f>ROUND(F71-F70,0)</f>
         <v/>
       </c>
-      <c r="G72" s="88">
+      <c r="G72" s="96">
         <f>ROUND(G71-G70,0)</f>
         <v/>
       </c>
-      <c r="H72" s="88">
+      <c r="H72" s="96">
         <f>ROUND(H71-H70,0)</f>
         <v/>
       </c>
-      <c r="I72" s="88">
+      <c r="I72" s="96">
         <f>ROUND(I71-I70,0)</f>
         <v/>
       </c>
-      <c r="J72" s="88">
+      <c r="J72" s="96">
         <f>ROUND(J71-J70,0)</f>
         <v/>
       </c>
-      <c r="K72" s="88">
+      <c r="K72" s="96">
         <f>ROUND(K71-K70,0)</f>
         <v/>
       </c>
-      <c r="L72" s="88">
+      <c r="L72" s="96">
         <f>ROUND(L71-L70,0)</f>
         <v/>
       </c>
@@ -8275,43 +11927,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C75" s="90">
+      <c r="C75" s="98">
         <f>BalanceSheet!C20</f>
         <v/>
       </c>
-      <c r="D75" s="90">
+      <c r="D75" s="98">
         <f>BalanceSheet!D20</f>
         <v/>
       </c>
-      <c r="E75" s="90">
+      <c r="E75" s="98">
         <f>BalanceSheet!E20</f>
         <v/>
       </c>
-      <c r="F75" s="90">
+      <c r="F75" s="98">
         <f>BalanceSheet!F20</f>
         <v/>
       </c>
-      <c r="G75" s="90">
+      <c r="G75" s="98">
         <f>BalanceSheet!G20</f>
         <v/>
       </c>
-      <c r="H75" s="90">
+      <c r="H75" s="98">
         <f>BalanceSheet!H20</f>
         <v/>
       </c>
-      <c r="I75" s="90">
+      <c r="I75" s="98">
         <f>BalanceSheet!I20</f>
         <v/>
       </c>
-      <c r="J75" s="90">
+      <c r="J75" s="98">
         <f>BalanceSheet!J20</f>
         <v/>
       </c>
-      <c r="K75" s="90">
+      <c r="K75" s="98">
         <f>BalanceSheet!K20</f>
         <v/>
       </c>
-      <c r="L75" s="90">
+      <c r="L75" s="98">
         <f>BalanceSheet!L20</f>
         <v/>
       </c>
